--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="850" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B96CBE0-23B9-4030-928F-6EFE6EE0E5ED}"/>
+  <xr:revisionPtr revIDLastSave="853" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E9DF501-2FF6-4289-B146-A361D0BE00CF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="-25935" yWindow="5655" windowWidth="21600" windowHeight="11085" firstSheet="2" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -273,7 +273,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -361,10 +361,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -373,11 +373,11 @@
       <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1069,8 +1069,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
-  <dimension ref="A9:I331"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:I331"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
@@ -1084,13 +1084,18 @@
     <col min="12" max="12" width="33.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9">
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
         <v>298</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1119,7 +1124,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -1145,7 +1150,7 @@
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -1171,7 +1176,7 @@
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9">
       <c r="A13" s="1">
         <v>3</v>
       </c>
@@ -1197,7 +1202,7 @@
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9">
       <c r="A14" s="1">
         <v>4</v>
       </c>
@@ -1223,7 +1228,7 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>5</v>
       </c>
@@ -1249,7 +1254,7 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9">
       <c r="A16" s="1">
         <v>6</v>
       </c>
@@ -1275,7 +1280,7 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9">
       <c r="A17" s="1">
         <v>7</v>
       </c>
@@ -1301,7 +1306,7 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9">
       <c r="A18" s="1">
         <v>8</v>
       </c>
@@ -1327,7 +1332,7 @@
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9">
       <c r="A19" s="1">
         <v>9</v>
       </c>
@@ -1353,7 +1358,7 @@
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9">
       <c r="A20" s="1">
         <v>10</v>
       </c>
@@ -1379,7 +1384,7 @@
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9">
       <c r="A21" s="1">
         <v>11</v>
       </c>
@@ -1405,7 +1410,7 @@
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9">
       <c r="A22" s="1">
         <v>12</v>
       </c>
@@ -1431,7 +1436,7 @@
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9">
       <c r="A23" s="1">
         <v>13</v>
       </c>
@@ -1457,7 +1462,7 @@
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9">
       <c r="A24" s="1">
         <v>14</v>
       </c>
@@ -1483,7 +1488,7 @@
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9">
       <c r="A25" s="1">
         <v>15</v>
       </c>
@@ -1509,7 +1514,7 @@
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9">
       <c r="A26" s="1">
         <v>16</v>
       </c>
@@ -1535,7 +1540,7 @@
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9">
       <c r="A27" s="1">
         <v>17</v>
       </c>
@@ -1561,7 +1566,7 @@
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9">
       <c r="A28" s="1">
         <v>18</v>
       </c>
@@ -1587,7 +1592,7 @@
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9">
       <c r="A29" s="1">
         <v>19</v>
       </c>
@@ -1613,7 +1618,7 @@
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9">
       <c r="A30" s="1">
         <v>20</v>
       </c>
@@ -1639,7 +1644,7 @@
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9">
       <c r="A31" s="1">
         <v>21</v>
       </c>
@@ -1665,7 +1670,7 @@
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9">
       <c r="A32" s="1">
         <v>22</v>
       </c>
@@ -1691,7 +1696,7 @@
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9">
       <c r="A33" s="1">
         <v>23</v>
       </c>
@@ -1717,7 +1722,7 @@
       <c r="H33" s="11"/>
       <c r="I33" s="11"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9">
       <c r="A34" s="1">
         <v>24</v>
       </c>
@@ -1743,7 +1748,7 @@
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9">
       <c r="A35" s="1">
         <v>25</v>
       </c>
@@ -1769,7 +1774,7 @@
       <c r="H35" s="11"/>
       <c r="I35" s="11"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9">
       <c r="A36" s="1">
         <v>26</v>
       </c>
@@ -1795,7 +1800,7 @@
       <c r="H36" s="11"/>
       <c r="I36" s="11"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9">
       <c r="A37" s="1">
         <v>27</v>
       </c>
@@ -1821,7 +1826,7 @@
       <c r="H37" s="11"/>
       <c r="I37" s="11"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9">
       <c r="A38" s="1">
         <v>28</v>
       </c>
@@ -1847,7 +1852,7 @@
       <c r="H38" s="11"/>
       <c r="I38" s="11"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9">
       <c r="A39" s="1">
         <v>29</v>
       </c>
@@ -1873,7 +1878,7 @@
       <c r="H39" s="11"/>
       <c r="I39" s="11"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9">
       <c r="A40" s="1">
         <v>30</v>
       </c>
@@ -1899,7 +1904,7 @@
       <c r="H40" s="11"/>
       <c r="I40" s="11"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9">
       <c r="A41" s="1">
         <v>31</v>
       </c>
@@ -1925,7 +1930,7 @@
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9">
       <c r="A42" s="1">
         <v>32</v>
       </c>
@@ -1951,7 +1956,7 @@
       <c r="H42" s="11"/>
       <c r="I42" s="11"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9">
       <c r="A43" s="1">
         <v>33</v>
       </c>
@@ -1977,7 +1982,7 @@
       <c r="H43" s="11"/>
       <c r="I43" s="11"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9">
       <c r="A44" s="1">
         <v>34</v>
       </c>
@@ -2003,7 +2008,7 @@
       <c r="H44" s="11"/>
       <c r="I44" s="11"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9">
       <c r="A45" s="1">
         <v>35</v>
       </c>
@@ -2029,7 +2034,7 @@
       <c r="H45" s="11"/>
       <c r="I45" s="11"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9">
       <c r="A46" s="1">
         <v>36</v>
       </c>
@@ -2055,7 +2060,7 @@
       <c r="H46" s="11"/>
       <c r="I46" s="11"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9">
       <c r="A47" s="1">
         <v>37</v>
       </c>
@@ -2081,7 +2086,7 @@
       <c r="H47" s="11"/>
       <c r="I47" s="11"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9">
       <c r="A48" s="1">
         <v>38</v>
       </c>
@@ -2107,7 +2112,7 @@
       <c r="H48" s="11"/>
       <c r="I48" s="11"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9">
       <c r="A49" s="1">
         <v>39</v>
       </c>
@@ -2133,7 +2138,7 @@
       <c r="H49" s="11"/>
       <c r="I49" s="11"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9">
       <c r="A50" s="1">
         <v>40</v>
       </c>
@@ -2159,7 +2164,7 @@
       <c r="H50" s="11"/>
       <c r="I50" s="11"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9">
       <c r="A51" s="1">
         <v>41</v>
       </c>
@@ -2185,7 +2190,7 @@
       <c r="H51" s="11"/>
       <c r="I51" s="11"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9">
       <c r="A52" s="1">
         <v>42</v>
       </c>
@@ -2211,7 +2216,7 @@
       <c r="H52" s="11"/>
       <c r="I52" s="11"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9">
       <c r="A53" s="1">
         <v>43</v>
       </c>
@@ -2237,7 +2242,7 @@
       <c r="H53" s="11"/>
       <c r="I53" s="11"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9">
       <c r="A54" s="1">
         <v>44</v>
       </c>
@@ -2263,7 +2268,7 @@
       <c r="H54" s="11"/>
       <c r="I54" s="11"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9">
       <c r="A55" s="1">
         <v>45</v>
       </c>
@@ -2289,7 +2294,7 @@
       <c r="H55" s="11"/>
       <c r="I55" s="11"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9">
       <c r="A56" s="1">
         <v>46</v>
       </c>
@@ -2315,7 +2320,7 @@
       <c r="H56" s="11"/>
       <c r="I56" s="11"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9">
       <c r="A57" s="1">
         <v>47</v>
       </c>
@@ -2341,7 +2346,7 @@
       <c r="H57" s="11"/>
       <c r="I57" s="11"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9">
       <c r="A58" s="1">
         <v>48</v>
       </c>
@@ -2367,7 +2372,7 @@
       <c r="H58" s="11"/>
       <c r="I58" s="11"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9">
       <c r="A59" s="1">
         <v>49</v>
       </c>
@@ -2393,7 +2398,7 @@
       <c r="H59" s="11"/>
       <c r="I59" s="11"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9">
       <c r="A60" s="1">
         <v>50</v>
       </c>
@@ -2419,7 +2424,7 @@
       <c r="H60" s="11"/>
       <c r="I60" s="11"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9">
       <c r="A61" s="1">
         <v>51</v>
       </c>
@@ -2445,7 +2450,7 @@
       <c r="H61" s="11"/>
       <c r="I61" s="11"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9">
       <c r="A62" s="1">
         <v>52</v>
       </c>
@@ -2471,7 +2476,7 @@
       <c r="H62" s="11"/>
       <c r="I62" s="11"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9">
       <c r="A63" s="1">
         <v>53</v>
       </c>
@@ -2497,7 +2502,7 @@
       <c r="H63" s="11"/>
       <c r="I63" s="11"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9">
       <c r="A64" s="1">
         <v>54</v>
       </c>
@@ -2523,7 +2528,7 @@
       <c r="H64" s="11"/>
       <c r="I64" s="11"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9">
       <c r="A65" s="1">
         <v>55</v>
       </c>
@@ -2549,7 +2554,7 @@
       <c r="H65" s="11"/>
       <c r="I65" s="11"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9">
       <c r="A66" s="1">
         <v>56</v>
       </c>
@@ -2575,7 +2580,7 @@
       <c r="H66" s="11"/>
       <c r="I66" s="11"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9">
       <c r="A67" s="1">
         <v>57</v>
       </c>
@@ -2601,7 +2606,7 @@
       <c r="H67" s="11"/>
       <c r="I67" s="11"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9">
       <c r="A68" s="1">
         <v>58</v>
       </c>
@@ -2627,7 +2632,7 @@
       <c r="H68" s="11"/>
       <c r="I68" s="11"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9">
       <c r="A69" s="1">
         <v>59</v>
       </c>
@@ -2653,7 +2658,7 @@
       <c r="H69" s="11"/>
       <c r="I69" s="11"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9">
       <c r="A70" s="1">
         <v>60</v>
       </c>
@@ -2679,7 +2684,7 @@
       <c r="H70" s="11"/>
       <c r="I70" s="11"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9">
       <c r="A71" s="1">
         <v>61</v>
       </c>
@@ -2705,7 +2710,7 @@
       <c r="H71" s="11"/>
       <c r="I71" s="11"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9">
       <c r="A72" s="1">
         <v>62</v>
       </c>
@@ -2731,7 +2736,7 @@
       <c r="H72" s="11"/>
       <c r="I72" s="11"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9">
       <c r="A73" s="1">
         <v>63</v>
       </c>
@@ -2757,7 +2762,7 @@
       <c r="H73" s="11"/>
       <c r="I73" s="11"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9">
       <c r="A74" s="1">
         <v>64</v>
       </c>
@@ -2783,7 +2788,7 @@
       <c r="H74" s="11"/>
       <c r="I74" s="11"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9">
       <c r="A75" s="1">
         <v>65</v>
       </c>
@@ -2809,7 +2814,7 @@
       <c r="H75" s="11"/>
       <c r="I75" s="11"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9">
       <c r="A76" s="1">
         <v>66</v>
       </c>
@@ -2835,7 +2840,7 @@
       <c r="H76" s="11"/>
       <c r="I76" s="11"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9">
       <c r="A77" s="1">
         <v>67</v>
       </c>
@@ -2861,7 +2866,7 @@
       <c r="H77" s="11"/>
       <c r="I77" s="11"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9">
       <c r="A78" s="1">
         <v>68</v>
       </c>
@@ -2887,7 +2892,7 @@
       <c r="H78" s="11"/>
       <c r="I78" s="11"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9">
       <c r="A79" s="1">
         <v>69</v>
       </c>
@@ -2913,7 +2918,7 @@
       <c r="H79" s="11"/>
       <c r="I79" s="11"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9">
       <c r="A80" s="1">
         <v>70</v>
       </c>
@@ -2939,7 +2944,7 @@
       <c r="H80" s="11"/>
       <c r="I80" s="11"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9">
       <c r="A81" s="1">
         <v>71</v>
       </c>
@@ -2965,7 +2970,7 @@
       <c r="H81" s="11"/>
       <c r="I81" s="11"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9">
       <c r="A82" s="1">
         <v>72</v>
       </c>
@@ -2991,7 +2996,7 @@
       <c r="H82" s="11"/>
       <c r="I82" s="11"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9">
       <c r="A83" s="1">
         <v>73</v>
       </c>
@@ -3017,7 +3022,7 @@
       <c r="H83" s="11"/>
       <c r="I83" s="11"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9">
       <c r="A84" s="1">
         <v>74</v>
       </c>
@@ -3043,7 +3048,7 @@
       <c r="H84" s="11"/>
       <c r="I84" s="11"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9">
       <c r="A85" s="1">
         <v>75</v>
       </c>
@@ -3069,7 +3074,7 @@
       <c r="H85" s="11"/>
       <c r="I85" s="11"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9">
       <c r="A86" s="1">
         <v>76</v>
       </c>
@@ -3095,7 +3100,7 @@
       <c r="H86" s="11"/>
       <c r="I86" s="11"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9">
       <c r="A87" s="1">
         <v>77</v>
       </c>
@@ -3121,7 +3126,7 @@
       <c r="H87" s="11"/>
       <c r="I87" s="11"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9">
       <c r="A88" s="1">
         <v>78</v>
       </c>
@@ -3147,7 +3152,7 @@
       <c r="H88" s="11"/>
       <c r="I88" s="11"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9">
       <c r="A89" s="1">
         <v>79</v>
       </c>
@@ -3173,7 +3178,7 @@
       <c r="H89" s="11"/>
       <c r="I89" s="11"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9">
       <c r="A90" s="1">
         <v>80</v>
       </c>
@@ -3199,7 +3204,7 @@
       <c r="H90" s="11"/>
       <c r="I90" s="11"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9">
       <c r="A91" s="1">
         <v>81</v>
       </c>
@@ -3225,7 +3230,7 @@
       <c r="H91" s="11"/>
       <c r="I91" s="11"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9">
       <c r="A92" s="1">
         <v>82</v>
       </c>
@@ -3251,7 +3256,7 @@
       <c r="H92" s="11"/>
       <c r="I92" s="11"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9">
       <c r="A93" s="1">
         <v>83</v>
       </c>
@@ -3277,7 +3282,7 @@
       <c r="H93" s="11"/>
       <c r="I93" s="11"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9">
       <c r="A94" s="1">
         <v>84</v>
       </c>
@@ -3303,7 +3308,7 @@
       <c r="H94" s="11"/>
       <c r="I94" s="11"/>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9">
       <c r="A95" s="1">
         <v>85</v>
       </c>
@@ -3329,7 +3334,7 @@
       <c r="H95" s="11"/>
       <c r="I95" s="11"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9">
       <c r="A96" s="1">
         <v>86</v>
       </c>
@@ -3355,7 +3360,7 @@
       <c r="H96" s="11"/>
       <c r="I96" s="11"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9">
       <c r="A97" s="1">
         <v>87</v>
       </c>
@@ -3381,7 +3386,7 @@
       <c r="H97" s="11"/>
       <c r="I97" s="11"/>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9">
       <c r="A98" s="1">
         <v>88</v>
       </c>
@@ -3407,7 +3412,7 @@
       <c r="H98" s="11"/>
       <c r="I98" s="11"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9">
       <c r="A99" s="1">
         <v>89</v>
       </c>
@@ -3433,7 +3438,7 @@
       <c r="H99" s="11"/>
       <c r="I99" s="11"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9">
       <c r="A100" s="1">
         <v>90</v>
       </c>
@@ -3459,7 +3464,7 @@
       <c r="H100" s="11"/>
       <c r="I100" s="11"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9">
       <c r="A101" s="1">
         <v>91</v>
       </c>
@@ -3485,7 +3490,7 @@
       <c r="H101" s="11"/>
       <c r="I101" s="11"/>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9">
       <c r="A102" s="1">
         <v>92</v>
       </c>
@@ -3511,7 +3516,7 @@
       <c r="H102" s="11"/>
       <c r="I102" s="11"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9">
       <c r="A103" s="1">
         <v>93</v>
       </c>
@@ -3537,7 +3542,7 @@
       <c r="H103" s="11"/>
       <c r="I103" s="11"/>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9">
       <c r="A104" s="1">
         <v>94</v>
       </c>
@@ -3563,7 +3568,7 @@
       <c r="H104" s="11"/>
       <c r="I104" s="11"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9">
       <c r="A105" s="1">
         <v>95</v>
       </c>
@@ -3589,7 +3594,7 @@
       <c r="H105" s="11"/>
       <c r="I105" s="11"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9">
       <c r="A106" s="1">
         <v>96</v>
       </c>
@@ -3615,7 +3620,7 @@
       <c r="H106" s="11"/>
       <c r="I106" s="11"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9">
       <c r="A107" s="1">
         <v>97</v>
       </c>
@@ -3641,7 +3646,7 @@
       <c r="H107" s="11"/>
       <c r="I107" s="11"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9">
       <c r="A108" s="1">
         <v>98</v>
       </c>
@@ -3667,7 +3672,7 @@
       <c r="H108" s="11"/>
       <c r="I108" s="11"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9">
       <c r="A109" s="1">
         <v>99</v>
       </c>
@@ -3693,7 +3698,7 @@
       <c r="H109" s="11"/>
       <c r="I109" s="11"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9">
       <c r="A110" s="1">
         <v>100</v>
       </c>
@@ -3719,7 +3724,7 @@
       <c r="H110" s="11"/>
       <c r="I110" s="11"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9">
       <c r="A111" s="1">
         <v>101</v>
       </c>
@@ -3745,7 +3750,7 @@
       <c r="H111" s="11"/>
       <c r="I111" s="11"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9">
       <c r="A112" s="1">
         <v>102</v>
       </c>
@@ -3771,7 +3776,7 @@
       <c r="H112" s="11"/>
       <c r="I112" s="11"/>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9">
       <c r="A113" s="1">
         <v>103</v>
       </c>
@@ -3797,7 +3802,7 @@
       <c r="H113" s="11"/>
       <c r="I113" s="11"/>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9">
       <c r="A114" s="1">
         <v>104</v>
       </c>
@@ -3823,7 +3828,7 @@
       <c r="H114" s="11"/>
       <c r="I114" s="11"/>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9">
       <c r="A115" s="1">
         <v>105</v>
       </c>
@@ -3849,7 +3854,7 @@
       <c r="H115" s="11"/>
       <c r="I115" s="11"/>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9">
       <c r="A116" s="1">
         <v>106</v>
       </c>
@@ -3875,7 +3880,7 @@
       <c r="H116" s="11"/>
       <c r="I116" s="11"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9">
       <c r="A117" s="1">
         <v>107</v>
       </c>
@@ -3901,7 +3906,7 @@
       <c r="H117" s="11"/>
       <c r="I117" s="11"/>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9">
       <c r="A118" s="1">
         <v>108</v>
       </c>
@@ -3927,7 +3932,7 @@
       <c r="H118" s="11"/>
       <c r="I118" s="11"/>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9">
       <c r="A119" s="1">
         <v>109</v>
       </c>
@@ -3953,7 +3958,7 @@
       <c r="H119" s="11"/>
       <c r="I119" s="11"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9">
       <c r="A120" s="1">
         <v>110</v>
       </c>
@@ -3979,7 +3984,7 @@
       <c r="H120" s="11"/>
       <c r="I120" s="11"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9">
       <c r="A121" s="1">
         <v>111</v>
       </c>
@@ -4005,7 +4010,7 @@
       <c r="H121" s="11"/>
       <c r="I121" s="11"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9">
       <c r="A122" s="1">
         <v>112</v>
       </c>
@@ -4031,7 +4036,7 @@
       <c r="H122" s="11"/>
       <c r="I122" s="11"/>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9">
       <c r="A123" s="1">
         <v>113</v>
       </c>
@@ -4057,7 +4062,7 @@
       <c r="H123" s="11"/>
       <c r="I123" s="11"/>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9">
       <c r="A124" s="1">
         <v>114</v>
       </c>
@@ -4083,7 +4088,7 @@
       <c r="H124" s="11"/>
       <c r="I124" s="11"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9">
       <c r="A125" s="1">
         <v>115</v>
       </c>
@@ -4109,7 +4114,7 @@
       <c r="H125" s="11"/>
       <c r="I125" s="11"/>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9">
       <c r="A126" s="1">
         <v>116</v>
       </c>
@@ -4135,7 +4140,7 @@
       <c r="H126" s="11"/>
       <c r="I126" s="11"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9">
       <c r="A127" s="1">
         <v>117</v>
       </c>
@@ -4161,7 +4166,7 @@
       <c r="H127" s="11"/>
       <c r="I127" s="11"/>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9">
       <c r="A128" s="1">
         <v>118</v>
       </c>
@@ -4187,7 +4192,7 @@
       <c r="H128" s="11"/>
       <c r="I128" s="11"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9">
       <c r="A129" s="1">
         <v>119</v>
       </c>
@@ -4213,7 +4218,7 @@
       <c r="H129" s="11"/>
       <c r="I129" s="11"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9">
       <c r="A130" s="1">
         <v>120</v>
       </c>
@@ -4239,7 +4244,7 @@
       <c r="H130" s="11"/>
       <c r="I130" s="11"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9">
       <c r="A131" s="1">
         <v>121</v>
       </c>
@@ -4265,7 +4270,7 @@
       <c r="H131" s="11"/>
       <c r="I131" s="11"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9">
       <c r="A132" s="1">
         <v>122</v>
       </c>
@@ -4291,7 +4296,7 @@
       <c r="H132" s="11"/>
       <c r="I132" s="11"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9">
       <c r="A133" s="1">
         <v>123</v>
       </c>
@@ -4317,7 +4322,7 @@
       <c r="H133" s="11"/>
       <c r="I133" s="11"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9">
       <c r="A134" s="1">
         <v>124</v>
       </c>
@@ -4343,7 +4348,7 @@
       <c r="H134" s="11"/>
       <c r="I134" s="11"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9">
       <c r="A135" s="1">
         <v>125</v>
       </c>
@@ -4369,7 +4374,7 @@
       <c r="H135" s="11"/>
       <c r="I135" s="11"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9">
       <c r="A136" s="1">
         <v>126</v>
       </c>
@@ -4395,7 +4400,7 @@
       <c r="H136" s="11"/>
       <c r="I136" s="11"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9">
       <c r="A137" s="1">
         <v>127</v>
       </c>
@@ -4421,7 +4426,7 @@
       <c r="H137" s="11"/>
       <c r="I137" s="11"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9">
       <c r="A138" s="1">
         <v>128</v>
       </c>
@@ -4447,7 +4452,7 @@
       <c r="H138" s="11"/>
       <c r="I138" s="11"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9">
       <c r="A139" s="1">
         <v>129</v>
       </c>
@@ -4473,7 +4478,7 @@
       <c r="H139" s="11"/>
       <c r="I139" s="11"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9">
       <c r="A140" s="1">
         <v>130</v>
       </c>
@@ -4499,7 +4504,7 @@
       <c r="H140" s="11"/>
       <c r="I140" s="11"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9">
       <c r="A141" s="1">
         <v>131</v>
       </c>
@@ -4525,7 +4530,7 @@
       <c r="H141" s="11"/>
       <c r="I141" s="11"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9">
       <c r="A142" s="1">
         <v>132</v>
       </c>
@@ -4551,7 +4556,7 @@
       <c r="H142" s="11"/>
       <c r="I142" s="11"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9">
       <c r="A143" s="1">
         <v>133</v>
       </c>
@@ -4577,7 +4582,7 @@
       <c r="H143" s="11"/>
       <c r="I143" s="11"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9">
       <c r="A144" s="1">
         <v>134</v>
       </c>
@@ -4603,7 +4608,7 @@
       <c r="H144" s="11"/>
       <c r="I144" s="11"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9">
       <c r="A145" s="1">
         <v>135</v>
       </c>
@@ -4629,7 +4634,7 @@
       <c r="H145" s="11"/>
       <c r="I145" s="11"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9">
       <c r="A146" s="1">
         <v>136</v>
       </c>
@@ -4655,7 +4660,7 @@
       <c r="H146" s="11"/>
       <c r="I146" s="11"/>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9">
       <c r="A147" s="1">
         <v>137</v>
       </c>
@@ -4681,7 +4686,7 @@
       <c r="H147" s="11"/>
       <c r="I147" s="11"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9">
       <c r="A148" s="1">
         <v>138</v>
       </c>
@@ -4707,7 +4712,7 @@
       <c r="H148" s="11"/>
       <c r="I148" s="11"/>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9">
       <c r="A149" s="1">
         <v>139</v>
       </c>
@@ -4733,7 +4738,7 @@
       <c r="H149" s="11"/>
       <c r="I149" s="11"/>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9">
       <c r="A150" s="1">
         <v>140</v>
       </c>
@@ -4759,7 +4764,7 @@
       <c r="H150" s="11"/>
       <c r="I150" s="11"/>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9">
       <c r="A151" s="1">
         <v>141</v>
       </c>
@@ -4785,7 +4790,7 @@
       <c r="H151" s="11"/>
       <c r="I151" s="11"/>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9">
       <c r="A152" s="1">
         <v>142</v>
       </c>
@@ -4811,7 +4816,7 @@
       <c r="H152" s="11"/>
       <c r="I152" s="11"/>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9">
       <c r="A153" s="1">
         <v>143</v>
       </c>
@@ -4837,7 +4842,7 @@
       <c r="H153" s="11"/>
       <c r="I153" s="11"/>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9">
       <c r="A154" s="1">
         <v>144</v>
       </c>
@@ -4863,7 +4868,7 @@
       <c r="H154" s="11"/>
       <c r="I154" s="11"/>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9">
       <c r="A155" s="1">
         <v>145</v>
       </c>
@@ -4889,7 +4894,7 @@
       <c r="H155" s="11"/>
       <c r="I155" s="11"/>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9">
       <c r="A156" s="1">
         <v>146</v>
       </c>
@@ -4915,7 +4920,7 @@
       <c r="H156" s="11"/>
       <c r="I156" s="11"/>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9">
       <c r="A157" s="1">
         <v>147</v>
       </c>
@@ -4941,7 +4946,7 @@
       <c r="H157" s="11"/>
       <c r="I157" s="11"/>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9">
       <c r="A158" s="1">
         <v>148</v>
       </c>
@@ -4967,7 +4972,7 @@
       <c r="H158" s="11"/>
       <c r="I158" s="11"/>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9">
       <c r="A159" s="1">
         <v>149</v>
       </c>
@@ -4993,7 +4998,7 @@
       <c r="H159" s="11"/>
       <c r="I159" s="11"/>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9">
       <c r="A160" s="1">
         <v>150</v>
       </c>
@@ -5019,7 +5024,7 @@
       <c r="H160" s="11"/>
       <c r="I160" s="11"/>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9">
       <c r="A161" s="1">
         <v>151</v>
       </c>
@@ -5045,7 +5050,7 @@
       <c r="H161" s="11"/>
       <c r="I161" s="11"/>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9">
       <c r="A162" s="1">
         <v>152</v>
       </c>
@@ -5071,7 +5076,7 @@
       <c r="H162" s="11"/>
       <c r="I162" s="11"/>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9">
       <c r="A163" s="1">
         <v>153</v>
       </c>
@@ -5097,7 +5102,7 @@
       <c r="H163" s="11"/>
       <c r="I163" s="11"/>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9">
       <c r="A164" s="1">
         <v>154</v>
       </c>
@@ -5123,7 +5128,7 @@
       <c r="H164" s="11"/>
       <c r="I164" s="11"/>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9">
       <c r="A165" s="1">
         <v>155</v>
       </c>
@@ -5149,7 +5154,7 @@
       <c r="H165" s="11"/>
       <c r="I165" s="11"/>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9">
       <c r="A166" s="1">
         <v>156</v>
       </c>
@@ -5175,7 +5180,7 @@
       <c r="H166" s="11"/>
       <c r="I166" s="11"/>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9">
       <c r="A167" s="1">
         <v>157</v>
       </c>
@@ -5201,7 +5206,7 @@
       <c r="H167" s="11"/>
       <c r="I167" s="11"/>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9">
       <c r="A168" s="1">
         <v>158</v>
       </c>
@@ -5227,7 +5232,7 @@
       <c r="H168" s="11"/>
       <c r="I168" s="11"/>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9">
       <c r="A169" s="1">
         <v>159</v>
       </c>
@@ -5253,7 +5258,7 @@
       <c r="H169" s="11"/>
       <c r="I169" s="11"/>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9">
       <c r="A170" s="1">
         <v>160</v>
       </c>
@@ -5279,7 +5284,7 @@
       <c r="H170" s="11"/>
       <c r="I170" s="11"/>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9">
       <c r="A171" s="1">
         <v>161</v>
       </c>
@@ -5305,7 +5310,7 @@
       <c r="H171" s="11"/>
       <c r="I171" s="11"/>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9">
       <c r="A172" s="1">
         <v>162</v>
       </c>
@@ -5331,7 +5336,7 @@
       <c r="H172" s="11"/>
       <c r="I172" s="11"/>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9">
       <c r="A173" s="1">
         <v>163</v>
       </c>
@@ -5357,7 +5362,7 @@
       <c r="H173" s="11"/>
       <c r="I173" s="11"/>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9">
       <c r="A174" s="1">
         <v>164</v>
       </c>
@@ -5383,7 +5388,7 @@
       <c r="H174" s="11"/>
       <c r="I174" s="11"/>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9">
       <c r="A175" s="1">
         <v>165</v>
       </c>
@@ -5409,7 +5414,7 @@
       <c r="H175" s="11"/>
       <c r="I175" s="11"/>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9">
       <c r="A176" s="1">
         <v>166</v>
       </c>
@@ -5435,7 +5440,7 @@
       <c r="H176" s="11"/>
       <c r="I176" s="11"/>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9">
       <c r="A177" s="1">
         <v>167</v>
       </c>
@@ -5461,7 +5466,7 @@
       <c r="H177" s="11"/>
       <c r="I177" s="11"/>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9">
       <c r="A178" s="1">
         <v>168</v>
       </c>
@@ -5487,7 +5492,7 @@
       <c r="H178" s="11"/>
       <c r="I178" s="11"/>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9">
       <c r="A179" s="1">
         <v>169</v>
       </c>
@@ -5513,7 +5518,7 @@
       <c r="H179" s="11"/>
       <c r="I179" s="11"/>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9">
       <c r="A180" s="1">
         <v>170</v>
       </c>
@@ -5539,7 +5544,7 @@
       <c r="H180" s="11"/>
       <c r="I180" s="11"/>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9">
       <c r="A181" s="1">
         <v>171</v>
       </c>
@@ -5565,7 +5570,7 @@
       <c r="H181" s="11"/>
       <c r="I181" s="11"/>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9">
       <c r="A182" s="1">
         <v>172</v>
       </c>
@@ -5591,7 +5596,7 @@
       <c r="H182" s="11"/>
       <c r="I182" s="11"/>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9">
       <c r="A183" s="1">
         <v>173</v>
       </c>
@@ -5617,7 +5622,7 @@
       <c r="H183" s="11"/>
       <c r="I183" s="11"/>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9">
       <c r="A184" s="1">
         <v>174</v>
       </c>
@@ -5643,7 +5648,7 @@
       <c r="H184" s="11"/>
       <c r="I184" s="11"/>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9">
       <c r="A185" s="1">
         <v>175</v>
       </c>
@@ -5669,7 +5674,7 @@
       <c r="H185" s="11"/>
       <c r="I185" s="11"/>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9">
       <c r="A186" s="1">
         <v>176</v>
       </c>
@@ -5695,7 +5700,7 @@
       <c r="H186" s="11"/>
       <c r="I186" s="11"/>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9">
       <c r="A187" s="1">
         <v>177</v>
       </c>
@@ -5721,7 +5726,7 @@
       <c r="H187" s="11"/>
       <c r="I187" s="11"/>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9">
       <c r="A188" s="1">
         <v>178</v>
       </c>
@@ -5747,7 +5752,7 @@
       <c r="H188" s="11"/>
       <c r="I188" s="11"/>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9">
       <c r="A189" s="1">
         <v>179</v>
       </c>
@@ -5773,7 +5778,7 @@
       <c r="H189" s="11"/>
       <c r="I189" s="11"/>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9">
       <c r="A190" s="1">
         <v>180</v>
       </c>
@@ -5799,7 +5804,7 @@
       <c r="H190" s="11"/>
       <c r="I190" s="11"/>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9">
       <c r="A191" s="1">
         <v>181</v>
       </c>
@@ -5825,7 +5830,7 @@
       <c r="H191" s="11"/>
       <c r="I191" s="11"/>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9">
       <c r="A192" s="1">
         <v>182</v>
       </c>
@@ -5851,7 +5856,7 @@
       <c r="H192" s="11"/>
       <c r="I192" s="11"/>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9">
       <c r="A193" s="1">
         <v>183</v>
       </c>
@@ -5877,7 +5882,7 @@
       <c r="H193" s="11"/>
       <c r="I193" s="11"/>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9">
       <c r="A194" s="1">
         <v>184</v>
       </c>
@@ -5903,7 +5908,7 @@
       <c r="H194" s="11"/>
       <c r="I194" s="11"/>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9">
       <c r="A195" s="1">
         <v>185</v>
       </c>
@@ -5929,7 +5934,7 @@
       <c r="H195" s="11"/>
       <c r="I195" s="11"/>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9">
       <c r="A196" s="1">
         <v>186</v>
       </c>
@@ -5955,7 +5960,7 @@
       <c r="H196" s="11"/>
       <c r="I196" s="11"/>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9">
       <c r="A197" s="1">
         <v>187</v>
       </c>
@@ -5981,7 +5986,7 @@
       <c r="H197" s="11"/>
       <c r="I197" s="11"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9">
       <c r="A198" s="1">
         <v>188</v>
       </c>
@@ -6007,7 +6012,7 @@
       <c r="H198" s="11"/>
       <c r="I198" s="11"/>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9">
       <c r="A199" s="1">
         <v>189</v>
       </c>
@@ -6033,7 +6038,7 @@
       <c r="H199" s="11"/>
       <c r="I199" s="11"/>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9">
       <c r="A200" s="1">
         <v>190</v>
       </c>
@@ -6059,7 +6064,7 @@
       <c r="H200" s="11"/>
       <c r="I200" s="11"/>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9">
       <c r="A201" s="1">
         <v>191</v>
       </c>
@@ -6085,7 +6090,7 @@
       <c r="H201" s="11"/>
       <c r="I201" s="11"/>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9">
       <c r="A202" s="1">
         <v>192</v>
       </c>
@@ -6111,7 +6116,7 @@
       <c r="H202" s="11"/>
       <c r="I202" s="11"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9">
       <c r="A203" s="1">
         <v>193</v>
       </c>
@@ -6137,7 +6142,7 @@
       <c r="H203" s="11"/>
       <c r="I203" s="11"/>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9">
       <c r="A204" s="1">
         <v>194</v>
       </c>
@@ -6163,7 +6168,7 @@
       <c r="H204" s="11"/>
       <c r="I204" s="11"/>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9">
       <c r="A205" s="1">
         <v>195</v>
       </c>
@@ -6189,7 +6194,7 @@
       <c r="H205" s="11"/>
       <c r="I205" s="11"/>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9">
       <c r="A206" s="1">
         <v>196</v>
       </c>
@@ -6215,7 +6220,7 @@
       <c r="H206" s="11"/>
       <c r="I206" s="11"/>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9">
       <c r="A207" s="1">
         <v>197</v>
       </c>
@@ -6241,7 +6246,7 @@
       <c r="H207" s="11"/>
       <c r="I207" s="11"/>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9">
       <c r="A208" s="1">
         <v>198</v>
       </c>
@@ -6267,7 +6272,7 @@
       <c r="H208" s="11"/>
       <c r="I208" s="11"/>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9">
       <c r="A209" s="1">
         <v>199</v>
       </c>
@@ -6293,7 +6298,7 @@
       <c r="H209" s="11"/>
       <c r="I209" s="11"/>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9">
       <c r="A210" s="1">
         <v>200</v>
       </c>
@@ -6319,7 +6324,7 @@
       <c r="H210" s="11"/>
       <c r="I210" s="11"/>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9">
       <c r="A211" s="1">
         <v>201</v>
       </c>
@@ -6345,7 +6350,7 @@
       <c r="H211" s="11"/>
       <c r="I211" s="11"/>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9">
       <c r="A212" s="1">
         <v>202</v>
       </c>
@@ -6371,7 +6376,7 @@
       <c r="H212" s="11"/>
       <c r="I212" s="11"/>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9">
       <c r="A213" s="1">
         <v>203</v>
       </c>
@@ -6397,7 +6402,7 @@
       <c r="H213" s="11"/>
       <c r="I213" s="11"/>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9">
       <c r="A214" s="1">
         <v>204</v>
       </c>
@@ -6423,7 +6428,7 @@
       <c r="H214" s="11"/>
       <c r="I214" s="11"/>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9">
       <c r="A215" s="1">
         <v>205</v>
       </c>
@@ -6449,7 +6454,7 @@
       <c r="H215" s="11"/>
       <c r="I215" s="11"/>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9">
       <c r="A216" s="1">
         <v>206</v>
       </c>
@@ -6475,7 +6480,7 @@
       <c r="H216" s="11"/>
       <c r="I216" s="11"/>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9">
       <c r="A217" s="1">
         <v>207</v>
       </c>
@@ -6501,7 +6506,7 @@
       <c r="H217" s="11"/>
       <c r="I217" s="11"/>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9">
       <c r="A218" s="1">
         <v>208</v>
       </c>
@@ -6527,7 +6532,7 @@
       <c r="H218" s="11"/>
       <c r="I218" s="11"/>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9">
       <c r="A219" s="1">
         <v>209</v>
       </c>
@@ -6553,7 +6558,7 @@
       <c r="H219" s="11"/>
       <c r="I219" s="11"/>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9">
       <c r="A220" s="1">
         <v>210</v>
       </c>
@@ -6579,7 +6584,7 @@
       <c r="H220" s="11"/>
       <c r="I220" s="11"/>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9">
       <c r="A221" s="1">
         <v>211</v>
       </c>
@@ -6605,7 +6610,7 @@
       <c r="H221" s="11"/>
       <c r="I221" s="11"/>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9">
       <c r="A222" s="1">
         <v>212</v>
       </c>
@@ -6631,7 +6636,7 @@
       <c r="H222" s="11"/>
       <c r="I222" s="11"/>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9">
       <c r="A223" s="1">
         <v>213</v>
       </c>
@@ -6657,7 +6662,7 @@
       <c r="H223" s="11"/>
       <c r="I223" s="11"/>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9">
       <c r="A224" s="1">
         <v>214</v>
       </c>
@@ -6683,7 +6688,7 @@
       <c r="H224" s="11"/>
       <c r="I224" s="11"/>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9">
       <c r="A225" s="1">
         <v>215</v>
       </c>
@@ -6709,7 +6714,7 @@
       <c r="H225" s="11"/>
       <c r="I225" s="11"/>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9">
       <c r="A226" s="1">
         <v>216</v>
       </c>
@@ -6735,7 +6740,7 @@
       <c r="H226" s="11"/>
       <c r="I226" s="11"/>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9">
       <c r="A227" s="1">
         <v>217</v>
       </c>
@@ -6761,7 +6766,7 @@
       <c r="H227" s="11"/>
       <c r="I227" s="11"/>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9">
       <c r="A228" s="1">
         <v>218</v>
       </c>
@@ -6787,7 +6792,7 @@
       <c r="H228" s="11"/>
       <c r="I228" s="11"/>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9">
       <c r="A229" s="1">
         <v>219</v>
       </c>
@@ -6813,7 +6818,7 @@
       <c r="H229" s="11"/>
       <c r="I229" s="11"/>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9">
       <c r="A230" s="1">
         <v>220</v>
       </c>
@@ -6839,7 +6844,7 @@
       <c r="H230" s="11"/>
       <c r="I230" s="11"/>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9">
       <c r="A231" s="1">
         <v>221</v>
       </c>
@@ -6865,7 +6870,7 @@
       <c r="H231" s="11"/>
       <c r="I231" s="11"/>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9">
       <c r="A232" s="1">
         <v>222</v>
       </c>
@@ -6891,7 +6896,7 @@
       <c r="H232" s="11"/>
       <c r="I232" s="11"/>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9">
       <c r="A233" s="1">
         <v>223</v>
       </c>
@@ -6917,7 +6922,7 @@
       <c r="H233" s="11"/>
       <c r="I233" s="11"/>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9">
       <c r="A234" s="1">
         <v>224</v>
       </c>
@@ -6943,7 +6948,7 @@
       <c r="H234" s="11"/>
       <c r="I234" s="11"/>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9">
       <c r="A235" s="1">
         <v>225</v>
       </c>
@@ -6969,7 +6974,7 @@
       <c r="H235" s="11"/>
       <c r="I235" s="11"/>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9">
       <c r="A236" s="1">
         <v>226</v>
       </c>
@@ -6995,7 +7000,7 @@
       <c r="H236" s="11"/>
       <c r="I236" s="11"/>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9">
       <c r="A237" s="1">
         <v>227</v>
       </c>
@@ -7021,7 +7026,7 @@
       <c r="H237" s="11"/>
       <c r="I237" s="11"/>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9">
       <c r="A238" s="1">
         <v>228</v>
       </c>
@@ -7047,7 +7052,7 @@
       <c r="H238" s="11"/>
       <c r="I238" s="11"/>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9">
       <c r="A239" s="1">
         <v>229</v>
       </c>
@@ -7073,7 +7078,7 @@
       <c r="H239" s="11"/>
       <c r="I239" s="11"/>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9">
       <c r="A240" s="1">
         <v>230</v>
       </c>
@@ -7099,7 +7104,7 @@
       <c r="H240" s="11"/>
       <c r="I240" s="11"/>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9">
       <c r="A241" s="1">
         <v>231</v>
       </c>
@@ -7125,7 +7130,7 @@
       <c r="H241" s="11"/>
       <c r="I241" s="11"/>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9">
       <c r="A242" s="1">
         <v>232</v>
       </c>
@@ -7151,7 +7156,7 @@
       <c r="H242" s="11"/>
       <c r="I242" s="11"/>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9">
       <c r="A243" s="1">
         <v>233</v>
       </c>
@@ -7177,7 +7182,7 @@
       <c r="H243" s="11"/>
       <c r="I243" s="11"/>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9">
       <c r="A244" s="1">
         <v>234</v>
       </c>
@@ -7203,7 +7208,7 @@
       <c r="H244" s="11"/>
       <c r="I244" s="11"/>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9">
       <c r="A245" s="1">
         <v>235</v>
       </c>
@@ -7229,7 +7234,7 @@
       <c r="H245" s="11"/>
       <c r="I245" s="11"/>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9">
       <c r="A246" s="1">
         <v>236</v>
       </c>
@@ -7255,7 +7260,7 @@
       <c r="H246" s="11"/>
       <c r="I246" s="11"/>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9">
       <c r="A247" s="1">
         <v>237</v>
       </c>
@@ -7281,7 +7286,7 @@
       <c r="H247" s="11"/>
       <c r="I247" s="11"/>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9">
       <c r="A248" s="1">
         <v>238</v>
       </c>
@@ -7307,7 +7312,7 @@
       <c r="H248" s="11"/>
       <c r="I248" s="11"/>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9">
       <c r="A249" s="1">
         <v>239</v>
       </c>
@@ -7333,7 +7338,7 @@
       <c r="H249" s="11"/>
       <c r="I249" s="11"/>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9">
       <c r="A250" s="1">
         <v>240</v>
       </c>
@@ -7359,7 +7364,7 @@
       <c r="H250" s="11"/>
       <c r="I250" s="11"/>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9">
       <c r="A251" s="1">
         <v>241</v>
       </c>
@@ -7385,7 +7390,7 @@
       <c r="H251" s="11"/>
       <c r="I251" s="11"/>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9">
       <c r="A252" s="1">
         <v>242</v>
       </c>
@@ -7411,7 +7416,7 @@
       <c r="H252" s="11"/>
       <c r="I252" s="11"/>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9">
       <c r="A253" s="1">
         <v>243</v>
       </c>
@@ -7437,7 +7442,7 @@
       <c r="H253" s="11"/>
       <c r="I253" s="11"/>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9">
       <c r="A254" s="1">
         <v>244</v>
       </c>
@@ -7463,7 +7468,7 @@
       <c r="H254" s="11"/>
       <c r="I254" s="11"/>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9">
       <c r="A255" s="1">
         <v>245</v>
       </c>
@@ -7489,7 +7494,7 @@
       <c r="H255" s="11"/>
       <c r="I255" s="11"/>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9">
       <c r="A256" s="1">
         <v>246</v>
       </c>
@@ -7515,7 +7520,7 @@
       <c r="H256" s="11"/>
       <c r="I256" s="11"/>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9">
       <c r="A257" s="1">
         <v>247</v>
       </c>
@@ -7541,7 +7546,7 @@
       <c r="H257" s="11"/>
       <c r="I257" s="11"/>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9">
       <c r="A258" s="1">
         <v>248</v>
       </c>
@@ -7567,7 +7572,7 @@
       <c r="H258" s="11"/>
       <c r="I258" s="11"/>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9">
       <c r="A259" s="1">
         <v>249</v>
       </c>
@@ -7593,7 +7598,7 @@
       <c r="H259" s="11"/>
       <c r="I259" s="11"/>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9">
       <c r="A260" s="1">
         <v>250</v>
       </c>
@@ -7619,7 +7624,7 @@
       <c r="H260" s="11"/>
       <c r="I260" s="11"/>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9">
       <c r="A261" s="1">
         <v>251</v>
       </c>
@@ -7645,7 +7650,7 @@
       <c r="H261" s="11"/>
       <c r="I261" s="11"/>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9">
       <c r="A262" s="1">
         <v>252</v>
       </c>
@@ -7671,7 +7676,7 @@
       <c r="H262" s="11"/>
       <c r="I262" s="11"/>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9">
       <c r="A263" s="1">
         <v>253</v>
       </c>
@@ -7697,7 +7702,7 @@
       <c r="H263" s="11"/>
       <c r="I263" s="11"/>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9">
       <c r="A264" s="1">
         <v>254</v>
       </c>
@@ -7723,7 +7728,7 @@
       <c r="H264" s="11"/>
       <c r="I264" s="11"/>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9">
       <c r="A265" s="1">
         <v>255</v>
       </c>
@@ -7749,7 +7754,7 @@
       <c r="H265" s="11"/>
       <c r="I265" s="11"/>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9">
       <c r="A266" s="1">
         <v>256</v>
       </c>
@@ -7775,7 +7780,7 @@
       <c r="H266" s="11"/>
       <c r="I266" s="11"/>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9">
       <c r="A267" s="1">
         <v>257</v>
       </c>
@@ -7801,7 +7806,7 @@
       <c r="H267" s="11"/>
       <c r="I267" s="11"/>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9">
       <c r="A268" s="1">
         <v>258</v>
       </c>
@@ -7827,7 +7832,7 @@
       <c r="H268" s="11"/>
       <c r="I268" s="11"/>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9">
       <c r="A269" s="1">
         <v>259</v>
       </c>
@@ -7853,7 +7858,7 @@
       <c r="H269" s="11"/>
       <c r="I269" s="11"/>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9">
       <c r="A270" s="1">
         <v>260</v>
       </c>
@@ -7879,7 +7884,7 @@
       <c r="H270" s="11"/>
       <c r="I270" s="11"/>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9">
       <c r="A271" s="1">
         <v>261</v>
       </c>
@@ -7905,7 +7910,7 @@
       <c r="H271" s="11"/>
       <c r="I271" s="11"/>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9">
       <c r="A272" s="1">
         <v>262</v>
       </c>
@@ -7931,7 +7936,7 @@
       <c r="H272" s="11"/>
       <c r="I272" s="11"/>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9">
       <c r="A273" s="1">
         <v>263</v>
       </c>
@@ -7957,7 +7962,7 @@
       <c r="H273" s="11"/>
       <c r="I273" s="11"/>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9">
       <c r="A274" s="1">
         <v>264</v>
       </c>
@@ -7983,7 +7988,7 @@
       <c r="H274" s="11"/>
       <c r="I274" s="11"/>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9">
       <c r="A275" s="1">
         <v>265</v>
       </c>
@@ -8009,7 +8014,7 @@
       <c r="H275" s="11"/>
       <c r="I275" s="11"/>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9">
       <c r="A276" s="1">
         <v>266</v>
       </c>
@@ -8035,7 +8040,7 @@
       <c r="H276" s="11"/>
       <c r="I276" s="11"/>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9">
       <c r="A277" s="1">
         <v>267</v>
       </c>
@@ -8061,7 +8066,7 @@
       <c r="H277" s="11"/>
       <c r="I277" s="11"/>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9">
       <c r="A278" s="1">
         <v>268</v>
       </c>
@@ -8087,7 +8092,7 @@
       <c r="H278" s="11"/>
       <c r="I278" s="11"/>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9">
       <c r="A279" s="1">
         <v>269</v>
       </c>
@@ -8113,7 +8118,7 @@
       <c r="H279" s="11"/>
       <c r="I279" s="11"/>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9">
       <c r="A280" s="1">
         <v>270</v>
       </c>
@@ -8139,7 +8144,7 @@
       <c r="H280" s="11"/>
       <c r="I280" s="11"/>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9">
       <c r="A281" s="1">
         <v>271</v>
       </c>
@@ -8165,7 +8170,7 @@
       <c r="H281" s="11"/>
       <c r="I281" s="11"/>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9">
       <c r="A282" s="1">
         <v>272</v>
       </c>
@@ -8191,7 +8196,7 @@
       <c r="H282" s="11"/>
       <c r="I282" s="11"/>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9">
       <c r="A283" s="1">
         <v>273</v>
       </c>
@@ -8217,7 +8222,7 @@
       <c r="H283" s="11"/>
       <c r="I283" s="11"/>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9">
       <c r="A284" s="1">
         <v>274</v>
       </c>
@@ -8243,7 +8248,7 @@
       <c r="H284" s="11"/>
       <c r="I284" s="11"/>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9">
       <c r="A285" s="1">
         <v>275</v>
       </c>
@@ -8269,7 +8274,7 @@
       <c r="H285" s="11"/>
       <c r="I285" s="11"/>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9">
       <c r="A286" s="1">
         <v>276</v>
       </c>
@@ -8299,7 +8304,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9">
       <c r="A287" s="1">
         <v>277</v>
       </c>
@@ -8329,7 +8334,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9">
       <c r="A288" s="1">
         <v>278</v>
       </c>
@@ -8359,7 +8364,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9">
       <c r="A289" s="1">
         <v>279</v>
       </c>
@@ -8389,7 +8394,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9">
       <c r="A290" s="1">
         <v>280</v>
       </c>
@@ -8419,7 +8424,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9">
       <c r="A291" s="1">
         <v>281</v>
       </c>
@@ -8449,7 +8454,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9">
       <c r="A292" s="1">
         <v>282</v>
       </c>
@@ -8479,7 +8484,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9">
       <c r="A293" s="1">
         <v>283</v>
       </c>
@@ -8509,7 +8514,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9">
       <c r="A294" s="1">
         <v>284</v>
       </c>
@@ -8539,7 +8544,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9">
       <c r="A295" s="1">
         <v>285</v>
       </c>
@@ -8569,7 +8574,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9">
       <c r="A296" s="1">
         <v>286</v>
       </c>
@@ -8599,7 +8604,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9">
       <c r="A297" s="1">
         <v>287</v>
       </c>
@@ -8629,7 +8634,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9">
       <c r="A298" s="1">
         <v>288</v>
       </c>
@@ -8659,7 +8664,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9">
       <c r="A299" s="1">
         <v>289</v>
       </c>
@@ -8689,7 +8694,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9">
       <c r="A300" s="1">
         <v>290</v>
       </c>
@@ -8719,7 +8724,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9">
       <c r="A301" s="1">
         <v>291</v>
       </c>
@@ -8749,7 +8754,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9">
       <c r="A302" s="1">
         <v>292</v>
       </c>
@@ -8779,7 +8784,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="303" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" s="1" customFormat="1">
       <c r="A303" s="1">
         <v>293</v>
       </c>
@@ -8809,7 +8814,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="304" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" s="1" customFormat="1">
       <c r="A304" s="1">
         <v>294</v>
       </c>
@@ -8839,7 +8844,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9">
       <c r="A305" s="1">
         <v>295</v>
       </c>
@@ -8869,7 +8874,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9">
       <c r="A306" s="1">
         <v>296</v>
       </c>
@@ -8899,7 +8904,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9">
       <c r="A307" s="1">
         <v>297</v>
       </c>
@@ -8929,7 +8934,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9">
       <c r="A308" s="1">
         <v>298</v>
       </c>
@@ -8959,73 +8964,73 @@
         <v>56</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9">
       <c r="A309" s="1"/>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9">
       <c r="A310" s="1"/>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9">
       <c r="A311" s="1"/>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9">
       <c r="A312" s="1"/>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9">
       <c r="A313" s="1"/>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9">
       <c r="A314" s="1"/>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9">
       <c r="A315" s="1"/>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9">
       <c r="A316" s="1"/>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9">
       <c r="A317" s="1"/>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9">
       <c r="A318" s="1"/>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9">
       <c r="A319" s="1"/>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9">
       <c r="A320" s="1"/>
     </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:1">
       <c r="A321" s="1"/>
     </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:1">
       <c r="A322" s="1"/>
     </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:1">
       <c r="A323" s="1"/>
     </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:1">
       <c r="A324" s="1"/>
     </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:1">
       <c r="A325" s="1"/>
     </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:1">
       <c r="A326" s="1"/>
     </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:1">
       <c r="A327" s="1"/>
     </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:1">
       <c r="A328" s="1"/>
     </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:1">
       <c r="A329" s="1"/>
     </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:1">
       <c r="A330" s="1"/>
     </row>
-    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:1">
       <c r="A331" s="1"/>
     </row>
   </sheetData>
@@ -9047,13 +9052,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{797F1036-D41E-43A4-9E6E-CBBB62F3CD31}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="13.28515625" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9067,7 +9072,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -9081,7 +9086,7 @@
         <v>234.67</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -9095,7 +9100,7 @@
         <v>161.15</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -9109,7 +9114,7 @@
         <v>157.61000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -9123,7 +9128,7 @@
         <v>347.95</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -9137,7 +9142,7 @@
         <v>393.57</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -9151,7 +9156,7 @@
         <v>19.87</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -9165,7 +9170,7 @@
         <v>19.57</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>61</v>
       </c>
@@ -9179,7 +9184,7 @@
         <v>19.86</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -9193,7 +9198,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -9218,7 +9223,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56220E0F-EC16-4A8C-9E04-C7F8849C4B4D}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
@@ -9226,7 +9231,7 @@
     <col min="5" max="5" width="30.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9243,7 +9248,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -9260,7 +9265,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -9277,7 +9282,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -9294,7 +9299,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -9311,7 +9316,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -9328,7 +9333,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -9345,7 +9350,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -9373,14 +9378,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83DAFC4B-C207-418A-8501-0E1EC9E673B7}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9391,7 +9396,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -9402,7 +9407,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -9413,7 +9418,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -9424,7 +9429,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>61</v>
       </c>
@@ -9435,7 +9440,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -9446,7 +9451,7 @@
         <v>46631</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -9457,7 +9462,7 @@
         <v>48579</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -9468,7 +9473,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -9479,7 +9484,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -9490,7 +9495,7 @@
         <v>48579</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -9510,6 +9515,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -9518,7 +9537,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100FB7AAE8C8816FD47B559A0CCF555AFF0" ma:contentTypeVersion="10" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5c9910934a78ddf693a6b708b52e9b37">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f95d585e-e7a7-414c-955d-38a47c8579bd" xmlns:ns3="33ab045e-9213-4eea-a9f2-a5b809105d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a9c61c95b4e11caed4e46447c2ca01e7" ns2:_="" ns3:_="">
     <xsd:import namespace="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
@@ -9721,47 +9740,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="853" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E9DF501-2FF6-4289-B146-A361D0BE00CF}"/>
+  <xr:revisionPtr revIDLastSave="851" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F98DAED3-7D28-4389-9118-EA4B08D88D0A}"/>
   <bookViews>
-    <workbookView xWindow="-25935" yWindow="5655" windowWidth="21600" windowHeight="11085" firstSheet="2" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="28695" yWindow="3180" windowWidth="21600" windowHeight="11085" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -273,7 +273,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -357,27 +357,17 @@
   </cellStyles>
   <dxfs count="12">
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -396,6 +386,16 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -688,23 +688,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:I308" totalsRowShown="0" headerRowDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:I308" totalsRowShown="0" headerRowDxfId="8">
   <autoFilter ref="A10:I308" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
   <tableColumns count="9">
     <tableColumn id="3" xr3:uid="{AFE823F6-980E-4E32-B4F4-6ECDE10F377D}" name="ID"/>
-    <tableColumn id="1" xr3:uid="{CD000998-6E2C-4963-8605-37081D9C1A64}" name="Unidad" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{542F6635-555D-4F04-8C27-263AF6E0C9F1}" name="Sitio" dataDxfId="9">
+    <tableColumn id="1" xr3:uid="{CD000998-6E2C-4963-8605-37081D9C1A64}" name="Unidad" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{542F6635-555D-4F04-8C27-263AF6E0C9F1}" name="Sitio" dataDxfId="6">
       <calculatedColumnFormula>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6D2AC534-BC70-4E36-815D-053C7EC9A0CE}" name="Carga_Disponible" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{FBB18F6C-27E4-42D9-9835-9152B6D0D871}" name="Estado_Op" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{21A32989-F167-49C0-9D41-2BD3A8923998}" name="Fecha_Hora_Inicio" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{713F74B7-95D9-4F96-AA1E-57E68B8A7FE7}" name="Fecha_Hora_Final" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{20481209-2CB3-4DCC-A330-D866983AA4F9}" name="Motivo" dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{55FF6738-9798-4086-9AA1-DC8A3EF8081F}" name="Detalle" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{6D2AC534-BC70-4E36-815D-053C7EC9A0CE}" name="Carga_Disponible" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{FBB18F6C-27E4-42D9-9835-9152B6D0D871}" name="Estado_Op" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{21A32989-F167-49C0-9D41-2BD3A8923998}" name="Fecha_Hora_Inicio" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{713F74B7-95D9-4F96-AA1E-57E68B8A7FE7}" name="Fecha_Hora_Final" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{20481209-2CB3-4DCC-A330-D866983AA4F9}" name="Motivo" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{55FF6738-9798-4086-9AA1-DC8A3EF8081F}" name="Detalle" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -731,9 +731,9 @@
   </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{1EEE0FFC-B699-4850-9A13-72CF6FB78CA6}" name="Unidad"/>
-    <tableColumn id="2" xr3:uid="{BDB3B76C-8D9D-4A32-9C94-204172B9E68C}" name="Fecha_Hora_Inicio" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{A21A7F07-F50E-4006-B601-758B5E8BD7BE}" name="Fecha_Hora_Fin" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{F49EC928-7A7A-47BB-9275-EDE8B8DF6BC7}" name="Días_de_Mantenimiento" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{BDB3B76C-8D9D-4A32-9C94-204172B9E68C}" name="Fecha_Hora_Inicio" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{A21A7F07-F50E-4006-B601-758B5E8BD7BE}" name="Fecha_Hora_Fin" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{F49EC928-7A7A-47BB-9275-EDE8B8DF6BC7}" name="Días_de_Mantenimiento" dataDxfId="9"/>
     <tableColumn id="5" xr3:uid="{E5C19B72-F1F0-4F1D-9466-99048BCEFC0C}" name="Motivo"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1069,8 +1069,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
-  <dimension ref="A2:I331"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <dimension ref="A9:I331"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
@@ -1084,18 +1084,13 @@
     <col min="12" max="12" width="33.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9">
-      <c r="H2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
         <v>298</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1124,7 +1119,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -1150,7 +1145,7 @@
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -1176,7 +1171,7 @@
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>3</v>
       </c>
@@ -1202,7 +1197,7 @@
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>4</v>
       </c>
@@ -1228,7 +1223,7 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>5</v>
       </c>
@@ -1254,7 +1249,7 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>6</v>
       </c>
@@ -1280,7 +1275,7 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>7</v>
       </c>
@@ -1306,7 +1301,7 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>8</v>
       </c>
@@ -1332,7 +1327,7 @@
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>9</v>
       </c>
@@ -1358,7 +1353,7 @@
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>10</v>
       </c>
@@ -1384,7 +1379,7 @@
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>11</v>
       </c>
@@ -1410,7 +1405,7 @@
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>12</v>
       </c>
@@ -1436,7 +1431,7 @@
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>13</v>
       </c>
@@ -1462,7 +1457,7 @@
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>14</v>
       </c>
@@ -1488,7 +1483,7 @@
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>15</v>
       </c>
@@ -1514,7 +1509,7 @@
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>16</v>
       </c>
@@ -1540,7 +1535,7 @@
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>17</v>
       </c>
@@ -1566,7 +1561,7 @@
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>18</v>
       </c>
@@ -1592,7 +1587,7 @@
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>19</v>
       </c>
@@ -1618,7 +1613,7 @@
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>20</v>
       </c>
@@ -1644,7 +1639,7 @@
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>21</v>
       </c>
@@ -1670,7 +1665,7 @@
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>22</v>
       </c>
@@ -1696,7 +1691,7 @@
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>23</v>
       </c>
@@ -1722,7 +1717,7 @@
       <c r="H33" s="11"/>
       <c r="I33" s="11"/>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24</v>
       </c>
@@ -1748,7 +1743,7 @@
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>25</v>
       </c>
@@ -1774,7 +1769,7 @@
       <c r="H35" s="11"/>
       <c r="I35" s="11"/>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>26</v>
       </c>
@@ -1800,7 +1795,7 @@
       <c r="H36" s="11"/>
       <c r="I36" s="11"/>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>27</v>
       </c>
@@ -1826,7 +1821,7 @@
       <c r="H37" s="11"/>
       <c r="I37" s="11"/>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>28</v>
       </c>
@@ -1852,7 +1847,7 @@
       <c r="H38" s="11"/>
       <c r="I38" s="11"/>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>29</v>
       </c>
@@ -1878,7 +1873,7 @@
       <c r="H39" s="11"/>
       <c r="I39" s="11"/>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>30</v>
       </c>
@@ -1904,7 +1899,7 @@
       <c r="H40" s="11"/>
       <c r="I40" s="11"/>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>31</v>
       </c>
@@ -1930,7 +1925,7 @@
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>32</v>
       </c>
@@ -1956,7 +1951,7 @@
       <c r="H42" s="11"/>
       <c r="I42" s="11"/>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>33</v>
       </c>
@@ -1982,7 +1977,7 @@
       <c r="H43" s="11"/>
       <c r="I43" s="11"/>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>34</v>
       </c>
@@ -2008,7 +2003,7 @@
       <c r="H44" s="11"/>
       <c r="I44" s="11"/>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>35</v>
       </c>
@@ -2034,7 +2029,7 @@
       <c r="H45" s="11"/>
       <c r="I45" s="11"/>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>36</v>
       </c>
@@ -2060,7 +2055,7 @@
       <c r="H46" s="11"/>
       <c r="I46" s="11"/>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>37</v>
       </c>
@@ -2086,7 +2081,7 @@
       <c r="H47" s="11"/>
       <c r="I47" s="11"/>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>38</v>
       </c>
@@ -2112,7 +2107,7 @@
       <c r="H48" s="11"/>
       <c r="I48" s="11"/>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>39</v>
       </c>
@@ -2138,7 +2133,7 @@
       <c r="H49" s="11"/>
       <c r="I49" s="11"/>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>40</v>
       </c>
@@ -2164,7 +2159,7 @@
       <c r="H50" s="11"/>
       <c r="I50" s="11"/>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>41</v>
       </c>
@@ -2190,7 +2185,7 @@
       <c r="H51" s="11"/>
       <c r="I51" s="11"/>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>42</v>
       </c>
@@ -2216,7 +2211,7 @@
       <c r="H52" s="11"/>
       <c r="I52" s="11"/>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>43</v>
       </c>
@@ -2242,7 +2237,7 @@
       <c r="H53" s="11"/>
       <c r="I53" s="11"/>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>44</v>
       </c>
@@ -2268,7 +2263,7 @@
       <c r="H54" s="11"/>
       <c r="I54" s="11"/>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>45</v>
       </c>
@@ -2294,7 +2289,7 @@
       <c r="H55" s="11"/>
       <c r="I55" s="11"/>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>46</v>
       </c>
@@ -2320,7 +2315,7 @@
       <c r="H56" s="11"/>
       <c r="I56" s="11"/>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>47</v>
       </c>
@@ -2346,7 +2341,7 @@
       <c r="H57" s="11"/>
       <c r="I57" s="11"/>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>48</v>
       </c>
@@ -2372,7 +2367,7 @@
       <c r="H58" s="11"/>
       <c r="I58" s="11"/>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>49</v>
       </c>
@@ -2398,7 +2393,7 @@
       <c r="H59" s="11"/>
       <c r="I59" s="11"/>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>50</v>
       </c>
@@ -2424,7 +2419,7 @@
       <c r="H60" s="11"/>
       <c r="I60" s="11"/>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>51</v>
       </c>
@@ -2450,7 +2445,7 @@
       <c r="H61" s="11"/>
       <c r="I61" s="11"/>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>52</v>
       </c>
@@ -2476,7 +2471,7 @@
       <c r="H62" s="11"/>
       <c r="I62" s="11"/>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>53</v>
       </c>
@@ -2502,7 +2497,7 @@
       <c r="H63" s="11"/>
       <c r="I63" s="11"/>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>54</v>
       </c>
@@ -2528,7 +2523,7 @@
       <c r="H64" s="11"/>
       <c r="I64" s="11"/>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>55</v>
       </c>
@@ -2554,7 +2549,7 @@
       <c r="H65" s="11"/>
       <c r="I65" s="11"/>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>56</v>
       </c>
@@ -2580,7 +2575,7 @@
       <c r="H66" s="11"/>
       <c r="I66" s="11"/>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>57</v>
       </c>
@@ -2606,7 +2601,7 @@
       <c r="H67" s="11"/>
       <c r="I67" s="11"/>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>58</v>
       </c>
@@ -2632,7 +2627,7 @@
       <c r="H68" s="11"/>
       <c r="I68" s="11"/>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>59</v>
       </c>
@@ -2658,7 +2653,7 @@
       <c r="H69" s="11"/>
       <c r="I69" s="11"/>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>60</v>
       </c>
@@ -2684,7 +2679,7 @@
       <c r="H70" s="11"/>
       <c r="I70" s="11"/>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>61</v>
       </c>
@@ -2710,7 +2705,7 @@
       <c r="H71" s="11"/>
       <c r="I71" s="11"/>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>62</v>
       </c>
@@ -2736,7 +2731,7 @@
       <c r="H72" s="11"/>
       <c r="I72" s="11"/>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>63</v>
       </c>
@@ -2762,7 +2757,7 @@
       <c r="H73" s="11"/>
       <c r="I73" s="11"/>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>64</v>
       </c>
@@ -2788,7 +2783,7 @@
       <c r="H74" s="11"/>
       <c r="I74" s="11"/>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>65</v>
       </c>
@@ -2814,7 +2809,7 @@
       <c r="H75" s="11"/>
       <c r="I75" s="11"/>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>66</v>
       </c>
@@ -2840,7 +2835,7 @@
       <c r="H76" s="11"/>
       <c r="I76" s="11"/>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>67</v>
       </c>
@@ -2866,7 +2861,7 @@
       <c r="H77" s="11"/>
       <c r="I77" s="11"/>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>68</v>
       </c>
@@ -2892,7 +2887,7 @@
       <c r="H78" s="11"/>
       <c r="I78" s="11"/>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>69</v>
       </c>
@@ -2918,7 +2913,7 @@
       <c r="H79" s="11"/>
       <c r="I79" s="11"/>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>70</v>
       </c>
@@ -2944,7 +2939,7 @@
       <c r="H80" s="11"/>
       <c r="I80" s="11"/>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>71</v>
       </c>
@@ -2970,7 +2965,7 @@
       <c r="H81" s="11"/>
       <c r="I81" s="11"/>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>72</v>
       </c>
@@ -2996,7 +2991,7 @@
       <c r="H82" s="11"/>
       <c r="I82" s="11"/>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>73</v>
       </c>
@@ -3022,7 +3017,7 @@
       <c r="H83" s="11"/>
       <c r="I83" s="11"/>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>74</v>
       </c>
@@ -3048,7 +3043,7 @@
       <c r="H84" s="11"/>
       <c r="I84" s="11"/>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>75</v>
       </c>
@@ -3074,7 +3069,7 @@
       <c r="H85" s="11"/>
       <c r="I85" s="11"/>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>76</v>
       </c>
@@ -3100,7 +3095,7 @@
       <c r="H86" s="11"/>
       <c r="I86" s="11"/>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>77</v>
       </c>
@@ -3126,7 +3121,7 @@
       <c r="H87" s="11"/>
       <c r="I87" s="11"/>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>78</v>
       </c>
@@ -3152,7 +3147,7 @@
       <c r="H88" s="11"/>
       <c r="I88" s="11"/>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>79</v>
       </c>
@@ -3178,7 +3173,7 @@
       <c r="H89" s="11"/>
       <c r="I89" s="11"/>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>80</v>
       </c>
@@ -3204,7 +3199,7 @@
       <c r="H90" s="11"/>
       <c r="I90" s="11"/>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>81</v>
       </c>
@@ -3230,7 +3225,7 @@
       <c r="H91" s="11"/>
       <c r="I91" s="11"/>
     </row>
-    <row r="92" spans="1:9">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>82</v>
       </c>
@@ -3256,7 +3251,7 @@
       <c r="H92" s="11"/>
       <c r="I92" s="11"/>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>83</v>
       </c>
@@ -3282,7 +3277,7 @@
       <c r="H93" s="11"/>
       <c r="I93" s="11"/>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>84</v>
       </c>
@@ -3308,7 +3303,7 @@
       <c r="H94" s="11"/>
       <c r="I94" s="11"/>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>85</v>
       </c>
@@ -3334,7 +3329,7 @@
       <c r="H95" s="11"/>
       <c r="I95" s="11"/>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>86</v>
       </c>
@@ -3360,7 +3355,7 @@
       <c r="H96" s="11"/>
       <c r="I96" s="11"/>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>87</v>
       </c>
@@ -3386,7 +3381,7 @@
       <c r="H97" s="11"/>
       <c r="I97" s="11"/>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>88</v>
       </c>
@@ -3412,7 +3407,7 @@
       <c r="H98" s="11"/>
       <c r="I98" s="11"/>
     </row>
-    <row r="99" spans="1:9">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>89</v>
       </c>
@@ -3438,7 +3433,7 @@
       <c r="H99" s="11"/>
       <c r="I99" s="11"/>
     </row>
-    <row r="100" spans="1:9">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>90</v>
       </c>
@@ -3464,7 +3459,7 @@
       <c r="H100" s="11"/>
       <c r="I100" s="11"/>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>91</v>
       </c>
@@ -3490,7 +3485,7 @@
       <c r="H101" s="11"/>
       <c r="I101" s="11"/>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>92</v>
       </c>
@@ -3516,7 +3511,7 @@
       <c r="H102" s="11"/>
       <c r="I102" s="11"/>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>93</v>
       </c>
@@ -3542,7 +3537,7 @@
       <c r="H103" s="11"/>
       <c r="I103" s="11"/>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>94</v>
       </c>
@@ -3568,7 +3563,7 @@
       <c r="H104" s="11"/>
       <c r="I104" s="11"/>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>95</v>
       </c>
@@ -3594,7 +3589,7 @@
       <c r="H105" s="11"/>
       <c r="I105" s="11"/>
     </row>
-    <row r="106" spans="1:9">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>96</v>
       </c>
@@ -3620,7 +3615,7 @@
       <c r="H106" s="11"/>
       <c r="I106" s="11"/>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>97</v>
       </c>
@@ -3646,7 +3641,7 @@
       <c r="H107" s="11"/>
       <c r="I107" s="11"/>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>98</v>
       </c>
@@ -3672,7 +3667,7 @@
       <c r="H108" s="11"/>
       <c r="I108" s="11"/>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>99</v>
       </c>
@@ -3698,7 +3693,7 @@
       <c r="H109" s="11"/>
       <c r="I109" s="11"/>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>100</v>
       </c>
@@ -3724,7 +3719,7 @@
       <c r="H110" s="11"/>
       <c r="I110" s="11"/>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>101</v>
       </c>
@@ -3750,7 +3745,7 @@
       <c r="H111" s="11"/>
       <c r="I111" s="11"/>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>102</v>
       </c>
@@ -3776,7 +3771,7 @@
       <c r="H112" s="11"/>
       <c r="I112" s="11"/>
     </row>
-    <row r="113" spans="1:9">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>103</v>
       </c>
@@ -3802,7 +3797,7 @@
       <c r="H113" s="11"/>
       <c r="I113" s="11"/>
     </row>
-    <row r="114" spans="1:9">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>104</v>
       </c>
@@ -3828,7 +3823,7 @@
       <c r="H114" s="11"/>
       <c r="I114" s="11"/>
     </row>
-    <row r="115" spans="1:9">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>105</v>
       </c>
@@ -3854,7 +3849,7 @@
       <c r="H115" s="11"/>
       <c r="I115" s="11"/>
     </row>
-    <row r="116" spans="1:9">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>106</v>
       </c>
@@ -3880,7 +3875,7 @@
       <c r="H116" s="11"/>
       <c r="I116" s="11"/>
     </row>
-    <row r="117" spans="1:9">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>107</v>
       </c>
@@ -3906,7 +3901,7 @@
       <c r="H117" s="11"/>
       <c r="I117" s="11"/>
     </row>
-    <row r="118" spans="1:9">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>108</v>
       </c>
@@ -3932,7 +3927,7 @@
       <c r="H118" s="11"/>
       <c r="I118" s="11"/>
     </row>
-    <row r="119" spans="1:9">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>109</v>
       </c>
@@ -3958,7 +3953,7 @@
       <c r="H119" s="11"/>
       <c r="I119" s="11"/>
     </row>
-    <row r="120" spans="1:9">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>110</v>
       </c>
@@ -3984,7 +3979,7 @@
       <c r="H120" s="11"/>
       <c r="I120" s="11"/>
     </row>
-    <row r="121" spans="1:9">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>111</v>
       </c>
@@ -4010,7 +4005,7 @@
       <c r="H121" s="11"/>
       <c r="I121" s="11"/>
     </row>
-    <row r="122" spans="1:9">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>112</v>
       </c>
@@ -4036,7 +4031,7 @@
       <c r="H122" s="11"/>
       <c r="I122" s="11"/>
     </row>
-    <row r="123" spans="1:9">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>113</v>
       </c>
@@ -4062,7 +4057,7 @@
       <c r="H123" s="11"/>
       <c r="I123" s="11"/>
     </row>
-    <row r="124" spans="1:9">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>114</v>
       </c>
@@ -4088,7 +4083,7 @@
       <c r="H124" s="11"/>
       <c r="I124" s="11"/>
     </row>
-    <row r="125" spans="1:9">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>115</v>
       </c>
@@ -4114,7 +4109,7 @@
       <c r="H125" s="11"/>
       <c r="I125" s="11"/>
     </row>
-    <row r="126" spans="1:9">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>116</v>
       </c>
@@ -4140,7 +4135,7 @@
       <c r="H126" s="11"/>
       <c r="I126" s="11"/>
     </row>
-    <row r="127" spans="1:9">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>117</v>
       </c>
@@ -4166,7 +4161,7 @@
       <c r="H127" s="11"/>
       <c r="I127" s="11"/>
     </row>
-    <row r="128" spans="1:9">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>118</v>
       </c>
@@ -4192,7 +4187,7 @@
       <c r="H128" s="11"/>
       <c r="I128" s="11"/>
     </row>
-    <row r="129" spans="1:9">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>119</v>
       </c>
@@ -4218,7 +4213,7 @@
       <c r="H129" s="11"/>
       <c r="I129" s="11"/>
     </row>
-    <row r="130" spans="1:9">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>120</v>
       </c>
@@ -4244,7 +4239,7 @@
       <c r="H130" s="11"/>
       <c r="I130" s="11"/>
     </row>
-    <row r="131" spans="1:9">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>121</v>
       </c>
@@ -4270,7 +4265,7 @@
       <c r="H131" s="11"/>
       <c r="I131" s="11"/>
     </row>
-    <row r="132" spans="1:9">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>122</v>
       </c>
@@ -4296,7 +4291,7 @@
       <c r="H132" s="11"/>
       <c r="I132" s="11"/>
     </row>
-    <row r="133" spans="1:9">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>123</v>
       </c>
@@ -4322,7 +4317,7 @@
       <c r="H133" s="11"/>
       <c r="I133" s="11"/>
     </row>
-    <row r="134" spans="1:9">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>124</v>
       </c>
@@ -4348,7 +4343,7 @@
       <c r="H134" s="11"/>
       <c r="I134" s="11"/>
     </row>
-    <row r="135" spans="1:9">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>125</v>
       </c>
@@ -4374,7 +4369,7 @@
       <c r="H135" s="11"/>
       <c r="I135" s="11"/>
     </row>
-    <row r="136" spans="1:9">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>126</v>
       </c>
@@ -4400,7 +4395,7 @@
       <c r="H136" s="11"/>
       <c r="I136" s="11"/>
     </row>
-    <row r="137" spans="1:9">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>127</v>
       </c>
@@ -4426,7 +4421,7 @@
       <c r="H137" s="11"/>
       <c r="I137" s="11"/>
     </row>
-    <row r="138" spans="1:9">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>128</v>
       </c>
@@ -4452,7 +4447,7 @@
       <c r="H138" s="11"/>
       <c r="I138" s="11"/>
     </row>
-    <row r="139" spans="1:9">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>129</v>
       </c>
@@ -4478,7 +4473,7 @@
       <c r="H139" s="11"/>
       <c r="I139" s="11"/>
     </row>
-    <row r="140" spans="1:9">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>130</v>
       </c>
@@ -4504,7 +4499,7 @@
       <c r="H140" s="11"/>
       <c r="I140" s="11"/>
     </row>
-    <row r="141" spans="1:9">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>131</v>
       </c>
@@ -4530,7 +4525,7 @@
       <c r="H141" s="11"/>
       <c r="I141" s="11"/>
     </row>
-    <row r="142" spans="1:9">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>132</v>
       </c>
@@ -4556,7 +4551,7 @@
       <c r="H142" s="11"/>
       <c r="I142" s="11"/>
     </row>
-    <row r="143" spans="1:9">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>133</v>
       </c>
@@ -4582,7 +4577,7 @@
       <c r="H143" s="11"/>
       <c r="I143" s="11"/>
     </row>
-    <row r="144" spans="1:9">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>134</v>
       </c>
@@ -4608,7 +4603,7 @@
       <c r="H144" s="11"/>
       <c r="I144" s="11"/>
     </row>
-    <row r="145" spans="1:9">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>135</v>
       </c>
@@ -4634,7 +4629,7 @@
       <c r="H145" s="11"/>
       <c r="I145" s="11"/>
     </row>
-    <row r="146" spans="1:9">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>136</v>
       </c>
@@ -4660,7 +4655,7 @@
       <c r="H146" s="11"/>
       <c r="I146" s="11"/>
     </row>
-    <row r="147" spans="1:9">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>137</v>
       </c>
@@ -4686,7 +4681,7 @@
       <c r="H147" s="11"/>
       <c r="I147" s="11"/>
     </row>
-    <row r="148" spans="1:9">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>138</v>
       </c>
@@ -4712,7 +4707,7 @@
       <c r="H148" s="11"/>
       <c r="I148" s="11"/>
     </row>
-    <row r="149" spans="1:9">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>139</v>
       </c>
@@ -4738,7 +4733,7 @@
       <c r="H149" s="11"/>
       <c r="I149" s="11"/>
     </row>
-    <row r="150" spans="1:9">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>140</v>
       </c>
@@ -4764,7 +4759,7 @@
       <c r="H150" s="11"/>
       <c r="I150" s="11"/>
     </row>
-    <row r="151" spans="1:9">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>141</v>
       </c>
@@ -4790,7 +4785,7 @@
       <c r="H151" s="11"/>
       <c r="I151" s="11"/>
     </row>
-    <row r="152" spans="1:9">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>142</v>
       </c>
@@ -4816,7 +4811,7 @@
       <c r="H152" s="11"/>
       <c r="I152" s="11"/>
     </row>
-    <row r="153" spans="1:9">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>143</v>
       </c>
@@ -4842,7 +4837,7 @@
       <c r="H153" s="11"/>
       <c r="I153" s="11"/>
     </row>
-    <row r="154" spans="1:9">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>144</v>
       </c>
@@ -4868,7 +4863,7 @@
       <c r="H154" s="11"/>
       <c r="I154" s="11"/>
     </row>
-    <row r="155" spans="1:9">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>145</v>
       </c>
@@ -4894,7 +4889,7 @@
       <c r="H155" s="11"/>
       <c r="I155" s="11"/>
     </row>
-    <row r="156" spans="1:9">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>146</v>
       </c>
@@ -4920,7 +4915,7 @@
       <c r="H156" s="11"/>
       <c r="I156" s="11"/>
     </row>
-    <row r="157" spans="1:9">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>147</v>
       </c>
@@ -4946,7 +4941,7 @@
       <c r="H157" s="11"/>
       <c r="I157" s="11"/>
     </row>
-    <row r="158" spans="1:9">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>148</v>
       </c>
@@ -4972,7 +4967,7 @@
       <c r="H158" s="11"/>
       <c r="I158" s="11"/>
     </row>
-    <row r="159" spans="1:9">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>149</v>
       </c>
@@ -4998,7 +4993,7 @@
       <c r="H159" s="11"/>
       <c r="I159" s="11"/>
     </row>
-    <row r="160" spans="1:9">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>150</v>
       </c>
@@ -5024,7 +5019,7 @@
       <c r="H160" s="11"/>
       <c r="I160" s="11"/>
     </row>
-    <row r="161" spans="1:9">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>151</v>
       </c>
@@ -5050,7 +5045,7 @@
       <c r="H161" s="11"/>
       <c r="I161" s="11"/>
     </row>
-    <row r="162" spans="1:9">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>152</v>
       </c>
@@ -5076,7 +5071,7 @@
       <c r="H162" s="11"/>
       <c r="I162" s="11"/>
     </row>
-    <row r="163" spans="1:9">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>153</v>
       </c>
@@ -5102,7 +5097,7 @@
       <c r="H163" s="11"/>
       <c r="I163" s="11"/>
     </row>
-    <row r="164" spans="1:9">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>154</v>
       </c>
@@ -5128,7 +5123,7 @@
       <c r="H164" s="11"/>
       <c r="I164" s="11"/>
     </row>
-    <row r="165" spans="1:9">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>155</v>
       </c>
@@ -5154,7 +5149,7 @@
       <c r="H165" s="11"/>
       <c r="I165" s="11"/>
     </row>
-    <row r="166" spans="1:9">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>156</v>
       </c>
@@ -5180,7 +5175,7 @@
       <c r="H166" s="11"/>
       <c r="I166" s="11"/>
     </row>
-    <row r="167" spans="1:9">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>157</v>
       </c>
@@ -5206,7 +5201,7 @@
       <c r="H167" s="11"/>
       <c r="I167" s="11"/>
     </row>
-    <row r="168" spans="1:9">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>158</v>
       </c>
@@ -5232,7 +5227,7 @@
       <c r="H168" s="11"/>
       <c r="I168" s="11"/>
     </row>
-    <row r="169" spans="1:9">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>159</v>
       </c>
@@ -5258,7 +5253,7 @@
       <c r="H169" s="11"/>
       <c r="I169" s="11"/>
     </row>
-    <row r="170" spans="1:9">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>160</v>
       </c>
@@ -5284,7 +5279,7 @@
       <c r="H170" s="11"/>
       <c r="I170" s="11"/>
     </row>
-    <row r="171" spans="1:9">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>161</v>
       </c>
@@ -5310,7 +5305,7 @@
       <c r="H171" s="11"/>
       <c r="I171" s="11"/>
     </row>
-    <row r="172" spans="1:9">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>162</v>
       </c>
@@ -5336,7 +5331,7 @@
       <c r="H172" s="11"/>
       <c r="I172" s="11"/>
     </row>
-    <row r="173" spans="1:9">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>163</v>
       </c>
@@ -5362,7 +5357,7 @@
       <c r="H173" s="11"/>
       <c r="I173" s="11"/>
     </row>
-    <row r="174" spans="1:9">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>164</v>
       </c>
@@ -5388,7 +5383,7 @@
       <c r="H174" s="11"/>
       <c r="I174" s="11"/>
     </row>
-    <row r="175" spans="1:9">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>165</v>
       </c>
@@ -5414,7 +5409,7 @@
       <c r="H175" s="11"/>
       <c r="I175" s="11"/>
     </row>
-    <row r="176" spans="1:9">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>166</v>
       </c>
@@ -5440,7 +5435,7 @@
       <c r="H176" s="11"/>
       <c r="I176" s="11"/>
     </row>
-    <row r="177" spans="1:9">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>167</v>
       </c>
@@ -5466,7 +5461,7 @@
       <c r="H177" s="11"/>
       <c r="I177" s="11"/>
     </row>
-    <row r="178" spans="1:9">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>168</v>
       </c>
@@ -5492,7 +5487,7 @@
       <c r="H178" s="11"/>
       <c r="I178" s="11"/>
     </row>
-    <row r="179" spans="1:9">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>169</v>
       </c>
@@ -5518,7 +5513,7 @@
       <c r="H179" s="11"/>
       <c r="I179" s="11"/>
     </row>
-    <row r="180" spans="1:9">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>170</v>
       </c>
@@ -5544,7 +5539,7 @@
       <c r="H180" s="11"/>
       <c r="I180" s="11"/>
     </row>
-    <row r="181" spans="1:9">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>171</v>
       </c>
@@ -5570,7 +5565,7 @@
       <c r="H181" s="11"/>
       <c r="I181" s="11"/>
     </row>
-    <row r="182" spans="1:9">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>172</v>
       </c>
@@ -5596,7 +5591,7 @@
       <c r="H182" s="11"/>
       <c r="I182" s="11"/>
     </row>
-    <row r="183" spans="1:9">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>173</v>
       </c>
@@ -5622,7 +5617,7 @@
       <c r="H183" s="11"/>
       <c r="I183" s="11"/>
     </row>
-    <row r="184" spans="1:9">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>174</v>
       </c>
@@ -5648,7 +5643,7 @@
       <c r="H184" s="11"/>
       <c r="I184" s="11"/>
     </row>
-    <row r="185" spans="1:9">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>175</v>
       </c>
@@ -5674,7 +5669,7 @@
       <c r="H185" s="11"/>
       <c r="I185" s="11"/>
     </row>
-    <row r="186" spans="1:9">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>176</v>
       </c>
@@ -5700,7 +5695,7 @@
       <c r="H186" s="11"/>
       <c r="I186" s="11"/>
     </row>
-    <row r="187" spans="1:9">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>177</v>
       </c>
@@ -5726,7 +5721,7 @@
       <c r="H187" s="11"/>
       <c r="I187" s="11"/>
     </row>
-    <row r="188" spans="1:9">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>178</v>
       </c>
@@ -5752,7 +5747,7 @@
       <c r="H188" s="11"/>
       <c r="I188" s="11"/>
     </row>
-    <row r="189" spans="1:9">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>179</v>
       </c>
@@ -5778,7 +5773,7 @@
       <c r="H189" s="11"/>
       <c r="I189" s="11"/>
     </row>
-    <row r="190" spans="1:9">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>180</v>
       </c>
@@ -5804,7 +5799,7 @@
       <c r="H190" s="11"/>
       <c r="I190" s="11"/>
     </row>
-    <row r="191" spans="1:9">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>181</v>
       </c>
@@ -5830,7 +5825,7 @@
       <c r="H191" s="11"/>
       <c r="I191" s="11"/>
     </row>
-    <row r="192" spans="1:9">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>182</v>
       </c>
@@ -5856,7 +5851,7 @@
       <c r="H192" s="11"/>
       <c r="I192" s="11"/>
     </row>
-    <row r="193" spans="1:9">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>183</v>
       </c>
@@ -5882,7 +5877,7 @@
       <c r="H193" s="11"/>
       <c r="I193" s="11"/>
     </row>
-    <row r="194" spans="1:9">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>184</v>
       </c>
@@ -5908,7 +5903,7 @@
       <c r="H194" s="11"/>
       <c r="I194" s="11"/>
     </row>
-    <row r="195" spans="1:9">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>185</v>
       </c>
@@ -5934,7 +5929,7 @@
       <c r="H195" s="11"/>
       <c r="I195" s="11"/>
     </row>
-    <row r="196" spans="1:9">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>186</v>
       </c>
@@ -5960,7 +5955,7 @@
       <c r="H196" s="11"/>
       <c r="I196" s="11"/>
     </row>
-    <row r="197" spans="1:9">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>187</v>
       </c>
@@ -5986,7 +5981,7 @@
       <c r="H197" s="11"/>
       <c r="I197" s="11"/>
     </row>
-    <row r="198" spans="1:9">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>188</v>
       </c>
@@ -6012,7 +6007,7 @@
       <c r="H198" s="11"/>
       <c r="I198" s="11"/>
     </row>
-    <row r="199" spans="1:9">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>189</v>
       </c>
@@ -6038,7 +6033,7 @@
       <c r="H199" s="11"/>
       <c r="I199" s="11"/>
     </row>
-    <row r="200" spans="1:9">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>190</v>
       </c>
@@ -6064,7 +6059,7 @@
       <c r="H200" s="11"/>
       <c r="I200" s="11"/>
     </row>
-    <row r="201" spans="1:9">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>191</v>
       </c>
@@ -6090,7 +6085,7 @@
       <c r="H201" s="11"/>
       <c r="I201" s="11"/>
     </row>
-    <row r="202" spans="1:9">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>192</v>
       </c>
@@ -6116,7 +6111,7 @@
       <c r="H202" s="11"/>
       <c r="I202" s="11"/>
     </row>
-    <row r="203" spans="1:9">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>193</v>
       </c>
@@ -6142,7 +6137,7 @@
       <c r="H203" s="11"/>
       <c r="I203" s="11"/>
     </row>
-    <row r="204" spans="1:9">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>194</v>
       </c>
@@ -6168,7 +6163,7 @@
       <c r="H204" s="11"/>
       <c r="I204" s="11"/>
     </row>
-    <row r="205" spans="1:9">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>195</v>
       </c>
@@ -6194,7 +6189,7 @@
       <c r="H205" s="11"/>
       <c r="I205" s="11"/>
     </row>
-    <row r="206" spans="1:9">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>196</v>
       </c>
@@ -6220,7 +6215,7 @@
       <c r="H206" s="11"/>
       <c r="I206" s="11"/>
     </row>
-    <row r="207" spans="1:9">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>197</v>
       </c>
@@ -6246,7 +6241,7 @@
       <c r="H207" s="11"/>
       <c r="I207" s="11"/>
     </row>
-    <row r="208" spans="1:9">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>198</v>
       </c>
@@ -6272,7 +6267,7 @@
       <c r="H208" s="11"/>
       <c r="I208" s="11"/>
     </row>
-    <row r="209" spans="1:9">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>199</v>
       </c>
@@ -6298,7 +6293,7 @@
       <c r="H209" s="11"/>
       <c r="I209" s="11"/>
     </row>
-    <row r="210" spans="1:9">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>200</v>
       </c>
@@ -6324,7 +6319,7 @@
       <c r="H210" s="11"/>
       <c r="I210" s="11"/>
     </row>
-    <row r="211" spans="1:9">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <v>201</v>
       </c>
@@ -6350,7 +6345,7 @@
       <c r="H211" s="11"/>
       <c r="I211" s="11"/>
     </row>
-    <row r="212" spans="1:9">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>202</v>
       </c>
@@ -6376,7 +6371,7 @@
       <c r="H212" s="11"/>
       <c r="I212" s="11"/>
     </row>
-    <row r="213" spans="1:9">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <v>203</v>
       </c>
@@ -6402,7 +6397,7 @@
       <c r="H213" s="11"/>
       <c r="I213" s="11"/>
     </row>
-    <row r="214" spans="1:9">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>204</v>
       </c>
@@ -6428,7 +6423,7 @@
       <c r="H214" s="11"/>
       <c r="I214" s="11"/>
     </row>
-    <row r="215" spans="1:9">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>205</v>
       </c>
@@ -6454,7 +6449,7 @@
       <c r="H215" s="11"/>
       <c r="I215" s="11"/>
     </row>
-    <row r="216" spans="1:9">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <v>206</v>
       </c>
@@ -6480,7 +6475,7 @@
       <c r="H216" s="11"/>
       <c r="I216" s="11"/>
     </row>
-    <row r="217" spans="1:9">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <v>207</v>
       </c>
@@ -6506,7 +6501,7 @@
       <c r="H217" s="11"/>
       <c r="I217" s="11"/>
     </row>
-    <row r="218" spans="1:9">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <v>208</v>
       </c>
@@ -6532,7 +6527,7 @@
       <c r="H218" s="11"/>
       <c r="I218" s="11"/>
     </row>
-    <row r="219" spans="1:9">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <v>209</v>
       </c>
@@ -6558,7 +6553,7 @@
       <c r="H219" s="11"/>
       <c r="I219" s="11"/>
     </row>
-    <row r="220" spans="1:9">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <v>210</v>
       </c>
@@ -6584,7 +6579,7 @@
       <c r="H220" s="11"/>
       <c r="I220" s="11"/>
     </row>
-    <row r="221" spans="1:9">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <v>211</v>
       </c>
@@ -6610,7 +6605,7 @@
       <c r="H221" s="11"/>
       <c r="I221" s="11"/>
     </row>
-    <row r="222" spans="1:9">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <v>212</v>
       </c>
@@ -6636,7 +6631,7 @@
       <c r="H222" s="11"/>
       <c r="I222" s="11"/>
     </row>
-    <row r="223" spans="1:9">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <v>213</v>
       </c>
@@ -6662,7 +6657,7 @@
       <c r="H223" s="11"/>
       <c r="I223" s="11"/>
     </row>
-    <row r="224" spans="1:9">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <v>214</v>
       </c>
@@ -6688,7 +6683,7 @@
       <c r="H224" s="11"/>
       <c r="I224" s="11"/>
     </row>
-    <row r="225" spans="1:9">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>215</v>
       </c>
@@ -6714,7 +6709,7 @@
       <c r="H225" s="11"/>
       <c r="I225" s="11"/>
     </row>
-    <row r="226" spans="1:9">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <v>216</v>
       </c>
@@ -6740,7 +6735,7 @@
       <c r="H226" s="11"/>
       <c r="I226" s="11"/>
     </row>
-    <row r="227" spans="1:9">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
         <v>217</v>
       </c>
@@ -6766,7 +6761,7 @@
       <c r="H227" s="11"/>
       <c r="I227" s="11"/>
     </row>
-    <row r="228" spans="1:9">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <v>218</v>
       </c>
@@ -6792,7 +6787,7 @@
       <c r="H228" s="11"/>
       <c r="I228" s="11"/>
     </row>
-    <row r="229" spans="1:9">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <v>219</v>
       </c>
@@ -6818,7 +6813,7 @@
       <c r="H229" s="11"/>
       <c r="I229" s="11"/>
     </row>
-    <row r="230" spans="1:9">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <v>220</v>
       </c>
@@ -6844,7 +6839,7 @@
       <c r="H230" s="11"/>
       <c r="I230" s="11"/>
     </row>
-    <row r="231" spans="1:9">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
         <v>221</v>
       </c>
@@ -6870,7 +6865,7 @@
       <c r="H231" s="11"/>
       <c r="I231" s="11"/>
     </row>
-    <row r="232" spans="1:9">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
         <v>222</v>
       </c>
@@ -6896,7 +6891,7 @@
       <c r="H232" s="11"/>
       <c r="I232" s="11"/>
     </row>
-    <row r="233" spans="1:9">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <v>223</v>
       </c>
@@ -6922,7 +6917,7 @@
       <c r="H233" s="11"/>
       <c r="I233" s="11"/>
     </row>
-    <row r="234" spans="1:9">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <v>224</v>
       </c>
@@ -6948,7 +6943,7 @@
       <c r="H234" s="11"/>
       <c r="I234" s="11"/>
     </row>
-    <row r="235" spans="1:9">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <v>225</v>
       </c>
@@ -6974,7 +6969,7 @@
       <c r="H235" s="11"/>
       <c r="I235" s="11"/>
     </row>
-    <row r="236" spans="1:9">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <v>226</v>
       </c>
@@ -7000,7 +6995,7 @@
       <c r="H236" s="11"/>
       <c r="I236" s="11"/>
     </row>
-    <row r="237" spans="1:9">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <v>227</v>
       </c>
@@ -7026,7 +7021,7 @@
       <c r="H237" s="11"/>
       <c r="I237" s="11"/>
     </row>
-    <row r="238" spans="1:9">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <v>228</v>
       </c>
@@ -7052,7 +7047,7 @@
       <c r="H238" s="11"/>
       <c r="I238" s="11"/>
     </row>
-    <row r="239" spans="1:9">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <v>229</v>
       </c>
@@ -7078,7 +7073,7 @@
       <c r="H239" s="11"/>
       <c r="I239" s="11"/>
     </row>
-    <row r="240" spans="1:9">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <v>230</v>
       </c>
@@ -7104,7 +7099,7 @@
       <c r="H240" s="11"/>
       <c r="I240" s="11"/>
     </row>
-    <row r="241" spans="1:9">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
         <v>231</v>
       </c>
@@ -7130,7 +7125,7 @@
       <c r="H241" s="11"/>
       <c r="I241" s="11"/>
     </row>
-    <row r="242" spans="1:9">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
         <v>232</v>
       </c>
@@ -7156,7 +7151,7 @@
       <c r="H242" s="11"/>
       <c r="I242" s="11"/>
     </row>
-    <row r="243" spans="1:9">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
         <v>233</v>
       </c>
@@ -7182,7 +7177,7 @@
       <c r="H243" s="11"/>
       <c r="I243" s="11"/>
     </row>
-    <row r="244" spans="1:9">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
         <v>234</v>
       </c>
@@ -7208,7 +7203,7 @@
       <c r="H244" s="11"/>
       <c r="I244" s="11"/>
     </row>
-    <row r="245" spans="1:9">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
         <v>235</v>
       </c>
@@ -7234,7 +7229,7 @@
       <c r="H245" s="11"/>
       <c r="I245" s="11"/>
     </row>
-    <row r="246" spans="1:9">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
         <v>236</v>
       </c>
@@ -7260,7 +7255,7 @@
       <c r="H246" s="11"/>
       <c r="I246" s="11"/>
     </row>
-    <row r="247" spans="1:9">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
         <v>237</v>
       </c>
@@ -7286,7 +7281,7 @@
       <c r="H247" s="11"/>
       <c r="I247" s="11"/>
     </row>
-    <row r="248" spans="1:9">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <v>238</v>
       </c>
@@ -7312,7 +7307,7 @@
       <c r="H248" s="11"/>
       <c r="I248" s="11"/>
     </row>
-    <row r="249" spans="1:9">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
         <v>239</v>
       </c>
@@ -7338,7 +7333,7 @@
       <c r="H249" s="11"/>
       <c r="I249" s="11"/>
     </row>
-    <row r="250" spans="1:9">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
         <v>240</v>
       </c>
@@ -7364,7 +7359,7 @@
       <c r="H250" s="11"/>
       <c r="I250" s="11"/>
     </row>
-    <row r="251" spans="1:9">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
         <v>241</v>
       </c>
@@ -7390,7 +7385,7 @@
       <c r="H251" s="11"/>
       <c r="I251" s="11"/>
     </row>
-    <row r="252" spans="1:9">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
         <v>242</v>
       </c>
@@ -7416,7 +7411,7 @@
       <c r="H252" s="11"/>
       <c r="I252" s="11"/>
     </row>
-    <row r="253" spans="1:9">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
         <v>243</v>
       </c>
@@ -7442,7 +7437,7 @@
       <c r="H253" s="11"/>
       <c r="I253" s="11"/>
     </row>
-    <row r="254" spans="1:9">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
         <v>244</v>
       </c>
@@ -7468,7 +7463,7 @@
       <c r="H254" s="11"/>
       <c r="I254" s="11"/>
     </row>
-    <row r="255" spans="1:9">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
         <v>245</v>
       </c>
@@ -7494,7 +7489,7 @@
       <c r="H255" s="11"/>
       <c r="I255" s="11"/>
     </row>
-    <row r="256" spans="1:9">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
         <v>246</v>
       </c>
@@ -7520,7 +7515,7 @@
       <c r="H256" s="11"/>
       <c r="I256" s="11"/>
     </row>
-    <row r="257" spans="1:9">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
         <v>247</v>
       </c>
@@ -7546,7 +7541,7 @@
       <c r="H257" s="11"/>
       <c r="I257" s="11"/>
     </row>
-    <row r="258" spans="1:9">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
         <v>248</v>
       </c>
@@ -7572,7 +7567,7 @@
       <c r="H258" s="11"/>
       <c r="I258" s="11"/>
     </row>
-    <row r="259" spans="1:9">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
         <v>249</v>
       </c>
@@ -7598,7 +7593,7 @@
       <c r="H259" s="11"/>
       <c r="I259" s="11"/>
     </row>
-    <row r="260" spans="1:9">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
         <v>250</v>
       </c>
@@ -7624,7 +7619,7 @@
       <c r="H260" s="11"/>
       <c r="I260" s="11"/>
     </row>
-    <row r="261" spans="1:9">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
         <v>251</v>
       </c>
@@ -7650,7 +7645,7 @@
       <c r="H261" s="11"/>
       <c r="I261" s="11"/>
     </row>
-    <row r="262" spans="1:9">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
         <v>252</v>
       </c>
@@ -7676,7 +7671,7 @@
       <c r="H262" s="11"/>
       <c r="I262" s="11"/>
     </row>
-    <row r="263" spans="1:9">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
         <v>253</v>
       </c>
@@ -7702,7 +7697,7 @@
       <c r="H263" s="11"/>
       <c r="I263" s="11"/>
     </row>
-    <row r="264" spans="1:9">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
         <v>254</v>
       </c>
@@ -7728,7 +7723,7 @@
       <c r="H264" s="11"/>
       <c r="I264" s="11"/>
     </row>
-    <row r="265" spans="1:9">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
         <v>255</v>
       </c>
@@ -7754,7 +7749,7 @@
       <c r="H265" s="11"/>
       <c r="I265" s="11"/>
     </row>
-    <row r="266" spans="1:9">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
         <v>256</v>
       </c>
@@ -7780,7 +7775,7 @@
       <c r="H266" s="11"/>
       <c r="I266" s="11"/>
     </row>
-    <row r="267" spans="1:9">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
         <v>257</v>
       </c>
@@ -7806,7 +7801,7 @@
       <c r="H267" s="11"/>
       <c r="I267" s="11"/>
     </row>
-    <row r="268" spans="1:9">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
         <v>258</v>
       </c>
@@ -7832,7 +7827,7 @@
       <c r="H268" s="11"/>
       <c r="I268" s="11"/>
     </row>
-    <row r="269" spans="1:9">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
         <v>259</v>
       </c>
@@ -7858,7 +7853,7 @@
       <c r="H269" s="11"/>
       <c r="I269" s="11"/>
     </row>
-    <row r="270" spans="1:9">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
         <v>260</v>
       </c>
@@ -7884,7 +7879,7 @@
       <c r="H270" s="11"/>
       <c r="I270" s="11"/>
     </row>
-    <row r="271" spans="1:9">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
         <v>261</v>
       </c>
@@ -7910,7 +7905,7 @@
       <c r="H271" s="11"/>
       <c r="I271" s="11"/>
     </row>
-    <row r="272" spans="1:9">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
         <v>262</v>
       </c>
@@ -7936,7 +7931,7 @@
       <c r="H272" s="11"/>
       <c r="I272" s="11"/>
     </row>
-    <row r="273" spans="1:9">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
         <v>263</v>
       </c>
@@ -7962,7 +7957,7 @@
       <c r="H273" s="11"/>
       <c r="I273" s="11"/>
     </row>
-    <row r="274" spans="1:9">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
         <v>264</v>
       </c>
@@ -7988,7 +7983,7 @@
       <c r="H274" s="11"/>
       <c r="I274" s="11"/>
     </row>
-    <row r="275" spans="1:9">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
         <v>265</v>
       </c>
@@ -8014,7 +8009,7 @@
       <c r="H275" s="11"/>
       <c r="I275" s="11"/>
     </row>
-    <row r="276" spans="1:9">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
         <v>266</v>
       </c>
@@ -8040,7 +8035,7 @@
       <c r="H276" s="11"/>
       <c r="I276" s="11"/>
     </row>
-    <row r="277" spans="1:9">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
         <v>267</v>
       </c>
@@ -8066,7 +8061,7 @@
       <c r="H277" s="11"/>
       <c r="I277" s="11"/>
     </row>
-    <row r="278" spans="1:9">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
         <v>268</v>
       </c>
@@ -8092,7 +8087,7 @@
       <c r="H278" s="11"/>
       <c r="I278" s="11"/>
     </row>
-    <row r="279" spans="1:9">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
         <v>269</v>
       </c>
@@ -8118,7 +8113,7 @@
       <c r="H279" s="11"/>
       <c r="I279" s="11"/>
     </row>
-    <row r="280" spans="1:9">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
         <v>270</v>
       </c>
@@ -8144,7 +8139,7 @@
       <c r="H280" s="11"/>
       <c r="I280" s="11"/>
     </row>
-    <row r="281" spans="1:9">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
         <v>271</v>
       </c>
@@ -8170,7 +8165,7 @@
       <c r="H281" s="11"/>
       <c r="I281" s="11"/>
     </row>
-    <row r="282" spans="1:9">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
         <v>272</v>
       </c>
@@ -8196,7 +8191,7 @@
       <c r="H282" s="11"/>
       <c r="I282" s="11"/>
     </row>
-    <row r="283" spans="1:9">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
         <v>273</v>
       </c>
@@ -8222,7 +8217,7 @@
       <c r="H283" s="11"/>
       <c r="I283" s="11"/>
     </row>
-    <row r="284" spans="1:9">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
         <v>274</v>
       </c>
@@ -8248,7 +8243,7 @@
       <c r="H284" s="11"/>
       <c r="I284" s="11"/>
     </row>
-    <row r="285" spans="1:9">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
         <v>275</v>
       </c>
@@ -8274,7 +8269,7 @@
       <c r="H285" s="11"/>
       <c r="I285" s="11"/>
     </row>
-    <row r="286" spans="1:9">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
         <v>276</v>
       </c>
@@ -8304,7 +8299,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="287" spans="1:9">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
         <v>277</v>
       </c>
@@ -8334,7 +8329,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="288" spans="1:9">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
         <v>278</v>
       </c>
@@ -8364,7 +8359,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="289" spans="1:9">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
         <v>279</v>
       </c>
@@ -8394,7 +8389,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="290" spans="1:9">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
         <v>280</v>
       </c>
@@ -8424,7 +8419,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="291" spans="1:9">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
         <v>281</v>
       </c>
@@ -8454,7 +8449,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="292" spans="1:9">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
         <v>282</v>
       </c>
@@ -8484,7 +8479,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="293" spans="1:9">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
         <v>283</v>
       </c>
@@ -8514,7 +8509,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="294" spans="1:9">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
         <v>284</v>
       </c>
@@ -8544,7 +8539,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="295" spans="1:9">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
         <v>285</v>
       </c>
@@ -8574,7 +8569,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="296" spans="1:9">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
         <v>286</v>
       </c>
@@ -8604,7 +8599,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="297" spans="1:9">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
         <v>287</v>
       </c>
@@ -8634,7 +8629,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="298" spans="1:9">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
         <v>288</v>
       </c>
@@ -8664,7 +8659,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="299" spans="1:9">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
         <v>289</v>
       </c>
@@ -8694,7 +8689,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="300" spans="1:9">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
         <v>290</v>
       </c>
@@ -8724,7 +8719,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="301" spans="1:9">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
         <v>291</v>
       </c>
@@ -8754,7 +8749,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="302" spans="1:9">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
         <v>292</v>
       </c>
@@ -8784,7 +8779,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="303" spans="1:9" s="1" customFormat="1">
+    <row r="303" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
         <v>293</v>
       </c>
@@ -8814,7 +8809,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="304" spans="1:9" s="1" customFormat="1">
+    <row r="304" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
         <v>294</v>
       </c>
@@ -8844,7 +8839,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="305" spans="1:9">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
         <v>295</v>
       </c>
@@ -8874,7 +8869,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="306" spans="1:9">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
         <v>296</v>
       </c>
@@ -8904,7 +8899,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="307" spans="1:9">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
         <v>297</v>
       </c>
@@ -8934,7 +8929,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="308" spans="1:9">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
         <v>298</v>
       </c>
@@ -8964,73 +8959,73 @@
         <v>56</v>
       </c>
     </row>
-    <row r="309" spans="1:9">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" s="1"/>
     </row>
-    <row r="310" spans="1:9">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" s="1"/>
     </row>
-    <row r="311" spans="1:9">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" s="1"/>
     </row>
-    <row r="312" spans="1:9">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" s="1"/>
     </row>
-    <row r="313" spans="1:9">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" s="1"/>
     </row>
-    <row r="314" spans="1:9">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" s="1"/>
     </row>
-    <row r="315" spans="1:9">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" s="1"/>
     </row>
-    <row r="316" spans="1:9">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" s="1"/>
     </row>
-    <row r="317" spans="1:9">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" s="1"/>
     </row>
-    <row r="318" spans="1:9">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" s="1"/>
     </row>
-    <row r="319" spans="1:9">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" s="1"/>
     </row>
-    <row r="320" spans="1:9">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" s="1"/>
     </row>
-    <row r="321" spans="1:1">
+    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A321" s="1"/>
     </row>
-    <row r="322" spans="1:1">
+    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A322" s="1"/>
     </row>
-    <row r="323" spans="1:1">
+    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>
     </row>
-    <row r="324" spans="1:1">
+    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A324" s="1"/>
     </row>
-    <row r="325" spans="1:1">
+    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A325" s="1"/>
     </row>
-    <row r="326" spans="1:1">
+    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A326" s="1"/>
     </row>
-    <row r="327" spans="1:1">
+    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
     </row>
-    <row r="328" spans="1:1">
+    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A328" s="1"/>
     </row>
-    <row r="329" spans="1:1">
+    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A329" s="1"/>
     </row>
-    <row r="330" spans="1:1">
+    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>
     </row>
-    <row r="331" spans="1:1">
+    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A331" s="1"/>
     </row>
   </sheetData>
@@ -9052,13 +9047,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{797F1036-D41E-43A4-9E6E-CBBB62F3CD31}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="13.28515625" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9072,7 +9067,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -9086,7 +9081,7 @@
         <v>234.67</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -9100,7 +9095,7 @@
         <v>161.15</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -9114,7 +9109,7 @@
         <v>157.61000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -9128,7 +9123,7 @@
         <v>347.95</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -9142,7 +9137,7 @@
         <v>393.57</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -9156,7 +9151,7 @@
         <v>19.87</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -9170,7 +9165,7 @@
         <v>19.57</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>61</v>
       </c>
@@ -9184,7 +9179,7 @@
         <v>19.86</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -9198,7 +9193,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -9222,8 +9217,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56220E0F-EC16-4A8C-9E04-C7F8849C4B4D}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
@@ -9231,7 +9226,7 @@
     <col min="5" max="5" width="30.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9247,8 +9242,11 @@
       <c r="E1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="G1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -9265,7 +9263,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -9282,7 +9280,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -9299,7 +9297,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -9316,7 +9314,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -9333,7 +9331,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -9350,7 +9348,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -9378,14 +9376,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83DAFC4B-C207-418A-8501-0E1EC9E673B7}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9396,7 +9394,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -9407,7 +9405,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -9418,7 +9416,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -9429,7 +9427,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>61</v>
       </c>
@@ -9440,7 +9438,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -9451,7 +9449,7 @@
         <v>46631</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -9462,7 +9460,7 @@
         <v>48579</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -9473,7 +9471,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -9484,7 +9482,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -9495,7 +9493,7 @@
         <v>48579</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -9529,15 +9527,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100FB7AAE8C8816FD47B559A0CCF555AFF0" ma:contentTypeVersion="10" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5c9910934a78ddf693a6b708b52e9b37">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f95d585e-e7a7-414c-955d-38a47c8579bd" xmlns:ns3="33ab045e-9213-4eea-a9f2-a5b809105d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a9c61c95b4e11caed4e46447c2ca01e7" ns2:_="" ns3:_="">
     <xsd:import namespace="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
@@ -9740,16 +9729,57 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
+    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="851" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F98DAED3-7D28-4389-9118-EA4B08D88D0A}"/>
+  <xr:revisionPtr revIDLastSave="857" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16D657B8-4F27-4CE4-B140-B8BA0DAE14CC}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="3180" windowWidth="21600" windowHeight="11085" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="-25935" yWindow="5655" windowWidth="21600" windowHeight="11085" firstSheet="2" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -273,7 +273,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -357,17 +357,27 @@
   </cellStyles>
   <dxfs count="12">
     <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -386,16 +396,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -688,23 +688,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:I308" totalsRowShown="0" headerRowDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:I308" totalsRowShown="0" headerRowDxfId="11">
   <autoFilter ref="A10:I308" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
   <tableColumns count="9">
     <tableColumn id="3" xr3:uid="{AFE823F6-980E-4E32-B4F4-6ECDE10F377D}" name="ID"/>
-    <tableColumn id="1" xr3:uid="{CD000998-6E2C-4963-8605-37081D9C1A64}" name="Unidad" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{542F6635-555D-4F04-8C27-263AF6E0C9F1}" name="Sitio" dataDxfId="6">
+    <tableColumn id="1" xr3:uid="{CD000998-6E2C-4963-8605-37081D9C1A64}" name="Unidad" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{542F6635-555D-4F04-8C27-263AF6E0C9F1}" name="Sitio" dataDxfId="9">
       <calculatedColumnFormula>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6D2AC534-BC70-4E36-815D-053C7EC9A0CE}" name="Carga_Disponible" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{FBB18F6C-27E4-42D9-9835-9152B6D0D871}" name="Estado_Op" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{21A32989-F167-49C0-9D41-2BD3A8923998}" name="Fecha_Hora_Inicio" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{713F74B7-95D9-4F96-AA1E-57E68B8A7FE7}" name="Fecha_Hora_Final" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{20481209-2CB3-4DCC-A330-D866983AA4F9}" name="Motivo" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{55FF6738-9798-4086-9AA1-DC8A3EF8081F}" name="Detalle" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{6D2AC534-BC70-4E36-815D-053C7EC9A0CE}" name="Carga_Disponible" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{FBB18F6C-27E4-42D9-9835-9152B6D0D871}" name="Estado_Op" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{21A32989-F167-49C0-9D41-2BD3A8923998}" name="Fecha_Hora_Inicio" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{713F74B7-95D9-4F96-AA1E-57E68B8A7FE7}" name="Fecha_Hora_Final" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{20481209-2CB3-4DCC-A330-D866983AA4F9}" name="Motivo" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{55FF6738-9798-4086-9AA1-DC8A3EF8081F}" name="Detalle" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -731,9 +731,9 @@
   </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{1EEE0FFC-B699-4850-9A13-72CF6FB78CA6}" name="Unidad"/>
-    <tableColumn id="2" xr3:uid="{BDB3B76C-8D9D-4A32-9C94-204172B9E68C}" name="Fecha_Hora_Inicio" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{A21A7F07-F50E-4006-B601-758B5E8BD7BE}" name="Fecha_Hora_Fin" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{F49EC928-7A7A-47BB-9275-EDE8B8DF6BC7}" name="Días_de_Mantenimiento" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{BDB3B76C-8D9D-4A32-9C94-204172B9E68C}" name="Fecha_Hora_Inicio" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{A21A7F07-F50E-4006-B601-758B5E8BD7BE}" name="Fecha_Hora_Fin" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{F49EC928-7A7A-47BB-9275-EDE8B8DF6BC7}" name="Días_de_Mantenimiento" dataDxfId="0"/>
     <tableColumn id="5" xr3:uid="{E5C19B72-F1F0-4F1D-9466-99048BCEFC0C}" name="Motivo"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1069,8 +1069,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
-  <dimension ref="A9:I331"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A3:I331"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
@@ -1084,13 +1084,18 @@
     <col min="12" max="12" width="33.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9">
+      <c r="H3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
         <v>298</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1119,7 +1124,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -1145,7 +1150,7 @@
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -1171,7 +1176,7 @@
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9">
       <c r="A13" s="1">
         <v>3</v>
       </c>
@@ -1197,7 +1202,7 @@
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9">
       <c r="A14" s="1">
         <v>4</v>
       </c>
@@ -1223,7 +1228,7 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>5</v>
       </c>
@@ -1249,7 +1254,7 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9">
       <c r="A16" s="1">
         <v>6</v>
       </c>
@@ -1275,7 +1280,7 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9">
       <c r="A17" s="1">
         <v>7</v>
       </c>
@@ -1301,7 +1306,7 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9">
       <c r="A18" s="1">
         <v>8</v>
       </c>
@@ -1327,7 +1332,7 @@
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9">
       <c r="A19" s="1">
         <v>9</v>
       </c>
@@ -1353,7 +1358,7 @@
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9">
       <c r="A20" s="1">
         <v>10</v>
       </c>
@@ -1379,7 +1384,7 @@
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9">
       <c r="A21" s="1">
         <v>11</v>
       </c>
@@ -1405,7 +1410,7 @@
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9">
       <c r="A22" s="1">
         <v>12</v>
       </c>
@@ -1431,7 +1436,7 @@
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9">
       <c r="A23" s="1">
         <v>13</v>
       </c>
@@ -1457,7 +1462,7 @@
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9">
       <c r="A24" s="1">
         <v>14</v>
       </c>
@@ -1483,7 +1488,7 @@
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9">
       <c r="A25" s="1">
         <v>15</v>
       </c>
@@ -1509,7 +1514,7 @@
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9">
       <c r="A26" s="1">
         <v>16</v>
       </c>
@@ -1535,7 +1540,7 @@
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9">
       <c r="A27" s="1">
         <v>17</v>
       </c>
@@ -1561,7 +1566,7 @@
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9">
       <c r="A28" s="1">
         <v>18</v>
       </c>
@@ -1587,7 +1592,7 @@
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9">
       <c r="A29" s="1">
         <v>19</v>
       </c>
@@ -1613,7 +1618,7 @@
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9">
       <c r="A30" s="1">
         <v>20</v>
       </c>
@@ -1639,7 +1644,7 @@
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9">
       <c r="A31" s="1">
         <v>21</v>
       </c>
@@ -1665,7 +1670,7 @@
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9">
       <c r="A32" s="1">
         <v>22</v>
       </c>
@@ -1691,7 +1696,7 @@
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9">
       <c r="A33" s="1">
         <v>23</v>
       </c>
@@ -1717,7 +1722,7 @@
       <c r="H33" s="11"/>
       <c r="I33" s="11"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9">
       <c r="A34" s="1">
         <v>24</v>
       </c>
@@ -1743,7 +1748,7 @@
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9">
       <c r="A35" s="1">
         <v>25</v>
       </c>
@@ -1769,7 +1774,7 @@
       <c r="H35" s="11"/>
       <c r="I35" s="11"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9">
       <c r="A36" s="1">
         <v>26</v>
       </c>
@@ -1795,7 +1800,7 @@
       <c r="H36" s="11"/>
       <c r="I36" s="11"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9">
       <c r="A37" s="1">
         <v>27</v>
       </c>
@@ -1821,7 +1826,7 @@
       <c r="H37" s="11"/>
       <c r="I37" s="11"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9">
       <c r="A38" s="1">
         <v>28</v>
       </c>
@@ -1847,7 +1852,7 @@
       <c r="H38" s="11"/>
       <c r="I38" s="11"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9">
       <c r="A39" s="1">
         <v>29</v>
       </c>
@@ -1873,7 +1878,7 @@
       <c r="H39" s="11"/>
       <c r="I39" s="11"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9">
       <c r="A40" s="1">
         <v>30</v>
       </c>
@@ -1899,7 +1904,7 @@
       <c r="H40" s="11"/>
       <c r="I40" s="11"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9">
       <c r="A41" s="1">
         <v>31</v>
       </c>
@@ -1925,7 +1930,7 @@
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9">
       <c r="A42" s="1">
         <v>32</v>
       </c>
@@ -1951,7 +1956,7 @@
       <c r="H42" s="11"/>
       <c r="I42" s="11"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9">
       <c r="A43" s="1">
         <v>33</v>
       </c>
@@ -1977,7 +1982,7 @@
       <c r="H43" s="11"/>
       <c r="I43" s="11"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9">
       <c r="A44" s="1">
         <v>34</v>
       </c>
@@ -2003,7 +2008,7 @@
       <c r="H44" s="11"/>
       <c r="I44" s="11"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9">
       <c r="A45" s="1">
         <v>35</v>
       </c>
@@ -2029,7 +2034,7 @@
       <c r="H45" s="11"/>
       <c r="I45" s="11"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9">
       <c r="A46" s="1">
         <v>36</v>
       </c>
@@ -2055,7 +2060,7 @@
       <c r="H46" s="11"/>
       <c r="I46" s="11"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9">
       <c r="A47" s="1">
         <v>37</v>
       </c>
@@ -2081,7 +2086,7 @@
       <c r="H47" s="11"/>
       <c r="I47" s="11"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9">
       <c r="A48" s="1">
         <v>38</v>
       </c>
@@ -2107,7 +2112,7 @@
       <c r="H48" s="11"/>
       <c r="I48" s="11"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9">
       <c r="A49" s="1">
         <v>39</v>
       </c>
@@ -2133,7 +2138,7 @@
       <c r="H49" s="11"/>
       <c r="I49" s="11"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9">
       <c r="A50" s="1">
         <v>40</v>
       </c>
@@ -2159,7 +2164,7 @@
       <c r="H50" s="11"/>
       <c r="I50" s="11"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9">
       <c r="A51" s="1">
         <v>41</v>
       </c>
@@ -2185,7 +2190,7 @@
       <c r="H51" s="11"/>
       <c r="I51" s="11"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9">
       <c r="A52" s="1">
         <v>42</v>
       </c>
@@ -2211,7 +2216,7 @@
       <c r="H52" s="11"/>
       <c r="I52" s="11"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9">
       <c r="A53" s="1">
         <v>43</v>
       </c>
@@ -2237,7 +2242,7 @@
       <c r="H53" s="11"/>
       <c r="I53" s="11"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9">
       <c r="A54" s="1">
         <v>44</v>
       </c>
@@ -2263,7 +2268,7 @@
       <c r="H54" s="11"/>
       <c r="I54" s="11"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9">
       <c r="A55" s="1">
         <v>45</v>
       </c>
@@ -2289,7 +2294,7 @@
       <c r="H55" s="11"/>
       <c r="I55" s="11"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9">
       <c r="A56" s="1">
         <v>46</v>
       </c>
@@ -2315,7 +2320,7 @@
       <c r="H56" s="11"/>
       <c r="I56" s="11"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9">
       <c r="A57" s="1">
         <v>47</v>
       </c>
@@ -2341,7 +2346,7 @@
       <c r="H57" s="11"/>
       <c r="I57" s="11"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9">
       <c r="A58" s="1">
         <v>48</v>
       </c>
@@ -2367,7 +2372,7 @@
       <c r="H58" s="11"/>
       <c r="I58" s="11"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9">
       <c r="A59" s="1">
         <v>49</v>
       </c>
@@ -2393,7 +2398,7 @@
       <c r="H59" s="11"/>
       <c r="I59" s="11"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9">
       <c r="A60" s="1">
         <v>50</v>
       </c>
@@ -2419,7 +2424,7 @@
       <c r="H60" s="11"/>
       <c r="I60" s="11"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9">
       <c r="A61" s="1">
         <v>51</v>
       </c>
@@ -2445,7 +2450,7 @@
       <c r="H61" s="11"/>
       <c r="I61" s="11"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9">
       <c r="A62" s="1">
         <v>52</v>
       </c>
@@ -2471,7 +2476,7 @@
       <c r="H62" s="11"/>
       <c r="I62" s="11"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9">
       <c r="A63" s="1">
         <v>53</v>
       </c>
@@ -2497,7 +2502,7 @@
       <c r="H63" s="11"/>
       <c r="I63" s="11"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9">
       <c r="A64" s="1">
         <v>54</v>
       </c>
@@ -2523,7 +2528,7 @@
       <c r="H64" s="11"/>
       <c r="I64" s="11"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9">
       <c r="A65" s="1">
         <v>55</v>
       </c>
@@ -2549,7 +2554,7 @@
       <c r="H65" s="11"/>
       <c r="I65" s="11"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9">
       <c r="A66" s="1">
         <v>56</v>
       </c>
@@ -2575,7 +2580,7 @@
       <c r="H66" s="11"/>
       <c r="I66" s="11"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9">
       <c r="A67" s="1">
         <v>57</v>
       </c>
@@ -2601,7 +2606,7 @@
       <c r="H67" s="11"/>
       <c r="I67" s="11"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9">
       <c r="A68" s="1">
         <v>58</v>
       </c>
@@ -2627,7 +2632,7 @@
       <c r="H68" s="11"/>
       <c r="I68" s="11"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9">
       <c r="A69" s="1">
         <v>59</v>
       </c>
@@ -2653,7 +2658,7 @@
       <c r="H69" s="11"/>
       <c r="I69" s="11"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9">
       <c r="A70" s="1">
         <v>60</v>
       </c>
@@ -2679,7 +2684,7 @@
       <c r="H70" s="11"/>
       <c r="I70" s="11"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9">
       <c r="A71" s="1">
         <v>61</v>
       </c>
@@ -2705,7 +2710,7 @@
       <c r="H71" s="11"/>
       <c r="I71" s="11"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9">
       <c r="A72" s="1">
         <v>62</v>
       </c>
@@ -2731,7 +2736,7 @@
       <c r="H72" s="11"/>
       <c r="I72" s="11"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9">
       <c r="A73" s="1">
         <v>63</v>
       </c>
@@ -2757,7 +2762,7 @@
       <c r="H73" s="11"/>
       <c r="I73" s="11"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9">
       <c r="A74" s="1">
         <v>64</v>
       </c>
@@ -2783,7 +2788,7 @@
       <c r="H74" s="11"/>
       <c r="I74" s="11"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9">
       <c r="A75" s="1">
         <v>65</v>
       </c>
@@ -2809,7 +2814,7 @@
       <c r="H75" s="11"/>
       <c r="I75" s="11"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9">
       <c r="A76" s="1">
         <v>66</v>
       </c>
@@ -2835,7 +2840,7 @@
       <c r="H76" s="11"/>
       <c r="I76" s="11"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9">
       <c r="A77" s="1">
         <v>67</v>
       </c>
@@ -2861,7 +2866,7 @@
       <c r="H77" s="11"/>
       <c r="I77" s="11"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9">
       <c r="A78" s="1">
         <v>68</v>
       </c>
@@ -2887,7 +2892,7 @@
       <c r="H78" s="11"/>
       <c r="I78" s="11"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9">
       <c r="A79" s="1">
         <v>69</v>
       </c>
@@ -2913,7 +2918,7 @@
       <c r="H79" s="11"/>
       <c r="I79" s="11"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9">
       <c r="A80" s="1">
         <v>70</v>
       </c>
@@ -2939,7 +2944,7 @@
       <c r="H80" s="11"/>
       <c r="I80" s="11"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9">
       <c r="A81" s="1">
         <v>71</v>
       </c>
@@ -2965,7 +2970,7 @@
       <c r="H81" s="11"/>
       <c r="I81" s="11"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9">
       <c r="A82" s="1">
         <v>72</v>
       </c>
@@ -2991,7 +2996,7 @@
       <c r="H82" s="11"/>
       <c r="I82" s="11"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9">
       <c r="A83" s="1">
         <v>73</v>
       </c>
@@ -3017,7 +3022,7 @@
       <c r="H83" s="11"/>
       <c r="I83" s="11"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9">
       <c r="A84" s="1">
         <v>74</v>
       </c>
@@ -3043,7 +3048,7 @@
       <c r="H84" s="11"/>
       <c r="I84" s="11"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9">
       <c r="A85" s="1">
         <v>75</v>
       </c>
@@ -3069,7 +3074,7 @@
       <c r="H85" s="11"/>
       <c r="I85" s="11"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9">
       <c r="A86" s="1">
         <v>76</v>
       </c>
@@ -3095,7 +3100,7 @@
       <c r="H86" s="11"/>
       <c r="I86" s="11"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9">
       <c r="A87" s="1">
         <v>77</v>
       </c>
@@ -3121,7 +3126,7 @@
       <c r="H87" s="11"/>
       <c r="I87" s="11"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9">
       <c r="A88" s="1">
         <v>78</v>
       </c>
@@ -3147,7 +3152,7 @@
       <c r="H88" s="11"/>
       <c r="I88" s="11"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9">
       <c r="A89" s="1">
         <v>79</v>
       </c>
@@ -3173,7 +3178,7 @@
       <c r="H89" s="11"/>
       <c r="I89" s="11"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9">
       <c r="A90" s="1">
         <v>80</v>
       </c>
@@ -3199,7 +3204,7 @@
       <c r="H90" s="11"/>
       <c r="I90" s="11"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9">
       <c r="A91" s="1">
         <v>81</v>
       </c>
@@ -3225,7 +3230,7 @@
       <c r="H91" s="11"/>
       <c r="I91" s="11"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9">
       <c r="A92" s="1">
         <v>82</v>
       </c>
@@ -3251,7 +3256,7 @@
       <c r="H92" s="11"/>
       <c r="I92" s="11"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9">
       <c r="A93" s="1">
         <v>83</v>
       </c>
@@ -3277,7 +3282,7 @@
       <c r="H93" s="11"/>
       <c r="I93" s="11"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9">
       <c r="A94" s="1">
         <v>84</v>
       </c>
@@ -3303,7 +3308,7 @@
       <c r="H94" s="11"/>
       <c r="I94" s="11"/>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9">
       <c r="A95" s="1">
         <v>85</v>
       </c>
@@ -3329,7 +3334,7 @@
       <c r="H95" s="11"/>
       <c r="I95" s="11"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9">
       <c r="A96" s="1">
         <v>86</v>
       </c>
@@ -3355,7 +3360,7 @@
       <c r="H96" s="11"/>
       <c r="I96" s="11"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9">
       <c r="A97" s="1">
         <v>87</v>
       </c>
@@ -3381,7 +3386,7 @@
       <c r="H97" s="11"/>
       <c r="I97" s="11"/>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9">
       <c r="A98" s="1">
         <v>88</v>
       </c>
@@ -3407,7 +3412,7 @@
       <c r="H98" s="11"/>
       <c r="I98" s="11"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9">
       <c r="A99" s="1">
         <v>89</v>
       </c>
@@ -3433,7 +3438,7 @@
       <c r="H99" s="11"/>
       <c r="I99" s="11"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9">
       <c r="A100" s="1">
         <v>90</v>
       </c>
@@ -3459,7 +3464,7 @@
       <c r="H100" s="11"/>
       <c r="I100" s="11"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9">
       <c r="A101" s="1">
         <v>91</v>
       </c>
@@ -3485,7 +3490,7 @@
       <c r="H101" s="11"/>
       <c r="I101" s="11"/>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9">
       <c r="A102" s="1">
         <v>92</v>
       </c>
@@ -3511,7 +3516,7 @@
       <c r="H102" s="11"/>
       <c r="I102" s="11"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9">
       <c r="A103" s="1">
         <v>93</v>
       </c>
@@ -3537,7 +3542,7 @@
       <c r="H103" s="11"/>
       <c r="I103" s="11"/>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9">
       <c r="A104" s="1">
         <v>94</v>
       </c>
@@ -3563,7 +3568,7 @@
       <c r="H104" s="11"/>
       <c r="I104" s="11"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9">
       <c r="A105" s="1">
         <v>95</v>
       </c>
@@ -3589,7 +3594,7 @@
       <c r="H105" s="11"/>
       <c r="I105" s="11"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9">
       <c r="A106" s="1">
         <v>96</v>
       </c>
@@ -3615,7 +3620,7 @@
       <c r="H106" s="11"/>
       <c r="I106" s="11"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9">
       <c r="A107" s="1">
         <v>97</v>
       </c>
@@ -3641,7 +3646,7 @@
       <c r="H107" s="11"/>
       <c r="I107" s="11"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9">
       <c r="A108" s="1">
         <v>98</v>
       </c>
@@ -3667,7 +3672,7 @@
       <c r="H108" s="11"/>
       <c r="I108" s="11"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9">
       <c r="A109" s="1">
         <v>99</v>
       </c>
@@ -3693,7 +3698,7 @@
       <c r="H109" s="11"/>
       <c r="I109" s="11"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9">
       <c r="A110" s="1">
         <v>100</v>
       </c>
@@ -3719,7 +3724,7 @@
       <c r="H110" s="11"/>
       <c r="I110" s="11"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9">
       <c r="A111" s="1">
         <v>101</v>
       </c>
@@ -3745,7 +3750,7 @@
       <c r="H111" s="11"/>
       <c r="I111" s="11"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9">
       <c r="A112" s="1">
         <v>102</v>
       </c>
@@ -3771,7 +3776,7 @@
       <c r="H112" s="11"/>
       <c r="I112" s="11"/>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9">
       <c r="A113" s="1">
         <v>103</v>
       </c>
@@ -3797,7 +3802,7 @@
       <c r="H113" s="11"/>
       <c r="I113" s="11"/>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9">
       <c r="A114" s="1">
         <v>104</v>
       </c>
@@ -3823,7 +3828,7 @@
       <c r="H114" s="11"/>
       <c r="I114" s="11"/>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9">
       <c r="A115" s="1">
         <v>105</v>
       </c>
@@ -3849,7 +3854,7 @@
       <c r="H115" s="11"/>
       <c r="I115" s="11"/>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9">
       <c r="A116" s="1">
         <v>106</v>
       </c>
@@ -3875,7 +3880,7 @@
       <c r="H116" s="11"/>
       <c r="I116" s="11"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9">
       <c r="A117" s="1">
         <v>107</v>
       </c>
@@ -3901,7 +3906,7 @@
       <c r="H117" s="11"/>
       <c r="I117" s="11"/>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9">
       <c r="A118" s="1">
         <v>108</v>
       </c>
@@ -3927,7 +3932,7 @@
       <c r="H118" s="11"/>
       <c r="I118" s="11"/>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9">
       <c r="A119" s="1">
         <v>109</v>
       </c>
@@ -3953,7 +3958,7 @@
       <c r="H119" s="11"/>
       <c r="I119" s="11"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9">
       <c r="A120" s="1">
         <v>110</v>
       </c>
@@ -3979,7 +3984,7 @@
       <c r="H120" s="11"/>
       <c r="I120" s="11"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9">
       <c r="A121" s="1">
         <v>111</v>
       </c>
@@ -4005,7 +4010,7 @@
       <c r="H121" s="11"/>
       <c r="I121" s="11"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9">
       <c r="A122" s="1">
         <v>112</v>
       </c>
@@ -4031,7 +4036,7 @@
       <c r="H122" s="11"/>
       <c r="I122" s="11"/>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9">
       <c r="A123" s="1">
         <v>113</v>
       </c>
@@ -4057,7 +4062,7 @@
       <c r="H123" s="11"/>
       <c r="I123" s="11"/>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9">
       <c r="A124" s="1">
         <v>114</v>
       </c>
@@ -4083,7 +4088,7 @@
       <c r="H124" s="11"/>
       <c r="I124" s="11"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9">
       <c r="A125" s="1">
         <v>115</v>
       </c>
@@ -4109,7 +4114,7 @@
       <c r="H125" s="11"/>
       <c r="I125" s="11"/>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9">
       <c r="A126" s="1">
         <v>116</v>
       </c>
@@ -4135,7 +4140,7 @@
       <c r="H126" s="11"/>
       <c r="I126" s="11"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9">
       <c r="A127" s="1">
         <v>117</v>
       </c>
@@ -4161,7 +4166,7 @@
       <c r="H127" s="11"/>
       <c r="I127" s="11"/>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9">
       <c r="A128" s="1">
         <v>118</v>
       </c>
@@ -4187,7 +4192,7 @@
       <c r="H128" s="11"/>
       <c r="I128" s="11"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9">
       <c r="A129" s="1">
         <v>119</v>
       </c>
@@ -4213,7 +4218,7 @@
       <c r="H129" s="11"/>
       <c r="I129" s="11"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9">
       <c r="A130" s="1">
         <v>120</v>
       </c>
@@ -4239,7 +4244,7 @@
       <c r="H130" s="11"/>
       <c r="I130" s="11"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9">
       <c r="A131" s="1">
         <v>121</v>
       </c>
@@ -4265,7 +4270,7 @@
       <c r="H131" s="11"/>
       <c r="I131" s="11"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9">
       <c r="A132" s="1">
         <v>122</v>
       </c>
@@ -4291,7 +4296,7 @@
       <c r="H132" s="11"/>
       <c r="I132" s="11"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9">
       <c r="A133" s="1">
         <v>123</v>
       </c>
@@ -4317,7 +4322,7 @@
       <c r="H133" s="11"/>
       <c r="I133" s="11"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9">
       <c r="A134" s="1">
         <v>124</v>
       </c>
@@ -4343,7 +4348,7 @@
       <c r="H134" s="11"/>
       <c r="I134" s="11"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9">
       <c r="A135" s="1">
         <v>125</v>
       </c>
@@ -4369,7 +4374,7 @@
       <c r="H135" s="11"/>
       <c r="I135" s="11"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9">
       <c r="A136" s="1">
         <v>126</v>
       </c>
@@ -4395,7 +4400,7 @@
       <c r="H136" s="11"/>
       <c r="I136" s="11"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9">
       <c r="A137" s="1">
         <v>127</v>
       </c>
@@ -4421,7 +4426,7 @@
       <c r="H137" s="11"/>
       <c r="I137" s="11"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9">
       <c r="A138" s="1">
         <v>128</v>
       </c>
@@ -4447,7 +4452,7 @@
       <c r="H138" s="11"/>
       <c r="I138" s="11"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9">
       <c r="A139" s="1">
         <v>129</v>
       </c>
@@ -4473,7 +4478,7 @@
       <c r="H139" s="11"/>
       <c r="I139" s="11"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9">
       <c r="A140" s="1">
         <v>130</v>
       </c>
@@ -4499,7 +4504,7 @@
       <c r="H140" s="11"/>
       <c r="I140" s="11"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9">
       <c r="A141" s="1">
         <v>131</v>
       </c>
@@ -4525,7 +4530,7 @@
       <c r="H141" s="11"/>
       <c r="I141" s="11"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9">
       <c r="A142" s="1">
         <v>132</v>
       </c>
@@ -4551,7 +4556,7 @@
       <c r="H142" s="11"/>
       <c r="I142" s="11"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9">
       <c r="A143" s="1">
         <v>133</v>
       </c>
@@ -4577,7 +4582,7 @@
       <c r="H143" s="11"/>
       <c r="I143" s="11"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9">
       <c r="A144" s="1">
         <v>134</v>
       </c>
@@ -4603,7 +4608,7 @@
       <c r="H144" s="11"/>
       <c r="I144" s="11"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9">
       <c r="A145" s="1">
         <v>135</v>
       </c>
@@ -4629,7 +4634,7 @@
       <c r="H145" s="11"/>
       <c r="I145" s="11"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9">
       <c r="A146" s="1">
         <v>136</v>
       </c>
@@ -4655,7 +4660,7 @@
       <c r="H146" s="11"/>
       <c r="I146" s="11"/>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9">
       <c r="A147" s="1">
         <v>137</v>
       </c>
@@ -4681,7 +4686,7 @@
       <c r="H147" s="11"/>
       <c r="I147" s="11"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9">
       <c r="A148" s="1">
         <v>138</v>
       </c>
@@ -4707,7 +4712,7 @@
       <c r="H148" s="11"/>
       <c r="I148" s="11"/>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9">
       <c r="A149" s="1">
         <v>139</v>
       </c>
@@ -4733,7 +4738,7 @@
       <c r="H149" s="11"/>
       <c r="I149" s="11"/>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9">
       <c r="A150" s="1">
         <v>140</v>
       </c>
@@ -4759,7 +4764,7 @@
       <c r="H150" s="11"/>
       <c r="I150" s="11"/>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9">
       <c r="A151" s="1">
         <v>141</v>
       </c>
@@ -4785,7 +4790,7 @@
       <c r="H151" s="11"/>
       <c r="I151" s="11"/>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9">
       <c r="A152" s="1">
         <v>142</v>
       </c>
@@ -4811,7 +4816,7 @@
       <c r="H152" s="11"/>
       <c r="I152" s="11"/>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9">
       <c r="A153" s="1">
         <v>143</v>
       </c>
@@ -4837,7 +4842,7 @@
       <c r="H153" s="11"/>
       <c r="I153" s="11"/>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9">
       <c r="A154" s="1">
         <v>144</v>
       </c>
@@ -4863,7 +4868,7 @@
       <c r="H154" s="11"/>
       <c r="I154" s="11"/>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9">
       <c r="A155" s="1">
         <v>145</v>
       </c>
@@ -4889,7 +4894,7 @@
       <c r="H155" s="11"/>
       <c r="I155" s="11"/>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9">
       <c r="A156" s="1">
         <v>146</v>
       </c>
@@ -4915,7 +4920,7 @@
       <c r="H156" s="11"/>
       <c r="I156" s="11"/>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9">
       <c r="A157" s="1">
         <v>147</v>
       </c>
@@ -4941,7 +4946,7 @@
       <c r="H157" s="11"/>
       <c r="I157" s="11"/>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9">
       <c r="A158" s="1">
         <v>148</v>
       </c>
@@ -4967,7 +4972,7 @@
       <c r="H158" s="11"/>
       <c r="I158" s="11"/>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9">
       <c r="A159" s="1">
         <v>149</v>
       </c>
@@ -4993,7 +4998,7 @@
       <c r="H159" s="11"/>
       <c r="I159" s="11"/>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9">
       <c r="A160" s="1">
         <v>150</v>
       </c>
@@ -5019,7 +5024,7 @@
       <c r="H160" s="11"/>
       <c r="I160" s="11"/>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9">
       <c r="A161" s="1">
         <v>151</v>
       </c>
@@ -5045,7 +5050,7 @@
       <c r="H161" s="11"/>
       <c r="I161" s="11"/>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9">
       <c r="A162" s="1">
         <v>152</v>
       </c>
@@ -5071,7 +5076,7 @@
       <c r="H162" s="11"/>
       <c r="I162" s="11"/>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9">
       <c r="A163" s="1">
         <v>153</v>
       </c>
@@ -5097,7 +5102,7 @@
       <c r="H163" s="11"/>
       <c r="I163" s="11"/>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9">
       <c r="A164" s="1">
         <v>154</v>
       </c>
@@ -5123,7 +5128,7 @@
       <c r="H164" s="11"/>
       <c r="I164" s="11"/>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9">
       <c r="A165" s="1">
         <v>155</v>
       </c>
@@ -5149,7 +5154,7 @@
       <c r="H165" s="11"/>
       <c r="I165" s="11"/>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9">
       <c r="A166" s="1">
         <v>156</v>
       </c>
@@ -5175,7 +5180,7 @@
       <c r="H166" s="11"/>
       <c r="I166" s="11"/>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9">
       <c r="A167" s="1">
         <v>157</v>
       </c>
@@ -5201,7 +5206,7 @@
       <c r="H167" s="11"/>
       <c r="I167" s="11"/>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9">
       <c r="A168" s="1">
         <v>158</v>
       </c>
@@ -5227,7 +5232,7 @@
       <c r="H168" s="11"/>
       <c r="I168" s="11"/>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9">
       <c r="A169" s="1">
         <v>159</v>
       </c>
@@ -5253,7 +5258,7 @@
       <c r="H169" s="11"/>
       <c r="I169" s="11"/>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9">
       <c r="A170" s="1">
         <v>160</v>
       </c>
@@ -5279,7 +5284,7 @@
       <c r="H170" s="11"/>
       <c r="I170" s="11"/>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9">
       <c r="A171" s="1">
         <v>161</v>
       </c>
@@ -5305,7 +5310,7 @@
       <c r="H171" s="11"/>
       <c r="I171" s="11"/>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9">
       <c r="A172" s="1">
         <v>162</v>
       </c>
@@ -5331,7 +5336,7 @@
       <c r="H172" s="11"/>
       <c r="I172" s="11"/>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9">
       <c r="A173" s="1">
         <v>163</v>
       </c>
@@ -5357,7 +5362,7 @@
       <c r="H173" s="11"/>
       <c r="I173" s="11"/>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9">
       <c r="A174" s="1">
         <v>164</v>
       </c>
@@ -5383,7 +5388,7 @@
       <c r="H174" s="11"/>
       <c r="I174" s="11"/>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9">
       <c r="A175" s="1">
         <v>165</v>
       </c>
@@ -5409,7 +5414,7 @@
       <c r="H175" s="11"/>
       <c r="I175" s="11"/>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9">
       <c r="A176" s="1">
         <v>166</v>
       </c>
@@ -5435,7 +5440,7 @@
       <c r="H176" s="11"/>
       <c r="I176" s="11"/>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9">
       <c r="A177" s="1">
         <v>167</v>
       </c>
@@ -5461,7 +5466,7 @@
       <c r="H177" s="11"/>
       <c r="I177" s="11"/>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9">
       <c r="A178" s="1">
         <v>168</v>
       </c>
@@ -5487,7 +5492,7 @@
       <c r="H178" s="11"/>
       <c r="I178" s="11"/>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9">
       <c r="A179" s="1">
         <v>169</v>
       </c>
@@ -5513,7 +5518,7 @@
       <c r="H179" s="11"/>
       <c r="I179" s="11"/>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9">
       <c r="A180" s="1">
         <v>170</v>
       </c>
@@ -5539,7 +5544,7 @@
       <c r="H180" s="11"/>
       <c r="I180" s="11"/>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9">
       <c r="A181" s="1">
         <v>171</v>
       </c>
@@ -5565,7 +5570,7 @@
       <c r="H181" s="11"/>
       <c r="I181" s="11"/>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9">
       <c r="A182" s="1">
         <v>172</v>
       </c>
@@ -5591,7 +5596,7 @@
       <c r="H182" s="11"/>
       <c r="I182" s="11"/>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9">
       <c r="A183" s="1">
         <v>173</v>
       </c>
@@ -5617,7 +5622,7 @@
       <c r="H183" s="11"/>
       <c r="I183" s="11"/>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9">
       <c r="A184" s="1">
         <v>174</v>
       </c>
@@ -5643,7 +5648,7 @@
       <c r="H184" s="11"/>
       <c r="I184" s="11"/>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9">
       <c r="A185" s="1">
         <v>175</v>
       </c>
@@ -5669,7 +5674,7 @@
       <c r="H185" s="11"/>
       <c r="I185" s="11"/>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9">
       <c r="A186" s="1">
         <v>176</v>
       </c>
@@ -5695,7 +5700,7 @@
       <c r="H186" s="11"/>
       <c r="I186" s="11"/>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9">
       <c r="A187" s="1">
         <v>177</v>
       </c>
@@ -5721,7 +5726,7 @@
       <c r="H187" s="11"/>
       <c r="I187" s="11"/>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9">
       <c r="A188" s="1">
         <v>178</v>
       </c>
@@ -5747,7 +5752,7 @@
       <c r="H188" s="11"/>
       <c r="I188" s="11"/>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9">
       <c r="A189" s="1">
         <v>179</v>
       </c>
@@ -5773,7 +5778,7 @@
       <c r="H189" s="11"/>
       <c r="I189" s="11"/>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9">
       <c r="A190" s="1">
         <v>180</v>
       </c>
@@ -5799,7 +5804,7 @@
       <c r="H190" s="11"/>
       <c r="I190" s="11"/>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9">
       <c r="A191" s="1">
         <v>181</v>
       </c>
@@ -5825,7 +5830,7 @@
       <c r="H191" s="11"/>
       <c r="I191" s="11"/>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9">
       <c r="A192" s="1">
         <v>182</v>
       </c>
@@ -5851,7 +5856,7 @@
       <c r="H192" s="11"/>
       <c r="I192" s="11"/>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9">
       <c r="A193" s="1">
         <v>183</v>
       </c>
@@ -5877,7 +5882,7 @@
       <c r="H193" s="11"/>
       <c r="I193" s="11"/>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9">
       <c r="A194" s="1">
         <v>184</v>
       </c>
@@ -5903,7 +5908,7 @@
       <c r="H194" s="11"/>
       <c r="I194" s="11"/>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9">
       <c r="A195" s="1">
         <v>185</v>
       </c>
@@ -5929,7 +5934,7 @@
       <c r="H195" s="11"/>
       <c r="I195" s="11"/>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9">
       <c r="A196" s="1">
         <v>186</v>
       </c>
@@ -5955,7 +5960,7 @@
       <c r="H196" s="11"/>
       <c r="I196" s="11"/>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9">
       <c r="A197" s="1">
         <v>187</v>
       </c>
@@ -5981,7 +5986,7 @@
       <c r="H197" s="11"/>
       <c r="I197" s="11"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9">
       <c r="A198" s="1">
         <v>188</v>
       </c>
@@ -6007,7 +6012,7 @@
       <c r="H198" s="11"/>
       <c r="I198" s="11"/>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9">
       <c r="A199" s="1">
         <v>189</v>
       </c>
@@ -6033,7 +6038,7 @@
       <c r="H199" s="11"/>
       <c r="I199" s="11"/>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9">
       <c r="A200" s="1">
         <v>190</v>
       </c>
@@ -6059,7 +6064,7 @@
       <c r="H200" s="11"/>
       <c r="I200" s="11"/>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9">
       <c r="A201" s="1">
         <v>191</v>
       </c>
@@ -6085,7 +6090,7 @@
       <c r="H201" s="11"/>
       <c r="I201" s="11"/>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9">
       <c r="A202" s="1">
         <v>192</v>
       </c>
@@ -6111,7 +6116,7 @@
       <c r="H202" s="11"/>
       <c r="I202" s="11"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9">
       <c r="A203" s="1">
         <v>193</v>
       </c>
@@ -6137,7 +6142,7 @@
       <c r="H203" s="11"/>
       <c r="I203" s="11"/>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9">
       <c r="A204" s="1">
         <v>194</v>
       </c>
@@ -6163,7 +6168,7 @@
       <c r="H204" s="11"/>
       <c r="I204" s="11"/>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9">
       <c r="A205" s="1">
         <v>195</v>
       </c>
@@ -6189,7 +6194,7 @@
       <c r="H205" s="11"/>
       <c r="I205" s="11"/>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9">
       <c r="A206" s="1">
         <v>196</v>
       </c>
@@ -6215,7 +6220,7 @@
       <c r="H206" s="11"/>
       <c r="I206" s="11"/>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9">
       <c r="A207" s="1">
         <v>197</v>
       </c>
@@ -6241,7 +6246,7 @@
       <c r="H207" s="11"/>
       <c r="I207" s="11"/>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9">
       <c r="A208" s="1">
         <v>198</v>
       </c>
@@ -6267,7 +6272,7 @@
       <c r="H208" s="11"/>
       <c r="I208" s="11"/>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9">
       <c r="A209" s="1">
         <v>199</v>
       </c>
@@ -6293,7 +6298,7 @@
       <c r="H209" s="11"/>
       <c r="I209" s="11"/>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9">
       <c r="A210" s="1">
         <v>200</v>
       </c>
@@ -6319,7 +6324,7 @@
       <c r="H210" s="11"/>
       <c r="I210" s="11"/>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9">
       <c r="A211" s="1">
         <v>201</v>
       </c>
@@ -6345,7 +6350,7 @@
       <c r="H211" s="11"/>
       <c r="I211" s="11"/>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9">
       <c r="A212" s="1">
         <v>202</v>
       </c>
@@ -6371,7 +6376,7 @@
       <c r="H212" s="11"/>
       <c r="I212" s="11"/>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9">
       <c r="A213" s="1">
         <v>203</v>
       </c>
@@ -6397,7 +6402,7 @@
       <c r="H213" s="11"/>
       <c r="I213" s="11"/>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9">
       <c r="A214" s="1">
         <v>204</v>
       </c>
@@ -6423,7 +6428,7 @@
       <c r="H214" s="11"/>
       <c r="I214" s="11"/>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9">
       <c r="A215" s="1">
         <v>205</v>
       </c>
@@ -6449,7 +6454,7 @@
       <c r="H215" s="11"/>
       <c r="I215" s="11"/>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9">
       <c r="A216" s="1">
         <v>206</v>
       </c>
@@ -6475,7 +6480,7 @@
       <c r="H216" s="11"/>
       <c r="I216" s="11"/>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9">
       <c r="A217" s="1">
         <v>207</v>
       </c>
@@ -6501,7 +6506,7 @@
       <c r="H217" s="11"/>
       <c r="I217" s="11"/>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9">
       <c r="A218" s="1">
         <v>208</v>
       </c>
@@ -6527,7 +6532,7 @@
       <c r="H218" s="11"/>
       <c r="I218" s="11"/>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9">
       <c r="A219" s="1">
         <v>209</v>
       </c>
@@ -6553,7 +6558,7 @@
       <c r="H219" s="11"/>
       <c r="I219" s="11"/>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9">
       <c r="A220" s="1">
         <v>210</v>
       </c>
@@ -6579,7 +6584,7 @@
       <c r="H220" s="11"/>
       <c r="I220" s="11"/>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9">
       <c r="A221" s="1">
         <v>211</v>
       </c>
@@ -6605,7 +6610,7 @@
       <c r="H221" s="11"/>
       <c r="I221" s="11"/>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9">
       <c r="A222" s="1">
         <v>212</v>
       </c>
@@ -6631,7 +6636,7 @@
       <c r="H222" s="11"/>
       <c r="I222" s="11"/>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9">
       <c r="A223" s="1">
         <v>213</v>
       </c>
@@ -6657,7 +6662,7 @@
       <c r="H223" s="11"/>
       <c r="I223" s="11"/>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9">
       <c r="A224" s="1">
         <v>214</v>
       </c>
@@ -6683,7 +6688,7 @@
       <c r="H224" s="11"/>
       <c r="I224" s="11"/>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9">
       <c r="A225" s="1">
         <v>215</v>
       </c>
@@ -6709,7 +6714,7 @@
       <c r="H225" s="11"/>
       <c r="I225" s="11"/>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9">
       <c r="A226" s="1">
         <v>216</v>
       </c>
@@ -6735,7 +6740,7 @@
       <c r="H226" s="11"/>
       <c r="I226" s="11"/>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9">
       <c r="A227" s="1">
         <v>217</v>
       </c>
@@ -6761,7 +6766,7 @@
       <c r="H227" s="11"/>
       <c r="I227" s="11"/>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9">
       <c r="A228" s="1">
         <v>218</v>
       </c>
@@ -6787,7 +6792,7 @@
       <c r="H228" s="11"/>
       <c r="I228" s="11"/>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9">
       <c r="A229" s="1">
         <v>219</v>
       </c>
@@ -6813,7 +6818,7 @@
       <c r="H229" s="11"/>
       <c r="I229" s="11"/>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9">
       <c r="A230" s="1">
         <v>220</v>
       </c>
@@ -6839,7 +6844,7 @@
       <c r="H230" s="11"/>
       <c r="I230" s="11"/>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9">
       <c r="A231" s="1">
         <v>221</v>
       </c>
@@ -6865,7 +6870,7 @@
       <c r="H231" s="11"/>
       <c r="I231" s="11"/>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9">
       <c r="A232" s="1">
         <v>222</v>
       </c>
@@ -6891,7 +6896,7 @@
       <c r="H232" s="11"/>
       <c r="I232" s="11"/>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9">
       <c r="A233" s="1">
         <v>223</v>
       </c>
@@ -6917,7 +6922,7 @@
       <c r="H233" s="11"/>
       <c r="I233" s="11"/>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9">
       <c r="A234" s="1">
         <v>224</v>
       </c>
@@ -6943,7 +6948,7 @@
       <c r="H234" s="11"/>
       <c r="I234" s="11"/>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9">
       <c r="A235" s="1">
         <v>225</v>
       </c>
@@ -6969,7 +6974,7 @@
       <c r="H235" s="11"/>
       <c r="I235" s="11"/>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9">
       <c r="A236" s="1">
         <v>226</v>
       </c>
@@ -6995,7 +7000,7 @@
       <c r="H236" s="11"/>
       <c r="I236" s="11"/>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9">
       <c r="A237" s="1">
         <v>227</v>
       </c>
@@ -7021,7 +7026,7 @@
       <c r="H237" s="11"/>
       <c r="I237" s="11"/>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9">
       <c r="A238" s="1">
         <v>228</v>
       </c>
@@ -7047,7 +7052,7 @@
       <c r="H238" s="11"/>
       <c r="I238" s="11"/>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9">
       <c r="A239" s="1">
         <v>229</v>
       </c>
@@ -7073,7 +7078,7 @@
       <c r="H239" s="11"/>
       <c r="I239" s="11"/>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9">
       <c r="A240" s="1">
         <v>230</v>
       </c>
@@ -7099,7 +7104,7 @@
       <c r="H240" s="11"/>
       <c r="I240" s="11"/>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9">
       <c r="A241" s="1">
         <v>231</v>
       </c>
@@ -7125,7 +7130,7 @@
       <c r="H241" s="11"/>
       <c r="I241" s="11"/>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9">
       <c r="A242" s="1">
         <v>232</v>
       </c>
@@ -7151,7 +7156,7 @@
       <c r="H242" s="11"/>
       <c r="I242" s="11"/>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9">
       <c r="A243" s="1">
         <v>233</v>
       </c>
@@ -7177,7 +7182,7 @@
       <c r="H243" s="11"/>
       <c r="I243" s="11"/>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9">
       <c r="A244" s="1">
         <v>234</v>
       </c>
@@ -7203,7 +7208,7 @@
       <c r="H244" s="11"/>
       <c r="I244" s="11"/>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9">
       <c r="A245" s="1">
         <v>235</v>
       </c>
@@ -7229,7 +7234,7 @@
       <c r="H245" s="11"/>
       <c r="I245" s="11"/>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9">
       <c r="A246" s="1">
         <v>236</v>
       </c>
@@ -7255,7 +7260,7 @@
       <c r="H246" s="11"/>
       <c r="I246" s="11"/>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9">
       <c r="A247" s="1">
         <v>237</v>
       </c>
@@ -7281,7 +7286,7 @@
       <c r="H247" s="11"/>
       <c r="I247" s="11"/>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9">
       <c r="A248" s="1">
         <v>238</v>
       </c>
@@ -7307,7 +7312,7 @@
       <c r="H248" s="11"/>
       <c r="I248" s="11"/>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9">
       <c r="A249" s="1">
         <v>239</v>
       </c>
@@ -7333,7 +7338,7 @@
       <c r="H249" s="11"/>
       <c r="I249" s="11"/>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9">
       <c r="A250" s="1">
         <v>240</v>
       </c>
@@ -7359,7 +7364,7 @@
       <c r="H250" s="11"/>
       <c r="I250" s="11"/>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9">
       <c r="A251" s="1">
         <v>241</v>
       </c>
@@ -7385,7 +7390,7 @@
       <c r="H251" s="11"/>
       <c r="I251" s="11"/>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9">
       <c r="A252" s="1">
         <v>242</v>
       </c>
@@ -7411,7 +7416,7 @@
       <c r="H252" s="11"/>
       <c r="I252" s="11"/>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9">
       <c r="A253" s="1">
         <v>243</v>
       </c>
@@ -7437,7 +7442,7 @@
       <c r="H253" s="11"/>
       <c r="I253" s="11"/>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9">
       <c r="A254" s="1">
         <v>244</v>
       </c>
@@ -7463,7 +7468,7 @@
       <c r="H254" s="11"/>
       <c r="I254" s="11"/>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9">
       <c r="A255" s="1">
         <v>245</v>
       </c>
@@ -7489,7 +7494,7 @@
       <c r="H255" s="11"/>
       <c r="I255" s="11"/>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9">
       <c r="A256" s="1">
         <v>246</v>
       </c>
@@ -7515,7 +7520,7 @@
       <c r="H256" s="11"/>
       <c r="I256" s="11"/>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9">
       <c r="A257" s="1">
         <v>247</v>
       </c>
@@ -7541,7 +7546,7 @@
       <c r="H257" s="11"/>
       <c r="I257" s="11"/>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9">
       <c r="A258" s="1">
         <v>248</v>
       </c>
@@ -7567,7 +7572,7 @@
       <c r="H258" s="11"/>
       <c r="I258" s="11"/>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9">
       <c r="A259" s="1">
         <v>249</v>
       </c>
@@ -7593,7 +7598,7 @@
       <c r="H259" s="11"/>
       <c r="I259" s="11"/>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9">
       <c r="A260" s="1">
         <v>250</v>
       </c>
@@ -7619,7 +7624,7 @@
       <c r="H260" s="11"/>
       <c r="I260" s="11"/>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9">
       <c r="A261" s="1">
         <v>251</v>
       </c>
@@ -7645,7 +7650,7 @@
       <c r="H261" s="11"/>
       <c r="I261" s="11"/>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9">
       <c r="A262" s="1">
         <v>252</v>
       </c>
@@ -7671,7 +7676,7 @@
       <c r="H262" s="11"/>
       <c r="I262" s="11"/>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9">
       <c r="A263" s="1">
         <v>253</v>
       </c>
@@ -7697,7 +7702,7 @@
       <c r="H263" s="11"/>
       <c r="I263" s="11"/>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9">
       <c r="A264" s="1">
         <v>254</v>
       </c>
@@ -7723,7 +7728,7 @@
       <c r="H264" s="11"/>
       <c r="I264" s="11"/>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9">
       <c r="A265" s="1">
         <v>255</v>
       </c>
@@ -7749,7 +7754,7 @@
       <c r="H265" s="11"/>
       <c r="I265" s="11"/>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9">
       <c r="A266" s="1">
         <v>256</v>
       </c>
@@ -7775,7 +7780,7 @@
       <c r="H266" s="11"/>
       <c r="I266" s="11"/>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9">
       <c r="A267" s="1">
         <v>257</v>
       </c>
@@ -7801,7 +7806,7 @@
       <c r="H267" s="11"/>
       <c r="I267" s="11"/>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9">
       <c r="A268" s="1">
         <v>258</v>
       </c>
@@ -7827,7 +7832,7 @@
       <c r="H268" s="11"/>
       <c r="I268" s="11"/>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9">
       <c r="A269" s="1">
         <v>259</v>
       </c>
@@ -7853,7 +7858,7 @@
       <c r="H269" s="11"/>
       <c r="I269" s="11"/>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9">
       <c r="A270" s="1">
         <v>260</v>
       </c>
@@ -7879,7 +7884,7 @@
       <c r="H270" s="11"/>
       <c r="I270" s="11"/>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9">
       <c r="A271" s="1">
         <v>261</v>
       </c>
@@ -7905,7 +7910,7 @@
       <c r="H271" s="11"/>
       <c r="I271" s="11"/>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9">
       <c r="A272" s="1">
         <v>262</v>
       </c>
@@ -7931,7 +7936,7 @@
       <c r="H272" s="11"/>
       <c r="I272" s="11"/>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9">
       <c r="A273" s="1">
         <v>263</v>
       </c>
@@ -7957,7 +7962,7 @@
       <c r="H273" s="11"/>
       <c r="I273" s="11"/>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9">
       <c r="A274" s="1">
         <v>264</v>
       </c>
@@ -7983,7 +7988,7 @@
       <c r="H274" s="11"/>
       <c r="I274" s="11"/>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9">
       <c r="A275" s="1">
         <v>265</v>
       </c>
@@ -8009,7 +8014,7 @@
       <c r="H275" s="11"/>
       <c r="I275" s="11"/>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9">
       <c r="A276" s="1">
         <v>266</v>
       </c>
@@ -8035,7 +8040,7 @@
       <c r="H276" s="11"/>
       <c r="I276" s="11"/>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9">
       <c r="A277" s="1">
         <v>267</v>
       </c>
@@ -8061,7 +8066,7 @@
       <c r="H277" s="11"/>
       <c r="I277" s="11"/>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9">
       <c r="A278" s="1">
         <v>268</v>
       </c>
@@ -8087,7 +8092,7 @@
       <c r="H278" s="11"/>
       <c r="I278" s="11"/>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9">
       <c r="A279" s="1">
         <v>269</v>
       </c>
@@ -8113,7 +8118,7 @@
       <c r="H279" s="11"/>
       <c r="I279" s="11"/>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9">
       <c r="A280" s="1">
         <v>270</v>
       </c>
@@ -8139,7 +8144,7 @@
       <c r="H280" s="11"/>
       <c r="I280" s="11"/>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9">
       <c r="A281" s="1">
         <v>271</v>
       </c>
@@ -8165,7 +8170,7 @@
       <c r="H281" s="11"/>
       <c r="I281" s="11"/>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9">
       <c r="A282" s="1">
         <v>272</v>
       </c>
@@ -8191,7 +8196,7 @@
       <c r="H282" s="11"/>
       <c r="I282" s="11"/>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9">
       <c r="A283" s="1">
         <v>273</v>
       </c>
@@ -8217,7 +8222,7 @@
       <c r="H283" s="11"/>
       <c r="I283" s="11"/>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9">
       <c r="A284" s="1">
         <v>274</v>
       </c>
@@ -8243,7 +8248,7 @@
       <c r="H284" s="11"/>
       <c r="I284" s="11"/>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9">
       <c r="A285" s="1">
         <v>275</v>
       </c>
@@ -8269,7 +8274,7 @@
       <c r="H285" s="11"/>
       <c r="I285" s="11"/>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9">
       <c r="A286" s="1">
         <v>276</v>
       </c>
@@ -8299,7 +8304,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9">
       <c r="A287" s="1">
         <v>277</v>
       </c>
@@ -8329,7 +8334,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9">
       <c r="A288" s="1">
         <v>278</v>
       </c>
@@ -8359,7 +8364,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9">
       <c r="A289" s="1">
         <v>279</v>
       </c>
@@ -8389,7 +8394,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9">
       <c r="A290" s="1">
         <v>280</v>
       </c>
@@ -8419,7 +8424,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9">
       <c r="A291" s="1">
         <v>281</v>
       </c>
@@ -8449,7 +8454,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9">
       <c r="A292" s="1">
         <v>282</v>
       </c>
@@ -8479,7 +8484,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9">
       <c r="A293" s="1">
         <v>283</v>
       </c>
@@ -8509,7 +8514,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9">
       <c r="A294" s="1">
         <v>284</v>
       </c>
@@ -8539,7 +8544,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9">
       <c r="A295" s="1">
         <v>285</v>
       </c>
@@ -8569,7 +8574,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9">
       <c r="A296" s="1">
         <v>286</v>
       </c>
@@ -8599,7 +8604,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9">
       <c r="A297" s="1">
         <v>287</v>
       </c>
@@ -8629,7 +8634,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9">
       <c r="A298" s="1">
         <v>288</v>
       </c>
@@ -8659,7 +8664,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9">
       <c r="A299" s="1">
         <v>289</v>
       </c>
@@ -8689,7 +8694,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9">
       <c r="A300" s="1">
         <v>290</v>
       </c>
@@ -8719,7 +8724,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9">
       <c r="A301" s="1">
         <v>291</v>
       </c>
@@ -8749,7 +8754,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9">
       <c r="A302" s="1">
         <v>292</v>
       </c>
@@ -8779,7 +8784,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="303" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" s="1" customFormat="1">
       <c r="A303" s="1">
         <v>293</v>
       </c>
@@ -8809,7 +8814,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="304" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" s="1" customFormat="1">
       <c r="A304" s="1">
         <v>294</v>
       </c>
@@ -8839,7 +8844,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9">
       <c r="A305" s="1">
         <v>295</v>
       </c>
@@ -8869,7 +8874,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9">
       <c r="A306" s="1">
         <v>296</v>
       </c>
@@ -8899,7 +8904,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9">
       <c r="A307" s="1">
         <v>297</v>
       </c>
@@ -8929,7 +8934,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9">
       <c r="A308" s="1">
         <v>298</v>
       </c>
@@ -8959,73 +8964,73 @@
         <v>56</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9">
       <c r="A309" s="1"/>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9">
       <c r="A310" s="1"/>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9">
       <c r="A311" s="1"/>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9">
       <c r="A312" s="1"/>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9">
       <c r="A313" s="1"/>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9">
       <c r="A314" s="1"/>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9">
       <c r="A315" s="1"/>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9">
       <c r="A316" s="1"/>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9">
       <c r="A317" s="1"/>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9">
       <c r="A318" s="1"/>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9">
       <c r="A319" s="1"/>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9">
       <c r="A320" s="1"/>
     </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:1">
       <c r="A321" s="1"/>
     </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:1">
       <c r="A322" s="1"/>
     </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:1">
       <c r="A323" s="1"/>
     </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:1">
       <c r="A324" s="1"/>
     </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:1">
       <c r="A325" s="1"/>
     </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:1">
       <c r="A326" s="1"/>
     </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:1">
       <c r="A327" s="1"/>
     </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:1">
       <c r="A328" s="1"/>
     </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:1">
       <c r="A329" s="1"/>
     </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:1">
       <c r="A330" s="1"/>
     </row>
-    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:1">
       <c r="A331" s="1"/>
     </row>
   </sheetData>
@@ -9047,13 +9052,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{797F1036-D41E-43A4-9E6E-CBBB62F3CD31}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="13.28515625" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9067,7 +9072,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -9081,7 +9086,7 @@
         <v>234.67</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -9095,7 +9100,7 @@
         <v>161.15</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -9109,7 +9114,7 @@
         <v>157.61000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -9123,7 +9128,7 @@
         <v>347.95</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -9137,7 +9142,7 @@
         <v>393.57</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -9151,7 +9156,7 @@
         <v>19.87</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -9165,7 +9170,7 @@
         <v>19.57</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>61</v>
       </c>
@@ -9179,7 +9184,7 @@
         <v>19.86</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -9193,7 +9198,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -9217,8 +9222,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56220E0F-EC16-4A8C-9E04-C7F8849C4B4D}">
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
@@ -9226,7 +9231,7 @@
     <col min="5" max="5" width="30.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9242,11 +9247,8 @@
       <c r="E1" t="s">
         <v>7</v>
       </c>
-      <c r="G1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -9263,7 +9265,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -9280,7 +9282,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -9297,7 +9299,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -9314,7 +9316,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -9331,7 +9333,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -9348,7 +9350,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -9376,14 +9378,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83DAFC4B-C207-418A-8501-0E1EC9E673B7}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9394,7 +9396,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -9405,7 +9407,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -9416,7 +9418,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -9427,7 +9429,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>61</v>
       </c>
@@ -9438,7 +9440,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -9449,7 +9451,7 @@
         <v>46631</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -9460,7 +9462,7 @@
         <v>48579</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -9471,7 +9473,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -9482,7 +9484,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -9493,7 +9495,7 @@
         <v>48579</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -9513,17 +9515,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9730,56 +9727,29 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
-    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="857" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16D657B8-4F27-4CE4-B140-B8BA0DAE14CC}"/>
+  <xr:revisionPtr revIDLastSave="858" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFF811AD-F8F0-46D1-8F66-F41B5999FE68}"/>
   <bookViews>
     <workbookView xWindow="-25935" yWindow="5655" windowWidth="21600" windowHeight="11085" firstSheet="2" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -1069,7 +1069,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
-  <dimension ref="A3:I331"/>
+  <dimension ref="A9:I331"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -1084,11 +1084,6 @@
     <col min="12" max="12" width="33.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:9">
-      <c r="H3">
-        <v>0</v>
-      </c>
-    </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
@@ -9515,12 +9510,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9727,21 +9727,16 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9749,7 +9744,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="858" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFF811AD-F8F0-46D1-8F66-F41B5999FE68}"/>
+  <xr:revisionPtr revIDLastSave="874" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5063DA84-1CAB-4443-AB90-BBB3A290DD81}"/>
   <bookViews>
-    <workbookView xWindow="-25935" yWindow="5655" windowWidth="21600" windowHeight="11085" firstSheet="2" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -273,7 +273,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -361,10 +361,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -373,11 +373,11 @@
       <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1070,7 +1070,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
   <dimension ref="A9:I331"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
@@ -1084,13 +1084,13 @@
     <col min="12" max="12" width="33.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
         <v>298</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -1145,7 +1145,7 @@
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -1171,7 +1171,7 @@
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>3</v>
       </c>
@@ -1197,7 +1197,7 @@
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>4</v>
       </c>
@@ -1223,7 +1223,7 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>5</v>
       </c>
@@ -1249,7 +1249,7 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>6</v>
       </c>
@@ -1275,7 +1275,7 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>7</v>
       </c>
@@ -1301,7 +1301,7 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>8</v>
       </c>
@@ -1327,7 +1327,7 @@
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>9</v>
       </c>
@@ -1353,7 +1353,7 @@
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>10</v>
       </c>
@@ -1379,7 +1379,7 @@
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>11</v>
       </c>
@@ -1405,7 +1405,7 @@
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>12</v>
       </c>
@@ -1431,7 +1431,7 @@
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>13</v>
       </c>
@@ -1457,7 +1457,7 @@
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>14</v>
       </c>
@@ -1483,7 +1483,7 @@
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>15</v>
       </c>
@@ -1509,7 +1509,7 @@
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>16</v>
       </c>
@@ -1535,7 +1535,7 @@
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>17</v>
       </c>
@@ -1561,7 +1561,7 @@
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>18</v>
       </c>
@@ -1587,7 +1587,7 @@
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>19</v>
       </c>
@@ -1613,7 +1613,7 @@
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>20</v>
       </c>
@@ -1639,7 +1639,7 @@
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>21</v>
       </c>
@@ -1665,7 +1665,7 @@
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>22</v>
       </c>
@@ -1691,7 +1691,7 @@
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>23</v>
       </c>
@@ -1717,7 +1717,7 @@
       <c r="H33" s="11"/>
       <c r="I33" s="11"/>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24</v>
       </c>
@@ -1743,7 +1743,7 @@
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>25</v>
       </c>
@@ -1769,7 +1769,7 @@
       <c r="H35" s="11"/>
       <c r="I35" s="11"/>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>26</v>
       </c>
@@ -1795,7 +1795,7 @@
       <c r="H36" s="11"/>
       <c r="I36" s="11"/>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>27</v>
       </c>
@@ -1821,7 +1821,7 @@
       <c r="H37" s="11"/>
       <c r="I37" s="11"/>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>28</v>
       </c>
@@ -1847,7 +1847,7 @@
       <c r="H38" s="11"/>
       <c r="I38" s="11"/>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>29</v>
       </c>
@@ -1873,7 +1873,7 @@
       <c r="H39" s="11"/>
       <c r="I39" s="11"/>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>30</v>
       </c>
@@ -1899,7 +1899,7 @@
       <c r="H40" s="11"/>
       <c r="I40" s="11"/>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>31</v>
       </c>
@@ -1925,7 +1925,7 @@
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>32</v>
       </c>
@@ -1951,7 +1951,7 @@
       <c r="H42" s="11"/>
       <c r="I42" s="11"/>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>33</v>
       </c>
@@ -1977,7 +1977,7 @@
       <c r="H43" s="11"/>
       <c r="I43" s="11"/>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>34</v>
       </c>
@@ -2003,7 +2003,7 @@
       <c r="H44" s="11"/>
       <c r="I44" s="11"/>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>35</v>
       </c>
@@ -2029,7 +2029,7 @@
       <c r="H45" s="11"/>
       <c r="I45" s="11"/>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>36</v>
       </c>
@@ -2055,7 +2055,7 @@
       <c r="H46" s="11"/>
       <c r="I46" s="11"/>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>37</v>
       </c>
@@ -2081,7 +2081,7 @@
       <c r="H47" s="11"/>
       <c r="I47" s="11"/>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>38</v>
       </c>
@@ -2107,7 +2107,7 @@
       <c r="H48" s="11"/>
       <c r="I48" s="11"/>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>39</v>
       </c>
@@ -2133,7 +2133,7 @@
       <c r="H49" s="11"/>
       <c r="I49" s="11"/>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>40</v>
       </c>
@@ -2159,7 +2159,7 @@
       <c r="H50" s="11"/>
       <c r="I50" s="11"/>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>41</v>
       </c>
@@ -2185,7 +2185,7 @@
       <c r="H51" s="11"/>
       <c r="I51" s="11"/>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>42</v>
       </c>
@@ -2211,7 +2211,7 @@
       <c r="H52" s="11"/>
       <c r="I52" s="11"/>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>43</v>
       </c>
@@ -2237,7 +2237,7 @@
       <c r="H53" s="11"/>
       <c r="I53" s="11"/>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>44</v>
       </c>
@@ -2263,7 +2263,7 @@
       <c r="H54" s="11"/>
       <c r="I54" s="11"/>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>45</v>
       </c>
@@ -2289,7 +2289,7 @@
       <c r="H55" s="11"/>
       <c r="I55" s="11"/>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>46</v>
       </c>
@@ -2315,7 +2315,7 @@
       <c r="H56" s="11"/>
       <c r="I56" s="11"/>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>47</v>
       </c>
@@ -2341,7 +2341,7 @@
       <c r="H57" s="11"/>
       <c r="I57" s="11"/>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>48</v>
       </c>
@@ -2367,7 +2367,7 @@
       <c r="H58" s="11"/>
       <c r="I58" s="11"/>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>49</v>
       </c>
@@ -2393,7 +2393,7 @@
       <c r="H59" s="11"/>
       <c r="I59" s="11"/>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>50</v>
       </c>
@@ -2419,7 +2419,7 @@
       <c r="H60" s="11"/>
       <c r="I60" s="11"/>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>51</v>
       </c>
@@ -2445,7 +2445,7 @@
       <c r="H61" s="11"/>
       <c r="I61" s="11"/>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>52</v>
       </c>
@@ -2471,7 +2471,7 @@
       <c r="H62" s="11"/>
       <c r="I62" s="11"/>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>53</v>
       </c>
@@ -2497,7 +2497,7 @@
       <c r="H63" s="11"/>
       <c r="I63" s="11"/>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>54</v>
       </c>
@@ -2523,7 +2523,7 @@
       <c r="H64" s="11"/>
       <c r="I64" s="11"/>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>55</v>
       </c>
@@ -2549,7 +2549,7 @@
       <c r="H65" s="11"/>
       <c r="I65" s="11"/>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>56</v>
       </c>
@@ -2575,7 +2575,7 @@
       <c r="H66" s="11"/>
       <c r="I66" s="11"/>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>57</v>
       </c>
@@ -2601,7 +2601,7 @@
       <c r="H67" s="11"/>
       <c r="I67" s="11"/>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>58</v>
       </c>
@@ -2627,7 +2627,7 @@
       <c r="H68" s="11"/>
       <c r="I68" s="11"/>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>59</v>
       </c>
@@ -2653,7 +2653,7 @@
       <c r="H69" s="11"/>
       <c r="I69" s="11"/>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>60</v>
       </c>
@@ -2679,7 +2679,7 @@
       <c r="H70" s="11"/>
       <c r="I70" s="11"/>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>61</v>
       </c>
@@ -2705,7 +2705,7 @@
       <c r="H71" s="11"/>
       <c r="I71" s="11"/>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>62</v>
       </c>
@@ -2731,7 +2731,7 @@
       <c r="H72" s="11"/>
       <c r="I72" s="11"/>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>63</v>
       </c>
@@ -2757,7 +2757,7 @@
       <c r="H73" s="11"/>
       <c r="I73" s="11"/>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>64</v>
       </c>
@@ -2783,7 +2783,7 @@
       <c r="H74" s="11"/>
       <c r="I74" s="11"/>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>65</v>
       </c>
@@ -2809,7 +2809,7 @@
       <c r="H75" s="11"/>
       <c r="I75" s="11"/>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>66</v>
       </c>
@@ -2835,7 +2835,7 @@
       <c r="H76" s="11"/>
       <c r="I76" s="11"/>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>67</v>
       </c>
@@ -2861,7 +2861,7 @@
       <c r="H77" s="11"/>
       <c r="I77" s="11"/>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>68</v>
       </c>
@@ -2887,7 +2887,7 @@
       <c r="H78" s="11"/>
       <c r="I78" s="11"/>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>69</v>
       </c>
@@ -2913,7 +2913,7 @@
       <c r="H79" s="11"/>
       <c r="I79" s="11"/>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>70</v>
       </c>
@@ -2939,7 +2939,7 @@
       <c r="H80" s="11"/>
       <c r="I80" s="11"/>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>71</v>
       </c>
@@ -2965,7 +2965,7 @@
       <c r="H81" s="11"/>
       <c r="I81" s="11"/>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>72</v>
       </c>
@@ -2991,7 +2991,7 @@
       <c r="H82" s="11"/>
       <c r="I82" s="11"/>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>73</v>
       </c>
@@ -3017,7 +3017,7 @@
       <c r="H83" s="11"/>
       <c r="I83" s="11"/>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>74</v>
       </c>
@@ -3043,7 +3043,7 @@
       <c r="H84" s="11"/>
       <c r="I84" s="11"/>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>75</v>
       </c>
@@ -3069,7 +3069,7 @@
       <c r="H85" s="11"/>
       <c r="I85" s="11"/>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>76</v>
       </c>
@@ -3095,7 +3095,7 @@
       <c r="H86" s="11"/>
       <c r="I86" s="11"/>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>77</v>
       </c>
@@ -3121,7 +3121,7 @@
       <c r="H87" s="11"/>
       <c r="I87" s="11"/>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>78</v>
       </c>
@@ -3147,7 +3147,7 @@
       <c r="H88" s="11"/>
       <c r="I88" s="11"/>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>79</v>
       </c>
@@ -3173,7 +3173,7 @@
       <c r="H89" s="11"/>
       <c r="I89" s="11"/>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>80</v>
       </c>
@@ -3199,7 +3199,7 @@
       <c r="H90" s="11"/>
       <c r="I90" s="11"/>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>81</v>
       </c>
@@ -3225,7 +3225,7 @@
       <c r="H91" s="11"/>
       <c r="I91" s="11"/>
     </row>
-    <row r="92" spans="1:9">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>82</v>
       </c>
@@ -3251,7 +3251,7 @@
       <c r="H92" s="11"/>
       <c r="I92" s="11"/>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>83</v>
       </c>
@@ -3277,7 +3277,7 @@
       <c r="H93" s="11"/>
       <c r="I93" s="11"/>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>84</v>
       </c>
@@ -3303,7 +3303,7 @@
       <c r="H94" s="11"/>
       <c r="I94" s="11"/>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>85</v>
       </c>
@@ -3329,7 +3329,7 @@
       <c r="H95" s="11"/>
       <c r="I95" s="11"/>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>86</v>
       </c>
@@ -3355,7 +3355,7 @@
       <c r="H96" s="11"/>
       <c r="I96" s="11"/>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>87</v>
       </c>
@@ -3381,7 +3381,7 @@
       <c r="H97" s="11"/>
       <c r="I97" s="11"/>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>88</v>
       </c>
@@ -3407,7 +3407,7 @@
       <c r="H98" s="11"/>
       <c r="I98" s="11"/>
     </row>
-    <row r="99" spans="1:9">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>89</v>
       </c>
@@ -3433,7 +3433,7 @@
       <c r="H99" s="11"/>
       <c r="I99" s="11"/>
     </row>
-    <row r="100" spans="1:9">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>90</v>
       </c>
@@ -3459,7 +3459,7 @@
       <c r="H100" s="11"/>
       <c r="I100" s="11"/>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>91</v>
       </c>
@@ -3485,7 +3485,7 @@
       <c r="H101" s="11"/>
       <c r="I101" s="11"/>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>92</v>
       </c>
@@ -3511,7 +3511,7 @@
       <c r="H102" s="11"/>
       <c r="I102" s="11"/>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>93</v>
       </c>
@@ -3537,7 +3537,7 @@
       <c r="H103" s="11"/>
       <c r="I103" s="11"/>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>94</v>
       </c>
@@ -3563,7 +3563,7 @@
       <c r="H104" s="11"/>
       <c r="I104" s="11"/>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>95</v>
       </c>
@@ -3589,7 +3589,7 @@
       <c r="H105" s="11"/>
       <c r="I105" s="11"/>
     </row>
-    <row r="106" spans="1:9">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>96</v>
       </c>
@@ -3615,7 +3615,7 @@
       <c r="H106" s="11"/>
       <c r="I106" s="11"/>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>97</v>
       </c>
@@ -3641,7 +3641,7 @@
       <c r="H107" s="11"/>
       <c r="I107" s="11"/>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>98</v>
       </c>
@@ -3667,7 +3667,7 @@
       <c r="H108" s="11"/>
       <c r="I108" s="11"/>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>99</v>
       </c>
@@ -3693,7 +3693,7 @@
       <c r="H109" s="11"/>
       <c r="I109" s="11"/>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>100</v>
       </c>
@@ -3719,7 +3719,7 @@
       <c r="H110" s="11"/>
       <c r="I110" s="11"/>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>101</v>
       </c>
@@ -3745,7 +3745,7 @@
       <c r="H111" s="11"/>
       <c r="I111" s="11"/>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>102</v>
       </c>
@@ -3771,7 +3771,7 @@
       <c r="H112" s="11"/>
       <c r="I112" s="11"/>
     </row>
-    <row r="113" spans="1:9">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>103</v>
       </c>
@@ -3797,7 +3797,7 @@
       <c r="H113" s="11"/>
       <c r="I113" s="11"/>
     </row>
-    <row r="114" spans="1:9">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>104</v>
       </c>
@@ -3823,7 +3823,7 @@
       <c r="H114" s="11"/>
       <c r="I114" s="11"/>
     </row>
-    <row r="115" spans="1:9">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>105</v>
       </c>
@@ -3849,7 +3849,7 @@
       <c r="H115" s="11"/>
       <c r="I115" s="11"/>
     </row>
-    <row r="116" spans="1:9">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>106</v>
       </c>
@@ -3875,7 +3875,7 @@
       <c r="H116" s="11"/>
       <c r="I116" s="11"/>
     </row>
-    <row r="117" spans="1:9">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>107</v>
       </c>
@@ -3901,7 +3901,7 @@
       <c r="H117" s="11"/>
       <c r="I117" s="11"/>
     </row>
-    <row r="118" spans="1:9">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>108</v>
       </c>
@@ -3927,7 +3927,7 @@
       <c r="H118" s="11"/>
       <c r="I118" s="11"/>
     </row>
-    <row r="119" spans="1:9">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>109</v>
       </c>
@@ -3953,7 +3953,7 @@
       <c r="H119" s="11"/>
       <c r="I119" s="11"/>
     </row>
-    <row r="120" spans="1:9">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>110</v>
       </c>
@@ -3979,7 +3979,7 @@
       <c r="H120" s="11"/>
       <c r="I120" s="11"/>
     </row>
-    <row r="121" spans="1:9">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>111</v>
       </c>
@@ -4005,7 +4005,7 @@
       <c r="H121" s="11"/>
       <c r="I121" s="11"/>
     </row>
-    <row r="122" spans="1:9">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>112</v>
       </c>
@@ -4031,7 +4031,7 @@
       <c r="H122" s="11"/>
       <c r="I122" s="11"/>
     </row>
-    <row r="123" spans="1:9">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>113</v>
       </c>
@@ -4057,7 +4057,7 @@
       <c r="H123" s="11"/>
       <c r="I123" s="11"/>
     </row>
-    <row r="124" spans="1:9">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>114</v>
       </c>
@@ -4083,7 +4083,7 @@
       <c r="H124" s="11"/>
       <c r="I124" s="11"/>
     </row>
-    <row r="125" spans="1:9">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>115</v>
       </c>
@@ -4109,7 +4109,7 @@
       <c r="H125" s="11"/>
       <c r="I125" s="11"/>
     </row>
-    <row r="126" spans="1:9">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>116</v>
       </c>
@@ -4135,7 +4135,7 @@
       <c r="H126" s="11"/>
       <c r="I126" s="11"/>
     </row>
-    <row r="127" spans="1:9">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>117</v>
       </c>
@@ -4161,7 +4161,7 @@
       <c r="H127" s="11"/>
       <c r="I127" s="11"/>
     </row>
-    <row r="128" spans="1:9">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>118</v>
       </c>
@@ -4187,7 +4187,7 @@
       <c r="H128" s="11"/>
       <c r="I128" s="11"/>
     </row>
-    <row r="129" spans="1:9">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>119</v>
       </c>
@@ -4213,7 +4213,7 @@
       <c r="H129" s="11"/>
       <c r="I129" s="11"/>
     </row>
-    <row r="130" spans="1:9">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>120</v>
       </c>
@@ -4239,7 +4239,7 @@
       <c r="H130" s="11"/>
       <c r="I130" s="11"/>
     </row>
-    <row r="131" spans="1:9">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>121</v>
       </c>
@@ -4265,7 +4265,7 @@
       <c r="H131" s="11"/>
       <c r="I131" s="11"/>
     </row>
-    <row r="132" spans="1:9">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>122</v>
       </c>
@@ -4291,7 +4291,7 @@
       <c r="H132" s="11"/>
       <c r="I132" s="11"/>
     </row>
-    <row r="133" spans="1:9">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>123</v>
       </c>
@@ -4317,7 +4317,7 @@
       <c r="H133" s="11"/>
       <c r="I133" s="11"/>
     </row>
-    <row r="134" spans="1:9">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>124</v>
       </c>
@@ -4343,7 +4343,7 @@
       <c r="H134" s="11"/>
       <c r="I134" s="11"/>
     </row>
-    <row r="135" spans="1:9">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>125</v>
       </c>
@@ -4369,7 +4369,7 @@
       <c r="H135" s="11"/>
       <c r="I135" s="11"/>
     </row>
-    <row r="136" spans="1:9">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>126</v>
       </c>
@@ -4395,7 +4395,7 @@
       <c r="H136" s="11"/>
       <c r="I136" s="11"/>
     </row>
-    <row r="137" spans="1:9">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>127</v>
       </c>
@@ -4421,7 +4421,7 @@
       <c r="H137" s="11"/>
       <c r="I137" s="11"/>
     </row>
-    <row r="138" spans="1:9">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>128</v>
       </c>
@@ -4447,7 +4447,7 @@
       <c r="H138" s="11"/>
       <c r="I138" s="11"/>
     </row>
-    <row r="139" spans="1:9">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>129</v>
       </c>
@@ -4473,7 +4473,7 @@
       <c r="H139" s="11"/>
       <c r="I139" s="11"/>
     </row>
-    <row r="140" spans="1:9">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>130</v>
       </c>
@@ -4499,7 +4499,7 @@
       <c r="H140" s="11"/>
       <c r="I140" s="11"/>
     </row>
-    <row r="141" spans="1:9">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>131</v>
       </c>
@@ -4525,7 +4525,7 @@
       <c r="H141" s="11"/>
       <c r="I141" s="11"/>
     </row>
-    <row r="142" spans="1:9">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>132</v>
       </c>
@@ -4551,7 +4551,7 @@
       <c r="H142" s="11"/>
       <c r="I142" s="11"/>
     </row>
-    <row r="143" spans="1:9">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>133</v>
       </c>
@@ -4577,7 +4577,7 @@
       <c r="H143" s="11"/>
       <c r="I143" s="11"/>
     </row>
-    <row r="144" spans="1:9">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>134</v>
       </c>
@@ -4603,7 +4603,7 @@
       <c r="H144" s="11"/>
       <c r="I144" s="11"/>
     </row>
-    <row r="145" spans="1:9">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>135</v>
       </c>
@@ -4629,7 +4629,7 @@
       <c r="H145" s="11"/>
       <c r="I145" s="11"/>
     </row>
-    <row r="146" spans="1:9">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>136</v>
       </c>
@@ -4655,7 +4655,7 @@
       <c r="H146" s="11"/>
       <c r="I146" s="11"/>
     </row>
-    <row r="147" spans="1:9">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>137</v>
       </c>
@@ -4681,7 +4681,7 @@
       <c r="H147" s="11"/>
       <c r="I147" s="11"/>
     </row>
-    <row r="148" spans="1:9">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>138</v>
       </c>
@@ -4707,7 +4707,7 @@
       <c r="H148" s="11"/>
       <c r="I148" s="11"/>
     </row>
-    <row r="149" spans="1:9">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>139</v>
       </c>
@@ -4733,7 +4733,7 @@
       <c r="H149" s="11"/>
       <c r="I149" s="11"/>
     </row>
-    <row r="150" spans="1:9">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>140</v>
       </c>
@@ -4759,7 +4759,7 @@
       <c r="H150" s="11"/>
       <c r="I150" s="11"/>
     </row>
-    <row r="151" spans="1:9">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>141</v>
       </c>
@@ -4785,7 +4785,7 @@
       <c r="H151" s="11"/>
       <c r="I151" s="11"/>
     </row>
-    <row r="152" spans="1:9">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>142</v>
       </c>
@@ -4811,7 +4811,7 @@
       <c r="H152" s="11"/>
       <c r="I152" s="11"/>
     </row>
-    <row r="153" spans="1:9">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>143</v>
       </c>
@@ -4837,7 +4837,7 @@
       <c r="H153" s="11"/>
       <c r="I153" s="11"/>
     </row>
-    <row r="154" spans="1:9">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>144</v>
       </c>
@@ -4863,7 +4863,7 @@
       <c r="H154" s="11"/>
       <c r="I154" s="11"/>
     </row>
-    <row r="155" spans="1:9">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>145</v>
       </c>
@@ -4889,7 +4889,7 @@
       <c r="H155" s="11"/>
       <c r="I155" s="11"/>
     </row>
-    <row r="156" spans="1:9">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>146</v>
       </c>
@@ -4915,7 +4915,7 @@
       <c r="H156" s="11"/>
       <c r="I156" s="11"/>
     </row>
-    <row r="157" spans="1:9">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>147</v>
       </c>
@@ -4941,7 +4941,7 @@
       <c r="H157" s="11"/>
       <c r="I157" s="11"/>
     </row>
-    <row r="158" spans="1:9">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>148</v>
       </c>
@@ -4967,7 +4967,7 @@
       <c r="H158" s="11"/>
       <c r="I158" s="11"/>
     </row>
-    <row r="159" spans="1:9">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>149</v>
       </c>
@@ -4993,7 +4993,7 @@
       <c r="H159" s="11"/>
       <c r="I159" s="11"/>
     </row>
-    <row r="160" spans="1:9">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>150</v>
       </c>
@@ -5019,7 +5019,7 @@
       <c r="H160" s="11"/>
       <c r="I160" s="11"/>
     </row>
-    <row r="161" spans="1:9">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>151</v>
       </c>
@@ -5045,7 +5045,7 @@
       <c r="H161" s="11"/>
       <c r="I161" s="11"/>
     </row>
-    <row r="162" spans="1:9">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>152</v>
       </c>
@@ -5071,7 +5071,7 @@
       <c r="H162" s="11"/>
       <c r="I162" s="11"/>
     </row>
-    <row r="163" spans="1:9">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>153</v>
       </c>
@@ -5097,7 +5097,7 @@
       <c r="H163" s="11"/>
       <c r="I163" s="11"/>
     </row>
-    <row r="164" spans="1:9">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>154</v>
       </c>
@@ -5123,7 +5123,7 @@
       <c r="H164" s="11"/>
       <c r="I164" s="11"/>
     </row>
-    <row r="165" spans="1:9">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>155</v>
       </c>
@@ -5149,7 +5149,7 @@
       <c r="H165" s="11"/>
       <c r="I165" s="11"/>
     </row>
-    <row r="166" spans="1:9">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>156</v>
       </c>
@@ -5175,7 +5175,7 @@
       <c r="H166" s="11"/>
       <c r="I166" s="11"/>
     </row>
-    <row r="167" spans="1:9">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>157</v>
       </c>
@@ -5201,7 +5201,7 @@
       <c r="H167" s="11"/>
       <c r="I167" s="11"/>
     </row>
-    <row r="168" spans="1:9">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>158</v>
       </c>
@@ -5227,7 +5227,7 @@
       <c r="H168" s="11"/>
       <c r="I168" s="11"/>
     </row>
-    <row r="169" spans="1:9">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>159</v>
       </c>
@@ -5253,7 +5253,7 @@
       <c r="H169" s="11"/>
       <c r="I169" s="11"/>
     </row>
-    <row r="170" spans="1:9">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>160</v>
       </c>
@@ -5279,7 +5279,7 @@
       <c r="H170" s="11"/>
       <c r="I170" s="11"/>
     </row>
-    <row r="171" spans="1:9">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>161</v>
       </c>
@@ -5305,7 +5305,7 @@
       <c r="H171" s="11"/>
       <c r="I171" s="11"/>
     </row>
-    <row r="172" spans="1:9">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>162</v>
       </c>
@@ -5331,7 +5331,7 @@
       <c r="H172" s="11"/>
       <c r="I172" s="11"/>
     </row>
-    <row r="173" spans="1:9">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>163</v>
       </c>
@@ -5357,7 +5357,7 @@
       <c r="H173" s="11"/>
       <c r="I173" s="11"/>
     </row>
-    <row r="174" spans="1:9">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>164</v>
       </c>
@@ -5383,7 +5383,7 @@
       <c r="H174" s="11"/>
       <c r="I174" s="11"/>
     </row>
-    <row r="175" spans="1:9">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>165</v>
       </c>
@@ -5409,7 +5409,7 @@
       <c r="H175" s="11"/>
       <c r="I175" s="11"/>
     </row>
-    <row r="176" spans="1:9">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>166</v>
       </c>
@@ -5435,7 +5435,7 @@
       <c r="H176" s="11"/>
       <c r="I176" s="11"/>
     </row>
-    <row r="177" spans="1:9">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>167</v>
       </c>
@@ -5461,7 +5461,7 @@
       <c r="H177" s="11"/>
       <c r="I177" s="11"/>
     </row>
-    <row r="178" spans="1:9">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>168</v>
       </c>
@@ -5487,7 +5487,7 @@
       <c r="H178" s="11"/>
       <c r="I178" s="11"/>
     </row>
-    <row r="179" spans="1:9">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>169</v>
       </c>
@@ -5513,7 +5513,7 @@
       <c r="H179" s="11"/>
       <c r="I179" s="11"/>
     </row>
-    <row r="180" spans="1:9">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>170</v>
       </c>
@@ -5539,7 +5539,7 @@
       <c r="H180" s="11"/>
       <c r="I180" s="11"/>
     </row>
-    <row r="181" spans="1:9">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>171</v>
       </c>
@@ -5565,7 +5565,7 @@
       <c r="H181" s="11"/>
       <c r="I181" s="11"/>
     </row>
-    <row r="182" spans="1:9">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>172</v>
       </c>
@@ -5591,7 +5591,7 @@
       <c r="H182" s="11"/>
       <c r="I182" s="11"/>
     </row>
-    <row r="183" spans="1:9">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>173</v>
       </c>
@@ -5617,7 +5617,7 @@
       <c r="H183" s="11"/>
       <c r="I183" s="11"/>
     </row>
-    <row r="184" spans="1:9">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>174</v>
       </c>
@@ -5643,7 +5643,7 @@
       <c r="H184" s="11"/>
       <c r="I184" s="11"/>
     </row>
-    <row r="185" spans="1:9">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>175</v>
       </c>
@@ -5669,7 +5669,7 @@
       <c r="H185" s="11"/>
       <c r="I185" s="11"/>
     </row>
-    <row r="186" spans="1:9">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>176</v>
       </c>
@@ -5695,7 +5695,7 @@
       <c r="H186" s="11"/>
       <c r="I186" s="11"/>
     </row>
-    <row r="187" spans="1:9">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>177</v>
       </c>
@@ -5721,7 +5721,7 @@
       <c r="H187" s="11"/>
       <c r="I187" s="11"/>
     </row>
-    <row r="188" spans="1:9">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>178</v>
       </c>
@@ -5747,7 +5747,7 @@
       <c r="H188" s="11"/>
       <c r="I188" s="11"/>
     </row>
-    <row r="189" spans="1:9">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>179</v>
       </c>
@@ -5773,7 +5773,7 @@
       <c r="H189" s="11"/>
       <c r="I189" s="11"/>
     </row>
-    <row r="190" spans="1:9">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>180</v>
       </c>
@@ -5799,7 +5799,7 @@
       <c r="H190" s="11"/>
       <c r="I190" s="11"/>
     </row>
-    <row r="191" spans="1:9">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>181</v>
       </c>
@@ -5825,7 +5825,7 @@
       <c r="H191" s="11"/>
       <c r="I191" s="11"/>
     </row>
-    <row r="192" spans="1:9">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>182</v>
       </c>
@@ -5851,7 +5851,7 @@
       <c r="H192" s="11"/>
       <c r="I192" s="11"/>
     </row>
-    <row r="193" spans="1:9">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>183</v>
       </c>
@@ -5877,7 +5877,7 @@
       <c r="H193" s="11"/>
       <c r="I193" s="11"/>
     </row>
-    <row r="194" spans="1:9">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>184</v>
       </c>
@@ -5903,7 +5903,7 @@
       <c r="H194" s="11"/>
       <c r="I194" s="11"/>
     </row>
-    <row r="195" spans="1:9">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>185</v>
       </c>
@@ -5929,7 +5929,7 @@
       <c r="H195" s="11"/>
       <c r="I195" s="11"/>
     </row>
-    <row r="196" spans="1:9">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>186</v>
       </c>
@@ -5955,7 +5955,7 @@
       <c r="H196" s="11"/>
       <c r="I196" s="11"/>
     </row>
-    <row r="197" spans="1:9">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>187</v>
       </c>
@@ -5981,7 +5981,7 @@
       <c r="H197" s="11"/>
       <c r="I197" s="11"/>
     </row>
-    <row r="198" spans="1:9">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>188</v>
       </c>
@@ -6007,7 +6007,7 @@
       <c r="H198" s="11"/>
       <c r="I198" s="11"/>
     </row>
-    <row r="199" spans="1:9">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>189</v>
       </c>
@@ -6033,7 +6033,7 @@
       <c r="H199" s="11"/>
       <c r="I199" s="11"/>
     </row>
-    <row r="200" spans="1:9">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>190</v>
       </c>
@@ -6059,7 +6059,7 @@
       <c r="H200" s="11"/>
       <c r="I200" s="11"/>
     </row>
-    <row r="201" spans="1:9">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>191</v>
       </c>
@@ -6085,7 +6085,7 @@
       <c r="H201" s="11"/>
       <c r="I201" s="11"/>
     </row>
-    <row r="202" spans="1:9">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>192</v>
       </c>
@@ -6111,7 +6111,7 @@
       <c r="H202" s="11"/>
       <c r="I202" s="11"/>
     </row>
-    <row r="203" spans="1:9">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>193</v>
       </c>
@@ -6137,7 +6137,7 @@
       <c r="H203" s="11"/>
       <c r="I203" s="11"/>
     </row>
-    <row r="204" spans="1:9">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>194</v>
       </c>
@@ -6163,7 +6163,7 @@
       <c r="H204" s="11"/>
       <c r="I204" s="11"/>
     </row>
-    <row r="205" spans="1:9">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>195</v>
       </c>
@@ -6189,7 +6189,7 @@
       <c r="H205" s="11"/>
       <c r="I205" s="11"/>
     </row>
-    <row r="206" spans="1:9">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>196</v>
       </c>
@@ -6215,7 +6215,7 @@
       <c r="H206" s="11"/>
       <c r="I206" s="11"/>
     </row>
-    <row r="207" spans="1:9">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>197</v>
       </c>
@@ -6241,7 +6241,7 @@
       <c r="H207" s="11"/>
       <c r="I207" s="11"/>
     </row>
-    <row r="208" spans="1:9">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>198</v>
       </c>
@@ -6267,7 +6267,7 @@
       <c r="H208" s="11"/>
       <c r="I208" s="11"/>
     </row>
-    <row r="209" spans="1:9">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>199</v>
       </c>
@@ -6293,7 +6293,7 @@
       <c r="H209" s="11"/>
       <c r="I209" s="11"/>
     </row>
-    <row r="210" spans="1:9">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>200</v>
       </c>
@@ -6319,7 +6319,7 @@
       <c r="H210" s="11"/>
       <c r="I210" s="11"/>
     </row>
-    <row r="211" spans="1:9">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <v>201</v>
       </c>
@@ -6345,7 +6345,7 @@
       <c r="H211" s="11"/>
       <c r="I211" s="11"/>
     </row>
-    <row r="212" spans="1:9">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>202</v>
       </c>
@@ -6371,7 +6371,7 @@
       <c r="H212" s="11"/>
       <c r="I212" s="11"/>
     </row>
-    <row r="213" spans="1:9">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <v>203</v>
       </c>
@@ -6397,7 +6397,7 @@
       <c r="H213" s="11"/>
       <c r="I213" s="11"/>
     </row>
-    <row r="214" spans="1:9">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>204</v>
       </c>
@@ -6423,7 +6423,7 @@
       <c r="H214" s="11"/>
       <c r="I214" s="11"/>
     </row>
-    <row r="215" spans="1:9">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>205</v>
       </c>
@@ -6449,7 +6449,7 @@
       <c r="H215" s="11"/>
       <c r="I215" s="11"/>
     </row>
-    <row r="216" spans="1:9">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <v>206</v>
       </c>
@@ -6475,7 +6475,7 @@
       <c r="H216" s="11"/>
       <c r="I216" s="11"/>
     </row>
-    <row r="217" spans="1:9">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <v>207</v>
       </c>
@@ -6501,7 +6501,7 @@
       <c r="H217" s="11"/>
       <c r="I217" s="11"/>
     </row>
-    <row r="218" spans="1:9">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <v>208</v>
       </c>
@@ -6527,7 +6527,7 @@
       <c r="H218" s="11"/>
       <c r="I218" s="11"/>
     </row>
-    <row r="219" spans="1:9">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <v>209</v>
       </c>
@@ -6553,7 +6553,7 @@
       <c r="H219" s="11"/>
       <c r="I219" s="11"/>
     </row>
-    <row r="220" spans="1:9">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <v>210</v>
       </c>
@@ -6579,7 +6579,7 @@
       <c r="H220" s="11"/>
       <c r="I220" s="11"/>
     </row>
-    <row r="221" spans="1:9">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <v>211</v>
       </c>
@@ -6605,7 +6605,7 @@
       <c r="H221" s="11"/>
       <c r="I221" s="11"/>
     </row>
-    <row r="222" spans="1:9">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <v>212</v>
       </c>
@@ -6631,7 +6631,7 @@
       <c r="H222" s="11"/>
       <c r="I222" s="11"/>
     </row>
-    <row r="223" spans="1:9">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <v>213</v>
       </c>
@@ -6657,7 +6657,7 @@
       <c r="H223" s="11"/>
       <c r="I223" s="11"/>
     </row>
-    <row r="224" spans="1:9">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <v>214</v>
       </c>
@@ -6683,7 +6683,7 @@
       <c r="H224" s="11"/>
       <c r="I224" s="11"/>
     </row>
-    <row r="225" spans="1:9">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>215</v>
       </c>
@@ -6709,7 +6709,7 @@
       <c r="H225" s="11"/>
       <c r="I225" s="11"/>
     </row>
-    <row r="226" spans="1:9">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <v>216</v>
       </c>
@@ -6735,7 +6735,7 @@
       <c r="H226" s="11"/>
       <c r="I226" s="11"/>
     </row>
-    <row r="227" spans="1:9">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
         <v>217</v>
       </c>
@@ -6761,7 +6761,7 @@
       <c r="H227" s="11"/>
       <c r="I227" s="11"/>
     </row>
-    <row r="228" spans="1:9">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <v>218</v>
       </c>
@@ -6787,7 +6787,7 @@
       <c r="H228" s="11"/>
       <c r="I228" s="11"/>
     </row>
-    <row r="229" spans="1:9">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <v>219</v>
       </c>
@@ -6813,7 +6813,7 @@
       <c r="H229" s="11"/>
       <c r="I229" s="11"/>
     </row>
-    <row r="230" spans="1:9">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <v>220</v>
       </c>
@@ -6839,7 +6839,7 @@
       <c r="H230" s="11"/>
       <c r="I230" s="11"/>
     </row>
-    <row r="231" spans="1:9">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
         <v>221</v>
       </c>
@@ -6865,7 +6865,7 @@
       <c r="H231" s="11"/>
       <c r="I231" s="11"/>
     </row>
-    <row r="232" spans="1:9">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
         <v>222</v>
       </c>
@@ -6891,7 +6891,7 @@
       <c r="H232" s="11"/>
       <c r="I232" s="11"/>
     </row>
-    <row r="233" spans="1:9">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <v>223</v>
       </c>
@@ -6917,7 +6917,7 @@
       <c r="H233" s="11"/>
       <c r="I233" s="11"/>
     </row>
-    <row r="234" spans="1:9">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <v>224</v>
       </c>
@@ -6943,7 +6943,7 @@
       <c r="H234" s="11"/>
       <c r="I234" s="11"/>
     </row>
-    <row r="235" spans="1:9">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <v>225</v>
       </c>
@@ -6969,7 +6969,7 @@
       <c r="H235" s="11"/>
       <c r="I235" s="11"/>
     </row>
-    <row r="236" spans="1:9">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <v>226</v>
       </c>
@@ -6995,7 +6995,7 @@
       <c r="H236" s="11"/>
       <c r="I236" s="11"/>
     </row>
-    <row r="237" spans="1:9">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <v>227</v>
       </c>
@@ -7021,7 +7021,7 @@
       <c r="H237" s="11"/>
       <c r="I237" s="11"/>
     </row>
-    <row r="238" spans="1:9">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <v>228</v>
       </c>
@@ -7047,7 +7047,7 @@
       <c r="H238" s="11"/>
       <c r="I238" s="11"/>
     </row>
-    <row r="239" spans="1:9">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <v>229</v>
       </c>
@@ -7073,7 +7073,7 @@
       <c r="H239" s="11"/>
       <c r="I239" s="11"/>
     </row>
-    <row r="240" spans="1:9">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <v>230</v>
       </c>
@@ -7099,7 +7099,7 @@
       <c r="H240" s="11"/>
       <c r="I240" s="11"/>
     </row>
-    <row r="241" spans="1:9">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
         <v>231</v>
       </c>
@@ -7125,7 +7125,7 @@
       <c r="H241" s="11"/>
       <c r="I241" s="11"/>
     </row>
-    <row r="242" spans="1:9">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
         <v>232</v>
       </c>
@@ -7151,7 +7151,7 @@
       <c r="H242" s="11"/>
       <c r="I242" s="11"/>
     </row>
-    <row r="243" spans="1:9">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
         <v>233</v>
       </c>
@@ -7177,7 +7177,7 @@
       <c r="H243" s="11"/>
       <c r="I243" s="11"/>
     </row>
-    <row r="244" spans="1:9">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
         <v>234</v>
       </c>
@@ -7203,7 +7203,7 @@
       <c r="H244" s="11"/>
       <c r="I244" s="11"/>
     </row>
-    <row r="245" spans="1:9">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
         <v>235</v>
       </c>
@@ -7229,7 +7229,7 @@
       <c r="H245" s="11"/>
       <c r="I245" s="11"/>
     </row>
-    <row r="246" spans="1:9">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
         <v>236</v>
       </c>
@@ -7255,7 +7255,7 @@
       <c r="H246" s="11"/>
       <c r="I246" s="11"/>
     </row>
-    <row r="247" spans="1:9">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
         <v>237</v>
       </c>
@@ -7281,7 +7281,7 @@
       <c r="H247" s="11"/>
       <c r="I247" s="11"/>
     </row>
-    <row r="248" spans="1:9">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <v>238</v>
       </c>
@@ -7307,7 +7307,7 @@
       <c r="H248" s="11"/>
       <c r="I248" s="11"/>
     </row>
-    <row r="249" spans="1:9">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
         <v>239</v>
       </c>
@@ -7333,7 +7333,7 @@
       <c r="H249" s="11"/>
       <c r="I249" s="11"/>
     </row>
-    <row r="250" spans="1:9">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
         <v>240</v>
       </c>
@@ -7359,7 +7359,7 @@
       <c r="H250" s="11"/>
       <c r="I250" s="11"/>
     </row>
-    <row r="251" spans="1:9">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
         <v>241</v>
       </c>
@@ -7385,7 +7385,7 @@
       <c r="H251" s="11"/>
       <c r="I251" s="11"/>
     </row>
-    <row r="252" spans="1:9">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
         <v>242</v>
       </c>
@@ -7411,7 +7411,7 @@
       <c r="H252" s="11"/>
       <c r="I252" s="11"/>
     </row>
-    <row r="253" spans="1:9">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
         <v>243</v>
       </c>
@@ -7437,7 +7437,7 @@
       <c r="H253" s="11"/>
       <c r="I253" s="11"/>
     </row>
-    <row r="254" spans="1:9">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
         <v>244</v>
       </c>
@@ -7463,7 +7463,7 @@
       <c r="H254" s="11"/>
       <c r="I254" s="11"/>
     </row>
-    <row r="255" spans="1:9">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
         <v>245</v>
       </c>
@@ -7489,7 +7489,7 @@
       <c r="H255" s="11"/>
       <c r="I255" s="11"/>
     </row>
-    <row r="256" spans="1:9">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
         <v>246</v>
       </c>
@@ -7515,7 +7515,7 @@
       <c r="H256" s="11"/>
       <c r="I256" s="11"/>
     </row>
-    <row r="257" spans="1:9">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
         <v>247</v>
       </c>
@@ -7541,7 +7541,7 @@
       <c r="H257" s="11"/>
       <c r="I257" s="11"/>
     </row>
-    <row r="258" spans="1:9">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
         <v>248</v>
       </c>
@@ -7567,7 +7567,7 @@
       <c r="H258" s="11"/>
       <c r="I258" s="11"/>
     </row>
-    <row r="259" spans="1:9">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
         <v>249</v>
       </c>
@@ -7593,7 +7593,7 @@
       <c r="H259" s="11"/>
       <c r="I259" s="11"/>
     </row>
-    <row r="260" spans="1:9">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
         <v>250</v>
       </c>
@@ -7619,7 +7619,7 @@
       <c r="H260" s="11"/>
       <c r="I260" s="11"/>
     </row>
-    <row r="261" spans="1:9">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
         <v>251</v>
       </c>
@@ -7645,7 +7645,7 @@
       <c r="H261" s="11"/>
       <c r="I261" s="11"/>
     </row>
-    <row r="262" spans="1:9">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
         <v>252</v>
       </c>
@@ -7671,7 +7671,7 @@
       <c r="H262" s="11"/>
       <c r="I262" s="11"/>
     </row>
-    <row r="263" spans="1:9">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
         <v>253</v>
       </c>
@@ -7697,7 +7697,7 @@
       <c r="H263" s="11"/>
       <c r="I263" s="11"/>
     </row>
-    <row r="264" spans="1:9">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
         <v>254</v>
       </c>
@@ -7723,7 +7723,7 @@
       <c r="H264" s="11"/>
       <c r="I264" s="11"/>
     </row>
-    <row r="265" spans="1:9">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
         <v>255</v>
       </c>
@@ -7749,7 +7749,7 @@
       <c r="H265" s="11"/>
       <c r="I265" s="11"/>
     </row>
-    <row r="266" spans="1:9">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
         <v>256</v>
       </c>
@@ -7775,7 +7775,7 @@
       <c r="H266" s="11"/>
       <c r="I266" s="11"/>
     </row>
-    <row r="267" spans="1:9">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
         <v>257</v>
       </c>
@@ -7801,7 +7801,7 @@
       <c r="H267" s="11"/>
       <c r="I267" s="11"/>
     </row>
-    <row r="268" spans="1:9">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
         <v>258</v>
       </c>
@@ -7827,7 +7827,7 @@
       <c r="H268" s="11"/>
       <c r="I268" s="11"/>
     </row>
-    <row r="269" spans="1:9">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
         <v>259</v>
       </c>
@@ -7853,7 +7853,7 @@
       <c r="H269" s="11"/>
       <c r="I269" s="11"/>
     </row>
-    <row r="270" spans="1:9">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
         <v>260</v>
       </c>
@@ -7879,7 +7879,7 @@
       <c r="H270" s="11"/>
       <c r="I270" s="11"/>
     </row>
-    <row r="271" spans="1:9">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
         <v>261</v>
       </c>
@@ -7905,7 +7905,7 @@
       <c r="H271" s="11"/>
       <c r="I271" s="11"/>
     </row>
-    <row r="272" spans="1:9">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
         <v>262</v>
       </c>
@@ -7931,7 +7931,7 @@
       <c r="H272" s="11"/>
       <c r="I272" s="11"/>
     </row>
-    <row r="273" spans="1:9">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
         <v>263</v>
       </c>
@@ -7957,7 +7957,7 @@
       <c r="H273" s="11"/>
       <c r="I273" s="11"/>
     </row>
-    <row r="274" spans="1:9">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
         <v>264</v>
       </c>
@@ -7983,7 +7983,7 @@
       <c r="H274" s="11"/>
       <c r="I274" s="11"/>
     </row>
-    <row r="275" spans="1:9">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
         <v>265</v>
       </c>
@@ -8009,7 +8009,7 @@
       <c r="H275" s="11"/>
       <c r="I275" s="11"/>
     </row>
-    <row r="276" spans="1:9">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
         <v>266</v>
       </c>
@@ -8035,7 +8035,7 @@
       <c r="H276" s="11"/>
       <c r="I276" s="11"/>
     </row>
-    <row r="277" spans="1:9">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
         <v>267</v>
       </c>
@@ -8061,7 +8061,7 @@
       <c r="H277" s="11"/>
       <c r="I277" s="11"/>
     </row>
-    <row r="278" spans="1:9">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
         <v>268</v>
       </c>
@@ -8087,7 +8087,7 @@
       <c r="H278" s="11"/>
       <c r="I278" s="11"/>
     </row>
-    <row r="279" spans="1:9">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
         <v>269</v>
       </c>
@@ -8113,7 +8113,7 @@
       <c r="H279" s="11"/>
       <c r="I279" s="11"/>
     </row>
-    <row r="280" spans="1:9">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
         <v>270</v>
       </c>
@@ -8139,7 +8139,7 @@
       <c r="H280" s="11"/>
       <c r="I280" s="11"/>
     </row>
-    <row r="281" spans="1:9">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
         <v>271</v>
       </c>
@@ -8165,7 +8165,7 @@
       <c r="H281" s="11"/>
       <c r="I281" s="11"/>
     </row>
-    <row r="282" spans="1:9">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
         <v>272</v>
       </c>
@@ -8191,7 +8191,7 @@
       <c r="H282" s="11"/>
       <c r="I282" s="11"/>
     </row>
-    <row r="283" spans="1:9">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
         <v>273</v>
       </c>
@@ -8217,7 +8217,7 @@
       <c r="H283" s="11"/>
       <c r="I283" s="11"/>
     </row>
-    <row r="284" spans="1:9">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
         <v>274</v>
       </c>
@@ -8243,7 +8243,7 @@
       <c r="H284" s="11"/>
       <c r="I284" s="11"/>
     </row>
-    <row r="285" spans="1:9">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
         <v>275</v>
       </c>
@@ -8269,7 +8269,7 @@
       <c r="H285" s="11"/>
       <c r="I285" s="11"/>
     </row>
-    <row r="286" spans="1:9">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
         <v>276</v>
       </c>
@@ -8299,7 +8299,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="287" spans="1:9">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
         <v>277</v>
       </c>
@@ -8329,7 +8329,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="288" spans="1:9">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
         <v>278</v>
       </c>
@@ -8359,7 +8359,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="289" spans="1:9">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
         <v>279</v>
       </c>
@@ -8389,7 +8389,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="290" spans="1:9">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
         <v>280</v>
       </c>
@@ -8419,7 +8419,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="291" spans="1:9">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
         <v>281</v>
       </c>
@@ -8449,7 +8449,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="292" spans="1:9">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
         <v>282</v>
       </c>
@@ -8479,7 +8479,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="293" spans="1:9">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
         <v>283</v>
       </c>
@@ -8509,7 +8509,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="294" spans="1:9">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
         <v>284</v>
       </c>
@@ -8539,7 +8539,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="295" spans="1:9">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
         <v>285</v>
       </c>
@@ -8569,7 +8569,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="296" spans="1:9">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
         <v>286</v>
       </c>
@@ -8599,7 +8599,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="297" spans="1:9">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
         <v>287</v>
       </c>
@@ -8629,7 +8629,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="298" spans="1:9">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
         <v>288</v>
       </c>
@@ -8659,7 +8659,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="299" spans="1:9">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
         <v>289</v>
       </c>
@@ -8689,7 +8689,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="300" spans="1:9">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
         <v>290</v>
       </c>
@@ -8719,7 +8719,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="301" spans="1:9">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
         <v>291</v>
       </c>
@@ -8749,7 +8749,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="302" spans="1:9">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
         <v>292</v>
       </c>
@@ -8779,7 +8779,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="303" spans="1:9" s="1" customFormat="1">
+    <row r="303" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
         <v>293</v>
       </c>
@@ -8809,7 +8809,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="304" spans="1:9" s="1" customFormat="1">
+    <row r="304" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
         <v>294</v>
       </c>
@@ -8839,7 +8839,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="305" spans="1:9">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
         <v>295</v>
       </c>
@@ -8869,7 +8869,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="306" spans="1:9">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
         <v>296</v>
       </c>
@@ -8899,7 +8899,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="307" spans="1:9">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
         <v>297</v>
       </c>
@@ -8929,7 +8929,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="308" spans="1:9">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
         <v>298</v>
       </c>
@@ -8959,73 +8959,73 @@
         <v>56</v>
       </c>
     </row>
-    <row r="309" spans="1:9">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" s="1"/>
     </row>
-    <row r="310" spans="1:9">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" s="1"/>
     </row>
-    <row r="311" spans="1:9">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" s="1"/>
     </row>
-    <row r="312" spans="1:9">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" s="1"/>
     </row>
-    <row r="313" spans="1:9">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" s="1"/>
     </row>
-    <row r="314" spans="1:9">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" s="1"/>
     </row>
-    <row r="315" spans="1:9">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" s="1"/>
     </row>
-    <row r="316" spans="1:9">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" s="1"/>
     </row>
-    <row r="317" spans="1:9">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" s="1"/>
     </row>
-    <row r="318" spans="1:9">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" s="1"/>
     </row>
-    <row r="319" spans="1:9">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" s="1"/>
     </row>
-    <row r="320" spans="1:9">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" s="1"/>
     </row>
-    <row r="321" spans="1:1">
+    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A321" s="1"/>
     </row>
-    <row r="322" spans="1:1">
+    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A322" s="1"/>
     </row>
-    <row r="323" spans="1:1">
+    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>
     </row>
-    <row r="324" spans="1:1">
+    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A324" s="1"/>
     </row>
-    <row r="325" spans="1:1">
+    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A325" s="1"/>
     </row>
-    <row r="326" spans="1:1">
+    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A326" s="1"/>
     </row>
-    <row r="327" spans="1:1">
+    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
     </row>
-    <row r="328" spans="1:1">
+    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A328" s="1"/>
     </row>
-    <row r="329" spans="1:1">
+    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A329" s="1"/>
     </row>
-    <row r="330" spans="1:1">
+    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>
     </row>
-    <row r="331" spans="1:1">
+    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A331" s="1"/>
     </row>
   </sheetData>
@@ -9047,13 +9047,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{797F1036-D41E-43A4-9E6E-CBBB62F3CD31}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="13.28515625" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9067,7 +9067,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -9081,7 +9081,7 @@
         <v>234.67</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -9095,7 +9095,7 @@
         <v>161.15</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -9109,7 +9109,7 @@
         <v>157.61000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -9123,7 +9123,7 @@
         <v>347.95</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -9137,7 +9137,7 @@
         <v>393.57</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -9151,7 +9151,7 @@
         <v>19.87</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -9165,7 +9165,7 @@
         <v>19.57</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>61</v>
       </c>
@@ -9179,7 +9179,7 @@
         <v>19.86</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -9193,7 +9193,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -9218,7 +9218,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56220E0F-EC16-4A8C-9E04-C7F8849C4B4D}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
@@ -9226,7 +9226,7 @@
     <col min="5" max="5" width="30.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9243,7 +9243,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -9260,7 +9260,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -9277,7 +9277,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -9294,7 +9294,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -9311,7 +9311,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -9328,15 +9328,15 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="3">
-        <v>46143</v>
+        <v>46163</v>
       </c>
       <c r="C7" s="3">
-        <v>46146</v>
+        <v>46166</v>
       </c>
       <c r="D7" s="14">
         <v>4</v>
@@ -9345,18 +9345,19 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="3">
-        <v>46148</v>
+        <v>46143</v>
       </c>
       <c r="C8" s="3">
-        <v>46152</v>
+        <v>46147.999988425923</v>
       </c>
       <c r="D8" s="14">
-        <v>4</v>
+        <f>Indisp_Prog[[#This Row],[Fecha_Hora_Fin]]-Indisp_Prog[[#This Row],[Fecha_Hora_Inicio]]</f>
+        <v>4.9999884259232203</v>
       </c>
       <c r="E8" t="s">
         <v>68</v>
@@ -9373,14 +9374,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83DAFC4B-C207-418A-8501-0E1EC9E673B7}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9391,7 +9392,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -9402,7 +9403,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -9413,7 +9414,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -9424,7 +9425,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>61</v>
       </c>
@@ -9435,7 +9436,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -9446,7 +9447,7 @@
         <v>46631</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -9457,7 +9458,7 @@
         <v>48579</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -9468,7 +9469,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -9479,7 +9480,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -9490,7 +9491,7 @@
         <v>48579</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -9510,17 +9511,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9727,24 +9723,61 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
+    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="874" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5063DA84-1CAB-4443-AB90-BBB3A290DD81}"/>
+  <xr:revisionPtr revIDLastSave="877" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC190627-9207-417A-943E-57A4CEA4DA50}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -9336,10 +9336,10 @@
         <v>46163</v>
       </c>
       <c r="C7" s="3">
-        <v>46166</v>
+        <v>46166.999988425923</v>
       </c>
       <c r="D7" s="14">
-        <v>4</v>
+        <v>3.9999884259232203</v>
       </c>
       <c r="E7" t="s">
         <v>68</v>
@@ -9356,7 +9356,6 @@
         <v>46147.999988425923</v>
       </c>
       <c r="D8" s="14">
-        <f>Indisp_Prog[[#This Row],[Fecha_Hora_Fin]]-Indisp_Prog[[#This Row],[Fecha_Hora_Inicio]]</f>
         <v>4.9999884259232203</v>
       </c>
       <c r="E8" t="s">

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="877" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC190627-9207-417A-943E-57A4CEA4DA50}"/>
+  <xr:revisionPtr revIDLastSave="883" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F23C0ABD-ACA8-445F-A1E7-C065AFC5B1AE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="71">
   <si>
     <t>ID</t>
   </si>
@@ -310,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -349,6 +349,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -688,8 +691,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:I308" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:I308" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:I309" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:I309" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1087,7 +1090,7 @@
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -8960,7 +8963,30 @@
       </c>
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A309" s="1"/>
+      <c r="A309" s="1">
+        <v>298</v>
+      </c>
+      <c r="B309" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C309" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
+      </c>
+      <c r="D309" s="14">
+        <v>0</v>
+      </c>
+      <c r="E309" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F309" s="15">
+        <v>46141.029166666667</v>
+      </c>
+      <c r="G309" s="15">
+        <v>46141.057638888888</v>
+      </c>
+      <c r="H309" s="11"/>
+      <c r="I309" s="11"/>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" s="1"/>
@@ -9519,6 +9545,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100FB7AAE8C8816FD47B559A0CCF555AFF0" ma:contentTypeVersion="10" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5c9910934a78ddf693a6b708b52e9b37">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f95d585e-e7a7-414c-955d-38a47c8579bd" xmlns:ns3="33ab045e-9213-4eea-a9f2-a5b809105d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a9c61c95b4e11caed4e46447c2ca01e7" ns2:_="" ns3:_="">
     <xsd:import namespace="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
@@ -9721,20 +9761,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
   <ds:schemaRefs>
@@ -9744,6 +9770,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9762,23 +9805,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{0a9b9e15-83d2-4075-9282-a04e05c6580a}" enabled="1" method="Standard" siteId="{24139d14-c62c-4c47-8bdd-ce71ea1d50cf}" contentBits="0" removed="0"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="883" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F23C0ABD-ACA8-445F-A1E7-C065AFC5B1AE}"/>
+  <xr:revisionPtr revIDLastSave="885" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{081B4EA4-620D-4F63-8DD0-475534C0BC40}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <definedName name="SegmentaciónDeDatos_Sitio">#N/A</definedName>
     <definedName name="SegmentaciónDeDatos_Unidad">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="73">
   <si>
     <t>ID</t>
   </si>
@@ -267,6 +267,12 @@
   </si>
   <si>
     <t>FechaFinVigencia</t>
+  </si>
+  <si>
+    <t>Desenganche por protección sobre velocidad</t>
+  </si>
+  <si>
+    <t>Actua protección sobre velocidad por perturbaciones de señales en protección.</t>
   </si>
 </sst>
 </file>
@@ -8985,8 +8991,12 @@
       <c r="G309" s="15">
         <v>46141.057638888888</v>
       </c>
-      <c r="H309" s="11"/>
-      <c r="I309" s="11"/>
+      <c r="H309" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="I309" s="11" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" s="1"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="885" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{081B4EA4-620D-4F63-8DD0-475534C0BC40}"/>
+  <xr:revisionPtr revIDLastSave="895" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABEC2A29-750B-440E-993C-96736A648864}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="75">
   <si>
     <t>ID</t>
   </si>
@@ -273,6 +273,12 @@
   </si>
   <si>
     <t>Actua protección sobre velocidad por perturbaciones de señales en protección.</t>
+  </si>
+  <si>
+    <t>Falla arranque unidad</t>
+  </si>
+  <si>
+    <t>Filtros de succión bombas agua alimentación saturados.</t>
   </si>
 </sst>
 </file>
@@ -697,8 +703,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:I309" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:I309" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:I310" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:I310" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1096,7 +1102,7 @@
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -8975,7 +8981,7 @@
       <c r="B309" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C309" s="16" t="str">
+      <c r="C309" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
@@ -8999,7 +9005,32 @@
       </c>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A310" s="1"/>
+      <c r="A310" s="1">
+        <v>299</v>
+      </c>
+      <c r="B310" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C310" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
+      </c>
+      <c r="D310" s="14">
+        <v>0</v>
+      </c>
+      <c r="E310" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F310" s="15">
+        <v>46136.638194444444</v>
+      </c>
+      <c r="G310" s="15"/>
+      <c r="H310" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="I310" s="11" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" s="1"/>
@@ -9304,10 +9335,10 @@
         <v>46134</v>
       </c>
       <c r="C3" s="3">
-        <v>46139.999988425923</v>
+        <v>46141.638194444444</v>
       </c>
       <c r="D3" s="14">
-        <v>6.9999884259232203</v>
+        <v>7.6381944444437977</v>
       </c>
       <c r="E3" t="s">
         <v>65</v>
@@ -9546,15 +9577,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
@@ -9566,6 +9588,15 @@
     </SharedWithUsers>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9772,26 +9803,26 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="895" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABEC2A29-750B-440E-993C-96736A648864}"/>
+  <xr:revisionPtr revIDLastSave="901" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{911DA0BE-38E8-4E2C-B3ED-DFCCC6A4A00C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <definedName name="SegmentaciónDeDatos_Sitio">#N/A</definedName>
     <definedName name="SegmentaciónDeDatos_Unidad">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="78">
   <si>
     <t>ID</t>
   </si>
@@ -279,6 +279,15 @@
   </si>
   <si>
     <t>Filtros de succión bombas agua alimentación saturados.</t>
+  </si>
+  <si>
+    <t>Verificación</t>
+  </si>
+  <si>
+    <t>Cerrado</t>
+  </si>
+  <si>
+    <t>En proceso</t>
   </si>
 </sst>
 </file>
@@ -703,12 +712,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:I310" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:I310" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J310" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J310" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
-  <tableColumns count="9">
+  <tableColumns count="10">
     <tableColumn id="3" xr3:uid="{AFE823F6-980E-4E32-B4F4-6ECDE10F377D}" name="ID"/>
     <tableColumn id="1" xr3:uid="{CD000998-6E2C-4963-8605-37081D9C1A64}" name="Unidad" dataDxfId="10"/>
     <tableColumn id="7" xr3:uid="{542F6635-555D-4F04-8C27-263AF6E0C9F1}" name="Sitio" dataDxfId="9">
@@ -720,6 +729,7 @@
     <tableColumn id="8" xr3:uid="{713F74B7-95D9-4F96-AA1E-57E68B8A7FE7}" name="Fecha_Hora_Final" dataDxfId="5"/>
     <tableColumn id="11" xr3:uid="{20481209-2CB3-4DCC-A330-D866983AA4F9}" name="Motivo" dataDxfId="4"/>
     <tableColumn id="12" xr3:uid="{55FF6738-9798-4086-9AA1-DC8A3EF8081F}" name="Detalle" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{C2DE1A32-EBAC-4C95-A60E-FB6BAE643966}" name="Verificación"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1084,7 +1094,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
-  <dimension ref="A9:I331"/>
+  <dimension ref="A9:J331"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -1095,17 +1105,18 @@
     <col min="6" max="7" width="21.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="41.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="151.28515625" customWidth="1"/>
+    <col min="10" max="10" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.7109375" customWidth="1"/>
     <col min="12" max="12" width="33.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
         <v>300</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1133,8 +1144,11 @@
       <c r="I10" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J10" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -1160,7 +1174,7 @@
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -1186,7 +1200,7 @@
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>3</v>
       </c>
@@ -1212,7 +1226,7 @@
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>4</v>
       </c>
@@ -1238,7 +1252,7 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>5</v>
       </c>
@@ -1264,7 +1278,7 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>6</v>
       </c>
@@ -7946,7 +7960,7 @@
       <c r="H272" s="11"/>
       <c r="I272" s="11"/>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
         <v>263</v>
       </c>
@@ -7972,7 +7986,7 @@
       <c r="H273" s="11"/>
       <c r="I273" s="11"/>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
         <v>264</v>
       </c>
@@ -7998,7 +8012,7 @@
       <c r="H274" s="11"/>
       <c r="I274" s="11"/>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
         <v>265</v>
       </c>
@@ -8024,7 +8038,7 @@
       <c r="H275" s="11"/>
       <c r="I275" s="11"/>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
         <v>266</v>
       </c>
@@ -8050,7 +8064,7 @@
       <c r="H276" s="11"/>
       <c r="I276" s="11"/>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
         <v>267</v>
       </c>
@@ -8076,7 +8090,7 @@
       <c r="H277" s="11"/>
       <c r="I277" s="11"/>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
         <v>268</v>
       </c>
@@ -8102,7 +8116,7 @@
       <c r="H278" s="11"/>
       <c r="I278" s="11"/>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
         <v>269</v>
       </c>
@@ -8128,7 +8142,7 @@
       <c r="H279" s="11"/>
       <c r="I279" s="11"/>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
         <v>270</v>
       </c>
@@ -8154,7 +8168,7 @@
       <c r="H280" s="11"/>
       <c r="I280" s="11"/>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
         <v>271</v>
       </c>
@@ -8180,7 +8194,7 @@
       <c r="H281" s="11"/>
       <c r="I281" s="11"/>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
         <v>272</v>
       </c>
@@ -8206,7 +8220,7 @@
       <c r="H282" s="11"/>
       <c r="I282" s="11"/>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
         <v>273</v>
       </c>
@@ -8232,7 +8246,7 @@
       <c r="H283" s="11"/>
       <c r="I283" s="11"/>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
         <v>274</v>
       </c>
@@ -8258,7 +8272,7 @@
       <c r="H284" s="11"/>
       <c r="I284" s="11"/>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
         <v>275</v>
       </c>
@@ -8284,7 +8298,7 @@
       <c r="H285" s="11"/>
       <c r="I285" s="11"/>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
         <v>276</v>
       </c>
@@ -8313,8 +8327,11 @@
       <c r="I286" s="10" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J286" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
         <v>277</v>
       </c>
@@ -8343,8 +8360,11 @@
       <c r="I287" s="10" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J287" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
         <v>278</v>
       </c>
@@ -8373,8 +8393,11 @@
       <c r="I288" s="10" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J288" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
         <v>279</v>
       </c>
@@ -8403,8 +8426,11 @@
       <c r="I289" s="10" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J289" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
         <v>280</v>
       </c>
@@ -8433,8 +8459,11 @@
       <c r="I290" s="10" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J290" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
         <v>281</v>
       </c>
@@ -8463,8 +8492,11 @@
       <c r="I291" s="10" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J291" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
         <v>282</v>
       </c>
@@ -8493,8 +8525,11 @@
       <c r="I292" s="10" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J292" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
         <v>283</v>
       </c>
@@ -8523,8 +8558,11 @@
       <c r="I293" s="10" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J293" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
         <v>284</v>
       </c>
@@ -8553,8 +8591,11 @@
       <c r="I294" s="10" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J294" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
         <v>285</v>
       </c>
@@ -8583,8 +8624,11 @@
       <c r="I295" s="10" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J295" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
         <v>286</v>
       </c>
@@ -8613,8 +8657,11 @@
       <c r="I296" s="10" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J296" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
         <v>287</v>
       </c>
@@ -8643,8 +8690,11 @@
       <c r="I297" s="10" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J297" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
         <v>288</v>
       </c>
@@ -8673,8 +8723,11 @@
       <c r="I298" s="10" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J298" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
         <v>289</v>
       </c>
@@ -8703,8 +8756,11 @@
       <c r="I299" s="10" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J299" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
         <v>290</v>
       </c>
@@ -8733,8 +8789,11 @@
       <c r="I300" s="10" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J300" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
         <v>291</v>
       </c>
@@ -8763,8 +8822,11 @@
       <c r="I301" s="10" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J301" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
         <v>292</v>
       </c>
@@ -8793,8 +8855,11 @@
       <c r="I302" s="10" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="303" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J302" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="303" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
         <v>293</v>
       </c>
@@ -8823,8 +8888,11 @@
       <c r="I303" s="10" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="304" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J303" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="304" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
         <v>294</v>
       </c>
@@ -8853,8 +8921,11 @@
       <c r="I304" s="10" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J304" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
         <v>295</v>
       </c>
@@ -8883,8 +8954,11 @@
       <c r="I305" s="11" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J305" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
         <v>296</v>
       </c>
@@ -8913,8 +8987,11 @@
       <c r="I306" s="11" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J306" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
         <v>297</v>
       </c>
@@ -8943,8 +9020,11 @@
       <c r="I307" s="11" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J307" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
         <v>298</v>
       </c>
@@ -8973,8 +9053,11 @@
       <c r="I308" s="11" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J308" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
         <v>298</v>
       </c>
@@ -9003,8 +9086,11 @@
       <c r="I309" s="11" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J309" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
         <v>299</v>
       </c>
@@ -9031,35 +9117,38 @@
       <c r="I310" s="11" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J310" s="13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A311" s="1"/>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A312" s="1"/>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A313" s="1"/>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A314" s="1"/>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A315" s="1"/>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A316" s="1"/>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A317" s="1"/>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A318" s="1"/>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A319" s="1"/>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A320" s="1"/>
     </row>
     <row r="321" spans="1:1" x14ac:dyDescent="0.25">

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="901" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{911DA0BE-38E8-4E2C-B3ED-DFCCC6A4A00C}"/>
+  <xr:revisionPtr revIDLastSave="902" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C132D7BE-5D94-445A-B315-902F75BAC25B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -331,7 +331,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -370,9 +370,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -439,15 +436,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>461062</xdr:colOff>
+      <xdr:colOff>462967</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>947377</xdr:colOff>
+      <xdr:colOff>945472</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>148500</xdr:rowOff>
+      <xdr:rowOff>146595</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -525,7 +522,7 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>225435</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>148500</xdr:rowOff>
+      <xdr:rowOff>146595</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -601,9 +598,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>871230</xdr:colOff>
+      <xdr:colOff>869325</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>148500</xdr:rowOff>
+      <xdr:rowOff>146595</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -1095,28 +1092,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
   <dimension ref="A9:J331"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="41.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="151.28515625" customWidth="1"/>
-    <col min="10" max="10" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" customWidth="1"/>
-    <col min="12" max="12" width="33.28515625" customWidth="1"/>
+    <col min="6" max="7" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="151.33203125" customWidth="1"/>
+    <col min="10" max="10" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" customWidth="1"/>
+    <col min="12" max="12" width="33.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
         <v>300</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1148,7 +1145,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -1174,7 +1171,7 @@
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -1200,7 +1197,7 @@
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>3</v>
       </c>
@@ -1226,7 +1223,7 @@
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>4</v>
       </c>
@@ -1252,7 +1249,7 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>5</v>
       </c>
@@ -1278,7 +1275,7 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>6</v>
       </c>
@@ -1304,7 +1301,7 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>7</v>
       </c>
@@ -1330,7 +1327,7 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>8</v>
       </c>
@@ -1356,7 +1353,7 @@
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>9</v>
       </c>
@@ -1382,7 +1379,7 @@
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>10</v>
       </c>
@@ -1408,7 +1405,7 @@
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>11</v>
       </c>
@@ -1434,7 +1431,7 @@
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>12</v>
       </c>
@@ -1460,7 +1457,7 @@
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>13</v>
       </c>
@@ -1486,7 +1483,7 @@
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>14</v>
       </c>
@@ -1512,7 +1509,7 @@
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>15</v>
       </c>
@@ -1538,7 +1535,7 @@
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>16</v>
       </c>
@@ -1564,7 +1561,7 @@
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>17</v>
       </c>
@@ -1590,7 +1587,7 @@
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>18</v>
       </c>
@@ -1616,7 +1613,7 @@
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>19</v>
       </c>
@@ -1642,7 +1639,7 @@
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>20</v>
       </c>
@@ -1668,7 +1665,7 @@
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>21</v>
       </c>
@@ -1694,7 +1691,7 @@
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>22</v>
       </c>
@@ -1720,7 +1717,7 @@
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>23</v>
       </c>
@@ -1746,7 +1743,7 @@
       <c r="H33" s="11"/>
       <c r="I33" s="11"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>24</v>
       </c>
@@ -1772,7 +1769,7 @@
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>25</v>
       </c>
@@ -1798,7 +1795,7 @@
       <c r="H35" s="11"/>
       <c r="I35" s="11"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>26</v>
       </c>
@@ -1824,7 +1821,7 @@
       <c r="H36" s="11"/>
       <c r="I36" s="11"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>27</v>
       </c>
@@ -1850,7 +1847,7 @@
       <c r="H37" s="11"/>
       <c r="I37" s="11"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>28</v>
       </c>
@@ -1876,7 +1873,7 @@
       <c r="H38" s="11"/>
       <c r="I38" s="11"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>29</v>
       </c>
@@ -1902,7 +1899,7 @@
       <c r="H39" s="11"/>
       <c r="I39" s="11"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>30</v>
       </c>
@@ -1928,7 +1925,7 @@
       <c r="H40" s="11"/>
       <c r="I40" s="11"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>31</v>
       </c>
@@ -1954,7 +1951,7 @@
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>32</v>
       </c>
@@ -1980,7 +1977,7 @@
       <c r="H42" s="11"/>
       <c r="I42" s="11"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>33</v>
       </c>
@@ -2006,7 +2003,7 @@
       <c r="H43" s="11"/>
       <c r="I43" s="11"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>34</v>
       </c>
@@ -2032,7 +2029,7 @@
       <c r="H44" s="11"/>
       <c r="I44" s="11"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>35</v>
       </c>
@@ -2058,7 +2055,7 @@
       <c r="H45" s="11"/>
       <c r="I45" s="11"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>36</v>
       </c>
@@ -2084,7 +2081,7 @@
       <c r="H46" s="11"/>
       <c r="I46" s="11"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>37</v>
       </c>
@@ -2110,7 +2107,7 @@
       <c r="H47" s="11"/>
       <c r="I47" s="11"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>38</v>
       </c>
@@ -2136,7 +2133,7 @@
       <c r="H48" s="11"/>
       <c r="I48" s="11"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>39</v>
       </c>
@@ -2162,7 +2159,7 @@
       <c r="H49" s="11"/>
       <c r="I49" s="11"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>40</v>
       </c>
@@ -2188,7 +2185,7 @@
       <c r="H50" s="11"/>
       <c r="I50" s="11"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>41</v>
       </c>
@@ -2214,7 +2211,7 @@
       <c r="H51" s="11"/>
       <c r="I51" s="11"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>42</v>
       </c>
@@ -2240,7 +2237,7 @@
       <c r="H52" s="11"/>
       <c r="I52" s="11"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>43</v>
       </c>
@@ -2266,7 +2263,7 @@
       <c r="H53" s="11"/>
       <c r="I53" s="11"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>44</v>
       </c>
@@ -2292,7 +2289,7 @@
       <c r="H54" s="11"/>
       <c r="I54" s="11"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>45</v>
       </c>
@@ -2318,7 +2315,7 @@
       <c r="H55" s="11"/>
       <c r="I55" s="11"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>46</v>
       </c>
@@ -2344,7 +2341,7 @@
       <c r="H56" s="11"/>
       <c r="I56" s="11"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>47</v>
       </c>
@@ -2370,7 +2367,7 @@
       <c r="H57" s="11"/>
       <c r="I57" s="11"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>48</v>
       </c>
@@ -2396,7 +2393,7 @@
       <c r="H58" s="11"/>
       <c r="I58" s="11"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>49</v>
       </c>
@@ -2422,7 +2419,7 @@
       <c r="H59" s="11"/>
       <c r="I59" s="11"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>50</v>
       </c>
@@ -2448,7 +2445,7 @@
       <c r="H60" s="11"/>
       <c r="I60" s="11"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>51</v>
       </c>
@@ -2474,7 +2471,7 @@
       <c r="H61" s="11"/>
       <c r="I61" s="11"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>52</v>
       </c>
@@ -2500,7 +2497,7 @@
       <c r="H62" s="11"/>
       <c r="I62" s="11"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>53</v>
       </c>
@@ -2526,7 +2523,7 @@
       <c r="H63" s="11"/>
       <c r="I63" s="11"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>54</v>
       </c>
@@ -2552,7 +2549,7 @@
       <c r="H64" s="11"/>
       <c r="I64" s="11"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>55</v>
       </c>
@@ -2578,7 +2575,7 @@
       <c r="H65" s="11"/>
       <c r="I65" s="11"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>56</v>
       </c>
@@ -2604,7 +2601,7 @@
       <c r="H66" s="11"/>
       <c r="I66" s="11"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>57</v>
       </c>
@@ -2630,7 +2627,7 @@
       <c r="H67" s="11"/>
       <c r="I67" s="11"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>58</v>
       </c>
@@ -2656,7 +2653,7 @@
       <c r="H68" s="11"/>
       <c r="I68" s="11"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>59</v>
       </c>
@@ -2682,7 +2679,7 @@
       <c r="H69" s="11"/>
       <c r="I69" s="11"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>60</v>
       </c>
@@ -2708,7 +2705,7 @@
       <c r="H70" s="11"/>
       <c r="I70" s="11"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>61</v>
       </c>
@@ -2734,7 +2731,7 @@
       <c r="H71" s="11"/>
       <c r="I71" s="11"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>62</v>
       </c>
@@ -2760,7 +2757,7 @@
       <c r="H72" s="11"/>
       <c r="I72" s="11"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>63</v>
       </c>
@@ -2786,7 +2783,7 @@
       <c r="H73" s="11"/>
       <c r="I73" s="11"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>64</v>
       </c>
@@ -2812,7 +2809,7 @@
       <c r="H74" s="11"/>
       <c r="I74" s="11"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>65</v>
       </c>
@@ -2838,7 +2835,7 @@
       <c r="H75" s="11"/>
       <c r="I75" s="11"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>66</v>
       </c>
@@ -2864,7 +2861,7 @@
       <c r="H76" s="11"/>
       <c r="I76" s="11"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>67</v>
       </c>
@@ -2890,7 +2887,7 @@
       <c r="H77" s="11"/>
       <c r="I77" s="11"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>68</v>
       </c>
@@ -2916,7 +2913,7 @@
       <c r="H78" s="11"/>
       <c r="I78" s="11"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>69</v>
       </c>
@@ -2942,7 +2939,7 @@
       <c r="H79" s="11"/>
       <c r="I79" s="11"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>70</v>
       </c>
@@ -2968,7 +2965,7 @@
       <c r="H80" s="11"/>
       <c r="I80" s="11"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>71</v>
       </c>
@@ -2994,7 +2991,7 @@
       <c r="H81" s="11"/>
       <c r="I81" s="11"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>72</v>
       </c>
@@ -3020,7 +3017,7 @@
       <c r="H82" s="11"/>
       <c r="I82" s="11"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>73</v>
       </c>
@@ -3046,7 +3043,7 @@
       <c r="H83" s="11"/>
       <c r="I83" s="11"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>74</v>
       </c>
@@ -3072,7 +3069,7 @@
       <c r="H84" s="11"/>
       <c r="I84" s="11"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>75</v>
       </c>
@@ -3098,7 +3095,7 @@
       <c r="H85" s="11"/>
       <c r="I85" s="11"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>76</v>
       </c>
@@ -3124,7 +3121,7 @@
       <c r="H86" s="11"/>
       <c r="I86" s="11"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>77</v>
       </c>
@@ -3150,7 +3147,7 @@
       <c r="H87" s="11"/>
       <c r="I87" s="11"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>78</v>
       </c>
@@ -3176,7 +3173,7 @@
       <c r="H88" s="11"/>
       <c r="I88" s="11"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>79</v>
       </c>
@@ -3202,7 +3199,7 @@
       <c r="H89" s="11"/>
       <c r="I89" s="11"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>80</v>
       </c>
@@ -3228,7 +3225,7 @@
       <c r="H90" s="11"/>
       <c r="I90" s="11"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>81</v>
       </c>
@@ -3254,7 +3251,7 @@
       <c r="H91" s="11"/>
       <c r="I91" s="11"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>82</v>
       </c>
@@ -3280,7 +3277,7 @@
       <c r="H92" s="11"/>
       <c r="I92" s="11"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>83</v>
       </c>
@@ -3306,7 +3303,7 @@
       <c r="H93" s="11"/>
       <c r="I93" s="11"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>84</v>
       </c>
@@ -3332,7 +3329,7 @@
       <c r="H94" s="11"/>
       <c r="I94" s="11"/>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>85</v>
       </c>
@@ -3358,7 +3355,7 @@
       <c r="H95" s="11"/>
       <c r="I95" s="11"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>86</v>
       </c>
@@ -3384,7 +3381,7 @@
       <c r="H96" s="11"/>
       <c r="I96" s="11"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>87</v>
       </c>
@@ -3410,7 +3407,7 @@
       <c r="H97" s="11"/>
       <c r="I97" s="11"/>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>88</v>
       </c>
@@ -3436,7 +3433,7 @@
       <c r="H98" s="11"/>
       <c r="I98" s="11"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>89</v>
       </c>
@@ -3462,7 +3459,7 @@
       <c r="H99" s="11"/>
       <c r="I99" s="11"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>90</v>
       </c>
@@ -3488,7 +3485,7 @@
       <c r="H100" s="11"/>
       <c r="I100" s="11"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>91</v>
       </c>
@@ -3514,7 +3511,7 @@
       <c r="H101" s="11"/>
       <c r="I101" s="11"/>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>92</v>
       </c>
@@ -3540,7 +3537,7 @@
       <c r="H102" s="11"/>
       <c r="I102" s="11"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>93</v>
       </c>
@@ -3566,7 +3563,7 @@
       <c r="H103" s="11"/>
       <c r="I103" s="11"/>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>94</v>
       </c>
@@ -3592,7 +3589,7 @@
       <c r="H104" s="11"/>
       <c r="I104" s="11"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>95</v>
       </c>
@@ -3618,7 +3615,7 @@
       <c r="H105" s="11"/>
       <c r="I105" s="11"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>96</v>
       </c>
@@ -3644,7 +3641,7 @@
       <c r="H106" s="11"/>
       <c r="I106" s="11"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>97</v>
       </c>
@@ -3670,7 +3667,7 @@
       <c r="H107" s="11"/>
       <c r="I107" s="11"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>98</v>
       </c>
@@ -3696,7 +3693,7 @@
       <c r="H108" s="11"/>
       <c r="I108" s="11"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>99</v>
       </c>
@@ -3722,7 +3719,7 @@
       <c r="H109" s="11"/>
       <c r="I109" s="11"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>100</v>
       </c>
@@ -3748,7 +3745,7 @@
       <c r="H110" s="11"/>
       <c r="I110" s="11"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>101</v>
       </c>
@@ -3774,7 +3771,7 @@
       <c r="H111" s="11"/>
       <c r="I111" s="11"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>102</v>
       </c>
@@ -3800,7 +3797,7 @@
       <c r="H112" s="11"/>
       <c r="I112" s="11"/>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>103</v>
       </c>
@@ -3826,7 +3823,7 @@
       <c r="H113" s="11"/>
       <c r="I113" s="11"/>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>104</v>
       </c>
@@ -3852,7 +3849,7 @@
       <c r="H114" s="11"/>
       <c r="I114" s="11"/>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>105</v>
       </c>
@@ -3878,7 +3875,7 @@
       <c r="H115" s="11"/>
       <c r="I115" s="11"/>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>106</v>
       </c>
@@ -3904,7 +3901,7 @@
       <c r="H116" s="11"/>
       <c r="I116" s="11"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>107</v>
       </c>
@@ -3930,7 +3927,7 @@
       <c r="H117" s="11"/>
       <c r="I117" s="11"/>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>108</v>
       </c>
@@ -3956,7 +3953,7 @@
       <c r="H118" s="11"/>
       <c r="I118" s="11"/>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>109</v>
       </c>
@@ -3982,7 +3979,7 @@
       <c r="H119" s="11"/>
       <c r="I119" s="11"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>110</v>
       </c>
@@ -4008,7 +4005,7 @@
       <c r="H120" s="11"/>
       <c r="I120" s="11"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>111</v>
       </c>
@@ -4034,7 +4031,7 @@
       <c r="H121" s="11"/>
       <c r="I121" s="11"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>112</v>
       </c>
@@ -4060,7 +4057,7 @@
       <c r="H122" s="11"/>
       <c r="I122" s="11"/>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>113</v>
       </c>
@@ -4086,7 +4083,7 @@
       <c r="H123" s="11"/>
       <c r="I123" s="11"/>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>114</v>
       </c>
@@ -4112,7 +4109,7 @@
       <c r="H124" s="11"/>
       <c r="I124" s="11"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>115</v>
       </c>
@@ -4138,7 +4135,7 @@
       <c r="H125" s="11"/>
       <c r="I125" s="11"/>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>116</v>
       </c>
@@ -4164,7 +4161,7 @@
       <c r="H126" s="11"/>
       <c r="I126" s="11"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>117</v>
       </c>
@@ -4190,7 +4187,7 @@
       <c r="H127" s="11"/>
       <c r="I127" s="11"/>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>118</v>
       </c>
@@ -4216,7 +4213,7 @@
       <c r="H128" s="11"/>
       <c r="I128" s="11"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>119</v>
       </c>
@@ -4242,7 +4239,7 @@
       <c r="H129" s="11"/>
       <c r="I129" s="11"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>120</v>
       </c>
@@ -4268,7 +4265,7 @@
       <c r="H130" s="11"/>
       <c r="I130" s="11"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>121</v>
       </c>
@@ -4294,7 +4291,7 @@
       <c r="H131" s="11"/>
       <c r="I131" s="11"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>122</v>
       </c>
@@ -4320,7 +4317,7 @@
       <c r="H132" s="11"/>
       <c r="I132" s="11"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>123</v>
       </c>
@@ -4346,7 +4343,7 @@
       <c r="H133" s="11"/>
       <c r="I133" s="11"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>124</v>
       </c>
@@ -4372,7 +4369,7 @@
       <c r="H134" s="11"/>
       <c r="I134" s="11"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>125</v>
       </c>
@@ -4398,7 +4395,7 @@
       <c r="H135" s="11"/>
       <c r="I135" s="11"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>126</v>
       </c>
@@ -4424,7 +4421,7 @@
       <c r="H136" s="11"/>
       <c r="I136" s="11"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>127</v>
       </c>
@@ -4450,7 +4447,7 @@
       <c r="H137" s="11"/>
       <c r="I137" s="11"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>128</v>
       </c>
@@ -4476,7 +4473,7 @@
       <c r="H138" s="11"/>
       <c r="I138" s="11"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>129</v>
       </c>
@@ -4502,7 +4499,7 @@
       <c r="H139" s="11"/>
       <c r="I139" s="11"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>130</v>
       </c>
@@ -4528,7 +4525,7 @@
       <c r="H140" s="11"/>
       <c r="I140" s="11"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>131</v>
       </c>
@@ -4554,7 +4551,7 @@
       <c r="H141" s="11"/>
       <c r="I141" s="11"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>132</v>
       </c>
@@ -4580,7 +4577,7 @@
       <c r="H142" s="11"/>
       <c r="I142" s="11"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>133</v>
       </c>
@@ -4606,7 +4603,7 @@
       <c r="H143" s="11"/>
       <c r="I143" s="11"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>134</v>
       </c>
@@ -4632,7 +4629,7 @@
       <c r="H144" s="11"/>
       <c r="I144" s="11"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>135</v>
       </c>
@@ -4658,7 +4655,7 @@
       <c r="H145" s="11"/>
       <c r="I145" s="11"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>136</v>
       </c>
@@ -4684,7 +4681,7 @@
       <c r="H146" s="11"/>
       <c r="I146" s="11"/>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>137</v>
       </c>
@@ -4710,7 +4707,7 @@
       <c r="H147" s="11"/>
       <c r="I147" s="11"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>138</v>
       </c>
@@ -4736,7 +4733,7 @@
       <c r="H148" s="11"/>
       <c r="I148" s="11"/>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>139</v>
       </c>
@@ -4762,7 +4759,7 @@
       <c r="H149" s="11"/>
       <c r="I149" s="11"/>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>140</v>
       </c>
@@ -4788,7 +4785,7 @@
       <c r="H150" s="11"/>
       <c r="I150" s="11"/>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>141</v>
       </c>
@@ -4814,7 +4811,7 @@
       <c r="H151" s="11"/>
       <c r="I151" s="11"/>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>142</v>
       </c>
@@ -4840,7 +4837,7 @@
       <c r="H152" s="11"/>
       <c r="I152" s="11"/>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>143</v>
       </c>
@@ -4866,7 +4863,7 @@
       <c r="H153" s="11"/>
       <c r="I153" s="11"/>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>144</v>
       </c>
@@ -4892,7 +4889,7 @@
       <c r="H154" s="11"/>
       <c r="I154" s="11"/>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>145</v>
       </c>
@@ -4918,7 +4915,7 @@
       <c r="H155" s="11"/>
       <c r="I155" s="11"/>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>146</v>
       </c>
@@ -4944,7 +4941,7 @@
       <c r="H156" s="11"/>
       <c r="I156" s="11"/>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>147</v>
       </c>
@@ -4970,7 +4967,7 @@
       <c r="H157" s="11"/>
       <c r="I157" s="11"/>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>148</v>
       </c>
@@ -4996,7 +4993,7 @@
       <c r="H158" s="11"/>
       <c r="I158" s="11"/>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>149</v>
       </c>
@@ -5022,7 +5019,7 @@
       <c r="H159" s="11"/>
       <c r="I159" s="11"/>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>150</v>
       </c>
@@ -5048,7 +5045,7 @@
       <c r="H160" s="11"/>
       <c r="I160" s="11"/>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>151</v>
       </c>
@@ -5074,7 +5071,7 @@
       <c r="H161" s="11"/>
       <c r="I161" s="11"/>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>152</v>
       </c>
@@ -5100,7 +5097,7 @@
       <c r="H162" s="11"/>
       <c r="I162" s="11"/>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>153</v>
       </c>
@@ -5126,7 +5123,7 @@
       <c r="H163" s="11"/>
       <c r="I163" s="11"/>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>154</v>
       </c>
@@ -5152,7 +5149,7 @@
       <c r="H164" s="11"/>
       <c r="I164" s="11"/>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>155</v>
       </c>
@@ -5178,7 +5175,7 @@
       <c r="H165" s="11"/>
       <c r="I165" s="11"/>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>156</v>
       </c>
@@ -5204,7 +5201,7 @@
       <c r="H166" s="11"/>
       <c r="I166" s="11"/>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>157</v>
       </c>
@@ -5230,7 +5227,7 @@
       <c r="H167" s="11"/>
       <c r="I167" s="11"/>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>158</v>
       </c>
@@ -5256,7 +5253,7 @@
       <c r="H168" s="11"/>
       <c r="I168" s="11"/>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>159</v>
       </c>
@@ -5282,7 +5279,7 @@
       <c r="H169" s="11"/>
       <c r="I169" s="11"/>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>160</v>
       </c>
@@ -5308,7 +5305,7 @@
       <c r="H170" s="11"/>
       <c r="I170" s="11"/>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>161</v>
       </c>
@@ -5334,7 +5331,7 @@
       <c r="H171" s="11"/>
       <c r="I171" s="11"/>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>162</v>
       </c>
@@ -5360,7 +5357,7 @@
       <c r="H172" s="11"/>
       <c r="I172" s="11"/>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>163</v>
       </c>
@@ -5386,7 +5383,7 @@
       <c r="H173" s="11"/>
       <c r="I173" s="11"/>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>164</v>
       </c>
@@ -5412,7 +5409,7 @@
       <c r="H174" s="11"/>
       <c r="I174" s="11"/>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>165</v>
       </c>
@@ -5438,7 +5435,7 @@
       <c r="H175" s="11"/>
       <c r="I175" s="11"/>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>166</v>
       </c>
@@ -5464,7 +5461,7 @@
       <c r="H176" s="11"/>
       <c r="I176" s="11"/>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>167</v>
       </c>
@@ -5490,7 +5487,7 @@
       <c r="H177" s="11"/>
       <c r="I177" s="11"/>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>168</v>
       </c>
@@ -5516,7 +5513,7 @@
       <c r="H178" s="11"/>
       <c r="I178" s="11"/>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>169</v>
       </c>
@@ -5542,7 +5539,7 @@
       <c r="H179" s="11"/>
       <c r="I179" s="11"/>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>170</v>
       </c>
@@ -5568,7 +5565,7 @@
       <c r="H180" s="11"/>
       <c r="I180" s="11"/>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>171</v>
       </c>
@@ -5594,7 +5591,7 @@
       <c r="H181" s="11"/>
       <c r="I181" s="11"/>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>172</v>
       </c>
@@ -5620,7 +5617,7 @@
       <c r="H182" s="11"/>
       <c r="I182" s="11"/>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>173</v>
       </c>
@@ -5646,7 +5643,7 @@
       <c r="H183" s="11"/>
       <c r="I183" s="11"/>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>174</v>
       </c>
@@ -5672,7 +5669,7 @@
       <c r="H184" s="11"/>
       <c r="I184" s="11"/>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>175</v>
       </c>
@@ -5698,7 +5695,7 @@
       <c r="H185" s="11"/>
       <c r="I185" s="11"/>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>176</v>
       </c>
@@ -5724,7 +5721,7 @@
       <c r="H186" s="11"/>
       <c r="I186" s="11"/>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>177</v>
       </c>
@@ -5750,7 +5747,7 @@
       <c r="H187" s="11"/>
       <c r="I187" s="11"/>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>178</v>
       </c>
@@ -5776,7 +5773,7 @@
       <c r="H188" s="11"/>
       <c r="I188" s="11"/>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>179</v>
       </c>
@@ -5802,7 +5799,7 @@
       <c r="H189" s="11"/>
       <c r="I189" s="11"/>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>180</v>
       </c>
@@ -5828,7 +5825,7 @@
       <c r="H190" s="11"/>
       <c r="I190" s="11"/>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>181</v>
       </c>
@@ -5854,7 +5851,7 @@
       <c r="H191" s="11"/>
       <c r="I191" s="11"/>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>182</v>
       </c>
@@ -5880,7 +5877,7 @@
       <c r="H192" s="11"/>
       <c r="I192" s="11"/>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>183</v>
       </c>
@@ -5906,7 +5903,7 @@
       <c r="H193" s="11"/>
       <c r="I193" s="11"/>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>184</v>
       </c>
@@ -5932,7 +5929,7 @@
       <c r="H194" s="11"/>
       <c r="I194" s="11"/>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>185</v>
       </c>
@@ -5958,7 +5955,7 @@
       <c r="H195" s="11"/>
       <c r="I195" s="11"/>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>186</v>
       </c>
@@ -5984,7 +5981,7 @@
       <c r="H196" s="11"/>
       <c r="I196" s="11"/>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>187</v>
       </c>
@@ -6010,7 +6007,7 @@
       <c r="H197" s="11"/>
       <c r="I197" s="11"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>188</v>
       </c>
@@ -6036,7 +6033,7 @@
       <c r="H198" s="11"/>
       <c r="I198" s="11"/>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>189</v>
       </c>
@@ -6062,7 +6059,7 @@
       <c r="H199" s="11"/>
       <c r="I199" s="11"/>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>190</v>
       </c>
@@ -6088,7 +6085,7 @@
       <c r="H200" s="11"/>
       <c r="I200" s="11"/>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>191</v>
       </c>
@@ -6114,7 +6111,7 @@
       <c r="H201" s="11"/>
       <c r="I201" s="11"/>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>192</v>
       </c>
@@ -6140,7 +6137,7 @@
       <c r="H202" s="11"/>
       <c r="I202" s="11"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>193</v>
       </c>
@@ -6166,7 +6163,7 @@
       <c r="H203" s="11"/>
       <c r="I203" s="11"/>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>194</v>
       </c>
@@ -6192,7 +6189,7 @@
       <c r="H204" s="11"/>
       <c r="I204" s="11"/>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>195</v>
       </c>
@@ -6218,7 +6215,7 @@
       <c r="H205" s="11"/>
       <c r="I205" s="11"/>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>196</v>
       </c>
@@ -6244,7 +6241,7 @@
       <c r="H206" s="11"/>
       <c r="I206" s="11"/>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>197</v>
       </c>
@@ -6270,7 +6267,7 @@
       <c r="H207" s="11"/>
       <c r="I207" s="11"/>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>198</v>
       </c>
@@ -6296,7 +6293,7 @@
       <c r="H208" s="11"/>
       <c r="I208" s="11"/>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>199</v>
       </c>
@@ -6322,7 +6319,7 @@
       <c r="H209" s="11"/>
       <c r="I209" s="11"/>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>200</v>
       </c>
@@ -6348,7 +6345,7 @@
       <c r="H210" s="11"/>
       <c r="I210" s="11"/>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>201</v>
       </c>
@@ -6374,7 +6371,7 @@
       <c r="H211" s="11"/>
       <c r="I211" s="11"/>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>202</v>
       </c>
@@ -6400,7 +6397,7 @@
       <c r="H212" s="11"/>
       <c r="I212" s="11"/>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>203</v>
       </c>
@@ -6426,7 +6423,7 @@
       <c r="H213" s="11"/>
       <c r="I213" s="11"/>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>204</v>
       </c>
@@ -6452,7 +6449,7 @@
       <c r="H214" s="11"/>
       <c r="I214" s="11"/>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>205</v>
       </c>
@@ -6478,7 +6475,7 @@
       <c r="H215" s="11"/>
       <c r="I215" s="11"/>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>206</v>
       </c>
@@ -6504,7 +6501,7 @@
       <c r="H216" s="11"/>
       <c r="I216" s="11"/>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>207</v>
       </c>
@@ -6530,7 +6527,7 @@
       <c r="H217" s="11"/>
       <c r="I217" s="11"/>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>208</v>
       </c>
@@ -6556,7 +6553,7 @@
       <c r="H218" s="11"/>
       <c r="I218" s="11"/>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>209</v>
       </c>
@@ -6582,7 +6579,7 @@
       <c r="H219" s="11"/>
       <c r="I219" s="11"/>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>210</v>
       </c>
@@ -6608,7 +6605,7 @@
       <c r="H220" s="11"/>
       <c r="I220" s="11"/>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>211</v>
       </c>
@@ -6634,7 +6631,7 @@
       <c r="H221" s="11"/>
       <c r="I221" s="11"/>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>212</v>
       </c>
@@ -6660,7 +6657,7 @@
       <c r="H222" s="11"/>
       <c r="I222" s="11"/>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>213</v>
       </c>
@@ -6686,7 +6683,7 @@
       <c r="H223" s="11"/>
       <c r="I223" s="11"/>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>214</v>
       </c>
@@ -6712,7 +6709,7 @@
       <c r="H224" s="11"/>
       <c r="I224" s="11"/>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>215</v>
       </c>
@@ -6738,7 +6735,7 @@
       <c r="H225" s="11"/>
       <c r="I225" s="11"/>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>216</v>
       </c>
@@ -6764,7 +6761,7 @@
       <c r="H226" s="11"/>
       <c r="I226" s="11"/>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>217</v>
       </c>
@@ -6790,7 +6787,7 @@
       <c r="H227" s="11"/>
       <c r="I227" s="11"/>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>218</v>
       </c>
@@ -6816,7 +6813,7 @@
       <c r="H228" s="11"/>
       <c r="I228" s="11"/>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
         <v>219</v>
       </c>
@@ -6842,7 +6839,7 @@
       <c r="H229" s="11"/>
       <c r="I229" s="11"/>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>220</v>
       </c>
@@ -6868,7 +6865,7 @@
       <c r="H230" s="11"/>
       <c r="I230" s="11"/>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>221</v>
       </c>
@@ -6894,7 +6891,7 @@
       <c r="H231" s="11"/>
       <c r="I231" s="11"/>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>222</v>
       </c>
@@ -6920,7 +6917,7 @@
       <c r="H232" s="11"/>
       <c r="I232" s="11"/>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>223</v>
       </c>
@@ -6946,7 +6943,7 @@
       <c r="H233" s="11"/>
       <c r="I233" s="11"/>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>224</v>
       </c>
@@ -6972,7 +6969,7 @@
       <c r="H234" s="11"/>
       <c r="I234" s="11"/>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>225</v>
       </c>
@@ -6998,7 +6995,7 @@
       <c r="H235" s="11"/>
       <c r="I235" s="11"/>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>226</v>
       </c>
@@ -7024,7 +7021,7 @@
       <c r="H236" s="11"/>
       <c r="I236" s="11"/>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>227</v>
       </c>
@@ -7050,7 +7047,7 @@
       <c r="H237" s="11"/>
       <c r="I237" s="11"/>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>228</v>
       </c>
@@ -7076,7 +7073,7 @@
       <c r="H238" s="11"/>
       <c r="I238" s="11"/>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>229</v>
       </c>
@@ -7102,7 +7099,7 @@
       <c r="H239" s="11"/>
       <c r="I239" s="11"/>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>230</v>
       </c>
@@ -7128,7 +7125,7 @@
       <c r="H240" s="11"/>
       <c r="I240" s="11"/>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>231</v>
       </c>
@@ -7154,7 +7151,7 @@
       <c r="H241" s="11"/>
       <c r="I241" s="11"/>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
         <v>232</v>
       </c>
@@ -7180,7 +7177,7 @@
       <c r="H242" s="11"/>
       <c r="I242" s="11"/>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" s="1">
         <v>233</v>
       </c>
@@ -7206,7 +7203,7 @@
       <c r="H243" s="11"/>
       <c r="I243" s="11"/>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" s="1">
         <v>234</v>
       </c>
@@ -7232,7 +7229,7 @@
       <c r="H244" s="11"/>
       <c r="I244" s="11"/>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
         <v>235</v>
       </c>
@@ -7258,7 +7255,7 @@
       <c r="H245" s="11"/>
       <c r="I245" s="11"/>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
         <v>236</v>
       </c>
@@ -7284,7 +7281,7 @@
       <c r="H246" s="11"/>
       <c r="I246" s="11"/>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
         <v>237</v>
       </c>
@@ -7310,7 +7307,7 @@
       <c r="H247" s="11"/>
       <c r="I247" s="11"/>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
         <v>238</v>
       </c>
@@ -7336,7 +7333,7 @@
       <c r="H248" s="11"/>
       <c r="I248" s="11"/>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
         <v>239</v>
       </c>
@@ -7362,7 +7359,7 @@
       <c r="H249" s="11"/>
       <c r="I249" s="11"/>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
         <v>240</v>
       </c>
@@ -7388,7 +7385,7 @@
       <c r="H250" s="11"/>
       <c r="I250" s="11"/>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" s="1">
         <v>241</v>
       </c>
@@ -7414,7 +7411,7 @@
       <c r="H251" s="11"/>
       <c r="I251" s="11"/>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>242</v>
       </c>
@@ -7440,7 +7437,7 @@
       <c r="H252" s="11"/>
       <c r="I252" s="11"/>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>243</v>
       </c>
@@ -7466,7 +7463,7 @@
       <c r="H253" s="11"/>
       <c r="I253" s="11"/>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>244</v>
       </c>
@@ -7492,7 +7489,7 @@
       <c r="H254" s="11"/>
       <c r="I254" s="11"/>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>245</v>
       </c>
@@ -7518,7 +7515,7 @@
       <c r="H255" s="11"/>
       <c r="I255" s="11"/>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>246</v>
       </c>
@@ -7544,7 +7541,7 @@
       <c r="H256" s="11"/>
       <c r="I256" s="11"/>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>247</v>
       </c>
@@ -7570,7 +7567,7 @@
       <c r="H257" s="11"/>
       <c r="I257" s="11"/>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>248</v>
       </c>
@@ -7596,7 +7593,7 @@
       <c r="H258" s="11"/>
       <c r="I258" s="11"/>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>249</v>
       </c>
@@ -7622,7 +7619,7 @@
       <c r="H259" s="11"/>
       <c r="I259" s="11"/>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>250</v>
       </c>
@@ -7648,7 +7645,7 @@
       <c r="H260" s="11"/>
       <c r="I260" s="11"/>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>251</v>
       </c>
@@ -7674,7 +7671,7 @@
       <c r="H261" s="11"/>
       <c r="I261" s="11"/>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>252</v>
       </c>
@@ -7700,7 +7697,7 @@
       <c r="H262" s="11"/>
       <c r="I262" s="11"/>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>253</v>
       </c>
@@ -7726,7 +7723,7 @@
       <c r="H263" s="11"/>
       <c r="I263" s="11"/>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
         <v>254</v>
       </c>
@@ -7752,7 +7749,7 @@
       <c r="H264" s="11"/>
       <c r="I264" s="11"/>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
         <v>255</v>
       </c>
@@ -7778,7 +7775,7 @@
       <c r="H265" s="11"/>
       <c r="I265" s="11"/>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266" s="1">
         <v>256</v>
       </c>
@@ -7804,7 +7801,7 @@
       <c r="H266" s="11"/>
       <c r="I266" s="11"/>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A267" s="1">
         <v>257</v>
       </c>
@@ -7830,7 +7827,7 @@
       <c r="H267" s="11"/>
       <c r="I267" s="11"/>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268" s="1">
         <v>258</v>
       </c>
@@ -7856,7 +7853,7 @@
       <c r="H268" s="11"/>
       <c r="I268" s="11"/>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
         <v>259</v>
       </c>
@@ -7882,7 +7879,7 @@
       <c r="H269" s="11"/>
       <c r="I269" s="11"/>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
         <v>260</v>
       </c>
@@ -7908,7 +7905,7 @@
       <c r="H270" s="11"/>
       <c r="I270" s="11"/>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
         <v>261</v>
       </c>
@@ -7934,7 +7931,7 @@
       <c r="H271" s="11"/>
       <c r="I271" s="11"/>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
         <v>262</v>
       </c>
@@ -7960,7 +7957,7 @@
       <c r="H272" s="11"/>
       <c r="I272" s="11"/>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A273" s="1">
         <v>263</v>
       </c>
@@ -7986,7 +7983,7 @@
       <c r="H273" s="11"/>
       <c r="I273" s="11"/>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" s="1">
         <v>264</v>
       </c>
@@ -8012,7 +8009,7 @@
       <c r="H274" s="11"/>
       <c r="I274" s="11"/>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" s="1">
         <v>265</v>
       </c>
@@ -8038,7 +8035,7 @@
       <c r="H275" s="11"/>
       <c r="I275" s="11"/>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" s="1">
         <v>266</v>
       </c>
@@ -8064,7 +8061,7 @@
       <c r="H276" s="11"/>
       <c r="I276" s="11"/>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" s="1">
         <v>267</v>
       </c>
@@ -8090,7 +8087,7 @@
       <c r="H277" s="11"/>
       <c r="I277" s="11"/>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" s="1">
         <v>268</v>
       </c>
@@ -8116,7 +8113,7 @@
       <c r="H278" s="11"/>
       <c r="I278" s="11"/>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
         <v>269</v>
       </c>
@@ -8142,7 +8139,7 @@
       <c r="H279" s="11"/>
       <c r="I279" s="11"/>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" s="1">
         <v>270</v>
       </c>
@@ -8168,7 +8165,7 @@
       <c r="H280" s="11"/>
       <c r="I280" s="11"/>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" s="1">
         <v>271</v>
       </c>
@@ -8194,7 +8191,7 @@
       <c r="H281" s="11"/>
       <c r="I281" s="11"/>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A282" s="1">
         <v>272</v>
       </c>
@@ -8220,7 +8217,7 @@
       <c r="H282" s="11"/>
       <c r="I282" s="11"/>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A283" s="1">
         <v>273</v>
       </c>
@@ -8246,7 +8243,7 @@
       <c r="H283" s="11"/>
       <c r="I283" s="11"/>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284" s="1">
         <v>274</v>
       </c>
@@ -8272,7 +8269,7 @@
       <c r="H284" s="11"/>
       <c r="I284" s="11"/>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" s="1">
         <v>275</v>
       </c>
@@ -8298,7 +8295,7 @@
       <c r="H285" s="11"/>
       <c r="I285" s="11"/>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" s="1">
         <v>276</v>
       </c>
@@ -8331,7 +8328,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
         <v>277</v>
       </c>
@@ -8364,7 +8361,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
         <v>278</v>
       </c>
@@ -8397,7 +8394,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" s="1">
         <v>279</v>
       </c>
@@ -8430,7 +8427,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" s="1">
         <v>280</v>
       </c>
@@ -8463,7 +8460,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A291" s="1">
         <v>281</v>
       </c>
@@ -8496,7 +8493,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A292" s="1">
         <v>282</v>
       </c>
@@ -8529,7 +8526,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A293" s="1">
         <v>283</v>
       </c>
@@ -8562,7 +8559,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>284</v>
       </c>
@@ -8595,7 +8592,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>285</v>
       </c>
@@ -8628,7 +8625,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>286</v>
       </c>
@@ -8661,7 +8658,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>287</v>
       </c>
@@ -8694,7 +8691,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>288</v>
       </c>
@@ -8727,7 +8724,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>289</v>
       </c>
@@ -8760,7 +8757,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>290</v>
       </c>
@@ -8793,7 +8790,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>291</v>
       </c>
@@ -8826,7 +8823,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>292</v>
       </c>
@@ -8859,7 +8856,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="303" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>293</v>
       </c>
@@ -8892,7 +8889,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="304" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>294</v>
       </c>
@@ -8925,7 +8922,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>295</v>
       </c>
@@ -8958,7 +8955,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>296</v>
       </c>
@@ -8991,7 +8988,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>297</v>
       </c>
@@ -9024,7 +9021,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>298</v>
       </c>
@@ -9057,7 +9054,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>298</v>
       </c>
@@ -9090,14 +9087,14 @@
         <v>76</v>
       </c>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A310" s="1">
         <v>299</v>
       </c>
       <c r="B310" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C310" s="16" t="str">
+      <c r="C310" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
@@ -9110,7 +9107,9 @@
       <c r="F310" s="15">
         <v>46136.638194444444</v>
       </c>
-      <c r="G310" s="15"/>
+      <c r="G310" s="15">
+        <v>46143.779166666667</v>
+      </c>
       <c r="H310" s="11" t="s">
         <v>73</v>
       </c>
@@ -9121,67 +9120,67 @@
         <v>77</v>
       </c>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A311" s="1"/>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A312" s="1"/>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A313" s="1"/>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A314" s="1"/>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A315" s="1"/>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A316" s="1"/>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A317" s="1"/>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A318" s="1"/>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A319" s="1"/>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A320" s="1"/>
     </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A321" s="1"/>
     </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A322" s="1"/>
     </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A323" s="1"/>
     </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A324" s="1"/>
     </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A325" s="1"/>
     </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A326" s="1"/>
     </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A327" s="1"/>
     </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A328" s="1"/>
     </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A329" s="1"/>
     </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A330" s="1"/>
     </row>
-    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A331" s="1"/>
     </row>
   </sheetData>
@@ -9203,13 +9202,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{797F1036-D41E-43A4-9E6E-CBBB62F3CD31}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="13.28515625" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9223,7 +9222,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -9237,7 +9236,7 @@
         <v>234.67</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -9251,7 +9250,7 @@
         <v>161.15</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -9265,7 +9264,7 @@
         <v>157.61000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -9279,7 +9278,7 @@
         <v>347.95</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -9293,7 +9292,7 @@
         <v>393.57</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -9307,7 +9306,7 @@
         <v>19.87</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -9321,7 +9320,7 @@
         <v>19.57</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>61</v>
       </c>
@@ -9335,7 +9334,7 @@
         <v>19.86</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -9349,7 +9348,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -9374,15 +9373,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56220E0F-EC16-4A8C-9E04-C7F8849C4B4D}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9399,7 +9398,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -9416,7 +9415,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -9433,7 +9432,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -9450,7 +9449,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -9467,7 +9466,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -9484,7 +9483,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -9501,7 +9500,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -9529,14 +9528,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83DAFC4B-C207-418A-8501-0E1EC9E673B7}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9547,7 +9546,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -9558,7 +9557,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -9569,7 +9568,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -9580,7 +9579,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>61</v>
       </c>
@@ -9591,7 +9590,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -9602,7 +9601,7 @@
         <v>46631</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -9613,7 +9612,7 @@
         <v>48579</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -9624,7 +9623,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -9635,7 +9634,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -9646,7 +9645,7 @@
         <v>48579</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -9666,29 +9665,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100FB7AAE8C8816FD47B559A0CCF555AFF0" ma:contentTypeVersion="10" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5c9910934a78ddf693a6b708b52e9b37">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f95d585e-e7a7-414c-955d-38a47c8579bd" xmlns:ns3="33ab045e-9213-4eea-a9f2-a5b809105d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a9c61c95b4e11caed4e46447c2ca01e7" ns2:_="" ns3:_="">
     <xsd:import namespace="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
@@ -9891,32 +9867,30 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9935,6 +9909,31 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{0a9b9e15-83d2-4075-9282-a04e05c6580a}" enabled="1" method="Standard" siteId="{24139d14-c62c-4c47-8bdd-ce71ea1d50cf}" contentBits="0" removed="0"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="902" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C132D7BE-5D94-445A-B315-902F75BAC25B}"/>
+  <xr:revisionPtr revIDLastSave="911" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E0FA8CC-6E0F-4FE5-9C84-0026AB4F6A45}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <definedName name="SegmentaciónDeDatos_Sitio">#N/A</definedName>
     <definedName name="SegmentaciónDeDatos_Unidad">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="80">
   <si>
     <t>ID</t>
   </si>
@@ -289,6 +289,12 @@
   <si>
     <t>En proceso</t>
   </si>
+  <si>
+    <t>Inspección VTI2</t>
+  </si>
+  <si>
+    <t>Se realiza inspección componentea, alinamiento, GAP en VTI2</t>
+  </si>
 </sst>
 </file>
 
@@ -331,7 +337,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -370,6 +376,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -436,15 +445,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>462967</xdr:colOff>
+      <xdr:colOff>476302</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>945472</xdr:colOff>
+      <xdr:colOff>932137</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>146595</xdr:rowOff>
+      <xdr:rowOff>133260</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -522,7 +531,7 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>225435</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>146595</xdr:rowOff>
+      <xdr:rowOff>133260</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -598,9 +607,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>869325</xdr:colOff>
+      <xdr:colOff>855990</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>146595</xdr:rowOff>
+      <xdr:rowOff>133260</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -709,8 +718,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J310" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J310" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J311" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J311" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1110,7 +1119,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -9105,7 +9114,7 @@
         <v>12</v>
       </c>
       <c r="F310" s="15">
-        <v>46136.638194444444</v>
+        <v>46141.638194444444</v>
       </c>
       <c r="G310" s="15">
         <v>46143.779166666667</v>
@@ -9121,7 +9130,34 @@
       </c>
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A311" s="1"/>
+      <c r="A311" s="1">
+        <v>300</v>
+      </c>
+      <c r="B311" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C311" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CEM</v>
+      </c>
+      <c r="D311" s="14">
+        <v>80</v>
+      </c>
+      <c r="E311" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F311" s="15">
+        <v>46144.731249999997</v>
+      </c>
+      <c r="G311" s="15">
+        <v>46144.795138888891</v>
+      </c>
+      <c r="H311" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="I311" s="11" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A312" s="1"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="911" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E0FA8CC-6E0F-4FE5-9C84-0026AB4F6A45}"/>
+  <xr:revisionPtr revIDLastSave="912" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA25E40C-FDB9-4451-B12E-FBA30199B4F9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="SegmentaciónDeDatos_Sitio">#N/A</definedName>
     <definedName name="SegmentaciónDeDatos_Unidad">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
@@ -9541,7 +9541,7 @@
         <v>18</v>
       </c>
       <c r="B8" s="3">
-        <v>46143</v>
+        <v>46144.101388888892</v>
       </c>
       <c r="C8" s="3">
         <v>46147.999988425923</v>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="912" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA25E40C-FDB9-4451-B12E-FBA30199B4F9}"/>
+  <xr:revisionPtr revIDLastSave="918" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B96BBCC0-B866-482A-A828-D7F0447C094F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="79">
   <si>
     <t>ID</t>
   </si>
@@ -287,9 +287,6 @@
     <t>Cerrado</t>
   </si>
   <si>
-    <t>En proceso</t>
-  </si>
-  <si>
     <t>Inspección VTI2</t>
   </si>
   <si>
@@ -445,15 +442,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>476302</xdr:colOff>
+      <xdr:colOff>472492</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>932137</xdr:colOff>
+      <xdr:colOff>935947</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>133260</xdr:rowOff>
+      <xdr:rowOff>137070</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -531,7 +528,7 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>225435</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>133260</xdr:rowOff>
+      <xdr:rowOff>137070</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -607,9 +604,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>855990</xdr:colOff>
+      <xdr:colOff>859800</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>133260</xdr:rowOff>
+      <xdr:rowOff>137070</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -9126,7 +9123,7 @@
         <v>74</v>
       </c>
       <c r="J310" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.3">
@@ -9153,10 +9150,13 @@
         <v>46144.795138888891</v>
       </c>
       <c r="H311" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="I311" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="I311" s="11" t="s">
-        <v>79</v>
+      <c r="J311" s="13" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.3">
@@ -9544,10 +9544,10 @@
         <v>46144.101388888892</v>
       </c>
       <c r="C8" s="3">
-        <v>46147.999988425923</v>
+        <v>46148.999988425923</v>
       </c>
       <c r="D8" s="14">
-        <v>4.9999884259232203</v>
+        <v>5</v>
       </c>
       <c r="E8" t="s">
         <v>68</v>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="918" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B96BBCC0-B866-482A-A828-D7F0447C094F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="918" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B96BBCC0-B866-482A-A828-D7F0447C094F}"/>
+  <xr:revisionPtr revIDLastSave="919" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA1FE2B6-6DAD-4BBE-990C-5735CEFFF639}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView minimized="1" xWindow="2616" yWindow="2616" windowWidth="17280" windowHeight="8880" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="SegmentaciónDeDatos_Sitio">#N/A</definedName>
     <definedName name="SegmentaciónDeDatos_Unidad">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
@@ -334,7 +334,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -373,9 +373,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -9133,7 +9130,7 @@
       <c r="B311" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C311" s="16" t="str">
+      <c r="C311" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
@@ -9544,7 +9541,7 @@
         <v>46144.101388888892</v>
       </c>
       <c r="C8" s="3">
-        <v>46148.999988425923</v>
+        <v>46151.999988425923</v>
       </c>
       <c r="D8" s="14">
         <v>5</v>
@@ -9701,6 +9698,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100FB7AAE8C8816FD47B559A0CCF555AFF0" ma:contentTypeVersion="10" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5c9910934a78ddf693a6b708b52e9b37">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f95d585e-e7a7-414c-955d-38a47c8579bd" xmlns:ns3="33ab045e-9213-4eea-a9f2-a5b809105d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a9c61c95b4e11caed4e46447c2ca01e7" ns2:_="" ns3:_="">
     <xsd:import namespace="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
@@ -9903,30 +9923,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9945,31 +9967,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{0a9b9e15-83d2-4075-9282-a04e05c6580a}" enabled="1" method="Standard" siteId="{24139d14-c62c-4c47-8bdd-ce71ea1d50cf}" contentBits="0" removed="0"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="919" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA1FE2B6-6DAD-4BBE-990C-5735CEFFF639}"/>
+  <xr:revisionPtr revIDLastSave="920" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EAB04E3-A257-4415-91B1-39B256F5FC06}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2616" yWindow="2616" windowWidth="17280" windowHeight="8880" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView minimized="1" xWindow="-480000" yWindow="-480000" windowWidth="2985" windowHeight="705" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="SegmentaciónDeDatos_Sitio">#N/A</definedName>
     <definedName name="SegmentaciónDeDatos_Unidad">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
@@ -9541,7 +9541,7 @@
         <v>46144.101388888892</v>
       </c>
       <c r="C8" s="3">
-        <v>46151.999988425923</v>
+        <v>46152.999988425923</v>
       </c>
       <c r="D8" s="14">
         <v>5</v>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="920" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EAB04E3-A257-4415-91B1-39B256F5FC06}"/>
+  <xr:revisionPtr revIDLastSave="924" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8148453C-044B-44A7-B6D6-09CEDAE28B04}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="-480000" yWindow="-480000" windowWidth="2985" windowHeight="705" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="79">
   <si>
     <t>ID</t>
   </si>
@@ -334,7 +334,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -373,6 +373,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -712,8 +715,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J311" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J311" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J312" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J312" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1095,28 +1098,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
   <dimension ref="A9:J331"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="41.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="151.33203125" customWidth="1"/>
-    <col min="10" max="10" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" customWidth="1"/>
-    <col min="12" max="12" width="33.33203125" customWidth="1"/>
+    <col min="6" max="7" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="151.28515625" customWidth="1"/>
+    <col min="10" max="10" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="33.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>301</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1148,7 +1151,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -1174,7 +1177,7 @@
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -1200,7 +1203,7 @@
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>3</v>
       </c>
@@ -1226,7 +1229,7 @@
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>4</v>
       </c>
@@ -1252,7 +1255,7 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>5</v>
       </c>
@@ -1278,7 +1281,7 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>6</v>
       </c>
@@ -1304,7 +1307,7 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>7</v>
       </c>
@@ -1330,7 +1333,7 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>8</v>
       </c>
@@ -1356,7 +1359,7 @@
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>9</v>
       </c>
@@ -1382,7 +1385,7 @@
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>10</v>
       </c>
@@ -1408,7 +1411,7 @@
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>11</v>
       </c>
@@ -1434,7 +1437,7 @@
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>12</v>
       </c>
@@ -1460,7 +1463,7 @@
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>13</v>
       </c>
@@ -1486,7 +1489,7 @@
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>14</v>
       </c>
@@ -1512,7 +1515,7 @@
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>15</v>
       </c>
@@ -1538,7 +1541,7 @@
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>16</v>
       </c>
@@ -1564,7 +1567,7 @@
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>17</v>
       </c>
@@ -1590,7 +1593,7 @@
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>18</v>
       </c>
@@ -1616,7 +1619,7 @@
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>19</v>
       </c>
@@ -1642,7 +1645,7 @@
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>20</v>
       </c>
@@ -1668,7 +1671,7 @@
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>21</v>
       </c>
@@ -1694,7 +1697,7 @@
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>22</v>
       </c>
@@ -1720,7 +1723,7 @@
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>23</v>
       </c>
@@ -1746,7 +1749,7 @@
       <c r="H33" s="11"/>
       <c r="I33" s="11"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24</v>
       </c>
@@ -1772,7 +1775,7 @@
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>25</v>
       </c>
@@ -1798,7 +1801,7 @@
       <c r="H35" s="11"/>
       <c r="I35" s="11"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>26</v>
       </c>
@@ -1824,7 +1827,7 @@
       <c r="H36" s="11"/>
       <c r="I36" s="11"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>27</v>
       </c>
@@ -1850,7 +1853,7 @@
       <c r="H37" s="11"/>
       <c r="I37" s="11"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>28</v>
       </c>
@@ -1876,7 +1879,7 @@
       <c r="H38" s="11"/>
       <c r="I38" s="11"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>29</v>
       </c>
@@ -1902,7 +1905,7 @@
       <c r="H39" s="11"/>
       <c r="I39" s="11"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>30</v>
       </c>
@@ -1928,7 +1931,7 @@
       <c r="H40" s="11"/>
       <c r="I40" s="11"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>31</v>
       </c>
@@ -1954,7 +1957,7 @@
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>32</v>
       </c>
@@ -1980,7 +1983,7 @@
       <c r="H42" s="11"/>
       <c r="I42" s="11"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>33</v>
       </c>
@@ -2006,7 +2009,7 @@
       <c r="H43" s="11"/>
       <c r="I43" s="11"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>34</v>
       </c>
@@ -2032,7 +2035,7 @@
       <c r="H44" s="11"/>
       <c r="I44" s="11"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>35</v>
       </c>
@@ -2058,7 +2061,7 @@
       <c r="H45" s="11"/>
       <c r="I45" s="11"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>36</v>
       </c>
@@ -2084,7 +2087,7 @@
       <c r="H46" s="11"/>
       <c r="I46" s="11"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>37</v>
       </c>
@@ -2110,7 +2113,7 @@
       <c r="H47" s="11"/>
       <c r="I47" s="11"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>38</v>
       </c>
@@ -2136,7 +2139,7 @@
       <c r="H48" s="11"/>
       <c r="I48" s="11"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>39</v>
       </c>
@@ -2162,7 +2165,7 @@
       <c r="H49" s="11"/>
       <c r="I49" s="11"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>40</v>
       </c>
@@ -2188,7 +2191,7 @@
       <c r="H50" s="11"/>
       <c r="I50" s="11"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>41</v>
       </c>
@@ -2214,7 +2217,7 @@
       <c r="H51" s="11"/>
       <c r="I51" s="11"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>42</v>
       </c>
@@ -2240,7 +2243,7 @@
       <c r="H52" s="11"/>
       <c r="I52" s="11"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>43</v>
       </c>
@@ -2266,7 +2269,7 @@
       <c r="H53" s="11"/>
       <c r="I53" s="11"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>44</v>
       </c>
@@ -2292,7 +2295,7 @@
       <c r="H54" s="11"/>
       <c r="I54" s="11"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>45</v>
       </c>
@@ -2318,7 +2321,7 @@
       <c r="H55" s="11"/>
       <c r="I55" s="11"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>46</v>
       </c>
@@ -2344,7 +2347,7 @@
       <c r="H56" s="11"/>
       <c r="I56" s="11"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>47</v>
       </c>
@@ -2370,7 +2373,7 @@
       <c r="H57" s="11"/>
       <c r="I57" s="11"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>48</v>
       </c>
@@ -2396,7 +2399,7 @@
       <c r="H58" s="11"/>
       <c r="I58" s="11"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>49</v>
       </c>
@@ -2422,7 +2425,7 @@
       <c r="H59" s="11"/>
       <c r="I59" s="11"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>50</v>
       </c>
@@ -2448,7 +2451,7 @@
       <c r="H60" s="11"/>
       <c r="I60" s="11"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>51</v>
       </c>
@@ -2474,7 +2477,7 @@
       <c r="H61" s="11"/>
       <c r="I61" s="11"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>52</v>
       </c>
@@ -2500,7 +2503,7 @@
       <c r="H62" s="11"/>
       <c r="I62" s="11"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>53</v>
       </c>
@@ -2526,7 +2529,7 @@
       <c r="H63" s="11"/>
       <c r="I63" s="11"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>54</v>
       </c>
@@ -2552,7 +2555,7 @@
       <c r="H64" s="11"/>
       <c r="I64" s="11"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>55</v>
       </c>
@@ -2578,7 +2581,7 @@
       <c r="H65" s="11"/>
       <c r="I65" s="11"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>56</v>
       </c>
@@ -2604,7 +2607,7 @@
       <c r="H66" s="11"/>
       <c r="I66" s="11"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>57</v>
       </c>
@@ -2630,7 +2633,7 @@
       <c r="H67" s="11"/>
       <c r="I67" s="11"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>58</v>
       </c>
@@ -2656,7 +2659,7 @@
       <c r="H68" s="11"/>
       <c r="I68" s="11"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>59</v>
       </c>
@@ -2682,7 +2685,7 @@
       <c r="H69" s="11"/>
       <c r="I69" s="11"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>60</v>
       </c>
@@ -2708,7 +2711,7 @@
       <c r="H70" s="11"/>
       <c r="I70" s="11"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>61</v>
       </c>
@@ -2734,7 +2737,7 @@
       <c r="H71" s="11"/>
       <c r="I71" s="11"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>62</v>
       </c>
@@ -2760,7 +2763,7 @@
       <c r="H72" s="11"/>
       <c r="I72" s="11"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>63</v>
       </c>
@@ -2786,7 +2789,7 @@
       <c r="H73" s="11"/>
       <c r="I73" s="11"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>64</v>
       </c>
@@ -2812,7 +2815,7 @@
       <c r="H74" s="11"/>
       <c r="I74" s="11"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>65</v>
       </c>
@@ -2838,7 +2841,7 @@
       <c r="H75" s="11"/>
       <c r="I75" s="11"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>66</v>
       </c>
@@ -2864,7 +2867,7 @@
       <c r="H76" s="11"/>
       <c r="I76" s="11"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>67</v>
       </c>
@@ -2890,7 +2893,7 @@
       <c r="H77" s="11"/>
       <c r="I77" s="11"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>68</v>
       </c>
@@ -2916,7 +2919,7 @@
       <c r="H78" s="11"/>
       <c r="I78" s="11"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>69</v>
       </c>
@@ -2942,7 +2945,7 @@
       <c r="H79" s="11"/>
       <c r="I79" s="11"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>70</v>
       </c>
@@ -2968,7 +2971,7 @@
       <c r="H80" s="11"/>
       <c r="I80" s="11"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>71</v>
       </c>
@@ -2994,7 +2997,7 @@
       <c r="H81" s="11"/>
       <c r="I81" s="11"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>72</v>
       </c>
@@ -3020,7 +3023,7 @@
       <c r="H82" s="11"/>
       <c r="I82" s="11"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>73</v>
       </c>
@@ -3046,7 +3049,7 @@
       <c r="H83" s="11"/>
       <c r="I83" s="11"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>74</v>
       </c>
@@ -3072,7 +3075,7 @@
       <c r="H84" s="11"/>
       <c r="I84" s="11"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>75</v>
       </c>
@@ -3098,7 +3101,7 @@
       <c r="H85" s="11"/>
       <c r="I85" s="11"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>76</v>
       </c>
@@ -3124,7 +3127,7 @@
       <c r="H86" s="11"/>
       <c r="I86" s="11"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>77</v>
       </c>
@@ -3150,7 +3153,7 @@
       <c r="H87" s="11"/>
       <c r="I87" s="11"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>78</v>
       </c>
@@ -3176,7 +3179,7 @@
       <c r="H88" s="11"/>
       <c r="I88" s="11"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>79</v>
       </c>
@@ -3202,7 +3205,7 @@
       <c r="H89" s="11"/>
       <c r="I89" s="11"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>80</v>
       </c>
@@ -3228,7 +3231,7 @@
       <c r="H90" s="11"/>
       <c r="I90" s="11"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>81</v>
       </c>
@@ -3254,7 +3257,7 @@
       <c r="H91" s="11"/>
       <c r="I91" s="11"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>82</v>
       </c>
@@ -3280,7 +3283,7 @@
       <c r="H92" s="11"/>
       <c r="I92" s="11"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>83</v>
       </c>
@@ -3306,7 +3309,7 @@
       <c r="H93" s="11"/>
       <c r="I93" s="11"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>84</v>
       </c>
@@ -3332,7 +3335,7 @@
       <c r="H94" s="11"/>
       <c r="I94" s="11"/>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>85</v>
       </c>
@@ -3358,7 +3361,7 @@
       <c r="H95" s="11"/>
       <c r="I95" s="11"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>86</v>
       </c>
@@ -3384,7 +3387,7 @@
       <c r="H96" s="11"/>
       <c r="I96" s="11"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>87</v>
       </c>
@@ -3410,7 +3413,7 @@
       <c r="H97" s="11"/>
       <c r="I97" s="11"/>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>88</v>
       </c>
@@ -3436,7 +3439,7 @@
       <c r="H98" s="11"/>
       <c r="I98" s="11"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>89</v>
       </c>
@@ -3462,7 +3465,7 @@
       <c r="H99" s="11"/>
       <c r="I99" s="11"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>90</v>
       </c>
@@ -3488,7 +3491,7 @@
       <c r="H100" s="11"/>
       <c r="I100" s="11"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>91</v>
       </c>
@@ -3514,7 +3517,7 @@
       <c r="H101" s="11"/>
       <c r="I101" s="11"/>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>92</v>
       </c>
@@ -3540,7 +3543,7 @@
       <c r="H102" s="11"/>
       <c r="I102" s="11"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>93</v>
       </c>
@@ -3566,7 +3569,7 @@
       <c r="H103" s="11"/>
       <c r="I103" s="11"/>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>94</v>
       </c>
@@ -3592,7 +3595,7 @@
       <c r="H104" s="11"/>
       <c r="I104" s="11"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>95</v>
       </c>
@@ -3618,7 +3621,7 @@
       <c r="H105" s="11"/>
       <c r="I105" s="11"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>96</v>
       </c>
@@ -3644,7 +3647,7 @@
       <c r="H106" s="11"/>
       <c r="I106" s="11"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>97</v>
       </c>
@@ -3670,7 +3673,7 @@
       <c r="H107" s="11"/>
       <c r="I107" s="11"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>98</v>
       </c>
@@ -3696,7 +3699,7 @@
       <c r="H108" s="11"/>
       <c r="I108" s="11"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>99</v>
       </c>
@@ -3722,7 +3725,7 @@
       <c r="H109" s="11"/>
       <c r="I109" s="11"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>100</v>
       </c>
@@ -3748,7 +3751,7 @@
       <c r="H110" s="11"/>
       <c r="I110" s="11"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>101</v>
       </c>
@@ -3774,7 +3777,7 @@
       <c r="H111" s="11"/>
       <c r="I111" s="11"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>102</v>
       </c>
@@ -3800,7 +3803,7 @@
       <c r="H112" s="11"/>
       <c r="I112" s="11"/>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>103</v>
       </c>
@@ -3826,7 +3829,7 @@
       <c r="H113" s="11"/>
       <c r="I113" s="11"/>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>104</v>
       </c>
@@ -3852,7 +3855,7 @@
       <c r="H114" s="11"/>
       <c r="I114" s="11"/>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>105</v>
       </c>
@@ -3878,7 +3881,7 @@
       <c r="H115" s="11"/>
       <c r="I115" s="11"/>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>106</v>
       </c>
@@ -3904,7 +3907,7 @@
       <c r="H116" s="11"/>
       <c r="I116" s="11"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>107</v>
       </c>
@@ -3930,7 +3933,7 @@
       <c r="H117" s="11"/>
       <c r="I117" s="11"/>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>108</v>
       </c>
@@ -3956,7 +3959,7 @@
       <c r="H118" s="11"/>
       <c r="I118" s="11"/>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>109</v>
       </c>
@@ -3982,7 +3985,7 @@
       <c r="H119" s="11"/>
       <c r="I119" s="11"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>110</v>
       </c>
@@ -4008,7 +4011,7 @@
       <c r="H120" s="11"/>
       <c r="I120" s="11"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>111</v>
       </c>
@@ -4034,7 +4037,7 @@
       <c r="H121" s="11"/>
       <c r="I121" s="11"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>112</v>
       </c>
@@ -4060,7 +4063,7 @@
       <c r="H122" s="11"/>
       <c r="I122" s="11"/>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>113</v>
       </c>
@@ -4086,7 +4089,7 @@
       <c r="H123" s="11"/>
       <c r="I123" s="11"/>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>114</v>
       </c>
@@ -4112,7 +4115,7 @@
       <c r="H124" s="11"/>
       <c r="I124" s="11"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>115</v>
       </c>
@@ -4138,7 +4141,7 @@
       <c r="H125" s="11"/>
       <c r="I125" s="11"/>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>116</v>
       </c>
@@ -4164,7 +4167,7 @@
       <c r="H126" s="11"/>
       <c r="I126" s="11"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>117</v>
       </c>
@@ -4190,7 +4193,7 @@
       <c r="H127" s="11"/>
       <c r="I127" s="11"/>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>118</v>
       </c>
@@ -4216,7 +4219,7 @@
       <c r="H128" s="11"/>
       <c r="I128" s="11"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>119</v>
       </c>
@@ -4242,7 +4245,7 @@
       <c r="H129" s="11"/>
       <c r="I129" s="11"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>120</v>
       </c>
@@ -4268,7 +4271,7 @@
       <c r="H130" s="11"/>
       <c r="I130" s="11"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>121</v>
       </c>
@@ -4294,7 +4297,7 @@
       <c r="H131" s="11"/>
       <c r="I131" s="11"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>122</v>
       </c>
@@ -4320,7 +4323,7 @@
       <c r="H132" s="11"/>
       <c r="I132" s="11"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>123</v>
       </c>
@@ -4346,7 +4349,7 @@
       <c r="H133" s="11"/>
       <c r="I133" s="11"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>124</v>
       </c>
@@ -4372,7 +4375,7 @@
       <c r="H134" s="11"/>
       <c r="I134" s="11"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>125</v>
       </c>
@@ -4398,7 +4401,7 @@
       <c r="H135" s="11"/>
       <c r="I135" s="11"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>126</v>
       </c>
@@ -4424,7 +4427,7 @@
       <c r="H136" s="11"/>
       <c r="I136" s="11"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>127</v>
       </c>
@@ -4450,7 +4453,7 @@
       <c r="H137" s="11"/>
       <c r="I137" s="11"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>128</v>
       </c>
@@ -4476,7 +4479,7 @@
       <c r="H138" s="11"/>
       <c r="I138" s="11"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>129</v>
       </c>
@@ -4502,7 +4505,7 @@
       <c r="H139" s="11"/>
       <c r="I139" s="11"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>130</v>
       </c>
@@ -4528,7 +4531,7 @@
       <c r="H140" s="11"/>
       <c r="I140" s="11"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>131</v>
       </c>
@@ -4554,7 +4557,7 @@
       <c r="H141" s="11"/>
       <c r="I141" s="11"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>132</v>
       </c>
@@ -4580,7 +4583,7 @@
       <c r="H142" s="11"/>
       <c r="I142" s="11"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>133</v>
       </c>
@@ -4606,7 +4609,7 @@
       <c r="H143" s="11"/>
       <c r="I143" s="11"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>134</v>
       </c>
@@ -4632,7 +4635,7 @@
       <c r="H144" s="11"/>
       <c r="I144" s="11"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>135</v>
       </c>
@@ -4658,7 +4661,7 @@
       <c r="H145" s="11"/>
       <c r="I145" s="11"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>136</v>
       </c>
@@ -4684,7 +4687,7 @@
       <c r="H146" s="11"/>
       <c r="I146" s="11"/>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>137</v>
       </c>
@@ -4710,7 +4713,7 @@
       <c r="H147" s="11"/>
       <c r="I147" s="11"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>138</v>
       </c>
@@ -4736,7 +4739,7 @@
       <c r="H148" s="11"/>
       <c r="I148" s="11"/>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>139</v>
       </c>
@@ -4762,7 +4765,7 @@
       <c r="H149" s="11"/>
       <c r="I149" s="11"/>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>140</v>
       </c>
@@ -4788,7 +4791,7 @@
       <c r="H150" s="11"/>
       <c r="I150" s="11"/>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>141</v>
       </c>
@@ -4814,7 +4817,7 @@
       <c r="H151" s="11"/>
       <c r="I151" s="11"/>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>142</v>
       </c>
@@ -4840,7 +4843,7 @@
       <c r="H152" s="11"/>
       <c r="I152" s="11"/>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>143</v>
       </c>
@@ -4866,7 +4869,7 @@
       <c r="H153" s="11"/>
       <c r="I153" s="11"/>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>144</v>
       </c>
@@ -4892,7 +4895,7 @@
       <c r="H154" s="11"/>
       <c r="I154" s="11"/>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>145</v>
       </c>
@@ -4918,7 +4921,7 @@
       <c r="H155" s="11"/>
       <c r="I155" s="11"/>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>146</v>
       </c>
@@ -4944,7 +4947,7 @@
       <c r="H156" s="11"/>
       <c r="I156" s="11"/>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>147</v>
       </c>
@@ -4970,7 +4973,7 @@
       <c r="H157" s="11"/>
       <c r="I157" s="11"/>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>148</v>
       </c>
@@ -4996,7 +4999,7 @@
       <c r="H158" s="11"/>
       <c r="I158" s="11"/>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>149</v>
       </c>
@@ -5022,7 +5025,7 @@
       <c r="H159" s="11"/>
       <c r="I159" s="11"/>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>150</v>
       </c>
@@ -5048,7 +5051,7 @@
       <c r="H160" s="11"/>
       <c r="I160" s="11"/>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>151</v>
       </c>
@@ -5074,7 +5077,7 @@
       <c r="H161" s="11"/>
       <c r="I161" s="11"/>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>152</v>
       </c>
@@ -5100,7 +5103,7 @@
       <c r="H162" s="11"/>
       <c r="I162" s="11"/>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>153</v>
       </c>
@@ -5126,7 +5129,7 @@
       <c r="H163" s="11"/>
       <c r="I163" s="11"/>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>154</v>
       </c>
@@ -5152,7 +5155,7 @@
       <c r="H164" s="11"/>
       <c r="I164" s="11"/>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>155</v>
       </c>
@@ -5178,7 +5181,7 @@
       <c r="H165" s="11"/>
       <c r="I165" s="11"/>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>156</v>
       </c>
@@ -5204,7 +5207,7 @@
       <c r="H166" s="11"/>
       <c r="I166" s="11"/>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>157</v>
       </c>
@@ -5230,7 +5233,7 @@
       <c r="H167" s="11"/>
       <c r="I167" s="11"/>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>158</v>
       </c>
@@ -5256,7 +5259,7 @@
       <c r="H168" s="11"/>
       <c r="I168" s="11"/>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>159</v>
       </c>
@@ -5282,7 +5285,7 @@
       <c r="H169" s="11"/>
       <c r="I169" s="11"/>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>160</v>
       </c>
@@ -5308,7 +5311,7 @@
       <c r="H170" s="11"/>
       <c r="I170" s="11"/>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>161</v>
       </c>
@@ -5334,7 +5337,7 @@
       <c r="H171" s="11"/>
       <c r="I171" s="11"/>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>162</v>
       </c>
@@ -5360,7 +5363,7 @@
       <c r="H172" s="11"/>
       <c r="I172" s="11"/>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>163</v>
       </c>
@@ -5386,7 +5389,7 @@
       <c r="H173" s="11"/>
       <c r="I173" s="11"/>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>164</v>
       </c>
@@ -5412,7 +5415,7 @@
       <c r="H174" s="11"/>
       <c r="I174" s="11"/>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>165</v>
       </c>
@@ -5438,7 +5441,7 @@
       <c r="H175" s="11"/>
       <c r="I175" s="11"/>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>166</v>
       </c>
@@ -5464,7 +5467,7 @@
       <c r="H176" s="11"/>
       <c r="I176" s="11"/>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>167</v>
       </c>
@@ -5490,7 +5493,7 @@
       <c r="H177" s="11"/>
       <c r="I177" s="11"/>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>168</v>
       </c>
@@ -5516,7 +5519,7 @@
       <c r="H178" s="11"/>
       <c r="I178" s="11"/>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>169</v>
       </c>
@@ -5542,7 +5545,7 @@
       <c r="H179" s="11"/>
       <c r="I179" s="11"/>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>170</v>
       </c>
@@ -5568,7 +5571,7 @@
       <c r="H180" s="11"/>
       <c r="I180" s="11"/>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>171</v>
       </c>
@@ -5594,7 +5597,7 @@
       <c r="H181" s="11"/>
       <c r="I181" s="11"/>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>172</v>
       </c>
@@ -5620,7 +5623,7 @@
       <c r="H182" s="11"/>
       <c r="I182" s="11"/>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>173</v>
       </c>
@@ -5646,7 +5649,7 @@
       <c r="H183" s="11"/>
       <c r="I183" s="11"/>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>174</v>
       </c>
@@ -5672,7 +5675,7 @@
       <c r="H184" s="11"/>
       <c r="I184" s="11"/>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>175</v>
       </c>
@@ -5698,7 +5701,7 @@
       <c r="H185" s="11"/>
       <c r="I185" s="11"/>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>176</v>
       </c>
@@ -5724,7 +5727,7 @@
       <c r="H186" s="11"/>
       <c r="I186" s="11"/>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>177</v>
       </c>
@@ -5750,7 +5753,7 @@
       <c r="H187" s="11"/>
       <c r="I187" s="11"/>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>178</v>
       </c>
@@ -5776,7 +5779,7 @@
       <c r="H188" s="11"/>
       <c r="I188" s="11"/>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>179</v>
       </c>
@@ -5802,7 +5805,7 @@
       <c r="H189" s="11"/>
       <c r="I189" s="11"/>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>180</v>
       </c>
@@ -5828,7 +5831,7 @@
       <c r="H190" s="11"/>
       <c r="I190" s="11"/>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>181</v>
       </c>
@@ -5854,7 +5857,7 @@
       <c r="H191" s="11"/>
       <c r="I191" s="11"/>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>182</v>
       </c>
@@ -5880,7 +5883,7 @@
       <c r="H192" s="11"/>
       <c r="I192" s="11"/>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>183</v>
       </c>
@@ -5906,7 +5909,7 @@
       <c r="H193" s="11"/>
       <c r="I193" s="11"/>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>184</v>
       </c>
@@ -5932,7 +5935,7 @@
       <c r="H194" s="11"/>
       <c r="I194" s="11"/>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>185</v>
       </c>
@@ -5958,7 +5961,7 @@
       <c r="H195" s="11"/>
       <c r="I195" s="11"/>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>186</v>
       </c>
@@ -5984,7 +5987,7 @@
       <c r="H196" s="11"/>
       <c r="I196" s="11"/>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>187</v>
       </c>
@@ -6010,7 +6013,7 @@
       <c r="H197" s="11"/>
       <c r="I197" s="11"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>188</v>
       </c>
@@ -6036,7 +6039,7 @@
       <c r="H198" s="11"/>
       <c r="I198" s="11"/>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>189</v>
       </c>
@@ -6062,7 +6065,7 @@
       <c r="H199" s="11"/>
       <c r="I199" s="11"/>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>190</v>
       </c>
@@ -6088,7 +6091,7 @@
       <c r="H200" s="11"/>
       <c r="I200" s="11"/>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>191</v>
       </c>
@@ -6114,7 +6117,7 @@
       <c r="H201" s="11"/>
       <c r="I201" s="11"/>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>192</v>
       </c>
@@ -6140,7 +6143,7 @@
       <c r="H202" s="11"/>
       <c r="I202" s="11"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>193</v>
       </c>
@@ -6166,7 +6169,7 @@
       <c r="H203" s="11"/>
       <c r="I203" s="11"/>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>194</v>
       </c>
@@ -6192,7 +6195,7 @@
       <c r="H204" s="11"/>
       <c r="I204" s="11"/>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>195</v>
       </c>
@@ -6218,7 +6221,7 @@
       <c r="H205" s="11"/>
       <c r="I205" s="11"/>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>196</v>
       </c>
@@ -6244,7 +6247,7 @@
       <c r="H206" s="11"/>
       <c r="I206" s="11"/>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>197</v>
       </c>
@@ -6270,7 +6273,7 @@
       <c r="H207" s="11"/>
       <c r="I207" s="11"/>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>198</v>
       </c>
@@ -6296,7 +6299,7 @@
       <c r="H208" s="11"/>
       <c r="I208" s="11"/>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>199</v>
       </c>
@@ -6322,7 +6325,7 @@
       <c r="H209" s="11"/>
       <c r="I209" s="11"/>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>200</v>
       </c>
@@ -6348,7 +6351,7 @@
       <c r="H210" s="11"/>
       <c r="I210" s="11"/>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <v>201</v>
       </c>
@@ -6374,7 +6377,7 @@
       <c r="H211" s="11"/>
       <c r="I211" s="11"/>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>202</v>
       </c>
@@ -6400,7 +6403,7 @@
       <c r="H212" s="11"/>
       <c r="I212" s="11"/>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <v>203</v>
       </c>
@@ -6426,7 +6429,7 @@
       <c r="H213" s="11"/>
       <c r="I213" s="11"/>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>204</v>
       </c>
@@ -6452,7 +6455,7 @@
       <c r="H214" s="11"/>
       <c r="I214" s="11"/>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>205</v>
       </c>
@@ -6478,7 +6481,7 @@
       <c r="H215" s="11"/>
       <c r="I215" s="11"/>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <v>206</v>
       </c>
@@ -6504,7 +6507,7 @@
       <c r="H216" s="11"/>
       <c r="I216" s="11"/>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <v>207</v>
       </c>
@@ -6530,7 +6533,7 @@
       <c r="H217" s="11"/>
       <c r="I217" s="11"/>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <v>208</v>
       </c>
@@ -6556,7 +6559,7 @@
       <c r="H218" s="11"/>
       <c r="I218" s="11"/>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <v>209</v>
       </c>
@@ -6582,7 +6585,7 @@
       <c r="H219" s="11"/>
       <c r="I219" s="11"/>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <v>210</v>
       </c>
@@ -6608,7 +6611,7 @@
       <c r="H220" s="11"/>
       <c r="I220" s="11"/>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <v>211</v>
       </c>
@@ -6634,7 +6637,7 @@
       <c r="H221" s="11"/>
       <c r="I221" s="11"/>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <v>212</v>
       </c>
@@ -6660,7 +6663,7 @@
       <c r="H222" s="11"/>
       <c r="I222" s="11"/>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <v>213</v>
       </c>
@@ -6686,7 +6689,7 @@
       <c r="H223" s="11"/>
       <c r="I223" s="11"/>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <v>214</v>
       </c>
@@ -6712,7 +6715,7 @@
       <c r="H224" s="11"/>
       <c r="I224" s="11"/>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>215</v>
       </c>
@@ -6738,7 +6741,7 @@
       <c r="H225" s="11"/>
       <c r="I225" s="11"/>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <v>216</v>
       </c>
@@ -6764,7 +6767,7 @@
       <c r="H226" s="11"/>
       <c r="I226" s="11"/>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
         <v>217</v>
       </c>
@@ -6790,7 +6793,7 @@
       <c r="H227" s="11"/>
       <c r="I227" s="11"/>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <v>218</v>
       </c>
@@ -6816,7 +6819,7 @@
       <c r="H228" s="11"/>
       <c r="I228" s="11"/>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <v>219</v>
       </c>
@@ -6842,7 +6845,7 @@
       <c r="H229" s="11"/>
       <c r="I229" s="11"/>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <v>220</v>
       </c>
@@ -6868,7 +6871,7 @@
       <c r="H230" s="11"/>
       <c r="I230" s="11"/>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
         <v>221</v>
       </c>
@@ -6894,7 +6897,7 @@
       <c r="H231" s="11"/>
       <c r="I231" s="11"/>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
         <v>222</v>
       </c>
@@ -6920,7 +6923,7 @@
       <c r="H232" s="11"/>
       <c r="I232" s="11"/>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <v>223</v>
       </c>
@@ -6946,7 +6949,7 @@
       <c r="H233" s="11"/>
       <c r="I233" s="11"/>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <v>224</v>
       </c>
@@ -6972,7 +6975,7 @@
       <c r="H234" s="11"/>
       <c r="I234" s="11"/>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <v>225</v>
       </c>
@@ -6998,7 +7001,7 @@
       <c r="H235" s="11"/>
       <c r="I235" s="11"/>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <v>226</v>
       </c>
@@ -7024,7 +7027,7 @@
       <c r="H236" s="11"/>
       <c r="I236" s="11"/>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <v>227</v>
       </c>
@@ -7050,7 +7053,7 @@
       <c r="H237" s="11"/>
       <c r="I237" s="11"/>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <v>228</v>
       </c>
@@ -7076,7 +7079,7 @@
       <c r="H238" s="11"/>
       <c r="I238" s="11"/>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <v>229</v>
       </c>
@@ -7102,7 +7105,7 @@
       <c r="H239" s="11"/>
       <c r="I239" s="11"/>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <v>230</v>
       </c>
@@ -7128,7 +7131,7 @@
       <c r="H240" s="11"/>
       <c r="I240" s="11"/>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
         <v>231</v>
       </c>
@@ -7154,7 +7157,7 @@
       <c r="H241" s="11"/>
       <c r="I241" s="11"/>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
         <v>232</v>
       </c>
@@ -7180,7 +7183,7 @@
       <c r="H242" s="11"/>
       <c r="I242" s="11"/>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
         <v>233</v>
       </c>
@@ -7206,7 +7209,7 @@
       <c r="H243" s="11"/>
       <c r="I243" s="11"/>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
         <v>234</v>
       </c>
@@ -7232,7 +7235,7 @@
       <c r="H244" s="11"/>
       <c r="I244" s="11"/>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
         <v>235</v>
       </c>
@@ -7258,7 +7261,7 @@
       <c r="H245" s="11"/>
       <c r="I245" s="11"/>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
         <v>236</v>
       </c>
@@ -7284,7 +7287,7 @@
       <c r="H246" s="11"/>
       <c r="I246" s="11"/>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
         <v>237</v>
       </c>
@@ -7310,7 +7313,7 @@
       <c r="H247" s="11"/>
       <c r="I247" s="11"/>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <v>238</v>
       </c>
@@ -7336,7 +7339,7 @@
       <c r="H248" s="11"/>
       <c r="I248" s="11"/>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
         <v>239</v>
       </c>
@@ -7362,7 +7365,7 @@
       <c r="H249" s="11"/>
       <c r="I249" s="11"/>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
         <v>240</v>
       </c>
@@ -7388,7 +7391,7 @@
       <c r="H250" s="11"/>
       <c r="I250" s="11"/>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
         <v>241</v>
       </c>
@@ -7414,7 +7417,7 @@
       <c r="H251" s="11"/>
       <c r="I251" s="11"/>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
         <v>242</v>
       </c>
@@ -7440,7 +7443,7 @@
       <c r="H252" s="11"/>
       <c r="I252" s="11"/>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
         <v>243</v>
       </c>
@@ -7466,7 +7469,7 @@
       <c r="H253" s="11"/>
       <c r="I253" s="11"/>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
         <v>244</v>
       </c>
@@ -7492,7 +7495,7 @@
       <c r="H254" s="11"/>
       <c r="I254" s="11"/>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
         <v>245</v>
       </c>
@@ -7518,7 +7521,7 @@
       <c r="H255" s="11"/>
       <c r="I255" s="11"/>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
         <v>246</v>
       </c>
@@ -7544,7 +7547,7 @@
       <c r="H256" s="11"/>
       <c r="I256" s="11"/>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
         <v>247</v>
       </c>
@@ -7570,7 +7573,7 @@
       <c r="H257" s="11"/>
       <c r="I257" s="11"/>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
         <v>248</v>
       </c>
@@ -7596,7 +7599,7 @@
       <c r="H258" s="11"/>
       <c r="I258" s="11"/>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
         <v>249</v>
       </c>
@@ -7622,7 +7625,7 @@
       <c r="H259" s="11"/>
       <c r="I259" s="11"/>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
         <v>250</v>
       </c>
@@ -7648,7 +7651,7 @@
       <c r="H260" s="11"/>
       <c r="I260" s="11"/>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
         <v>251</v>
       </c>
@@ -7674,7 +7677,7 @@
       <c r="H261" s="11"/>
       <c r="I261" s="11"/>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
         <v>252</v>
       </c>
@@ -7700,7 +7703,7 @@
       <c r="H262" s="11"/>
       <c r="I262" s="11"/>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
         <v>253</v>
       </c>
@@ -7726,7 +7729,7 @@
       <c r="H263" s="11"/>
       <c r="I263" s="11"/>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
         <v>254</v>
       </c>
@@ -7752,7 +7755,7 @@
       <c r="H264" s="11"/>
       <c r="I264" s="11"/>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
         <v>255</v>
       </c>
@@ -7778,7 +7781,7 @@
       <c r="H265" s="11"/>
       <c r="I265" s="11"/>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
         <v>256</v>
       </c>
@@ -7804,7 +7807,7 @@
       <c r="H266" s="11"/>
       <c r="I266" s="11"/>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
         <v>257</v>
       </c>
@@ -7830,7 +7833,7 @@
       <c r="H267" s="11"/>
       <c r="I267" s="11"/>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
         <v>258</v>
       </c>
@@ -7856,7 +7859,7 @@
       <c r="H268" s="11"/>
       <c r="I268" s="11"/>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
         <v>259</v>
       </c>
@@ -7882,7 +7885,7 @@
       <c r="H269" s="11"/>
       <c r="I269" s="11"/>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
         <v>260</v>
       </c>
@@ -7908,7 +7911,7 @@
       <c r="H270" s="11"/>
       <c r="I270" s="11"/>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
         <v>261</v>
       </c>
@@ -7934,7 +7937,7 @@
       <c r="H271" s="11"/>
       <c r="I271" s="11"/>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
         <v>262</v>
       </c>
@@ -7960,7 +7963,7 @@
       <c r="H272" s="11"/>
       <c r="I272" s="11"/>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
         <v>263</v>
       </c>
@@ -7986,7 +7989,7 @@
       <c r="H273" s="11"/>
       <c r="I273" s="11"/>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
         <v>264</v>
       </c>
@@ -8012,7 +8015,7 @@
       <c r="H274" s="11"/>
       <c r="I274" s="11"/>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
         <v>265</v>
       </c>
@@ -8038,7 +8041,7 @@
       <c r="H275" s="11"/>
       <c r="I275" s="11"/>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
         <v>266</v>
       </c>
@@ -8064,7 +8067,7 @@
       <c r="H276" s="11"/>
       <c r="I276" s="11"/>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
         <v>267</v>
       </c>
@@ -8090,7 +8093,7 @@
       <c r="H277" s="11"/>
       <c r="I277" s="11"/>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
         <v>268</v>
       </c>
@@ -8116,7 +8119,7 @@
       <c r="H278" s="11"/>
       <c r="I278" s="11"/>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
         <v>269</v>
       </c>
@@ -8142,7 +8145,7 @@
       <c r="H279" s="11"/>
       <c r="I279" s="11"/>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
         <v>270</v>
       </c>
@@ -8168,7 +8171,7 @@
       <c r="H280" s="11"/>
       <c r="I280" s="11"/>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
         <v>271</v>
       </c>
@@ -8194,7 +8197,7 @@
       <c r="H281" s="11"/>
       <c r="I281" s="11"/>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
         <v>272</v>
       </c>
@@ -8220,7 +8223,7 @@
       <c r="H282" s="11"/>
       <c r="I282" s="11"/>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
         <v>273</v>
       </c>
@@ -8246,7 +8249,7 @@
       <c r="H283" s="11"/>
       <c r="I283" s="11"/>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
         <v>274</v>
       </c>
@@ -8272,7 +8275,7 @@
       <c r="H284" s="11"/>
       <c r="I284" s="11"/>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
         <v>275</v>
       </c>
@@ -8298,7 +8301,7 @@
       <c r="H285" s="11"/>
       <c r="I285" s="11"/>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
         <v>276</v>
       </c>
@@ -8331,7 +8334,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
         <v>277</v>
       </c>
@@ -8364,7 +8367,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
         <v>278</v>
       </c>
@@ -8397,7 +8400,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
         <v>279</v>
       </c>
@@ -8430,7 +8433,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
         <v>280</v>
       </c>
@@ -8463,7 +8466,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
         <v>281</v>
       </c>
@@ -8496,7 +8499,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
         <v>282</v>
       </c>
@@ -8529,7 +8532,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
         <v>283</v>
       </c>
@@ -8562,7 +8565,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
         <v>284</v>
       </c>
@@ -8595,7 +8598,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
         <v>285</v>
       </c>
@@ -8628,7 +8631,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
         <v>286</v>
       </c>
@@ -8661,7 +8664,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
         <v>287</v>
       </c>
@@ -8694,7 +8697,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
         <v>288</v>
       </c>
@@ -8727,7 +8730,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
         <v>289</v>
       </c>
@@ -8760,7 +8763,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
         <v>290</v>
       </c>
@@ -8793,7 +8796,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
         <v>291</v>
       </c>
@@ -8826,7 +8829,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
         <v>292</v>
       </c>
@@ -8859,7 +8862,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="303" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
         <v>293</v>
       </c>
@@ -8892,7 +8895,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="304" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
         <v>294</v>
       </c>
@@ -8925,7 +8928,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
         <v>295</v>
       </c>
@@ -8958,7 +8961,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
         <v>296</v>
       </c>
@@ -8991,7 +8994,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
         <v>297</v>
       </c>
@@ -9024,7 +9027,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
         <v>298</v>
       </c>
@@ -9057,7 +9060,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
         <v>298</v>
       </c>
@@ -9090,7 +9093,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
         <v>299</v>
       </c>
@@ -9123,7 +9126,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
         <v>300</v>
       </c>
@@ -9156,64 +9159,83 @@
         <v>76</v>
       </c>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A312" s="1"/>
-    </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A312" s="1">
+        <v>301</v>
+      </c>
+      <c r="B312" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C312" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CEM</v>
+      </c>
+      <c r="D312" s="14">
+        <v>0</v>
+      </c>
+      <c r="E312" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F312" s="15"/>
+      <c r="G312" s="15"/>
+      <c r="H312" s="11"/>
+      <c r="I312" s="11"/>
+    </row>
+    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A313" s="1"/>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A314" s="1"/>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A315" s="1"/>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A316" s="1"/>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A317" s="1"/>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A318" s="1"/>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A319" s="1"/>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A320" s="1"/>
     </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A321" s="1"/>
     </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A322" s="1"/>
     </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>
     </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A324" s="1"/>
     </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A325" s="1"/>
     </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A326" s="1"/>
     </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
     </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A328" s="1"/>
     </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A329" s="1"/>
     </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>
     </row>
-    <row r="331" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A331" s="1"/>
     </row>
   </sheetData>
@@ -9235,13 +9257,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{797F1036-D41E-43A4-9E6E-CBBB62F3CD31}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.33203125" customWidth="1"/>
-    <col min="4" max="4" width="12.88671875" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9255,7 +9277,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -9269,7 +9291,7 @@
         <v>234.67</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -9283,7 +9305,7 @@
         <v>161.15</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -9297,7 +9319,7 @@
         <v>157.61000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -9311,7 +9333,7 @@
         <v>347.95</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -9325,7 +9347,7 @@
         <v>393.57</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -9339,7 +9361,7 @@
         <v>19.87</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -9353,7 +9375,7 @@
         <v>19.57</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>61</v>
       </c>
@@ -9367,7 +9389,7 @@
         <v>19.86</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -9381,7 +9403,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -9406,15 +9428,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56220E0F-EC16-4A8C-9E04-C7F8849C4B4D}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9431,7 +9453,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -9448,7 +9470,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -9465,7 +9487,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -9482,7 +9504,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -9499,7 +9521,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -9516,7 +9538,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -9533,7 +9555,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -9561,14 +9583,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83DAFC4B-C207-418A-8501-0E1EC9E673B7}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9579,7 +9601,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -9590,7 +9612,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -9601,7 +9623,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -9612,7 +9634,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>61</v>
       </c>
@@ -9623,7 +9645,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -9634,7 +9656,7 @@
         <v>46631</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -9645,7 +9667,7 @@
         <v>48579</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -9656,7 +9678,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -9667,7 +9689,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -9678,7 +9700,7 @@
         <v>48579</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -9712,15 +9734,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100FB7AAE8C8816FD47B559A0CCF555AFF0" ma:contentTypeVersion="10" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5c9910934a78ddf693a6b708b52e9b37">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f95d585e-e7a7-414c-955d-38a47c8579bd" xmlns:ns3="33ab045e-9213-4eea-a9f2-a5b809105d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a9c61c95b4e11caed4e46447c2ca01e7" ns2:_="" ns3:_="">
     <xsd:import namespace="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
@@ -9923,32 +9936,33 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9967,6 +9981,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{0a9b9e15-83d2-4075-9282-a04e05c6580a}" enabled="1" method="Standard" siteId="{24139d14-c62c-4c47-8bdd-ce71ea1d50cf}" contentBits="0" removed="0"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="924" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8148453C-044B-44A7-B6D6-09CEDAE28B04}"/>
+  <xr:revisionPtr revIDLastSave="929" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3BBBB89-979D-488D-8B48-F321C1957B52}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="82">
   <si>
     <t>ID</t>
   </si>
@@ -291,6 +291,15 @@
   </si>
   <si>
     <t>Se realiza inspección componentea, alinamiento, GAP en VTI2</t>
+  </si>
+  <si>
+    <t>Rotura tubo de caldera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rotura tubo vapor SH </t>
+  </si>
+  <si>
+    <t>Abierto</t>
   </si>
 </sst>
 </file>
@@ -9176,10 +9185,19 @@
       <c r="E312" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F312" s="15"/>
+      <c r="F312" s="15">
+        <v>46151.263194444444</v>
+      </c>
       <c r="G312" s="15"/>
-      <c r="H312" s="11"/>
-      <c r="I312" s="11"/>
+      <c r="H312" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="I312" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="J312" s="13" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A313" s="1"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="929" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3BBBB89-979D-488D-8B48-F321C1957B52}"/>
+  <xr:revisionPtr revIDLastSave="930" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43B98E5A-107A-4A4E-B4C3-629295FD3D22}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -9581,7 +9581,7 @@
         <v>46144.101388888892</v>
       </c>
       <c r="C8" s="3">
-        <v>46152.999988425923</v>
+        <v>46152.989583333336</v>
       </c>
       <c r="D8" s="14">
         <v>5</v>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="930" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43B98E5A-107A-4A4E-B4C3-629295FD3D22}"/>
+  <xr:revisionPtr revIDLastSave="937" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCDD47DF-DE11-49C7-B39E-842B9967F250}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="12" yWindow="12" windowWidth="23016" windowHeight="12216" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="83">
   <si>
     <t>ID</t>
   </si>
@@ -301,6 +301,9 @@
   <si>
     <t>Abierto</t>
   </si>
+  <si>
+    <t>Bajo nivel del Domo</t>
+  </si>
 </sst>
 </file>
 
@@ -451,15 +454,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>472492</xdr:colOff>
+      <xdr:colOff>485827</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>935947</xdr:colOff>
+      <xdr:colOff>945472</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>137070</xdr:rowOff>
+      <xdr:rowOff>146595</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -537,7 +540,7 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>225435</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>137070</xdr:rowOff>
+      <xdr:rowOff>146595</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -613,9 +616,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>859800</xdr:colOff>
+      <xdr:colOff>869325</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>137070</xdr:rowOff>
+      <xdr:rowOff>146595</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -724,8 +727,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J312" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J312" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J313" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J313" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1125,7 +1128,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -9175,7 +9178,7 @@
       <c r="B312" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C312" s="16" t="str">
+      <c r="C312" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
@@ -9200,7 +9203,32 @@
       </c>
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A313" s="1"/>
+      <c r="A313" s="1">
+        <v>302</v>
+      </c>
+      <c r="B313" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C313" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CEM</v>
+      </c>
+      <c r="D313" s="14">
+        <v>0</v>
+      </c>
+      <c r="E313" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F313" s="15">
+        <v>46154.693055555559</v>
+      </c>
+      <c r="G313" s="15">
+        <v>46154.719444444447</v>
+      </c>
+      <c r="H313" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I313" s="11"/>
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A314" s="1"/>
@@ -9752,6 +9780,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100FB7AAE8C8816FD47B559A0CCF555AFF0" ma:contentTypeVersion="10" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5c9910934a78ddf693a6b708b52e9b37">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f95d585e-e7a7-414c-955d-38a47c8579bd" xmlns:ns3="33ab045e-9213-4eea-a9f2-a5b809105d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a9c61c95b4e11caed4e46447c2ca01e7" ns2:_="" ns3:_="">
     <xsd:import namespace="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
@@ -9954,33 +9991,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9999,14 +10035,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{0a9b9e15-83d2-4075-9282-a04e05c6580a}" enabled="1" method="Standard" siteId="{24139d14-c62c-4c47-8bdd-ce71ea1d50cf}" contentBits="0" removed="0"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="937" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCDD47DF-DE11-49C7-B39E-842B9967F250}"/>
+  <xr:revisionPtr revIDLastSave="940" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51A7CDD2-E0A0-48E4-ABC1-CE56A69E730E}"/>
   <bookViews>
     <workbookView xWindow="12" yWindow="12" windowWidth="23016" windowHeight="12216" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="84">
   <si>
     <t>ID</t>
   </si>
@@ -303,6 +303,9 @@
   </si>
   <si>
     <t>Bajo nivel del Domo</t>
+  </si>
+  <si>
+    <t>Trip LAC10 por baja presión de aceite, LAC30 trip por sobreflujo de descarga y LAC20 no entra en servicio de forma automatica</t>
   </si>
 </sst>
 </file>
@@ -9228,7 +9231,12 @@
       <c r="H313" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="I313" s="11"/>
+      <c r="I313" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="J313" s="13" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A314" s="1"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="940" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51A7CDD2-E0A0-48E4-ABC1-CE56A69E730E}"/>
+  <xr:revisionPtr revIDLastSave="941" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7524B0D3-C015-43F7-81DD-8E22FF1802B9}"/>
   <bookViews>
-    <workbookView xWindow="12" yWindow="12" windowWidth="23016" windowHeight="12216" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView minimized="1" xWindow="690" yWindow="1785" windowWidth="27000" windowHeight="14040" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="SegmentaciónDeDatos_Sitio">#N/A</definedName>
     <definedName name="SegmentaciónDeDatos_Unidad">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
@@ -349,7 +349,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -388,9 +388,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -9194,7 +9191,9 @@
       <c r="F312" s="15">
         <v>46151.263194444444</v>
       </c>
-      <c r="G312" s="15"/>
+      <c r="G312" s="15">
+        <v>46163.999305555553</v>
+      </c>
       <c r="H312" s="11" t="s">
         <v>79</v>
       </c>
@@ -9212,7 +9211,7 @@
       <c r="B313" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C313" s="16" t="str">
+      <c r="C313" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
@@ -9774,29 +9773,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100FB7AAE8C8816FD47B559A0CCF555AFF0" ma:contentTypeVersion="10" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5c9910934a78ddf693a6b708b52e9b37">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f95d585e-e7a7-414c-955d-38a47c8579bd" xmlns:ns3="33ab045e-9213-4eea-a9f2-a5b809105d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a9c61c95b4e11caed4e46447c2ca01e7" ns2:_="" ns3:_="">
     <xsd:import namespace="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
@@ -9999,32 +9975,30 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10043,6 +10017,31 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{0a9b9e15-83d2-4075-9282-a04e05c6580a}" enabled="1" method="Standard" siteId="{24139d14-c62c-4c47-8bdd-ce71ea1d50cf}" contentBits="0" removed="0"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="941" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7524B0D3-C015-43F7-81DD-8E22FF1802B9}"/>
+  <xr:revisionPtr revIDLastSave="947" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6A9E40B-265F-4F2D-B58A-5F883321F016}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="690" yWindow="1785" windowWidth="27000" windowHeight="14040" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="SegmentaciónDeDatos_Sitio">#N/A</definedName>
     <definedName name="SegmentaciónDeDatos_Unidad">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="84">
   <si>
     <t>ID</t>
   </si>
@@ -349,7 +349,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -388,6 +388,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -727,8 +730,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J313" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J313" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J315" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J315" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1128,7 +1131,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -9238,10 +9241,44 @@
       </c>
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A314" s="1"/>
+      <c r="A314" s="1">
+        <v>303</v>
+      </c>
+      <c r="B314" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C314" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
+      </c>
+      <c r="D314" s="14">
+        <v>0</v>
+      </c>
+      <c r="E314" s="13"/>
+      <c r="F314" s="15"/>
+      <c r="G314" s="15"/>
+      <c r="H314" s="11"/>
+      <c r="I314" s="11"/>
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A315" s="1"/>
+      <c r="A315" s="1">
+        <v>304</v>
+      </c>
+      <c r="B315" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C315" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
+      </c>
+      <c r="D315" s="14">
+        <v>0</v>
+      </c>
+      <c r="E315" s="13"/>
+      <c r="F315" s="15"/>
+      <c r="G315" s="15"/>
+      <c r="H315" s="11"/>
+      <c r="I315" s="11"/>
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A316" s="1"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="947" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6A9E40B-265F-4F2D-B58A-5F883321F016}"/>
+  <xr:revisionPtr revIDLastSave="951" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19587348-9D4B-43D0-BD28-19380B9B7C65}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <definedName name="SegmentaciónDeDatos_Sitio">#N/A</definedName>
     <definedName name="SegmentaciónDeDatos_Unidad">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="84">
   <si>
     <t>ID</t>
   </si>
@@ -9254,8 +9254,12 @@
       <c r="D314" s="14">
         <v>0</v>
       </c>
-      <c r="E314" s="13"/>
-      <c r="F314" s="15"/>
+      <c r="E314" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F314" s="15">
+        <v>46156.012499999997</v>
+      </c>
       <c r="G314" s="15"/>
       <c r="H314" s="11"/>
       <c r="I314" s="11"/>
@@ -9274,8 +9278,12 @@
       <c r="D315" s="14">
         <v>0</v>
       </c>
-      <c r="E315" s="13"/>
-      <c r="F315" s="15"/>
+      <c r="E315" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F315" s="15">
+        <v>46156.085416666669</v>
+      </c>
       <c r="G315" s="15"/>
       <c r="H315" s="11"/>
       <c r="I315" s="11"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="951" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19587348-9D4B-43D0-BD28-19380B9B7C65}"/>
+  <xr:revisionPtr revIDLastSave="963" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C97FE67-5A81-4CD2-97BB-54316C980E7F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <definedName name="SegmentaciónDeDatos_Sitio">#N/A</definedName>
     <definedName name="SegmentaciónDeDatos_Unidad">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="86">
   <si>
     <t>ID</t>
   </si>
@@ -306,6 +306,12 @@
   </si>
   <si>
     <t>Trip LAC10 por baja presión de aceite, LAC30 trip por sobreflujo de descarga y LAC20 no entra en servicio de forma automatica</t>
+  </si>
+  <si>
+    <t>Alta diferencia T° gases de escape</t>
+  </si>
+  <si>
+    <t>Trip por diferencial de T° en los gases de escape (ensuciamineto del sensor de medición)</t>
   </si>
 </sst>
 </file>
@@ -9260,9 +9266,18 @@
       <c r="F314" s="15">
         <v>46156.012499999997</v>
       </c>
-      <c r="G314" s="15"/>
-      <c r="H314" s="11"/>
-      <c r="I314" s="11"/>
+      <c r="G314" s="15">
+        <v>46156.082638888889</v>
+      </c>
+      <c r="H314" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="I314" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="J314" s="13" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
@@ -9284,9 +9299,18 @@
       <c r="F315" s="15">
         <v>46156.085416666669</v>
       </c>
-      <c r="G315" s="15"/>
-      <c r="H315" s="11"/>
-      <c r="I315" s="11"/>
+      <c r="G315" s="15">
+        <v>46156.152777777781</v>
+      </c>
+      <c r="H315" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="I315" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="J315" s="13" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A316" s="1"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="963" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C97FE67-5A81-4CD2-97BB-54316C980E7F}"/>
+  <xr:revisionPtr revIDLastSave="973" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BD5B27A-8CB1-4490-A8F0-55DCF92600DF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView minimized="1" xWindow="1875" yWindow="2565" windowWidth="17280" windowHeight="8880" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="88">
   <si>
     <t>ID</t>
   </si>
@@ -313,6 +313,12 @@
   <si>
     <t>Trip por diferencial de T° en los gases de escape (ensuciamineto del sensor de medición)</t>
   </si>
+  <si>
+    <t>Cambio motor eléctrico VAS1</t>
+  </si>
+  <si>
+    <t>Se realiza cambio motor eléctrico VAS1 por alta temperatura en cojinete</t>
+  </si>
 </sst>
 </file>
 
@@ -463,15 +469,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>485827</xdr:colOff>
+      <xdr:colOff>478207</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>945472</xdr:colOff>
+      <xdr:colOff>932137</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>146595</xdr:rowOff>
+      <xdr:rowOff>133260</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -549,7 +555,7 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>225435</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>146595</xdr:rowOff>
+      <xdr:rowOff>133260</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -625,9 +631,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>869325</xdr:colOff>
+      <xdr:colOff>855990</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>146595</xdr:rowOff>
+      <xdr:rowOff>133260</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -736,8 +742,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J315" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J315" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J316" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J316" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1119,28 +1125,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
   <dimension ref="A9:J331"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="41.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="151.28515625" customWidth="1"/>
-    <col min="10" max="10" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" customWidth="1"/>
-    <col min="12" max="12" width="33.28515625" customWidth="1"/>
+    <col min="6" max="7" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="151.33203125" customWidth="1"/>
+    <col min="10" max="10" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" customWidth="1"/>
+    <col min="12" max="12" width="33.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>305</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1172,7 +1178,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -1198,7 +1204,7 @@
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -1224,7 +1230,7 @@
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>3</v>
       </c>
@@ -1250,7 +1256,7 @@
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>4</v>
       </c>
@@ -1276,7 +1282,7 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>5</v>
       </c>
@@ -1302,7 +1308,7 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>6</v>
       </c>
@@ -1328,7 +1334,7 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>7</v>
       </c>
@@ -1354,7 +1360,7 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>8</v>
       </c>
@@ -1380,7 +1386,7 @@
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>9</v>
       </c>
@@ -1406,7 +1412,7 @@
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>10</v>
       </c>
@@ -1432,7 +1438,7 @@
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>11</v>
       </c>
@@ -1458,7 +1464,7 @@
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>12</v>
       </c>
@@ -1484,7 +1490,7 @@
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>13</v>
       </c>
@@ -1510,7 +1516,7 @@
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>14</v>
       </c>
@@ -1536,7 +1542,7 @@
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>15</v>
       </c>
@@ -1562,7 +1568,7 @@
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>16</v>
       </c>
@@ -1588,7 +1594,7 @@
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>17</v>
       </c>
@@ -1614,7 +1620,7 @@
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>18</v>
       </c>
@@ -1640,7 +1646,7 @@
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>19</v>
       </c>
@@ -1666,7 +1672,7 @@
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>20</v>
       </c>
@@ -1692,7 +1698,7 @@
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>21</v>
       </c>
@@ -1718,7 +1724,7 @@
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>22</v>
       </c>
@@ -1744,7 +1750,7 @@
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>23</v>
       </c>
@@ -1770,7 +1776,7 @@
       <c r="H33" s="11"/>
       <c r="I33" s="11"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>24</v>
       </c>
@@ -1796,7 +1802,7 @@
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>25</v>
       </c>
@@ -1822,7 +1828,7 @@
       <c r="H35" s="11"/>
       <c r="I35" s="11"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>26</v>
       </c>
@@ -1848,7 +1854,7 @@
       <c r="H36" s="11"/>
       <c r="I36" s="11"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>27</v>
       </c>
@@ -1874,7 +1880,7 @@
       <c r="H37" s="11"/>
       <c r="I37" s="11"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>28</v>
       </c>
@@ -1900,7 +1906,7 @@
       <c r="H38" s="11"/>
       <c r="I38" s="11"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>29</v>
       </c>
@@ -1926,7 +1932,7 @@
       <c r="H39" s="11"/>
       <c r="I39" s="11"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>30</v>
       </c>
@@ -1952,7 +1958,7 @@
       <c r="H40" s="11"/>
       <c r="I40" s="11"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>31</v>
       </c>
@@ -1978,7 +1984,7 @@
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>32</v>
       </c>
@@ -2004,7 +2010,7 @@
       <c r="H42" s="11"/>
       <c r="I42" s="11"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>33</v>
       </c>
@@ -2030,7 +2036,7 @@
       <c r="H43" s="11"/>
       <c r="I43" s="11"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>34</v>
       </c>
@@ -2056,7 +2062,7 @@
       <c r="H44" s="11"/>
       <c r="I44" s="11"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>35</v>
       </c>
@@ -2082,7 +2088,7 @@
       <c r="H45" s="11"/>
       <c r="I45" s="11"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>36</v>
       </c>
@@ -2108,7 +2114,7 @@
       <c r="H46" s="11"/>
       <c r="I46" s="11"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>37</v>
       </c>
@@ -2134,7 +2140,7 @@
       <c r="H47" s="11"/>
       <c r="I47" s="11"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>38</v>
       </c>
@@ -2160,7 +2166,7 @@
       <c r="H48" s="11"/>
       <c r="I48" s="11"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>39</v>
       </c>
@@ -2186,7 +2192,7 @@
       <c r="H49" s="11"/>
       <c r="I49" s="11"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>40</v>
       </c>
@@ -2212,7 +2218,7 @@
       <c r="H50" s="11"/>
       <c r="I50" s="11"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>41</v>
       </c>
@@ -2238,7 +2244,7 @@
       <c r="H51" s="11"/>
       <c r="I51" s="11"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>42</v>
       </c>
@@ -2264,7 +2270,7 @@
       <c r="H52" s="11"/>
       <c r="I52" s="11"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>43</v>
       </c>
@@ -2290,7 +2296,7 @@
       <c r="H53" s="11"/>
       <c r="I53" s="11"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>44</v>
       </c>
@@ -2316,7 +2322,7 @@
       <c r="H54" s="11"/>
       <c r="I54" s="11"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>45</v>
       </c>
@@ -2342,7 +2348,7 @@
       <c r="H55" s="11"/>
       <c r="I55" s="11"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>46</v>
       </c>
@@ -2368,7 +2374,7 @@
       <c r="H56" s="11"/>
       <c r="I56" s="11"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>47</v>
       </c>
@@ -2394,7 +2400,7 @@
       <c r="H57" s="11"/>
       <c r="I57" s="11"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>48</v>
       </c>
@@ -2420,7 +2426,7 @@
       <c r="H58" s="11"/>
       <c r="I58" s="11"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>49</v>
       </c>
@@ -2446,7 +2452,7 @@
       <c r="H59" s="11"/>
       <c r="I59" s="11"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>50</v>
       </c>
@@ -2472,7 +2478,7 @@
       <c r="H60" s="11"/>
       <c r="I60" s="11"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>51</v>
       </c>
@@ -2498,7 +2504,7 @@
       <c r="H61" s="11"/>
       <c r="I61" s="11"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>52</v>
       </c>
@@ -2524,7 +2530,7 @@
       <c r="H62" s="11"/>
       <c r="I62" s="11"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>53</v>
       </c>
@@ -2550,7 +2556,7 @@
       <c r="H63" s="11"/>
       <c r="I63" s="11"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>54</v>
       </c>
@@ -2576,7 +2582,7 @@
       <c r="H64" s="11"/>
       <c r="I64" s="11"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>55</v>
       </c>
@@ -2602,7 +2608,7 @@
       <c r="H65" s="11"/>
       <c r="I65" s="11"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>56</v>
       </c>
@@ -2628,7 +2634,7 @@
       <c r="H66" s="11"/>
       <c r="I66" s="11"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>57</v>
       </c>
@@ -2654,7 +2660,7 @@
       <c r="H67" s="11"/>
       <c r="I67" s="11"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>58</v>
       </c>
@@ -2680,7 +2686,7 @@
       <c r="H68" s="11"/>
       <c r="I68" s="11"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>59</v>
       </c>
@@ -2706,7 +2712,7 @@
       <c r="H69" s="11"/>
       <c r="I69" s="11"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>60</v>
       </c>
@@ -2732,7 +2738,7 @@
       <c r="H70" s="11"/>
       <c r="I70" s="11"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>61</v>
       </c>
@@ -2758,7 +2764,7 @@
       <c r="H71" s="11"/>
       <c r="I71" s="11"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>62</v>
       </c>
@@ -2784,7 +2790,7 @@
       <c r="H72" s="11"/>
       <c r="I72" s="11"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>63</v>
       </c>
@@ -2810,7 +2816,7 @@
       <c r="H73" s="11"/>
       <c r="I73" s="11"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>64</v>
       </c>
@@ -2836,7 +2842,7 @@
       <c r="H74" s="11"/>
       <c r="I74" s="11"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>65</v>
       </c>
@@ -2862,7 +2868,7 @@
       <c r="H75" s="11"/>
       <c r="I75" s="11"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>66</v>
       </c>
@@ -2888,7 +2894,7 @@
       <c r="H76" s="11"/>
       <c r="I76" s="11"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>67</v>
       </c>
@@ -2914,7 +2920,7 @@
       <c r="H77" s="11"/>
       <c r="I77" s="11"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>68</v>
       </c>
@@ -2940,7 +2946,7 @@
       <c r="H78" s="11"/>
       <c r="I78" s="11"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>69</v>
       </c>
@@ -2966,7 +2972,7 @@
       <c r="H79" s="11"/>
       <c r="I79" s="11"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>70</v>
       </c>
@@ -2992,7 +2998,7 @@
       <c r="H80" s="11"/>
       <c r="I80" s="11"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>71</v>
       </c>
@@ -3018,7 +3024,7 @@
       <c r="H81" s="11"/>
       <c r="I81" s="11"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>72</v>
       </c>
@@ -3044,7 +3050,7 @@
       <c r="H82" s="11"/>
       <c r="I82" s="11"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>73</v>
       </c>
@@ -3070,7 +3076,7 @@
       <c r="H83" s="11"/>
       <c r="I83" s="11"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>74</v>
       </c>
@@ -3096,7 +3102,7 @@
       <c r="H84" s="11"/>
       <c r="I84" s="11"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>75</v>
       </c>
@@ -3122,7 +3128,7 @@
       <c r="H85" s="11"/>
       <c r="I85" s="11"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>76</v>
       </c>
@@ -3148,7 +3154,7 @@
       <c r="H86" s="11"/>
       <c r="I86" s="11"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>77</v>
       </c>
@@ -3174,7 +3180,7 @@
       <c r="H87" s="11"/>
       <c r="I87" s="11"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>78</v>
       </c>
@@ -3200,7 +3206,7 @@
       <c r="H88" s="11"/>
       <c r="I88" s="11"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>79</v>
       </c>
@@ -3226,7 +3232,7 @@
       <c r="H89" s="11"/>
       <c r="I89" s="11"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>80</v>
       </c>
@@ -3252,7 +3258,7 @@
       <c r="H90" s="11"/>
       <c r="I90" s="11"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>81</v>
       </c>
@@ -3278,7 +3284,7 @@
       <c r="H91" s="11"/>
       <c r="I91" s="11"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>82</v>
       </c>
@@ -3304,7 +3310,7 @@
       <c r="H92" s="11"/>
       <c r="I92" s="11"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>83</v>
       </c>
@@ -3330,7 +3336,7 @@
       <c r="H93" s="11"/>
       <c r="I93" s="11"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>84</v>
       </c>
@@ -3356,7 +3362,7 @@
       <c r="H94" s="11"/>
       <c r="I94" s="11"/>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>85</v>
       </c>
@@ -3382,7 +3388,7 @@
       <c r="H95" s="11"/>
       <c r="I95" s="11"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>86</v>
       </c>
@@ -3408,7 +3414,7 @@
       <c r="H96" s="11"/>
       <c r="I96" s="11"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>87</v>
       </c>
@@ -3434,7 +3440,7 @@
       <c r="H97" s="11"/>
       <c r="I97" s="11"/>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>88</v>
       </c>
@@ -3460,7 +3466,7 @@
       <c r="H98" s="11"/>
       <c r="I98" s="11"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>89</v>
       </c>
@@ -3486,7 +3492,7 @@
       <c r="H99" s="11"/>
       <c r="I99" s="11"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>90</v>
       </c>
@@ -3512,7 +3518,7 @@
       <c r="H100" s="11"/>
       <c r="I100" s="11"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>91</v>
       </c>
@@ -3538,7 +3544,7 @@
       <c r="H101" s="11"/>
       <c r="I101" s="11"/>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>92</v>
       </c>
@@ -3564,7 +3570,7 @@
       <c r="H102" s="11"/>
       <c r="I102" s="11"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>93</v>
       </c>
@@ -3590,7 +3596,7 @@
       <c r="H103" s="11"/>
       <c r="I103" s="11"/>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>94</v>
       </c>
@@ -3616,7 +3622,7 @@
       <c r="H104" s="11"/>
       <c r="I104" s="11"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>95</v>
       </c>
@@ -3642,7 +3648,7 @@
       <c r="H105" s="11"/>
       <c r="I105" s="11"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>96</v>
       </c>
@@ -3668,7 +3674,7 @@
       <c r="H106" s="11"/>
       <c r="I106" s="11"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>97</v>
       </c>
@@ -3694,7 +3700,7 @@
       <c r="H107" s="11"/>
       <c r="I107" s="11"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>98</v>
       </c>
@@ -3720,7 +3726,7 @@
       <c r="H108" s="11"/>
       <c r="I108" s="11"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>99</v>
       </c>
@@ -3746,7 +3752,7 @@
       <c r="H109" s="11"/>
       <c r="I109" s="11"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>100</v>
       </c>
@@ -3772,7 +3778,7 @@
       <c r="H110" s="11"/>
       <c r="I110" s="11"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>101</v>
       </c>
@@ -3798,7 +3804,7 @@
       <c r="H111" s="11"/>
       <c r="I111" s="11"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>102</v>
       </c>
@@ -3824,7 +3830,7 @@
       <c r="H112" s="11"/>
       <c r="I112" s="11"/>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>103</v>
       </c>
@@ -3850,7 +3856,7 @@
       <c r="H113" s="11"/>
       <c r="I113" s="11"/>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>104</v>
       </c>
@@ -3876,7 +3882,7 @@
       <c r="H114" s="11"/>
       <c r="I114" s="11"/>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>105</v>
       </c>
@@ -3902,7 +3908,7 @@
       <c r="H115" s="11"/>
       <c r="I115" s="11"/>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>106</v>
       </c>
@@ -3928,7 +3934,7 @@
       <c r="H116" s="11"/>
       <c r="I116" s="11"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>107</v>
       </c>
@@ -3954,7 +3960,7 @@
       <c r="H117" s="11"/>
       <c r="I117" s="11"/>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>108</v>
       </c>
@@ -3980,7 +3986,7 @@
       <c r="H118" s="11"/>
       <c r="I118" s="11"/>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>109</v>
       </c>
@@ -4006,7 +4012,7 @@
       <c r="H119" s="11"/>
       <c r="I119" s="11"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>110</v>
       </c>
@@ -4032,7 +4038,7 @@
       <c r="H120" s="11"/>
       <c r="I120" s="11"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>111</v>
       </c>
@@ -4058,7 +4064,7 @@
       <c r="H121" s="11"/>
       <c r="I121" s="11"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>112</v>
       </c>
@@ -4084,7 +4090,7 @@
       <c r="H122" s="11"/>
       <c r="I122" s="11"/>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>113</v>
       </c>
@@ -4110,7 +4116,7 @@
       <c r="H123" s="11"/>
       <c r="I123" s="11"/>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>114</v>
       </c>
@@ -4136,7 +4142,7 @@
       <c r="H124" s="11"/>
       <c r="I124" s="11"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>115</v>
       </c>
@@ -4162,7 +4168,7 @@
       <c r="H125" s="11"/>
       <c r="I125" s="11"/>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>116</v>
       </c>
@@ -4188,7 +4194,7 @@
       <c r="H126" s="11"/>
       <c r="I126" s="11"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>117</v>
       </c>
@@ -4214,7 +4220,7 @@
       <c r="H127" s="11"/>
       <c r="I127" s="11"/>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>118</v>
       </c>
@@ -4240,7 +4246,7 @@
       <c r="H128" s="11"/>
       <c r="I128" s="11"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>119</v>
       </c>
@@ -4266,7 +4272,7 @@
       <c r="H129" s="11"/>
       <c r="I129" s="11"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>120</v>
       </c>
@@ -4292,7 +4298,7 @@
       <c r="H130" s="11"/>
       <c r="I130" s="11"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>121</v>
       </c>
@@ -4318,7 +4324,7 @@
       <c r="H131" s="11"/>
       <c r="I131" s="11"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>122</v>
       </c>
@@ -4344,7 +4350,7 @@
       <c r="H132" s="11"/>
       <c r="I132" s="11"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>123</v>
       </c>
@@ -4370,7 +4376,7 @@
       <c r="H133" s="11"/>
       <c r="I133" s="11"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>124</v>
       </c>
@@ -4396,7 +4402,7 @@
       <c r="H134" s="11"/>
       <c r="I134" s="11"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>125</v>
       </c>
@@ -4422,7 +4428,7 @@
       <c r="H135" s="11"/>
       <c r="I135" s="11"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>126</v>
       </c>
@@ -4448,7 +4454,7 @@
       <c r="H136" s="11"/>
       <c r="I136" s="11"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>127</v>
       </c>
@@ -4474,7 +4480,7 @@
       <c r="H137" s="11"/>
       <c r="I137" s="11"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>128</v>
       </c>
@@ -4500,7 +4506,7 @@
       <c r="H138" s="11"/>
       <c r="I138" s="11"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>129</v>
       </c>
@@ -4526,7 +4532,7 @@
       <c r="H139" s="11"/>
       <c r="I139" s="11"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>130</v>
       </c>
@@ -4552,7 +4558,7 @@
       <c r="H140" s="11"/>
       <c r="I140" s="11"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>131</v>
       </c>
@@ -4578,7 +4584,7 @@
       <c r="H141" s="11"/>
       <c r="I141" s="11"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>132</v>
       </c>
@@ -4604,7 +4610,7 @@
       <c r="H142" s="11"/>
       <c r="I142" s="11"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>133</v>
       </c>
@@ -4630,7 +4636,7 @@
       <c r="H143" s="11"/>
       <c r="I143" s="11"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>134</v>
       </c>
@@ -4656,7 +4662,7 @@
       <c r="H144" s="11"/>
       <c r="I144" s="11"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>135</v>
       </c>
@@ -4682,7 +4688,7 @@
       <c r="H145" s="11"/>
       <c r="I145" s="11"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>136</v>
       </c>
@@ -4708,7 +4714,7 @@
       <c r="H146" s="11"/>
       <c r="I146" s="11"/>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>137</v>
       </c>
@@ -4734,7 +4740,7 @@
       <c r="H147" s="11"/>
       <c r="I147" s="11"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>138</v>
       </c>
@@ -4760,7 +4766,7 @@
       <c r="H148" s="11"/>
       <c r="I148" s="11"/>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>139</v>
       </c>
@@ -4786,7 +4792,7 @@
       <c r="H149" s="11"/>
       <c r="I149" s="11"/>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>140</v>
       </c>
@@ -4812,7 +4818,7 @@
       <c r="H150" s="11"/>
       <c r="I150" s="11"/>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>141</v>
       </c>
@@ -4838,7 +4844,7 @@
       <c r="H151" s="11"/>
       <c r="I151" s="11"/>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>142</v>
       </c>
@@ -4864,7 +4870,7 @@
       <c r="H152" s="11"/>
       <c r="I152" s="11"/>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>143</v>
       </c>
@@ -4890,7 +4896,7 @@
       <c r="H153" s="11"/>
       <c r="I153" s="11"/>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>144</v>
       </c>
@@ -4916,7 +4922,7 @@
       <c r="H154" s="11"/>
       <c r="I154" s="11"/>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>145</v>
       </c>
@@ -4942,7 +4948,7 @@
       <c r="H155" s="11"/>
       <c r="I155" s="11"/>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>146</v>
       </c>
@@ -4968,7 +4974,7 @@
       <c r="H156" s="11"/>
       <c r="I156" s="11"/>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>147</v>
       </c>
@@ -4994,7 +5000,7 @@
       <c r="H157" s="11"/>
       <c r="I157" s="11"/>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>148</v>
       </c>
@@ -5020,7 +5026,7 @@
       <c r="H158" s="11"/>
       <c r="I158" s="11"/>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>149</v>
       </c>
@@ -5046,7 +5052,7 @@
       <c r="H159" s="11"/>
       <c r="I159" s="11"/>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>150</v>
       </c>
@@ -5072,7 +5078,7 @@
       <c r="H160" s="11"/>
       <c r="I160" s="11"/>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>151</v>
       </c>
@@ -5098,7 +5104,7 @@
       <c r="H161" s="11"/>
       <c r="I161" s="11"/>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>152</v>
       </c>
@@ -5124,7 +5130,7 @@
       <c r="H162" s="11"/>
       <c r="I162" s="11"/>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>153</v>
       </c>
@@ -5150,7 +5156,7 @@
       <c r="H163" s="11"/>
       <c r="I163" s="11"/>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>154</v>
       </c>
@@ -5176,7 +5182,7 @@
       <c r="H164" s="11"/>
       <c r="I164" s="11"/>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>155</v>
       </c>
@@ -5202,7 +5208,7 @@
       <c r="H165" s="11"/>
       <c r="I165" s="11"/>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>156</v>
       </c>
@@ -5228,7 +5234,7 @@
       <c r="H166" s="11"/>
       <c r="I166" s="11"/>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>157</v>
       </c>
@@ -5254,7 +5260,7 @@
       <c r="H167" s="11"/>
       <c r="I167" s="11"/>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>158</v>
       </c>
@@ -5280,7 +5286,7 @@
       <c r="H168" s="11"/>
       <c r="I168" s="11"/>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>159</v>
       </c>
@@ -5306,7 +5312,7 @@
       <c r="H169" s="11"/>
       <c r="I169" s="11"/>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>160</v>
       </c>
@@ -5332,7 +5338,7 @@
       <c r="H170" s="11"/>
       <c r="I170" s="11"/>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>161</v>
       </c>
@@ -5358,7 +5364,7 @@
       <c r="H171" s="11"/>
       <c r="I171" s="11"/>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>162</v>
       </c>
@@ -5384,7 +5390,7 @@
       <c r="H172" s="11"/>
       <c r="I172" s="11"/>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>163</v>
       </c>
@@ -5410,7 +5416,7 @@
       <c r="H173" s="11"/>
       <c r="I173" s="11"/>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>164</v>
       </c>
@@ -5436,7 +5442,7 @@
       <c r="H174" s="11"/>
       <c r="I174" s="11"/>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>165</v>
       </c>
@@ -5462,7 +5468,7 @@
       <c r="H175" s="11"/>
       <c r="I175" s="11"/>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>166</v>
       </c>
@@ -5488,7 +5494,7 @@
       <c r="H176" s="11"/>
       <c r="I176" s="11"/>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>167</v>
       </c>
@@ -5514,7 +5520,7 @@
       <c r="H177" s="11"/>
       <c r="I177" s="11"/>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>168</v>
       </c>
@@ -5540,7 +5546,7 @@
       <c r="H178" s="11"/>
       <c r="I178" s="11"/>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>169</v>
       </c>
@@ -5566,7 +5572,7 @@
       <c r="H179" s="11"/>
       <c r="I179" s="11"/>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>170</v>
       </c>
@@ -5592,7 +5598,7 @@
       <c r="H180" s="11"/>
       <c r="I180" s="11"/>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>171</v>
       </c>
@@ -5618,7 +5624,7 @@
       <c r="H181" s="11"/>
       <c r="I181" s="11"/>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>172</v>
       </c>
@@ -5644,7 +5650,7 @@
       <c r="H182" s="11"/>
       <c r="I182" s="11"/>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>173</v>
       </c>
@@ -5670,7 +5676,7 @@
       <c r="H183" s="11"/>
       <c r="I183" s="11"/>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>174</v>
       </c>
@@ -5696,7 +5702,7 @@
       <c r="H184" s="11"/>
       <c r="I184" s="11"/>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>175</v>
       </c>
@@ -5722,7 +5728,7 @@
       <c r="H185" s="11"/>
       <c r="I185" s="11"/>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>176</v>
       </c>
@@ -5748,7 +5754,7 @@
       <c r="H186" s="11"/>
       <c r="I186" s="11"/>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>177</v>
       </c>
@@ -5774,7 +5780,7 @@
       <c r="H187" s="11"/>
       <c r="I187" s="11"/>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>178</v>
       </c>
@@ -5800,7 +5806,7 @@
       <c r="H188" s="11"/>
       <c r="I188" s="11"/>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>179</v>
       </c>
@@ -5826,7 +5832,7 @@
       <c r="H189" s="11"/>
       <c r="I189" s="11"/>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>180</v>
       </c>
@@ -5852,7 +5858,7 @@
       <c r="H190" s="11"/>
       <c r="I190" s="11"/>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>181</v>
       </c>
@@ -5878,7 +5884,7 @@
       <c r="H191" s="11"/>
       <c r="I191" s="11"/>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>182</v>
       </c>
@@ -5904,7 +5910,7 @@
       <c r="H192" s="11"/>
       <c r="I192" s="11"/>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>183</v>
       </c>
@@ -5930,7 +5936,7 @@
       <c r="H193" s="11"/>
       <c r="I193" s="11"/>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>184</v>
       </c>
@@ -5956,7 +5962,7 @@
       <c r="H194" s="11"/>
       <c r="I194" s="11"/>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>185</v>
       </c>
@@ -5982,7 +5988,7 @@
       <c r="H195" s="11"/>
       <c r="I195" s="11"/>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>186</v>
       </c>
@@ -6008,7 +6014,7 @@
       <c r="H196" s="11"/>
       <c r="I196" s="11"/>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>187</v>
       </c>
@@ -6034,7 +6040,7 @@
       <c r="H197" s="11"/>
       <c r="I197" s="11"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>188</v>
       </c>
@@ -6060,7 +6066,7 @@
       <c r="H198" s="11"/>
       <c r="I198" s="11"/>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>189</v>
       </c>
@@ -6086,7 +6092,7 @@
       <c r="H199" s="11"/>
       <c r="I199" s="11"/>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>190</v>
       </c>
@@ -6112,7 +6118,7 @@
       <c r="H200" s="11"/>
       <c r="I200" s="11"/>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>191</v>
       </c>
@@ -6138,7 +6144,7 @@
       <c r="H201" s="11"/>
       <c r="I201" s="11"/>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>192</v>
       </c>
@@ -6164,7 +6170,7 @@
       <c r="H202" s="11"/>
       <c r="I202" s="11"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>193</v>
       </c>
@@ -6190,7 +6196,7 @@
       <c r="H203" s="11"/>
       <c r="I203" s="11"/>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>194</v>
       </c>
@@ -6216,7 +6222,7 @@
       <c r="H204" s="11"/>
       <c r="I204" s="11"/>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>195</v>
       </c>
@@ -6242,7 +6248,7 @@
       <c r="H205" s="11"/>
       <c r="I205" s="11"/>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>196</v>
       </c>
@@ -6268,7 +6274,7 @@
       <c r="H206" s="11"/>
       <c r="I206" s="11"/>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>197</v>
       </c>
@@ -6294,7 +6300,7 @@
       <c r="H207" s="11"/>
       <c r="I207" s="11"/>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>198</v>
       </c>
@@ -6320,7 +6326,7 @@
       <c r="H208" s="11"/>
       <c r="I208" s="11"/>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>199</v>
       </c>
@@ -6346,7 +6352,7 @@
       <c r="H209" s="11"/>
       <c r="I209" s="11"/>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>200</v>
       </c>
@@ -6372,7 +6378,7 @@
       <c r="H210" s="11"/>
       <c r="I210" s="11"/>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>201</v>
       </c>
@@ -6398,7 +6404,7 @@
       <c r="H211" s="11"/>
       <c r="I211" s="11"/>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>202</v>
       </c>
@@ -6424,7 +6430,7 @@
       <c r="H212" s="11"/>
       <c r="I212" s="11"/>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>203</v>
       </c>
@@ -6450,7 +6456,7 @@
       <c r="H213" s="11"/>
       <c r="I213" s="11"/>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>204</v>
       </c>
@@ -6476,7 +6482,7 @@
       <c r="H214" s="11"/>
       <c r="I214" s="11"/>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>205</v>
       </c>
@@ -6502,7 +6508,7 @@
       <c r="H215" s="11"/>
       <c r="I215" s="11"/>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>206</v>
       </c>
@@ -6528,7 +6534,7 @@
       <c r="H216" s="11"/>
       <c r="I216" s="11"/>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>207</v>
       </c>
@@ -6554,7 +6560,7 @@
       <c r="H217" s="11"/>
       <c r="I217" s="11"/>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>208</v>
       </c>
@@ -6580,7 +6586,7 @@
       <c r="H218" s="11"/>
       <c r="I218" s="11"/>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>209</v>
       </c>
@@ -6606,7 +6612,7 @@
       <c r="H219" s="11"/>
       <c r="I219" s="11"/>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>210</v>
       </c>
@@ -6632,7 +6638,7 @@
       <c r="H220" s="11"/>
       <c r="I220" s="11"/>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>211</v>
       </c>
@@ -6658,7 +6664,7 @@
       <c r="H221" s="11"/>
       <c r="I221" s="11"/>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>212</v>
       </c>
@@ -6684,7 +6690,7 @@
       <c r="H222" s="11"/>
       <c r="I222" s="11"/>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>213</v>
       </c>
@@ -6710,7 +6716,7 @@
       <c r="H223" s="11"/>
       <c r="I223" s="11"/>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>214</v>
       </c>
@@ -6736,7 +6742,7 @@
       <c r="H224" s="11"/>
       <c r="I224" s="11"/>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>215</v>
       </c>
@@ -6762,7 +6768,7 @@
       <c r="H225" s="11"/>
       <c r="I225" s="11"/>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>216</v>
       </c>
@@ -6788,7 +6794,7 @@
       <c r="H226" s="11"/>
       <c r="I226" s="11"/>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>217</v>
       </c>
@@ -6814,7 +6820,7 @@
       <c r="H227" s="11"/>
       <c r="I227" s="11"/>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>218</v>
       </c>
@@ -6840,7 +6846,7 @@
       <c r="H228" s="11"/>
       <c r="I228" s="11"/>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
         <v>219</v>
       </c>
@@ -6866,7 +6872,7 @@
       <c r="H229" s="11"/>
       <c r="I229" s="11"/>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>220</v>
       </c>
@@ -6892,7 +6898,7 @@
       <c r="H230" s="11"/>
       <c r="I230" s="11"/>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>221</v>
       </c>
@@ -6918,7 +6924,7 @@
       <c r="H231" s="11"/>
       <c r="I231" s="11"/>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>222</v>
       </c>
@@ -6944,7 +6950,7 @@
       <c r="H232" s="11"/>
       <c r="I232" s="11"/>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>223</v>
       </c>
@@ -6970,7 +6976,7 @@
       <c r="H233" s="11"/>
       <c r="I233" s="11"/>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>224</v>
       </c>
@@ -6996,7 +7002,7 @@
       <c r="H234" s="11"/>
       <c r="I234" s="11"/>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>225</v>
       </c>
@@ -7022,7 +7028,7 @@
       <c r="H235" s="11"/>
       <c r="I235" s="11"/>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>226</v>
       </c>
@@ -7048,7 +7054,7 @@
       <c r="H236" s="11"/>
       <c r="I236" s="11"/>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>227</v>
       </c>
@@ -7074,7 +7080,7 @@
       <c r="H237" s="11"/>
       <c r="I237" s="11"/>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>228</v>
       </c>
@@ -7100,7 +7106,7 @@
       <c r="H238" s="11"/>
       <c r="I238" s="11"/>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>229</v>
       </c>
@@ -7126,7 +7132,7 @@
       <c r="H239" s="11"/>
       <c r="I239" s="11"/>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>230</v>
       </c>
@@ -7152,7 +7158,7 @@
       <c r="H240" s="11"/>
       <c r="I240" s="11"/>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>231</v>
       </c>
@@ -7178,7 +7184,7 @@
       <c r="H241" s="11"/>
       <c r="I241" s="11"/>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
         <v>232</v>
       </c>
@@ -7204,7 +7210,7 @@
       <c r="H242" s="11"/>
       <c r="I242" s="11"/>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" s="1">
         <v>233</v>
       </c>
@@ -7230,7 +7236,7 @@
       <c r="H243" s="11"/>
       <c r="I243" s="11"/>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" s="1">
         <v>234</v>
       </c>
@@ -7256,7 +7262,7 @@
       <c r="H244" s="11"/>
       <c r="I244" s="11"/>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
         <v>235</v>
       </c>
@@ -7282,7 +7288,7 @@
       <c r="H245" s="11"/>
       <c r="I245" s="11"/>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
         <v>236</v>
       </c>
@@ -7308,7 +7314,7 @@
       <c r="H246" s="11"/>
       <c r="I246" s="11"/>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
         <v>237</v>
       </c>
@@ -7334,7 +7340,7 @@
       <c r="H247" s="11"/>
       <c r="I247" s="11"/>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
         <v>238</v>
       </c>
@@ -7360,7 +7366,7 @@
       <c r="H248" s="11"/>
       <c r="I248" s="11"/>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
         <v>239</v>
       </c>
@@ -7386,7 +7392,7 @@
       <c r="H249" s="11"/>
       <c r="I249" s="11"/>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
         <v>240</v>
       </c>
@@ -7412,7 +7418,7 @@
       <c r="H250" s="11"/>
       <c r="I250" s="11"/>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" s="1">
         <v>241</v>
       </c>
@@ -7438,7 +7444,7 @@
       <c r="H251" s="11"/>
       <c r="I251" s="11"/>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>242</v>
       </c>
@@ -7464,7 +7470,7 @@
       <c r="H252" s="11"/>
       <c r="I252" s="11"/>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>243</v>
       </c>
@@ -7490,7 +7496,7 @@
       <c r="H253" s="11"/>
       <c r="I253" s="11"/>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>244</v>
       </c>
@@ -7516,7 +7522,7 @@
       <c r="H254" s="11"/>
       <c r="I254" s="11"/>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>245</v>
       </c>
@@ -7542,7 +7548,7 @@
       <c r="H255" s="11"/>
       <c r="I255" s="11"/>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>246</v>
       </c>
@@ -7568,7 +7574,7 @@
       <c r="H256" s="11"/>
       <c r="I256" s="11"/>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>247</v>
       </c>
@@ -7594,7 +7600,7 @@
       <c r="H257" s="11"/>
       <c r="I257" s="11"/>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>248</v>
       </c>
@@ -7620,7 +7626,7 @@
       <c r="H258" s="11"/>
       <c r="I258" s="11"/>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>249</v>
       </c>
@@ -7646,7 +7652,7 @@
       <c r="H259" s="11"/>
       <c r="I259" s="11"/>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>250</v>
       </c>
@@ -7672,7 +7678,7 @@
       <c r="H260" s="11"/>
       <c r="I260" s="11"/>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>251</v>
       </c>
@@ -7698,7 +7704,7 @@
       <c r="H261" s="11"/>
       <c r="I261" s="11"/>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>252</v>
       </c>
@@ -7724,7 +7730,7 @@
       <c r="H262" s="11"/>
       <c r="I262" s="11"/>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>253</v>
       </c>
@@ -7750,7 +7756,7 @@
       <c r="H263" s="11"/>
       <c r="I263" s="11"/>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
         <v>254</v>
       </c>
@@ -7776,7 +7782,7 @@
       <c r="H264" s="11"/>
       <c r="I264" s="11"/>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
         <v>255</v>
       </c>
@@ -7802,7 +7808,7 @@
       <c r="H265" s="11"/>
       <c r="I265" s="11"/>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266" s="1">
         <v>256</v>
       </c>
@@ -7828,7 +7834,7 @@
       <c r="H266" s="11"/>
       <c r="I266" s="11"/>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A267" s="1">
         <v>257</v>
       </c>
@@ -7854,7 +7860,7 @@
       <c r="H267" s="11"/>
       <c r="I267" s="11"/>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268" s="1">
         <v>258</v>
       </c>
@@ -7880,7 +7886,7 @@
       <c r="H268" s="11"/>
       <c r="I268" s="11"/>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
         <v>259</v>
       </c>
@@ -7906,7 +7912,7 @@
       <c r="H269" s="11"/>
       <c r="I269" s="11"/>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
         <v>260</v>
       </c>
@@ -7932,7 +7938,7 @@
       <c r="H270" s="11"/>
       <c r="I270" s="11"/>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
         <v>261</v>
       </c>
@@ -7958,7 +7964,7 @@
       <c r="H271" s="11"/>
       <c r="I271" s="11"/>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
         <v>262</v>
       </c>
@@ -7984,7 +7990,7 @@
       <c r="H272" s="11"/>
       <c r="I272" s="11"/>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A273" s="1">
         <v>263</v>
       </c>
@@ -8010,7 +8016,7 @@
       <c r="H273" s="11"/>
       <c r="I273" s="11"/>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" s="1">
         <v>264</v>
       </c>
@@ -8036,7 +8042,7 @@
       <c r="H274" s="11"/>
       <c r="I274" s="11"/>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" s="1">
         <v>265</v>
       </c>
@@ -8062,7 +8068,7 @@
       <c r="H275" s="11"/>
       <c r="I275" s="11"/>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" s="1">
         <v>266</v>
       </c>
@@ -8088,7 +8094,7 @@
       <c r="H276" s="11"/>
       <c r="I276" s="11"/>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" s="1">
         <v>267</v>
       </c>
@@ -8114,7 +8120,7 @@
       <c r="H277" s="11"/>
       <c r="I277" s="11"/>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" s="1">
         <v>268</v>
       </c>
@@ -8140,7 +8146,7 @@
       <c r="H278" s="11"/>
       <c r="I278" s="11"/>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
         <v>269</v>
       </c>
@@ -8166,7 +8172,7 @@
       <c r="H279" s="11"/>
       <c r="I279" s="11"/>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" s="1">
         <v>270</v>
       </c>
@@ -8192,7 +8198,7 @@
       <c r="H280" s="11"/>
       <c r="I280" s="11"/>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" s="1">
         <v>271</v>
       </c>
@@ -8218,7 +8224,7 @@
       <c r="H281" s="11"/>
       <c r="I281" s="11"/>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A282" s="1">
         <v>272</v>
       </c>
@@ -8244,7 +8250,7 @@
       <c r="H282" s="11"/>
       <c r="I282" s="11"/>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A283" s="1">
         <v>273</v>
       </c>
@@ -8270,7 +8276,7 @@
       <c r="H283" s="11"/>
       <c r="I283" s="11"/>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284" s="1">
         <v>274</v>
       </c>
@@ -8296,7 +8302,7 @@
       <c r="H284" s="11"/>
       <c r="I284" s="11"/>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" s="1">
         <v>275</v>
       </c>
@@ -8322,7 +8328,7 @@
       <c r="H285" s="11"/>
       <c r="I285" s="11"/>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" s="1">
         <v>276</v>
       </c>
@@ -8355,7 +8361,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
         <v>277</v>
       </c>
@@ -8388,7 +8394,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
         <v>278</v>
       </c>
@@ -8421,7 +8427,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" s="1">
         <v>279</v>
       </c>
@@ -8454,7 +8460,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" s="1">
         <v>280</v>
       </c>
@@ -8487,7 +8493,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A291" s="1">
         <v>281</v>
       </c>
@@ -8520,7 +8526,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A292" s="1">
         <v>282</v>
       </c>
@@ -8553,7 +8559,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A293" s="1">
         <v>283</v>
       </c>
@@ -8586,7 +8592,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>284</v>
       </c>
@@ -8619,7 +8625,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>285</v>
       </c>
@@ -8652,7 +8658,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>286</v>
       </c>
@@ -8685,7 +8691,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>287</v>
       </c>
@@ -8718,7 +8724,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>288</v>
       </c>
@@ -8751,7 +8757,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>289</v>
       </c>
@@ -8784,7 +8790,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>290</v>
       </c>
@@ -8817,7 +8823,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>291</v>
       </c>
@@ -8850,7 +8856,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>292</v>
       </c>
@@ -8883,7 +8889,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="303" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>293</v>
       </c>
@@ -8916,7 +8922,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="304" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>294</v>
       </c>
@@ -8949,7 +8955,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>295</v>
       </c>
@@ -8982,7 +8988,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>296</v>
       </c>
@@ -9015,7 +9021,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>297</v>
       </c>
@@ -9048,7 +9054,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>298</v>
       </c>
@@ -9081,7 +9087,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>298</v>
       </c>
@@ -9114,7 +9120,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A310" s="1">
         <v>299</v>
       </c>
@@ -9147,7 +9153,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A311" s="1">
         <v>300</v>
       </c>
@@ -9180,7 +9186,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A312" s="1">
         <v>301</v>
       </c>
@@ -9213,7 +9219,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A313" s="1">
         <v>302</v>
       </c>
@@ -9246,14 +9252,14 @@
         <v>76</v>
       </c>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
         <v>303</v>
       </c>
       <c r="B314" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C314" s="16" t="str">
+      <c r="C314" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
@@ -9279,14 +9285,14 @@
         <v>76</v>
       </c>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A315" s="1">
         <v>304</v>
       </c>
       <c r="B315" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C315" s="16" t="str">
+      <c r="C315" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
@@ -9312,52 +9318,82 @@
         <v>76</v>
       </c>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A316" s="1"/>
-    </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A316" s="1">
+        <v>305</v>
+      </c>
+      <c r="B316" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C316" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CEM</v>
+      </c>
+      <c r="D316" s="14">
+        <v>70</v>
+      </c>
+      <c r="E316" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F316" s="15">
+        <v>46158.34375</v>
+      </c>
+      <c r="G316" s="15">
+        <v>46158.885416666664</v>
+      </c>
+      <c r="H316" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I316" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="J316" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="317" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A317" s="1"/>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A318" s="1"/>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A319" s="1"/>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A320" s="1"/>
     </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A321" s="1"/>
     </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A322" s="1"/>
     </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A323" s="1"/>
     </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A324" s="1"/>
     </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A325" s="1"/>
     </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A326" s="1"/>
     </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A327" s="1"/>
     </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A328" s="1"/>
     </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A329" s="1"/>
     </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A330" s="1"/>
     </row>
-    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A331" s="1"/>
     </row>
   </sheetData>
@@ -9379,13 +9415,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{797F1036-D41E-43A4-9E6E-CBBB62F3CD31}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="13.28515625" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9399,7 +9435,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -9413,7 +9449,7 @@
         <v>234.67</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -9427,7 +9463,7 @@
         <v>161.15</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -9441,7 +9477,7 @@
         <v>157.61000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -9455,7 +9491,7 @@
         <v>347.95</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -9469,7 +9505,7 @@
         <v>393.57</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -9483,7 +9519,7 @@
         <v>19.87</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -9497,7 +9533,7 @@
         <v>19.57</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>61</v>
       </c>
@@ -9511,7 +9547,7 @@
         <v>19.86</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -9525,7 +9561,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -9550,15 +9586,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56220E0F-EC16-4A8C-9E04-C7F8849C4B4D}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9575,7 +9611,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -9592,7 +9628,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -9609,7 +9645,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -9626,7 +9662,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -9643,7 +9679,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -9660,7 +9696,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -9677,7 +9713,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -9705,14 +9741,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83DAFC4B-C207-418A-8501-0E1EC9E673B7}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9723,7 +9759,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -9734,7 +9770,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -9745,7 +9781,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -9756,7 +9792,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>61</v>
       </c>
@@ -9767,7 +9803,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -9778,7 +9814,7 @@
         <v>46631</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -9789,7 +9825,7 @@
         <v>48579</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -9800,7 +9836,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -9811,7 +9847,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -9822,7 +9858,7 @@
         <v>48579</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -10045,15 +10081,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
@@ -10065,6 +10092,15 @@
     </SharedWithUsers>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10087,26 +10123,26 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="973" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BD5B27A-8CB1-4490-A8F0-55DCF92600DF}"/>
+  <xr:revisionPtr revIDLastSave="978" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{193B4E4B-F4EC-4E4E-9E2E-40D1F1B1CF52}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1875" yWindow="2565" windowWidth="17280" windowHeight="8880" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="88">
   <si>
     <t>ID</t>
   </si>
@@ -742,8 +742,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J316" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J316" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J317" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J317" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1125,28 +1125,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
   <dimension ref="A9:J331"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="41.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="151.33203125" customWidth="1"/>
-    <col min="10" max="10" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" customWidth="1"/>
-    <col min="12" max="12" width="33.33203125" customWidth="1"/>
+    <col min="6" max="7" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="151.28515625" customWidth="1"/>
+    <col min="10" max="10" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="33.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>306</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1178,7 +1178,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -1204,7 +1204,7 @@
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -1230,7 +1230,7 @@
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>3</v>
       </c>
@@ -1256,7 +1256,7 @@
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>4</v>
       </c>
@@ -1282,7 +1282,7 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>5</v>
       </c>
@@ -1308,7 +1308,7 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>6</v>
       </c>
@@ -1334,7 +1334,7 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>7</v>
       </c>
@@ -1360,7 +1360,7 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>8</v>
       </c>
@@ -1386,7 +1386,7 @@
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>9</v>
       </c>
@@ -1412,7 +1412,7 @@
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>10</v>
       </c>
@@ -1438,7 +1438,7 @@
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>11</v>
       </c>
@@ -1464,7 +1464,7 @@
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>12</v>
       </c>
@@ -1490,7 +1490,7 @@
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>13</v>
       </c>
@@ -1516,7 +1516,7 @@
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>14</v>
       </c>
@@ -1542,7 +1542,7 @@
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>15</v>
       </c>
@@ -1568,7 +1568,7 @@
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>16</v>
       </c>
@@ -1594,7 +1594,7 @@
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>17</v>
       </c>
@@ -1620,7 +1620,7 @@
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>18</v>
       </c>
@@ -1646,7 +1646,7 @@
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>19</v>
       </c>
@@ -1672,7 +1672,7 @@
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>20</v>
       </c>
@@ -1698,7 +1698,7 @@
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>21</v>
       </c>
@@ -1724,7 +1724,7 @@
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>22</v>
       </c>
@@ -1750,7 +1750,7 @@
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>23</v>
       </c>
@@ -1776,7 +1776,7 @@
       <c r="H33" s="11"/>
       <c r="I33" s="11"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24</v>
       </c>
@@ -1802,7 +1802,7 @@
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>25</v>
       </c>
@@ -1828,7 +1828,7 @@
       <c r="H35" s="11"/>
       <c r="I35" s="11"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>26</v>
       </c>
@@ -1854,7 +1854,7 @@
       <c r="H36" s="11"/>
       <c r="I36" s="11"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>27</v>
       </c>
@@ -1880,7 +1880,7 @@
       <c r="H37" s="11"/>
       <c r="I37" s="11"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>28</v>
       </c>
@@ -1906,7 +1906,7 @@
       <c r="H38" s="11"/>
       <c r="I38" s="11"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>29</v>
       </c>
@@ -1932,7 +1932,7 @@
       <c r="H39" s="11"/>
       <c r="I39" s="11"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>30</v>
       </c>
@@ -1958,7 +1958,7 @@
       <c r="H40" s="11"/>
       <c r="I40" s="11"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>31</v>
       </c>
@@ -1984,7 +1984,7 @@
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>32</v>
       </c>
@@ -2010,7 +2010,7 @@
       <c r="H42" s="11"/>
       <c r="I42" s="11"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>33</v>
       </c>
@@ -2036,7 +2036,7 @@
       <c r="H43" s="11"/>
       <c r="I43" s="11"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>34</v>
       </c>
@@ -2062,7 +2062,7 @@
       <c r="H44" s="11"/>
       <c r="I44" s="11"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>35</v>
       </c>
@@ -2088,7 +2088,7 @@
       <c r="H45" s="11"/>
       <c r="I45" s="11"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>36</v>
       </c>
@@ -2114,7 +2114,7 @@
       <c r="H46" s="11"/>
       <c r="I46" s="11"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>37</v>
       </c>
@@ -2140,7 +2140,7 @@
       <c r="H47" s="11"/>
       <c r="I47" s="11"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>38</v>
       </c>
@@ -2166,7 +2166,7 @@
       <c r="H48" s="11"/>
       <c r="I48" s="11"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>39</v>
       </c>
@@ -2192,7 +2192,7 @@
       <c r="H49" s="11"/>
       <c r="I49" s="11"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>40</v>
       </c>
@@ -2218,7 +2218,7 @@
       <c r="H50" s="11"/>
       <c r="I50" s="11"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>41</v>
       </c>
@@ -2244,7 +2244,7 @@
       <c r="H51" s="11"/>
       <c r="I51" s="11"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>42</v>
       </c>
@@ -2270,7 +2270,7 @@
       <c r="H52" s="11"/>
       <c r="I52" s="11"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>43</v>
       </c>
@@ -2296,7 +2296,7 @@
       <c r="H53" s="11"/>
       <c r="I53" s="11"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>44</v>
       </c>
@@ -2322,7 +2322,7 @@
       <c r="H54" s="11"/>
       <c r="I54" s="11"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>45</v>
       </c>
@@ -2348,7 +2348,7 @@
       <c r="H55" s="11"/>
       <c r="I55" s="11"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>46</v>
       </c>
@@ -2374,7 +2374,7 @@
       <c r="H56" s="11"/>
       <c r="I56" s="11"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>47</v>
       </c>
@@ -2400,7 +2400,7 @@
       <c r="H57" s="11"/>
       <c r="I57" s="11"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>48</v>
       </c>
@@ -2426,7 +2426,7 @@
       <c r="H58" s="11"/>
       <c r="I58" s="11"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>49</v>
       </c>
@@ -2452,7 +2452,7 @@
       <c r="H59" s="11"/>
       <c r="I59" s="11"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>50</v>
       </c>
@@ -2478,7 +2478,7 @@
       <c r="H60" s="11"/>
       <c r="I60" s="11"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>51</v>
       </c>
@@ -2504,7 +2504,7 @@
       <c r="H61" s="11"/>
       <c r="I61" s="11"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>52</v>
       </c>
@@ -2530,7 +2530,7 @@
       <c r="H62" s="11"/>
       <c r="I62" s="11"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>53</v>
       </c>
@@ -2556,7 +2556,7 @@
       <c r="H63" s="11"/>
       <c r="I63" s="11"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>54</v>
       </c>
@@ -2582,7 +2582,7 @@
       <c r="H64" s="11"/>
       <c r="I64" s="11"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>55</v>
       </c>
@@ -2608,7 +2608,7 @@
       <c r="H65" s="11"/>
       <c r="I65" s="11"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>56</v>
       </c>
@@ -2634,7 +2634,7 @@
       <c r="H66" s="11"/>
       <c r="I66" s="11"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>57</v>
       </c>
@@ -2660,7 +2660,7 @@
       <c r="H67" s="11"/>
       <c r="I67" s="11"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>58</v>
       </c>
@@ -2686,7 +2686,7 @@
       <c r="H68" s="11"/>
       <c r="I68" s="11"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>59</v>
       </c>
@@ -2712,7 +2712,7 @@
       <c r="H69" s="11"/>
       <c r="I69" s="11"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>60</v>
       </c>
@@ -2738,7 +2738,7 @@
       <c r="H70" s="11"/>
       <c r="I70" s="11"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>61</v>
       </c>
@@ -2764,7 +2764,7 @@
       <c r="H71" s="11"/>
       <c r="I71" s="11"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>62</v>
       </c>
@@ -2790,7 +2790,7 @@
       <c r="H72" s="11"/>
       <c r="I72" s="11"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>63</v>
       </c>
@@ -2816,7 +2816,7 @@
       <c r="H73" s="11"/>
       <c r="I73" s="11"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>64</v>
       </c>
@@ -2842,7 +2842,7 @@
       <c r="H74" s="11"/>
       <c r="I74" s="11"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>65</v>
       </c>
@@ -2868,7 +2868,7 @@
       <c r="H75" s="11"/>
       <c r="I75" s="11"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>66</v>
       </c>
@@ -2894,7 +2894,7 @@
       <c r="H76" s="11"/>
       <c r="I76" s="11"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>67</v>
       </c>
@@ -2920,7 +2920,7 @@
       <c r="H77" s="11"/>
       <c r="I77" s="11"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>68</v>
       </c>
@@ -2946,7 +2946,7 @@
       <c r="H78" s="11"/>
       <c r="I78" s="11"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>69</v>
       </c>
@@ -2972,7 +2972,7 @@
       <c r="H79" s="11"/>
       <c r="I79" s="11"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>70</v>
       </c>
@@ -2998,7 +2998,7 @@
       <c r="H80" s="11"/>
       <c r="I80" s="11"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>71</v>
       </c>
@@ -3024,7 +3024,7 @@
       <c r="H81" s="11"/>
       <c r="I81" s="11"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>72</v>
       </c>
@@ -3050,7 +3050,7 @@
       <c r="H82" s="11"/>
       <c r="I82" s="11"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>73</v>
       </c>
@@ -3076,7 +3076,7 @@
       <c r="H83" s="11"/>
       <c r="I83" s="11"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>74</v>
       </c>
@@ -3102,7 +3102,7 @@
       <c r="H84" s="11"/>
       <c r="I84" s="11"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>75</v>
       </c>
@@ -3128,7 +3128,7 @@
       <c r="H85" s="11"/>
       <c r="I85" s="11"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>76</v>
       </c>
@@ -3154,7 +3154,7 @@
       <c r="H86" s="11"/>
       <c r="I86" s="11"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>77</v>
       </c>
@@ -3180,7 +3180,7 @@
       <c r="H87" s="11"/>
       <c r="I87" s="11"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>78</v>
       </c>
@@ -3206,7 +3206,7 @@
       <c r="H88" s="11"/>
       <c r="I88" s="11"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>79</v>
       </c>
@@ -3232,7 +3232,7 @@
       <c r="H89" s="11"/>
       <c r="I89" s="11"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>80</v>
       </c>
@@ -3258,7 +3258,7 @@
       <c r="H90" s="11"/>
       <c r="I90" s="11"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>81</v>
       </c>
@@ -3284,7 +3284,7 @@
       <c r="H91" s="11"/>
       <c r="I91" s="11"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>82</v>
       </c>
@@ -3310,7 +3310,7 @@
       <c r="H92" s="11"/>
       <c r="I92" s="11"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>83</v>
       </c>
@@ -3336,7 +3336,7 @@
       <c r="H93" s="11"/>
       <c r="I93" s="11"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>84</v>
       </c>
@@ -3362,7 +3362,7 @@
       <c r="H94" s="11"/>
       <c r="I94" s="11"/>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>85</v>
       </c>
@@ -3388,7 +3388,7 @@
       <c r="H95" s="11"/>
       <c r="I95" s="11"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>86</v>
       </c>
@@ -3414,7 +3414,7 @@
       <c r="H96" s="11"/>
       <c r="I96" s="11"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>87</v>
       </c>
@@ -3440,7 +3440,7 @@
       <c r="H97" s="11"/>
       <c r="I97" s="11"/>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>88</v>
       </c>
@@ -3466,7 +3466,7 @@
       <c r="H98" s="11"/>
       <c r="I98" s="11"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>89</v>
       </c>
@@ -3492,7 +3492,7 @@
       <c r="H99" s="11"/>
       <c r="I99" s="11"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>90</v>
       </c>
@@ -3518,7 +3518,7 @@
       <c r="H100" s="11"/>
       <c r="I100" s="11"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>91</v>
       </c>
@@ -3544,7 +3544,7 @@
       <c r="H101" s="11"/>
       <c r="I101" s="11"/>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>92</v>
       </c>
@@ -3570,7 +3570,7 @@
       <c r="H102" s="11"/>
       <c r="I102" s="11"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>93</v>
       </c>
@@ -3596,7 +3596,7 @@
       <c r="H103" s="11"/>
       <c r="I103" s="11"/>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>94</v>
       </c>
@@ -3622,7 +3622,7 @@
       <c r="H104" s="11"/>
       <c r="I104" s="11"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>95</v>
       </c>
@@ -3648,7 +3648,7 @@
       <c r="H105" s="11"/>
       <c r="I105" s="11"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>96</v>
       </c>
@@ -3674,7 +3674,7 @@
       <c r="H106" s="11"/>
       <c r="I106" s="11"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>97</v>
       </c>
@@ -3700,7 +3700,7 @@
       <c r="H107" s="11"/>
       <c r="I107" s="11"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>98</v>
       </c>
@@ -3726,7 +3726,7 @@
       <c r="H108" s="11"/>
       <c r="I108" s="11"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>99</v>
       </c>
@@ -3752,7 +3752,7 @@
       <c r="H109" s="11"/>
       <c r="I109" s="11"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>100</v>
       </c>
@@ -3778,7 +3778,7 @@
       <c r="H110" s="11"/>
       <c r="I110" s="11"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>101</v>
       </c>
@@ -3804,7 +3804,7 @@
       <c r="H111" s="11"/>
       <c r="I111" s="11"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>102</v>
       </c>
@@ -3830,7 +3830,7 @@
       <c r="H112" s="11"/>
       <c r="I112" s="11"/>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>103</v>
       </c>
@@ -3856,7 +3856,7 @@
       <c r="H113" s="11"/>
       <c r="I113" s="11"/>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>104</v>
       </c>
@@ -3882,7 +3882,7 @@
       <c r="H114" s="11"/>
       <c r="I114" s="11"/>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>105</v>
       </c>
@@ -3908,7 +3908,7 @@
       <c r="H115" s="11"/>
       <c r="I115" s="11"/>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>106</v>
       </c>
@@ -3934,7 +3934,7 @@
       <c r="H116" s="11"/>
       <c r="I116" s="11"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>107</v>
       </c>
@@ -3960,7 +3960,7 @@
       <c r="H117" s="11"/>
       <c r="I117" s="11"/>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>108</v>
       </c>
@@ -3986,7 +3986,7 @@
       <c r="H118" s="11"/>
       <c r="I118" s="11"/>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>109</v>
       </c>
@@ -4012,7 +4012,7 @@
       <c r="H119" s="11"/>
       <c r="I119" s="11"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>110</v>
       </c>
@@ -4038,7 +4038,7 @@
       <c r="H120" s="11"/>
       <c r="I120" s="11"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>111</v>
       </c>
@@ -4064,7 +4064,7 @@
       <c r="H121" s="11"/>
       <c r="I121" s="11"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>112</v>
       </c>
@@ -4090,7 +4090,7 @@
       <c r="H122" s="11"/>
       <c r="I122" s="11"/>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>113</v>
       </c>
@@ -4116,7 +4116,7 @@
       <c r="H123" s="11"/>
       <c r="I123" s="11"/>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>114</v>
       </c>
@@ -4142,7 +4142,7 @@
       <c r="H124" s="11"/>
       <c r="I124" s="11"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>115</v>
       </c>
@@ -4168,7 +4168,7 @@
       <c r="H125" s="11"/>
       <c r="I125" s="11"/>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>116</v>
       </c>
@@ -4194,7 +4194,7 @@
       <c r="H126" s="11"/>
       <c r="I126" s="11"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>117</v>
       </c>
@@ -4220,7 +4220,7 @@
       <c r="H127" s="11"/>
       <c r="I127" s="11"/>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>118</v>
       </c>
@@ -4246,7 +4246,7 @@
       <c r="H128" s="11"/>
       <c r="I128" s="11"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>119</v>
       </c>
@@ -4272,7 +4272,7 @@
       <c r="H129" s="11"/>
       <c r="I129" s="11"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>120</v>
       </c>
@@ -4298,7 +4298,7 @@
       <c r="H130" s="11"/>
       <c r="I130" s="11"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>121</v>
       </c>
@@ -4324,7 +4324,7 @@
       <c r="H131" s="11"/>
       <c r="I131" s="11"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>122</v>
       </c>
@@ -4350,7 +4350,7 @@
       <c r="H132" s="11"/>
       <c r="I132" s="11"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>123</v>
       </c>
@@ -4376,7 +4376,7 @@
       <c r="H133" s="11"/>
       <c r="I133" s="11"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>124</v>
       </c>
@@ -4402,7 +4402,7 @@
       <c r="H134" s="11"/>
       <c r="I134" s="11"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>125</v>
       </c>
@@ -4428,7 +4428,7 @@
       <c r="H135" s="11"/>
       <c r="I135" s="11"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>126</v>
       </c>
@@ -4454,7 +4454,7 @@
       <c r="H136" s="11"/>
       <c r="I136" s="11"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>127</v>
       </c>
@@ -4480,7 +4480,7 @@
       <c r="H137" s="11"/>
       <c r="I137" s="11"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>128</v>
       </c>
@@ -4506,7 +4506,7 @@
       <c r="H138" s="11"/>
       <c r="I138" s="11"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>129</v>
       </c>
@@ -4532,7 +4532,7 @@
       <c r="H139" s="11"/>
       <c r="I139" s="11"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>130</v>
       </c>
@@ -4558,7 +4558,7 @@
       <c r="H140" s="11"/>
       <c r="I140" s="11"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>131</v>
       </c>
@@ -4584,7 +4584,7 @@
       <c r="H141" s="11"/>
       <c r="I141" s="11"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>132</v>
       </c>
@@ -4610,7 +4610,7 @@
       <c r="H142" s="11"/>
       <c r="I142" s="11"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>133</v>
       </c>
@@ -4636,7 +4636,7 @@
       <c r="H143" s="11"/>
       <c r="I143" s="11"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>134</v>
       </c>
@@ -4662,7 +4662,7 @@
       <c r="H144" s="11"/>
       <c r="I144" s="11"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>135</v>
       </c>
@@ -4688,7 +4688,7 @@
       <c r="H145" s="11"/>
       <c r="I145" s="11"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>136</v>
       </c>
@@ -4714,7 +4714,7 @@
       <c r="H146" s="11"/>
       <c r="I146" s="11"/>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>137</v>
       </c>
@@ -4740,7 +4740,7 @@
       <c r="H147" s="11"/>
       <c r="I147" s="11"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>138</v>
       </c>
@@ -4766,7 +4766,7 @@
       <c r="H148" s="11"/>
       <c r="I148" s="11"/>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>139</v>
       </c>
@@ -4792,7 +4792,7 @@
       <c r="H149" s="11"/>
       <c r="I149" s="11"/>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>140</v>
       </c>
@@ -4818,7 +4818,7 @@
       <c r="H150" s="11"/>
       <c r="I150" s="11"/>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>141</v>
       </c>
@@ -4844,7 +4844,7 @@
       <c r="H151" s="11"/>
       <c r="I151" s="11"/>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>142</v>
       </c>
@@ -4870,7 +4870,7 @@
       <c r="H152" s="11"/>
       <c r="I152" s="11"/>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>143</v>
       </c>
@@ -4896,7 +4896,7 @@
       <c r="H153" s="11"/>
       <c r="I153" s="11"/>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>144</v>
       </c>
@@ -4922,7 +4922,7 @@
       <c r="H154" s="11"/>
       <c r="I154" s="11"/>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>145</v>
       </c>
@@ -4948,7 +4948,7 @@
       <c r="H155" s="11"/>
       <c r="I155" s="11"/>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>146</v>
       </c>
@@ -4974,7 +4974,7 @@
       <c r="H156" s="11"/>
       <c r="I156" s="11"/>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>147</v>
       </c>
@@ -5000,7 +5000,7 @@
       <c r="H157" s="11"/>
       <c r="I157" s="11"/>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>148</v>
       </c>
@@ -5026,7 +5026,7 @@
       <c r="H158" s="11"/>
       <c r="I158" s="11"/>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>149</v>
       </c>
@@ -5052,7 +5052,7 @@
       <c r="H159" s="11"/>
       <c r="I159" s="11"/>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>150</v>
       </c>
@@ -5078,7 +5078,7 @@
       <c r="H160" s="11"/>
       <c r="I160" s="11"/>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>151</v>
       </c>
@@ -5104,7 +5104,7 @@
       <c r="H161" s="11"/>
       <c r="I161" s="11"/>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>152</v>
       </c>
@@ -5130,7 +5130,7 @@
       <c r="H162" s="11"/>
       <c r="I162" s="11"/>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>153</v>
       </c>
@@ -5156,7 +5156,7 @@
       <c r="H163" s="11"/>
       <c r="I163" s="11"/>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>154</v>
       </c>
@@ -5182,7 +5182,7 @@
       <c r="H164" s="11"/>
       <c r="I164" s="11"/>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>155</v>
       </c>
@@ -5208,7 +5208,7 @@
       <c r="H165" s="11"/>
       <c r="I165" s="11"/>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>156</v>
       </c>
@@ -5234,7 +5234,7 @@
       <c r="H166" s="11"/>
       <c r="I166" s="11"/>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>157</v>
       </c>
@@ -5260,7 +5260,7 @@
       <c r="H167" s="11"/>
       <c r="I167" s="11"/>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>158</v>
       </c>
@@ -5286,7 +5286,7 @@
       <c r="H168" s="11"/>
       <c r="I168" s="11"/>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>159</v>
       </c>
@@ -5312,7 +5312,7 @@
       <c r="H169" s="11"/>
       <c r="I169" s="11"/>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>160</v>
       </c>
@@ -5338,7 +5338,7 @@
       <c r="H170" s="11"/>
       <c r="I170" s="11"/>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>161</v>
       </c>
@@ -5364,7 +5364,7 @@
       <c r="H171" s="11"/>
       <c r="I171" s="11"/>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>162</v>
       </c>
@@ -5390,7 +5390,7 @@
       <c r="H172" s="11"/>
       <c r="I172" s="11"/>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>163</v>
       </c>
@@ -5416,7 +5416,7 @@
       <c r="H173" s="11"/>
       <c r="I173" s="11"/>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>164</v>
       </c>
@@ -5442,7 +5442,7 @@
       <c r="H174" s="11"/>
       <c r="I174" s="11"/>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>165</v>
       </c>
@@ -5468,7 +5468,7 @@
       <c r="H175" s="11"/>
       <c r="I175" s="11"/>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>166</v>
       </c>
@@ -5494,7 +5494,7 @@
       <c r="H176" s="11"/>
       <c r="I176" s="11"/>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>167</v>
       </c>
@@ -5520,7 +5520,7 @@
       <c r="H177" s="11"/>
       <c r="I177" s="11"/>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>168</v>
       </c>
@@ -5546,7 +5546,7 @@
       <c r="H178" s="11"/>
       <c r="I178" s="11"/>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>169</v>
       </c>
@@ -5572,7 +5572,7 @@
       <c r="H179" s="11"/>
       <c r="I179" s="11"/>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>170</v>
       </c>
@@ -5598,7 +5598,7 @@
       <c r="H180" s="11"/>
       <c r="I180" s="11"/>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>171</v>
       </c>
@@ -5624,7 +5624,7 @@
       <c r="H181" s="11"/>
       <c r="I181" s="11"/>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>172</v>
       </c>
@@ -5650,7 +5650,7 @@
       <c r="H182" s="11"/>
       <c r="I182" s="11"/>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>173</v>
       </c>
@@ -5676,7 +5676,7 @@
       <c r="H183" s="11"/>
       <c r="I183" s="11"/>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>174</v>
       </c>
@@ -5702,7 +5702,7 @@
       <c r="H184" s="11"/>
       <c r="I184" s="11"/>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>175</v>
       </c>
@@ -5728,7 +5728,7 @@
       <c r="H185" s="11"/>
       <c r="I185" s="11"/>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>176</v>
       </c>
@@ -5754,7 +5754,7 @@
       <c r="H186" s="11"/>
       <c r="I186" s="11"/>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>177</v>
       </c>
@@ -5780,7 +5780,7 @@
       <c r="H187" s="11"/>
       <c r="I187" s="11"/>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>178</v>
       </c>
@@ -5806,7 +5806,7 @@
       <c r="H188" s="11"/>
       <c r="I188" s="11"/>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>179</v>
       </c>
@@ -5832,7 +5832,7 @@
       <c r="H189" s="11"/>
       <c r="I189" s="11"/>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>180</v>
       </c>
@@ -5858,7 +5858,7 @@
       <c r="H190" s="11"/>
       <c r="I190" s="11"/>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>181</v>
       </c>
@@ -5884,7 +5884,7 @@
       <c r="H191" s="11"/>
       <c r="I191" s="11"/>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>182</v>
       </c>
@@ -5910,7 +5910,7 @@
       <c r="H192" s="11"/>
       <c r="I192" s="11"/>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>183</v>
       </c>
@@ -5936,7 +5936,7 @@
       <c r="H193" s="11"/>
       <c r="I193" s="11"/>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>184</v>
       </c>
@@ -5962,7 +5962,7 @@
       <c r="H194" s="11"/>
       <c r="I194" s="11"/>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>185</v>
       </c>
@@ -5988,7 +5988,7 @@
       <c r="H195" s="11"/>
       <c r="I195" s="11"/>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>186</v>
       </c>
@@ -6014,7 +6014,7 @@
       <c r="H196" s="11"/>
       <c r="I196" s="11"/>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>187</v>
       </c>
@@ -6040,7 +6040,7 @@
       <c r="H197" s="11"/>
       <c r="I197" s="11"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>188</v>
       </c>
@@ -6066,7 +6066,7 @@
       <c r="H198" s="11"/>
       <c r="I198" s="11"/>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>189</v>
       </c>
@@ -6092,7 +6092,7 @@
       <c r="H199" s="11"/>
       <c r="I199" s="11"/>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>190</v>
       </c>
@@ -6118,7 +6118,7 @@
       <c r="H200" s="11"/>
       <c r="I200" s="11"/>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>191</v>
       </c>
@@ -6144,7 +6144,7 @@
       <c r="H201" s="11"/>
       <c r="I201" s="11"/>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>192</v>
       </c>
@@ -6170,7 +6170,7 @@
       <c r="H202" s="11"/>
       <c r="I202" s="11"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>193</v>
       </c>
@@ -6196,7 +6196,7 @@
       <c r="H203" s="11"/>
       <c r="I203" s="11"/>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>194</v>
       </c>
@@ -6222,7 +6222,7 @@
       <c r="H204" s="11"/>
       <c r="I204" s="11"/>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>195</v>
       </c>
@@ -6248,7 +6248,7 @@
       <c r="H205" s="11"/>
       <c r="I205" s="11"/>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>196</v>
       </c>
@@ -6274,7 +6274,7 @@
       <c r="H206" s="11"/>
       <c r="I206" s="11"/>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>197</v>
       </c>
@@ -6300,7 +6300,7 @@
       <c r="H207" s="11"/>
       <c r="I207" s="11"/>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>198</v>
       </c>
@@ -6326,7 +6326,7 @@
       <c r="H208" s="11"/>
       <c r="I208" s="11"/>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>199</v>
       </c>
@@ -6352,7 +6352,7 @@
       <c r="H209" s="11"/>
       <c r="I209" s="11"/>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>200</v>
       </c>
@@ -6378,7 +6378,7 @@
       <c r="H210" s="11"/>
       <c r="I210" s="11"/>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <v>201</v>
       </c>
@@ -6404,7 +6404,7 @@
       <c r="H211" s="11"/>
       <c r="I211" s="11"/>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>202</v>
       </c>
@@ -6430,7 +6430,7 @@
       <c r="H212" s="11"/>
       <c r="I212" s="11"/>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <v>203</v>
       </c>
@@ -6456,7 +6456,7 @@
       <c r="H213" s="11"/>
       <c r="I213" s="11"/>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>204</v>
       </c>
@@ -6482,7 +6482,7 @@
       <c r="H214" s="11"/>
       <c r="I214" s="11"/>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>205</v>
       </c>
@@ -6508,7 +6508,7 @@
       <c r="H215" s="11"/>
       <c r="I215" s="11"/>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <v>206</v>
       </c>
@@ -6534,7 +6534,7 @@
       <c r="H216" s="11"/>
       <c r="I216" s="11"/>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <v>207</v>
       </c>
@@ -6560,7 +6560,7 @@
       <c r="H217" s="11"/>
       <c r="I217" s="11"/>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <v>208</v>
       </c>
@@ -6586,7 +6586,7 @@
       <c r="H218" s="11"/>
       <c r="I218" s="11"/>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <v>209</v>
       </c>
@@ -6612,7 +6612,7 @@
       <c r="H219" s="11"/>
       <c r="I219" s="11"/>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <v>210</v>
       </c>
@@ -6638,7 +6638,7 @@
       <c r="H220" s="11"/>
       <c r="I220" s="11"/>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <v>211</v>
       </c>
@@ -6664,7 +6664,7 @@
       <c r="H221" s="11"/>
       <c r="I221" s="11"/>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <v>212</v>
       </c>
@@ -6690,7 +6690,7 @@
       <c r="H222" s="11"/>
       <c r="I222" s="11"/>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <v>213</v>
       </c>
@@ -6716,7 +6716,7 @@
       <c r="H223" s="11"/>
       <c r="I223" s="11"/>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <v>214</v>
       </c>
@@ -6742,7 +6742,7 @@
       <c r="H224" s="11"/>
       <c r="I224" s="11"/>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>215</v>
       </c>
@@ -6768,7 +6768,7 @@
       <c r="H225" s="11"/>
       <c r="I225" s="11"/>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <v>216</v>
       </c>
@@ -6794,7 +6794,7 @@
       <c r="H226" s="11"/>
       <c r="I226" s="11"/>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
         <v>217</v>
       </c>
@@ -6820,7 +6820,7 @@
       <c r="H227" s="11"/>
       <c r="I227" s="11"/>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <v>218</v>
       </c>
@@ -6846,7 +6846,7 @@
       <c r="H228" s="11"/>
       <c r="I228" s="11"/>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <v>219</v>
       </c>
@@ -6872,7 +6872,7 @@
       <c r="H229" s="11"/>
       <c r="I229" s="11"/>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <v>220</v>
       </c>
@@ -6898,7 +6898,7 @@
       <c r="H230" s="11"/>
       <c r="I230" s="11"/>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
         <v>221</v>
       </c>
@@ -6924,7 +6924,7 @@
       <c r="H231" s="11"/>
       <c r="I231" s="11"/>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
         <v>222</v>
       </c>
@@ -6950,7 +6950,7 @@
       <c r="H232" s="11"/>
       <c r="I232" s="11"/>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <v>223</v>
       </c>
@@ -6976,7 +6976,7 @@
       <c r="H233" s="11"/>
       <c r="I233" s="11"/>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <v>224</v>
       </c>
@@ -7002,7 +7002,7 @@
       <c r="H234" s="11"/>
       <c r="I234" s="11"/>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <v>225</v>
       </c>
@@ -7028,7 +7028,7 @@
       <c r="H235" s="11"/>
       <c r="I235" s="11"/>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <v>226</v>
       </c>
@@ -7054,7 +7054,7 @@
       <c r="H236" s="11"/>
       <c r="I236" s="11"/>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <v>227</v>
       </c>
@@ -7080,7 +7080,7 @@
       <c r="H237" s="11"/>
       <c r="I237" s="11"/>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <v>228</v>
       </c>
@@ -7106,7 +7106,7 @@
       <c r="H238" s="11"/>
       <c r="I238" s="11"/>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <v>229</v>
       </c>
@@ -7132,7 +7132,7 @@
       <c r="H239" s="11"/>
       <c r="I239" s="11"/>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <v>230</v>
       </c>
@@ -7158,7 +7158,7 @@
       <c r="H240" s="11"/>
       <c r="I240" s="11"/>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
         <v>231</v>
       </c>
@@ -7184,7 +7184,7 @@
       <c r="H241" s="11"/>
       <c r="I241" s="11"/>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
         <v>232</v>
       </c>
@@ -7210,7 +7210,7 @@
       <c r="H242" s="11"/>
       <c r="I242" s="11"/>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
         <v>233</v>
       </c>
@@ -7236,7 +7236,7 @@
       <c r="H243" s="11"/>
       <c r="I243" s="11"/>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
         <v>234</v>
       </c>
@@ -7262,7 +7262,7 @@
       <c r="H244" s="11"/>
       <c r="I244" s="11"/>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
         <v>235</v>
       </c>
@@ -7288,7 +7288,7 @@
       <c r="H245" s="11"/>
       <c r="I245" s="11"/>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
         <v>236</v>
       </c>
@@ -7314,7 +7314,7 @@
       <c r="H246" s="11"/>
       <c r="I246" s="11"/>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
         <v>237</v>
       </c>
@@ -7340,7 +7340,7 @@
       <c r="H247" s="11"/>
       <c r="I247" s="11"/>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <v>238</v>
       </c>
@@ -7366,7 +7366,7 @@
       <c r="H248" s="11"/>
       <c r="I248" s="11"/>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
         <v>239</v>
       </c>
@@ -7392,7 +7392,7 @@
       <c r="H249" s="11"/>
       <c r="I249" s="11"/>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
         <v>240</v>
       </c>
@@ -7418,7 +7418,7 @@
       <c r="H250" s="11"/>
       <c r="I250" s="11"/>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
         <v>241</v>
       </c>
@@ -7444,7 +7444,7 @@
       <c r="H251" s="11"/>
       <c r="I251" s="11"/>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
         <v>242</v>
       </c>
@@ -7470,7 +7470,7 @@
       <c r="H252" s="11"/>
       <c r="I252" s="11"/>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
         <v>243</v>
       </c>
@@ -7496,7 +7496,7 @@
       <c r="H253" s="11"/>
       <c r="I253" s="11"/>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
         <v>244</v>
       </c>
@@ -7522,7 +7522,7 @@
       <c r="H254" s="11"/>
       <c r="I254" s="11"/>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
         <v>245</v>
       </c>
@@ -7548,7 +7548,7 @@
       <c r="H255" s="11"/>
       <c r="I255" s="11"/>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
         <v>246</v>
       </c>
@@ -7574,7 +7574,7 @@
       <c r="H256" s="11"/>
       <c r="I256" s="11"/>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
         <v>247</v>
       </c>
@@ -7600,7 +7600,7 @@
       <c r="H257" s="11"/>
       <c r="I257" s="11"/>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
         <v>248</v>
       </c>
@@ -7626,7 +7626,7 @@
       <c r="H258" s="11"/>
       <c r="I258" s="11"/>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
         <v>249</v>
       </c>
@@ -7652,7 +7652,7 @@
       <c r="H259" s="11"/>
       <c r="I259" s="11"/>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
         <v>250</v>
       </c>
@@ -7678,7 +7678,7 @@
       <c r="H260" s="11"/>
       <c r="I260" s="11"/>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
         <v>251</v>
       </c>
@@ -7704,7 +7704,7 @@
       <c r="H261" s="11"/>
       <c r="I261" s="11"/>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
         <v>252</v>
       </c>
@@ -7730,7 +7730,7 @@
       <c r="H262" s="11"/>
       <c r="I262" s="11"/>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
         <v>253</v>
       </c>
@@ -7756,7 +7756,7 @@
       <c r="H263" s="11"/>
       <c r="I263" s="11"/>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
         <v>254</v>
       </c>
@@ -7782,7 +7782,7 @@
       <c r="H264" s="11"/>
       <c r="I264" s="11"/>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
         <v>255</v>
       </c>
@@ -7808,7 +7808,7 @@
       <c r="H265" s="11"/>
       <c r="I265" s="11"/>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
         <v>256</v>
       </c>
@@ -7834,7 +7834,7 @@
       <c r="H266" s="11"/>
       <c r="I266" s="11"/>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
         <v>257</v>
       </c>
@@ -7860,7 +7860,7 @@
       <c r="H267" s="11"/>
       <c r="I267" s="11"/>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
         <v>258</v>
       </c>
@@ -7886,7 +7886,7 @@
       <c r="H268" s="11"/>
       <c r="I268" s="11"/>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
         <v>259</v>
       </c>
@@ -7912,7 +7912,7 @@
       <c r="H269" s="11"/>
       <c r="I269" s="11"/>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
         <v>260</v>
       </c>
@@ -7938,7 +7938,7 @@
       <c r="H270" s="11"/>
       <c r="I270" s="11"/>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
         <v>261</v>
       </c>
@@ -7964,7 +7964,7 @@
       <c r="H271" s="11"/>
       <c r="I271" s="11"/>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
         <v>262</v>
       </c>
@@ -7990,7 +7990,7 @@
       <c r="H272" s="11"/>
       <c r="I272" s="11"/>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
         <v>263</v>
       </c>
@@ -8016,7 +8016,7 @@
       <c r="H273" s="11"/>
       <c r="I273" s="11"/>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
         <v>264</v>
       </c>
@@ -8042,7 +8042,7 @@
       <c r="H274" s="11"/>
       <c r="I274" s="11"/>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
         <v>265</v>
       </c>
@@ -8068,7 +8068,7 @@
       <c r="H275" s="11"/>
       <c r="I275" s="11"/>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
         <v>266</v>
       </c>
@@ -8094,7 +8094,7 @@
       <c r="H276" s="11"/>
       <c r="I276" s="11"/>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
         <v>267</v>
       </c>
@@ -8120,7 +8120,7 @@
       <c r="H277" s="11"/>
       <c r="I277" s="11"/>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
         <v>268</v>
       </c>
@@ -8146,7 +8146,7 @@
       <c r="H278" s="11"/>
       <c r="I278" s="11"/>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
         <v>269</v>
       </c>
@@ -8172,7 +8172,7 @@
       <c r="H279" s="11"/>
       <c r="I279" s="11"/>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
         <v>270</v>
       </c>
@@ -8198,7 +8198,7 @@
       <c r="H280" s="11"/>
       <c r="I280" s="11"/>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
         <v>271</v>
       </c>
@@ -8224,7 +8224,7 @@
       <c r="H281" s="11"/>
       <c r="I281" s="11"/>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
         <v>272</v>
       </c>
@@ -8250,7 +8250,7 @@
       <c r="H282" s="11"/>
       <c r="I282" s="11"/>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
         <v>273</v>
       </c>
@@ -8276,7 +8276,7 @@
       <c r="H283" s="11"/>
       <c r="I283" s="11"/>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
         <v>274</v>
       </c>
@@ -8302,7 +8302,7 @@
       <c r="H284" s="11"/>
       <c r="I284" s="11"/>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
         <v>275</v>
       </c>
@@ -8328,7 +8328,7 @@
       <c r="H285" s="11"/>
       <c r="I285" s="11"/>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
         <v>276</v>
       </c>
@@ -8361,7 +8361,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
         <v>277</v>
       </c>
@@ -8394,7 +8394,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
         <v>278</v>
       </c>
@@ -8427,7 +8427,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
         <v>279</v>
       </c>
@@ -8460,7 +8460,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
         <v>280</v>
       </c>
@@ -8493,7 +8493,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
         <v>281</v>
       </c>
@@ -8526,7 +8526,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
         <v>282</v>
       </c>
@@ -8559,7 +8559,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
         <v>283</v>
       </c>
@@ -8592,7 +8592,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
         <v>284</v>
       </c>
@@ -8625,7 +8625,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
         <v>285</v>
       </c>
@@ -8658,7 +8658,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
         <v>286</v>
       </c>
@@ -8691,7 +8691,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
         <v>287</v>
       </c>
@@ -8724,7 +8724,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
         <v>288</v>
       </c>
@@ -8757,7 +8757,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
         <v>289</v>
       </c>
@@ -8790,7 +8790,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
         <v>290</v>
       </c>
@@ -8823,7 +8823,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
         <v>291</v>
       </c>
@@ -8856,7 +8856,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
         <v>292</v>
       </c>
@@ -8889,7 +8889,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="303" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
         <v>293</v>
       </c>
@@ -8922,7 +8922,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="304" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
         <v>294</v>
       </c>
@@ -8955,7 +8955,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
         <v>295</v>
       </c>
@@ -8988,7 +8988,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
         <v>296</v>
       </c>
@@ -9021,7 +9021,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
         <v>297</v>
       </c>
@@ -9054,7 +9054,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
         <v>298</v>
       </c>
@@ -9087,7 +9087,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
         <v>298</v>
       </c>
@@ -9120,7 +9120,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
         <v>299</v>
       </c>
@@ -9153,7 +9153,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
         <v>300</v>
       </c>
@@ -9186,7 +9186,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
         <v>301</v>
       </c>
@@ -9219,7 +9219,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A313" s="1">
         <v>302</v>
       </c>
@@ -9252,7 +9252,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A314" s="1">
         <v>303</v>
       </c>
@@ -9285,7 +9285,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
         <v>304</v>
       </c>
@@ -9318,14 +9318,14 @@
         <v>76</v>
       </c>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
         <v>305</v>
       </c>
       <c r="B316" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C316" s="16" t="str">
+      <c r="C316" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
@@ -9351,49 +9351,70 @@
         <v>76</v>
       </c>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A317" s="1"/>
-    </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A317" s="1">
+        <v>306</v>
+      </c>
+      <c r="B317" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C317" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
+      </c>
+      <c r="D317" s="14">
+        <v>0</v>
+      </c>
+      <c r="E317" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F317" s="15">
+        <v>46163.160416666666</v>
+      </c>
+      <c r="G317" s="15"/>
+      <c r="H317" s="11"/>
+      <c r="I317" s="11"/>
+    </row>
+    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A318" s="1"/>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A319" s="1"/>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A320" s="1"/>
     </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A321" s="1"/>
     </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A322" s="1"/>
     </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>
     </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A324" s="1"/>
     </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A325" s="1"/>
     </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A326" s="1"/>
     </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
     </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A328" s="1"/>
     </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A329" s="1"/>
     </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>
     </row>
-    <row r="331" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A331" s="1"/>
     </row>
   </sheetData>
@@ -9415,13 +9436,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{797F1036-D41E-43A4-9E6E-CBBB62F3CD31}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.33203125" customWidth="1"/>
-    <col min="4" max="4" width="12.88671875" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9435,7 +9456,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -9449,7 +9470,7 @@
         <v>234.67</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -9463,7 +9484,7 @@
         <v>161.15</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -9477,7 +9498,7 @@
         <v>157.61000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -9491,7 +9512,7 @@
         <v>347.95</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -9505,7 +9526,7 @@
         <v>393.57</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -9519,7 +9540,7 @@
         <v>19.87</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -9533,7 +9554,7 @@
         <v>19.57</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>61</v>
       </c>
@@ -9547,7 +9568,7 @@
         <v>19.86</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -9561,7 +9582,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -9586,15 +9607,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56220E0F-EC16-4A8C-9E04-C7F8849C4B4D}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9611,7 +9632,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -9628,7 +9649,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -9645,7 +9666,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -9662,7 +9683,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -9679,7 +9700,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -9696,7 +9717,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -9713,7 +9734,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -9741,14 +9762,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83DAFC4B-C207-418A-8501-0E1EC9E673B7}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9759,7 +9780,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -9770,7 +9791,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -9781,7 +9802,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -9792,7 +9813,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>61</v>
       </c>
@@ -9803,7 +9824,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -9814,7 +9835,7 @@
         <v>46631</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -9825,7 +9846,7 @@
         <v>48579</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -9836,7 +9857,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -9847,7 +9868,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -9858,7 +9879,7 @@
         <v>48579</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -10081,6 +10102,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
@@ -10092,15 +10122,6 @@
     </SharedWithUsers>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10123,26 +10144,26 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
+    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="978" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{193B4E4B-F4EC-4E4E-9E2E-40D1F1B1CF52}"/>
+  <xr:revisionPtr revIDLastSave="979" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39AA48FA-320B-490D-9286-64AE65D7D13B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -9371,7 +9371,9 @@
       <c r="F317" s="15">
         <v>46163.160416666666</v>
       </c>
-      <c r="G317" s="15"/>
+      <c r="G317" s="15">
+        <v>46163.326388888891</v>
+      </c>
       <c r="H317" s="11"/>
       <c r="I317" s="11"/>
     </row>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="979" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39AA48FA-320B-490D-9286-64AE65D7D13B}"/>
+  <xr:revisionPtr revIDLastSave="984" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0B34409-376D-4D24-AE6A-1F0CD4FF8AD0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="88">
   <si>
     <t>ID</t>
   </si>
@@ -742,8 +742,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J317" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J317" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J318" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J318" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1143,7 +1143,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -9378,7 +9378,28 @@
       <c r="I317" s="11"/>
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A318" s="1"/>
+      <c r="A318" s="1">
+        <v>307</v>
+      </c>
+      <c r="B318" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C318" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
+      </c>
+      <c r="D318" s="14">
+        <v>0</v>
+      </c>
+      <c r="E318" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F318" s="15">
+        <v>46164.215277777781</v>
+      </c>
+      <c r="G318" s="15"/>
+      <c r="H318" s="11"/>
+      <c r="I318" s="11"/>
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A319" s="1"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="984" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0B34409-376D-4D24-AE6A-1F0CD4FF8AD0}"/>
+  <xr:revisionPtr revIDLastSave="989" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{032061D8-923D-4F9A-9603-57C684B6C45B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="89">
   <si>
     <t>ID</t>
   </si>
@@ -318,6 +318,9 @@
   </si>
   <si>
     <t>Se realiza cambio motor eléctrico VAS1 por alta temperatura en cojinete</t>
+  </si>
+  <si>
+    <t>Falla en tarjeta de control de VIGB del sistema de admisión de aire al compresor de la turbina a gas.</t>
   </si>
 </sst>
 </file>
@@ -9375,7 +9378,12 @@
         <v>46163.326388888891</v>
       </c>
       <c r="H317" s="11"/>
-      <c r="I317" s="11"/>
+      <c r="I317" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="J317" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
@@ -9397,9 +9405,18 @@
       <c r="F318" s="15">
         <v>46164.215277777781</v>
       </c>
-      <c r="G318" s="15"/>
-      <c r="H318" s="11"/>
-      <c r="I318" s="11"/>
+      <c r="G318" s="15">
+        <v>46164.252083333333</v>
+      </c>
+      <c r="H318" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="I318" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="J318" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A319" s="1"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="989" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{032061D8-923D-4F9A-9603-57C684B6C45B}"/>
+  <xr:revisionPtr revIDLastSave="990" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E7206D6-89BD-4011-A071-27E01F3B9AA8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -9210,7 +9210,7 @@
         <v>46151.263194444444</v>
       </c>
       <c r="G312" s="15">
-        <v>46163.999305555553</v>
+        <v>46163.041666666664</v>
       </c>
       <c r="H312" s="11" t="s">
         <v>79</v>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="990" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E7206D6-89BD-4011-A071-27E01F3B9AA8}"/>
+  <xr:revisionPtr revIDLastSave="994" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2698F5E1-582B-4A21-8082-77B0034CF7FF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="89">
   <si>
     <t>ID</t>
   </si>
@@ -299,9 +299,6 @@
     <t xml:space="preserve">Rotura tubo vapor SH </t>
   </si>
   <si>
-    <t>Abierto</t>
-  </si>
-  <si>
     <t>Bajo nivel del Domo</t>
   </si>
   <si>
@@ -321,6 +318,9 @@
   </si>
   <si>
     <t>Falla en tarjeta de control de VIGB del sistema de admisión de aire al compresor de la turbina a gas.</t>
+  </si>
+  <si>
+    <t>Posición de desviación VV IGB</t>
   </si>
 </sst>
 </file>
@@ -9219,7 +9219,7 @@
         <v>80</v>
       </c>
       <c r="J312" s="13" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.25">
@@ -9246,10 +9246,10 @@
         <v>46154.719444444447</v>
       </c>
       <c r="H313" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="I313" s="11" t="s">
         <v>82</v>
-      </c>
-      <c r="I313" s="11" t="s">
-        <v>83</v>
       </c>
       <c r="J313" s="13" t="s">
         <v>76</v>
@@ -9279,10 +9279,10 @@
         <v>46156.082638888889</v>
       </c>
       <c r="H314" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="I314" s="11" t="s">
         <v>84</v>
-      </c>
-      <c r="I314" s="11" t="s">
-        <v>85</v>
       </c>
       <c r="J314" s="13" t="s">
         <v>76</v>
@@ -9312,10 +9312,10 @@
         <v>46156.152777777781</v>
       </c>
       <c r="H315" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="I315" s="11" t="s">
         <v>84</v>
-      </c>
-      <c r="I315" s="11" t="s">
-        <v>85</v>
       </c>
       <c r="J315" s="13" t="s">
         <v>76</v>
@@ -9345,10 +9345,10 @@
         <v>46158.885416666664</v>
       </c>
       <c r="H316" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="I316" s="11" t="s">
         <v>86</v>
-      </c>
-      <c r="I316" s="11" t="s">
-        <v>87</v>
       </c>
       <c r="J316" s="13" t="s">
         <v>76</v>
@@ -9377,11 +9377,13 @@
       <c r="G317" s="15">
         <v>46163.326388888891</v>
       </c>
-      <c r="H317" s="11"/>
+      <c r="H317" s="11" t="s">
+        <v>88</v>
+      </c>
       <c r="I317" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="J317" t="s">
+        <v>87</v>
+      </c>
+      <c r="J317" s="1" t="s">
         <v>76</v>
       </c>
     </row>
@@ -9409,12 +9411,12 @@
         <v>46164.252083333333</v>
       </c>
       <c r="H318" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="I318" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="I318" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="J318" t="s">
+      <c r="J318" s="1" t="s">
         <v>76</v>
       </c>
     </row>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="994" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2698F5E1-582B-4A21-8082-77B0034CF7FF}"/>
+  <xr:revisionPtr revIDLastSave="996" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B40EACB8-F0C9-453F-96AC-D11C124A6852}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <definedName name="SegmentaciónDeDatos_Sitio">#N/A</definedName>
     <definedName name="SegmentaciónDeDatos_Unidad">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="89">
   <si>
     <t>ID</t>
   </si>
@@ -745,8 +745,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J318" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J318" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J319" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J319" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1146,7 +1146,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -9361,7 +9361,7 @@
       <c r="B317" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C317" s="16" t="str">
+      <c r="C317" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
@@ -9394,7 +9394,7 @@
       <c r="B318" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C318" s="16" t="str">
+      <c r="C318" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
@@ -9421,7 +9421,22 @@
       </c>
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A319" s="1"/>
+      <c r="A319" s="1">
+        <v>308</v>
+      </c>
+      <c r="B319" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C319" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CEM</v>
+      </c>
+      <c r="D319" s="14"/>
+      <c r="E319" s="13"/>
+      <c r="F319" s="15"/>
+      <c r="G319" s="15"/>
+      <c r="H319" s="11"/>
+      <c r="I319" s="11"/>
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A320" s="1"/>
@@ -10144,15 +10159,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
@@ -10164,6 +10170,15 @@
     </SharedWithUsers>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10186,26 +10201,26 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
-    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="996" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B40EACB8-F0C9-453F-96AC-D11C124A6852}"/>
+  <xr:revisionPtr revIDLastSave="1000" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56072AC6-7C4F-4939-A27F-45C6DD73C6D1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="89">
   <si>
     <t>ID</t>
   </si>
@@ -9431,10 +9431,18 @@
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
-      <c r="D319" s="14"/>
-      <c r="E319" s="13"/>
-      <c r="F319" s="15"/>
-      <c r="G319" s="15"/>
+      <c r="D319" s="14">
+        <v>70</v>
+      </c>
+      <c r="E319" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F319" s="15">
+        <v>46171.208333333336</v>
+      </c>
+      <c r="G319" s="15">
+        <v>46171.681250000001</v>
+      </c>
       <c r="H319" s="11"/>
       <c r="I319" s="11"/>
     </row>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1000" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56072AC6-7C4F-4939-A27F-45C6DD73C6D1}"/>
+  <xr:revisionPtr revIDLastSave="1018" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35B6BF32-AC81-4413-B574-52D29AB00EB5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="92">
   <si>
     <t>ID</t>
   </si>
@@ -321,6 +321,15 @@
   </si>
   <si>
     <t>Posición de desviación VV IGB</t>
+  </si>
+  <si>
+    <t>Alta T° descarga agua de mar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limpieza de cajas enfrimaineto principal condensador. </t>
+  </si>
+  <si>
+    <t>Trip Bba. Agua aliemntación LAC30 por baja presión de aceite.</t>
   </si>
 </sst>
 </file>
@@ -745,8 +754,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J319" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J319" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J321" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J321" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1127,7 +1136,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
-  <dimension ref="A9:J331"/>
+  <dimension ref="A9:J332"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -1146,7 +1155,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -9425,62 +9434,116 @@
         <v>308</v>
       </c>
       <c r="B319" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C319" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CEM</v>
+      </c>
+      <c r="D319" s="14">
+        <v>0</v>
+      </c>
+      <c r="E319" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F319" s="15">
+        <v>46164.556944444441</v>
+      </c>
+      <c r="G319" s="15">
+        <v>46164.853472222225</v>
+      </c>
+      <c r="H319" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="I319" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="J319" s="1"/>
+    </row>
+    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A320" s="1">
+        <v>309</v>
+      </c>
+      <c r="B320" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C319" s="16" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
-        <v>CEM</v>
-      </c>
-      <c r="D319" s="14">
+      <c r="C320" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CEM</v>
+      </c>
+      <c r="D320" s="14">
         <v>70</v>
       </c>
-      <c r="E319" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F319" s="15">
+      <c r="E320" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F320" s="15">
         <v>46171.208333333336</v>
       </c>
-      <c r="G319" s="15">
+      <c r="G320" s="15">
         <v>46171.681250000001</v>
       </c>
-      <c r="H319" s="11"/>
-      <c r="I319" s="11"/>
-    </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A320" s="1"/>
-    </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A321" s="1"/>
-    </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="H320" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I320" s="11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A321" s="1">
+        <v>310</v>
+      </c>
+      <c r="B321" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C321" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CEM</v>
+      </c>
+      <c r="D321" s="14">
+        <v>70</v>
+      </c>
+      <c r="E321" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F321" s="15"/>
+      <c r="G321" s="15"/>
+      <c r="H321" s="11"/>
+      <c r="I321" s="11"/>
+    </row>
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322" s="1"/>
     </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>
     </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A324" s="1"/>
     </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325" s="1"/>
     </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A326" s="1"/>
     </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
     </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" s="1"/>
     </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" s="1"/>
     </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>
     </row>
-    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331" s="1"/>
+    </row>
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A332" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1018" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35B6BF32-AC81-4413-B574-52D29AB00EB5}"/>
+  <xr:revisionPtr revIDLastSave="1023" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B3AE2C5-C9CD-48AC-8731-E7EE1C1D65A8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="95">
   <si>
     <t>ID</t>
   </si>
@@ -330,6 +330,15 @@
   </si>
   <si>
     <t>Trip Bba. Agua aliemntación LAC30 por baja presión de aceite.</t>
+  </si>
+  <si>
+    <t>Falla alimentadores de combustibles.</t>
+  </si>
+  <si>
+    <t>Falla cadena de recuperación Alimentador N°5 y alimentador N°6 en reparación.</t>
+  </si>
+  <si>
+    <t>Abierto</t>
   </si>
 </sst>
 </file>
@@ -9458,7 +9467,9 @@
       <c r="I319" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="J319" s="1"/>
+      <c r="J319" s="1" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A320" s="1">
@@ -9489,8 +9500,11 @@
       <c r="I320" s="11" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J320" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A321" s="1">
         <v>310</v>
       </c>
@@ -9507,42 +9521,51 @@
       <c r="E321" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F321" s="15"/>
+      <c r="F321" s="15">
+        <v>46174.96597222222</v>
+      </c>
       <c r="G321" s="15"/>
-      <c r="H321" s="11"/>
-      <c r="I321" s="11"/>
-    </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H321" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="I321" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="J321" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A322" s="1"/>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A324" s="1"/>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A325" s="1"/>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A326" s="1"/>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A328" s="1"/>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A329" s="1"/>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A331" s="1"/>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A332" s="1"/>
     </row>
   </sheetData>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1023" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B3AE2C5-C9CD-48AC-8731-E7EE1C1D65A8}"/>
+  <xr:revisionPtr revIDLastSave="1030" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5E968FB-B02E-4E6A-97AC-0CBE8C8682AE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="SegmentaciónDeDatos_Sitio">#N/A</definedName>
     <definedName name="SegmentaciónDeDatos_Unidad">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="95">
   <si>
     <t>ID</t>
   </si>
@@ -763,8 +763,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J321" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J321" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J322" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J322" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1164,7 +1164,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -9536,7 +9536,28 @@
       </c>
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A322" s="1"/>
+      <c r="A322" s="1">
+        <v>311</v>
+      </c>
+      <c r="B322" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C322" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
+      </c>
+      <c r="D322" s="14">
+        <v>0</v>
+      </c>
+      <c r="E322" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F322" s="15">
+        <v>46175.010416666664</v>
+      </c>
+      <c r="G322" s="15"/>
+      <c r="H322" s="11"/>
+      <c r="I322" s="11"/>
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1030" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5E968FB-B02E-4E6A-97AC-0CBE8C8682AE}"/>
+  <xr:revisionPtr revIDLastSave="1035" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72DFBE2E-4DF3-4913-9D8F-F7BFEF42A29E}"/>
   <bookViews>
     <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="97">
   <si>
     <t>ID</t>
   </si>
@@ -339,6 +339,12 @@
   </si>
   <si>
     <t>Abierto</t>
+  </si>
+  <si>
+    <t>Protección TV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falla sensor de T° de vapor </t>
   </si>
 </sst>
 </file>
@@ -9555,9 +9561,15 @@
       <c r="F322" s="15">
         <v>46175.010416666664</v>
       </c>
-      <c r="G322" s="15"/>
-      <c r="H322" s="11"/>
-      <c r="I322" s="11"/>
+      <c r="G322" s="15">
+        <v>46175.112500000003</v>
+      </c>
+      <c r="H322" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="I322" s="11" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1035" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72DFBE2E-4DF3-4913-9D8F-F7BFEF42A29E}"/>
+  <xr:revisionPtr revIDLastSave="1041" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B797C3C3-CC57-40AC-BDA8-55FF33F6E6A5}"/>
   <bookViews>
     <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="96">
   <si>
     <t>ID</t>
   </si>
@@ -338,13 +338,10 @@
     <t>Falla cadena de recuperación Alimentador N°5 y alimentador N°6 en reparación.</t>
   </si>
   <si>
-    <t>Abierto</t>
-  </si>
-  <si>
     <t>Protección TV</t>
   </si>
   <si>
-    <t xml:space="preserve">Falla sensor de T° de vapor </t>
+    <t>Falla sensor de T° de vapor ingreso TV</t>
   </si>
 </sst>
 </file>
@@ -9530,7 +9527,9 @@
       <c r="F321" s="15">
         <v>46174.96597222222</v>
       </c>
-      <c r="G321" s="15"/>
+      <c r="G321" s="15">
+        <v>46175.465277777781</v>
+      </c>
       <c r="H321" s="11" t="s">
         <v>92</v>
       </c>
@@ -9538,7 +9537,7 @@
         <v>93</v>
       </c>
       <c r="J321" s="1" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.25">
@@ -9565,10 +9564,13 @@
         <v>46175.112500000003</v>
       </c>
       <c r="H322" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="I322" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="I322" s="11" t="s">
-        <v>96</v>
+      <c r="J322" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.25">

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1041" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B797C3C3-CC57-40AC-BDA8-55FF33F6E6A5}"/>
+  <xr:revisionPtr revIDLastSave="1046" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82197B66-EE86-4EB3-8A67-AC2AF8588411}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="SegmentaciónDeDatos_Sitio">#N/A</definedName>
     <definedName name="SegmentaciónDeDatos_Unidad">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="96">
   <si>
     <t>ID</t>
   </si>
@@ -766,8 +766,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J322" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J322" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J323" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J323" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1167,7 +1167,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -9574,7 +9574,28 @@
       </c>
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A323" s="1"/>
+      <c r="A323" s="1">
+        <v>312</v>
+      </c>
+      <c r="B323" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C323" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
+      </c>
+      <c r="D323" s="14">
+        <v>0</v>
+      </c>
+      <c r="E323" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F323" s="15">
+        <v>46176.1875</v>
+      </c>
+      <c r="G323" s="15"/>
+      <c r="H323" s="11"/>
+      <c r="I323" s="11"/>
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A324" s="1"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1046" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82197B66-EE86-4EB3-8A67-AC2AF8588411}"/>
+  <xr:revisionPtr revIDLastSave="1052" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEC1594F-4957-4FAA-A853-9B6ABD5DDD3F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="96">
   <si>
     <t>ID</t>
   </si>
@@ -1167,7 +1167,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -9574,25 +9574,12 @@
       </c>
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A323" s="1">
-        <v>312</v>
-      </c>
-      <c r="B323" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C323" s="16" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
-        <v>CET</v>
-      </c>
-      <c r="D323" s="14">
-        <v>0</v>
-      </c>
-      <c r="E323" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F323" s="15">
-        <v>46176.1875</v>
-      </c>
+      <c r="A323" s="1"/>
+      <c r="B323" s="13"/>
+      <c r="C323" s="16"/>
+      <c r="D323" s="14"/>
+      <c r="E323" s="13"/>
+      <c r="F323" s="15"/>
       <c r="G323" s="15"/>
       <c r="H323" s="11"/>
       <c r="I323" s="11"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1052" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEC1594F-4957-4FAA-A853-9B6ABD5DDD3F}"/>
+  <xr:revisionPtr revIDLastSave="1054" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F369E9FF-8E0C-404E-8377-63CDB3EFFA0C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <definedName name="SegmentaciónDeDatos_Sitio">#N/A</definedName>
     <definedName name="SegmentaciónDeDatos_Unidad">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
@@ -348,6 +348,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -426,9 +429,7 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9448,7 +9449,7 @@
       <c r="B319" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C319" s="16" t="str">
+      <c r="C319" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
@@ -9481,7 +9482,7 @@
       <c r="B320" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C320" s="16" t="str">
+      <c r="C320" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
@@ -9514,7 +9515,7 @@
       <c r="B321" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C321" s="16" t="str">
+      <c r="C321" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
@@ -9547,7 +9548,7 @@
       <c r="B322" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C322" s="16" t="str">
+      <c r="C322" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
@@ -9576,7 +9577,7 @@
     <row r="323" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>
       <c r="B323" s="13"/>
-      <c r="C323" s="16"/>
+      <c r="C323" s="13"/>
       <c r="D323" s="14"/>
       <c r="E323" s="13"/>
       <c r="F323" s="15"/>
@@ -9592,6 +9593,10 @@
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A326" s="1"/>
+      <c r="F326" s="16">
+        <f>G321-F321</f>
+        <v>0.49930555556056788</v>
+      </c>
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
@@ -10093,6 +10098,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100FB7AAE8C8816FD47B559A0CCF555AFF0" ma:contentTypeVersion="10" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5c9910934a78ddf693a6b708b52e9b37">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f95d585e-e7a7-414c-955d-38a47c8579bd" xmlns:ns3="33ab045e-9213-4eea-a9f2-a5b809105d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a9c61c95b4e11caed4e46447c2ca01e7" ns2:_="" ns3:_="">
     <xsd:import namespace="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
@@ -10295,20 +10314,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -10319,6 +10324,23 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10337,23 +10359,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
   <ds:schemaRefs>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1054" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F369E9FF-8E0C-404E-8377-63CDB3EFFA0C}"/>
+  <xr:revisionPtr revIDLastSave="1055" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EC02AE8-6C4F-4ED2-9AF8-FA71C55432EF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <definedName name="SegmentaciónDeDatos_Sitio">#N/A</definedName>
     <definedName name="SegmentaciónDeDatos_Unidad">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
@@ -349,7 +349,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -429,7 +429,7 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9593,10 +9593,7 @@
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A326" s="1"/>
-      <c r="F326" s="16">
-        <f>G321-F321</f>
-        <v>0.49930555556056788</v>
-      </c>
+      <c r="F326" s="16"/>
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
@@ -10098,20 +10095,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100FB7AAE8C8816FD47B559A0CCF555AFF0" ma:contentTypeVersion="10" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5c9910934a78ddf693a6b708b52e9b37">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f95d585e-e7a7-414c-955d-38a47c8579bd" xmlns:ns3="33ab045e-9213-4eea-a9f2-a5b809105d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a9c61c95b4e11caed4e46447c2ca01e7" ns2:_="" ns3:_="">
     <xsd:import namespace="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
@@ -10314,6 +10297,20 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -10324,23 +10321,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10359,6 +10339,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
   <ds:schemaRefs>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1055" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EC02AE8-6C4F-4ED2-9AF8-FA71C55432EF}"/>
+  <xr:revisionPtr revIDLastSave="1060" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61247F8B-894B-4DCF-8EF9-74BA46226B54}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="96">
   <si>
     <t>ID</t>
   </si>
@@ -1168,7 +1168,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -9575,11 +9575,22 @@
       </c>
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A323" s="1"/>
-      <c r="B323" s="13"/>
-      <c r="C323" s="13"/>
-      <c r="D323" s="14"/>
-      <c r="E323" s="13"/>
+      <c r="A323" s="1">
+        <v>312</v>
+      </c>
+      <c r="B323" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C323" s="13" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CEM</v>
+      </c>
+      <c r="D323" s="14">
+        <v>70</v>
+      </c>
+      <c r="E323" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="F323" s="15"/>
       <c r="G323" s="15"/>
       <c r="H323" s="11"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1060" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61247F8B-894B-4DCF-8EF9-74BA46226B54}"/>
+  <xr:revisionPtr revIDLastSave="1065" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5397D9ED-08EE-42D5-B260-9E301235E625}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="96">
   <si>
     <t>ID</t>
   </si>
@@ -9591,10 +9591,18 @@
       <c r="E323" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F323" s="15"/>
-      <c r="G323" s="15"/>
-      <c r="H323" s="11"/>
-      <c r="I323" s="11"/>
+      <c r="F323" s="15">
+        <v>46183.211111111108</v>
+      </c>
+      <c r="G323" s="15">
+        <v>46183.908333333333</v>
+      </c>
+      <c r="H323" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I323" s="11" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A324" s="1"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1065" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5397D9ED-08EE-42D5-B260-9E301235E625}"/>
+  <xr:revisionPtr revIDLastSave="1077" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93279B09-9797-468D-B0A0-3EF97CA96245}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <definedName name="SegmentaciónDeDatos_Sitio">#N/A</definedName>
     <definedName name="SegmentaciónDeDatos_Unidad">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="96">
   <si>
     <t>ID</t>
   </si>
@@ -348,9 +348,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -429,7 +426,9 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -767,8 +766,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J323" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J323" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J326" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J326" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1168,7 +1167,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -9605,14 +9604,70 @@
       </c>
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A324" s="1"/>
+      <c r="A324" s="1">
+        <v>313</v>
+      </c>
+      <c r="B324" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C324" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CEM</v>
+      </c>
+      <c r="D324" s="14">
+        <v>0</v>
+      </c>
+      <c r="E324" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F324" s="15"/>
+      <c r="G324" s="15"/>
+      <c r="H324" s="11"/>
+      <c r="I324" s="11"/>
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A325" s="1"/>
+      <c r="A325" s="1">
+        <v>314</v>
+      </c>
+      <c r="B325" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C325" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CEM</v>
+      </c>
+      <c r="D325" s="14">
+        <v>100</v>
+      </c>
+      <c r="E325" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F325" s="15"/>
+      <c r="G325" s="15"/>
+      <c r="H325" s="11"/>
+      <c r="I325" s="11"/>
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A326" s="1"/>
-      <c r="F326" s="16"/>
+      <c r="A326" s="1">
+        <v>315</v>
+      </c>
+      <c r="B326" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C326" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CEM</v>
+      </c>
+      <c r="D326" s="14">
+        <v>90</v>
+      </c>
+      <c r="E326" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F326" s="15"/>
+      <c r="G326" s="15"/>
+      <c r="H326" s="11"/>
+      <c r="I326" s="11"/>
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
@@ -10317,6 +10372,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
@@ -10328,15 +10392,6 @@
     </SharedWithUsers>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10359,26 +10414,26 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1077" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93279B09-9797-468D-B0A0-3EF97CA96245}"/>
+  <xr:revisionPtr revIDLastSave="1080" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D781C522-8C9B-46D5-8F4B-23C848792F7E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="98">
   <si>
     <t>ID</t>
   </si>
@@ -342,6 +342,12 @@
   </si>
   <si>
     <t>Falla sensor de T° de vapor ingreso TV</t>
+  </si>
+  <si>
+    <t>Alto consumo de agua en caldera</t>
+  </si>
+  <si>
+    <t>Ritura de tubos en calderRH1 y RH2</t>
   </si>
 </sst>
 </file>
@@ -9664,10 +9670,16 @@
       <c r="E326" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F326" s="15"/>
+      <c r="F326" s="15">
+        <v>46188.206250000003</v>
+      </c>
       <c r="G326" s="15"/>
-      <c r="H326" s="11"/>
-      <c r="I326" s="11"/>
+      <c r="H326" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="I326" s="11" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1080" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D781C522-8C9B-46D5-8F4B-23C848792F7E}"/>
+  <xr:revisionPtr revIDLastSave="1081" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80D7BABC-4FE1-40BA-8A58-1C93879A9A47}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -9648,7 +9648,9 @@
       <c r="E325" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F325" s="15"/>
+      <c r="F325" s="15">
+        <v>46186.011111111111</v>
+      </c>
       <c r="G325" s="15"/>
       <c r="H325" s="11"/>
       <c r="I325" s="11"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1081" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80D7BABC-4FE1-40BA-8A58-1C93879A9A47}"/>
+  <xr:revisionPtr revIDLastSave="1082" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EFB4833-2929-4846-A443-7E3E1E861564}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -9651,7 +9651,9 @@
       <c r="F325" s="15">
         <v>46186.011111111111</v>
       </c>
-      <c r="G325" s="15"/>
+      <c r="G325" s="15">
+        <v>46186.729166666664</v>
+      </c>
       <c r="H325" s="11"/>
       <c r="I325" s="11"/>
     </row>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1082" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EFB4833-2929-4846-A443-7E3E1E861564}"/>
+  <xr:revisionPtr revIDLastSave="1088" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D193CF21-9EC5-4D1E-A69E-24BB15F10382}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <definedName name="SegmentaciónDeDatos_Sitio">#N/A</definedName>
     <definedName name="SegmentaciónDeDatos_Unidad">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="100">
   <si>
     <t>ID</t>
   </si>
@@ -348,6 +348,12 @@
   </si>
   <si>
     <t>Ritura de tubos en calderRH1 y RH2</t>
+  </si>
+  <si>
+    <t>Bajo caudal de enfriamiento al cond. Ppal.</t>
+  </si>
+  <si>
+    <t>Falla bba PAJ53 y Paj33 lo cual deja indisponible el Sifon N°2 en cantara.</t>
   </si>
 </sst>
 </file>
@@ -9626,10 +9632,18 @@
       <c r="E324" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F324" s="15"/>
-      <c r="G324" s="15"/>
-      <c r="H324" s="11"/>
-      <c r="I324" s="11"/>
+      <c r="F324" s="15">
+        <v>46186.011111111111</v>
+      </c>
+      <c r="G324" s="15">
+        <v>46186.843055555553</v>
+      </c>
+      <c r="H324" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="I324" s="11" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A325" s="1">
@@ -9654,8 +9668,12 @@
       <c r="G325" s="15">
         <v>46186.729166666664</v>
       </c>
-      <c r="H325" s="11"/>
-      <c r="I325" s="11"/>
+      <c r="H325" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="I325" s="11" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A326" s="1">

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1088" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D193CF21-9EC5-4D1E-A69E-24BB15F10382}"/>
+  <xr:revisionPtr revIDLastSave="1100" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33F45EDB-92FD-46C9-A966-2AD94FA239B0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="100">
   <si>
     <t>ID</t>
   </si>
@@ -778,8 +778,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J326" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J326" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J327" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J327" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1160,7 +1160,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
-  <dimension ref="A9:J332"/>
+  <dimension ref="A9:J333"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -1179,7 +1179,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -9636,7 +9636,7 @@
         <v>46186.011111111111</v>
       </c>
       <c r="G324" s="15">
-        <v>46186.843055555553</v>
+        <v>46186.208333333336</v>
       </c>
       <c r="H324" s="11" t="s">
         <v>98</v>
@@ -9650,29 +9650,29 @@
         <v>314</v>
       </c>
       <c r="B325" s="13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C325" s="16" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D325" s="14">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="E325" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F325" s="15">
-        <v>46186.011111111111</v>
+        <v>46186.208333333336</v>
       </c>
       <c r="G325" s="15">
-        <v>46186.729166666664</v>
+        <v>46186.843055555553</v>
       </c>
       <c r="H325" s="11" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="I325" s="11" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.25">
@@ -9680,31 +9680,58 @@
         <v>315</v>
       </c>
       <c r="B326" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C326" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CEM</v>
+      </c>
+      <c r="D326" s="14">
+        <v>100</v>
+      </c>
+      <c r="E326" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F326" s="15">
+        <v>46186.011111111111</v>
+      </c>
+      <c r="G326" s="15">
+        <v>46186.729166666664</v>
+      </c>
+      <c r="H326" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="I326" s="11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A327" s="1">
+        <v>316</v>
+      </c>
+      <c r="B327" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C326" s="16" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
-        <v>CEM</v>
-      </c>
-      <c r="D326" s="14">
+      <c r="C327" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CEM</v>
+      </c>
+      <c r="D327" s="14">
         <v>90</v>
       </c>
-      <c r="E326" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F326" s="15">
+      <c r="E327" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F327" s="15">
         <v>46188.206250000003</v>
       </c>
-      <c r="G326" s="15"/>
-      <c r="H326" s="11" t="s">
+      <c r="G327" s="15"/>
+      <c r="H327" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="I326" s="11" t="s">
+      <c r="I327" s="11" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A327" s="1"/>
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A328" s="1"/>
@@ -9720,6 +9747,9 @@
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A332" s="1"/>
+    </row>
+    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A333" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1100" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33F45EDB-92FD-46C9-A966-2AD94FA239B0}"/>
+  <xr:revisionPtr revIDLastSave="1104" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6ED28B7B-029A-48CD-997B-2568BCB89D10}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="100">
   <si>
     <t>ID</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>Detalle</t>
+  </si>
+  <si>
+    <t>Verificación</t>
   </si>
   <si>
     <t>CTM1</t>
@@ -120,6 +123,9 @@
   </si>
   <si>
     <t>Kit hidráulico se encuentra descalibrado, bba de respaldo no entra e/s</t>
+  </si>
+  <si>
+    <t>Cerrado</t>
   </si>
   <si>
     <t>Alto consumo de agua en HRSG</t>
@@ -227,6 +233,87 @@
     <t>Corte de correas motriz HP N°3</t>
   </si>
   <si>
+    <t>Desenganche por protección sobre velocidad</t>
+  </si>
+  <si>
+    <t>Actua protección sobre velocidad por perturbaciones de señales en protección.</t>
+  </si>
+  <si>
+    <t>Falla arranque unidad</t>
+  </si>
+  <si>
+    <t>Filtros de succión bombas agua alimentación saturados.</t>
+  </si>
+  <si>
+    <t>Inspección VTI2</t>
+  </si>
+  <si>
+    <t>Se realiza inspección componentea, alinamiento, GAP en VTI2</t>
+  </si>
+  <si>
+    <t>Rotura tubo de caldera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rotura tubo vapor SH </t>
+  </si>
+  <si>
+    <t>Bajo nivel del Domo</t>
+  </si>
+  <si>
+    <t>Trip LAC10 por baja presión de aceite, LAC30 trip por sobreflujo de descarga y LAC20 no entra en servicio de forma automatica</t>
+  </si>
+  <si>
+    <t>Alta diferencia T° gases de escape</t>
+  </si>
+  <si>
+    <t>Trip por diferencial de T° en los gases de escape (ensuciamineto del sensor de medición)</t>
+  </si>
+  <si>
+    <t>Cambio motor eléctrico VAS1</t>
+  </si>
+  <si>
+    <t>Se realiza cambio motor eléctrico VAS1 por alta temperatura en cojinete</t>
+  </si>
+  <si>
+    <t>Posición de desviación VV IGB</t>
+  </si>
+  <si>
+    <t>Falla en tarjeta de control de VIGB del sistema de admisión de aire al compresor de la turbina a gas.</t>
+  </si>
+  <si>
+    <t>Trip Bba. Agua aliemntación LAC30 por baja presión de aceite.</t>
+  </si>
+  <si>
+    <t>Alta T° descarga agua de mar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limpieza de cajas enfrimaineto principal condensador. </t>
+  </si>
+  <si>
+    <t>Falla alimentadores de combustibles.</t>
+  </si>
+  <si>
+    <t>Falla cadena de recuperación Alimentador N°5 y alimentador N°6 en reparación.</t>
+  </si>
+  <si>
+    <t>Protección TV</t>
+  </si>
+  <si>
+    <t>Falla sensor de T° de vapor ingreso TV</t>
+  </si>
+  <si>
+    <t>Bajo caudal de enfriamiento al cond. Ppal.</t>
+  </si>
+  <si>
+    <t>Falla bba PAJ53 y Paj33 lo cual deja indisponible el Sifon N°2 en cantara.</t>
+  </si>
+  <si>
+    <t>Alto consumo de agua en caldera</t>
+  </si>
+  <si>
+    <t>Ritura de tubos en calderRH1 y RH2</t>
+  </si>
+  <si>
     <t>P_Max_Bruta</t>
   </si>
   <si>
@@ -267,93 +354,6 @@
   </si>
   <si>
     <t>FechaFinVigencia</t>
-  </si>
-  <si>
-    <t>Desenganche por protección sobre velocidad</t>
-  </si>
-  <si>
-    <t>Actua protección sobre velocidad por perturbaciones de señales en protección.</t>
-  </si>
-  <si>
-    <t>Falla arranque unidad</t>
-  </si>
-  <si>
-    <t>Filtros de succión bombas agua alimentación saturados.</t>
-  </si>
-  <si>
-    <t>Verificación</t>
-  </si>
-  <si>
-    <t>Cerrado</t>
-  </si>
-  <si>
-    <t>Inspección VTI2</t>
-  </si>
-  <si>
-    <t>Se realiza inspección componentea, alinamiento, GAP en VTI2</t>
-  </si>
-  <si>
-    <t>Rotura tubo de caldera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rotura tubo vapor SH </t>
-  </si>
-  <si>
-    <t>Bajo nivel del Domo</t>
-  </si>
-  <si>
-    <t>Trip LAC10 por baja presión de aceite, LAC30 trip por sobreflujo de descarga y LAC20 no entra en servicio de forma automatica</t>
-  </si>
-  <si>
-    <t>Alta diferencia T° gases de escape</t>
-  </si>
-  <si>
-    <t>Trip por diferencial de T° en los gases de escape (ensuciamineto del sensor de medición)</t>
-  </si>
-  <si>
-    <t>Cambio motor eléctrico VAS1</t>
-  </si>
-  <si>
-    <t>Se realiza cambio motor eléctrico VAS1 por alta temperatura en cojinete</t>
-  </si>
-  <si>
-    <t>Falla en tarjeta de control de VIGB del sistema de admisión de aire al compresor de la turbina a gas.</t>
-  </si>
-  <si>
-    <t>Posición de desviación VV IGB</t>
-  </si>
-  <si>
-    <t>Alta T° descarga agua de mar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limpieza de cajas enfrimaineto principal condensador. </t>
-  </si>
-  <si>
-    <t>Trip Bba. Agua aliemntación LAC30 por baja presión de aceite.</t>
-  </si>
-  <si>
-    <t>Falla alimentadores de combustibles.</t>
-  </si>
-  <si>
-    <t>Falla cadena de recuperación Alimentador N°5 y alimentador N°6 en reparación.</t>
-  </si>
-  <si>
-    <t>Protección TV</t>
-  </si>
-  <si>
-    <t>Falla sensor de T° de vapor ingreso TV</t>
-  </si>
-  <si>
-    <t>Alto consumo de agua en caldera</t>
-  </si>
-  <si>
-    <t>Ritura de tubos en calderRH1 y RH2</t>
-  </si>
-  <si>
-    <t>Bajo caudal de enfriamiento al cond. Ppal.</t>
-  </si>
-  <si>
-    <t>Falla bba PAJ53 y Paj33 lo cual deja indisponible el Sifon N°2 en cantara.</t>
   </si>
 </sst>
 </file>
@@ -778,8 +778,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J327" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J327" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J328" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J328" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1179,7 +1179,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -1211,7 +1211,7 @@
         <v>8</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -1219,7 +1219,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1229,7 +1229,7 @@
         <v>124</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F11" s="15">
         <v>44927</v>
@@ -1245,7 +1245,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F12" s="15">
         <v>44930.447916666664</v>
@@ -1271,7 +1271,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1281,7 +1281,7 @@
         <v>142</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F13" s="15">
         <v>44933.134027777778</v>
@@ -1297,7 +1297,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1307,7 +1307,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F14" s="15">
         <v>44935.831250000003</v>
@@ -1323,7 +1323,7 @@
         <v>5</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1333,7 +1333,7 @@
         <v>210</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F15" s="15">
         <v>44939.951388888891</v>
@@ -1349,7 +1349,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1359,7 +1359,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F16" s="15">
         <v>44943.804166666669</v>
@@ -1375,7 +1375,7 @@
         <v>7</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1385,7 +1385,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F17" s="15">
         <v>44949.084027777775</v>
@@ -1401,7 +1401,7 @@
         <v>8</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1411,7 +1411,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F18" s="15">
         <v>44949.13958333333</v>
@@ -1427,7 +1427,7 @@
         <v>9</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C19" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1437,7 +1437,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F19" s="15">
         <v>44950.40625</v>
@@ -1453,7 +1453,7 @@
         <v>10</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C20" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1463,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F20" s="15">
         <v>44950.636111111111</v>
@@ -1479,7 +1479,7 @@
         <v>11</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C21" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F21" s="15">
         <v>44955.75</v>
@@ -1505,7 +1505,7 @@
         <v>12</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C22" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1515,7 +1515,7 @@
         <v>130</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F22" s="15">
         <v>44955.777083333334</v>
@@ -1531,7 +1531,7 @@
         <v>13</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C23" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1541,7 +1541,7 @@
         <v>140</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F23" s="15">
         <v>44956.24722222222</v>
@@ -1557,7 +1557,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C24" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1567,7 +1567,7 @@
         <v>70</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F24" s="15">
         <v>44957.265972222223</v>
@@ -1583,7 +1583,7 @@
         <v>15</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C25" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1593,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F25" s="15">
         <v>44962.488888888889</v>
@@ -1609,7 +1609,7 @@
         <v>16</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1619,7 +1619,7 @@
         <v>25</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F26" s="15">
         <v>44962.875</v>
@@ -1635,7 +1635,7 @@
         <v>17</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C27" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1645,7 +1645,7 @@
         <v>25</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F27" s="15">
         <v>44963.838888888888</v>
@@ -1661,7 +1661,7 @@
         <v>18</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C28" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1671,7 +1671,7 @@
         <v>100</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F28" s="15">
         <v>44964.821527777778</v>
@@ -1687,7 +1687,7 @@
         <v>19</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C29" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1697,7 +1697,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F29" s="15">
         <v>44966.500694444447</v>
@@ -1713,7 +1713,7 @@
         <v>20</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C30" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1723,7 +1723,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F30" s="15">
         <v>44966.717361111114</v>
@@ -1739,7 +1739,7 @@
         <v>21</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C31" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1749,7 +1749,7 @@
         <v>100</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F31" s="15">
         <v>44967.847916666666</v>
@@ -1765,7 +1765,7 @@
         <v>22</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C32" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F32" s="15">
         <v>44970.777777777781</v>
@@ -1791,7 +1791,7 @@
         <v>23</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C33" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1801,7 +1801,7 @@
         <v>75</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F33" s="15">
         <v>44971.243055555555</v>
@@ -1817,7 +1817,7 @@
         <v>24</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C34" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1827,7 +1827,7 @@
         <v>100</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F34" s="15">
         <v>44971.326388888891</v>
@@ -1843,7 +1843,7 @@
         <v>25</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C35" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1853,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F35" s="15">
         <v>44972.761805555558</v>
@@ -1869,7 +1869,7 @@
         <v>26</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C36" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1879,7 +1879,7 @@
         <v>30</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F36" s="15">
         <v>44972.840277777781</v>
@@ -1895,7 +1895,7 @@
         <v>27</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C37" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1905,7 +1905,7 @@
         <v>30</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F37" s="15">
         <v>44973.10833333333</v>
@@ -1921,7 +1921,7 @@
         <v>28</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C38" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1931,7 +1931,7 @@
         <v>30</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F38" s="15">
         <v>44973.845138888886</v>
@@ -1947,7 +1947,7 @@
         <v>29</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C39" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1957,7 +1957,7 @@
         <v>30</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F39" s="15">
         <v>44973.849305555559</v>
@@ -1973,7 +1973,7 @@
         <v>30</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C40" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -1983,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F40" s="15">
         <v>44975</v>
@@ -1999,7 +1999,7 @@
         <v>31</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C41" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2009,7 +2009,7 @@
         <v>0</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F41" s="15">
         <v>44975.414583333331</v>
@@ -2025,7 +2025,7 @@
         <v>32</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C42" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2035,7 +2035,7 @@
         <v>0</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F42" s="15">
         <v>44978.819444444445</v>
@@ -2051,7 +2051,7 @@
         <v>33</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C43" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2061,7 +2061,7 @@
         <v>85</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F43" s="15">
         <v>44979.900694444441</v>
@@ -2077,7 +2077,7 @@
         <v>34</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C44" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2087,7 +2087,7 @@
         <v>0</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F44" s="15">
         <v>44980.459722222222</v>
@@ -2103,7 +2103,7 @@
         <v>35</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C45" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2113,7 +2113,7 @@
         <v>70</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F45" s="15">
         <v>44982.140277777777</v>
@@ -2129,7 +2129,7 @@
         <v>36</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C46" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2139,7 +2139,7 @@
         <v>90</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F46" s="15">
         <v>44983.083333333336</v>
@@ -2155,7 +2155,7 @@
         <v>37</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C47" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2165,7 +2165,7 @@
         <v>130</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F47" s="15">
         <v>44983.997916666667</v>
@@ -2181,7 +2181,7 @@
         <v>38</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C48" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2191,7 +2191,7 @@
         <v>0</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F48" s="15">
         <v>44994.680555555555</v>
@@ -2207,7 +2207,7 @@
         <v>39</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C49" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2217,7 +2217,7 @@
         <v>0</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F49" s="15">
         <v>44994.680555555555</v>
@@ -2233,7 +2233,7 @@
         <v>40</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C50" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2243,7 +2243,7 @@
         <v>0</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F50" s="15">
         <v>44995.305555555555</v>
@@ -2259,7 +2259,7 @@
         <v>41</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C51" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F51" s="15">
         <v>44998.6875</v>
@@ -2285,7 +2285,7 @@
         <v>42</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C52" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2295,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F52" s="15">
         <v>45003.220138888886</v>
@@ -2311,7 +2311,7 @@
         <v>43</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C53" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2321,7 +2321,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F53" s="15">
         <v>45010.994444444441</v>
@@ -2337,7 +2337,7 @@
         <v>44</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C54" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2347,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F54" s="15">
         <v>45011.21875</v>
@@ -2363,7 +2363,7 @@
         <v>45</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C55" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2373,7 +2373,7 @@
         <v>0</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F55" s="15">
         <v>45011.837500000001</v>
@@ -2389,7 +2389,7 @@
         <v>46</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C56" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2399,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F56" s="15">
         <v>45013.126388888886</v>
@@ -2415,7 +2415,7 @@
         <v>47</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C57" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F57" s="15">
         <v>45015.836111111108</v>
@@ -2441,7 +2441,7 @@
         <v>48</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C58" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2451,7 +2451,7 @@
         <v>0</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F58" s="15">
         <v>45017.836111111108</v>
@@ -2467,7 +2467,7 @@
         <v>49</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C59" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2477,7 +2477,7 @@
         <v>189</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F59" s="15">
         <v>45019.184027777781</v>
@@ -2493,7 +2493,7 @@
         <v>50</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C60" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2503,7 +2503,7 @@
         <v>0</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F60" s="15">
         <v>45020.996527777781</v>
@@ -2519,7 +2519,7 @@
         <v>51</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C61" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2529,7 +2529,7 @@
         <v>189</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F61" s="15">
         <v>45022.345138888886</v>
@@ -2545,7 +2545,7 @@
         <v>52</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C62" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2555,7 +2555,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F62" s="15">
         <v>45026.704861111109</v>
@@ -2571,7 +2571,7 @@
         <v>53</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C63" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2581,7 +2581,7 @@
         <v>85</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F63" s="15">
         <v>45027.711111111108</v>
@@ -2597,7 +2597,7 @@
         <v>54</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C64" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2607,7 +2607,7 @@
         <v>85</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F64" s="15">
         <v>45027.71875</v>
@@ -2623,7 +2623,7 @@
         <v>55</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C65" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2633,7 +2633,7 @@
         <v>0</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F65" s="15">
         <v>45029.12777777778</v>
@@ -2649,7 +2649,7 @@
         <v>56</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C66" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2659,7 +2659,7 @@
         <v>50</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F66" s="15">
         <v>45035.295138888891</v>
@@ -2675,7 +2675,7 @@
         <v>57</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C67" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2685,7 +2685,7 @@
         <v>115</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F67" s="15">
         <v>45037.253472222219</v>
@@ -2701,7 +2701,7 @@
         <v>58</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C68" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2711,7 +2711,7 @@
         <v>120</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F68" s="15">
         <v>45037.783333333333</v>
@@ -2727,7 +2727,7 @@
         <v>59</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C69" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2737,7 +2737,7 @@
         <v>145</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F69" s="15">
         <v>45039.927083333336</v>
@@ -2753,7 +2753,7 @@
         <v>60</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C70" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2763,7 +2763,7 @@
         <v>0</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F70" s="15">
         <v>45040.813888888886</v>
@@ -2779,7 +2779,7 @@
         <v>61</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C71" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F71" s="15">
         <v>45042.328472222223</v>
@@ -2805,7 +2805,7 @@
         <v>62</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C72" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2815,7 +2815,7 @@
         <v>145</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F72" s="15">
         <v>45042.781944444447</v>
@@ -2831,7 +2831,7 @@
         <v>63</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C73" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2841,7 +2841,7 @@
         <v>165</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" s="15">
         <v>45043.364583333336</v>
@@ -2857,7 +2857,7 @@
         <v>64</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C74" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2867,7 +2867,7 @@
         <v>122</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F74" s="15">
         <v>45047.042361111111</v>
@@ -2883,7 +2883,7 @@
         <v>65</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C75" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2893,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F75" s="15">
         <v>45052.635416666664</v>
@@ -2909,7 +2909,7 @@
         <v>66</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C76" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2919,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F76" s="15">
         <v>45055.776388888888</v>
@@ -2935,7 +2935,7 @@
         <v>67</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C77" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2945,7 +2945,7 @@
         <v>96</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F77" s="15">
         <v>45055.822222222225</v>
@@ -2961,7 +2961,7 @@
         <v>68</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C78" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2971,7 +2971,7 @@
         <v>0</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F78" s="15">
         <v>45058.507638888892</v>
@@ -2987,7 +2987,7 @@
         <v>69</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C79" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -2997,7 +2997,7 @@
         <v>120</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F79" s="15">
         <v>45061.666666666664</v>
@@ -3013,7 +3013,7 @@
         <v>70</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C80" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3023,7 +3023,7 @@
         <v>0</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F80" s="15">
         <v>45068.156944444447</v>
@@ -3039,7 +3039,7 @@
         <v>71</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C81" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3049,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F81" s="15">
         <v>45079.692361111112</v>
@@ -3065,7 +3065,7 @@
         <v>72</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C82" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F82" s="15">
         <v>45080.038194444445</v>
@@ -3091,7 +3091,7 @@
         <v>73</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C83" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3101,7 +3101,7 @@
         <v>0</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F83" s="15">
         <v>45085.048611111109</v>
@@ -3117,7 +3117,7 @@
         <v>74</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C84" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3127,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F84" s="15">
         <v>45085.109027777777</v>
@@ -3143,7 +3143,7 @@
         <v>75</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C85" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3153,7 +3153,7 @@
         <v>0</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F85" s="15">
         <v>45091.675000000003</v>
@@ -3169,7 +3169,7 @@
         <v>76</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C86" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3179,7 +3179,7 @@
         <v>189</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F86" s="15">
         <v>45094.098611111112</v>
@@ -3195,7 +3195,7 @@
         <v>77</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C87" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3205,7 +3205,7 @@
         <v>0</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F87" s="15">
         <v>45097.116666666669</v>
@@ -3221,7 +3221,7 @@
         <v>78</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C88" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3231,7 +3231,7 @@
         <v>0</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F88" s="15">
         <v>45105.760416666664</v>
@@ -3247,7 +3247,7 @@
         <v>79</v>
       </c>
       <c r="B89" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C89" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3257,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F89" s="15">
         <v>45106.540277777778</v>
@@ -3273,7 +3273,7 @@
         <v>80</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C90" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3283,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F90" s="15">
         <v>45107.772916666669</v>
@@ -3299,7 +3299,7 @@
         <v>81</v>
       </c>
       <c r="B91" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C91" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F91" s="15">
         <v>45108.753472222219</v>
@@ -3325,7 +3325,7 @@
         <v>82</v>
       </c>
       <c r="B92" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C92" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F92" s="15">
         <v>45108.842361111114</v>
@@ -3351,7 +3351,7 @@
         <v>83</v>
       </c>
       <c r="B93" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C93" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F93" s="15">
         <v>45109.604166666664</v>
@@ -3377,7 +3377,7 @@
         <v>84</v>
       </c>
       <c r="B94" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C94" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3387,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F94" s="15">
         <v>45109.62777777778</v>
@@ -3403,7 +3403,7 @@
         <v>85</v>
       </c>
       <c r="B95" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C95" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3413,7 +3413,7 @@
         <v>0</v>
       </c>
       <c r="E95" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F95" s="15">
         <v>45111.791666666664</v>
@@ -3429,7 +3429,7 @@
         <v>86</v>
       </c>
       <c r="B96" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C96" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="E96" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F96" s="15">
         <v>45113.779861111114</v>
@@ -3455,7 +3455,7 @@
         <v>87</v>
       </c>
       <c r="B97" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C97" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="E97" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F97" s="15">
         <v>45114.775694444441</v>
@@ -3481,7 +3481,7 @@
         <v>88</v>
       </c>
       <c r="B98" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C98" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3491,7 +3491,7 @@
         <v>0</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F98" s="15">
         <v>45117.761111111111</v>
@@ -3507,7 +3507,7 @@
         <v>89</v>
       </c>
       <c r="B99" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C99" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3517,7 +3517,7 @@
         <v>0</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F99" s="15">
         <v>45117.804166666669</v>
@@ -3533,7 +3533,7 @@
         <v>90</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C100" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3543,7 +3543,7 @@
         <v>0</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F100" s="15">
         <v>45120.70416666667</v>
@@ -3559,7 +3559,7 @@
         <v>91</v>
       </c>
       <c r="B101" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C101" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3569,7 +3569,7 @@
         <v>0</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F101" s="15">
         <v>45122.381944444445</v>
@@ -3585,7 +3585,7 @@
         <v>92</v>
       </c>
       <c r="B102" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C102" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F102" s="15">
         <v>45122.54583333333</v>
@@ -3611,7 +3611,7 @@
         <v>93</v>
       </c>
       <c r="B103" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C103" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3621,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F103" s="15">
         <v>45124.541666666664</v>
@@ -3637,7 +3637,7 @@
         <v>94</v>
       </c>
       <c r="B104" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C104" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3647,7 +3647,7 @@
         <v>0</v>
       </c>
       <c r="E104" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F104" s="15">
         <v>45126.739583333336</v>
@@ -3663,7 +3663,7 @@
         <v>95</v>
       </c>
       <c r="B105" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C105" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3673,7 +3673,7 @@
         <v>0</v>
       </c>
       <c r="E105" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F105" s="15">
         <v>45134.799305555556</v>
@@ -3689,7 +3689,7 @@
         <v>96</v>
       </c>
       <c r="B106" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C106" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3699,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="E106" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F106" s="15">
         <v>45137.817361111112</v>
@@ -3715,7 +3715,7 @@
         <v>97</v>
       </c>
       <c r="B107" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C107" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3725,7 +3725,7 @@
         <v>0</v>
       </c>
       <c r="E107" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F107" s="15">
         <v>45138</v>
@@ -3741,7 +3741,7 @@
         <v>98</v>
       </c>
       <c r="B108" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C108" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3751,7 +3751,7 @@
         <v>0</v>
       </c>
       <c r="E108" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F108" s="15">
         <v>45142.810416666667</v>
@@ -3767,7 +3767,7 @@
         <v>99</v>
       </c>
       <c r="B109" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C109" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3777,7 +3777,7 @@
         <v>0</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F109" s="15">
         <v>45143.791666666664</v>
@@ -3793,7 +3793,7 @@
         <v>100</v>
       </c>
       <c r="B110" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C110" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="E110" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F110" s="15">
         <v>45145.788888888892</v>
@@ -3819,7 +3819,7 @@
         <v>101</v>
       </c>
       <c r="B111" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C111" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3829,7 +3829,7 @@
         <v>0</v>
       </c>
       <c r="E111" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F111" s="15">
         <v>45146.311111111114</v>
@@ -3845,7 +3845,7 @@
         <v>102</v>
       </c>
       <c r="B112" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C112" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3855,7 +3855,7 @@
         <v>0</v>
       </c>
       <c r="E112" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F112" s="15">
         <v>45148.792361111111</v>
@@ -3871,7 +3871,7 @@
         <v>103</v>
       </c>
       <c r="B113" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C113" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3881,7 +3881,7 @@
         <v>0</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F113" s="15">
         <v>45157.870138888888</v>
@@ -3897,7 +3897,7 @@
         <v>104</v>
       </c>
       <c r="B114" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C114" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3907,7 +3907,7 @@
         <v>0</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F114" s="15">
         <v>45159.308333333334</v>
@@ -3923,7 +3923,7 @@
         <v>105</v>
       </c>
       <c r="B115" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C115" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3933,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F115" s="15">
         <v>45169.604166666664</v>
@@ -3949,7 +3949,7 @@
         <v>106</v>
       </c>
       <c r="B116" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C116" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3959,7 +3959,7 @@
         <v>0</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F116" s="15">
         <v>45171.625</v>
@@ -3975,7 +3975,7 @@
         <v>107</v>
       </c>
       <c r="B117" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C117" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -3985,7 +3985,7 @@
         <v>0</v>
       </c>
       <c r="E117" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F117" s="15">
         <v>45177.047222222223</v>
@@ -4001,7 +4001,7 @@
         <v>108</v>
       </c>
       <c r="B118" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C118" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4011,7 +4011,7 @@
         <v>0</v>
       </c>
       <c r="E118" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F118" s="15">
         <v>45194.831944444442</v>
@@ -4027,7 +4027,7 @@
         <v>109</v>
       </c>
       <c r="B119" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C119" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4037,7 +4037,7 @@
         <v>110</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F119" s="15">
         <v>45196.001388888886</v>
@@ -4053,7 +4053,7 @@
         <v>110</v>
       </c>
       <c r="B120" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C120" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4063,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F120" s="15">
         <v>45196.293749999997</v>
@@ -4079,7 +4079,7 @@
         <v>111</v>
       </c>
       <c r="B121" s="13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C121" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4089,7 +4089,7 @@
         <v>0</v>
       </c>
       <c r="E121" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F121" s="15">
         <v>45196.320138888892</v>
@@ -4105,7 +4105,7 @@
         <v>112</v>
       </c>
       <c r="B122" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C122" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4115,7 +4115,7 @@
         <v>0</v>
       </c>
       <c r="E122" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F122" s="15">
         <v>45197.996527777781</v>
@@ -4131,7 +4131,7 @@
         <v>113</v>
       </c>
       <c r="B123" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C123" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4141,7 +4141,7 @@
         <v>0</v>
       </c>
       <c r="E123" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F123" s="15">
         <v>45198.865277777775</v>
@@ -4157,7 +4157,7 @@
         <v>114</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C124" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4167,7 +4167,7 @@
         <v>260</v>
       </c>
       <c r="E124" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F124" s="15">
         <v>45202.789583333331</v>
@@ -4183,7 +4183,7 @@
         <v>115</v>
       </c>
       <c r="B125" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C125" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4193,7 +4193,7 @@
         <v>0</v>
       </c>
       <c r="E125" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F125" s="15">
         <v>45207.118055555555</v>
@@ -4209,7 +4209,7 @@
         <v>116</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C126" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4219,7 +4219,7 @@
         <v>0</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F126" s="15">
         <v>45232.663194444445</v>
@@ -4235,7 +4235,7 @@
         <v>117</v>
       </c>
       <c r="B127" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C127" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4245,7 +4245,7 @@
         <v>0</v>
       </c>
       <c r="E127" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F127" s="15">
         <v>45235.90625</v>
@@ -4261,7 +4261,7 @@
         <v>118</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C128" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4271,7 +4271,7 @@
         <v>0</v>
       </c>
       <c r="E128" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F128" s="15">
         <v>45236</v>
@@ -4287,7 +4287,7 @@
         <v>119</v>
       </c>
       <c r="B129" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C129" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4297,7 +4297,7 @@
         <v>0</v>
       </c>
       <c r="E129" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F129" s="15">
         <v>45260.151388888888</v>
@@ -4313,7 +4313,7 @@
         <v>120</v>
       </c>
       <c r="B130" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C130" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4323,7 +4323,7 @@
         <v>0</v>
       </c>
       <c r="E130" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F130" s="15">
         <v>45260.666666666664</v>
@@ -4339,7 +4339,7 @@
         <v>121</v>
       </c>
       <c r="B131" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C131" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4349,7 +4349,7 @@
         <v>0</v>
       </c>
       <c r="E131" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F131" s="15">
         <v>45260.869444444441</v>
@@ -4365,7 +4365,7 @@
         <v>122</v>
       </c>
       <c r="B132" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C132" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4375,7 +4375,7 @@
         <v>0</v>
       </c>
       <c r="E132" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F132" s="15">
         <v>45263.459027777775</v>
@@ -4391,7 +4391,7 @@
         <v>123</v>
       </c>
       <c r="B133" s="13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C133" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4401,7 +4401,7 @@
         <v>0</v>
       </c>
       <c r="E133" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F133" s="15">
         <v>45263.463194444441</v>
@@ -4417,7 +4417,7 @@
         <v>124</v>
       </c>
       <c r="B134" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C134" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4427,7 +4427,7 @@
         <v>0</v>
       </c>
       <c r="E134" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F134" s="15">
         <v>45266.671527777777</v>
@@ -4443,7 +4443,7 @@
         <v>125</v>
       </c>
       <c r="B135" s="13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C135" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4453,7 +4453,7 @@
         <v>0</v>
       </c>
       <c r="E135" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F135" s="15">
         <v>45267</v>
@@ -4469,7 +4469,7 @@
         <v>126</v>
       </c>
       <c r="B136" s="13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C136" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4479,7 +4479,7 @@
         <v>0</v>
       </c>
       <c r="E136" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F136" s="15">
         <v>45267.965277777781</v>
@@ -4495,7 +4495,7 @@
         <v>127</v>
       </c>
       <c r="B137" s="13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C137" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4505,7 +4505,7 @@
         <v>0</v>
       </c>
       <c r="E137" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F137" s="15">
         <v>45268.086111111108</v>
@@ -4521,7 +4521,7 @@
         <v>128</v>
       </c>
       <c r="B138" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C138" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4531,7 +4531,7 @@
         <v>0</v>
       </c>
       <c r="E138" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F138" s="15">
         <v>45268.565972222219</v>
@@ -4547,7 +4547,7 @@
         <v>129</v>
       </c>
       <c r="B139" s="13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C139" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4557,7 +4557,7 @@
         <v>0</v>
       </c>
       <c r="E139" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F139" s="15">
         <v>45269.543749999997</v>
@@ -4573,7 +4573,7 @@
         <v>130</v>
       </c>
       <c r="B140" s="13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C140" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4583,7 +4583,7 @@
         <v>0</v>
       </c>
       <c r="E140" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F140" s="15">
         <v>45269.987500000003</v>
@@ -4599,7 +4599,7 @@
         <v>131</v>
       </c>
       <c r="B141" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C141" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4609,7 +4609,7 @@
         <v>0</v>
       </c>
       <c r="E141" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F141" s="15">
         <v>45270.161111111112</v>
@@ -4625,7 +4625,7 @@
         <v>132</v>
       </c>
       <c r="B142" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C142" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4635,7 +4635,7 @@
         <v>0</v>
       </c>
       <c r="E142" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F142" s="15">
         <v>45270.636111111111</v>
@@ -4651,7 +4651,7 @@
         <v>133</v>
       </c>
       <c r="B143" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C143" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4661,7 +4661,7 @@
         <v>0</v>
       </c>
       <c r="E143" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F143" s="15">
         <v>45658.945138888892</v>
@@ -4677,7 +4677,7 @@
         <v>134</v>
       </c>
       <c r="B144" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C144" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4687,7 +4687,7 @@
         <v>103.07</v>
       </c>
       <c r="E144" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F144" s="15">
         <v>45659.180555555555</v>
@@ -4703,7 +4703,7 @@
         <v>135</v>
       </c>
       <c r="B145" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C145" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4713,7 +4713,7 @@
         <v>80.52</v>
       </c>
       <c r="E145" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F145" s="15">
         <v>45659.25</v>
@@ -4729,7 +4729,7 @@
         <v>136</v>
       </c>
       <c r="B146" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C146" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4739,7 +4739,7 @@
         <v>0</v>
       </c>
       <c r="E146" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F146" s="15">
         <v>45659.397222222222</v>
@@ -4755,7 +4755,7 @@
         <v>137</v>
       </c>
       <c r="B147" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C147" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4765,7 +4765,7 @@
         <v>0</v>
       </c>
       <c r="E147" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F147" s="15">
         <v>45659.758333333331</v>
@@ -4781,7 +4781,7 @@
         <v>138</v>
       </c>
       <c r="B148" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C148" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4791,7 +4791,7 @@
         <v>20</v>
       </c>
       <c r="E148" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F148" s="15">
         <v>45660.459722222222</v>
@@ -4807,7 +4807,7 @@
         <v>139</v>
       </c>
       <c r="B149" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C149" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4817,7 +4817,7 @@
         <v>220</v>
       </c>
       <c r="E149" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F149" s="15">
         <v>45662.833333333336</v>
@@ -4833,7 +4833,7 @@
         <v>140</v>
       </c>
       <c r="B150" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C150" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4843,7 +4843,7 @@
         <v>0</v>
       </c>
       <c r="E150" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F150" s="15">
         <v>45663.923611111109</v>
@@ -4859,7 +4859,7 @@
         <v>141</v>
       </c>
       <c r="B151" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C151" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4869,7 +4869,7 @@
         <v>0</v>
       </c>
       <c r="E151" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F151" s="15">
         <v>45663.964583333334</v>
@@ -4885,7 +4885,7 @@
         <v>142</v>
       </c>
       <c r="B152" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C152" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4895,7 +4895,7 @@
         <v>0</v>
       </c>
       <c r="E152" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F152" s="15">
         <v>45664.708333333336</v>
@@ -4911,7 +4911,7 @@
         <v>143</v>
       </c>
       <c r="B153" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C153" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4921,7 +4921,7 @@
         <v>0</v>
       </c>
       <c r="E153" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F153" s="15">
         <v>45665.574999999997</v>
@@ -4937,7 +4937,7 @@
         <v>144</v>
       </c>
       <c r="B154" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C154" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4947,7 +4947,7 @@
         <v>340</v>
       </c>
       <c r="E154" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F154" s="15">
         <v>45665.979166666664</v>
@@ -4963,7 +4963,7 @@
         <v>145</v>
       </c>
       <c r="B155" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C155" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4973,7 +4973,7 @@
         <v>83.745098517759232</v>
       </c>
       <c r="E155" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F155" s="15">
         <v>45666.820138888892</v>
@@ -4989,7 +4989,7 @@
         <v>146</v>
       </c>
       <c r="B156" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C156" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -4999,7 +4999,7 @@
         <v>0</v>
       </c>
       <c r="E156" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F156" s="15">
         <v>45672.867361111108</v>
@@ -5015,7 +5015,7 @@
         <v>147</v>
       </c>
       <c r="B157" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C157" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5025,7 +5025,7 @@
         <v>220</v>
       </c>
       <c r="E157" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F157" s="15">
         <v>45673.824305555558</v>
@@ -5041,7 +5041,7 @@
         <v>148</v>
       </c>
       <c r="B158" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C158" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5051,7 +5051,7 @@
         <v>250</v>
       </c>
       <c r="E158" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F158" s="15">
         <v>45674.039583333331</v>
@@ -5067,7 +5067,7 @@
         <v>149</v>
       </c>
       <c r="B159" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C159" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5077,7 +5077,7 @@
         <v>300</v>
       </c>
       <c r="E159" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F159" s="15">
         <v>45675.127083333333</v>
@@ -5093,7 +5093,7 @@
         <v>150</v>
       </c>
       <c r="B160" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C160" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5103,7 +5103,7 @@
         <v>0</v>
       </c>
       <c r="E160" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F160" s="15">
         <v>45675.739583333336</v>
@@ -5119,7 +5119,7 @@
         <v>151</v>
       </c>
       <c r="B161" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C161" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5129,7 +5129,7 @@
         <v>355</v>
       </c>
       <c r="E161" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F161" s="15">
         <v>45677.163194444445</v>
@@ -5145,7 +5145,7 @@
         <v>152</v>
       </c>
       <c r="B162" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C162" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5155,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="E162" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F162" s="15">
         <v>45677.224305555559</v>
@@ -5171,7 +5171,7 @@
         <v>153</v>
       </c>
       <c r="B163" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C163" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5181,7 +5181,7 @@
         <v>0</v>
       </c>
       <c r="E163" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F163" s="15">
         <v>45681.357638888891</v>
@@ -5197,7 +5197,7 @@
         <v>154</v>
       </c>
       <c r="B164" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C164" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5207,7 +5207,7 @@
         <v>0</v>
       </c>
       <c r="E164" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F164" s="15">
         <v>45693.038194444445</v>
@@ -5223,7 +5223,7 @@
         <v>155</v>
       </c>
       <c r="B165" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C165" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5233,7 +5233,7 @@
         <v>0</v>
       </c>
       <c r="E165" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F165" s="15">
         <v>45697.510416666664</v>
@@ -5249,7 +5249,7 @@
         <v>156</v>
       </c>
       <c r="B166" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C166" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5259,7 +5259,7 @@
         <v>0</v>
       </c>
       <c r="E166" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F166" s="15">
         <v>45699.036805555559</v>
@@ -5275,7 +5275,7 @@
         <v>157</v>
       </c>
       <c r="B167" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C167" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5285,7 +5285,7 @@
         <v>0</v>
       </c>
       <c r="E167" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F167" s="15">
         <v>45704.229861111111</v>
@@ -5301,7 +5301,7 @@
         <v>158</v>
       </c>
       <c r="B168" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C168" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5311,7 +5311,7 @@
         <v>210</v>
       </c>
       <c r="E168" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F168" s="15">
         <v>45705.25</v>
@@ -5327,7 +5327,7 @@
         <v>159</v>
       </c>
       <c r="B169" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C169" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5337,7 +5337,7 @@
         <v>106</v>
       </c>
       <c r="E169" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F169" s="15">
         <v>45706.152777777781</v>
@@ -5353,7 +5353,7 @@
         <v>160</v>
       </c>
       <c r="B170" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C170" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5363,7 +5363,7 @@
         <v>0</v>
       </c>
       <c r="E170" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F170" s="15">
         <v>45706.211805555555</v>
@@ -5379,7 +5379,7 @@
         <v>161</v>
       </c>
       <c r="B171" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C171" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5389,7 +5389,7 @@
         <v>0</v>
       </c>
       <c r="E171" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F171" s="15">
         <v>45706.700694444444</v>
@@ -5405,7 +5405,7 @@
         <v>162</v>
       </c>
       <c r="B172" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C172" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5415,7 +5415,7 @@
         <v>0</v>
       </c>
       <c r="E172" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F172" s="15">
         <v>45708.625</v>
@@ -5431,7 +5431,7 @@
         <v>163</v>
       </c>
       <c r="B173" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C173" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5441,7 +5441,7 @@
         <v>0</v>
       </c>
       <c r="E173" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F173" s="15">
         <v>45709.972222222219</v>
@@ -5457,7 +5457,7 @@
         <v>164</v>
       </c>
       <c r="B174" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C174" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="E174" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F174" s="15">
         <v>45713.724305555559</v>
@@ -5483,7 +5483,7 @@
         <v>165</v>
       </c>
       <c r="B175" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C175" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5493,7 +5493,7 @@
         <v>106</v>
       </c>
       <c r="E175" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F175" s="15">
         <v>45715.526388888888</v>
@@ -5509,7 +5509,7 @@
         <v>166</v>
       </c>
       <c r="B176" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C176" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5519,7 +5519,7 @@
         <v>130</v>
       </c>
       <c r="E176" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F176" s="15">
         <v>45715.875</v>
@@ -5535,7 +5535,7 @@
         <v>167</v>
       </c>
       <c r="B177" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C177" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5545,7 +5545,7 @@
         <v>180</v>
       </c>
       <c r="E177" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F177" s="15">
         <v>45717.78125</v>
@@ -5561,7 +5561,7 @@
         <v>168</v>
       </c>
       <c r="B178" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C178" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5571,7 +5571,7 @@
         <v>0</v>
       </c>
       <c r="E178" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F178" s="15">
         <v>45721.611805555556</v>
@@ -5587,7 +5587,7 @@
         <v>169</v>
       </c>
       <c r="B179" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C179" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5597,7 +5597,7 @@
         <v>168</v>
       </c>
       <c r="E179" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F179" s="15">
         <v>45728.333333333336</v>
@@ -5613,7 +5613,7 @@
         <v>170</v>
       </c>
       <c r="B180" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C180" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5623,7 +5623,7 @@
         <v>180</v>
       </c>
       <c r="E180" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F180" s="15">
         <v>45729.075694444444</v>
@@ -5639,7 +5639,7 @@
         <v>171</v>
       </c>
       <c r="B181" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C181" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5649,7 +5649,7 @@
         <v>95</v>
       </c>
       <c r="E181" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F181" s="15">
         <v>45732.791666666664</v>
@@ -5665,7 +5665,7 @@
         <v>172</v>
       </c>
       <c r="B182" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C182" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5675,7 +5675,7 @@
         <v>110</v>
       </c>
       <c r="E182" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F182" s="15">
         <v>45732.881944444445</v>
@@ -5691,7 +5691,7 @@
         <v>173</v>
       </c>
       <c r="B183" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C183" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5701,7 +5701,7 @@
         <v>140</v>
       </c>
       <c r="E183" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F183" s="15">
         <v>45740.870833333334</v>
@@ -5717,7 +5717,7 @@
         <v>174</v>
       </c>
       <c r="B184" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C184" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5727,7 +5727,7 @@
         <v>180</v>
       </c>
       <c r="E184" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F184" s="15">
         <v>45741.15625</v>
@@ -5743,7 +5743,7 @@
         <v>175</v>
       </c>
       <c r="B185" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C185" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5753,7 +5753,7 @@
         <v>0</v>
       </c>
       <c r="E185" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F185" s="15">
         <v>45747.081944444442</v>
@@ -5769,7 +5769,7 @@
         <v>176</v>
       </c>
       <c r="B186" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C186" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="E186" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F186" s="15">
         <v>45750.03402777778</v>
@@ -5795,7 +5795,7 @@
         <v>177</v>
       </c>
       <c r="B187" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C187" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5805,7 +5805,7 @@
         <v>0</v>
       </c>
       <c r="E187" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F187" s="15">
         <v>45752.597222222219</v>
@@ -5821,7 +5821,7 @@
         <v>178</v>
       </c>
       <c r="B188" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C188" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5831,7 +5831,7 @@
         <v>83</v>
       </c>
       <c r="E188" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F188" s="15">
         <v>45761.225694444445</v>
@@ -5847,7 +5847,7 @@
         <v>179</v>
       </c>
       <c r="B189" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C189" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5857,7 +5857,7 @@
         <v>60</v>
       </c>
       <c r="E189" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F189" s="15">
         <v>45762.388888888891</v>
@@ -5873,7 +5873,7 @@
         <v>180</v>
       </c>
       <c r="B190" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C190" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5883,7 +5883,7 @@
         <v>185</v>
       </c>
       <c r="E190" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F190" s="15">
         <v>45764.722222222219</v>
@@ -5899,7 +5899,7 @@
         <v>181</v>
       </c>
       <c r="B191" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C191" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5909,7 +5909,7 @@
         <v>0</v>
       </c>
       <c r="E191" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F191" s="15">
         <v>45765.583333333336</v>
@@ -5925,7 +5925,7 @@
         <v>182</v>
       </c>
       <c r="B192" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C192" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5935,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="E192" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F192" s="15">
         <v>45766.544444444444</v>
@@ -5951,7 +5951,7 @@
         <v>183</v>
       </c>
       <c r="B193" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C193" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5961,7 +5961,7 @@
         <v>0</v>
       </c>
       <c r="E193" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F193" s="15">
         <v>45767.606249999997</v>
@@ -5977,7 +5977,7 @@
         <v>184</v>
       </c>
       <c r="B194" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C194" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -5987,7 +5987,7 @@
         <v>0</v>
       </c>
       <c r="E194" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F194" s="15">
         <v>45768.576388888891</v>
@@ -6003,7 +6003,7 @@
         <v>185</v>
       </c>
       <c r="B195" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C195" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6013,7 +6013,7 @@
         <v>83.745098517759232</v>
       </c>
       <c r="E195" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F195" s="15">
         <v>45771.135416666664</v>
@@ -6029,7 +6029,7 @@
         <v>186</v>
       </c>
       <c r="B196" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C196" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6039,7 +6039,7 @@
         <v>0</v>
       </c>
       <c r="E196" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F196" s="15">
         <v>45773.441666666666</v>
@@ -6055,7 +6055,7 @@
         <v>187</v>
       </c>
       <c r="B197" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C197" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6065,7 +6065,7 @@
         <v>0</v>
       </c>
       <c r="E197" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F197" s="15">
         <v>45776.875</v>
@@ -6081,7 +6081,7 @@
         <v>188</v>
       </c>
       <c r="B198" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C198" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6091,7 +6091,7 @@
         <v>0</v>
       </c>
       <c r="E198" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F198" s="15">
         <v>45778.280555555553</v>
@@ -6107,7 +6107,7 @@
         <v>189</v>
       </c>
       <c r="B199" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C199" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6117,7 +6117,7 @@
         <v>0</v>
       </c>
       <c r="E199" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F199" s="15">
         <v>45786.127083333333</v>
@@ -6133,7 +6133,7 @@
         <v>190</v>
       </c>
       <c r="B200" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C200" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="E200" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F200" s="15">
         <v>45786.518750000003</v>
@@ -6159,7 +6159,7 @@
         <v>191</v>
       </c>
       <c r="B201" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C201" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6169,7 +6169,7 @@
         <v>0</v>
       </c>
       <c r="E201" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F201" s="15">
         <v>45790.563194444447</v>
@@ -6185,7 +6185,7 @@
         <v>192</v>
       </c>
       <c r="B202" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C202" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6195,7 +6195,7 @@
         <v>0</v>
       </c>
       <c r="E202" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F202" s="15">
         <v>45795.073611111111</v>
@@ -6211,7 +6211,7 @@
         <v>193</v>
       </c>
       <c r="B203" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C203" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6221,7 +6221,7 @@
         <v>0</v>
       </c>
       <c r="E203" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F203" s="15">
         <v>45796.169444444444</v>
@@ -6237,7 +6237,7 @@
         <v>194</v>
       </c>
       <c r="B204" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C204" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6247,7 +6247,7 @@
         <v>0</v>
       </c>
       <c r="E204" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F204" s="15">
         <v>45800.496527777781</v>
@@ -6263,7 +6263,7 @@
         <v>195</v>
       </c>
       <c r="B205" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C205" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6273,7 +6273,7 @@
         <v>0</v>
       </c>
       <c r="E205" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F205" s="15">
         <v>45801.076388888891</v>
@@ -6289,7 +6289,7 @@
         <v>196</v>
       </c>
       <c r="B206" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C206" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6299,7 +6299,7 @@
         <v>115.95475179382048</v>
       </c>
       <c r="E206" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F206" s="15">
         <v>45801.75</v>
@@ -6315,7 +6315,7 @@
         <v>197</v>
       </c>
       <c r="B207" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C207" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6325,7 +6325,7 @@
         <v>0</v>
       </c>
       <c r="E207" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F207" s="15">
         <v>45801.760416666664</v>
@@ -6341,7 +6341,7 @@
         <v>198</v>
       </c>
       <c r="B208" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C208" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6351,7 +6351,7 @@
         <v>77.303167862546985</v>
       </c>
       <c r="E208" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F208" s="15">
         <v>45802.006944444445</v>
@@ -6367,7 +6367,7 @@
         <v>199</v>
       </c>
       <c r="B209" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C209" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6377,7 +6377,7 @@
         <v>0</v>
       </c>
       <c r="E209" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F209" s="15">
         <v>45802.095833333333</v>
@@ -6393,7 +6393,7 @@
         <v>200</v>
       </c>
       <c r="B210" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C210" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6403,7 +6403,7 @@
         <v>60</v>
       </c>
       <c r="E210" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F210" s="15">
         <v>45803.645833333336</v>
@@ -6419,7 +6419,7 @@
         <v>201</v>
       </c>
       <c r="B211" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C211" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6429,7 +6429,7 @@
         <v>0</v>
       </c>
       <c r="E211" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F211" s="15">
         <v>45810.543749999997</v>
@@ -6445,7 +6445,7 @@
         <v>202</v>
       </c>
       <c r="B212" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C212" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6455,7 +6455,7 @@
         <v>0</v>
       </c>
       <c r="E212" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F212" s="15">
         <v>45811.423611111109</v>
@@ -6471,7 +6471,7 @@
         <v>203</v>
       </c>
       <c r="B213" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C213" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6481,7 +6481,7 @@
         <v>0</v>
       </c>
       <c r="E213" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F213" s="15">
         <v>45812.681250000001</v>
@@ -6497,7 +6497,7 @@
         <v>204</v>
       </c>
       <c r="B214" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C214" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6507,7 +6507,7 @@
         <v>0</v>
       </c>
       <c r="E214" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F214" s="15">
         <v>45813.458333333336</v>
@@ -6523,7 +6523,7 @@
         <v>205</v>
       </c>
       <c r="B215" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C215" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6533,7 +6533,7 @@
         <v>0</v>
       </c>
       <c r="E215" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F215" s="15">
         <v>45815.393055555556</v>
@@ -6549,7 +6549,7 @@
         <v>206</v>
       </c>
       <c r="B216" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C216" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6559,7 +6559,7 @@
         <v>0</v>
       </c>
       <c r="E216" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F216" s="15">
         <v>45820.647916666669</v>
@@ -6575,7 +6575,7 @@
         <v>207</v>
       </c>
       <c r="B217" s="13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C217" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6585,7 +6585,7 @@
         <v>0</v>
       </c>
       <c r="E217" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F217" s="15">
         <v>45825.854861111111</v>
@@ -6601,7 +6601,7 @@
         <v>208</v>
       </c>
       <c r="B218" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C218" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6611,7 +6611,7 @@
         <v>0</v>
       </c>
       <c r="E218" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F218" s="15">
         <v>45827.788194444445</v>
@@ -6627,7 +6627,7 @@
         <v>209</v>
       </c>
       <c r="B219" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C219" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6637,7 +6637,7 @@
         <v>220</v>
       </c>
       <c r="E219" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F219" s="15">
         <v>45828.925000000003</v>
@@ -6653,7 +6653,7 @@
         <v>210</v>
       </c>
       <c r="B220" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C220" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6663,7 +6663,7 @@
         <v>163.9536770259308</v>
       </c>
       <c r="E220" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F220" s="15">
         <v>45833.887499999997</v>
@@ -6679,7 +6679,7 @@
         <v>211</v>
       </c>
       <c r="B221" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C221" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6689,7 +6689,7 @@
         <v>70</v>
       </c>
       <c r="E221" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F221" s="15">
         <v>45837.635416666664</v>
@@ -6705,7 +6705,7 @@
         <v>212</v>
       </c>
       <c r="B222" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C222" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6715,7 +6715,7 @@
         <v>70</v>
       </c>
       <c r="E222" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F222" s="15">
         <v>45837.635416666664</v>
@@ -6731,7 +6731,7 @@
         <v>213</v>
       </c>
       <c r="B223" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C223" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6741,7 +6741,7 @@
         <v>0</v>
       </c>
       <c r="E223" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F223" s="15">
         <v>45842.489583333336</v>
@@ -6757,7 +6757,7 @@
         <v>214</v>
       </c>
       <c r="B224" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C224" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6767,7 +6767,7 @@
         <v>0</v>
       </c>
       <c r="E224" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F224" s="15">
         <v>45844.583333333336</v>
@@ -6783,7 +6783,7 @@
         <v>215</v>
       </c>
       <c r="B225" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C225" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6793,7 +6793,7 @@
         <v>124</v>
       </c>
       <c r="E225" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F225" s="15">
         <v>45844.726388888892</v>
@@ -6809,7 +6809,7 @@
         <v>216</v>
       </c>
       <c r="B226" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C226" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6819,7 +6819,7 @@
         <v>0</v>
       </c>
       <c r="E226" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F226" s="15">
         <v>45845.951388888891</v>
@@ -6835,7 +6835,7 @@
         <v>217</v>
       </c>
       <c r="B227" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C227" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6845,7 +6845,7 @@
         <v>210</v>
       </c>
       <c r="E227" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F227" s="15">
         <v>45846.775000000001</v>
@@ -6861,7 +6861,7 @@
         <v>218</v>
       </c>
       <c r="B228" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C228" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6871,7 +6871,7 @@
         <v>0</v>
       </c>
       <c r="E228" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F228" s="15">
         <v>45847.393750000003</v>
@@ -6887,7 +6887,7 @@
         <v>219</v>
       </c>
       <c r="B229" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C229" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6897,7 +6897,7 @@
         <v>200</v>
       </c>
       <c r="E229" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F229" s="15">
         <v>45850.663194444445</v>
@@ -6913,7 +6913,7 @@
         <v>220</v>
       </c>
       <c r="B230" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C230" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6923,7 +6923,7 @@
         <v>70</v>
       </c>
       <c r="E230" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F230" s="15">
         <v>45852.502083333333</v>
@@ -6939,7 +6939,7 @@
         <v>221</v>
       </c>
       <c r="B231" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C231" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6949,7 +6949,7 @@
         <v>70</v>
       </c>
       <c r="E231" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F231" s="15">
         <v>45852.502083333333</v>
@@ -6965,7 +6965,7 @@
         <v>222</v>
       </c>
       <c r="B232" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C232" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -6975,7 +6975,7 @@
         <v>210</v>
       </c>
       <c r="E232" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F232" s="15">
         <v>45853.768750000003</v>
@@ -6991,7 +6991,7 @@
         <v>223</v>
       </c>
       <c r="B233" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C233" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7001,7 +7001,7 @@
         <v>220</v>
       </c>
       <c r="E233" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F233" s="15">
         <v>45858.90902777778</v>
@@ -7017,7 +7017,7 @@
         <v>224</v>
       </c>
       <c r="B234" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C234" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7027,7 +7027,7 @@
         <v>0</v>
       </c>
       <c r="E234" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F234" s="15">
         <v>45859.583333333336</v>
@@ -7043,7 +7043,7 @@
         <v>225</v>
       </c>
       <c r="B235" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C235" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7053,7 +7053,7 @@
         <v>0</v>
       </c>
       <c r="E235" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F235" s="15">
         <v>45860.834027777775</v>
@@ -7069,7 +7069,7 @@
         <v>226</v>
       </c>
       <c r="B236" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C236" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7079,7 +7079,7 @@
         <v>0</v>
       </c>
       <c r="E236" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F236" s="15">
         <v>45863.583333333336</v>
@@ -7095,7 +7095,7 @@
         <v>227</v>
       </c>
       <c r="B237" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C237" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7105,7 +7105,7 @@
         <v>0</v>
       </c>
       <c r="E237" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F237" s="15">
         <v>45866.988888888889</v>
@@ -7121,7 +7121,7 @@
         <v>228</v>
       </c>
       <c r="B238" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C238" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7131,7 +7131,7 @@
         <v>0</v>
       </c>
       <c r="E238" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F238" s="15">
         <v>45869.39166666667</v>
@@ -7147,7 +7147,7 @@
         <v>229</v>
       </c>
       <c r="B239" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C239" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7157,7 +7157,7 @@
         <v>0</v>
       </c>
       <c r="E239" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F239" s="15">
         <v>45869.507638888892</v>
@@ -7173,7 +7173,7 @@
         <v>230</v>
       </c>
       <c r="B240" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C240" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7183,7 +7183,7 @@
         <v>0</v>
       </c>
       <c r="E240" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F240" s="15">
         <v>45874.413888888892</v>
@@ -7199,7 +7199,7 @@
         <v>231</v>
       </c>
       <c r="B241" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C241" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7209,7 +7209,7 @@
         <v>300</v>
       </c>
       <c r="E241" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F241" s="15">
         <v>45876.074999999997</v>
@@ -7225,7 +7225,7 @@
         <v>232</v>
       </c>
       <c r="B242" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C242" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7235,7 +7235,7 @@
         <v>0</v>
       </c>
       <c r="E242" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F242" s="15">
         <v>45876.147916666669</v>
@@ -7251,7 +7251,7 @@
         <v>233</v>
       </c>
       <c r="B243" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C243" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7261,7 +7261,7 @@
         <v>85</v>
       </c>
       <c r="E243" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F243" s="15">
         <v>45876.795138888891</v>
@@ -7277,7 +7277,7 @@
         <v>234</v>
       </c>
       <c r="B244" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C244" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7287,7 +7287,7 @@
         <v>0</v>
       </c>
       <c r="E244" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F244" s="15">
         <v>45880.761805555558</v>
@@ -7303,7 +7303,7 @@
         <v>235</v>
       </c>
       <c r="B245" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C245" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7313,7 +7313,7 @@
         <v>0</v>
       </c>
       <c r="E245" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F245" s="15">
         <v>45883.34097222222</v>
@@ -7329,7 +7329,7 @@
         <v>236</v>
       </c>
       <c r="B246" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C246" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7339,7 +7339,7 @@
         <v>47</v>
       </c>
       <c r="E246" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F246" s="15">
         <v>45883.771527777775</v>
@@ -7355,7 +7355,7 @@
         <v>237</v>
       </c>
       <c r="B247" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C247" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7365,7 +7365,7 @@
         <v>200</v>
       </c>
       <c r="E247" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F247" s="15">
         <v>45888.741666666669</v>
@@ -7381,7 +7381,7 @@
         <v>238</v>
       </c>
       <c r="B248" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C248" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7391,7 +7391,7 @@
         <v>0</v>
       </c>
       <c r="E248" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F248" s="15">
         <v>45891.650694444441</v>
@@ -7407,7 +7407,7 @@
         <v>239</v>
       </c>
       <c r="B249" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C249" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7417,7 +7417,7 @@
         <v>0</v>
       </c>
       <c r="E249" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F249" s="15">
         <v>45900.981249999997</v>
@@ -7433,7 +7433,7 @@
         <v>240</v>
       </c>
       <c r="B250" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C250" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7443,7 +7443,7 @@
         <v>250</v>
       </c>
       <c r="E250" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F250" s="15">
         <v>45908.064583333333</v>
@@ -7459,7 +7459,7 @@
         <v>241</v>
       </c>
       <c r="B251" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C251" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7469,7 +7469,7 @@
         <v>0</v>
       </c>
       <c r="E251" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F251" s="15">
         <v>45910.459722222222</v>
@@ -7485,7 +7485,7 @@
         <v>242</v>
       </c>
       <c r="B252" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C252" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7495,7 +7495,7 @@
         <v>0</v>
       </c>
       <c r="E252" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F252" s="15">
         <v>45912.831944444442</v>
@@ -7511,7 +7511,7 @@
         <v>243</v>
       </c>
       <c r="B253" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C253" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7521,7 +7521,7 @@
         <v>106</v>
       </c>
       <c r="E253" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F253" s="15">
         <v>45915.876388888886</v>
@@ -7537,7 +7537,7 @@
         <v>244</v>
       </c>
       <c r="B254" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C254" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7547,7 +7547,7 @@
         <v>330</v>
       </c>
       <c r="E254" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F254" s="15">
         <v>45916.833333333336</v>
@@ -7563,7 +7563,7 @@
         <v>245</v>
       </c>
       <c r="B255" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C255" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7573,7 +7573,7 @@
         <v>0</v>
       </c>
       <c r="E255" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F255" s="15">
         <v>45929.609722222223</v>
@@ -7589,7 +7589,7 @@
         <v>246</v>
       </c>
       <c r="B256" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C256" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7599,7 +7599,7 @@
         <v>0</v>
       </c>
       <c r="E256" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F256" s="15">
         <v>45932.822222222225</v>
@@ -7615,7 +7615,7 @@
         <v>247</v>
       </c>
       <c r="B257" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C257" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7625,7 +7625,7 @@
         <v>0</v>
       </c>
       <c r="E257" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F257" s="15">
         <v>45934.320138888892</v>
@@ -7641,7 +7641,7 @@
         <v>248</v>
       </c>
       <c r="B258" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C258" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7651,7 +7651,7 @@
         <v>0</v>
       </c>
       <c r="E258" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F258" s="15">
         <v>45936.256249999999</v>
@@ -7667,7 +7667,7 @@
         <v>249</v>
       </c>
       <c r="B259" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C259" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7677,7 +7677,7 @@
         <v>0</v>
       </c>
       <c r="E259" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F259" s="15">
         <v>45939.625</v>
@@ -7693,7 +7693,7 @@
         <v>250</v>
       </c>
       <c r="B260" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C260" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7703,7 +7703,7 @@
         <v>150.91</v>
       </c>
       <c r="E260" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F260" s="15">
         <v>45945.079861111109</v>
@@ -7719,7 +7719,7 @@
         <v>251</v>
       </c>
       <c r="B261" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C261" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7729,7 +7729,7 @@
         <v>0</v>
       </c>
       <c r="E261" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F261" s="15">
         <v>45947.802777777775</v>
@@ -7745,7 +7745,7 @@
         <v>252</v>
       </c>
       <c r="B262" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C262" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7755,7 +7755,7 @@
         <v>0</v>
       </c>
       <c r="E262" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F262" s="15">
         <v>45951.710416666669</v>
@@ -7771,7 +7771,7 @@
         <v>253</v>
       </c>
       <c r="B263" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C263" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7781,7 +7781,7 @@
         <v>200</v>
       </c>
       <c r="E263" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F263" s="15">
         <v>45954.886111111111</v>
@@ -7797,7 +7797,7 @@
         <v>254</v>
       </c>
       <c r="B264" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C264" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7807,7 +7807,7 @@
         <v>220</v>
       </c>
       <c r="E264" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F264" s="15">
         <v>45959.863194444442</v>
@@ -7823,7 +7823,7 @@
         <v>255</v>
       </c>
       <c r="B265" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C265" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7833,7 +7833,7 @@
         <v>203.41</v>
       </c>
       <c r="E265" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F265" s="15">
         <v>45960.864583333336</v>
@@ -7849,7 +7849,7 @@
         <v>256</v>
       </c>
       <c r="B266" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C266" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7859,7 +7859,7 @@
         <v>0</v>
       </c>
       <c r="E266" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F266" s="15">
         <v>45960.916666666664</v>
@@ -7875,7 +7875,7 @@
         <v>257</v>
       </c>
       <c r="B267" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C267" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7885,7 +7885,7 @@
         <v>150.91</v>
       </c>
       <c r="E267" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F267" s="15">
         <v>45963.875</v>
@@ -7901,7 +7901,7 @@
         <v>258</v>
       </c>
       <c r="B268" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C268" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7911,7 +7911,7 @@
         <v>0</v>
       </c>
       <c r="E268" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F268" s="15">
         <v>45965.224305555559</v>
@@ -7927,7 +7927,7 @@
         <v>259</v>
       </c>
       <c r="B269" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C269" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7937,7 +7937,7 @@
         <v>131.22999999999999</v>
       </c>
       <c r="E269" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F269" s="15">
         <v>45965.870833333334</v>
@@ -7953,7 +7953,7 @@
         <v>260</v>
       </c>
       <c r="B270" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C270" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7963,7 +7963,7 @@
         <v>85.3</v>
       </c>
       <c r="E270" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F270" s="15">
         <v>45966.193055555559</v>
@@ -7979,7 +7979,7 @@
         <v>261</v>
       </c>
       <c r="B271" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C271" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -7989,7 +7989,7 @@
         <v>85.3</v>
       </c>
       <c r="E271" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F271" s="15">
         <v>45966.258333333331</v>
@@ -8005,7 +8005,7 @@
         <v>262</v>
       </c>
       <c r="B272" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C272" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8015,7 +8015,7 @@
         <v>196.85</v>
       </c>
       <c r="E272" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F272" s="15">
         <v>45969.253472222219</v>
@@ -8031,7 +8031,7 @@
         <v>263</v>
       </c>
       <c r="B273" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C273" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8041,7 +8041,7 @@
         <v>220</v>
       </c>
       <c r="E273" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F273" s="15">
         <v>45972.041666666664</v>
@@ -8057,7 +8057,7 @@
         <v>264</v>
       </c>
       <c r="B274" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C274" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8067,7 +8067,7 @@
         <v>110</v>
       </c>
       <c r="E274" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F274" s="15">
         <v>45972.739583333336</v>
@@ -8083,7 +8083,7 @@
         <v>265</v>
       </c>
       <c r="B275" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C275" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8093,7 +8093,7 @@
         <v>220</v>
       </c>
       <c r="E275" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F275" s="15">
         <v>45972.888888888891</v>
@@ -8109,7 +8109,7 @@
         <v>266</v>
       </c>
       <c r="B276" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C276" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8119,7 +8119,7 @@
         <v>0</v>
       </c>
       <c r="E276" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F276" s="15">
         <v>45974.01458333333</v>
@@ -8135,7 +8135,7 @@
         <v>267</v>
       </c>
       <c r="B277" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C277" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8145,7 +8145,7 @@
         <v>203.41</v>
       </c>
       <c r="E277" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F277" s="15">
         <v>45979.871527777781</v>
@@ -8161,7 +8161,7 @@
         <v>268</v>
       </c>
       <c r="B278" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C278" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8171,7 +8171,7 @@
         <v>210</v>
       </c>
       <c r="E278" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F278" s="15">
         <v>45980.773611111108</v>
@@ -8187,7 +8187,7 @@
         <v>269</v>
       </c>
       <c r="B279" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C279" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8197,7 +8197,7 @@
         <v>0</v>
       </c>
       <c r="E279" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F279" s="15">
         <v>45997.393750000003</v>
@@ -8213,7 +8213,7 @@
         <v>270</v>
       </c>
       <c r="B280" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C280" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8223,7 +8223,7 @@
         <v>0</v>
       </c>
       <c r="E280" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F280" s="15">
         <v>45998.750694444447</v>
@@ -8239,7 +8239,7 @@
         <v>271</v>
       </c>
       <c r="B281" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C281" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8249,7 +8249,7 @@
         <v>100</v>
       </c>
       <c r="E281" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F281" s="15">
         <v>46000.805555555555</v>
@@ -8265,7 +8265,7 @@
         <v>272</v>
       </c>
       <c r="B282" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C282" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8275,7 +8275,7 @@
         <v>100</v>
       </c>
       <c r="E282" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F282" s="15">
         <v>46000.805555555555</v>
@@ -8291,7 +8291,7 @@
         <v>273</v>
       </c>
       <c r="B283" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C283" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8301,7 +8301,7 @@
         <v>0</v>
       </c>
       <c r="E283" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F283" s="15">
         <v>46005.275694444441</v>
@@ -8317,7 +8317,7 @@
         <v>274</v>
       </c>
       <c r="B284" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C284" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8327,7 +8327,7 @@
         <v>0</v>
       </c>
       <c r="E284" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F284" s="15">
         <v>46017.061111111114</v>
@@ -8343,7 +8343,7 @@
         <v>275</v>
       </c>
       <c r="B285" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C285" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8353,7 +8353,7 @@
         <v>0</v>
       </c>
       <c r="E285" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F285" s="15">
         <v>46022.899305555555</v>
@@ -8369,7 +8369,7 @@
         <v>276</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C286" s="1" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8379,7 +8379,7 @@
         <v>0</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F286" s="6">
         <v>46025.93472222222</v>
@@ -8388,13 +8388,13 @@
         <v>46026.004861111112</v>
       </c>
       <c r="H286" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I286" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J286" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.25">
@@ -8402,7 +8402,7 @@
         <v>277</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C287" s="1" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8412,7 +8412,7 @@
         <v>0</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F287" s="6">
         <v>46036.70416666667</v>
@@ -8421,13 +8421,13 @@
         <v>46039.024305555555</v>
       </c>
       <c r="H287" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I287" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="J287" s="13" t="s">
         <v>23</v>
-      </c>
-      <c r="J287" s="13" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.25">
@@ -8435,7 +8435,7 @@
         <v>278</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C288" s="1" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8445,7 +8445,7 @@
         <v>0</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F288" s="6">
         <v>46059.571527777778</v>
@@ -8454,13 +8454,13 @@
         <v>46059.804861111108</v>
       </c>
       <c r="H288" s="10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I288" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J288" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.25">
@@ -8468,7 +8468,7 @@
         <v>279</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C289" s="1" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8478,7 +8478,7 @@
         <v>158.37</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F289" s="6">
         <v>46059.595833333333</v>
@@ -8487,13 +8487,13 @@
         <v>46059.654861111114</v>
       </c>
       <c r="H289" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I289" s="10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J289" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.25">
@@ -8501,7 +8501,7 @@
         <v>280</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C290" s="1" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8511,7 +8511,7 @@
         <v>262.08</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F290" s="6">
         <v>46060.808333333334</v>
@@ -8520,13 +8520,13 @@
         <v>46060.820138888892</v>
       </c>
       <c r="H290" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I290" s="10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J290" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.25">
@@ -8534,7 +8534,7 @@
         <v>281</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C291" s="1" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8544,7 +8544,7 @@
         <v>0</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F291" s="6">
         <v>46065.659722222219</v>
@@ -8553,13 +8553,13 @@
         <v>46065.696527777778</v>
       </c>
       <c r="H291" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I291" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J291" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.25">
@@ -8567,7 +8567,7 @@
         <v>282</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C292" s="1" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8577,7 +8577,7 @@
         <v>0</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F292" s="6">
         <v>46066.063194444447</v>
@@ -8586,13 +8586,13 @@
         <v>46066.169444444444</v>
       </c>
       <c r="H292" s="10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I292" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J292" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.25">
@@ -8600,7 +8600,7 @@
         <v>283</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C293" s="1" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8610,7 +8610,7 @@
         <v>0</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F293" s="6">
         <v>46070.286805555559</v>
@@ -8619,13 +8619,13 @@
         <v>46070.676388888889</v>
       </c>
       <c r="H293" s="12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I293" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J293" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.25">
@@ -8633,7 +8633,7 @@
         <v>284</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C294" s="4" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8643,7 +8643,7 @@
         <v>0</v>
       </c>
       <c r="E294" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F294" s="9">
         <v>46070.724305555559</v>
@@ -8652,13 +8652,13 @@
         <v>46070.757638888892</v>
       </c>
       <c r="H294" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I294" s="10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J294" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.25">
@@ -8666,7 +8666,7 @@
         <v>285</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C295" s="1" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8676,7 +8676,7 @@
         <v>0</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F295" s="6">
         <v>46070.825694444444</v>
@@ -8685,13 +8685,13 @@
         <v>46070.897222222222</v>
       </c>
       <c r="H295" s="12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I295" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J295" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.25">
@@ -8699,7 +8699,7 @@
         <v>286</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C296" s="4" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8709,7 +8709,7 @@
         <v>100</v>
       </c>
       <c r="E296" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F296" s="9">
         <v>46070.836805555555</v>
@@ -8718,13 +8718,13 @@
         <v>46070.870833333334</v>
       </c>
       <c r="H296" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I296" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J296" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.25">
@@ -8732,7 +8732,7 @@
         <v>287</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C297" s="4" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8742,7 +8742,7 @@
         <v>0</v>
       </c>
       <c r="E297" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F297" s="9">
         <v>46074.788888888892</v>
@@ -8751,13 +8751,13 @@
         <v>46074.916666666664</v>
       </c>
       <c r="H297" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I297" s="10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J297" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.25">
@@ -8765,7 +8765,7 @@
         <v>288</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C298" s="1" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8775,7 +8775,7 @@
         <v>115</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F298" s="6">
         <v>46082.008333333331</v>
@@ -8784,13 +8784,13 @@
         <v>46082.041666666664</v>
       </c>
       <c r="H298" s="10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I298" s="10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J298" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.25">
@@ -8798,7 +8798,7 @@
         <v>289</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C299" s="1" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8808,7 +8808,7 @@
         <v>70</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F299" s="6">
         <v>46082.041666666664</v>
@@ -8817,13 +8817,13 @@
         <v>46082.061805555553</v>
       </c>
       <c r="H299" s="10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I299" s="10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J299" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.25">
@@ -8831,7 +8831,7 @@
         <v>290</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C300" s="1" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8841,7 +8841,7 @@
         <v>60</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F300" s="6">
         <v>46084.739583333336</v>
@@ -8850,13 +8850,13 @@
         <v>46088.0625</v>
       </c>
       <c r="H300" s="10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I300" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J300" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.25">
@@ -8864,7 +8864,7 @@
         <v>291</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C301" s="4" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8874,7 +8874,7 @@
         <v>125</v>
       </c>
       <c r="E301" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F301" s="9">
         <v>46088.201388888891</v>
@@ -8883,13 +8883,13 @@
         <v>46088.547222222223</v>
       </c>
       <c r="H301" s="10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I301" s="10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J301" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.25">
@@ -8897,7 +8897,7 @@
         <v>292</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C302" s="4" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8907,7 +8907,7 @@
         <v>35</v>
       </c>
       <c r="E302" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F302" s="9">
         <v>46092.44027777778</v>
@@ -8916,13 +8916,13 @@
         <v>46092.8125</v>
       </c>
       <c r="H302" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I302" s="10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J302" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="303" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -8930,7 +8930,7 @@
         <v>293</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C303" s="4" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8940,7 +8940,7 @@
         <v>0</v>
       </c>
       <c r="E303" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F303" s="9">
         <v>46093.331250000003</v>
@@ -8949,13 +8949,13 @@
         <v>46093.396527777775</v>
       </c>
       <c r="H303" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I303" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J303" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="304" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -8963,7 +8963,7 @@
         <v>294</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C304" s="1" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -8973,7 +8973,7 @@
         <v>70</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F304" s="6">
         <v>46100.088888888888</v>
@@ -8982,13 +8982,13 @@
         <v>46100.585416666669</v>
       </c>
       <c r="H304" s="12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I304" s="10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J304" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.25">
@@ -8996,7 +8996,7 @@
         <v>295</v>
       </c>
       <c r="B305" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C305" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -9006,7 +9006,7 @@
         <v>0</v>
       </c>
       <c r="E305" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F305" s="15">
         <v>46107.050694444442</v>
@@ -9015,13 +9015,13 @@
         <v>46107.477777777778</v>
       </c>
       <c r="H305" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I305" s="11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J305" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.25">
@@ -9029,7 +9029,7 @@
         <v>296</v>
       </c>
       <c r="B306" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C306" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -9039,7 +9039,7 @@
         <v>0</v>
       </c>
       <c r="E306" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F306" s="15">
         <v>46110.525000000001</v>
@@ -9048,13 +9048,13 @@
         <v>46111.086805555555</v>
       </c>
       <c r="H306" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I306" s="11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J306" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.25">
@@ -9062,7 +9062,7 @@
         <v>297</v>
       </c>
       <c r="B307" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C307" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -9072,7 +9072,7 @@
         <v>0</v>
       </c>
       <c r="E307" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F307" s="15">
         <v>46119.122916666667</v>
@@ -9081,13 +9081,13 @@
         <v>46119.466666666667</v>
       </c>
       <c r="H307" s="11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I307" s="11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J307" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.25">
@@ -9095,7 +9095,7 @@
         <v>298</v>
       </c>
       <c r="B308" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C308" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -9105,7 +9105,7 @@
         <v>0</v>
       </c>
       <c r="E308" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F308" s="15">
         <v>46123.663194444445</v>
@@ -9114,13 +9114,13 @@
         <v>46123.681944444441</v>
       </c>
       <c r="H308" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I308" s="11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J308" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.25">
@@ -9128,7 +9128,7 @@
         <v>298</v>
       </c>
       <c r="B309" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C309" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -9138,7 +9138,7 @@
         <v>0</v>
       </c>
       <c r="E309" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F309" s="15">
         <v>46141.029166666667</v>
@@ -9147,13 +9147,13 @@
         <v>46141.057638888888</v>
       </c>
       <c r="H309" s="11" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="I309" s="11" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="J309" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.25">
@@ -9161,7 +9161,7 @@
         <v>299</v>
       </c>
       <c r="B310" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C310" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -9171,7 +9171,7 @@
         <v>0</v>
       </c>
       <c r="E310" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F310" s="15">
         <v>46141.638194444444</v>
@@ -9180,13 +9180,13 @@
         <v>46143.779166666667</v>
       </c>
       <c r="H310" s="11" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="I310" s="11" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="J310" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.25">
@@ -9194,7 +9194,7 @@
         <v>300</v>
       </c>
       <c r="B311" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C311" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -9204,7 +9204,7 @@
         <v>80</v>
       </c>
       <c r="E311" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F311" s="15">
         <v>46144.731249999997</v>
@@ -9213,13 +9213,13 @@
         <v>46144.795138888891</v>
       </c>
       <c r="H311" s="11" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="I311" s="11" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="J311" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.25">
@@ -9227,7 +9227,7 @@
         <v>301</v>
       </c>
       <c r="B312" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C312" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -9237,7 +9237,7 @@
         <v>0</v>
       </c>
       <c r="E312" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F312" s="15">
         <v>46151.263194444444</v>
@@ -9246,13 +9246,13 @@
         <v>46163.041666666664</v>
       </c>
       <c r="H312" s="11" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="I312" s="11" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="J312" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.25">
@@ -9260,7 +9260,7 @@
         <v>302</v>
       </c>
       <c r="B313" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C313" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -9270,7 +9270,7 @@
         <v>0</v>
       </c>
       <c r="E313" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F313" s="15">
         <v>46154.693055555559</v>
@@ -9279,13 +9279,13 @@
         <v>46154.719444444447</v>
       </c>
       <c r="H313" s="11" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="I313" s="11" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="J313" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.25">
@@ -9293,7 +9293,7 @@
         <v>303</v>
       </c>
       <c r="B314" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C314" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -9303,7 +9303,7 @@
         <v>0</v>
       </c>
       <c r="E314" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F314" s="15">
         <v>46156.012499999997</v>
@@ -9312,13 +9312,13 @@
         <v>46156.082638888889</v>
       </c>
       <c r="H314" s="11" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="I314" s="11" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="J314" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.25">
@@ -9326,7 +9326,7 @@
         <v>304</v>
       </c>
       <c r="B315" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C315" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -9336,7 +9336,7 @@
         <v>0</v>
       </c>
       <c r="E315" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F315" s="15">
         <v>46156.085416666669</v>
@@ -9345,13 +9345,13 @@
         <v>46156.152777777781</v>
       </c>
       <c r="H315" s="11" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="I315" s="11" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="J315" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.25">
@@ -9359,7 +9359,7 @@
         <v>305</v>
       </c>
       <c r="B316" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C316" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -9369,7 +9369,7 @@
         <v>70</v>
       </c>
       <c r="E316" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F316" s="15">
         <v>46158.34375</v>
@@ -9378,13 +9378,13 @@
         <v>46158.885416666664</v>
       </c>
       <c r="H316" s="11" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="I316" s="11" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="J316" s="13" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.25">
@@ -9392,7 +9392,7 @@
         <v>306</v>
       </c>
       <c r="B317" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C317" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -9402,7 +9402,7 @@
         <v>0</v>
       </c>
       <c r="E317" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F317" s="15">
         <v>46163.160416666666</v>
@@ -9411,13 +9411,13 @@
         <v>46163.326388888891</v>
       </c>
       <c r="H317" s="11" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="I317" s="11" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="J317" s="1" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.25">
@@ -9425,7 +9425,7 @@
         <v>307</v>
       </c>
       <c r="B318" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C318" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -9435,7 +9435,7 @@
         <v>0</v>
       </c>
       <c r="E318" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F318" s="15">
         <v>46164.215277777781</v>
@@ -9444,13 +9444,13 @@
         <v>46164.252083333333</v>
       </c>
       <c r="H318" s="11" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="I318" s="11" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="J318" s="1" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.25">
@@ -9458,7 +9458,7 @@
         <v>308</v>
       </c>
       <c r="B319" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C319" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -9468,7 +9468,7 @@
         <v>0</v>
       </c>
       <c r="E319" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F319" s="15">
         <v>46164.556944444441</v>
@@ -9477,13 +9477,13 @@
         <v>46164.853472222225</v>
       </c>
       <c r="H319" s="11" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="I319" s="11" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="J319" s="1" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.25">
@@ -9491,7 +9491,7 @@
         <v>309</v>
       </c>
       <c r="B320" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C320" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -9501,7 +9501,7 @@
         <v>70</v>
       </c>
       <c r="E320" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F320" s="15">
         <v>46171.208333333336</v>
@@ -9510,13 +9510,13 @@
         <v>46171.681250000001</v>
       </c>
       <c r="H320" s="11" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="I320" s="11" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J320" s="1" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.25">
@@ -9524,7 +9524,7 @@
         <v>310</v>
       </c>
       <c r="B321" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C321" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -9534,7 +9534,7 @@
         <v>70</v>
       </c>
       <c r="E321" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F321" s="15">
         <v>46174.96597222222</v>
@@ -9543,13 +9543,13 @@
         <v>46175.465277777781</v>
       </c>
       <c r="H321" s="11" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="I321" s="11" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="J321" s="1" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.25">
@@ -9557,7 +9557,7 @@
         <v>311</v>
       </c>
       <c r="B322" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C322" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -9567,7 +9567,7 @@
         <v>0</v>
       </c>
       <c r="E322" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F322" s="15">
         <v>46175.010416666664</v>
@@ -9576,13 +9576,13 @@
         <v>46175.112500000003</v>
       </c>
       <c r="H322" s="11" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I322" s="11" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="J322" s="1" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.25">
@@ -9590,7 +9590,7 @@
         <v>312</v>
       </c>
       <c r="B323" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C323" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -9600,7 +9600,7 @@
         <v>70</v>
       </c>
       <c r="E323" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F323" s="15">
         <v>46183.211111111108</v>
@@ -9609,10 +9609,10 @@
         <v>46183.908333333333</v>
       </c>
       <c r="H323" s="11" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="I323" s="11" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.25">
@@ -9620,9 +9620,9 @@
         <v>313</v>
       </c>
       <c r="B324" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C324" s="16" t="str">
+        <v>19</v>
+      </c>
+      <c r="C324" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
@@ -9630,7 +9630,7 @@
         <v>0</v>
       </c>
       <c r="E324" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F324" s="15">
         <v>46186.011111111111</v>
@@ -9639,10 +9639,10 @@
         <v>46186.208333333336</v>
       </c>
       <c r="H324" s="11" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I324" s="11" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.25">
@@ -9650,9 +9650,9 @@
         <v>314</v>
       </c>
       <c r="B325" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C325" s="16" t="str">
+        <v>19</v>
+      </c>
+      <c r="C325" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
@@ -9660,7 +9660,7 @@
         <v>70</v>
       </c>
       <c r="E325" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F325" s="15">
         <v>46186.208333333336</v>
@@ -9669,10 +9669,10 @@
         <v>46186.843055555553</v>
       </c>
       <c r="H325" s="11" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="I325" s="11" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.25">
@@ -9680,9 +9680,9 @@
         <v>315</v>
       </c>
       <c r="B326" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C326" s="16" t="str">
+        <v>17</v>
+      </c>
+      <c r="C326" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
@@ -9690,7 +9690,7 @@
         <v>100</v>
       </c>
       <c r="E326" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F326" s="15">
         <v>46186.011111111111</v>
@@ -9699,10 +9699,10 @@
         <v>46186.729166666664</v>
       </c>
       <c r="H326" s="11" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I326" s="11" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.25">
@@ -9710,9 +9710,9 @@
         <v>316</v>
       </c>
       <c r="B327" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C327" s="16" t="str">
+        <v>19</v>
+      </c>
+      <c r="C327" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
@@ -9720,21 +9720,40 @@
         <v>90</v>
       </c>
       <c r="E327" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F327" s="15">
         <v>46188.206250000003</v>
       </c>
       <c r="G327" s="15"/>
       <c r="H327" s="11" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I327" s="11" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A328" s="1"/>
+      <c r="A328" s="1">
+        <v>317</v>
+      </c>
+      <c r="B328" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C328" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CEM</v>
+      </c>
+      <c r="D328" s="14">
+        <v>0</v>
+      </c>
+      <c r="E328" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F328" s="15"/>
+      <c r="G328" s="15"/>
+      <c r="H328" s="11"/>
+      <c r="I328" s="11"/>
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A329" s="1"/>
@@ -9784,18 +9803,18 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="D1" t="s">
-        <v>58</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="C2">
         <v>245.84</v>
@@ -9806,10 +9825,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="C3">
         <v>176.6</v>
@@ -9820,10 +9839,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="C4">
         <v>174.26</v>
@@ -9834,10 +9853,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="C5">
         <v>376.96</v>
@@ -9848,10 +9867,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C6">
         <v>399.41</v>
@@ -9862,10 +9881,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C7">
         <v>20</v>
@@ -9876,10 +9895,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C8">
         <v>21</v>
@@ -9890,10 +9909,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C9">
         <v>21</v>
@@ -9904,10 +9923,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="C10">
         <v>131</v>
@@ -9918,10 +9937,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="C11">
         <v>112</v>
@@ -9957,10 +9976,10 @@
         <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="D1" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="E1" t="s">
         <v>7</v>
@@ -9968,7 +9987,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="3">
         <v>46023</v>
@@ -9980,12 +9999,12 @@
         <v>181.99998842592322</v>
       </c>
       <c r="E2" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="3">
         <v>46134</v>
@@ -9997,12 +10016,12 @@
         <v>7.6381944444437977</v>
       </c>
       <c r="E3" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3">
         <v>46235</v>
@@ -10014,12 +10033,12 @@
         <v>29.99998842592322</v>
       </c>
       <c r="E4" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="3">
         <v>46264</v>
@@ -10031,12 +10050,12 @@
         <v>17.99998842592322</v>
       </c>
       <c r="E5" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="3">
         <v>46296</v>
@@ -10048,12 +10067,12 @@
         <v>59.99998842592322</v>
       </c>
       <c r="E6" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" s="3">
         <v>46163</v>
@@ -10065,12 +10084,12 @@
         <v>3.9999884259232203</v>
       </c>
       <c r="E7" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" s="3">
         <v>46144.101388888892</v>
@@ -10082,7 +10101,7 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -10108,15 +10127,15 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="C1" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="7">
         <v>35065</v>
@@ -10127,7 +10146,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="7">
         <v>35796</v>
@@ -10138,7 +10157,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" s="7">
         <v>27760</v>
@@ -10149,7 +10168,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="B5" s="7">
         <v>27760</v>
@@ -10160,7 +10179,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="7">
         <v>34335</v>
@@ -10171,7 +10190,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" s="7">
         <v>36526</v>
@@ -10182,7 +10201,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="7">
         <v>40544</v>
@@ -10193,7 +10212,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" s="7">
         <v>40909</v>
@@ -10204,7 +10223,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" s="7">
         <v>43466</v>
@@ -10215,7 +10234,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" s="7">
         <v>36892</v>
@@ -10488,16 +10507,16 @@
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1104" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6ED28B7B-029A-48CD-997B-2568BCB89D10}"/>
+  <xr:revisionPtr revIDLastSave="1113" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{233B2864-759B-4E30-8DF6-7EAEAE18BCFB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="102">
   <si>
     <t>ID</t>
   </si>
@@ -354,6 +354,12 @@
   </si>
   <si>
     <t>FechaFinVigencia</t>
+  </si>
+  <si>
+    <t>Rotura tubo de pared 9° piso y 2 tubos RH2</t>
+  </si>
+  <si>
+    <t>Abierto</t>
   </si>
 </sst>
 </file>
@@ -9614,6 +9620,9 @@
       <c r="I323" s="11" t="s">
         <v>77</v>
       </c>
+      <c r="J323" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
@@ -9644,6 +9653,9 @@
       <c r="I324" s="11" t="s">
         <v>83</v>
       </c>
+      <c r="J324" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A325" s="1">
@@ -9674,6 +9686,9 @@
       <c r="I325" s="11" t="s">
         <v>77</v>
       </c>
+      <c r="J325" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A326" s="1">
@@ -9704,6 +9719,9 @@
       <c r="I326" s="11" t="s">
         <v>83</v>
       </c>
+      <c r="J326" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A327" s="1">
@@ -9725,12 +9743,17 @@
       <c r="F327" s="15">
         <v>46188.206250000003</v>
       </c>
-      <c r="G327" s="15"/>
+      <c r="G327" s="15">
+        <v>46188.365277777775</v>
+      </c>
       <c r="H327" s="11" t="s">
         <v>84</v>
       </c>
       <c r="I327" s="11" t="s">
         <v>85</v>
+      </c>
+      <c r="J327" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.25">
@@ -9750,10 +9773,21 @@
       <c r="E328" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="F328" s="15"/>
-      <c r="G328" s="15"/>
-      <c r="H328" s="11"/>
-      <c r="I328" s="11"/>
+      <c r="F328" s="15">
+        <v>46188.365277777775</v>
+      </c>
+      <c r="G328" s="15">
+        <v>46195.999305555553</v>
+      </c>
+      <c r="H328" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="I328" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="J328" s="1" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A329" s="1"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1113" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{233B2864-759B-4E30-8DF6-7EAEAE18BCFB}"/>
+  <xr:revisionPtr revIDLastSave="1114" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CF30A6A-6CB2-4B2D-899A-6DD58B90798F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -9777,7 +9777,7 @@
         <v>46188.365277777775</v>
       </c>
       <c r="G328" s="15">
-        <v>46195.999305555553</v>
+        <v>46194.999305555553</v>
       </c>
       <c r="H328" s="11" t="s">
         <v>65</v>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1114" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CF30A6A-6CB2-4B2D-899A-6DD58B90798F}"/>
+  <xr:revisionPtr revIDLastSave="1123" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9F2C798-8D3B-45B6-B575-FFE02612B188}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="104">
   <si>
     <t>ID</t>
   </si>
@@ -360,6 +360,12 @@
   </si>
   <si>
     <t>Abierto</t>
+  </si>
+  <si>
+    <t>Falla en arranque</t>
+  </si>
+  <si>
+    <t>Sistema de arranque en falla</t>
   </si>
 </sst>
 </file>
@@ -784,8 +790,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J328" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J328" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J329" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J329" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1185,7 +1191,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -9790,7 +9796,35 @@
       </c>
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A329" s="1"/>
+      <c r="A329" s="1">
+        <v>318</v>
+      </c>
+      <c r="B329" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C329" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
+      </c>
+      <c r="D329" s="14">
+        <v>0</v>
+      </c>
+      <c r="E329" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F329" s="15">
+        <v>46192.025694444441</v>
+      </c>
+      <c r="G329" s="15"/>
+      <c r="H329" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="I329" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="J329" s="1" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1123" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9F2C798-8D3B-45B6-B575-FFE02612B188}"/>
+  <xr:revisionPtr revIDLastSave="1126" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{475D9A20-8EE8-4789-AEEF-AB19FAC19E60}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="103">
   <si>
     <t>ID</t>
   </si>
@@ -356,9 +356,6 @@
     <t>FechaFinVigencia</t>
   </si>
   <si>
-    <t>Rotura tubo de pared 9° piso y 2 tubos RH2</t>
-  </si>
-  <si>
     <t>Abierto</t>
   </si>
   <si>
@@ -409,7 +406,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -448,9 +445,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -790,8 +784,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J329" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J329" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J328" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J328" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1172,7 +1166,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
-  <dimension ref="A9:J333"/>
+  <dimension ref="A9:J332"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -1191,7 +1185,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -9764,14 +9758,14 @@
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A328" s="1">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B328" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C328" s="16" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
-        <v>CEM</v>
+        <v>90</v>
+      </c>
+      <c r="C328" s="13" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
       </c>
       <c r="D328" s="14">
         <v>0</v>
@@ -9780,51 +9774,21 @@
         <v>13</v>
       </c>
       <c r="F328" s="15">
-        <v>46188.365277777775</v>
-      </c>
-      <c r="G328" s="15">
-        <v>46194.999305555553</v>
-      </c>
+        <v>46192.025694444441</v>
+      </c>
+      <c r="G328" s="15"/>
       <c r="H328" s="11" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="I328" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="J328" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="J328" s="1" t="s">
-        <v>101</v>
-      </c>
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A329" s="1">
-        <v>318</v>
-      </c>
-      <c r="B329" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="C329" s="16" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
-        <v>CET</v>
-      </c>
-      <c r="D329" s="14">
-        <v>0</v>
-      </c>
-      <c r="E329" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F329" s="15">
-        <v>46192.025694444441</v>
-      </c>
-      <c r="G329" s="15"/>
-      <c r="H329" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="I329" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="J329" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="A329" s="1"/>
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>
@@ -9834,9 +9798,6 @@
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A332" s="1"/>
-    </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A333" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10320,6 +10281,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100FB7AAE8C8816FD47B559A0CCF555AFF0" ma:contentTypeVersion="10" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5c9910934a78ddf693a6b708b52e9b37">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f95d585e-e7a7-414c-955d-38a47c8579bd" xmlns:ns3="33ab045e-9213-4eea-a9f2-a5b809105d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a9c61c95b4e11caed4e46447c2ca01e7" ns2:_="" ns3:_="">
     <xsd:import namespace="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
@@ -10522,30 +10506,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10564,31 +10550,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{0a9b9e15-83d2-4075-9282-a04e05c6580a}" enabled="1" method="Standard" siteId="{24139d14-c62c-4c47-8bdd-ce71ea1d50cf}" contentBits="0" removed="0"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1126" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{475D9A20-8EE8-4789-AEEF-AB19FAC19E60}"/>
+  <xr:revisionPtr revIDLastSave="1138" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57789E70-1594-49F3-82BB-E2E51E94B22C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <definedName name="SegmentaciónDeDatos_Sitio">#N/A</definedName>
     <definedName name="SegmentaciónDeDatos_Unidad">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="105">
   <si>
     <t>ID</t>
   </si>
@@ -364,6 +364,12 @@
   <si>
     <t>Sistema de arranque en falla</t>
   </si>
+  <si>
+    <t>Inspección alimentador de carbón N°2</t>
+  </si>
+  <si>
+    <t>Se retira de gran granulometria alojado al interior del alimentador de carbón N°2, alimentador de carbón N°4 indisponible</t>
+  </si>
 </sst>
 </file>
 
@@ -406,7 +412,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -445,6 +451,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -784,8 +793,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J328" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J328" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J329" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J329" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1185,7 +1194,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -9788,7 +9797,37 @@
       </c>
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A329" s="1"/>
+      <c r="A329" s="1">
+        <v>319</v>
+      </c>
+      <c r="B329" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C329" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CEM</v>
+      </c>
+      <c r="D329" s="14">
+        <v>130</v>
+      </c>
+      <c r="E329" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F329" s="15">
+        <v>46198.567361111112</v>
+      </c>
+      <c r="G329" s="15">
+        <v>46198.677083333336</v>
+      </c>
+      <c r="H329" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="I329" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="J329" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>
@@ -10281,29 +10320,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100FB7AAE8C8816FD47B559A0CCF555AFF0" ma:contentTypeVersion="10" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5c9910934a78ddf693a6b708b52e9b37">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f95d585e-e7a7-414c-955d-38a47c8579bd" xmlns:ns3="33ab045e-9213-4eea-a9f2-a5b809105d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a9c61c95b4e11caed4e46447c2ca01e7" ns2:_="" ns3:_="">
     <xsd:import namespace="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
@@ -10506,32 +10522,30 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10550,6 +10564,31 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{0a9b9e15-83d2-4075-9282-a04e05c6580a}" enabled="1" method="Standard" siteId="{24139d14-c62c-4c47-8bdd-ce71ea1d50cf}" contentBits="0" removed="0"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1138" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57789E70-1594-49F3-82BB-E2E51E94B22C}"/>
+  <xr:revisionPtr revIDLastSave="1140" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B365BEFB-E714-49A7-975D-4AFF7E106FF5}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView minimized="1" xWindow="3330" yWindow="3600" windowWidth="17280" windowHeight="8880" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="104">
   <si>
     <t>ID</t>
   </si>
@@ -354,9 +354,6 @@
   </si>
   <si>
     <t>FechaFinVigencia</t>
-  </si>
-  <si>
-    <t>Abierto</t>
   </si>
   <si>
     <t>Falla en arranque</t>
@@ -9785,15 +9782,17 @@
       <c r="F328" s="15">
         <v>46192.025694444441</v>
       </c>
-      <c r="G328" s="15"/>
+      <c r="G328" s="15">
+        <v>46192.5</v>
+      </c>
       <c r="H328" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="I328" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="I328" s="11" t="s">
-        <v>102</v>
-      </c>
       <c r="J328" s="1" t="s">
-        <v>100</v>
+        <v>23</v>
       </c>
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.25">
@@ -9820,10 +9819,10 @@
         <v>46198.677083333336</v>
       </c>
       <c r="H329" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="I329" s="11" t="s">
         <v>103</v>
-      </c>
-      <c r="I329" s="11" t="s">
-        <v>104</v>
       </c>
       <c r="J329" s="1" t="s">
         <v>23</v>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1140" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B365BEFB-E714-49A7-975D-4AFF7E106FF5}"/>
+  <xr:revisionPtr revIDLastSave="1146" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BF43953-4479-4121-9A9C-AFEBAC67B009}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3330" yWindow="3600" windowWidth="17280" windowHeight="8880" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="104">
   <si>
     <t>ID</t>
   </si>
@@ -790,8 +790,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J329" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J329" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J330" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J330" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1191,7 +1191,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -9829,7 +9829,32 @@
       </c>
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A330" s="1"/>
+      <c r="A330" s="1">
+        <v>320</v>
+      </c>
+      <c r="B330" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C330" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CEM</v>
+      </c>
+      <c r="D330" s="14">
+        <v>75</v>
+      </c>
+      <c r="E330" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F330" s="15">
+        <v>46199.388888888891</v>
+      </c>
+      <c r="G330" s="15"/>
+      <c r="H330" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="I330" s="11" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A331" s="1"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1146" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BF43953-4479-4121-9A9C-AFEBAC67B009}"/>
+  <xr:revisionPtr revIDLastSave="1148" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{966EC9C1-1659-4575-A2CC-DAB42351DAC6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="104">
   <si>
     <t>ID</t>
   </si>
@@ -9848,12 +9848,17 @@
       <c r="F330" s="15">
         <v>46199.388888888891</v>
       </c>
-      <c r="G330" s="15"/>
+      <c r="G330" s="15">
+        <v>46199.916666666664</v>
+      </c>
       <c r="H330" s="11" t="s">
         <v>76</v>
       </c>
       <c r="I330" s="11" t="s">
         <v>77</v>
+      </c>
+      <c r="J330" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.25">

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1148" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{966EC9C1-1659-4575-A2CC-DAB42351DAC6}"/>
+  <xr:revisionPtr revIDLastSave="1155" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C23BE1DD-5AF8-4D2E-9E6D-9D6F48F9B747}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="104">
   <si>
     <t>ID</t>
   </si>
@@ -790,8 +790,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J330" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J330" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J331" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J331" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1191,7 +1191,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -9802,7 +9802,7 @@
       <c r="B329" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C329" s="16" t="str">
+      <c r="C329" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
@@ -9835,7 +9835,7 @@
       <c r="B330" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C330" s="16" t="str">
+      <c r="C330" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
@@ -9862,7 +9862,30 @@
       </c>
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A331" s="1"/>
+      <c r="A331" s="1">
+        <v>321</v>
+      </c>
+      <c r="B331" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C331" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
+      </c>
+      <c r="D331" s="14">
+        <v>0</v>
+      </c>
+      <c r="E331" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F331" s="15">
+        <v>46204.147916666669</v>
+      </c>
+      <c r="G331" s="15">
+        <v>46204.519444444442</v>
+      </c>
+      <c r="H331" s="11"/>
+      <c r="I331" s="11"/>
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A332" s="1"/>
@@ -10552,15 +10575,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
@@ -10572,6 +10586,15 @@
     </SharedWithUsers>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10594,26 +10617,26 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1155" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C23BE1DD-5AF8-4D2E-9E6D-9D6F48F9B747}"/>
+  <xr:revisionPtr revIDLastSave="1158" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BE38E7D-0236-4A38-A321-3BE5EAD6DAE2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="106">
   <si>
     <t>ID</t>
   </si>
@@ -366,6 +366,12 @@
   </si>
   <si>
     <t>Se retira de gran granulometria alojado al interior del alimentador de carbón N°2, alimentador de carbón N°4 indisponible</t>
+  </si>
+  <si>
+    <t>Activación fuga de gas en TG</t>
+  </si>
+  <si>
+    <t>Falla sensor detector de gas</t>
   </si>
 </sst>
 </file>
@@ -9884,8 +9890,15 @@
       <c r="G331" s="15">
         <v>46204.519444444442</v>
       </c>
-      <c r="H331" s="11"/>
-      <c r="I331" s="11"/>
+      <c r="H331" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="I331" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="J331" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A332" s="1"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1158" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BE38E7D-0236-4A38-A321-3BE5EAD6DAE2}"/>
+  <xr:revisionPtr revIDLastSave="1160" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1A9E4F0-CAED-4A29-9B02-955F3D29FC95}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="22932" yWindow="-144" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="106">
   <si>
     <t>ID</t>
   </si>
@@ -523,15 +523,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>478207</xdr:colOff>
+      <xdr:colOff>482017</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>932137</xdr:colOff>
+      <xdr:colOff>935947</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>133260</xdr:rowOff>
+      <xdr:rowOff>137070</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -609,7 +609,7 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>225435</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>133260</xdr:rowOff>
+      <xdr:rowOff>137070</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -685,9 +685,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>855990</xdr:colOff>
+      <xdr:colOff>859800</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>133260</xdr:rowOff>
+      <xdr:rowOff>137070</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -796,8 +796,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J331" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J331" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J332" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J332" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1197,7 +1197,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -9901,7 +9901,22 @@
       </c>
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A332" s="1"/>
+      <c r="A332" s="1">
+        <v>322</v>
+      </c>
+      <c r="B332" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C332" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
+      </c>
+      <c r="D332" s="14"/>
+      <c r="E332" s="13"/>
+      <c r="F332" s="15"/>
+      <c r="G332" s="15"/>
+      <c r="H332" s="11"/>
+      <c r="I332" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1160" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1A9E4F0-CAED-4A29-9B02-955F3D29FC95}"/>
+  <xr:revisionPtr revIDLastSave="1161" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCC75B6B-6880-4D7B-902F-29846D5562EA}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-144" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="22932" yWindow="-144" windowWidth="23256" windowHeight="12456" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="106">
   <si>
     <t>ID</t>
   </si>
@@ -833,8 +833,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F870A6C2-1511-4796-898C-4DDAC85DB998}" name="Indisp_Prog" displayName="Indisp_Prog" ref="A1:E8" totalsRowShown="0">
-  <autoFilter ref="A1:E8" xr:uid="{F870A6C2-1511-4796-898C-4DDAC85DB998}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F870A6C2-1511-4796-898C-4DDAC85DB998}" name="Indisp_Prog" displayName="Indisp_Prog" ref="A1:E9" totalsRowShown="0">
+  <autoFilter ref="A1:E9" xr:uid="{F870A6C2-1511-4796-898C-4DDAC85DB998}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E6">
     <sortCondition ref="B1:B6"/>
   </sortState>
@@ -10107,7 +10107,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56220E0F-EC16-4A8C-9E04-C7F8849C4B4D}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -10251,6 +10251,14 @@
       <c r="E8" t="s">
         <v>97</v>
       </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1161" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCC75B6B-6880-4D7B-902F-29846D5562EA}"/>
+  <xr:revisionPtr revIDLastSave="1162" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12738461-7D06-4E18-A138-73E4EE5AEB78}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-144" windowWidth="23256" windowHeight="12456" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="22932" yWindow="-144" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -10256,7 +10256,9 @@
       <c r="A9" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="3"/>
+      <c r="B9" s="3">
+        <v>46188.361111111109</v>
+      </c>
       <c r="C9" s="3"/>
       <c r="D9" s="14"/>
     </row>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1162" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12738461-7D06-4E18-A138-73E4EE5AEB78}"/>
+  <xr:revisionPtr revIDLastSave="1165" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EBD1B42-198E-4615-B405-F4B30DCE0108}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-144" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="106">
   <si>
     <t>ID</t>
   </si>
@@ -10259,8 +10259,15 @@
       <c r="B9" s="3">
         <v>46188.361111111109</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="14"/>
+      <c r="C9" s="3">
+        <v>46194.5</v>
+      </c>
+      <c r="D9" s="14">
+        <v>7</v>
+      </c>
+      <c r="E9" t="s">
+        <v>97</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1165" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EBD1B42-198E-4615-B405-F4B30DCE0108}"/>
+  <xr:revisionPtr revIDLastSave="1173" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3651EDAA-2B7D-474A-8AD1-7C89758EA2C1}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-144" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="22932" yWindow="-144" windowWidth="23256" windowHeight="12456" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="106">
   <si>
     <t>ID</t>
   </si>
@@ -523,15 +523,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>482017</xdr:colOff>
+      <xdr:colOff>485827</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>935947</xdr:colOff>
+      <xdr:colOff>941662</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>137070</xdr:rowOff>
+      <xdr:rowOff>142785</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -609,7 +609,7 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>225435</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>137070</xdr:rowOff>
+      <xdr:rowOff>142785</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -685,9 +685,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>859800</xdr:colOff>
+      <xdr:colOff>865515</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>137070</xdr:rowOff>
+      <xdr:rowOff>142785</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -9911,9 +9911,15 @@
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
-      <c r="D332" s="14"/>
-      <c r="E332" s="13"/>
-      <c r="F332" s="15"/>
+      <c r="D332" s="14">
+        <v>262</v>
+      </c>
+      <c r="E332" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F332" s="15">
+        <v>46205.390277777777</v>
+      </c>
       <c r="G332" s="15"/>
       <c r="H332" s="11"/>
       <c r="I332" s="11"/>
@@ -10141,10 +10147,10 @@
         <v>46023</v>
       </c>
       <c r="C2" s="3">
-        <v>46204.999988425923</v>
+        <v>46223.999988425923</v>
       </c>
       <c r="D2" s="14">
-        <v>181.99998842592322</v>
+        <v>200.99998842592322</v>
       </c>
       <c r="E2" t="s">
         <v>93</v>
@@ -10246,7 +10252,8 @@
         <v>46152.989583333336</v>
       </c>
       <c r="D8" s="14">
-        <v>5</v>
+        <f>Indisp_Prog[[#This Row],[Fecha_Hora_Fin]]-Indisp_Prog[[#This Row],[Fecha_Hora_Inicio]]</f>
+        <v>8.8881944444437977</v>
       </c>
       <c r="E8" t="s">
         <v>97</v>
@@ -10263,7 +10270,8 @@
         <v>46194.5</v>
       </c>
       <c r="D9" s="14">
-        <v>7</v>
+        <f>Indisp_Prog[[#This Row],[Fecha_Hora_Fin]]-Indisp_Prog[[#This Row],[Fecha_Hora_Inicio]]</f>
+        <v>6.1388888888905058</v>
       </c>
       <c r="E9" t="s">
         <v>97</v>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1173" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3651EDAA-2B7D-474A-8AD1-7C89758EA2C1}"/>
+  <xr:revisionPtr revIDLastSave="1177" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A88FDDB-4AF7-4CDD-9ACD-983CD8109F09}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-144" windowWidth="23256" windowHeight="12456" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="108">
   <si>
     <t>ID</t>
   </si>
@@ -373,6 +373,12 @@
   <si>
     <t>Falla sensor detector de gas</t>
   </si>
+  <si>
+    <t>Descalople TV</t>
+  </si>
+  <si>
+    <t>Altas vibraciónes TV</t>
+  </si>
 </sst>
 </file>
 
@@ -523,15 +529,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>485827</xdr:colOff>
+      <xdr:colOff>489637</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>941662</xdr:colOff>
+      <xdr:colOff>945472</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>142785</xdr:rowOff>
+      <xdr:rowOff>146595</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -609,7 +615,7 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>225435</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>142785</xdr:rowOff>
+      <xdr:rowOff>146595</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -685,9 +691,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>865515</xdr:colOff>
+      <xdr:colOff>869325</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>142785</xdr:rowOff>
+      <xdr:rowOff>146595</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -9920,9 +9926,18 @@
       <c r="F332" s="15">
         <v>46205.390277777777</v>
       </c>
-      <c r="G332" s="15"/>
-      <c r="H332" s="11"/>
-      <c r="I332" s="11"/>
+      <c r="G332" s="15">
+        <v>46205.434027777781</v>
+      </c>
+      <c r="H332" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="I332" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="J332" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1177" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A88FDDB-4AF7-4CDD-9ACD-983CD8109F09}"/>
+  <xr:revisionPtr revIDLastSave="1178" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94B37943-3FCF-4092-A6DE-88430B4FC0D4}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-144" windowWidth="23256" windowHeight="12456" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -377,7 +377,7 @@
     <t>Descalople TV</t>
   </si>
   <si>
-    <t>Altas vibraciónes TV</t>
+    <t>Altas vibraciónes TV cojinete N°5</t>
   </si>
 </sst>
 </file>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1178" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94B37943-3FCF-4092-A6DE-88430B4FC0D4}"/>
+  <xr:revisionPtr revIDLastSave="1180" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A5CE8B8-65A1-408F-9367-DFC522BD6C50}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-144" windowWidth="23256" windowHeight="12456" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -529,15 +529,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>489637</xdr:colOff>
+      <xdr:colOff>491542</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>945472</xdr:colOff>
+      <xdr:colOff>949282</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>146595</xdr:rowOff>
+      <xdr:rowOff>148500</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -615,7 +615,7 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>225435</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>146595</xdr:rowOff>
+      <xdr:rowOff>148500</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -691,9 +691,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>869325</xdr:colOff>
+      <xdr:colOff>873135</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>146595</xdr:rowOff>
+      <xdr:rowOff>148500</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -9924,10 +9924,10 @@
         <v>11</v>
       </c>
       <c r="F332" s="15">
-        <v>46205.390277777777</v>
+        <v>46205.393055555556</v>
       </c>
       <c r="G332" s="15">
-        <v>46205.434027777781</v>
+        <v>46205.420138888891</v>
       </c>
       <c r="H332" s="11" t="s">
         <v>106</v>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1180" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A5CE8B8-65A1-408F-9367-DFC522BD6C50}"/>
+  <xr:revisionPtr revIDLastSave="1185" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DAF567C-CD75-4443-9E53-6FD8B960946E}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-144" windowWidth="23256" windowHeight="12456" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="108">
   <si>
     <t>ID</t>
   </si>
@@ -802,8 +802,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J332" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J332" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J333" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J333" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1184,7 +1184,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
-  <dimension ref="A9:J332"/>
+  <dimension ref="A9:J333"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -1203,7 +1203,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -9880,7 +9880,7 @@
       <c r="B331" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C331" s="16" t="str">
+      <c r="C331" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
@@ -9913,7 +9913,7 @@
       <c r="B332" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C332" s="16" t="str">
+      <c r="C332" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
@@ -9938,6 +9938,30 @@
       <c r="J332" s="1" t="s">
         <v>23</v>
       </c>
+    </row>
+    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A333">
+        <v>323</v>
+      </c>
+      <c r="B333" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C333" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
+      </c>
+      <c r="D333" s="14">
+        <v>0</v>
+      </c>
+      <c r="E333" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F333" s="15">
+        <v>46207.680555555555</v>
+      </c>
+      <c r="G333" s="15"/>
+      <c r="H333" s="11"/>
+      <c r="I333" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10440,6 +10464,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100FB7AAE8C8816FD47B559A0CCF555AFF0" ma:contentTypeVersion="10" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5c9910934a78ddf693a6b708b52e9b37">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f95d585e-e7a7-414c-955d-38a47c8579bd" xmlns:ns3="33ab045e-9213-4eea-a9f2-a5b809105d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a9c61c95b4e11caed4e46447c2ca01e7" ns2:_="" ns3:_="">
     <xsd:import namespace="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
@@ -10642,30 +10689,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10684,31 +10733,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{0a9b9e15-83d2-4075-9282-a04e05c6580a}" enabled="1" method="Standard" siteId="{24139d14-c62c-4c47-8bdd-ce71ea1d50cf}" contentBits="0" removed="0"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1185" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DAF567C-CD75-4443-9E53-6FD8B960946E}"/>
+  <xr:revisionPtr revIDLastSave="1207" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E5B9BAE-8E9C-4DBB-8C3F-23F8A4061E12}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="110">
   <si>
     <t>ID</t>
   </si>
@@ -378,6 +378,12 @@
   </si>
   <si>
     <t>Altas vibraciónes TV cojinete N°5</t>
+  </si>
+  <si>
+    <t>Falla en la partida</t>
+  </si>
+  <si>
+    <t>Alta temperatura en generador</t>
   </si>
 </sst>
 </file>
@@ -802,8 +808,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J333" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J333" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J337" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J337" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1184,7 +1190,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
-  <dimension ref="A9:J333"/>
+  <dimension ref="A9:J342"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -1203,7 +1209,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -9940,7 +9946,7 @@
       </c>
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A333">
+      <c r="A333" s="1">
         <v>323</v>
       </c>
       <c r="B333" s="13" t="s">
@@ -9960,8 +9966,121 @@
         <v>46207.680555555555</v>
       </c>
       <c r="G333" s="15"/>
-      <c r="H333" s="11"/>
+      <c r="H333" s="11" t="s">
+        <v>108</v>
+      </c>
       <c r="I333" s="11"/>
+    </row>
+    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A334" s="1">
+        <v>324</v>
+      </c>
+      <c r="B334" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C334" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
+      </c>
+      <c r="D334" s="14">
+        <v>0</v>
+      </c>
+      <c r="E334" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F334" s="15">
+        <v>46207.869444444441</v>
+      </c>
+      <c r="G334" s="15"/>
+      <c r="H334" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="I334" s="11"/>
+    </row>
+    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A335" s="1">
+        <v>325</v>
+      </c>
+      <c r="B335" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C335" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
+      </c>
+      <c r="D335" s="14">
+        <v>0</v>
+      </c>
+      <c r="E335" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F335" s="15">
+        <v>46208</v>
+      </c>
+      <c r="G335" s="15"/>
+      <c r="H335" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="I335" s="11"/>
+    </row>
+    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A336" s="1">
+        <v>326</v>
+      </c>
+      <c r="B336" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C336" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
+      </c>
+      <c r="D336" s="14">
+        <v>0</v>
+      </c>
+      <c r="E336" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F336" s="15">
+        <v>46209.345833333333</v>
+      </c>
+      <c r="G336" s="15"/>
+      <c r="H336" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="I336" s="11"/>
+    </row>
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A337" s="1">
+        <v>327</v>
+      </c>
+      <c r="B337" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C337" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CEM</v>
+      </c>
+      <c r="D337" s="14"/>
+      <c r="E337" s="13"/>
+      <c r="F337" s="15"/>
+      <c r="G337" s="15"/>
+      <c r="H337" s="11"/>
+      <c r="I337" s="11"/>
+    </row>
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A338" s="1"/>
+    </row>
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A339" s="1"/>
+    </row>
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A340" s="1"/>
+    </row>
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A341" s="1"/>
+    </row>
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A342" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1207" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E5B9BAE-8E9C-4DBB-8C3F-23F8A4061E12}"/>
+  <xr:revisionPtr revIDLastSave="1218" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93D6343D-977E-4491-82AF-3F8CF6C5B440}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="112">
   <si>
     <t>ID</t>
   </si>
@@ -384,6 +384,12 @@
   </si>
   <si>
     <t>Alta temperatura en generador</t>
+  </si>
+  <si>
+    <t>Falla sistema combustible DO</t>
+  </si>
+  <si>
+    <t>Falla bomba transferencia</t>
   </si>
 </sst>
 </file>
@@ -808,8 +814,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J337" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J337" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J338" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J338" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1209,7 +1215,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -10060,15 +10066,50 @@
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
-      <c r="D337" s="14"/>
-      <c r="E337" s="13"/>
-      <c r="F337" s="15"/>
+      <c r="D337" s="14">
+        <v>70</v>
+      </c>
+      <c r="E337" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F337" s="15">
+        <v>46209.348611111112</v>
+      </c>
       <c r="G337" s="15"/>
-      <c r="H337" s="11"/>
-      <c r="I337" s="11"/>
+      <c r="H337" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="I337" s="11" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A338" s="1"/>
+      <c r="A338" s="1">
+        <v>328</v>
+      </c>
+      <c r="B338" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C338" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CEM</v>
+      </c>
+      <c r="D338" s="14">
+        <v>0</v>
+      </c>
+      <c r="E338" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F338" s="15">
+        <v>46209.40625</v>
+      </c>
+      <c r="G338" s="15"/>
+      <c r="H338" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="I338" s="11" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339" s="1"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1218" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93D6343D-977E-4491-82AF-3F8CF6C5B440}"/>
+  <xr:revisionPtr revIDLastSave="1222" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{471291B5-0796-4572-A6A4-7BD9DBBF8D38}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="112">
   <si>
     <t>ID</t>
   </si>
@@ -814,8 +814,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J338" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J338" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J339" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J339" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1215,7 +1215,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -10113,6 +10113,25 @@
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339" s="1"/>
+      <c r="B339" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C339" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
+      </c>
+      <c r="D339" s="14">
+        <v>0</v>
+      </c>
+      <c r="E339" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F339" s="15">
+        <v>46210.06527777778</v>
+      </c>
+      <c r="G339" s="15"/>
+      <c r="H339" s="11"/>
+      <c r="I339" s="11"/>
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A340" s="1"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1222" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{471291B5-0796-4572-A6A4-7BD9DBBF8D38}"/>
+  <xr:revisionPtr revIDLastSave="1234" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2647527B-A397-4FD0-A8D9-6680713D0254}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="114">
   <si>
     <t>ID</t>
   </si>
@@ -390,6 +390,12 @@
   </si>
   <si>
     <t>Falla bomba transferencia</t>
+  </si>
+  <si>
+    <t>Falla sistema de admisión</t>
+  </si>
+  <si>
+    <t>Obstrucciín filtro admisión</t>
   </si>
 </sst>
 </file>
@@ -814,8 +820,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J339" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J339" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J341" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J341" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1215,7 +1221,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -10112,7 +10118,9 @@
       </c>
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A339" s="1"/>
+      <c r="A339" s="1">
+        <v>329</v>
+      </c>
       <c r="B339" s="13" t="s">
         <v>20</v>
       </c>
@@ -10130,14 +10138,56 @@
         <v>46210.06527777778</v>
       </c>
       <c r="G339" s="15"/>
-      <c r="H339" s="11"/>
-      <c r="I339" s="11"/>
+      <c r="H339" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="I339" s="11" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A340" s="1"/>
+      <c r="A340" s="1">
+        <v>400</v>
+      </c>
+      <c r="B340" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C340" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CEM</v>
+      </c>
+      <c r="D340" s="14">
+        <v>70</v>
+      </c>
+      <c r="E340" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F340" s="15">
+        <v>46210.375</v>
+      </c>
+      <c r="G340" s="15"/>
+      <c r="H340" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="I340" s="11" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A341" s="1"/>
+      <c r="A341" s="1">
+        <v>401</v>
+      </c>
+      <c r="B341" s="13"/>
+      <c r="C341" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
+      </c>
+      <c r="D341" s="14"/>
+      <c r="E341" s="13"/>
+      <c r="F341" s="15"/>
+      <c r="G341" s="15"/>
+      <c r="H341" s="11"/>
+      <c r="I341" s="11"/>
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A342" s="1"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1234" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2647527B-A397-4FD0-A8D9-6680713D0254}"/>
+  <xr:revisionPtr revIDLastSave="1245" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{005EB9FE-3BC5-4DA1-B1B5-996117640BD9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="114">
   <si>
     <t>ID</t>
   </si>
@@ -820,8 +820,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J341" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J341" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J342" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J342" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1221,7 +1221,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -9982,6 +9982,9 @@
         <v>108</v>
       </c>
       <c r="I333" s="11"/>
+      <c r="J333" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A334" s="1">
@@ -10008,6 +10011,9 @@
         <v>109</v>
       </c>
       <c r="I334" s="11"/>
+      <c r="J334" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A335" s="1">
@@ -10034,6 +10040,9 @@
         <v>109</v>
       </c>
       <c r="I335" s="11"/>
+      <c r="J335" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A336" s="1">
@@ -10060,8 +10069,11 @@
         <v>109</v>
       </c>
       <c r="I336" s="11"/>
-    </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J336" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A337" s="1">
         <v>327</v>
       </c>
@@ -10088,8 +10100,11 @@
       <c r="I337" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J337" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A338" s="1">
         <v>328</v>
       </c>
@@ -10116,8 +10131,11 @@
       <c r="I338" s="11" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J338" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A339" s="1">
         <v>329</v>
       </c>
@@ -10144,8 +10162,11 @@
       <c r="I339" s="11" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J339" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
         <v>400</v>
       </c>
@@ -10172,25 +10193,69 @@
       <c r="I340" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J340" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
         <v>401</v>
       </c>
-      <c r="B341" s="13"/>
+      <c r="B341" s="13" t="s">
+        <v>17</v>
+      </c>
       <c r="C341" s="16" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
-        <v>CET</v>
-      </c>
-      <c r="D341" s="14"/>
-      <c r="E341" s="13"/>
-      <c r="F341" s="15"/>
+        <v>CEM</v>
+      </c>
+      <c r="D341" s="14">
+        <v>75</v>
+      </c>
+      <c r="E341" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F341" s="15">
+        <v>46223.669444444444</v>
+      </c>
       <c r="G341" s="15"/>
-      <c r="H341" s="11"/>
-      <c r="I341" s="11"/>
-    </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H341" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="I341" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="J341" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A342" s="1"/>
+      <c r="B342" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C342" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CEM</v>
+      </c>
+      <c r="D342" s="14">
+        <v>75</v>
+      </c>
+      <c r="E342" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F342" s="15">
+        <v>46223.669444444444</v>
+      </c>
+      <c r="G342" s="15"/>
+      <c r="H342" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="I342" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="J342" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1245" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{005EB9FE-3BC5-4DA1-B1B5-996117640BD9}"/>
+  <xr:revisionPtr revIDLastSave="1248" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{225E53FD-B3A6-4630-8D1C-4B2A9D070090}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -10480,10 +10480,10 @@
         <v>46023</v>
       </c>
       <c r="C2" s="3">
-        <v>46223.999988425923</v>
+        <v>46237.999988425923</v>
       </c>
       <c r="D2" s="14">
-        <v>200.99998842592322</v>
+        <v>214.99998842592322</v>
       </c>
       <c r="E2" t="s">
         <v>93</v>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1248" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{225E53FD-B3A6-4630-8D1C-4B2A9D070090}"/>
+  <xr:revisionPtr revIDLastSave="1249" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C104D522-5C9C-4AD9-BEBA-2F5A49AA73E0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -10124,7 +10124,9 @@
       <c r="F338" s="15">
         <v>46209.40625</v>
       </c>
-      <c r="G338" s="15"/>
+      <c r="G338" s="15">
+        <v>46209.45</v>
+      </c>
       <c r="H338" s="11" t="s">
         <v>110</v>
       </c>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1249" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C104D522-5C9C-4AD9-BEBA-2F5A49AA73E0}"/>
+  <xr:revisionPtr revIDLastSave="1250" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91573002-5D4C-46A6-B2C5-7A7F97B3DF4D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -389,13 +389,13 @@
     <t>Falla sistema combustible DO</t>
   </si>
   <si>
-    <t>Falla bomba transferencia</t>
-  </si>
-  <si>
     <t>Falla sistema de admisión</t>
   </si>
   <si>
     <t>Obstrucciín filtro admisión</t>
+  </si>
+  <si>
+    <t>Obstrucción filtro de succión bombas de transferencia</t>
   </si>
 </sst>
 </file>
@@ -10131,7 +10131,7 @@
         <v>110</v>
       </c>
       <c r="I338" s="11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J338" s="1" t="s">
         <v>23</v>
@@ -10159,10 +10159,10 @@
       </c>
       <c r="G339" s="15"/>
       <c r="H339" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I339" s="11" t="s">
         <v>112</v>
-      </c>
-      <c r="I339" s="11" t="s">
-        <v>113</v>
       </c>
       <c r="J339" s="1" t="s">
         <v>23</v>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1250" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91573002-5D4C-46A6-B2C5-7A7F97B3DF4D}"/>
+  <xr:revisionPtr revIDLastSave="1252" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BC0DD0C-CEEE-407D-B697-ED32023F69ED}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="22932" yWindow="-144" windowWidth="23256" windowHeight="12456" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -10093,7 +10093,9 @@
       <c r="F337" s="15">
         <v>46209.348611111112</v>
       </c>
-      <c r="G337" s="15"/>
+      <c r="G337" s="15">
+        <v>46210</v>
+      </c>
       <c r="H337" s="11" t="s">
         <v>76</v>
       </c>
@@ -10125,7 +10127,7 @@
         <v>46209.40625</v>
       </c>
       <c r="G338" s="15">
-        <v>46209.45</v>
+        <v>46209.4375</v>
       </c>
       <c r="H338" s="11" t="s">
         <v>110</v>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1252" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BC0DD0C-CEEE-407D-B697-ED32023F69ED}"/>
+  <xr:revisionPtr revIDLastSave="1253" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5C29CB3-F6DC-4BE6-9D73-28E3D8F61C99}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-144" windowWidth="23256" windowHeight="12456" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -10190,7 +10190,9 @@
       <c r="F340" s="15">
         <v>46210.375</v>
       </c>
-      <c r="G340" s="15"/>
+      <c r="G340" s="15">
+        <v>46210.916666666664</v>
+      </c>
       <c r="H340" s="11" t="s">
         <v>76</v>
       </c>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1253" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5C29CB3-F6DC-4BE6-9D73-28E3D8F61C99}"/>
+  <xr:revisionPtr revIDLastSave="1255" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31491CDB-75A2-45D3-A995-C3035D54C047}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-144" windowWidth="23256" windowHeight="12456" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -10223,7 +10223,9 @@
       <c r="F341" s="15">
         <v>46223.669444444444</v>
       </c>
-      <c r="G341" s="15"/>
+      <c r="G341" s="15">
+        <v>46223.743055555555</v>
+      </c>
       <c r="H341" s="11" t="s">
         <v>76</v>
       </c>
@@ -10252,7 +10254,9 @@
       <c r="F342" s="15">
         <v>46223.669444444444</v>
       </c>
-      <c r="G342" s="15"/>
+      <c r="G342" s="15">
+        <v>46223.699305555558</v>
+      </c>
       <c r="H342" s="11" t="s">
         <v>76</v>
       </c>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1255" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31491CDB-75A2-45D3-A995-C3035D54C047}"/>
+  <xr:revisionPtr revIDLastSave="1260" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E64BE2D-7428-45B0-A46E-1F5A990B340A}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-144" windowWidth="23256" windowHeight="12456" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="114">
   <si>
     <t>ID</t>
   </si>
@@ -820,8 +820,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J342" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J342" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J343" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J343" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1202,7 +1202,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
-  <dimension ref="A9:J342"/>
+  <dimension ref="A9:J343"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -1221,7 +1221,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -10208,38 +10208,26 @@
         <v>401</v>
       </c>
       <c r="B341" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C341" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CEM</v>
+      </c>
+      <c r="D341" s="14"/>
+      <c r="E341" s="13"/>
+      <c r="F341" s="15"/>
+      <c r="G341" s="15"/>
+      <c r="H341" s="11"/>
+      <c r="I341" s="11"/>
+      <c r="J341" s="1"/>
+    </row>
+    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A342" s="1">
+        <v>402</v>
+      </c>
+      <c r="B342" s="13" t="s">
         <v>17</v>
-      </c>
-      <c r="C341" s="16" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
-        <v>CEM</v>
-      </c>
-      <c r="D341" s="14">
-        <v>75</v>
-      </c>
-      <c r="E341" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F341" s="15">
-        <v>46223.669444444444</v>
-      </c>
-      <c r="G341" s="15">
-        <v>46223.743055555555</v>
-      </c>
-      <c r="H341" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="I341" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="J341" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A342" s="1"/>
-      <c r="B342" s="13" t="s">
-        <v>19</v>
       </c>
       <c r="C342" s="16" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -10255,7 +10243,7 @@
         <v>46223.669444444444</v>
       </c>
       <c r="G342" s="15">
-        <v>46223.699305555558</v>
+        <v>46223.743055555555</v>
       </c>
       <c r="H342" s="11" t="s">
         <v>76</v>
@@ -10264,6 +10252,39 @@
         <v>77</v>
       </c>
       <c r="J342" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A343" s="1">
+        <v>403</v>
+      </c>
+      <c r="B343" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C343" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CEM</v>
+      </c>
+      <c r="D343" s="14">
+        <v>75</v>
+      </c>
+      <c r="E343" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F343" s="15">
+        <v>46223.669444444444</v>
+      </c>
+      <c r="G343" s="15">
+        <v>46223.699305555558</v>
+      </c>
+      <c r="H343" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="I343" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="J343" s="1" t="s">
         <v>23</v>
       </c>
     </row>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1260" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E64BE2D-7428-45B0-A46E-1F5A990B340A}"/>
+  <xr:revisionPtr revIDLastSave="1269" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E12FB72-738D-417F-8FBA-4AA1BC1DD611}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="114">
   <si>
     <t>ID</t>
   </si>
@@ -10094,7 +10094,7 @@
         <v>46209.348611111112</v>
       </c>
       <c r="G337" s="15">
-        <v>46210</v>
+        <v>46209.999305555553</v>
       </c>
       <c r="H337" s="11" t="s">
         <v>76</v>
@@ -10214,13 +10214,27 @@
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
-      <c r="D341" s="14"/>
-      <c r="E341" s="13"/>
-      <c r="F341" s="15"/>
-      <c r="G341" s="15"/>
-      <c r="H341" s="11"/>
-      <c r="I341" s="11"/>
-      <c r="J341" s="1"/>
+      <c r="D341" s="14">
+        <v>70</v>
+      </c>
+      <c r="E341" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F341" s="15">
+        <v>46211.326388888891</v>
+      </c>
+      <c r="G341" s="15">
+        <v>46211.999305555553</v>
+      </c>
+      <c r="H341" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="I341" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="J341" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A342" s="1">

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1269" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E12FB72-738D-417F-8FBA-4AA1BC1DD611}"/>
+  <xr:revisionPtr revIDLastSave="1275" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5994ED9D-EEC6-40F2-A7E8-6D6A03FBC5B2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="114">
   <si>
     <t>ID</t>
   </si>
@@ -820,8 +820,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J343" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J343" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J344" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J344" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1202,7 +1202,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
-  <dimension ref="A9:J343"/>
+  <dimension ref="A9:J344"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -1221,7 +1221,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -10301,6 +10301,30 @@
       <c r="J343" s="1" t="s">
         <v>23</v>
       </c>
+    </row>
+    <row r="344" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A344">
+        <v>404</v>
+      </c>
+      <c r="B344" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C344" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
+      </c>
+      <c r="D344" s="14">
+        <v>0</v>
+      </c>
+      <c r="E344" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F344" s="15">
+        <v>46232.459722222222</v>
+      </c>
+      <c r="G344" s="15"/>
+      <c r="H344" s="11"/>
+      <c r="I344" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1275" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5994ED9D-EEC6-40F2-A7E8-6D6A03FBC5B2}"/>
+  <xr:revisionPtr revIDLastSave="1278" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00632109-2F47-441C-9A52-145D4853FEA6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="116">
   <si>
     <t>ID</t>
   </si>
@@ -396,6 +396,12 @@
   </si>
   <si>
     <t>Obstrucción filtro de succión bombas de transferencia</t>
+  </si>
+  <si>
+    <t>Falla sistema de combustible a gas</t>
+  </si>
+  <si>
+    <t>Falla valvúla control de gas a TG</t>
   </si>
 </sst>
 </file>
@@ -9977,7 +9983,9 @@
       <c r="F333" s="15">
         <v>46207.680555555555</v>
       </c>
-      <c r="G333" s="15"/>
+      <c r="G333" s="15">
+        <v>46207.8125</v>
+      </c>
       <c r="H333" s="11" t="s">
         <v>108</v>
       </c>
@@ -10323,8 +10331,12 @@
         <v>46232.459722222222</v>
       </c>
       <c r="G344" s="15"/>
-      <c r="H344" s="11"/>
-      <c r="I344" s="11"/>
+      <c r="H344" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="I344" s="11" t="s">
+        <v>115</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1278" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00632109-2F47-441C-9A52-145D4853FEA6}"/>
+  <xr:revisionPtr revIDLastSave="1279" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A6D487A-92A0-4A2D-814D-3029720D0B07}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="117">
   <si>
     <t>ID</t>
   </si>
@@ -402,6 +402,9 @@
   </si>
   <si>
     <t>Falla valvúla control de gas a TG</t>
+  </si>
+  <si>
+    <t>Falla sistema de sincronismo</t>
   </si>
 </sst>
 </file>
@@ -9989,7 +9992,9 @@
       <c r="H333" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="I333" s="11"/>
+      <c r="I333" s="11" t="s">
+        <v>116</v>
+      </c>
       <c r="J333" s="1" t="s">
         <v>23</v>
       </c>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1279" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A6D487A-92A0-4A2D-814D-3029720D0B07}"/>
+  <xr:revisionPtr revIDLastSave="1280" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F15DCA13-6EC3-49A7-AA63-3A2F4B3BCCAB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="118">
   <si>
     <t>ID</t>
   </si>
@@ -405,6 +405,9 @@
   </si>
   <si>
     <t>Falla sistema de sincronismo</t>
+  </si>
+  <si>
+    <t>Falla sistema enfriamiento</t>
   </si>
 </sst>
 </file>
@@ -10023,7 +10026,9 @@
       <c r="H334" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="I334" s="11"/>
+      <c r="I334" s="11" t="s">
+        <v>117</v>
+      </c>
       <c r="J334" s="1" t="s">
         <v>23</v>
       </c>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1280" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F15DCA13-6EC3-49A7-AA63-3A2F4B3BCCAB}"/>
+  <xr:revisionPtr revIDLastSave="1281" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D0E9B35-372B-451C-BD9B-2A5F313BB5F1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -9990,7 +9990,7 @@
         <v>46207.680555555555</v>
       </c>
       <c r="G333" s="15">
-        <v>46207.8125</v>
+        <v>46207.865972222222</v>
       </c>
       <c r="H333" s="11" t="s">
         <v>108</v>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1281" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D0E9B35-372B-451C-BD9B-2A5F313BB5F1}"/>
+  <xr:revisionPtr revIDLastSave="1282" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5701F90E-8396-4236-A758-993DCDABEC18}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -10022,7 +10022,9 @@
       <c r="F334" s="15">
         <v>46207.869444444441</v>
       </c>
-      <c r="G334" s="15"/>
+      <c r="G334" s="15">
+        <v>46208.73333333333</v>
+      </c>
       <c r="H334" s="11" t="s">
         <v>109</v>
       </c>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1282" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5701F90E-8396-4236-A758-993DCDABEC18}"/>
+  <xr:revisionPtr revIDLastSave="1295" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77AE2480-2DA9-4247-BBA4-2C23A2E73592}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="118">
   <si>
     <t>ID</t>
   </si>
@@ -832,8 +832,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J344" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J344" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J345" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J345" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1214,7 +1214,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
-  <dimension ref="A9:J344"/>
+  <dimension ref="A9:J345"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -10055,7 +10055,9 @@
       <c r="F335" s="15">
         <v>46208</v>
       </c>
-      <c r="G335" s="15"/>
+      <c r="G335" s="15">
+        <v>46208.607638888891</v>
+      </c>
       <c r="H335" s="11" t="s">
         <v>109</v>
       </c>
@@ -10084,7 +10086,9 @@
       <c r="F336" s="15">
         <v>46209.345833333333</v>
       </c>
-      <c r="G336" s="15"/>
+      <c r="G336" s="15">
+        <v>46209.997916666667</v>
+      </c>
       <c r="H336" s="11" t="s">
         <v>109</v>
       </c>
@@ -10160,64 +10164,54 @@
       </c>
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A339" s="1">
-        <v>329</v>
-      </c>
-      <c r="B339" s="13" t="s">
-        <v>20</v>
-      </c>
+      <c r="A339" s="1"/>
+      <c r="B339" s="13"/>
       <c r="C339" s="16" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D339" s="14">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E339" s="13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F339" s="15">
         <v>46210.06527777778</v>
       </c>
       <c r="G339" s="15"/>
-      <c r="H339" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="I339" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="J339" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="H339" s="11"/>
+      <c r="I339" s="11"/>
+      <c r="J339" s="1"/>
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
-        <v>400</v>
+        <v>329</v>
       </c>
       <c r="B340" s="13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C340" s="16" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
-        <v>CEM</v>
+        <v>CET</v>
       </c>
       <c r="D340" s="14">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="E340" s="13" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F340" s="15">
-        <v>46210.375</v>
+        <v>46210.694444444445</v>
       </c>
       <c r="G340" s="15">
-        <v>46210.916666666664</v>
+        <v>46212.39166666667</v>
       </c>
       <c r="H340" s="11" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="I340" s="11" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="J340" s="1" t="s">
         <v>23</v>
@@ -10225,10 +10219,10 @@
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B341" s="13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C341" s="16" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -10241,10 +10235,10 @@
         <v>11</v>
       </c>
       <c r="F341" s="15">
-        <v>46211.326388888891</v>
+        <v>46210.375</v>
       </c>
       <c r="G341" s="15">
-        <v>46211.999305555553</v>
+        <v>46210.916666666664</v>
       </c>
       <c r="H341" s="11" t="s">
         <v>76</v>
@@ -10258,26 +10252,26 @@
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A342" s="1">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B342" s="13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C342" s="16" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D342" s="14">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E342" s="13" t="s">
         <v>11</v>
       </c>
       <c r="F342" s="15">
-        <v>46223.669444444444</v>
+        <v>46211.326388888891</v>
       </c>
       <c r="G342" s="15">
-        <v>46223.743055555555</v>
+        <v>46211.999305555553</v>
       </c>
       <c r="H342" s="11" t="s">
         <v>76</v>
@@ -10291,10 +10285,10 @@
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A343" s="1">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B343" s="13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C343" s="16" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -10310,7 +10304,7 @@
         <v>46223.669444444444</v>
       </c>
       <c r="G343" s="15">
-        <v>46223.699305555558</v>
+        <v>46223.743055555555</v>
       </c>
       <c r="H343" s="11" t="s">
         <v>76</v>
@@ -10323,30 +10317,63 @@
       </c>
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A344">
+      <c r="A344" s="1">
+        <v>403</v>
+      </c>
+      <c r="B344" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C344" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CEM</v>
+      </c>
+      <c r="D344" s="14">
+        <v>75</v>
+      </c>
+      <c r="E344" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F344" s="15">
+        <v>46223.669444444444</v>
+      </c>
+      <c r="G344" s="15">
+        <v>46223.699305555558</v>
+      </c>
+      <c r="H344" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="I344" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="J344" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A345">
         <v>404</v>
       </c>
-      <c r="B344" s="13" t="s">
+      <c r="B345" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C344" s="16" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
-        <v>CET</v>
-      </c>
-      <c r="D344" s="14">
-        <v>0</v>
-      </c>
-      <c r="E344" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F344" s="15">
+      <c r="C345" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
+      </c>
+      <c r="D345" s="14">
+        <v>0</v>
+      </c>
+      <c r="E345" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F345" s="15">
         <v>46232.459722222222</v>
       </c>
-      <c r="G344" s="15"/>
-      <c r="H344" s="11" t="s">
+      <c r="G345" s="15"/>
+      <c r="H345" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="I344" s="11" t="s">
+      <c r="I345" s="11" t="s">
         <v>115</v>
       </c>
     </row>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1295" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77AE2480-2DA9-4247-BBA4-2C23A2E73592}"/>
+  <xr:revisionPtr revIDLastSave="1302" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEC0BC57-0D6A-4405-B746-6F0BEA98D152}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="119">
   <si>
     <t>ID</t>
   </si>
@@ -389,9 +389,6 @@
     <t>Falla sistema combustible DO</t>
   </si>
   <si>
-    <t>Falla sistema de admisión</t>
-  </si>
-  <si>
     <t>Obstrucciín filtro admisión</t>
   </si>
   <si>
@@ -408,6 +405,12 @@
   </si>
   <si>
     <t>Falla sistema enfriamiento</t>
+  </si>
+  <si>
+    <t>Sistema admisón compresor</t>
+  </si>
+  <si>
+    <t>Filtro de admisión obstruido</t>
   </si>
 </sst>
 </file>
@@ -1233,7 +1236,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -9996,7 +9999,7 @@
         <v>108</v>
       </c>
       <c r="I333" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J333" s="1" t="s">
         <v>23</v>
@@ -10029,7 +10032,7 @@
         <v>109</v>
       </c>
       <c r="I334" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J334" s="1" t="s">
         <v>23</v>
@@ -10157,15 +10160,19 @@
         <v>110</v>
       </c>
       <c r="I338" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J338" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A339" s="1"/>
-      <c r="B339" s="13"/>
+      <c r="A339" s="1">
+        <v>329</v>
+      </c>
+      <c r="B339" s="13" t="s">
+        <v>20</v>
+      </c>
       <c r="C339" s="16" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
@@ -10179,14 +10186,20 @@
       <c r="F339" s="15">
         <v>46210.06527777778</v>
       </c>
-      <c r="G339" s="15"/>
-      <c r="H339" s="11"/>
-      <c r="I339" s="11"/>
+      <c r="G339" s="15">
+        <v>46212.39166666667</v>
+      </c>
+      <c r="H339" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I339" s="11" t="s">
+        <v>118</v>
+      </c>
       <c r="J339" s="1"/>
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B340" s="13" t="s">
         <v>20</v>
@@ -10205,13 +10218,13 @@
         <v>46210.694444444445</v>
       </c>
       <c r="G340" s="15">
-        <v>46212.39166666667</v>
+        <v>46211.429166666669</v>
       </c>
       <c r="H340" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I340" s="11" t="s">
         <v>111</v>
-      </c>
-      <c r="I340" s="11" t="s">
-        <v>112</v>
       </c>
       <c r="J340" s="1" t="s">
         <v>23</v>
@@ -10219,7 +10232,7 @@
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
-        <v>400</v>
+        <v>331</v>
       </c>
       <c r="B341" s="13" t="s">
         <v>17</v>
@@ -10252,7 +10265,7 @@
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A342" s="1">
-        <v>401</v>
+        <v>332</v>
       </c>
       <c r="B342" s="13" t="s">
         <v>19</v>
@@ -10285,7 +10298,7 @@
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A343" s="1">
-        <v>402</v>
+        <v>333</v>
       </c>
       <c r="B343" s="13" t="s">
         <v>17</v>
@@ -10318,7 +10331,7 @@
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A344" s="1">
-        <v>403</v>
+        <v>334</v>
       </c>
       <c r="B344" s="13" t="s">
         <v>19</v>
@@ -10350,8 +10363,8 @@
       </c>
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A345">
-        <v>404</v>
+      <c r="A345" s="1">
+        <v>335</v>
       </c>
       <c r="B345" s="13" t="s">
         <v>12</v>
@@ -10371,10 +10384,10 @@
       </c>
       <c r="G345" s="15"/>
       <c r="H345" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="I345" s="11" t="s">
         <v>114</v>
-      </c>
-      <c r="I345" s="11" t="s">
-        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1302" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEC0BC57-0D6A-4405-B746-6F0BEA98D152}"/>
+  <xr:revisionPtr revIDLastSave="1304" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FDC2689-6532-4763-ADB6-E8FD2E68B365}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="119">
   <si>
     <t>ID</t>
   </si>
@@ -10064,7 +10064,9 @@
       <c r="H335" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="I335" s="11"/>
+      <c r="I335" s="11" t="s">
+        <v>116</v>
+      </c>
       <c r="J335" s="1" t="s">
         <v>23</v>
       </c>
@@ -10095,7 +10097,9 @@
       <c r="H336" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="I336" s="11"/>
+      <c r="I336" s="11" t="s">
+        <v>116</v>
+      </c>
       <c r="J336" s="1" t="s">
         <v>23</v>
       </c>
@@ -10195,7 +10199,9 @@
       <c r="I339" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="J339" s="1"/>
+      <c r="J339" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A340" s="1">

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1304" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FDC2689-6532-4763-ADB6-E8FD2E68B365}"/>
+  <xr:revisionPtr revIDLastSave="1308" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98B5A0EC-FF7C-4F0A-BC7E-A8D969745523}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="120">
   <si>
     <t>ID</t>
   </si>
@@ -314,6 +314,69 @@
     <t>Ritura de tubos en calderRH1 y RH2</t>
   </si>
   <si>
+    <t>TG2</t>
+  </si>
+  <si>
+    <t>Falla en arranque</t>
+  </si>
+  <si>
+    <t>Sistema de arranque en falla</t>
+  </si>
+  <si>
+    <t>Inspección alimentador de carbón N°2</t>
+  </si>
+  <si>
+    <t>Se retira de gran granulometria alojado al interior del alimentador de carbón N°2, alimentador de carbón N°4 indisponible</t>
+  </si>
+  <si>
+    <t>Activación fuga de gas en TG</t>
+  </si>
+  <si>
+    <t>Falla sensor detector de gas</t>
+  </si>
+  <si>
+    <t>Descalople TV</t>
+  </si>
+  <si>
+    <t>Altas vibraciónes TV cojinete N°5</t>
+  </si>
+  <si>
+    <t>Falla en la partida</t>
+  </si>
+  <si>
+    <t>Falla sistema de sincronismo</t>
+  </si>
+  <si>
+    <t>Alta temperatura en generador</t>
+  </si>
+  <si>
+    <t>Falla sistema enfriamiento</t>
+  </si>
+  <si>
+    <t>Falla sistema combustible DO</t>
+  </si>
+  <si>
+    <t>Obstrucción filtro de succión bombas de transferencia</t>
+  </si>
+  <si>
+    <t>Sistema admisón compresor</t>
+  </si>
+  <si>
+    <t>Filtro de admisión obstruido</t>
+  </si>
+  <si>
+    <t>Obstrucciín filtro admisión</t>
+  </si>
+  <si>
+    <t>7/29/2026  13:39:00 AM</t>
+  </si>
+  <si>
+    <t>Falla sistema de combustible a gas</t>
+  </si>
+  <si>
+    <t>Falla valvúla control de gas a TG</t>
+  </si>
+  <si>
     <t>P_Max_Bruta</t>
   </si>
   <si>
@@ -326,9 +389,6 @@
     <t>CET</t>
   </si>
   <si>
-    <t>TG2</t>
-  </si>
-  <si>
     <t>Fecha_Hora_Fin</t>
   </si>
   <si>
@@ -354,70 +414,13 @@
   </si>
   <si>
     <t>FechaFinVigencia</t>
-  </si>
-  <si>
-    <t>Falla en arranque</t>
-  </si>
-  <si>
-    <t>Sistema de arranque en falla</t>
-  </si>
-  <si>
-    <t>Inspección alimentador de carbón N°2</t>
-  </si>
-  <si>
-    <t>Se retira de gran granulometria alojado al interior del alimentador de carbón N°2, alimentador de carbón N°4 indisponible</t>
-  </si>
-  <si>
-    <t>Activación fuga de gas en TG</t>
-  </si>
-  <si>
-    <t>Falla sensor detector de gas</t>
-  </si>
-  <si>
-    <t>Descalople TV</t>
-  </si>
-  <si>
-    <t>Altas vibraciónes TV cojinete N°5</t>
-  </si>
-  <si>
-    <t>Falla en la partida</t>
-  </si>
-  <si>
-    <t>Alta temperatura en generador</t>
-  </si>
-  <si>
-    <t>Falla sistema combustible DO</t>
-  </si>
-  <si>
-    <t>Obstrucciín filtro admisión</t>
-  </si>
-  <si>
-    <t>Obstrucción filtro de succión bombas de transferencia</t>
-  </si>
-  <si>
-    <t>Falla sistema de combustible a gas</t>
-  </si>
-  <si>
-    <t>Falla valvúla control de gas a TG</t>
-  </si>
-  <si>
-    <t>Falla sistema de sincronismo</t>
-  </si>
-  <si>
-    <t>Falla sistema enfriamiento</t>
-  </si>
-  <si>
-    <t>Sistema admisón compresor</t>
-  </si>
-  <si>
-    <t>Filtro de admisión obstruido</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -454,7 +457,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -495,9 +498,6 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -508,10 +508,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -520,11 +520,11 @@
       <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1218,7 +1218,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
   <dimension ref="A9:J345"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
@@ -1233,13 +1233,13 @@
     <col min="12" max="12" width="33.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
         <v>335</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -1297,7 +1297,7 @@
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -1323,7 +1323,7 @@
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10">
       <c r="A13" s="1">
         <v>3</v>
       </c>
@@ -1349,7 +1349,7 @@
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10">
       <c r="A14" s="1">
         <v>4</v>
       </c>
@@ -1375,7 +1375,7 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10">
       <c r="A15" s="1">
         <v>5</v>
       </c>
@@ -1401,7 +1401,7 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10">
       <c r="A16" s="1">
         <v>6</v>
       </c>
@@ -1427,7 +1427,7 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9">
       <c r="A17" s="1">
         <v>7</v>
       </c>
@@ -1453,7 +1453,7 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9">
       <c r="A18" s="1">
         <v>8</v>
       </c>
@@ -1479,7 +1479,7 @@
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9">
       <c r="A19" s="1">
         <v>9</v>
       </c>
@@ -1505,7 +1505,7 @@
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9">
       <c r="A20" s="1">
         <v>10</v>
       </c>
@@ -1531,7 +1531,7 @@
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9">
       <c r="A21" s="1">
         <v>11</v>
       </c>
@@ -1557,7 +1557,7 @@
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9">
       <c r="A22" s="1">
         <v>12</v>
       </c>
@@ -1583,7 +1583,7 @@
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9">
       <c r="A23" s="1">
         <v>13</v>
       </c>
@@ -1609,7 +1609,7 @@
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9">
       <c r="A24" s="1">
         <v>14</v>
       </c>
@@ -1635,7 +1635,7 @@
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9">
       <c r="A25" s="1">
         <v>15</v>
       </c>
@@ -1661,7 +1661,7 @@
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9">
       <c r="A26" s="1">
         <v>16</v>
       </c>
@@ -1687,7 +1687,7 @@
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9">
       <c r="A27" s="1">
         <v>17</v>
       </c>
@@ -1713,7 +1713,7 @@
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9">
       <c r="A28" s="1">
         <v>18</v>
       </c>
@@ -1739,7 +1739,7 @@
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9">
       <c r="A29" s="1">
         <v>19</v>
       </c>
@@ -1765,7 +1765,7 @@
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9">
       <c r="A30" s="1">
         <v>20</v>
       </c>
@@ -1791,7 +1791,7 @@
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9">
       <c r="A31" s="1">
         <v>21</v>
       </c>
@@ -1817,7 +1817,7 @@
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9">
       <c r="A32" s="1">
         <v>22</v>
       </c>
@@ -1843,7 +1843,7 @@
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9">
       <c r="A33" s="1">
         <v>23</v>
       </c>
@@ -1869,7 +1869,7 @@
       <c r="H33" s="11"/>
       <c r="I33" s="11"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9">
       <c r="A34" s="1">
         <v>24</v>
       </c>
@@ -1895,7 +1895,7 @@
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9">
       <c r="A35" s="1">
         <v>25</v>
       </c>
@@ -1921,7 +1921,7 @@
       <c r="H35" s="11"/>
       <c r="I35" s="11"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9">
       <c r="A36" s="1">
         <v>26</v>
       </c>
@@ -1947,7 +1947,7 @@
       <c r="H36" s="11"/>
       <c r="I36" s="11"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9">
       <c r="A37" s="1">
         <v>27</v>
       </c>
@@ -1973,7 +1973,7 @@
       <c r="H37" s="11"/>
       <c r="I37" s="11"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9">
       <c r="A38" s="1">
         <v>28</v>
       </c>
@@ -1999,7 +1999,7 @@
       <c r="H38" s="11"/>
       <c r="I38" s="11"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9">
       <c r="A39" s="1">
         <v>29</v>
       </c>
@@ -2025,7 +2025,7 @@
       <c r="H39" s="11"/>
       <c r="I39" s="11"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9">
       <c r="A40" s="1">
         <v>30</v>
       </c>
@@ -2051,7 +2051,7 @@
       <c r="H40" s="11"/>
       <c r="I40" s="11"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9">
       <c r="A41" s="1">
         <v>31</v>
       </c>
@@ -2077,7 +2077,7 @@
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9">
       <c r="A42" s="1">
         <v>32</v>
       </c>
@@ -2103,7 +2103,7 @@
       <c r="H42" s="11"/>
       <c r="I42" s="11"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9">
       <c r="A43" s="1">
         <v>33</v>
       </c>
@@ -2129,7 +2129,7 @@
       <c r="H43" s="11"/>
       <c r="I43" s="11"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9">
       <c r="A44" s="1">
         <v>34</v>
       </c>
@@ -2155,7 +2155,7 @@
       <c r="H44" s="11"/>
       <c r="I44" s="11"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9">
       <c r="A45" s="1">
         <v>35</v>
       </c>
@@ -2181,7 +2181,7 @@
       <c r="H45" s="11"/>
       <c r="I45" s="11"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9">
       <c r="A46" s="1">
         <v>36</v>
       </c>
@@ -2207,7 +2207,7 @@
       <c r="H46" s="11"/>
       <c r="I46" s="11"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9">
       <c r="A47" s="1">
         <v>37</v>
       </c>
@@ -2233,7 +2233,7 @@
       <c r="H47" s="11"/>
       <c r="I47" s="11"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9">
       <c r="A48" s="1">
         <v>38</v>
       </c>
@@ -2259,7 +2259,7 @@
       <c r="H48" s="11"/>
       <c r="I48" s="11"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9">
       <c r="A49" s="1">
         <v>39</v>
       </c>
@@ -2285,7 +2285,7 @@
       <c r="H49" s="11"/>
       <c r="I49" s="11"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9">
       <c r="A50" s="1">
         <v>40</v>
       </c>
@@ -2311,7 +2311,7 @@
       <c r="H50" s="11"/>
       <c r="I50" s="11"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9">
       <c r="A51" s="1">
         <v>41</v>
       </c>
@@ -2337,7 +2337,7 @@
       <c r="H51" s="11"/>
       <c r="I51" s="11"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9">
       <c r="A52" s="1">
         <v>42</v>
       </c>
@@ -2363,7 +2363,7 @@
       <c r="H52" s="11"/>
       <c r="I52" s="11"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9">
       <c r="A53" s="1">
         <v>43</v>
       </c>
@@ -2389,7 +2389,7 @@
       <c r="H53" s="11"/>
       <c r="I53" s="11"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9">
       <c r="A54" s="1">
         <v>44</v>
       </c>
@@ -2415,7 +2415,7 @@
       <c r="H54" s="11"/>
       <c r="I54" s="11"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9">
       <c r="A55" s="1">
         <v>45</v>
       </c>
@@ -2441,7 +2441,7 @@
       <c r="H55" s="11"/>
       <c r="I55" s="11"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9">
       <c r="A56" s="1">
         <v>46</v>
       </c>
@@ -2467,7 +2467,7 @@
       <c r="H56" s="11"/>
       <c r="I56" s="11"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9">
       <c r="A57" s="1">
         <v>47</v>
       </c>
@@ -2493,7 +2493,7 @@
       <c r="H57" s="11"/>
       <c r="I57" s="11"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9">
       <c r="A58" s="1">
         <v>48</v>
       </c>
@@ -2519,7 +2519,7 @@
       <c r="H58" s="11"/>
       <c r="I58" s="11"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9">
       <c r="A59" s="1">
         <v>49</v>
       </c>
@@ -2545,7 +2545,7 @@
       <c r="H59" s="11"/>
       <c r="I59" s="11"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9">
       <c r="A60" s="1">
         <v>50</v>
       </c>
@@ -2571,7 +2571,7 @@
       <c r="H60" s="11"/>
       <c r="I60" s="11"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9">
       <c r="A61" s="1">
         <v>51</v>
       </c>
@@ -2597,7 +2597,7 @@
       <c r="H61" s="11"/>
       <c r="I61" s="11"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9">
       <c r="A62" s="1">
         <v>52</v>
       </c>
@@ -2623,7 +2623,7 @@
       <c r="H62" s="11"/>
       <c r="I62" s="11"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9">
       <c r="A63" s="1">
         <v>53</v>
       </c>
@@ -2649,7 +2649,7 @@
       <c r="H63" s="11"/>
       <c r="I63" s="11"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9">
       <c r="A64" s="1">
         <v>54</v>
       </c>
@@ -2675,7 +2675,7 @@
       <c r="H64" s="11"/>
       <c r="I64" s="11"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9">
       <c r="A65" s="1">
         <v>55</v>
       </c>
@@ -2701,7 +2701,7 @@
       <c r="H65" s="11"/>
       <c r="I65" s="11"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9">
       <c r="A66" s="1">
         <v>56</v>
       </c>
@@ -2727,7 +2727,7 @@
       <c r="H66" s="11"/>
       <c r="I66" s="11"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9">
       <c r="A67" s="1">
         <v>57</v>
       </c>
@@ -2753,7 +2753,7 @@
       <c r="H67" s="11"/>
       <c r="I67" s="11"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9">
       <c r="A68" s="1">
         <v>58</v>
       </c>
@@ -2779,7 +2779,7 @@
       <c r="H68" s="11"/>
       <c r="I68" s="11"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9">
       <c r="A69" s="1">
         <v>59</v>
       </c>
@@ -2805,7 +2805,7 @@
       <c r="H69" s="11"/>
       <c r="I69" s="11"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9">
       <c r="A70" s="1">
         <v>60</v>
       </c>
@@ -2831,7 +2831,7 @@
       <c r="H70" s="11"/>
       <c r="I70" s="11"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9">
       <c r="A71" s="1">
         <v>61</v>
       </c>
@@ -2857,7 +2857,7 @@
       <c r="H71" s="11"/>
       <c r="I71" s="11"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9">
       <c r="A72" s="1">
         <v>62</v>
       </c>
@@ -2883,7 +2883,7 @@
       <c r="H72" s="11"/>
       <c r="I72" s="11"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9">
       <c r="A73" s="1">
         <v>63</v>
       </c>
@@ -2909,7 +2909,7 @@
       <c r="H73" s="11"/>
       <c r="I73" s="11"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9">
       <c r="A74" s="1">
         <v>64</v>
       </c>
@@ -2935,7 +2935,7 @@
       <c r="H74" s="11"/>
       <c r="I74" s="11"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9">
       <c r="A75" s="1">
         <v>65</v>
       </c>
@@ -2961,7 +2961,7 @@
       <c r="H75" s="11"/>
       <c r="I75" s="11"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9">
       <c r="A76" s="1">
         <v>66</v>
       </c>
@@ -2987,7 +2987,7 @@
       <c r="H76" s="11"/>
       <c r="I76" s="11"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9">
       <c r="A77" s="1">
         <v>67</v>
       </c>
@@ -3013,7 +3013,7 @@
       <c r="H77" s="11"/>
       <c r="I77" s="11"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9">
       <c r="A78" s="1">
         <v>68</v>
       </c>
@@ -3039,7 +3039,7 @@
       <c r="H78" s="11"/>
       <c r="I78" s="11"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9">
       <c r="A79" s="1">
         <v>69</v>
       </c>
@@ -3065,7 +3065,7 @@
       <c r="H79" s="11"/>
       <c r="I79" s="11"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9">
       <c r="A80" s="1">
         <v>70</v>
       </c>
@@ -3091,7 +3091,7 @@
       <c r="H80" s="11"/>
       <c r="I80" s="11"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9">
       <c r="A81" s="1">
         <v>71</v>
       </c>
@@ -3117,7 +3117,7 @@
       <c r="H81" s="11"/>
       <c r="I81" s="11"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9">
       <c r="A82" s="1">
         <v>72</v>
       </c>
@@ -3143,7 +3143,7 @@
       <c r="H82" s="11"/>
       <c r="I82" s="11"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9">
       <c r="A83" s="1">
         <v>73</v>
       </c>
@@ -3169,7 +3169,7 @@
       <c r="H83" s="11"/>
       <c r="I83" s="11"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9">
       <c r="A84" s="1">
         <v>74</v>
       </c>
@@ -3195,7 +3195,7 @@
       <c r="H84" s="11"/>
       <c r="I84" s="11"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9">
       <c r="A85" s="1">
         <v>75</v>
       </c>
@@ -3221,7 +3221,7 @@
       <c r="H85" s="11"/>
       <c r="I85" s="11"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9">
       <c r="A86" s="1">
         <v>76</v>
       </c>
@@ -3247,7 +3247,7 @@
       <c r="H86" s="11"/>
       <c r="I86" s="11"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9">
       <c r="A87" s="1">
         <v>77</v>
       </c>
@@ -3273,7 +3273,7 @@
       <c r="H87" s="11"/>
       <c r="I87" s="11"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9">
       <c r="A88" s="1">
         <v>78</v>
       </c>
@@ -3299,7 +3299,7 @@
       <c r="H88" s="11"/>
       <c r="I88" s="11"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9">
       <c r="A89" s="1">
         <v>79</v>
       </c>
@@ -3325,7 +3325,7 @@
       <c r="H89" s="11"/>
       <c r="I89" s="11"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9">
       <c r="A90" s="1">
         <v>80</v>
       </c>
@@ -3351,7 +3351,7 @@
       <c r="H90" s="11"/>
       <c r="I90" s="11"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9">
       <c r="A91" s="1">
         <v>81</v>
       </c>
@@ -3377,7 +3377,7 @@
       <c r="H91" s="11"/>
       <c r="I91" s="11"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9">
       <c r="A92" s="1">
         <v>82</v>
       </c>
@@ -3403,7 +3403,7 @@
       <c r="H92" s="11"/>
       <c r="I92" s="11"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9">
       <c r="A93" s="1">
         <v>83</v>
       </c>
@@ -3429,7 +3429,7 @@
       <c r="H93" s="11"/>
       <c r="I93" s="11"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9">
       <c r="A94" s="1">
         <v>84</v>
       </c>
@@ -3455,7 +3455,7 @@
       <c r="H94" s="11"/>
       <c r="I94" s="11"/>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9">
       <c r="A95" s="1">
         <v>85</v>
       </c>
@@ -3481,7 +3481,7 @@
       <c r="H95" s="11"/>
       <c r="I95" s="11"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9">
       <c r="A96" s="1">
         <v>86</v>
       </c>
@@ -3507,7 +3507,7 @@
       <c r="H96" s="11"/>
       <c r="I96" s="11"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9">
       <c r="A97" s="1">
         <v>87</v>
       </c>
@@ -3533,7 +3533,7 @@
       <c r="H97" s="11"/>
       <c r="I97" s="11"/>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9">
       <c r="A98" s="1">
         <v>88</v>
       </c>
@@ -3559,7 +3559,7 @@
       <c r="H98" s="11"/>
       <c r="I98" s="11"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9">
       <c r="A99" s="1">
         <v>89</v>
       </c>
@@ -3585,7 +3585,7 @@
       <c r="H99" s="11"/>
       <c r="I99" s="11"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9">
       <c r="A100" s="1">
         <v>90</v>
       </c>
@@ -3611,7 +3611,7 @@
       <c r="H100" s="11"/>
       <c r="I100" s="11"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9">
       <c r="A101" s="1">
         <v>91</v>
       </c>
@@ -3637,7 +3637,7 @@
       <c r="H101" s="11"/>
       <c r="I101" s="11"/>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9">
       <c r="A102" s="1">
         <v>92</v>
       </c>
@@ -3663,7 +3663,7 @@
       <c r="H102" s="11"/>
       <c r="I102" s="11"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9">
       <c r="A103" s="1">
         <v>93</v>
       </c>
@@ -3689,7 +3689,7 @@
       <c r="H103" s="11"/>
       <c r="I103" s="11"/>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9">
       <c r="A104" s="1">
         <v>94</v>
       </c>
@@ -3715,7 +3715,7 @@
       <c r="H104" s="11"/>
       <c r="I104" s="11"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9">
       <c r="A105" s="1">
         <v>95</v>
       </c>
@@ -3741,7 +3741,7 @@
       <c r="H105" s="11"/>
       <c r="I105" s="11"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9">
       <c r="A106" s="1">
         <v>96</v>
       </c>
@@ -3767,7 +3767,7 @@
       <c r="H106" s="11"/>
       <c r="I106" s="11"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9">
       <c r="A107" s="1">
         <v>97</v>
       </c>
@@ -3793,7 +3793,7 @@
       <c r="H107" s="11"/>
       <c r="I107" s="11"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9">
       <c r="A108" s="1">
         <v>98</v>
       </c>
@@ -3819,7 +3819,7 @@
       <c r="H108" s="11"/>
       <c r="I108" s="11"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9">
       <c r="A109" s="1">
         <v>99</v>
       </c>
@@ -3845,7 +3845,7 @@
       <c r="H109" s="11"/>
       <c r="I109" s="11"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9">
       <c r="A110" s="1">
         <v>100</v>
       </c>
@@ -3871,7 +3871,7 @@
       <c r="H110" s="11"/>
       <c r="I110" s="11"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9">
       <c r="A111" s="1">
         <v>101</v>
       </c>
@@ -3897,7 +3897,7 @@
       <c r="H111" s="11"/>
       <c r="I111" s="11"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9">
       <c r="A112" s="1">
         <v>102</v>
       </c>
@@ -3923,7 +3923,7 @@
       <c r="H112" s="11"/>
       <c r="I112" s="11"/>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9">
       <c r="A113" s="1">
         <v>103</v>
       </c>
@@ -3949,7 +3949,7 @@
       <c r="H113" s="11"/>
       <c r="I113" s="11"/>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9">
       <c r="A114" s="1">
         <v>104</v>
       </c>
@@ -3975,7 +3975,7 @@
       <c r="H114" s="11"/>
       <c r="I114" s="11"/>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9">
       <c r="A115" s="1">
         <v>105</v>
       </c>
@@ -4001,7 +4001,7 @@
       <c r="H115" s="11"/>
       <c r="I115" s="11"/>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9">
       <c r="A116" s="1">
         <v>106</v>
       </c>
@@ -4027,7 +4027,7 @@
       <c r="H116" s="11"/>
       <c r="I116" s="11"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9">
       <c r="A117" s="1">
         <v>107</v>
       </c>
@@ -4053,7 +4053,7 @@
       <c r="H117" s="11"/>
       <c r="I117" s="11"/>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9">
       <c r="A118" s="1">
         <v>108</v>
       </c>
@@ -4079,7 +4079,7 @@
       <c r="H118" s="11"/>
       <c r="I118" s="11"/>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9">
       <c r="A119" s="1">
         <v>109</v>
       </c>
@@ -4105,7 +4105,7 @@
       <c r="H119" s="11"/>
       <c r="I119" s="11"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9">
       <c r="A120" s="1">
         <v>110</v>
       </c>
@@ -4131,7 +4131,7 @@
       <c r="H120" s="11"/>
       <c r="I120" s="11"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9">
       <c r="A121" s="1">
         <v>111</v>
       </c>
@@ -4157,7 +4157,7 @@
       <c r="H121" s="11"/>
       <c r="I121" s="11"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9">
       <c r="A122" s="1">
         <v>112</v>
       </c>
@@ -4183,7 +4183,7 @@
       <c r="H122" s="11"/>
       <c r="I122" s="11"/>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9">
       <c r="A123" s="1">
         <v>113</v>
       </c>
@@ -4209,7 +4209,7 @@
       <c r="H123" s="11"/>
       <c r="I123" s="11"/>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9">
       <c r="A124" s="1">
         <v>114</v>
       </c>
@@ -4235,7 +4235,7 @@
       <c r="H124" s="11"/>
       <c r="I124" s="11"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9">
       <c r="A125" s="1">
         <v>115</v>
       </c>
@@ -4261,7 +4261,7 @@
       <c r="H125" s="11"/>
       <c r="I125" s="11"/>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9">
       <c r="A126" s="1">
         <v>116</v>
       </c>
@@ -4287,7 +4287,7 @@
       <c r="H126" s="11"/>
       <c r="I126" s="11"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9">
       <c r="A127" s="1">
         <v>117</v>
       </c>
@@ -4313,7 +4313,7 @@
       <c r="H127" s="11"/>
       <c r="I127" s="11"/>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9">
       <c r="A128" s="1">
         <v>118</v>
       </c>
@@ -4339,7 +4339,7 @@
       <c r="H128" s="11"/>
       <c r="I128" s="11"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9">
       <c r="A129" s="1">
         <v>119</v>
       </c>
@@ -4365,7 +4365,7 @@
       <c r="H129" s="11"/>
       <c r="I129" s="11"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9">
       <c r="A130" s="1">
         <v>120</v>
       </c>
@@ -4391,7 +4391,7 @@
       <c r="H130" s="11"/>
       <c r="I130" s="11"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9">
       <c r="A131" s="1">
         <v>121</v>
       </c>
@@ -4417,7 +4417,7 @@
       <c r="H131" s="11"/>
       <c r="I131" s="11"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9">
       <c r="A132" s="1">
         <v>122</v>
       </c>
@@ -4443,7 +4443,7 @@
       <c r="H132" s="11"/>
       <c r="I132" s="11"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9">
       <c r="A133" s="1">
         <v>123</v>
       </c>
@@ -4469,7 +4469,7 @@
       <c r="H133" s="11"/>
       <c r="I133" s="11"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9">
       <c r="A134" s="1">
         <v>124</v>
       </c>
@@ -4495,7 +4495,7 @@
       <c r="H134" s="11"/>
       <c r="I134" s="11"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9">
       <c r="A135" s="1">
         <v>125</v>
       </c>
@@ -4521,7 +4521,7 @@
       <c r="H135" s="11"/>
       <c r="I135" s="11"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9">
       <c r="A136" s="1">
         <v>126</v>
       </c>
@@ -4547,7 +4547,7 @@
       <c r="H136" s="11"/>
       <c r="I136" s="11"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9">
       <c r="A137" s="1">
         <v>127</v>
       </c>
@@ -4573,7 +4573,7 @@
       <c r="H137" s="11"/>
       <c r="I137" s="11"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9">
       <c r="A138" s="1">
         <v>128</v>
       </c>
@@ -4599,7 +4599,7 @@
       <c r="H138" s="11"/>
       <c r="I138" s="11"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9">
       <c r="A139" s="1">
         <v>129</v>
       </c>
@@ -4625,7 +4625,7 @@
       <c r="H139" s="11"/>
       <c r="I139" s="11"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9">
       <c r="A140" s="1">
         <v>130</v>
       </c>
@@ -4651,7 +4651,7 @@
       <c r="H140" s="11"/>
       <c r="I140" s="11"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9">
       <c r="A141" s="1">
         <v>131</v>
       </c>
@@ -4677,7 +4677,7 @@
       <c r="H141" s="11"/>
       <c r="I141" s="11"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9">
       <c r="A142" s="1">
         <v>132</v>
       </c>
@@ -4703,7 +4703,7 @@
       <c r="H142" s="11"/>
       <c r="I142" s="11"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9">
       <c r="A143" s="1">
         <v>133</v>
       </c>
@@ -4729,7 +4729,7 @@
       <c r="H143" s="11"/>
       <c r="I143" s="11"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9">
       <c r="A144" s="1">
         <v>134</v>
       </c>
@@ -4755,7 +4755,7 @@
       <c r="H144" s="11"/>
       <c r="I144" s="11"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9">
       <c r="A145" s="1">
         <v>135</v>
       </c>
@@ -4781,7 +4781,7 @@
       <c r="H145" s="11"/>
       <c r="I145" s="11"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9">
       <c r="A146" s="1">
         <v>136</v>
       </c>
@@ -4807,7 +4807,7 @@
       <c r="H146" s="11"/>
       <c r="I146" s="11"/>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9">
       <c r="A147" s="1">
         <v>137</v>
       </c>
@@ -4833,7 +4833,7 @@
       <c r="H147" s="11"/>
       <c r="I147" s="11"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9">
       <c r="A148" s="1">
         <v>138</v>
       </c>
@@ -4859,7 +4859,7 @@
       <c r="H148" s="11"/>
       <c r="I148" s="11"/>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9">
       <c r="A149" s="1">
         <v>139</v>
       </c>
@@ -4885,7 +4885,7 @@
       <c r="H149" s="11"/>
       <c r="I149" s="11"/>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9">
       <c r="A150" s="1">
         <v>140</v>
       </c>
@@ -4911,7 +4911,7 @@
       <c r="H150" s="11"/>
       <c r="I150" s="11"/>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9">
       <c r="A151" s="1">
         <v>141</v>
       </c>
@@ -4937,7 +4937,7 @@
       <c r="H151" s="11"/>
       <c r="I151" s="11"/>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9">
       <c r="A152" s="1">
         <v>142</v>
       </c>
@@ -4963,7 +4963,7 @@
       <c r="H152" s="11"/>
       <c r="I152" s="11"/>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9">
       <c r="A153" s="1">
         <v>143</v>
       </c>
@@ -4989,7 +4989,7 @@
       <c r="H153" s="11"/>
       <c r="I153" s="11"/>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9">
       <c r="A154" s="1">
         <v>144</v>
       </c>
@@ -5015,7 +5015,7 @@
       <c r="H154" s="11"/>
       <c r="I154" s="11"/>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9">
       <c r="A155" s="1">
         <v>145</v>
       </c>
@@ -5041,7 +5041,7 @@
       <c r="H155" s="11"/>
       <c r="I155" s="11"/>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9">
       <c r="A156" s="1">
         <v>146</v>
       </c>
@@ -5067,7 +5067,7 @@
       <c r="H156" s="11"/>
       <c r="I156" s="11"/>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9">
       <c r="A157" s="1">
         <v>147</v>
       </c>
@@ -5093,7 +5093,7 @@
       <c r="H157" s="11"/>
       <c r="I157" s="11"/>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9">
       <c r="A158" s="1">
         <v>148</v>
       </c>
@@ -5119,7 +5119,7 @@
       <c r="H158" s="11"/>
       <c r="I158" s="11"/>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9">
       <c r="A159" s="1">
         <v>149</v>
       </c>
@@ -5145,7 +5145,7 @@
       <c r="H159" s="11"/>
       <c r="I159" s="11"/>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9">
       <c r="A160" s="1">
         <v>150</v>
       </c>
@@ -5171,7 +5171,7 @@
       <c r="H160" s="11"/>
       <c r="I160" s="11"/>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9">
       <c r="A161" s="1">
         <v>151</v>
       </c>
@@ -5197,7 +5197,7 @@
       <c r="H161" s="11"/>
       <c r="I161" s="11"/>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9">
       <c r="A162" s="1">
         <v>152</v>
       </c>
@@ -5223,7 +5223,7 @@
       <c r="H162" s="11"/>
       <c r="I162" s="11"/>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9">
       <c r="A163" s="1">
         <v>153</v>
       </c>
@@ -5249,7 +5249,7 @@
       <c r="H163" s="11"/>
       <c r="I163" s="11"/>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9">
       <c r="A164" s="1">
         <v>154</v>
       </c>
@@ -5275,7 +5275,7 @@
       <c r="H164" s="11"/>
       <c r="I164" s="11"/>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9">
       <c r="A165" s="1">
         <v>155</v>
       </c>
@@ -5301,7 +5301,7 @@
       <c r="H165" s="11"/>
       <c r="I165" s="11"/>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9">
       <c r="A166" s="1">
         <v>156</v>
       </c>
@@ -5327,7 +5327,7 @@
       <c r="H166" s="11"/>
       <c r="I166" s="11"/>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9">
       <c r="A167" s="1">
         <v>157</v>
       </c>
@@ -5353,7 +5353,7 @@
       <c r="H167" s="11"/>
       <c r="I167" s="11"/>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9">
       <c r="A168" s="1">
         <v>158</v>
       </c>
@@ -5379,7 +5379,7 @@
       <c r="H168" s="11"/>
       <c r="I168" s="11"/>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9">
       <c r="A169" s="1">
         <v>159</v>
       </c>
@@ -5405,7 +5405,7 @@
       <c r="H169" s="11"/>
       <c r="I169" s="11"/>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9">
       <c r="A170" s="1">
         <v>160</v>
       </c>
@@ -5431,7 +5431,7 @@
       <c r="H170" s="11"/>
       <c r="I170" s="11"/>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9">
       <c r="A171" s="1">
         <v>161</v>
       </c>
@@ -5457,7 +5457,7 @@
       <c r="H171" s="11"/>
       <c r="I171" s="11"/>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9">
       <c r="A172" s="1">
         <v>162</v>
       </c>
@@ -5483,7 +5483,7 @@
       <c r="H172" s="11"/>
       <c r="I172" s="11"/>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9">
       <c r="A173" s="1">
         <v>163</v>
       </c>
@@ -5509,7 +5509,7 @@
       <c r="H173" s="11"/>
       <c r="I173" s="11"/>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9">
       <c r="A174" s="1">
         <v>164</v>
       </c>
@@ -5535,7 +5535,7 @@
       <c r="H174" s="11"/>
       <c r="I174" s="11"/>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9">
       <c r="A175" s="1">
         <v>165</v>
       </c>
@@ -5561,7 +5561,7 @@
       <c r="H175" s="11"/>
       <c r="I175" s="11"/>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9">
       <c r="A176" s="1">
         <v>166</v>
       </c>
@@ -5587,7 +5587,7 @@
       <c r="H176" s="11"/>
       <c r="I176" s="11"/>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9">
       <c r="A177" s="1">
         <v>167</v>
       </c>
@@ -5613,7 +5613,7 @@
       <c r="H177" s="11"/>
       <c r="I177" s="11"/>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9">
       <c r="A178" s="1">
         <v>168</v>
       </c>
@@ -5639,7 +5639,7 @@
       <c r="H178" s="11"/>
       <c r="I178" s="11"/>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9">
       <c r="A179" s="1">
         <v>169</v>
       </c>
@@ -5665,7 +5665,7 @@
       <c r="H179" s="11"/>
       <c r="I179" s="11"/>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9">
       <c r="A180" s="1">
         <v>170</v>
       </c>
@@ -5691,7 +5691,7 @@
       <c r="H180" s="11"/>
       <c r="I180" s="11"/>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9">
       <c r="A181" s="1">
         <v>171</v>
       </c>
@@ -5717,7 +5717,7 @@
       <c r="H181" s="11"/>
       <c r="I181" s="11"/>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9">
       <c r="A182" s="1">
         <v>172</v>
       </c>
@@ -5743,7 +5743,7 @@
       <c r="H182" s="11"/>
       <c r="I182" s="11"/>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9">
       <c r="A183" s="1">
         <v>173</v>
       </c>
@@ -5769,7 +5769,7 @@
       <c r="H183" s="11"/>
       <c r="I183" s="11"/>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9">
       <c r="A184" s="1">
         <v>174</v>
       </c>
@@ -5795,7 +5795,7 @@
       <c r="H184" s="11"/>
       <c r="I184" s="11"/>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9">
       <c r="A185" s="1">
         <v>175</v>
       </c>
@@ -5821,7 +5821,7 @@
       <c r="H185" s="11"/>
       <c r="I185" s="11"/>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9">
       <c r="A186" s="1">
         <v>176</v>
       </c>
@@ -5847,7 +5847,7 @@
       <c r="H186" s="11"/>
       <c r="I186" s="11"/>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9">
       <c r="A187" s="1">
         <v>177</v>
       </c>
@@ -5873,7 +5873,7 @@
       <c r="H187" s="11"/>
       <c r="I187" s="11"/>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9">
       <c r="A188" s="1">
         <v>178</v>
       </c>
@@ -5899,7 +5899,7 @@
       <c r="H188" s="11"/>
       <c r="I188" s="11"/>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9">
       <c r="A189" s="1">
         <v>179</v>
       </c>
@@ -5925,7 +5925,7 @@
       <c r="H189" s="11"/>
       <c r="I189" s="11"/>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9">
       <c r="A190" s="1">
         <v>180</v>
       </c>
@@ -5951,7 +5951,7 @@
       <c r="H190" s="11"/>
       <c r="I190" s="11"/>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9">
       <c r="A191" s="1">
         <v>181</v>
       </c>
@@ -5977,7 +5977,7 @@
       <c r="H191" s="11"/>
       <c r="I191" s="11"/>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9">
       <c r="A192" s="1">
         <v>182</v>
       </c>
@@ -6003,7 +6003,7 @@
       <c r="H192" s="11"/>
       <c r="I192" s="11"/>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9">
       <c r="A193" s="1">
         <v>183</v>
       </c>
@@ -6029,7 +6029,7 @@
       <c r="H193" s="11"/>
       <c r="I193" s="11"/>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9">
       <c r="A194" s="1">
         <v>184</v>
       </c>
@@ -6055,7 +6055,7 @@
       <c r="H194" s="11"/>
       <c r="I194" s="11"/>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9">
       <c r="A195" s="1">
         <v>185</v>
       </c>
@@ -6081,7 +6081,7 @@
       <c r="H195" s="11"/>
       <c r="I195" s="11"/>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9">
       <c r="A196" s="1">
         <v>186</v>
       </c>
@@ -6107,7 +6107,7 @@
       <c r="H196" s="11"/>
       <c r="I196" s="11"/>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9">
       <c r="A197" s="1">
         <v>187</v>
       </c>
@@ -6133,7 +6133,7 @@
       <c r="H197" s="11"/>
       <c r="I197" s="11"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9">
       <c r="A198" s="1">
         <v>188</v>
       </c>
@@ -6159,7 +6159,7 @@
       <c r="H198" s="11"/>
       <c r="I198" s="11"/>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9">
       <c r="A199" s="1">
         <v>189</v>
       </c>
@@ -6185,7 +6185,7 @@
       <c r="H199" s="11"/>
       <c r="I199" s="11"/>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9">
       <c r="A200" s="1">
         <v>190</v>
       </c>
@@ -6211,7 +6211,7 @@
       <c r="H200" s="11"/>
       <c r="I200" s="11"/>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9">
       <c r="A201" s="1">
         <v>191</v>
       </c>
@@ -6237,7 +6237,7 @@
       <c r="H201" s="11"/>
       <c r="I201" s="11"/>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9">
       <c r="A202" s="1">
         <v>192</v>
       </c>
@@ -6263,7 +6263,7 @@
       <c r="H202" s="11"/>
       <c r="I202" s="11"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9">
       <c r="A203" s="1">
         <v>193</v>
       </c>
@@ -6289,7 +6289,7 @@
       <c r="H203" s="11"/>
       <c r="I203" s="11"/>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9">
       <c r="A204" s="1">
         <v>194</v>
       </c>
@@ -6315,7 +6315,7 @@
       <c r="H204" s="11"/>
       <c r="I204" s="11"/>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9">
       <c r="A205" s="1">
         <v>195</v>
       </c>
@@ -6341,7 +6341,7 @@
       <c r="H205" s="11"/>
       <c r="I205" s="11"/>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9">
       <c r="A206" s="1">
         <v>196</v>
       </c>
@@ -6367,7 +6367,7 @@
       <c r="H206" s="11"/>
       <c r="I206" s="11"/>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9">
       <c r="A207" s="1">
         <v>197</v>
       </c>
@@ -6393,7 +6393,7 @@
       <c r="H207" s="11"/>
       <c r="I207" s="11"/>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9">
       <c r="A208" s="1">
         <v>198</v>
       </c>
@@ -6419,7 +6419,7 @@
       <c r="H208" s="11"/>
       <c r="I208" s="11"/>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9">
       <c r="A209" s="1">
         <v>199</v>
       </c>
@@ -6445,7 +6445,7 @@
       <c r="H209" s="11"/>
       <c r="I209" s="11"/>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9">
       <c r="A210" s="1">
         <v>200</v>
       </c>
@@ -6471,7 +6471,7 @@
       <c r="H210" s="11"/>
       <c r="I210" s="11"/>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9">
       <c r="A211" s="1">
         <v>201</v>
       </c>
@@ -6497,7 +6497,7 @@
       <c r="H211" s="11"/>
       <c r="I211" s="11"/>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9">
       <c r="A212" s="1">
         <v>202</v>
       </c>
@@ -6523,7 +6523,7 @@
       <c r="H212" s="11"/>
       <c r="I212" s="11"/>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9">
       <c r="A213" s="1">
         <v>203</v>
       </c>
@@ -6549,7 +6549,7 @@
       <c r="H213" s="11"/>
       <c r="I213" s="11"/>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9">
       <c r="A214" s="1">
         <v>204</v>
       </c>
@@ -6575,7 +6575,7 @@
       <c r="H214" s="11"/>
       <c r="I214" s="11"/>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9">
       <c r="A215" s="1">
         <v>205</v>
       </c>
@@ -6601,7 +6601,7 @@
       <c r="H215" s="11"/>
       <c r="I215" s="11"/>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9">
       <c r="A216" s="1">
         <v>206</v>
       </c>
@@ -6627,7 +6627,7 @@
       <c r="H216" s="11"/>
       <c r="I216" s="11"/>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9">
       <c r="A217" s="1">
         <v>207</v>
       </c>
@@ -6653,7 +6653,7 @@
       <c r="H217" s="11"/>
       <c r="I217" s="11"/>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9">
       <c r="A218" s="1">
         <v>208</v>
       </c>
@@ -6679,7 +6679,7 @@
       <c r="H218" s="11"/>
       <c r="I218" s="11"/>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9">
       <c r="A219" s="1">
         <v>209</v>
       </c>
@@ -6705,7 +6705,7 @@
       <c r="H219" s="11"/>
       <c r="I219" s="11"/>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9">
       <c r="A220" s="1">
         <v>210</v>
       </c>
@@ -6731,7 +6731,7 @@
       <c r="H220" s="11"/>
       <c r="I220" s="11"/>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9">
       <c r="A221" s="1">
         <v>211</v>
       </c>
@@ -6757,7 +6757,7 @@
       <c r="H221" s="11"/>
       <c r="I221" s="11"/>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9">
       <c r="A222" s="1">
         <v>212</v>
       </c>
@@ -6783,7 +6783,7 @@
       <c r="H222" s="11"/>
       <c r="I222" s="11"/>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9">
       <c r="A223" s="1">
         <v>213</v>
       </c>
@@ -6809,7 +6809,7 @@
       <c r="H223" s="11"/>
       <c r="I223" s="11"/>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9">
       <c r="A224" s="1">
         <v>214</v>
       </c>
@@ -6835,7 +6835,7 @@
       <c r="H224" s="11"/>
       <c r="I224" s="11"/>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9">
       <c r="A225" s="1">
         <v>215</v>
       </c>
@@ -6861,7 +6861,7 @@
       <c r="H225" s="11"/>
       <c r="I225" s="11"/>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9">
       <c r="A226" s="1">
         <v>216</v>
       </c>
@@ -6887,7 +6887,7 @@
       <c r="H226" s="11"/>
       <c r="I226" s="11"/>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9">
       <c r="A227" s="1">
         <v>217</v>
       </c>
@@ -6913,7 +6913,7 @@
       <c r="H227" s="11"/>
       <c r="I227" s="11"/>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9">
       <c r="A228" s="1">
         <v>218</v>
       </c>
@@ -6939,7 +6939,7 @@
       <c r="H228" s="11"/>
       <c r="I228" s="11"/>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9">
       <c r="A229" s="1">
         <v>219</v>
       </c>
@@ -6965,7 +6965,7 @@
       <c r="H229" s="11"/>
       <c r="I229" s="11"/>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9">
       <c r="A230" s="1">
         <v>220</v>
       </c>
@@ -6991,7 +6991,7 @@
       <c r="H230" s="11"/>
       <c r="I230" s="11"/>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9">
       <c r="A231" s="1">
         <v>221</v>
       </c>
@@ -7017,7 +7017,7 @@
       <c r="H231" s="11"/>
       <c r="I231" s="11"/>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9">
       <c r="A232" s="1">
         <v>222</v>
       </c>
@@ -7043,7 +7043,7 @@
       <c r="H232" s="11"/>
       <c r="I232" s="11"/>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9">
       <c r="A233" s="1">
         <v>223</v>
       </c>
@@ -7069,7 +7069,7 @@
       <c r="H233" s="11"/>
       <c r="I233" s="11"/>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9">
       <c r="A234" s="1">
         <v>224</v>
       </c>
@@ -7095,7 +7095,7 @@
       <c r="H234" s="11"/>
       <c r="I234" s="11"/>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9">
       <c r="A235" s="1">
         <v>225</v>
       </c>
@@ -7121,7 +7121,7 @@
       <c r="H235" s="11"/>
       <c r="I235" s="11"/>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9">
       <c r="A236" s="1">
         <v>226</v>
       </c>
@@ -7147,7 +7147,7 @@
       <c r="H236" s="11"/>
       <c r="I236" s="11"/>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9">
       <c r="A237" s="1">
         <v>227</v>
       </c>
@@ -7173,7 +7173,7 @@
       <c r="H237" s="11"/>
       <c r="I237" s="11"/>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9">
       <c r="A238" s="1">
         <v>228</v>
       </c>
@@ -7199,7 +7199,7 @@
       <c r="H238" s="11"/>
       <c r="I238" s="11"/>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9">
       <c r="A239" s="1">
         <v>229</v>
       </c>
@@ -7225,7 +7225,7 @@
       <c r="H239" s="11"/>
       <c r="I239" s="11"/>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9">
       <c r="A240" s="1">
         <v>230</v>
       </c>
@@ -7251,7 +7251,7 @@
       <c r="H240" s="11"/>
       <c r="I240" s="11"/>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9">
       <c r="A241" s="1">
         <v>231</v>
       </c>
@@ -7277,7 +7277,7 @@
       <c r="H241" s="11"/>
       <c r="I241" s="11"/>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9">
       <c r="A242" s="1">
         <v>232</v>
       </c>
@@ -7303,7 +7303,7 @@
       <c r="H242" s="11"/>
       <c r="I242" s="11"/>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9">
       <c r="A243" s="1">
         <v>233</v>
       </c>
@@ -7329,7 +7329,7 @@
       <c r="H243" s="11"/>
       <c r="I243" s="11"/>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9">
       <c r="A244" s="1">
         <v>234</v>
       </c>
@@ -7355,7 +7355,7 @@
       <c r="H244" s="11"/>
       <c r="I244" s="11"/>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9">
       <c r="A245" s="1">
         <v>235</v>
       </c>
@@ -7381,7 +7381,7 @@
       <c r="H245" s="11"/>
       <c r="I245" s="11"/>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9">
       <c r="A246" s="1">
         <v>236</v>
       </c>
@@ -7407,7 +7407,7 @@
       <c r="H246" s="11"/>
       <c r="I246" s="11"/>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9">
       <c r="A247" s="1">
         <v>237</v>
       </c>
@@ -7433,7 +7433,7 @@
       <c r="H247" s="11"/>
       <c r="I247" s="11"/>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9">
       <c r="A248" s="1">
         <v>238</v>
       </c>
@@ -7459,7 +7459,7 @@
       <c r="H248" s="11"/>
       <c r="I248" s="11"/>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9">
       <c r="A249" s="1">
         <v>239</v>
       </c>
@@ -7485,7 +7485,7 @@
       <c r="H249" s="11"/>
       <c r="I249" s="11"/>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9">
       <c r="A250" s="1">
         <v>240</v>
       </c>
@@ -7511,7 +7511,7 @@
       <c r="H250" s="11"/>
       <c r="I250" s="11"/>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9">
       <c r="A251" s="1">
         <v>241</v>
       </c>
@@ -7537,7 +7537,7 @@
       <c r="H251" s="11"/>
       <c r="I251" s="11"/>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9">
       <c r="A252" s="1">
         <v>242</v>
       </c>
@@ -7563,7 +7563,7 @@
       <c r="H252" s="11"/>
       <c r="I252" s="11"/>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9">
       <c r="A253" s="1">
         <v>243</v>
       </c>
@@ -7589,7 +7589,7 @@
       <c r="H253" s="11"/>
       <c r="I253" s="11"/>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9">
       <c r="A254" s="1">
         <v>244</v>
       </c>
@@ -7615,7 +7615,7 @@
       <c r="H254" s="11"/>
       <c r="I254" s="11"/>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9">
       <c r="A255" s="1">
         <v>245</v>
       </c>
@@ -7641,7 +7641,7 @@
       <c r="H255" s="11"/>
       <c r="I255" s="11"/>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9">
       <c r="A256" s="1">
         <v>246</v>
       </c>
@@ -7667,7 +7667,7 @@
       <c r="H256" s="11"/>
       <c r="I256" s="11"/>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9">
       <c r="A257" s="1">
         <v>247</v>
       </c>
@@ -7693,7 +7693,7 @@
       <c r="H257" s="11"/>
       <c r="I257" s="11"/>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9">
       <c r="A258" s="1">
         <v>248</v>
       </c>
@@ -7719,7 +7719,7 @@
       <c r="H258" s="11"/>
       <c r="I258" s="11"/>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9">
       <c r="A259" s="1">
         <v>249</v>
       </c>
@@ -7745,7 +7745,7 @@
       <c r="H259" s="11"/>
       <c r="I259" s="11"/>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9">
       <c r="A260" s="1">
         <v>250</v>
       </c>
@@ -7771,7 +7771,7 @@
       <c r="H260" s="11"/>
       <c r="I260" s="11"/>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9">
       <c r="A261" s="1">
         <v>251</v>
       </c>
@@ -7797,7 +7797,7 @@
       <c r="H261" s="11"/>
       <c r="I261" s="11"/>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9">
       <c r="A262" s="1">
         <v>252</v>
       </c>
@@ -7823,7 +7823,7 @@
       <c r="H262" s="11"/>
       <c r="I262" s="11"/>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9">
       <c r="A263" s="1">
         <v>253</v>
       </c>
@@ -7849,7 +7849,7 @@
       <c r="H263" s="11"/>
       <c r="I263" s="11"/>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9">
       <c r="A264" s="1">
         <v>254</v>
       </c>
@@ -7875,7 +7875,7 @@
       <c r="H264" s="11"/>
       <c r="I264" s="11"/>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9">
       <c r="A265" s="1">
         <v>255</v>
       </c>
@@ -7901,7 +7901,7 @@
       <c r="H265" s="11"/>
       <c r="I265" s="11"/>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9">
       <c r="A266" s="1">
         <v>256</v>
       </c>
@@ -7927,7 +7927,7 @@
       <c r="H266" s="11"/>
       <c r="I266" s="11"/>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9">
       <c r="A267" s="1">
         <v>257</v>
       </c>
@@ -7953,7 +7953,7 @@
       <c r="H267" s="11"/>
       <c r="I267" s="11"/>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9">
       <c r="A268" s="1">
         <v>258</v>
       </c>
@@ -7979,7 +7979,7 @@
       <c r="H268" s="11"/>
       <c r="I268" s="11"/>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9">
       <c r="A269" s="1">
         <v>259</v>
       </c>
@@ -8005,7 +8005,7 @@
       <c r="H269" s="11"/>
       <c r="I269" s="11"/>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9">
       <c r="A270" s="1">
         <v>260</v>
       </c>
@@ -8031,7 +8031,7 @@
       <c r="H270" s="11"/>
       <c r="I270" s="11"/>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9">
       <c r="A271" s="1">
         <v>261</v>
       </c>
@@ -8057,7 +8057,7 @@
       <c r="H271" s="11"/>
       <c r="I271" s="11"/>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9">
       <c r="A272" s="1">
         <v>262</v>
       </c>
@@ -8083,7 +8083,7 @@
       <c r="H272" s="11"/>
       <c r="I272" s="11"/>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:10">
       <c r="A273" s="1">
         <v>263</v>
       </c>
@@ -8109,7 +8109,7 @@
       <c r="H273" s="11"/>
       <c r="I273" s="11"/>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:10">
       <c r="A274" s="1">
         <v>264</v>
       </c>
@@ -8135,7 +8135,7 @@
       <c r="H274" s="11"/>
       <c r="I274" s="11"/>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:10">
       <c r="A275" s="1">
         <v>265</v>
       </c>
@@ -8161,7 +8161,7 @@
       <c r="H275" s="11"/>
       <c r="I275" s="11"/>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:10">
       <c r="A276" s="1">
         <v>266</v>
       </c>
@@ -8187,7 +8187,7 @@
       <c r="H276" s="11"/>
       <c r="I276" s="11"/>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:10">
       <c r="A277" s="1">
         <v>267</v>
       </c>
@@ -8213,7 +8213,7 @@
       <c r="H277" s="11"/>
       <c r="I277" s="11"/>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:10">
       <c r="A278" s="1">
         <v>268</v>
       </c>
@@ -8239,7 +8239,7 @@
       <c r="H278" s="11"/>
       <c r="I278" s="11"/>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:10">
       <c r="A279" s="1">
         <v>269</v>
       </c>
@@ -8265,7 +8265,7 @@
       <c r="H279" s="11"/>
       <c r="I279" s="11"/>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:10">
       <c r="A280" s="1">
         <v>270</v>
       </c>
@@ -8291,7 +8291,7 @@
       <c r="H280" s="11"/>
       <c r="I280" s="11"/>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:10">
       <c r="A281" s="1">
         <v>271</v>
       </c>
@@ -8317,7 +8317,7 @@
       <c r="H281" s="11"/>
       <c r="I281" s="11"/>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:10">
       <c r="A282" s="1">
         <v>272</v>
       </c>
@@ -8343,7 +8343,7 @@
       <c r="H282" s="11"/>
       <c r="I282" s="11"/>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:10">
       <c r="A283" s="1">
         <v>273</v>
       </c>
@@ -8369,7 +8369,7 @@
       <c r="H283" s="11"/>
       <c r="I283" s="11"/>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:10">
       <c r="A284" s="1">
         <v>274</v>
       </c>
@@ -8395,7 +8395,7 @@
       <c r="H284" s="11"/>
       <c r="I284" s="11"/>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:10">
       <c r="A285" s="1">
         <v>275</v>
       </c>
@@ -8421,7 +8421,7 @@
       <c r="H285" s="11"/>
       <c r="I285" s="11"/>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:10">
       <c r="A286" s="1">
         <v>276</v>
       </c>
@@ -8454,7 +8454,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:10">
       <c r="A287" s="1">
         <v>277</v>
       </c>
@@ -8487,7 +8487,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:10">
       <c r="A288" s="1">
         <v>278</v>
       </c>
@@ -8520,7 +8520,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:10">
       <c r="A289" s="1">
         <v>279</v>
       </c>
@@ -8553,7 +8553,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:10">
       <c r="A290" s="1">
         <v>280</v>
       </c>
@@ -8586,7 +8586,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:10">
       <c r="A291" s="1">
         <v>281</v>
       </c>
@@ -8619,7 +8619,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:10">
       <c r="A292" s="1">
         <v>282</v>
       </c>
@@ -8652,7 +8652,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:10">
       <c r="A293" s="1">
         <v>283</v>
       </c>
@@ -8685,7 +8685,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:10">
       <c r="A294" s="1">
         <v>284</v>
       </c>
@@ -8718,7 +8718,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:10">
       <c r="A295" s="1">
         <v>285</v>
       </c>
@@ -8751,7 +8751,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:10">
       <c r="A296" s="1">
         <v>286</v>
       </c>
@@ -8784,7 +8784,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:10">
       <c r="A297" s="1">
         <v>287</v>
       </c>
@@ -8817,7 +8817,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:10">
       <c r="A298" s="1">
         <v>288</v>
       </c>
@@ -8850,7 +8850,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:10">
       <c r="A299" s="1">
         <v>289</v>
       </c>
@@ -8883,7 +8883,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:10">
       <c r="A300" s="1">
         <v>290</v>
       </c>
@@ -8916,7 +8916,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:10">
       <c r="A301" s="1">
         <v>291</v>
       </c>
@@ -8949,7 +8949,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:10">
       <c r="A302" s="1">
         <v>292</v>
       </c>
@@ -8982,7 +8982,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="303" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:10" s="1" customFormat="1">
       <c r="A303" s="1">
         <v>293</v>
       </c>
@@ -9015,7 +9015,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="304" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:10" s="1" customFormat="1">
       <c r="A304" s="1">
         <v>294</v>
       </c>
@@ -9048,7 +9048,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:10">
       <c r="A305" s="1">
         <v>295</v>
       </c>
@@ -9081,7 +9081,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:10">
       <c r="A306" s="1">
         <v>296</v>
       </c>
@@ -9114,7 +9114,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:10">
       <c r="A307" s="1">
         <v>297</v>
       </c>
@@ -9147,7 +9147,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:10">
       <c r="A308" s="1">
         <v>298</v>
       </c>
@@ -9180,7 +9180,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:10">
       <c r="A309" s="1">
         <v>298</v>
       </c>
@@ -9213,7 +9213,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:10">
       <c r="A310" s="1">
         <v>299</v>
       </c>
@@ -9246,7 +9246,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:10">
       <c r="A311" s="1">
         <v>300</v>
       </c>
@@ -9279,7 +9279,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:10">
       <c r="A312" s="1">
         <v>301</v>
       </c>
@@ -9312,7 +9312,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:10">
       <c r="A313" s="1">
         <v>302</v>
       </c>
@@ -9345,7 +9345,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:10">
       <c r="A314" s="1">
         <v>303</v>
       </c>
@@ -9378,7 +9378,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:10">
       <c r="A315" s="1">
         <v>304</v>
       </c>
@@ -9411,7 +9411,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:10">
       <c r="A316" s="1">
         <v>305</v>
       </c>
@@ -9444,7 +9444,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:10">
       <c r="A317" s="1">
         <v>306</v>
       </c>
@@ -9477,7 +9477,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:10">
       <c r="A318" s="1">
         <v>307</v>
       </c>
@@ -9510,7 +9510,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:10">
       <c r="A319" s="1">
         <v>308</v>
       </c>
@@ -9543,7 +9543,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:10">
       <c r="A320" s="1">
         <v>309</v>
       </c>
@@ -9576,7 +9576,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:10">
       <c r="A321" s="1">
         <v>310</v>
       </c>
@@ -9609,7 +9609,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:10">
       <c r="A322" s="1">
         <v>311</v>
       </c>
@@ -9642,7 +9642,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:10">
       <c r="A323" s="1">
         <v>312</v>
       </c>
@@ -9675,7 +9675,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:10">
       <c r="A324" s="1">
         <v>313</v>
       </c>
@@ -9708,7 +9708,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:10">
       <c r="A325" s="1">
         <v>314</v>
       </c>
@@ -9741,7 +9741,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:10">
       <c r="A326" s="1">
         <v>315</v>
       </c>
@@ -9774,7 +9774,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:10">
       <c r="A327" s="1">
         <v>316</v>
       </c>
@@ -9807,12 +9807,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:10">
       <c r="A328" s="1">
         <v>318</v>
       </c>
       <c r="B328" s="13" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C328" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
@@ -9831,16 +9831,16 @@
         <v>46192.5</v>
       </c>
       <c r="H328" s="11" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="I328" s="11" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="J328" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:10">
       <c r="A329" s="1">
         <v>319</v>
       </c>
@@ -9864,16 +9864,16 @@
         <v>46198.677083333336</v>
       </c>
       <c r="H329" s="11" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="I329" s="11" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="J329" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:10">
       <c r="A330" s="1">
         <v>320</v>
       </c>
@@ -9906,7 +9906,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:10">
       <c r="A331" s="1">
         <v>321</v>
       </c>
@@ -9930,16 +9930,16 @@
         <v>46204.519444444442</v>
       </c>
       <c r="H331" s="11" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="I331" s="11" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="J331" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:10">
       <c r="A332" s="1">
         <v>322</v>
       </c>
@@ -9963,23 +9963,23 @@
         <v>46205.420138888891</v>
       </c>
       <c r="H332" s="11" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="I332" s="11" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="J332" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:10">
       <c r="A333" s="1">
         <v>323</v>
       </c>
       <c r="B333" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="C333" s="16" t="str">
+        <v>86</v>
+      </c>
+      <c r="C333" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
@@ -9996,23 +9996,23 @@
         <v>46207.865972222222</v>
       </c>
       <c r="H333" s="11" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="I333" s="11" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="J333" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:10">
       <c r="A334" s="1">
         <v>324</v>
       </c>
       <c r="B334" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C334" s="16" t="str">
+      <c r="C334" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
@@ -10029,23 +10029,23 @@
         <v>46208.73333333333</v>
       </c>
       <c r="H334" s="11" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="I334" s="11" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="J334" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:10">
       <c r="A335" s="1">
         <v>325</v>
       </c>
       <c r="B335" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="C335" s="16" t="str">
+        <v>86</v>
+      </c>
+      <c r="C335" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
@@ -10062,23 +10062,23 @@
         <v>46208.607638888891</v>
       </c>
       <c r="H335" s="11" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="I335" s="11" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="J335" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:10">
       <c r="A336" s="1">
         <v>326</v>
       </c>
       <c r="B336" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C336" s="16" t="str">
+      <c r="C336" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
@@ -10095,23 +10095,23 @@
         <v>46209.997916666667</v>
       </c>
       <c r="H336" s="11" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="I336" s="11" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="J336" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:10">
       <c r="A337" s="1">
         <v>327</v>
       </c>
       <c r="B337" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C337" s="16" t="str">
+      <c r="C337" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
@@ -10137,14 +10137,14 @@
         <v>23</v>
       </c>
     </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:10">
       <c r="A338" s="1">
         <v>328</v>
       </c>
       <c r="B338" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C338" s="16" t="str">
+      <c r="C338" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
@@ -10161,23 +10161,23 @@
         <v>46209.4375</v>
       </c>
       <c r="H338" s="11" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="I338" s="11" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="J338" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:10">
       <c r="A339" s="1">
         <v>329</v>
       </c>
       <c r="B339" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C339" s="16" t="str">
+      <c r="C339" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
@@ -10194,23 +10194,23 @@
         <v>46212.39166666667</v>
       </c>
       <c r="H339" s="11" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="I339" s="11" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="J339" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:10">
       <c r="A340" s="1">
         <v>330</v>
       </c>
       <c r="B340" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C340" s="16" t="str">
+      <c r="C340" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
@@ -10227,23 +10227,23 @@
         <v>46211.429166666669</v>
       </c>
       <c r="H340" s="11" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="I340" s="11" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="J340" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:10">
       <c r="A341" s="1">
         <v>331</v>
       </c>
       <c r="B341" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C341" s="16" t="str">
+      <c r="C341" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
@@ -10269,14 +10269,14 @@
         <v>23</v>
       </c>
     </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:10">
       <c r="A342" s="1">
         <v>332</v>
       </c>
       <c r="B342" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C342" s="16" t="str">
+      <c r="C342" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
@@ -10302,14 +10302,14 @@
         <v>23</v>
       </c>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:10">
       <c r="A343" s="1">
         <v>333</v>
       </c>
       <c r="B343" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C343" s="16" t="str">
+      <c r="C343" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
@@ -10335,14 +10335,14 @@
         <v>23</v>
       </c>
     </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:10">
       <c r="A344" s="1">
         <v>334</v>
       </c>
       <c r="B344" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C344" s="16" t="str">
+      <c r="C344" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
@@ -10368,14 +10368,14 @@
         <v>23</v>
       </c>
     </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:10">
       <c r="A345" s="1">
         <v>335</v>
       </c>
       <c r="B345" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C345" s="16" t="str">
+      <c r="C345" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
@@ -10388,12 +10388,17 @@
       <c r="F345" s="15">
         <v>46232.459722222222</v>
       </c>
-      <c r="G345" s="15"/>
+      <c r="G345" s="15" t="s">
+        <v>104</v>
+      </c>
       <c r="H345" s="11" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="I345" s="11" t="s">
-        <v>114</v>
+        <v>106</v>
+      </c>
+      <c r="J345" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -10415,13 +10420,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{797F1036-D41E-43A4-9E6E-CBBB62F3CD31}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="13.28515625" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -10429,18 +10434,18 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="D1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C2">
         <v>245.84</v>
@@ -10449,12 +10454,12 @@
         <v>234.67</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C3">
         <v>176.6</v>
@@ -10463,12 +10468,12 @@
         <v>161.15</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C4">
         <v>174.26</v>
@@ -10477,12 +10482,12 @@
         <v>157.61000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C5">
         <v>376.96</v>
@@ -10491,12 +10496,12 @@
         <v>347.95</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="C6">
         <v>399.41</v>
@@ -10505,12 +10510,12 @@
         <v>393.57</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="C7">
         <v>20</v>
@@ -10519,12 +10524,12 @@
         <v>19.87</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="C8">
         <v>21</v>
@@ -10533,12 +10538,12 @@
         <v>19.57</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="C9">
         <v>21</v>
@@ -10547,12 +10552,12 @@
         <v>19.86</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C10">
         <v>131</v>
@@ -10561,12 +10566,12 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C11">
         <v>112</v>
@@ -10586,7 +10591,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56220E0F-EC16-4A8C-9E04-C7F8849C4B4D}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
@@ -10594,7 +10599,7 @@
     <col min="5" max="5" width="30.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -10602,16 +10607,16 @@
         <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="D1" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="E1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -10625,10 +10630,10 @@
         <v>214.99998842592322</v>
       </c>
       <c r="E2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -10642,10 +10647,10 @@
         <v>7.6381944444437977</v>
       </c>
       <c r="E3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -10659,10 +10664,10 @@
         <v>29.99998842592322</v>
       </c>
       <c r="E4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -10676,10 +10681,10 @@
         <v>17.99998842592322</v>
       </c>
       <c r="E5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -10693,10 +10698,10 @@
         <v>59.99998842592322</v>
       </c>
       <c r="E6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -10710,10 +10715,10 @@
         <v>3.9999884259232203</v>
       </c>
       <c r="E7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -10728,10 +10733,10 @@
         <v>8.8881944444437977</v>
       </c>
       <c r="E8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -10746,7 +10751,7 @@
         <v>6.1388888888905058</v>
       </c>
       <c r="E9" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -10760,25 +10765,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83DAFC4B-C207-418A-8501-0E1EC9E673B7}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="C1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -10789,7 +10794,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -10800,7 +10805,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -10811,9 +10816,9 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B5" s="7">
         <v>27760</v>
@@ -10822,7 +10827,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -10833,7 +10838,7 @@
         <v>46631</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -10844,7 +10849,7 @@
         <v>48579</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -10855,7 +10860,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -10866,7 +10871,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -10877,7 +10882,7 @@
         <v>48579</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -10897,29 +10902,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100FB7AAE8C8816FD47B559A0CCF555AFF0" ma:contentTypeVersion="10" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5c9910934a78ddf693a6b708b52e9b37">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f95d585e-e7a7-414c-955d-38a47c8579bd" xmlns:ns3="33ab045e-9213-4eea-a9f2-a5b809105d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a9c61c95b4e11caed4e46447c2ca01e7" ns2:_="" ns3:_="">
     <xsd:import namespace="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
@@ -11122,48 +11104,39 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
-    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1308" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98B5A0EC-FF7C-4F0A-BC7E-A8D969745523}"/>
+  <xr:revisionPtr revIDLastSave="1309" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C3FE980-3FC7-4A7A-AE2D-564F37E60E08}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="119">
   <si>
     <t>ID</t>
   </si>
@@ -366,9 +366,6 @@
   </si>
   <si>
     <t>Obstrucciín filtro admisión</t>
-  </si>
-  <si>
-    <t>7/29/2026  13:39:00 AM</t>
   </si>
   <si>
     <t>Falla sistema de combustible a gas</t>
@@ -10388,14 +10385,14 @@
       <c r="F345" s="15">
         <v>46232.459722222222</v>
       </c>
-      <c r="G345" s="15" t="s">
+      <c r="G345" s="15">
+        <v>46232.568749999999</v>
+      </c>
+      <c r="H345" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="H345" s="11" t="s">
+      <c r="I345" s="11" t="s">
         <v>105</v>
-      </c>
-      <c r="I345" s="11" t="s">
-        <v>106</v>
       </c>
       <c r="J345" s="1" t="s">
         <v>23</v>
@@ -10434,10 +10431,10 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" t="s">
         <v>107</v>
-      </c>
-      <c r="D1" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -10445,7 +10442,7 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C2">
         <v>245.84</v>
@@ -10459,7 +10456,7 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C3">
         <v>176.6</v>
@@ -10473,7 +10470,7 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C4">
         <v>174.26</v>
@@ -10487,7 +10484,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C5">
         <v>376.96</v>
@@ -10501,7 +10498,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C6">
         <v>399.41</v>
@@ -10515,7 +10512,7 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C7">
         <v>20</v>
@@ -10529,7 +10526,7 @@
         <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C8">
         <v>21</v>
@@ -10543,7 +10540,7 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9">
         <v>21</v>
@@ -10557,7 +10554,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C10">
         <v>131</v>
@@ -10571,7 +10568,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C11">
         <v>112</v>
@@ -10607,10 +10604,10 @@
         <v>5</v>
       </c>
       <c r="C1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D1" t="s">
         <v>111</v>
-      </c>
-      <c r="D1" t="s">
-        <v>112</v>
       </c>
       <c r="E1" t="s">
         <v>7</v>
@@ -10630,7 +10627,7 @@
         <v>214.99998842592322</v>
       </c>
       <c r="E2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -10647,7 +10644,7 @@
         <v>7.6381944444437977</v>
       </c>
       <c r="E3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -10664,7 +10661,7 @@
         <v>29.99998842592322</v>
       </c>
       <c r="E4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -10681,7 +10678,7 @@
         <v>17.99998842592322</v>
       </c>
       <c r="E5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -10698,7 +10695,7 @@
         <v>59.99998842592322</v>
       </c>
       <c r="E6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -10715,7 +10712,7 @@
         <v>3.9999884259232203</v>
       </c>
       <c r="E7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -10733,7 +10730,7 @@
         <v>8.8881944444437977</v>
       </c>
       <c r="E8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -10751,7 +10748,7 @@
         <v>6.1388888888905058</v>
       </c>
       <c r="E9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -10777,10 +10774,10 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" t="s">
         <v>118</v>
-      </c>
-      <c r="C1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:3">

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1309" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C3FE980-3FC7-4A7A-AE2D-564F37E60E08}"/>
+  <xr:revisionPtr revIDLastSave="1310" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{013298E2-44DF-4DB1-98C7-51585CA511D2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -417,7 +417,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -505,10 +505,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -517,11 +517,11 @@
       <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1215,28 +1215,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
   <dimension ref="A9:J345"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="41.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="151.28515625" customWidth="1"/>
-    <col min="10" max="10" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" customWidth="1"/>
-    <col min="12" max="12" width="33.28515625" customWidth="1"/>
+    <col min="6" max="7" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="151.33203125" customWidth="1"/>
+    <col min="10" max="10" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" customWidth="1"/>
+    <col min="12" max="12" width="33.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
         <v>335</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -1294,7 +1294,7 @@
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -1320,7 +1320,7 @@
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>3</v>
       </c>
@@ -1346,7 +1346,7 @@
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>4</v>
       </c>
@@ -1372,7 +1372,7 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>5</v>
       </c>
@@ -1398,7 +1398,7 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>6</v>
       </c>
@@ -1424,7 +1424,7 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>7</v>
       </c>
@@ -1450,7 +1450,7 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>8</v>
       </c>
@@ -1476,7 +1476,7 @@
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>9</v>
       </c>
@@ -1502,7 +1502,7 @@
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>10</v>
       </c>
@@ -1528,7 +1528,7 @@
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>11</v>
       </c>
@@ -1554,7 +1554,7 @@
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>12</v>
       </c>
@@ -1580,7 +1580,7 @@
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>13</v>
       </c>
@@ -1606,7 +1606,7 @@
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>14</v>
       </c>
@@ -1632,7 +1632,7 @@
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>15</v>
       </c>
@@ -1658,7 +1658,7 @@
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>16</v>
       </c>
@@ -1684,7 +1684,7 @@
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>17</v>
       </c>
@@ -1710,7 +1710,7 @@
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>18</v>
       </c>
@@ -1736,7 +1736,7 @@
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>19</v>
       </c>
@@ -1762,7 +1762,7 @@
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>20</v>
       </c>
@@ -1788,7 +1788,7 @@
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>21</v>
       </c>
@@ -1814,7 +1814,7 @@
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>22</v>
       </c>
@@ -1840,7 +1840,7 @@
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>23</v>
       </c>
@@ -1866,7 +1866,7 @@
       <c r="H33" s="11"/>
       <c r="I33" s="11"/>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>24</v>
       </c>
@@ -1892,7 +1892,7 @@
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>25</v>
       </c>
@@ -1918,7 +1918,7 @@
       <c r="H35" s="11"/>
       <c r="I35" s="11"/>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>26</v>
       </c>
@@ -1944,7 +1944,7 @@
       <c r="H36" s="11"/>
       <c r="I36" s="11"/>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>27</v>
       </c>
@@ -1970,7 +1970,7 @@
       <c r="H37" s="11"/>
       <c r="I37" s="11"/>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>28</v>
       </c>
@@ -1996,7 +1996,7 @@
       <c r="H38" s="11"/>
       <c r="I38" s="11"/>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>29</v>
       </c>
@@ -2022,7 +2022,7 @@
       <c r="H39" s="11"/>
       <c r="I39" s="11"/>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>30</v>
       </c>
@@ -2048,7 +2048,7 @@
       <c r="H40" s="11"/>
       <c r="I40" s="11"/>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>31</v>
       </c>
@@ -2074,7 +2074,7 @@
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>32</v>
       </c>
@@ -2100,7 +2100,7 @@
       <c r="H42" s="11"/>
       <c r="I42" s="11"/>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>33</v>
       </c>
@@ -2126,7 +2126,7 @@
       <c r="H43" s="11"/>
       <c r="I43" s="11"/>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>34</v>
       </c>
@@ -2152,7 +2152,7 @@
       <c r="H44" s="11"/>
       <c r="I44" s="11"/>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>35</v>
       </c>
@@ -2178,7 +2178,7 @@
       <c r="H45" s="11"/>
       <c r="I45" s="11"/>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>36</v>
       </c>
@@ -2204,7 +2204,7 @@
       <c r="H46" s="11"/>
       <c r="I46" s="11"/>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>37</v>
       </c>
@@ -2230,7 +2230,7 @@
       <c r="H47" s="11"/>
       <c r="I47" s="11"/>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>38</v>
       </c>
@@ -2256,7 +2256,7 @@
       <c r="H48" s="11"/>
       <c r="I48" s="11"/>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>39</v>
       </c>
@@ -2282,7 +2282,7 @@
       <c r="H49" s="11"/>
       <c r="I49" s="11"/>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>40</v>
       </c>
@@ -2308,7 +2308,7 @@
       <c r="H50" s="11"/>
       <c r="I50" s="11"/>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>41</v>
       </c>
@@ -2334,7 +2334,7 @@
       <c r="H51" s="11"/>
       <c r="I51" s="11"/>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>42</v>
       </c>
@@ -2360,7 +2360,7 @@
       <c r="H52" s="11"/>
       <c r="I52" s="11"/>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>43</v>
       </c>
@@ -2386,7 +2386,7 @@
       <c r="H53" s="11"/>
       <c r="I53" s="11"/>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>44</v>
       </c>
@@ -2412,7 +2412,7 @@
       <c r="H54" s="11"/>
       <c r="I54" s="11"/>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>45</v>
       </c>
@@ -2438,7 +2438,7 @@
       <c r="H55" s="11"/>
       <c r="I55" s="11"/>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>46</v>
       </c>
@@ -2464,7 +2464,7 @@
       <c r="H56" s="11"/>
       <c r="I56" s="11"/>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>47</v>
       </c>
@@ -2490,7 +2490,7 @@
       <c r="H57" s="11"/>
       <c r="I57" s="11"/>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>48</v>
       </c>
@@ -2516,7 +2516,7 @@
       <c r="H58" s="11"/>
       <c r="I58" s="11"/>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>49</v>
       </c>
@@ -2542,7 +2542,7 @@
       <c r="H59" s="11"/>
       <c r="I59" s="11"/>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>50</v>
       </c>
@@ -2568,7 +2568,7 @@
       <c r="H60" s="11"/>
       <c r="I60" s="11"/>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>51</v>
       </c>
@@ -2594,7 +2594,7 @@
       <c r="H61" s="11"/>
       <c r="I61" s="11"/>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>52</v>
       </c>
@@ -2620,7 +2620,7 @@
       <c r="H62" s="11"/>
       <c r="I62" s="11"/>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>53</v>
       </c>
@@ -2646,7 +2646,7 @@
       <c r="H63" s="11"/>
       <c r="I63" s="11"/>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>54</v>
       </c>
@@ -2672,7 +2672,7 @@
       <c r="H64" s="11"/>
       <c r="I64" s="11"/>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>55</v>
       </c>
@@ -2698,7 +2698,7 @@
       <c r="H65" s="11"/>
       <c r="I65" s="11"/>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>56</v>
       </c>
@@ -2724,7 +2724,7 @@
       <c r="H66" s="11"/>
       <c r="I66" s="11"/>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>57</v>
       </c>
@@ -2750,7 +2750,7 @@
       <c r="H67" s="11"/>
       <c r="I67" s="11"/>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>58</v>
       </c>
@@ -2776,7 +2776,7 @@
       <c r="H68" s="11"/>
       <c r="I68" s="11"/>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>59</v>
       </c>
@@ -2802,7 +2802,7 @@
       <c r="H69" s="11"/>
       <c r="I69" s="11"/>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>60</v>
       </c>
@@ -2828,7 +2828,7 @@
       <c r="H70" s="11"/>
       <c r="I70" s="11"/>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>61</v>
       </c>
@@ -2854,7 +2854,7 @@
       <c r="H71" s="11"/>
       <c r="I71" s="11"/>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>62</v>
       </c>
@@ -2880,7 +2880,7 @@
       <c r="H72" s="11"/>
       <c r="I72" s="11"/>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>63</v>
       </c>
@@ -2906,7 +2906,7 @@
       <c r="H73" s="11"/>
       <c r="I73" s="11"/>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>64</v>
       </c>
@@ -2932,7 +2932,7 @@
       <c r="H74" s="11"/>
       <c r="I74" s="11"/>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>65</v>
       </c>
@@ -2958,7 +2958,7 @@
       <c r="H75" s="11"/>
       <c r="I75" s="11"/>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>66</v>
       </c>
@@ -2984,7 +2984,7 @@
       <c r="H76" s="11"/>
       <c r="I76" s="11"/>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>67</v>
       </c>
@@ -3010,7 +3010,7 @@
       <c r="H77" s="11"/>
       <c r="I77" s="11"/>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>68</v>
       </c>
@@ -3036,7 +3036,7 @@
       <c r="H78" s="11"/>
       <c r="I78" s="11"/>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>69</v>
       </c>
@@ -3062,7 +3062,7 @@
       <c r="H79" s="11"/>
       <c r="I79" s="11"/>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>70</v>
       </c>
@@ -3088,7 +3088,7 @@
       <c r="H80" s="11"/>
       <c r="I80" s="11"/>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>71</v>
       </c>
@@ -3114,7 +3114,7 @@
       <c r="H81" s="11"/>
       <c r="I81" s="11"/>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>72</v>
       </c>
@@ -3140,7 +3140,7 @@
       <c r="H82" s="11"/>
       <c r="I82" s="11"/>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>73</v>
       </c>
@@ -3166,7 +3166,7 @@
       <c r="H83" s="11"/>
       <c r="I83" s="11"/>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>74</v>
       </c>
@@ -3192,7 +3192,7 @@
       <c r="H84" s="11"/>
       <c r="I84" s="11"/>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>75</v>
       </c>
@@ -3218,7 +3218,7 @@
       <c r="H85" s="11"/>
       <c r="I85" s="11"/>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>76</v>
       </c>
@@ -3244,7 +3244,7 @@
       <c r="H86" s="11"/>
       <c r="I86" s="11"/>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>77</v>
       </c>
@@ -3270,7 +3270,7 @@
       <c r="H87" s="11"/>
       <c r="I87" s="11"/>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>78</v>
       </c>
@@ -3296,7 +3296,7 @@
       <c r="H88" s="11"/>
       <c r="I88" s="11"/>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>79</v>
       </c>
@@ -3322,7 +3322,7 @@
       <c r="H89" s="11"/>
       <c r="I89" s="11"/>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>80</v>
       </c>
@@ -3348,7 +3348,7 @@
       <c r="H90" s="11"/>
       <c r="I90" s="11"/>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>81</v>
       </c>
@@ -3374,7 +3374,7 @@
       <c r="H91" s="11"/>
       <c r="I91" s="11"/>
     </row>
-    <row r="92" spans="1:9">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>82</v>
       </c>
@@ -3400,7 +3400,7 @@
       <c r="H92" s="11"/>
       <c r="I92" s="11"/>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>83</v>
       </c>
@@ -3426,7 +3426,7 @@
       <c r="H93" s="11"/>
       <c r="I93" s="11"/>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>84</v>
       </c>
@@ -3452,7 +3452,7 @@
       <c r="H94" s="11"/>
       <c r="I94" s="11"/>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>85</v>
       </c>
@@ -3478,7 +3478,7 @@
       <c r="H95" s="11"/>
       <c r="I95" s="11"/>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>86</v>
       </c>
@@ -3504,7 +3504,7 @@
       <c r="H96" s="11"/>
       <c r="I96" s="11"/>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>87</v>
       </c>
@@ -3530,7 +3530,7 @@
       <c r="H97" s="11"/>
       <c r="I97" s="11"/>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>88</v>
       </c>
@@ -3556,7 +3556,7 @@
       <c r="H98" s="11"/>
       <c r="I98" s="11"/>
     </row>
-    <row r="99" spans="1:9">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>89</v>
       </c>
@@ -3582,7 +3582,7 @@
       <c r="H99" s="11"/>
       <c r="I99" s="11"/>
     </row>
-    <row r="100" spans="1:9">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>90</v>
       </c>
@@ -3608,7 +3608,7 @@
       <c r="H100" s="11"/>
       <c r="I100" s="11"/>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>91</v>
       </c>
@@ -3634,7 +3634,7 @@
       <c r="H101" s="11"/>
       <c r="I101" s="11"/>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>92</v>
       </c>
@@ -3660,7 +3660,7 @@
       <c r="H102" s="11"/>
       <c r="I102" s="11"/>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>93</v>
       </c>
@@ -3686,7 +3686,7 @@
       <c r="H103" s="11"/>
       <c r="I103" s="11"/>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>94</v>
       </c>
@@ -3712,7 +3712,7 @@
       <c r="H104" s="11"/>
       <c r="I104" s="11"/>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>95</v>
       </c>
@@ -3738,7 +3738,7 @@
       <c r="H105" s="11"/>
       <c r="I105" s="11"/>
     </row>
-    <row r="106" spans="1:9">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>96</v>
       </c>
@@ -3764,7 +3764,7 @@
       <c r="H106" s="11"/>
       <c r="I106" s="11"/>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>97</v>
       </c>
@@ -3790,7 +3790,7 @@
       <c r="H107" s="11"/>
       <c r="I107" s="11"/>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>98</v>
       </c>
@@ -3816,7 +3816,7 @@
       <c r="H108" s="11"/>
       <c r="I108" s="11"/>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>99</v>
       </c>
@@ -3842,7 +3842,7 @@
       <c r="H109" s="11"/>
       <c r="I109" s="11"/>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>100</v>
       </c>
@@ -3868,7 +3868,7 @@
       <c r="H110" s="11"/>
       <c r="I110" s="11"/>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>101</v>
       </c>
@@ -3894,7 +3894,7 @@
       <c r="H111" s="11"/>
       <c r="I111" s="11"/>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>102</v>
       </c>
@@ -3920,7 +3920,7 @@
       <c r="H112" s="11"/>
       <c r="I112" s="11"/>
     </row>
-    <row r="113" spans="1:9">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>103</v>
       </c>
@@ -3946,7 +3946,7 @@
       <c r="H113" s="11"/>
       <c r="I113" s="11"/>
     </row>
-    <row r="114" spans="1:9">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>104</v>
       </c>
@@ -3972,7 +3972,7 @@
       <c r="H114" s="11"/>
       <c r="I114" s="11"/>
     </row>
-    <row r="115" spans="1:9">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>105</v>
       </c>
@@ -3998,7 +3998,7 @@
       <c r="H115" s="11"/>
       <c r="I115" s="11"/>
     </row>
-    <row r="116" spans="1:9">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>106</v>
       </c>
@@ -4024,7 +4024,7 @@
       <c r="H116" s="11"/>
       <c r="I116" s="11"/>
     </row>
-    <row r="117" spans="1:9">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>107</v>
       </c>
@@ -4050,7 +4050,7 @@
       <c r="H117" s="11"/>
       <c r="I117" s="11"/>
     </row>
-    <row r="118" spans="1:9">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>108</v>
       </c>
@@ -4076,7 +4076,7 @@
       <c r="H118" s="11"/>
       <c r="I118" s="11"/>
     </row>
-    <row r="119" spans="1:9">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>109</v>
       </c>
@@ -4102,7 +4102,7 @@
       <c r="H119" s="11"/>
       <c r="I119" s="11"/>
     </row>
-    <row r="120" spans="1:9">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>110</v>
       </c>
@@ -4128,7 +4128,7 @@
       <c r="H120" s="11"/>
       <c r="I120" s="11"/>
     </row>
-    <row r="121" spans="1:9">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>111</v>
       </c>
@@ -4154,7 +4154,7 @@
       <c r="H121" s="11"/>
       <c r="I121" s="11"/>
     </row>
-    <row r="122" spans="1:9">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>112</v>
       </c>
@@ -4180,7 +4180,7 @@
       <c r="H122" s="11"/>
       <c r="I122" s="11"/>
     </row>
-    <row r="123" spans="1:9">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>113</v>
       </c>
@@ -4206,7 +4206,7 @@
       <c r="H123" s="11"/>
       <c r="I123" s="11"/>
     </row>
-    <row r="124" spans="1:9">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>114</v>
       </c>
@@ -4232,7 +4232,7 @@
       <c r="H124" s="11"/>
       <c r="I124" s="11"/>
     </row>
-    <row r="125" spans="1:9">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>115</v>
       </c>
@@ -4258,7 +4258,7 @@
       <c r="H125" s="11"/>
       <c r="I125" s="11"/>
     </row>
-    <row r="126" spans="1:9">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>116</v>
       </c>
@@ -4284,7 +4284,7 @@
       <c r="H126" s="11"/>
       <c r="I126" s="11"/>
     </row>
-    <row r="127" spans="1:9">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>117</v>
       </c>
@@ -4310,7 +4310,7 @@
       <c r="H127" s="11"/>
       <c r="I127" s="11"/>
     </row>
-    <row r="128" spans="1:9">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>118</v>
       </c>
@@ -4336,7 +4336,7 @@
       <c r="H128" s="11"/>
       <c r="I128" s="11"/>
     </row>
-    <row r="129" spans="1:9">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>119</v>
       </c>
@@ -4362,7 +4362,7 @@
       <c r="H129" s="11"/>
       <c r="I129" s="11"/>
     </row>
-    <row r="130" spans="1:9">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>120</v>
       </c>
@@ -4388,7 +4388,7 @@
       <c r="H130" s="11"/>
       <c r="I130" s="11"/>
     </row>
-    <row r="131" spans="1:9">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>121</v>
       </c>
@@ -4414,7 +4414,7 @@
       <c r="H131" s="11"/>
       <c r="I131" s="11"/>
     </row>
-    <row r="132" spans="1:9">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>122</v>
       </c>
@@ -4440,7 +4440,7 @@
       <c r="H132" s="11"/>
       <c r="I132" s="11"/>
     </row>
-    <row r="133" spans="1:9">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>123</v>
       </c>
@@ -4466,7 +4466,7 @@
       <c r="H133" s="11"/>
       <c r="I133" s="11"/>
     </row>
-    <row r="134" spans="1:9">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>124</v>
       </c>
@@ -4492,7 +4492,7 @@
       <c r="H134" s="11"/>
       <c r="I134" s="11"/>
     </row>
-    <row r="135" spans="1:9">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>125</v>
       </c>
@@ -4518,7 +4518,7 @@
       <c r="H135" s="11"/>
       <c r="I135" s="11"/>
     </row>
-    <row r="136" spans="1:9">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>126</v>
       </c>
@@ -4544,7 +4544,7 @@
       <c r="H136" s="11"/>
       <c r="I136" s="11"/>
     </row>
-    <row r="137" spans="1:9">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>127</v>
       </c>
@@ -4570,7 +4570,7 @@
       <c r="H137" s="11"/>
       <c r="I137" s="11"/>
     </row>
-    <row r="138" spans="1:9">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>128</v>
       </c>
@@ -4596,7 +4596,7 @@
       <c r="H138" s="11"/>
       <c r="I138" s="11"/>
     </row>
-    <row r="139" spans="1:9">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>129</v>
       </c>
@@ -4622,7 +4622,7 @@
       <c r="H139" s="11"/>
       <c r="I139" s="11"/>
     </row>
-    <row r="140" spans="1:9">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>130</v>
       </c>
@@ -4648,7 +4648,7 @@
       <c r="H140" s="11"/>
       <c r="I140" s="11"/>
     </row>
-    <row r="141" spans="1:9">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>131</v>
       </c>
@@ -4674,7 +4674,7 @@
       <c r="H141" s="11"/>
       <c r="I141" s="11"/>
     </row>
-    <row r="142" spans="1:9">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>132</v>
       </c>
@@ -4700,7 +4700,7 @@
       <c r="H142" s="11"/>
       <c r="I142" s="11"/>
     </row>
-    <row r="143" spans="1:9">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>133</v>
       </c>
@@ -4726,7 +4726,7 @@
       <c r="H143" s="11"/>
       <c r="I143" s="11"/>
     </row>
-    <row r="144" spans="1:9">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>134</v>
       </c>
@@ -4752,7 +4752,7 @@
       <c r="H144" s="11"/>
       <c r="I144" s="11"/>
     </row>
-    <row r="145" spans="1:9">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>135</v>
       </c>
@@ -4778,7 +4778,7 @@
       <c r="H145" s="11"/>
       <c r="I145" s="11"/>
     </row>
-    <row r="146" spans="1:9">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>136</v>
       </c>
@@ -4804,7 +4804,7 @@
       <c r="H146" s="11"/>
       <c r="I146" s="11"/>
     </row>
-    <row r="147" spans="1:9">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>137</v>
       </c>
@@ -4830,7 +4830,7 @@
       <c r="H147" s="11"/>
       <c r="I147" s="11"/>
     </row>
-    <row r="148" spans="1:9">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>138</v>
       </c>
@@ -4856,7 +4856,7 @@
       <c r="H148" s="11"/>
       <c r="I148" s="11"/>
     </row>
-    <row r="149" spans="1:9">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>139</v>
       </c>
@@ -4882,7 +4882,7 @@
       <c r="H149" s="11"/>
       <c r="I149" s="11"/>
     </row>
-    <row r="150" spans="1:9">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>140</v>
       </c>
@@ -4908,7 +4908,7 @@
       <c r="H150" s="11"/>
       <c r="I150" s="11"/>
     </row>
-    <row r="151" spans="1:9">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>141</v>
       </c>
@@ -4934,7 +4934,7 @@
       <c r="H151" s="11"/>
       <c r="I151" s="11"/>
     </row>
-    <row r="152" spans="1:9">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>142</v>
       </c>
@@ -4960,7 +4960,7 @@
       <c r="H152" s="11"/>
       <c r="I152" s="11"/>
     </row>
-    <row r="153" spans="1:9">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>143</v>
       </c>
@@ -4986,7 +4986,7 @@
       <c r="H153" s="11"/>
       <c r="I153" s="11"/>
     </row>
-    <row r="154" spans="1:9">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>144</v>
       </c>
@@ -5012,7 +5012,7 @@
       <c r="H154" s="11"/>
       <c r="I154" s="11"/>
     </row>
-    <row r="155" spans="1:9">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>145</v>
       </c>
@@ -5038,7 +5038,7 @@
       <c r="H155" s="11"/>
       <c r="I155" s="11"/>
     </row>
-    <row r="156" spans="1:9">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>146</v>
       </c>
@@ -5064,7 +5064,7 @@
       <c r="H156" s="11"/>
       <c r="I156" s="11"/>
     </row>
-    <row r="157" spans="1:9">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>147</v>
       </c>
@@ -5090,7 +5090,7 @@
       <c r="H157" s="11"/>
       <c r="I157" s="11"/>
     </row>
-    <row r="158" spans="1:9">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>148</v>
       </c>
@@ -5116,7 +5116,7 @@
       <c r="H158" s="11"/>
       <c r="I158" s="11"/>
     </row>
-    <row r="159" spans="1:9">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>149</v>
       </c>
@@ -5142,7 +5142,7 @@
       <c r="H159" s="11"/>
       <c r="I159" s="11"/>
     </row>
-    <row r="160" spans="1:9">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>150</v>
       </c>
@@ -5168,7 +5168,7 @@
       <c r="H160" s="11"/>
       <c r="I160" s="11"/>
     </row>
-    <row r="161" spans="1:9">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>151</v>
       </c>
@@ -5194,7 +5194,7 @@
       <c r="H161" s="11"/>
       <c r="I161" s="11"/>
     </row>
-    <row r="162" spans="1:9">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>152</v>
       </c>
@@ -5220,7 +5220,7 @@
       <c r="H162" s="11"/>
       <c r="I162" s="11"/>
     </row>
-    <row r="163" spans="1:9">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>153</v>
       </c>
@@ -5246,7 +5246,7 @@
       <c r="H163" s="11"/>
       <c r="I163" s="11"/>
     </row>
-    <row r="164" spans="1:9">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>154</v>
       </c>
@@ -5272,7 +5272,7 @@
       <c r="H164" s="11"/>
       <c r="I164" s="11"/>
     </row>
-    <row r="165" spans="1:9">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>155</v>
       </c>
@@ -5298,7 +5298,7 @@
       <c r="H165" s="11"/>
       <c r="I165" s="11"/>
     </row>
-    <row r="166" spans="1:9">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>156</v>
       </c>
@@ -5324,7 +5324,7 @@
       <c r="H166" s="11"/>
       <c r="I166" s="11"/>
     </row>
-    <row r="167" spans="1:9">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>157</v>
       </c>
@@ -5350,7 +5350,7 @@
       <c r="H167" s="11"/>
       <c r="I167" s="11"/>
     </row>
-    <row r="168" spans="1:9">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>158</v>
       </c>
@@ -5376,7 +5376,7 @@
       <c r="H168" s="11"/>
       <c r="I168" s="11"/>
     </row>
-    <row r="169" spans="1:9">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>159</v>
       </c>
@@ -5402,7 +5402,7 @@
       <c r="H169" s="11"/>
       <c r="I169" s="11"/>
     </row>
-    <row r="170" spans="1:9">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>160</v>
       </c>
@@ -5428,7 +5428,7 @@
       <c r="H170" s="11"/>
       <c r="I170" s="11"/>
     </row>
-    <row r="171" spans="1:9">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>161</v>
       </c>
@@ -5454,7 +5454,7 @@
       <c r="H171" s="11"/>
       <c r="I171" s="11"/>
     </row>
-    <row r="172" spans="1:9">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>162</v>
       </c>
@@ -5480,7 +5480,7 @@
       <c r="H172" s="11"/>
       <c r="I172" s="11"/>
     </row>
-    <row r="173" spans="1:9">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>163</v>
       </c>
@@ -5506,7 +5506,7 @@
       <c r="H173" s="11"/>
       <c r="I173" s="11"/>
     </row>
-    <row r="174" spans="1:9">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>164</v>
       </c>
@@ -5532,7 +5532,7 @@
       <c r="H174" s="11"/>
       <c r="I174" s="11"/>
     </row>
-    <row r="175" spans="1:9">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>165</v>
       </c>
@@ -5558,7 +5558,7 @@
       <c r="H175" s="11"/>
       <c r="I175" s="11"/>
     </row>
-    <row r="176" spans="1:9">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>166</v>
       </c>
@@ -5584,7 +5584,7 @@
       <c r="H176" s="11"/>
       <c r="I176" s="11"/>
     </row>
-    <row r="177" spans="1:9">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>167</v>
       </c>
@@ -5610,7 +5610,7 @@
       <c r="H177" s="11"/>
       <c r="I177" s="11"/>
     </row>
-    <row r="178" spans="1:9">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>168</v>
       </c>
@@ -5636,7 +5636,7 @@
       <c r="H178" s="11"/>
       <c r="I178" s="11"/>
     </row>
-    <row r="179" spans="1:9">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>169</v>
       </c>
@@ -5662,7 +5662,7 @@
       <c r="H179" s="11"/>
       <c r="I179" s="11"/>
     </row>
-    <row r="180" spans="1:9">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>170</v>
       </c>
@@ -5688,7 +5688,7 @@
       <c r="H180" s="11"/>
       <c r="I180" s="11"/>
     </row>
-    <row r="181" spans="1:9">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>171</v>
       </c>
@@ -5714,7 +5714,7 @@
       <c r="H181" s="11"/>
       <c r="I181" s="11"/>
     </row>
-    <row r="182" spans="1:9">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>172</v>
       </c>
@@ -5740,7 +5740,7 @@
       <c r="H182" s="11"/>
       <c r="I182" s="11"/>
     </row>
-    <row r="183" spans="1:9">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>173</v>
       </c>
@@ -5766,7 +5766,7 @@
       <c r="H183" s="11"/>
       <c r="I183" s="11"/>
     </row>
-    <row r="184" spans="1:9">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>174</v>
       </c>
@@ -5792,7 +5792,7 @@
       <c r="H184" s="11"/>
       <c r="I184" s="11"/>
     </row>
-    <row r="185" spans="1:9">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>175</v>
       </c>
@@ -5818,7 +5818,7 @@
       <c r="H185" s="11"/>
       <c r="I185" s="11"/>
     </row>
-    <row r="186" spans="1:9">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>176</v>
       </c>
@@ -5844,7 +5844,7 @@
       <c r="H186" s="11"/>
       <c r="I186" s="11"/>
     </row>
-    <row r="187" spans="1:9">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>177</v>
       </c>
@@ -5870,7 +5870,7 @@
       <c r="H187" s="11"/>
       <c r="I187" s="11"/>
     </row>
-    <row r="188" spans="1:9">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>178</v>
       </c>
@@ -5896,7 +5896,7 @@
       <c r="H188" s="11"/>
       <c r="I188" s="11"/>
     </row>
-    <row r="189" spans="1:9">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>179</v>
       </c>
@@ -5922,7 +5922,7 @@
       <c r="H189" s="11"/>
       <c r="I189" s="11"/>
     </row>
-    <row r="190" spans="1:9">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>180</v>
       </c>
@@ -5948,7 +5948,7 @@
       <c r="H190" s="11"/>
       <c r="I190" s="11"/>
     </row>
-    <row r="191" spans="1:9">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>181</v>
       </c>
@@ -5974,7 +5974,7 @@
       <c r="H191" s="11"/>
       <c r="I191" s="11"/>
     </row>
-    <row r="192" spans="1:9">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>182</v>
       </c>
@@ -6000,7 +6000,7 @@
       <c r="H192" s="11"/>
       <c r="I192" s="11"/>
     </row>
-    <row r="193" spans="1:9">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>183</v>
       </c>
@@ -6026,7 +6026,7 @@
       <c r="H193" s="11"/>
       <c r="I193" s="11"/>
     </row>
-    <row r="194" spans="1:9">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>184</v>
       </c>
@@ -6052,7 +6052,7 @@
       <c r="H194" s="11"/>
       <c r="I194" s="11"/>
     </row>
-    <row r="195" spans="1:9">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>185</v>
       </c>
@@ -6078,7 +6078,7 @@
       <c r="H195" s="11"/>
       <c r="I195" s="11"/>
     </row>
-    <row r="196" spans="1:9">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>186</v>
       </c>
@@ -6104,7 +6104,7 @@
       <c r="H196" s="11"/>
       <c r="I196" s="11"/>
     </row>
-    <row r="197" spans="1:9">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>187</v>
       </c>
@@ -6130,7 +6130,7 @@
       <c r="H197" s="11"/>
       <c r="I197" s="11"/>
     </row>
-    <row r="198" spans="1:9">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>188</v>
       </c>
@@ -6156,7 +6156,7 @@
       <c r="H198" s="11"/>
       <c r="I198" s="11"/>
     </row>
-    <row r="199" spans="1:9">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>189</v>
       </c>
@@ -6182,7 +6182,7 @@
       <c r="H199" s="11"/>
       <c r="I199" s="11"/>
     </row>
-    <row r="200" spans="1:9">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>190</v>
       </c>
@@ -6208,7 +6208,7 @@
       <c r="H200" s="11"/>
       <c r="I200" s="11"/>
     </row>
-    <row r="201" spans="1:9">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>191</v>
       </c>
@@ -6234,7 +6234,7 @@
       <c r="H201" s="11"/>
       <c r="I201" s="11"/>
     </row>
-    <row r="202" spans="1:9">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>192</v>
       </c>
@@ -6260,7 +6260,7 @@
       <c r="H202" s="11"/>
       <c r="I202" s="11"/>
     </row>
-    <row r="203" spans="1:9">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>193</v>
       </c>
@@ -6286,7 +6286,7 @@
       <c r="H203" s="11"/>
       <c r="I203" s="11"/>
     </row>
-    <row r="204" spans="1:9">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>194</v>
       </c>
@@ -6312,7 +6312,7 @@
       <c r="H204" s="11"/>
       <c r="I204" s="11"/>
     </row>
-    <row r="205" spans="1:9">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>195</v>
       </c>
@@ -6338,7 +6338,7 @@
       <c r="H205" s="11"/>
       <c r="I205" s="11"/>
     </row>
-    <row r="206" spans="1:9">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>196</v>
       </c>
@@ -6364,7 +6364,7 @@
       <c r="H206" s="11"/>
       <c r="I206" s="11"/>
     </row>
-    <row r="207" spans="1:9">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>197</v>
       </c>
@@ -6390,7 +6390,7 @@
       <c r="H207" s="11"/>
       <c r="I207" s="11"/>
     </row>
-    <row r="208" spans="1:9">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>198</v>
       </c>
@@ -6416,7 +6416,7 @@
       <c r="H208" s="11"/>
       <c r="I208" s="11"/>
     </row>
-    <row r="209" spans="1:9">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>199</v>
       </c>
@@ -6442,7 +6442,7 @@
       <c r="H209" s="11"/>
       <c r="I209" s="11"/>
     </row>
-    <row r="210" spans="1:9">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>200</v>
       </c>
@@ -6468,7 +6468,7 @@
       <c r="H210" s="11"/>
       <c r="I210" s="11"/>
     </row>
-    <row r="211" spans="1:9">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>201</v>
       </c>
@@ -6494,7 +6494,7 @@
       <c r="H211" s="11"/>
       <c r="I211" s="11"/>
     </row>
-    <row r="212" spans="1:9">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>202</v>
       </c>
@@ -6520,7 +6520,7 @@
       <c r="H212" s="11"/>
       <c r="I212" s="11"/>
     </row>
-    <row r="213" spans="1:9">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>203</v>
       </c>
@@ -6546,7 +6546,7 @@
       <c r="H213" s="11"/>
       <c r="I213" s="11"/>
     </row>
-    <row r="214" spans="1:9">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>204</v>
       </c>
@@ -6572,7 +6572,7 @@
       <c r="H214" s="11"/>
       <c r="I214" s="11"/>
     </row>
-    <row r="215" spans="1:9">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>205</v>
       </c>
@@ -6598,7 +6598,7 @@
       <c r="H215" s="11"/>
       <c r="I215" s="11"/>
     </row>
-    <row r="216" spans="1:9">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>206</v>
       </c>
@@ -6624,7 +6624,7 @@
       <c r="H216" s="11"/>
       <c r="I216" s="11"/>
     </row>
-    <row r="217" spans="1:9">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>207</v>
       </c>
@@ -6650,7 +6650,7 @@
       <c r="H217" s="11"/>
       <c r="I217" s="11"/>
     </row>
-    <row r="218" spans="1:9">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>208</v>
       </c>
@@ -6676,7 +6676,7 @@
       <c r="H218" s="11"/>
       <c r="I218" s="11"/>
     </row>
-    <row r="219" spans="1:9">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>209</v>
       </c>
@@ -6702,7 +6702,7 @@
       <c r="H219" s="11"/>
       <c r="I219" s="11"/>
     </row>
-    <row r="220" spans="1:9">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>210</v>
       </c>
@@ -6728,7 +6728,7 @@
       <c r="H220" s="11"/>
       <c r="I220" s="11"/>
     </row>
-    <row r="221" spans="1:9">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>211</v>
       </c>
@@ -6754,7 +6754,7 @@
       <c r="H221" s="11"/>
       <c r="I221" s="11"/>
     </row>
-    <row r="222" spans="1:9">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>212</v>
       </c>
@@ -6780,7 +6780,7 @@
       <c r="H222" s="11"/>
       <c r="I222" s="11"/>
     </row>
-    <row r="223" spans="1:9">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>213</v>
       </c>
@@ -6806,7 +6806,7 @@
       <c r="H223" s="11"/>
       <c r="I223" s="11"/>
     </row>
-    <row r="224" spans="1:9">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>214</v>
       </c>
@@ -6832,7 +6832,7 @@
       <c r="H224" s="11"/>
       <c r="I224" s="11"/>
     </row>
-    <row r="225" spans="1:9">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>215</v>
       </c>
@@ -6858,7 +6858,7 @@
       <c r="H225" s="11"/>
       <c r="I225" s="11"/>
     </row>
-    <row r="226" spans="1:9">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>216</v>
       </c>
@@ -6884,7 +6884,7 @@
       <c r="H226" s="11"/>
       <c r="I226" s="11"/>
     </row>
-    <row r="227" spans="1:9">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>217</v>
       </c>
@@ -6910,7 +6910,7 @@
       <c r="H227" s="11"/>
       <c r="I227" s="11"/>
     </row>
-    <row r="228" spans="1:9">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>218</v>
       </c>
@@ -6936,7 +6936,7 @@
       <c r="H228" s="11"/>
       <c r="I228" s="11"/>
     </row>
-    <row r="229" spans="1:9">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
         <v>219</v>
       </c>
@@ -6962,7 +6962,7 @@
       <c r="H229" s="11"/>
       <c r="I229" s="11"/>
     </row>
-    <row r="230" spans="1:9">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>220</v>
       </c>
@@ -6988,7 +6988,7 @@
       <c r="H230" s="11"/>
       <c r="I230" s="11"/>
     </row>
-    <row r="231" spans="1:9">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>221</v>
       </c>
@@ -7014,7 +7014,7 @@
       <c r="H231" s="11"/>
       <c r="I231" s="11"/>
     </row>
-    <row r="232" spans="1:9">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>222</v>
       </c>
@@ -7040,7 +7040,7 @@
       <c r="H232" s="11"/>
       <c r="I232" s="11"/>
     </row>
-    <row r="233" spans="1:9">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>223</v>
       </c>
@@ -7066,7 +7066,7 @@
       <c r="H233" s="11"/>
       <c r="I233" s="11"/>
     </row>
-    <row r="234" spans="1:9">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>224</v>
       </c>
@@ -7092,7 +7092,7 @@
       <c r="H234" s="11"/>
       <c r="I234" s="11"/>
     </row>
-    <row r="235" spans="1:9">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>225</v>
       </c>
@@ -7118,7 +7118,7 @@
       <c r="H235" s="11"/>
       <c r="I235" s="11"/>
     </row>
-    <row r="236" spans="1:9">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>226</v>
       </c>
@@ -7144,7 +7144,7 @@
       <c r="H236" s="11"/>
       <c r="I236" s="11"/>
     </row>
-    <row r="237" spans="1:9">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>227</v>
       </c>
@@ -7170,7 +7170,7 @@
       <c r="H237" s="11"/>
       <c r="I237" s="11"/>
     </row>
-    <row r="238" spans="1:9">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>228</v>
       </c>
@@ -7196,7 +7196,7 @@
       <c r="H238" s="11"/>
       <c r="I238" s="11"/>
     </row>
-    <row r="239" spans="1:9">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>229</v>
       </c>
@@ -7222,7 +7222,7 @@
       <c r="H239" s="11"/>
       <c r="I239" s="11"/>
     </row>
-    <row r="240" spans="1:9">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>230</v>
       </c>
@@ -7248,7 +7248,7 @@
       <c r="H240" s="11"/>
       <c r="I240" s="11"/>
     </row>
-    <row r="241" spans="1:9">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>231</v>
       </c>
@@ -7274,7 +7274,7 @@
       <c r="H241" s="11"/>
       <c r="I241" s="11"/>
     </row>
-    <row r="242" spans="1:9">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
         <v>232</v>
       </c>
@@ -7300,7 +7300,7 @@
       <c r="H242" s="11"/>
       <c r="I242" s="11"/>
     </row>
-    <row r="243" spans="1:9">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" s="1">
         <v>233</v>
       </c>
@@ -7326,7 +7326,7 @@
       <c r="H243" s="11"/>
       <c r="I243" s="11"/>
     </row>
-    <row r="244" spans="1:9">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" s="1">
         <v>234</v>
       </c>
@@ -7352,7 +7352,7 @@
       <c r="H244" s="11"/>
       <c r="I244" s="11"/>
     </row>
-    <row r="245" spans="1:9">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
         <v>235</v>
       </c>
@@ -7378,7 +7378,7 @@
       <c r="H245" s="11"/>
       <c r="I245" s="11"/>
     </row>
-    <row r="246" spans="1:9">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
         <v>236</v>
       </c>
@@ -7404,7 +7404,7 @@
       <c r="H246" s="11"/>
       <c r="I246" s="11"/>
     </row>
-    <row r="247" spans="1:9">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
         <v>237</v>
       </c>
@@ -7430,7 +7430,7 @@
       <c r="H247" s="11"/>
       <c r="I247" s="11"/>
     </row>
-    <row r="248" spans="1:9">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
         <v>238</v>
       </c>
@@ -7456,7 +7456,7 @@
       <c r="H248" s="11"/>
       <c r="I248" s="11"/>
     </row>
-    <row r="249" spans="1:9">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
         <v>239</v>
       </c>
@@ -7482,7 +7482,7 @@
       <c r="H249" s="11"/>
       <c r="I249" s="11"/>
     </row>
-    <row r="250" spans="1:9">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
         <v>240</v>
       </c>
@@ -7508,7 +7508,7 @@
       <c r="H250" s="11"/>
       <c r="I250" s="11"/>
     </row>
-    <row r="251" spans="1:9">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" s="1">
         <v>241</v>
       </c>
@@ -7534,7 +7534,7 @@
       <c r="H251" s="11"/>
       <c r="I251" s="11"/>
     </row>
-    <row r="252" spans="1:9">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>242</v>
       </c>
@@ -7560,7 +7560,7 @@
       <c r="H252" s="11"/>
       <c r="I252" s="11"/>
     </row>
-    <row r="253" spans="1:9">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>243</v>
       </c>
@@ -7586,7 +7586,7 @@
       <c r="H253" s="11"/>
       <c r="I253" s="11"/>
     </row>
-    <row r="254" spans="1:9">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>244</v>
       </c>
@@ -7612,7 +7612,7 @@
       <c r="H254" s="11"/>
       <c r="I254" s="11"/>
     </row>
-    <row r="255" spans="1:9">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>245</v>
       </c>
@@ -7638,7 +7638,7 @@
       <c r="H255" s="11"/>
       <c r="I255" s="11"/>
     </row>
-    <row r="256" spans="1:9">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>246</v>
       </c>
@@ -7664,7 +7664,7 @@
       <c r="H256" s="11"/>
       <c r="I256" s="11"/>
     </row>
-    <row r="257" spans="1:9">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>247</v>
       </c>
@@ -7690,7 +7690,7 @@
       <c r="H257" s="11"/>
       <c r="I257" s="11"/>
     </row>
-    <row r="258" spans="1:9">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>248</v>
       </c>
@@ -7716,7 +7716,7 @@
       <c r="H258" s="11"/>
       <c r="I258" s="11"/>
     </row>
-    <row r="259" spans="1:9">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>249</v>
       </c>
@@ -7742,7 +7742,7 @@
       <c r="H259" s="11"/>
       <c r="I259" s="11"/>
     </row>
-    <row r="260" spans="1:9">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>250</v>
       </c>
@@ -7768,7 +7768,7 @@
       <c r="H260" s="11"/>
       <c r="I260" s="11"/>
     </row>
-    <row r="261" spans="1:9">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>251</v>
       </c>
@@ -7794,7 +7794,7 @@
       <c r="H261" s="11"/>
       <c r="I261" s="11"/>
     </row>
-    <row r="262" spans="1:9">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>252</v>
       </c>
@@ -7820,7 +7820,7 @@
       <c r="H262" s="11"/>
       <c r="I262" s="11"/>
     </row>
-    <row r="263" spans="1:9">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>253</v>
       </c>
@@ -7846,7 +7846,7 @@
       <c r="H263" s="11"/>
       <c r="I263" s="11"/>
     </row>
-    <row r="264" spans="1:9">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
         <v>254</v>
       </c>
@@ -7872,7 +7872,7 @@
       <c r="H264" s="11"/>
       <c r="I264" s="11"/>
     </row>
-    <row r="265" spans="1:9">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
         <v>255</v>
       </c>
@@ -7898,7 +7898,7 @@
       <c r="H265" s="11"/>
       <c r="I265" s="11"/>
     </row>
-    <row r="266" spans="1:9">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266" s="1">
         <v>256</v>
       </c>
@@ -7924,7 +7924,7 @@
       <c r="H266" s="11"/>
       <c r="I266" s="11"/>
     </row>
-    <row r="267" spans="1:9">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A267" s="1">
         <v>257</v>
       </c>
@@ -7950,7 +7950,7 @@
       <c r="H267" s="11"/>
       <c r="I267" s="11"/>
     </row>
-    <row r="268" spans="1:9">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268" s="1">
         <v>258</v>
       </c>
@@ -7976,7 +7976,7 @@
       <c r="H268" s="11"/>
       <c r="I268" s="11"/>
     </row>
-    <row r="269" spans="1:9">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
         <v>259</v>
       </c>
@@ -8002,7 +8002,7 @@
       <c r="H269" s="11"/>
       <c r="I269" s="11"/>
     </row>
-    <row r="270" spans="1:9">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
         <v>260</v>
       </c>
@@ -8028,7 +8028,7 @@
       <c r="H270" s="11"/>
       <c r="I270" s="11"/>
     </row>
-    <row r="271" spans="1:9">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
         <v>261</v>
       </c>
@@ -8054,7 +8054,7 @@
       <c r="H271" s="11"/>
       <c r="I271" s="11"/>
     </row>
-    <row r="272" spans="1:9">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
         <v>262</v>
       </c>
@@ -8080,7 +8080,7 @@
       <c r="H272" s="11"/>
       <c r="I272" s="11"/>
     </row>
-    <row r="273" spans="1:10">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A273" s="1">
         <v>263</v>
       </c>
@@ -8106,7 +8106,7 @@
       <c r="H273" s="11"/>
       <c r="I273" s="11"/>
     </row>
-    <row r="274" spans="1:10">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" s="1">
         <v>264</v>
       </c>
@@ -8132,7 +8132,7 @@
       <c r="H274" s="11"/>
       <c r="I274" s="11"/>
     </row>
-    <row r="275" spans="1:10">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" s="1">
         <v>265</v>
       </c>
@@ -8158,7 +8158,7 @@
       <c r="H275" s="11"/>
       <c r="I275" s="11"/>
     </row>
-    <row r="276" spans="1:10">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" s="1">
         <v>266</v>
       </c>
@@ -8184,7 +8184,7 @@
       <c r="H276" s="11"/>
       <c r="I276" s="11"/>
     </row>
-    <row r="277" spans="1:10">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" s="1">
         <v>267</v>
       </c>
@@ -8210,7 +8210,7 @@
       <c r="H277" s="11"/>
       <c r="I277" s="11"/>
     </row>
-    <row r="278" spans="1:10">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" s="1">
         <v>268</v>
       </c>
@@ -8236,7 +8236,7 @@
       <c r="H278" s="11"/>
       <c r="I278" s="11"/>
     </row>
-    <row r="279" spans="1:10">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
         <v>269</v>
       </c>
@@ -8262,7 +8262,7 @@
       <c r="H279" s="11"/>
       <c r="I279" s="11"/>
     </row>
-    <row r="280" spans="1:10">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" s="1">
         <v>270</v>
       </c>
@@ -8288,7 +8288,7 @@
       <c r="H280" s="11"/>
       <c r="I280" s="11"/>
     </row>
-    <row r="281" spans="1:10">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" s="1">
         <v>271</v>
       </c>
@@ -8314,7 +8314,7 @@
       <c r="H281" s="11"/>
       <c r="I281" s="11"/>
     </row>
-    <row r="282" spans="1:10">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A282" s="1">
         <v>272</v>
       </c>
@@ -8340,7 +8340,7 @@
       <c r="H282" s="11"/>
       <c r="I282" s="11"/>
     </row>
-    <row r="283" spans="1:10">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A283" s="1">
         <v>273</v>
       </c>
@@ -8366,7 +8366,7 @@
       <c r="H283" s="11"/>
       <c r="I283" s="11"/>
     </row>
-    <row r="284" spans="1:10">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284" s="1">
         <v>274</v>
       </c>
@@ -8392,7 +8392,7 @@
       <c r="H284" s="11"/>
       <c r="I284" s="11"/>
     </row>
-    <row r="285" spans="1:10">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" s="1">
         <v>275</v>
       </c>
@@ -8418,7 +8418,7 @@
       <c r="H285" s="11"/>
       <c r="I285" s="11"/>
     </row>
-    <row r="286" spans="1:10">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" s="1">
         <v>276</v>
       </c>
@@ -8451,7 +8451,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="287" spans="1:10">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
         <v>277</v>
       </c>
@@ -8484,7 +8484,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="288" spans="1:10">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
         <v>278</v>
       </c>
@@ -8517,7 +8517,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="289" spans="1:10">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" s="1">
         <v>279</v>
       </c>
@@ -8550,7 +8550,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="290" spans="1:10">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" s="1">
         <v>280</v>
       </c>
@@ -8583,7 +8583,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="291" spans="1:10">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A291" s="1">
         <v>281</v>
       </c>
@@ -8616,7 +8616,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="292" spans="1:10">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A292" s="1">
         <v>282</v>
       </c>
@@ -8649,7 +8649,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="293" spans="1:10">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A293" s="1">
         <v>283</v>
       </c>
@@ -8682,7 +8682,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="294" spans="1:10">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>284</v>
       </c>
@@ -8715,7 +8715,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="295" spans="1:10">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>285</v>
       </c>
@@ -8748,7 +8748,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="296" spans="1:10">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>286</v>
       </c>
@@ -8781,7 +8781,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="297" spans="1:10">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>287</v>
       </c>
@@ -8814,7 +8814,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="298" spans="1:10">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>288</v>
       </c>
@@ -8847,7 +8847,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="299" spans="1:10">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>289</v>
       </c>
@@ -8880,7 +8880,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="300" spans="1:10">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>290</v>
       </c>
@@ -8913,7 +8913,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="301" spans="1:10">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>291</v>
       </c>
@@ -8946,7 +8946,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="302" spans="1:10">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>292</v>
       </c>
@@ -8979,7 +8979,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="303" spans="1:10" s="1" customFormat="1">
+    <row r="303" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>293</v>
       </c>
@@ -9012,7 +9012,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="304" spans="1:10" s="1" customFormat="1">
+    <row r="304" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>294</v>
       </c>
@@ -9045,7 +9045,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="305" spans="1:10">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>295</v>
       </c>
@@ -9078,7 +9078,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="306" spans="1:10">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>296</v>
       </c>
@@ -9111,7 +9111,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="307" spans="1:10">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>297</v>
       </c>
@@ -9144,7 +9144,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="308" spans="1:10">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>298</v>
       </c>
@@ -9177,7 +9177,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="309" spans="1:10">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>298</v>
       </c>
@@ -9210,7 +9210,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="310" spans="1:10">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A310" s="1">
         <v>299</v>
       </c>
@@ -9243,7 +9243,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="311" spans="1:10">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A311" s="1">
         <v>300</v>
       </c>
@@ -9276,7 +9276,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="312" spans="1:10">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A312" s="1">
         <v>301</v>
       </c>
@@ -9309,7 +9309,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="313" spans="1:10">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A313" s="1">
         <v>302</v>
       </c>
@@ -9342,7 +9342,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="314" spans="1:10">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
         <v>303</v>
       </c>
@@ -9375,7 +9375,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="315" spans="1:10">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A315" s="1">
         <v>304</v>
       </c>
@@ -9408,7 +9408,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="316" spans="1:10">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A316" s="1">
         <v>305</v>
       </c>
@@ -9441,7 +9441,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="317" spans="1:10">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A317" s="1">
         <v>306</v>
       </c>
@@ -9474,7 +9474,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="318" spans="1:10">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A318" s="1">
         <v>307</v>
       </c>
@@ -9507,7 +9507,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="319" spans="1:10">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
         <v>308</v>
       </c>
@@ -9540,7 +9540,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="320" spans="1:10">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A320" s="1">
         <v>309</v>
       </c>
@@ -9573,7 +9573,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="321" spans="1:10">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A321" s="1">
         <v>310</v>
       </c>
@@ -9606,7 +9606,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="322" spans="1:10">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A322" s="1">
         <v>311</v>
       </c>
@@ -9639,7 +9639,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="323" spans="1:10">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A323" s="1">
         <v>312</v>
       </c>
@@ -9672,7 +9672,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="324" spans="1:10">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A324" s="1">
         <v>313</v>
       </c>
@@ -9705,7 +9705,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="325" spans="1:10">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
         <v>314</v>
       </c>
@@ -9738,7 +9738,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="326" spans="1:10">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
         <v>315</v>
       </c>
@@ -9771,7 +9771,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="327" spans="1:10">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A327" s="1">
         <v>316</v>
       </c>
@@ -9804,7 +9804,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="328" spans="1:10">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A328" s="1">
         <v>318</v>
       </c>
@@ -9837,7 +9837,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="329" spans="1:10">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A329" s="1">
         <v>319</v>
       </c>
@@ -9870,7 +9870,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="330" spans="1:10">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A330" s="1">
         <v>320</v>
       </c>
@@ -9903,7 +9903,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="331" spans="1:10">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A331" s="1">
         <v>321</v>
       </c>
@@ -9936,7 +9936,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="332" spans="1:10">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A332" s="1">
         <v>322</v>
       </c>
@@ -9969,7 +9969,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="333" spans="1:10">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A333" s="1">
         <v>323</v>
       </c>
@@ -10002,7 +10002,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="334" spans="1:10">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A334" s="1">
         <v>324</v>
       </c>
@@ -10035,7 +10035,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="335" spans="1:10">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A335" s="1">
         <v>325</v>
       </c>
@@ -10068,7 +10068,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="336" spans="1:10">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A336" s="1">
         <v>326</v>
       </c>
@@ -10101,7 +10101,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="337" spans="1:10">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A337" s="1">
         <v>327</v>
       </c>
@@ -10134,7 +10134,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="338" spans="1:10">
+    <row r="338" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A338" s="1">
         <v>328</v>
       </c>
@@ -10167,7 +10167,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="339" spans="1:10">
+    <row r="339" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A339" s="1">
         <v>329</v>
       </c>
@@ -10200,7 +10200,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="340" spans="1:10">
+    <row r="340" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A340" s="1">
         <v>330</v>
       </c>
@@ -10233,7 +10233,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="341" spans="1:10">
+    <row r="341" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A341" s="1">
         <v>331</v>
       </c>
@@ -10266,7 +10266,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="342" spans="1:10">
+    <row r="342" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A342" s="1">
         <v>332</v>
       </c>
@@ -10299,7 +10299,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="343" spans="1:10">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A343" s="1">
         <v>333</v>
       </c>
@@ -10332,7 +10332,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="344" spans="1:10">
+    <row r="344" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A344" s="1">
         <v>334</v>
       </c>
@@ -10365,7 +10365,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="345" spans="1:10">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A345" s="1">
         <v>335</v>
       </c>
@@ -10417,13 +10417,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{797F1036-D41E-43A4-9E6E-CBBB62F3CD31}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="13.28515625" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -10437,7 +10437,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -10451,7 +10451,7 @@
         <v>234.67</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -10465,7 +10465,7 @@
         <v>161.15</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -10479,7 +10479,7 @@
         <v>157.61000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -10493,7 +10493,7 @@
         <v>347.95</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -10507,7 +10507,7 @@
         <v>393.57</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -10521,7 +10521,7 @@
         <v>19.87</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -10535,7 +10535,7 @@
         <v>19.57</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>86</v>
       </c>
@@ -10549,7 +10549,7 @@
         <v>19.86</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -10563,7 +10563,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -10588,15 +10588,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56220E0F-EC16-4A8C-9E04-C7F8849C4B4D}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -10613,7 +10613,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -10621,7 +10621,7 @@
         <v>46023</v>
       </c>
       <c r="C2" s="3">
-        <v>46237.999988425923</v>
+        <v>46254.999988425923</v>
       </c>
       <c r="D2" s="14">
         <v>214.99998842592322</v>
@@ -10630,7 +10630,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -10647,7 +10647,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -10664,7 +10664,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -10681,7 +10681,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -10698,7 +10698,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -10715,7 +10715,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -10733,7 +10733,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -10762,14 +10762,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83DAFC4B-C207-418A-8501-0E1EC9E673B7}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -10780,7 +10780,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -10791,7 +10791,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -10802,7 +10802,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -10813,7 +10813,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>86</v>
       </c>
@@ -10824,7 +10824,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -10835,7 +10835,7 @@
         <v>46631</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -10846,7 +10846,7 @@
         <v>48579</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -10857,7 +10857,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -10868,7 +10868,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -10879,7 +10879,7 @@
         <v>48579</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -10899,6 +10899,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100FB7AAE8C8816FD47B559A0CCF555AFF0" ma:contentTypeVersion="10" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5c9910934a78ddf693a6b708b52e9b37">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f95d585e-e7a7-414c-955d-38a47c8579bd" xmlns:ns3="33ab045e-9213-4eea-a9f2-a5b809105d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a9c61c95b4e11caed4e46447c2ca01e7" ns2:_="" ns3:_="">
     <xsd:import namespace="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
@@ -11101,39 +11124,41 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
+    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1310" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{013298E2-44DF-4DB1-98C7-51585CA511D2}"/>
+  <xr:revisionPtr revIDLastSave="1312" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C49F1B7-9B6C-4756-A1AD-4F24B9BB33AF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -10669,13 +10669,14 @@
         <v>12</v>
       </c>
       <c r="B5" s="3">
-        <v>46264</v>
+        <v>46330</v>
       </c>
       <c r="C5" s="3">
         <v>46281.999988425923</v>
       </c>
       <c r="D5" s="14">
-        <v>17.99998842592322</v>
+        <f>Indisp_Prog[[#This Row],[Fecha_Hora_Fin]]-Indisp_Prog[[#This Row],[Fecha_Hora_Inicio]]</f>
+        <v>-48.00001157407678</v>
       </c>
       <c r="E5" t="s">
         <v>115</v>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1312" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C49F1B7-9B6C-4756-A1AD-4F24B9BB33AF}"/>
+  <xr:revisionPtr revIDLastSave="1316" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8682CAC0-F6D5-416A-8B5C-DB939D701554}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView minimized="1" xWindow="8595" yWindow="3435" windowWidth="17280" windowHeight="8985" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -10672,11 +10672,10 @@
         <v>46330</v>
       </c>
       <c r="C5" s="3">
-        <v>46281.999988425923</v>
+        <v>46348.999305555553</v>
       </c>
       <c r="D5" s="14">
-        <f>Indisp_Prog[[#This Row],[Fecha_Hora_Fin]]-Indisp_Prog[[#This Row],[Fecha_Hora_Inicio]]</f>
-        <v>-48.00001157407678</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
         <v>115</v>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1316" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8682CAC0-F6D5-416A-8B5C-DB939D701554}"/>
+  <xr:revisionPtr revIDLastSave="1320" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B4CC2DE-C17A-4C4C-B125-71F6215B8668}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="8595" yWindow="3435" windowWidth="17280" windowHeight="8985" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="119">
   <si>
     <t>ID</t>
   </si>
@@ -454,7 +454,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -495,21 +495,14 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="12">
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
-    </dxf>
     <dxf>
       <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -541,6 +534,16 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -567,7 +570,7 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>949282</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>148500</xdr:rowOff>
+      <xdr:rowOff>144690</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -645,7 +648,7 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>225435</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>148500</xdr:rowOff>
+      <xdr:rowOff>144690</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -723,7 +726,7 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>873135</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>148500</xdr:rowOff>
+      <xdr:rowOff>144690</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -832,23 +835,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J345" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J345" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J346" totalsRowShown="0" headerRowDxfId="8">
+  <autoFilter ref="A10:J346" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="3" xr3:uid="{AFE823F6-980E-4E32-B4F4-6ECDE10F377D}" name="ID"/>
-    <tableColumn id="1" xr3:uid="{CD000998-6E2C-4963-8605-37081D9C1A64}" name="Unidad" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{542F6635-555D-4F04-8C27-263AF6E0C9F1}" name="Sitio" dataDxfId="9">
+    <tableColumn id="1" xr3:uid="{CD000998-6E2C-4963-8605-37081D9C1A64}" name="Unidad" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{542F6635-555D-4F04-8C27-263AF6E0C9F1}" name="Sitio" dataDxfId="6">
       <calculatedColumnFormula>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6D2AC534-BC70-4E36-815D-053C7EC9A0CE}" name="Carga_Disponible" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{FBB18F6C-27E4-42D9-9835-9152B6D0D871}" name="Estado_Op" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{21A32989-F167-49C0-9D41-2BD3A8923998}" name="Fecha_Hora_Inicio" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{713F74B7-95D9-4F96-AA1E-57E68B8A7FE7}" name="Fecha_Hora_Final" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{20481209-2CB3-4DCC-A330-D866983AA4F9}" name="Motivo" dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{55FF6738-9798-4086-9AA1-DC8A3EF8081F}" name="Detalle" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{6D2AC534-BC70-4E36-815D-053C7EC9A0CE}" name="Carga_Disponible" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{FBB18F6C-27E4-42D9-9835-9152B6D0D871}" name="Estado_Op" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{21A32989-F167-49C0-9D41-2BD3A8923998}" name="Fecha_Hora_Inicio" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{713F74B7-95D9-4F96-AA1E-57E68B8A7FE7}" name="Fecha_Hora_Final" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{20481209-2CB3-4DCC-A330-D866983AA4F9}" name="Motivo" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{55FF6738-9798-4086-9AA1-DC8A3EF8081F}" name="Detalle" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{C2DE1A32-EBAC-4C95-A60E-FB6BAE643966}" name="Verificación"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -876,9 +879,9 @@
   </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{1EEE0FFC-B699-4850-9A13-72CF6FB78CA6}" name="Unidad"/>
-    <tableColumn id="2" xr3:uid="{BDB3B76C-8D9D-4A32-9C94-204172B9E68C}" name="Fecha_Hora_Inicio" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{A21A7F07-F50E-4006-B601-758B5E8BD7BE}" name="Fecha_Hora_Fin" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{F49EC928-7A7A-47BB-9275-EDE8B8DF6BC7}" name="Días_de_Mantenimiento" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{BDB3B76C-8D9D-4A32-9C94-204172B9E68C}" name="Fecha_Hora_Inicio" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{A21A7F07-F50E-4006-B601-758B5E8BD7BE}" name="Fecha_Hora_Fin" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{F49EC928-7A7A-47BB-9275-EDE8B8DF6BC7}" name="Días_de_Mantenimiento" dataDxfId="9"/>
     <tableColumn id="5" xr3:uid="{E5C19B72-F1F0-4F1D-9466-99048BCEFC0C}" name="Motivo"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1214,7 +1217,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
-  <dimension ref="A9:J345"/>
+  <dimension ref="A9:J346"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.5546875" bestFit="1" customWidth="1"/>
@@ -1233,7 +1236,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -10397,6 +10400,28 @@
       <c r="J345" s="1" t="s">
         <v>23</v>
       </c>
+    </row>
+    <row r="346" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A346">
+        <v>336</v>
+      </c>
+      <c r="B346" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C346" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
+      </c>
+      <c r="D346" s="14">
+        <v>0</v>
+      </c>
+      <c r="E346" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F346" s="15"/>
+      <c r="G346" s="15"/>
+      <c r="H346" s="11"/>
+      <c r="I346" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10908,20 +10933,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100FB7AAE8C8816FD47B559A0CCF555AFF0" ma:contentTypeVersion="10" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5c9910934a78ddf693a6b708b52e9b37">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f95d585e-e7a7-414c-955d-38a47c8579bd" xmlns:ns3="33ab045e-9213-4eea-a9f2-a5b809105d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a9c61c95b4e11caed4e46447c2ca01e7" ns2:_="" ns3:_="">
     <xsd:import namespace="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
@@ -11124,6 +11135,20 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
   <ds:schemaRefs>
@@ -11133,16 +11158,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11161,6 +11176,16 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{0a9b9e15-83d2-4075-9282-a04e05c6580a}" enabled="1" method="Standard" siteId="{24139d14-c62c-4c47-8bdd-ce71ea1d50cf}" contentBits="0" removed="0"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1320" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B4CC2DE-C17A-4C4C-B125-71F6215B8668}"/>
+  <xr:revisionPtr revIDLastSave="1339" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C5E01ED-0434-4830-BC9D-57230777ADFF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="123">
   <si>
     <t>ID</t>
   </si>
@@ -411,6 +411,18 @@
   </si>
   <si>
     <t>FechaFinVigencia</t>
+  </si>
+  <si>
+    <t>Cambio de filtro de admisión en caja intake</t>
+  </si>
+  <si>
+    <t>Alta diferencia de presión filtro de admisión en caja intake</t>
+  </si>
+  <si>
+    <t>Alta vibración descanso TV</t>
+  </si>
+  <si>
+    <t>Se realiza desacople TV para iniciar proceso de calentamiento uniforme.</t>
   </si>
 </sst>
 </file>
@@ -570,7 +582,7 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>949282</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>144690</xdr:rowOff>
+      <xdr:rowOff>137070</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -648,7 +660,7 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>225435</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>144690</xdr:rowOff>
+      <xdr:rowOff>137070</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -726,7 +738,7 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>873135</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>144690</xdr:rowOff>
+      <xdr:rowOff>137070</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -835,8 +847,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J346" totalsRowShown="0" headerRowDxfId="8">
-  <autoFilter ref="A10:J346" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J347" totalsRowShown="0" headerRowDxfId="8">
+  <autoFilter ref="A10:J347" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1217,7 +1229,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
-  <dimension ref="A9:J346"/>
+  <dimension ref="A9:J347"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.5546875" bestFit="1" customWidth="1"/>
@@ -1236,7 +1248,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -10402,7 +10414,7 @@
       </c>
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A346">
+      <c r="A346" s="1">
         <v>336</v>
       </c>
       <c r="B346" s="13" t="s">
@@ -10418,10 +10430,54 @@
       <c r="E346" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="F346" s="15"/>
-      <c r="G346" s="15"/>
-      <c r="H346" s="11"/>
-      <c r="I346" s="11"/>
+      <c r="F346" s="15">
+        <v>46248.513888888891</v>
+      </c>
+      <c r="G346" s="15">
+        <v>46248.813194444447</v>
+      </c>
+      <c r="H346" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="I346" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="J346" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="347" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A347">
+        <v>337</v>
+      </c>
+      <c r="B347" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C347" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
+      </c>
+      <c r="D347" s="14">
+        <v>262</v>
+      </c>
+      <c r="E347" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F347" s="15">
+        <v>46249.194444444445</v>
+      </c>
+      <c r="G347" s="15">
+        <v>46249.208333333336</v>
+      </c>
+      <c r="H347" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="I347" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="J347" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1339" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C5E01ED-0434-4830-BC9D-57230777ADFF}"/>
+  <xr:revisionPtr revIDLastSave="1342" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17E8552E-A87F-4961-95B9-5A91E977E556}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -374,6 +374,18 @@
     <t>Falla valvúla control de gas a TG</t>
   </si>
   <si>
+    <t>Cambio de filtro de admisión en caja intake</t>
+  </si>
+  <si>
+    <t>Alta diferencia de presión filtro de admisión en caja intake</t>
+  </si>
+  <si>
+    <t>Alta vibración descanso TV</t>
+  </si>
+  <si>
+    <t>Se realiza desacople TV para iniciar proceso de calentamiento uniforme.</t>
+  </si>
+  <si>
     <t>P_Max_Bruta</t>
   </si>
   <si>
@@ -411,25 +423,13 @@
   </si>
   <si>
     <t>FechaFinVigencia</t>
-  </si>
-  <si>
-    <t>Cambio de filtro de admisión en caja intake</t>
-  </si>
-  <si>
-    <t>Alta diferencia de presión filtro de admisión en caja intake</t>
-  </si>
-  <si>
-    <t>Alta vibración descanso TV</t>
-  </si>
-  <si>
-    <t>Se realiza desacople TV para iniciar proceso de calentamiento uniforme.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -466,7 +466,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -507,14 +507,21 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="12">
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
+    </dxf>
     <dxf>
       <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -522,11 +529,11 @@
       <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -545,16 +552,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -847,23 +844,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J347" totalsRowShown="0" headerRowDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J347" totalsRowShown="0" headerRowDxfId="11">
   <autoFilter ref="A10:J347" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="3" xr3:uid="{AFE823F6-980E-4E32-B4F4-6ECDE10F377D}" name="ID"/>
-    <tableColumn id="1" xr3:uid="{CD000998-6E2C-4963-8605-37081D9C1A64}" name="Unidad" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{542F6635-555D-4F04-8C27-263AF6E0C9F1}" name="Sitio" dataDxfId="6">
+    <tableColumn id="1" xr3:uid="{CD000998-6E2C-4963-8605-37081D9C1A64}" name="Unidad" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{542F6635-555D-4F04-8C27-263AF6E0C9F1}" name="Sitio" dataDxfId="9">
       <calculatedColumnFormula>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6D2AC534-BC70-4E36-815D-053C7EC9A0CE}" name="Carga_Disponible" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{FBB18F6C-27E4-42D9-9835-9152B6D0D871}" name="Estado_Op" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{21A32989-F167-49C0-9D41-2BD3A8923998}" name="Fecha_Hora_Inicio" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{713F74B7-95D9-4F96-AA1E-57E68B8A7FE7}" name="Fecha_Hora_Final" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{20481209-2CB3-4DCC-A330-D866983AA4F9}" name="Motivo" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{55FF6738-9798-4086-9AA1-DC8A3EF8081F}" name="Detalle" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{6D2AC534-BC70-4E36-815D-053C7EC9A0CE}" name="Carga_Disponible" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{FBB18F6C-27E4-42D9-9835-9152B6D0D871}" name="Estado_Op" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{21A32989-F167-49C0-9D41-2BD3A8923998}" name="Fecha_Hora_Inicio" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{713F74B7-95D9-4F96-AA1E-57E68B8A7FE7}" name="Fecha_Hora_Final" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{20481209-2CB3-4DCC-A330-D866983AA4F9}" name="Motivo" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{55FF6738-9798-4086-9AA1-DC8A3EF8081F}" name="Detalle" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{C2DE1A32-EBAC-4C95-A60E-FB6BAE643966}" name="Verificación"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -891,9 +888,9 @@
   </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{1EEE0FFC-B699-4850-9A13-72CF6FB78CA6}" name="Unidad"/>
-    <tableColumn id="2" xr3:uid="{BDB3B76C-8D9D-4A32-9C94-204172B9E68C}" name="Fecha_Hora_Inicio" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{A21A7F07-F50E-4006-B601-758B5E8BD7BE}" name="Fecha_Hora_Fin" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{F49EC928-7A7A-47BB-9275-EDE8B8DF6BC7}" name="Días_de_Mantenimiento" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{BDB3B76C-8D9D-4A32-9C94-204172B9E68C}" name="Fecha_Hora_Inicio" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{A21A7F07-F50E-4006-B601-758B5E8BD7BE}" name="Fecha_Hora_Fin" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{F49EC928-7A7A-47BB-9275-EDE8B8DF6BC7}" name="Días_de_Mantenimiento" dataDxfId="0"/>
     <tableColumn id="5" xr3:uid="{E5C19B72-F1F0-4F1D-9466-99048BCEFC0C}" name="Motivo"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1230,28 +1227,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
   <dimension ref="A9:J347"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="41.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="151.33203125" customWidth="1"/>
-    <col min="10" max="10" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" customWidth="1"/>
-    <col min="12" max="12" width="33.33203125" customWidth="1"/>
+    <col min="6" max="7" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="151.28515625" customWidth="1"/>
+    <col min="10" max="10" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="33.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
         <v>337</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1283,7 +1280,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -1309,7 +1306,7 @@
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -1335,7 +1332,7 @@
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10">
       <c r="A13" s="1">
         <v>3</v>
       </c>
@@ -1361,7 +1358,7 @@
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10">
       <c r="A14" s="1">
         <v>4</v>
       </c>
@@ -1387,7 +1384,7 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10">
       <c r="A15" s="1">
         <v>5</v>
       </c>
@@ -1413,7 +1410,7 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10">
       <c r="A16" s="1">
         <v>6</v>
       </c>
@@ -1439,7 +1436,7 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9">
       <c r="A17" s="1">
         <v>7</v>
       </c>
@@ -1465,7 +1462,7 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9">
       <c r="A18" s="1">
         <v>8</v>
       </c>
@@ -1491,7 +1488,7 @@
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9">
       <c r="A19" s="1">
         <v>9</v>
       </c>
@@ -1517,7 +1514,7 @@
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9">
       <c r="A20" s="1">
         <v>10</v>
       </c>
@@ -1543,7 +1540,7 @@
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9">
       <c r="A21" s="1">
         <v>11</v>
       </c>
@@ -1569,7 +1566,7 @@
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9">
       <c r="A22" s="1">
         <v>12</v>
       </c>
@@ -1595,7 +1592,7 @@
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9">
       <c r="A23" s="1">
         <v>13</v>
       </c>
@@ -1621,7 +1618,7 @@
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9">
       <c r="A24" s="1">
         <v>14</v>
       </c>
@@ -1647,7 +1644,7 @@
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9">
       <c r="A25" s="1">
         <v>15</v>
       </c>
@@ -1673,7 +1670,7 @@
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9">
       <c r="A26" s="1">
         <v>16</v>
       </c>
@@ -1699,7 +1696,7 @@
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9">
       <c r="A27" s="1">
         <v>17</v>
       </c>
@@ -1725,7 +1722,7 @@
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9">
       <c r="A28" s="1">
         <v>18</v>
       </c>
@@ -1751,7 +1748,7 @@
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9">
       <c r="A29" s="1">
         <v>19</v>
       </c>
@@ -1777,7 +1774,7 @@
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9">
       <c r="A30" s="1">
         <v>20</v>
       </c>
@@ -1803,7 +1800,7 @@
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9">
       <c r="A31" s="1">
         <v>21</v>
       </c>
@@ -1829,7 +1826,7 @@
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9">
       <c r="A32" s="1">
         <v>22</v>
       </c>
@@ -1855,7 +1852,7 @@
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9">
       <c r="A33" s="1">
         <v>23</v>
       </c>
@@ -1881,7 +1878,7 @@
       <c r="H33" s="11"/>
       <c r="I33" s="11"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9">
       <c r="A34" s="1">
         <v>24</v>
       </c>
@@ -1907,7 +1904,7 @@
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9">
       <c r="A35" s="1">
         <v>25</v>
       </c>
@@ -1933,7 +1930,7 @@
       <c r="H35" s="11"/>
       <c r="I35" s="11"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9">
       <c r="A36" s="1">
         <v>26</v>
       </c>
@@ -1959,7 +1956,7 @@
       <c r="H36" s="11"/>
       <c r="I36" s="11"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9">
       <c r="A37" s="1">
         <v>27</v>
       </c>
@@ -1985,7 +1982,7 @@
       <c r="H37" s="11"/>
       <c r="I37" s="11"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9">
       <c r="A38" s="1">
         <v>28</v>
       </c>
@@ -2011,7 +2008,7 @@
       <c r="H38" s="11"/>
       <c r="I38" s="11"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9">
       <c r="A39" s="1">
         <v>29</v>
       </c>
@@ -2037,7 +2034,7 @@
       <c r="H39" s="11"/>
       <c r="I39" s="11"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9">
       <c r="A40" s="1">
         <v>30</v>
       </c>
@@ -2063,7 +2060,7 @@
       <c r="H40" s="11"/>
       <c r="I40" s="11"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9">
       <c r="A41" s="1">
         <v>31</v>
       </c>
@@ -2089,7 +2086,7 @@
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9">
       <c r="A42" s="1">
         <v>32</v>
       </c>
@@ -2115,7 +2112,7 @@
       <c r="H42" s="11"/>
       <c r="I42" s="11"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9">
       <c r="A43" s="1">
         <v>33</v>
       </c>
@@ -2141,7 +2138,7 @@
       <c r="H43" s="11"/>
       <c r="I43" s="11"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9">
       <c r="A44" s="1">
         <v>34</v>
       </c>
@@ -2167,7 +2164,7 @@
       <c r="H44" s="11"/>
       <c r="I44" s="11"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9">
       <c r="A45" s="1">
         <v>35</v>
       </c>
@@ -2193,7 +2190,7 @@
       <c r="H45" s="11"/>
       <c r="I45" s="11"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9">
       <c r="A46" s="1">
         <v>36</v>
       </c>
@@ -2219,7 +2216,7 @@
       <c r="H46" s="11"/>
       <c r="I46" s="11"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9">
       <c r="A47" s="1">
         <v>37</v>
       </c>
@@ -2245,7 +2242,7 @@
       <c r="H47" s="11"/>
       <c r="I47" s="11"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9">
       <c r="A48" s="1">
         <v>38</v>
       </c>
@@ -2271,7 +2268,7 @@
       <c r="H48" s="11"/>
       <c r="I48" s="11"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9">
       <c r="A49" s="1">
         <v>39</v>
       </c>
@@ -2297,7 +2294,7 @@
       <c r="H49" s="11"/>
       <c r="I49" s="11"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9">
       <c r="A50" s="1">
         <v>40</v>
       </c>
@@ -2323,7 +2320,7 @@
       <c r="H50" s="11"/>
       <c r="I50" s="11"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9">
       <c r="A51" s="1">
         <v>41</v>
       </c>
@@ -2349,7 +2346,7 @@
       <c r="H51" s="11"/>
       <c r="I51" s="11"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9">
       <c r="A52" s="1">
         <v>42</v>
       </c>
@@ -2375,7 +2372,7 @@
       <c r="H52" s="11"/>
       <c r="I52" s="11"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9">
       <c r="A53" s="1">
         <v>43</v>
       </c>
@@ -2401,7 +2398,7 @@
       <c r="H53" s="11"/>
       <c r="I53" s="11"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9">
       <c r="A54" s="1">
         <v>44</v>
       </c>
@@ -2427,7 +2424,7 @@
       <c r="H54" s="11"/>
       <c r="I54" s="11"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9">
       <c r="A55" s="1">
         <v>45</v>
       </c>
@@ -2453,7 +2450,7 @@
       <c r="H55" s="11"/>
       <c r="I55" s="11"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9">
       <c r="A56" s="1">
         <v>46</v>
       </c>
@@ -2479,7 +2476,7 @@
       <c r="H56" s="11"/>
       <c r="I56" s="11"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9">
       <c r="A57" s="1">
         <v>47</v>
       </c>
@@ -2505,7 +2502,7 @@
       <c r="H57" s="11"/>
       <c r="I57" s="11"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9">
       <c r="A58" s="1">
         <v>48</v>
       </c>
@@ -2531,7 +2528,7 @@
       <c r="H58" s="11"/>
       <c r="I58" s="11"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9">
       <c r="A59" s="1">
         <v>49</v>
       </c>
@@ -2557,7 +2554,7 @@
       <c r="H59" s="11"/>
       <c r="I59" s="11"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9">
       <c r="A60" s="1">
         <v>50</v>
       </c>
@@ -2583,7 +2580,7 @@
       <c r="H60" s="11"/>
       <c r="I60" s="11"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9">
       <c r="A61" s="1">
         <v>51</v>
       </c>
@@ -2609,7 +2606,7 @@
       <c r="H61" s="11"/>
       <c r="I61" s="11"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9">
       <c r="A62" s="1">
         <v>52</v>
       </c>
@@ -2635,7 +2632,7 @@
       <c r="H62" s="11"/>
       <c r="I62" s="11"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9">
       <c r="A63" s="1">
         <v>53</v>
       </c>
@@ -2661,7 +2658,7 @@
       <c r="H63" s="11"/>
       <c r="I63" s="11"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9">
       <c r="A64" s="1">
         <v>54</v>
       </c>
@@ -2687,7 +2684,7 @@
       <c r="H64" s="11"/>
       <c r="I64" s="11"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9">
       <c r="A65" s="1">
         <v>55</v>
       </c>
@@ -2713,7 +2710,7 @@
       <c r="H65" s="11"/>
       <c r="I65" s="11"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9">
       <c r="A66" s="1">
         <v>56</v>
       </c>
@@ -2739,7 +2736,7 @@
       <c r="H66" s="11"/>
       <c r="I66" s="11"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9">
       <c r="A67" s="1">
         <v>57</v>
       </c>
@@ -2765,7 +2762,7 @@
       <c r="H67" s="11"/>
       <c r="I67" s="11"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9">
       <c r="A68" s="1">
         <v>58</v>
       </c>
@@ -2791,7 +2788,7 @@
       <c r="H68" s="11"/>
       <c r="I68" s="11"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9">
       <c r="A69" s="1">
         <v>59</v>
       </c>
@@ -2817,7 +2814,7 @@
       <c r="H69" s="11"/>
       <c r="I69" s="11"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9">
       <c r="A70" s="1">
         <v>60</v>
       </c>
@@ -2843,7 +2840,7 @@
       <c r="H70" s="11"/>
       <c r="I70" s="11"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9">
       <c r="A71" s="1">
         <v>61</v>
       </c>
@@ -2869,7 +2866,7 @@
       <c r="H71" s="11"/>
       <c r="I71" s="11"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9">
       <c r="A72" s="1">
         <v>62</v>
       </c>
@@ -2895,7 +2892,7 @@
       <c r="H72" s="11"/>
       <c r="I72" s="11"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9">
       <c r="A73" s="1">
         <v>63</v>
       </c>
@@ -2921,7 +2918,7 @@
       <c r="H73" s="11"/>
       <c r="I73" s="11"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9">
       <c r="A74" s="1">
         <v>64</v>
       </c>
@@ -2947,7 +2944,7 @@
       <c r="H74" s="11"/>
       <c r="I74" s="11"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9">
       <c r="A75" s="1">
         <v>65</v>
       </c>
@@ -2973,7 +2970,7 @@
       <c r="H75" s="11"/>
       <c r="I75" s="11"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9">
       <c r="A76" s="1">
         <v>66</v>
       </c>
@@ -2999,7 +2996,7 @@
       <c r="H76" s="11"/>
       <c r="I76" s="11"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9">
       <c r="A77" s="1">
         <v>67</v>
       </c>
@@ -3025,7 +3022,7 @@
       <c r="H77" s="11"/>
       <c r="I77" s="11"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9">
       <c r="A78" s="1">
         <v>68</v>
       </c>
@@ -3051,7 +3048,7 @@
       <c r="H78" s="11"/>
       <c r="I78" s="11"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9">
       <c r="A79" s="1">
         <v>69</v>
       </c>
@@ -3077,7 +3074,7 @@
       <c r="H79" s="11"/>
       <c r="I79" s="11"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9">
       <c r="A80" s="1">
         <v>70</v>
       </c>
@@ -3103,7 +3100,7 @@
       <c r="H80" s="11"/>
       <c r="I80" s="11"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9">
       <c r="A81" s="1">
         <v>71</v>
       </c>
@@ -3129,7 +3126,7 @@
       <c r="H81" s="11"/>
       <c r="I81" s="11"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9">
       <c r="A82" s="1">
         <v>72</v>
       </c>
@@ -3155,7 +3152,7 @@
       <c r="H82" s="11"/>
       <c r="I82" s="11"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9">
       <c r="A83" s="1">
         <v>73</v>
       </c>
@@ -3181,7 +3178,7 @@
       <c r="H83" s="11"/>
       <c r="I83" s="11"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9">
       <c r="A84" s="1">
         <v>74</v>
       </c>
@@ -3207,7 +3204,7 @@
       <c r="H84" s="11"/>
       <c r="I84" s="11"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9">
       <c r="A85" s="1">
         <v>75</v>
       </c>
@@ -3233,7 +3230,7 @@
       <c r="H85" s="11"/>
       <c r="I85" s="11"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9">
       <c r="A86" s="1">
         <v>76</v>
       </c>
@@ -3259,7 +3256,7 @@
       <c r="H86" s="11"/>
       <c r="I86" s="11"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9">
       <c r="A87" s="1">
         <v>77</v>
       </c>
@@ -3285,7 +3282,7 @@
       <c r="H87" s="11"/>
       <c r="I87" s="11"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9">
       <c r="A88" s="1">
         <v>78</v>
       </c>
@@ -3311,7 +3308,7 @@
       <c r="H88" s="11"/>
       <c r="I88" s="11"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9">
       <c r="A89" s="1">
         <v>79</v>
       </c>
@@ -3337,7 +3334,7 @@
       <c r="H89" s="11"/>
       <c r="I89" s="11"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9">
       <c r="A90" s="1">
         <v>80</v>
       </c>
@@ -3363,7 +3360,7 @@
       <c r="H90" s="11"/>
       <c r="I90" s="11"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9">
       <c r="A91" s="1">
         <v>81</v>
       </c>
@@ -3389,7 +3386,7 @@
       <c r="H91" s="11"/>
       <c r="I91" s="11"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9">
       <c r="A92" s="1">
         <v>82</v>
       </c>
@@ -3415,7 +3412,7 @@
       <c r="H92" s="11"/>
       <c r="I92" s="11"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9">
       <c r="A93" s="1">
         <v>83</v>
       </c>
@@ -3441,7 +3438,7 @@
       <c r="H93" s="11"/>
       <c r="I93" s="11"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9">
       <c r="A94" s="1">
         <v>84</v>
       </c>
@@ -3467,7 +3464,7 @@
       <c r="H94" s="11"/>
       <c r="I94" s="11"/>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9">
       <c r="A95" s="1">
         <v>85</v>
       </c>
@@ -3493,7 +3490,7 @@
       <c r="H95" s="11"/>
       <c r="I95" s="11"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9">
       <c r="A96" s="1">
         <v>86</v>
       </c>
@@ -3519,7 +3516,7 @@
       <c r="H96" s="11"/>
       <c r="I96" s="11"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9">
       <c r="A97" s="1">
         <v>87</v>
       </c>
@@ -3545,7 +3542,7 @@
       <c r="H97" s="11"/>
       <c r="I97" s="11"/>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9">
       <c r="A98" s="1">
         <v>88</v>
       </c>
@@ -3571,7 +3568,7 @@
       <c r="H98" s="11"/>
       <c r="I98" s="11"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9">
       <c r="A99" s="1">
         <v>89</v>
       </c>
@@ -3597,7 +3594,7 @@
       <c r="H99" s="11"/>
       <c r="I99" s="11"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9">
       <c r="A100" s="1">
         <v>90</v>
       </c>
@@ -3623,7 +3620,7 @@
       <c r="H100" s="11"/>
       <c r="I100" s="11"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9">
       <c r="A101" s="1">
         <v>91</v>
       </c>
@@ -3649,7 +3646,7 @@
       <c r="H101" s="11"/>
       <c r="I101" s="11"/>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9">
       <c r="A102" s="1">
         <v>92</v>
       </c>
@@ -3675,7 +3672,7 @@
       <c r="H102" s="11"/>
       <c r="I102" s="11"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9">
       <c r="A103" s="1">
         <v>93</v>
       </c>
@@ -3701,7 +3698,7 @@
       <c r="H103" s="11"/>
       <c r="I103" s="11"/>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9">
       <c r="A104" s="1">
         <v>94</v>
       </c>
@@ -3727,7 +3724,7 @@
       <c r="H104" s="11"/>
       <c r="I104" s="11"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9">
       <c r="A105" s="1">
         <v>95</v>
       </c>
@@ -3753,7 +3750,7 @@
       <c r="H105" s="11"/>
       <c r="I105" s="11"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9">
       <c r="A106" s="1">
         <v>96</v>
       </c>
@@ -3779,7 +3776,7 @@
       <c r="H106" s="11"/>
       <c r="I106" s="11"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9">
       <c r="A107" s="1">
         <v>97</v>
       </c>
@@ -3805,7 +3802,7 @@
       <c r="H107" s="11"/>
       <c r="I107" s="11"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9">
       <c r="A108" s="1">
         <v>98</v>
       </c>
@@ -3831,7 +3828,7 @@
       <c r="H108" s="11"/>
       <c r="I108" s="11"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9">
       <c r="A109" s="1">
         <v>99</v>
       </c>
@@ -3857,7 +3854,7 @@
       <c r="H109" s="11"/>
       <c r="I109" s="11"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9">
       <c r="A110" s="1">
         <v>100</v>
       </c>
@@ -3883,7 +3880,7 @@
       <c r="H110" s="11"/>
       <c r="I110" s="11"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9">
       <c r="A111" s="1">
         <v>101</v>
       </c>
@@ -3909,7 +3906,7 @@
       <c r="H111" s="11"/>
       <c r="I111" s="11"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9">
       <c r="A112" s="1">
         <v>102</v>
       </c>
@@ -3935,7 +3932,7 @@
       <c r="H112" s="11"/>
       <c r="I112" s="11"/>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9">
       <c r="A113" s="1">
         <v>103</v>
       </c>
@@ -3961,7 +3958,7 @@
       <c r="H113" s="11"/>
       <c r="I113" s="11"/>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9">
       <c r="A114" s="1">
         <v>104</v>
       </c>
@@ -3987,7 +3984,7 @@
       <c r="H114" s="11"/>
       <c r="I114" s="11"/>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9">
       <c r="A115" s="1">
         <v>105</v>
       </c>
@@ -4013,7 +4010,7 @@
       <c r="H115" s="11"/>
       <c r="I115" s="11"/>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9">
       <c r="A116" s="1">
         <v>106</v>
       </c>
@@ -4039,7 +4036,7 @@
       <c r="H116" s="11"/>
       <c r="I116" s="11"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9">
       <c r="A117" s="1">
         <v>107</v>
       </c>
@@ -4065,7 +4062,7 @@
       <c r="H117" s="11"/>
       <c r="I117" s="11"/>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9">
       <c r="A118" s="1">
         <v>108</v>
       </c>
@@ -4091,7 +4088,7 @@
       <c r="H118" s="11"/>
       <c r="I118" s="11"/>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9">
       <c r="A119" s="1">
         <v>109</v>
       </c>
@@ -4117,7 +4114,7 @@
       <c r="H119" s="11"/>
       <c r="I119" s="11"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9">
       <c r="A120" s="1">
         <v>110</v>
       </c>
@@ -4143,7 +4140,7 @@
       <c r="H120" s="11"/>
       <c r="I120" s="11"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9">
       <c r="A121" s="1">
         <v>111</v>
       </c>
@@ -4169,7 +4166,7 @@
       <c r="H121" s="11"/>
       <c r="I121" s="11"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9">
       <c r="A122" s="1">
         <v>112</v>
       </c>
@@ -4195,7 +4192,7 @@
       <c r="H122" s="11"/>
       <c r="I122" s="11"/>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9">
       <c r="A123" s="1">
         <v>113</v>
       </c>
@@ -4221,7 +4218,7 @@
       <c r="H123" s="11"/>
       <c r="I123" s="11"/>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9">
       <c r="A124" s="1">
         <v>114</v>
       </c>
@@ -4247,7 +4244,7 @@
       <c r="H124" s="11"/>
       <c r="I124" s="11"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9">
       <c r="A125" s="1">
         <v>115</v>
       </c>
@@ -4273,7 +4270,7 @@
       <c r="H125" s="11"/>
       <c r="I125" s="11"/>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9">
       <c r="A126" s="1">
         <v>116</v>
       </c>
@@ -4299,7 +4296,7 @@
       <c r="H126" s="11"/>
       <c r="I126" s="11"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9">
       <c r="A127" s="1">
         <v>117</v>
       </c>
@@ -4325,7 +4322,7 @@
       <c r="H127" s="11"/>
       <c r="I127" s="11"/>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9">
       <c r="A128" s="1">
         <v>118</v>
       </c>
@@ -4351,7 +4348,7 @@
       <c r="H128" s="11"/>
       <c r="I128" s="11"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9">
       <c r="A129" s="1">
         <v>119</v>
       </c>
@@ -4377,7 +4374,7 @@
       <c r="H129" s="11"/>
       <c r="I129" s="11"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9">
       <c r="A130" s="1">
         <v>120</v>
       </c>
@@ -4403,7 +4400,7 @@
       <c r="H130" s="11"/>
       <c r="I130" s="11"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9">
       <c r="A131" s="1">
         <v>121</v>
       </c>
@@ -4429,7 +4426,7 @@
       <c r="H131" s="11"/>
       <c r="I131" s="11"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9">
       <c r="A132" s="1">
         <v>122</v>
       </c>
@@ -4455,7 +4452,7 @@
       <c r="H132" s="11"/>
       <c r="I132" s="11"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9">
       <c r="A133" s="1">
         <v>123</v>
       </c>
@@ -4481,7 +4478,7 @@
       <c r="H133" s="11"/>
       <c r="I133" s="11"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9">
       <c r="A134" s="1">
         <v>124</v>
       </c>
@@ -4507,7 +4504,7 @@
       <c r="H134" s="11"/>
       <c r="I134" s="11"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9">
       <c r="A135" s="1">
         <v>125</v>
       </c>
@@ -4533,7 +4530,7 @@
       <c r="H135" s="11"/>
       <c r="I135" s="11"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9">
       <c r="A136" s="1">
         <v>126</v>
       </c>
@@ -4559,7 +4556,7 @@
       <c r="H136" s="11"/>
       <c r="I136" s="11"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9">
       <c r="A137" s="1">
         <v>127</v>
       </c>
@@ -4585,7 +4582,7 @@
       <c r="H137" s="11"/>
       <c r="I137" s="11"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9">
       <c r="A138" s="1">
         <v>128</v>
       </c>
@@ -4611,7 +4608,7 @@
       <c r="H138" s="11"/>
       <c r="I138" s="11"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9">
       <c r="A139" s="1">
         <v>129</v>
       </c>
@@ -4637,7 +4634,7 @@
       <c r="H139" s="11"/>
       <c r="I139" s="11"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9">
       <c r="A140" s="1">
         <v>130</v>
       </c>
@@ -4663,7 +4660,7 @@
       <c r="H140" s="11"/>
       <c r="I140" s="11"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9">
       <c r="A141" s="1">
         <v>131</v>
       </c>
@@ -4689,7 +4686,7 @@
       <c r="H141" s="11"/>
       <c r="I141" s="11"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9">
       <c r="A142" s="1">
         <v>132</v>
       </c>
@@ -4715,7 +4712,7 @@
       <c r="H142" s="11"/>
       <c r="I142" s="11"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9">
       <c r="A143" s="1">
         <v>133</v>
       </c>
@@ -4741,7 +4738,7 @@
       <c r="H143" s="11"/>
       <c r="I143" s="11"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9">
       <c r="A144" s="1">
         <v>134</v>
       </c>
@@ -4767,7 +4764,7 @@
       <c r="H144" s="11"/>
       <c r="I144" s="11"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9">
       <c r="A145" s="1">
         <v>135</v>
       </c>
@@ -4793,7 +4790,7 @@
       <c r="H145" s="11"/>
       <c r="I145" s="11"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9">
       <c r="A146" s="1">
         <v>136</v>
       </c>
@@ -4819,7 +4816,7 @@
       <c r="H146" s="11"/>
       <c r="I146" s="11"/>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9">
       <c r="A147" s="1">
         <v>137</v>
       </c>
@@ -4845,7 +4842,7 @@
       <c r="H147" s="11"/>
       <c r="I147" s="11"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9">
       <c r="A148" s="1">
         <v>138</v>
       </c>
@@ -4871,7 +4868,7 @@
       <c r="H148" s="11"/>
       <c r="I148" s="11"/>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9">
       <c r="A149" s="1">
         <v>139</v>
       </c>
@@ -4897,7 +4894,7 @@
       <c r="H149" s="11"/>
       <c r="I149" s="11"/>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9">
       <c r="A150" s="1">
         <v>140</v>
       </c>
@@ -4923,7 +4920,7 @@
       <c r="H150" s="11"/>
       <c r="I150" s="11"/>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9">
       <c r="A151" s="1">
         <v>141</v>
       </c>
@@ -4949,7 +4946,7 @@
       <c r="H151" s="11"/>
       <c r="I151" s="11"/>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9">
       <c r="A152" s="1">
         <v>142</v>
       </c>
@@ -4975,7 +4972,7 @@
       <c r="H152" s="11"/>
       <c r="I152" s="11"/>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9">
       <c r="A153" s="1">
         <v>143</v>
       </c>
@@ -5001,7 +4998,7 @@
       <c r="H153" s="11"/>
       <c r="I153" s="11"/>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9">
       <c r="A154" s="1">
         <v>144</v>
       </c>
@@ -5027,7 +5024,7 @@
       <c r="H154" s="11"/>
       <c r="I154" s="11"/>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9">
       <c r="A155" s="1">
         <v>145</v>
       </c>
@@ -5053,7 +5050,7 @@
       <c r="H155" s="11"/>
       <c r="I155" s="11"/>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9">
       <c r="A156" s="1">
         <v>146</v>
       </c>
@@ -5079,7 +5076,7 @@
       <c r="H156" s="11"/>
       <c r="I156" s="11"/>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9">
       <c r="A157" s="1">
         <v>147</v>
       </c>
@@ -5105,7 +5102,7 @@
       <c r="H157" s="11"/>
       <c r="I157" s="11"/>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9">
       <c r="A158" s="1">
         <v>148</v>
       </c>
@@ -5131,7 +5128,7 @@
       <c r="H158" s="11"/>
       <c r="I158" s="11"/>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9">
       <c r="A159" s="1">
         <v>149</v>
       </c>
@@ -5157,7 +5154,7 @@
       <c r="H159" s="11"/>
       <c r="I159" s="11"/>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9">
       <c r="A160" s="1">
         <v>150</v>
       </c>
@@ -5183,7 +5180,7 @@
       <c r="H160" s="11"/>
       <c r="I160" s="11"/>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9">
       <c r="A161" s="1">
         <v>151</v>
       </c>
@@ -5209,7 +5206,7 @@
       <c r="H161" s="11"/>
       <c r="I161" s="11"/>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9">
       <c r="A162" s="1">
         <v>152</v>
       </c>
@@ -5235,7 +5232,7 @@
       <c r="H162" s="11"/>
       <c r="I162" s="11"/>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9">
       <c r="A163" s="1">
         <v>153</v>
       </c>
@@ -5261,7 +5258,7 @@
       <c r="H163" s="11"/>
       <c r="I163" s="11"/>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9">
       <c r="A164" s="1">
         <v>154</v>
       </c>
@@ -5287,7 +5284,7 @@
       <c r="H164" s="11"/>
       <c r="I164" s="11"/>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9">
       <c r="A165" s="1">
         <v>155</v>
       </c>
@@ -5313,7 +5310,7 @@
       <c r="H165" s="11"/>
       <c r="I165" s="11"/>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9">
       <c r="A166" s="1">
         <v>156</v>
       </c>
@@ -5339,7 +5336,7 @@
       <c r="H166" s="11"/>
       <c r="I166" s="11"/>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9">
       <c r="A167" s="1">
         <v>157</v>
       </c>
@@ -5365,7 +5362,7 @@
       <c r="H167" s="11"/>
       <c r="I167" s="11"/>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9">
       <c r="A168" s="1">
         <v>158</v>
       </c>
@@ -5391,7 +5388,7 @@
       <c r="H168" s="11"/>
       <c r="I168" s="11"/>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9">
       <c r="A169" s="1">
         <v>159</v>
       </c>
@@ -5417,7 +5414,7 @@
       <c r="H169" s="11"/>
       <c r="I169" s="11"/>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9">
       <c r="A170" s="1">
         <v>160</v>
       </c>
@@ -5443,7 +5440,7 @@
       <c r="H170" s="11"/>
       <c r="I170" s="11"/>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9">
       <c r="A171" s="1">
         <v>161</v>
       </c>
@@ -5469,7 +5466,7 @@
       <c r="H171" s="11"/>
       <c r="I171" s="11"/>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9">
       <c r="A172" s="1">
         <v>162</v>
       </c>
@@ -5495,7 +5492,7 @@
       <c r="H172" s="11"/>
       <c r="I172" s="11"/>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9">
       <c r="A173" s="1">
         <v>163</v>
       </c>
@@ -5521,7 +5518,7 @@
       <c r="H173" s="11"/>
       <c r="I173" s="11"/>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9">
       <c r="A174" s="1">
         <v>164</v>
       </c>
@@ -5547,7 +5544,7 @@
       <c r="H174" s="11"/>
       <c r="I174" s="11"/>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9">
       <c r="A175" s="1">
         <v>165</v>
       </c>
@@ -5573,7 +5570,7 @@
       <c r="H175" s="11"/>
       <c r="I175" s="11"/>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9">
       <c r="A176" s="1">
         <v>166</v>
       </c>
@@ -5599,7 +5596,7 @@
       <c r="H176" s="11"/>
       <c r="I176" s="11"/>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9">
       <c r="A177" s="1">
         <v>167</v>
       </c>
@@ -5625,7 +5622,7 @@
       <c r="H177" s="11"/>
       <c r="I177" s="11"/>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9">
       <c r="A178" s="1">
         <v>168</v>
       </c>
@@ -5651,7 +5648,7 @@
       <c r="H178" s="11"/>
       <c r="I178" s="11"/>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9">
       <c r="A179" s="1">
         <v>169</v>
       </c>
@@ -5677,7 +5674,7 @@
       <c r="H179" s="11"/>
       <c r="I179" s="11"/>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9">
       <c r="A180" s="1">
         <v>170</v>
       </c>
@@ -5703,7 +5700,7 @@
       <c r="H180" s="11"/>
       <c r="I180" s="11"/>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9">
       <c r="A181" s="1">
         <v>171</v>
       </c>
@@ -5729,7 +5726,7 @@
       <c r="H181" s="11"/>
       <c r="I181" s="11"/>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9">
       <c r="A182" s="1">
         <v>172</v>
       </c>
@@ -5755,7 +5752,7 @@
       <c r="H182" s="11"/>
       <c r="I182" s="11"/>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9">
       <c r="A183" s="1">
         <v>173</v>
       </c>
@@ -5781,7 +5778,7 @@
       <c r="H183" s="11"/>
       <c r="I183" s="11"/>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9">
       <c r="A184" s="1">
         <v>174</v>
       </c>
@@ -5807,7 +5804,7 @@
       <c r="H184" s="11"/>
       <c r="I184" s="11"/>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9">
       <c r="A185" s="1">
         <v>175</v>
       </c>
@@ -5833,7 +5830,7 @@
       <c r="H185" s="11"/>
       <c r="I185" s="11"/>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9">
       <c r="A186" s="1">
         <v>176</v>
       </c>
@@ -5859,7 +5856,7 @@
       <c r="H186" s="11"/>
       <c r="I186" s="11"/>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9">
       <c r="A187" s="1">
         <v>177</v>
       </c>
@@ -5885,7 +5882,7 @@
       <c r="H187" s="11"/>
       <c r="I187" s="11"/>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9">
       <c r="A188" s="1">
         <v>178</v>
       </c>
@@ -5911,7 +5908,7 @@
       <c r="H188" s="11"/>
       <c r="I188" s="11"/>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9">
       <c r="A189" s="1">
         <v>179</v>
       </c>
@@ -5937,7 +5934,7 @@
       <c r="H189" s="11"/>
       <c r="I189" s="11"/>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9">
       <c r="A190" s="1">
         <v>180</v>
       </c>
@@ -5963,7 +5960,7 @@
       <c r="H190" s="11"/>
       <c r="I190" s="11"/>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9">
       <c r="A191" s="1">
         <v>181</v>
       </c>
@@ -5989,7 +5986,7 @@
       <c r="H191" s="11"/>
       <c r="I191" s="11"/>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9">
       <c r="A192" s="1">
         <v>182</v>
       </c>
@@ -6015,7 +6012,7 @@
       <c r="H192" s="11"/>
       <c r="I192" s="11"/>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9">
       <c r="A193" s="1">
         <v>183</v>
       </c>
@@ -6041,7 +6038,7 @@
       <c r="H193" s="11"/>
       <c r="I193" s="11"/>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9">
       <c r="A194" s="1">
         <v>184</v>
       </c>
@@ -6067,7 +6064,7 @@
       <c r="H194" s="11"/>
       <c r="I194" s="11"/>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9">
       <c r="A195" s="1">
         <v>185</v>
       </c>
@@ -6093,7 +6090,7 @@
       <c r="H195" s="11"/>
       <c r="I195" s="11"/>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9">
       <c r="A196" s="1">
         <v>186</v>
       </c>
@@ -6119,7 +6116,7 @@
       <c r="H196" s="11"/>
       <c r="I196" s="11"/>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9">
       <c r="A197" s="1">
         <v>187</v>
       </c>
@@ -6145,7 +6142,7 @@
       <c r="H197" s="11"/>
       <c r="I197" s="11"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9">
       <c r="A198" s="1">
         <v>188</v>
       </c>
@@ -6171,7 +6168,7 @@
       <c r="H198" s="11"/>
       <c r="I198" s="11"/>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9">
       <c r="A199" s="1">
         <v>189</v>
       </c>
@@ -6197,7 +6194,7 @@
       <c r="H199" s="11"/>
       <c r="I199" s="11"/>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9">
       <c r="A200" s="1">
         <v>190</v>
       </c>
@@ -6223,7 +6220,7 @@
       <c r="H200" s="11"/>
       <c r="I200" s="11"/>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9">
       <c r="A201" s="1">
         <v>191</v>
       </c>
@@ -6249,7 +6246,7 @@
       <c r="H201" s="11"/>
       <c r="I201" s="11"/>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9">
       <c r="A202" s="1">
         <v>192</v>
       </c>
@@ -6275,7 +6272,7 @@
       <c r="H202" s="11"/>
       <c r="I202" s="11"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9">
       <c r="A203" s="1">
         <v>193</v>
       </c>
@@ -6301,7 +6298,7 @@
       <c r="H203" s="11"/>
       <c r="I203" s="11"/>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9">
       <c r="A204" s="1">
         <v>194</v>
       </c>
@@ -6327,7 +6324,7 @@
       <c r="H204" s="11"/>
       <c r="I204" s="11"/>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9">
       <c r="A205" s="1">
         <v>195</v>
       </c>
@@ -6353,7 +6350,7 @@
       <c r="H205" s="11"/>
       <c r="I205" s="11"/>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9">
       <c r="A206" s="1">
         <v>196</v>
       </c>
@@ -6379,7 +6376,7 @@
       <c r="H206" s="11"/>
       <c r="I206" s="11"/>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9">
       <c r="A207" s="1">
         <v>197</v>
       </c>
@@ -6405,7 +6402,7 @@
       <c r="H207" s="11"/>
       <c r="I207" s="11"/>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9">
       <c r="A208" s="1">
         <v>198</v>
       </c>
@@ -6431,7 +6428,7 @@
       <c r="H208" s="11"/>
       <c r="I208" s="11"/>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9">
       <c r="A209" s="1">
         <v>199</v>
       </c>
@@ -6457,7 +6454,7 @@
       <c r="H209" s="11"/>
       <c r="I209" s="11"/>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:9">
       <c r="A210" s="1">
         <v>200</v>
       </c>
@@ -6483,7 +6480,7 @@
       <c r="H210" s="11"/>
       <c r="I210" s="11"/>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:9">
       <c r="A211" s="1">
         <v>201</v>
       </c>
@@ -6509,7 +6506,7 @@
       <c r="H211" s="11"/>
       <c r="I211" s="11"/>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:9">
       <c r="A212" s="1">
         <v>202</v>
       </c>
@@ -6535,7 +6532,7 @@
       <c r="H212" s="11"/>
       <c r="I212" s="11"/>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9">
       <c r="A213" s="1">
         <v>203</v>
       </c>
@@ -6561,7 +6558,7 @@
       <c r="H213" s="11"/>
       <c r="I213" s="11"/>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:9">
       <c r="A214" s="1">
         <v>204</v>
       </c>
@@ -6587,7 +6584,7 @@
       <c r="H214" s="11"/>
       <c r="I214" s="11"/>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:9">
       <c r="A215" s="1">
         <v>205</v>
       </c>
@@ -6613,7 +6610,7 @@
       <c r="H215" s="11"/>
       <c r="I215" s="11"/>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9">
       <c r="A216" s="1">
         <v>206</v>
       </c>
@@ -6639,7 +6636,7 @@
       <c r="H216" s="11"/>
       <c r="I216" s="11"/>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9">
       <c r="A217" s="1">
         <v>207</v>
       </c>
@@ -6665,7 +6662,7 @@
       <c r="H217" s="11"/>
       <c r="I217" s="11"/>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9">
       <c r="A218" s="1">
         <v>208</v>
       </c>
@@ -6691,7 +6688,7 @@
       <c r="H218" s="11"/>
       <c r="I218" s="11"/>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:9">
       <c r="A219" s="1">
         <v>209</v>
       </c>
@@ -6717,7 +6714,7 @@
       <c r="H219" s="11"/>
       <c r="I219" s="11"/>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:9">
       <c r="A220" s="1">
         <v>210</v>
       </c>
@@ -6743,7 +6740,7 @@
       <c r="H220" s="11"/>
       <c r="I220" s="11"/>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:9">
       <c r="A221" s="1">
         <v>211</v>
       </c>
@@ -6769,7 +6766,7 @@
       <c r="H221" s="11"/>
       <c r="I221" s="11"/>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:9">
       <c r="A222" s="1">
         <v>212</v>
       </c>
@@ -6795,7 +6792,7 @@
       <c r="H222" s="11"/>
       <c r="I222" s="11"/>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:9">
       <c r="A223" s="1">
         <v>213</v>
       </c>
@@ -6821,7 +6818,7 @@
       <c r="H223" s="11"/>
       <c r="I223" s="11"/>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:9">
       <c r="A224" s="1">
         <v>214</v>
       </c>
@@ -6847,7 +6844,7 @@
       <c r="H224" s="11"/>
       <c r="I224" s="11"/>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9">
       <c r="A225" s="1">
         <v>215</v>
       </c>
@@ -6873,7 +6870,7 @@
       <c r="H225" s="11"/>
       <c r="I225" s="11"/>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9">
       <c r="A226" s="1">
         <v>216</v>
       </c>
@@ -6899,7 +6896,7 @@
       <c r="H226" s="11"/>
       <c r="I226" s="11"/>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9">
       <c r="A227" s="1">
         <v>217</v>
       </c>
@@ -6925,7 +6922,7 @@
       <c r="H227" s="11"/>
       <c r="I227" s="11"/>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9">
       <c r="A228" s="1">
         <v>218</v>
       </c>
@@ -6951,7 +6948,7 @@
       <c r="H228" s="11"/>
       <c r="I228" s="11"/>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9">
       <c r="A229" s="1">
         <v>219</v>
       </c>
@@ -6977,7 +6974,7 @@
       <c r="H229" s="11"/>
       <c r="I229" s="11"/>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9">
       <c r="A230" s="1">
         <v>220</v>
       </c>
@@ -7003,7 +7000,7 @@
       <c r="H230" s="11"/>
       <c r="I230" s="11"/>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9">
       <c r="A231" s="1">
         <v>221</v>
       </c>
@@ -7029,7 +7026,7 @@
       <c r="H231" s="11"/>
       <c r="I231" s="11"/>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:9">
       <c r="A232" s="1">
         <v>222</v>
       </c>
@@ -7055,7 +7052,7 @@
       <c r="H232" s="11"/>
       <c r="I232" s="11"/>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:9">
       <c r="A233" s="1">
         <v>223</v>
       </c>
@@ -7081,7 +7078,7 @@
       <c r="H233" s="11"/>
       <c r="I233" s="11"/>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9">
       <c r="A234" s="1">
         <v>224</v>
       </c>
@@ -7107,7 +7104,7 @@
       <c r="H234" s="11"/>
       <c r="I234" s="11"/>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9">
       <c r="A235" s="1">
         <v>225</v>
       </c>
@@ -7133,7 +7130,7 @@
       <c r="H235" s="11"/>
       <c r="I235" s="11"/>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9">
       <c r="A236" s="1">
         <v>226</v>
       </c>
@@ -7159,7 +7156,7 @@
       <c r="H236" s="11"/>
       <c r="I236" s="11"/>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:9">
       <c r="A237" s="1">
         <v>227</v>
       </c>
@@ -7185,7 +7182,7 @@
       <c r="H237" s="11"/>
       <c r="I237" s="11"/>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:9">
       <c r="A238" s="1">
         <v>228</v>
       </c>
@@ -7211,7 +7208,7 @@
       <c r="H238" s="11"/>
       <c r="I238" s="11"/>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:9">
       <c r="A239" s="1">
         <v>229</v>
       </c>
@@ -7237,7 +7234,7 @@
       <c r="H239" s="11"/>
       <c r="I239" s="11"/>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:9">
       <c r="A240" s="1">
         <v>230</v>
       </c>
@@ -7263,7 +7260,7 @@
       <c r="H240" s="11"/>
       <c r="I240" s="11"/>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:9">
       <c r="A241" s="1">
         <v>231</v>
       </c>
@@ -7289,7 +7286,7 @@
       <c r="H241" s="11"/>
       <c r="I241" s="11"/>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:9">
       <c r="A242" s="1">
         <v>232</v>
       </c>
@@ -7315,7 +7312,7 @@
       <c r="H242" s="11"/>
       <c r="I242" s="11"/>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:9">
       <c r="A243" s="1">
         <v>233</v>
       </c>
@@ -7341,7 +7338,7 @@
       <c r="H243" s="11"/>
       <c r="I243" s="11"/>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9">
       <c r="A244" s="1">
         <v>234</v>
       </c>
@@ -7367,7 +7364,7 @@
       <c r="H244" s="11"/>
       <c r="I244" s="11"/>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:9">
       <c r="A245" s="1">
         <v>235</v>
       </c>
@@ -7393,7 +7390,7 @@
       <c r="H245" s="11"/>
       <c r="I245" s="11"/>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:9">
       <c r="A246" s="1">
         <v>236</v>
       </c>
@@ -7419,7 +7416,7 @@
       <c r="H246" s="11"/>
       <c r="I246" s="11"/>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:9">
       <c r="A247" s="1">
         <v>237</v>
       </c>
@@ -7445,7 +7442,7 @@
       <c r="H247" s="11"/>
       <c r="I247" s="11"/>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9">
       <c r="A248" s="1">
         <v>238</v>
       </c>
@@ -7471,7 +7468,7 @@
       <c r="H248" s="11"/>
       <c r="I248" s="11"/>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9">
       <c r="A249" s="1">
         <v>239</v>
       </c>
@@ -7497,7 +7494,7 @@
       <c r="H249" s="11"/>
       <c r="I249" s="11"/>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9">
       <c r="A250" s="1">
         <v>240</v>
       </c>
@@ -7523,7 +7520,7 @@
       <c r="H250" s="11"/>
       <c r="I250" s="11"/>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9">
       <c r="A251" s="1">
         <v>241</v>
       </c>
@@ -7549,7 +7546,7 @@
       <c r="H251" s="11"/>
       <c r="I251" s="11"/>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9">
       <c r="A252" s="1">
         <v>242</v>
       </c>
@@ -7575,7 +7572,7 @@
       <c r="H252" s="11"/>
       <c r="I252" s="11"/>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9">
       <c r="A253" s="1">
         <v>243</v>
       </c>
@@ -7601,7 +7598,7 @@
       <c r="H253" s="11"/>
       <c r="I253" s="11"/>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9">
       <c r="A254" s="1">
         <v>244</v>
       </c>
@@ -7627,7 +7624,7 @@
       <c r="H254" s="11"/>
       <c r="I254" s="11"/>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9">
       <c r="A255" s="1">
         <v>245</v>
       </c>
@@ -7653,7 +7650,7 @@
       <c r="H255" s="11"/>
       <c r="I255" s="11"/>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9">
       <c r="A256" s="1">
         <v>246</v>
       </c>
@@ -7679,7 +7676,7 @@
       <c r="H256" s="11"/>
       <c r="I256" s="11"/>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9">
       <c r="A257" s="1">
         <v>247</v>
       </c>
@@ -7705,7 +7702,7 @@
       <c r="H257" s="11"/>
       <c r="I257" s="11"/>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9">
       <c r="A258" s="1">
         <v>248</v>
       </c>
@@ -7731,7 +7728,7 @@
       <c r="H258" s="11"/>
       <c r="I258" s="11"/>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:9">
       <c r="A259" s="1">
         <v>249</v>
       </c>
@@ -7757,7 +7754,7 @@
       <c r="H259" s="11"/>
       <c r="I259" s="11"/>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:9">
       <c r="A260" s="1">
         <v>250</v>
       </c>
@@ -7783,7 +7780,7 @@
       <c r="H260" s="11"/>
       <c r="I260" s="11"/>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:9">
       <c r="A261" s="1">
         <v>251</v>
       </c>
@@ -7809,7 +7806,7 @@
       <c r="H261" s="11"/>
       <c r="I261" s="11"/>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:9">
       <c r="A262" s="1">
         <v>252</v>
       </c>
@@ -7835,7 +7832,7 @@
       <c r="H262" s="11"/>
       <c r="I262" s="11"/>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:9">
       <c r="A263" s="1">
         <v>253</v>
       </c>
@@ -7861,7 +7858,7 @@
       <c r="H263" s="11"/>
       <c r="I263" s="11"/>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:9">
       <c r="A264" s="1">
         <v>254</v>
       </c>
@@ -7887,7 +7884,7 @@
       <c r="H264" s="11"/>
       <c r="I264" s="11"/>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9">
       <c r="A265" s="1">
         <v>255</v>
       </c>
@@ -7913,7 +7910,7 @@
       <c r="H265" s="11"/>
       <c r="I265" s="11"/>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:9">
       <c r="A266" s="1">
         <v>256</v>
       </c>
@@ -7939,7 +7936,7 @@
       <c r="H266" s="11"/>
       <c r="I266" s="11"/>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:9">
       <c r="A267" s="1">
         <v>257</v>
       </c>
@@ -7965,7 +7962,7 @@
       <c r="H267" s="11"/>
       <c r="I267" s="11"/>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9">
       <c r="A268" s="1">
         <v>258</v>
       </c>
@@ -7991,7 +7988,7 @@
       <c r="H268" s="11"/>
       <c r="I268" s="11"/>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:9">
       <c r="A269" s="1">
         <v>259</v>
       </c>
@@ -8017,7 +8014,7 @@
       <c r="H269" s="11"/>
       <c r="I269" s="11"/>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:9">
       <c r="A270" s="1">
         <v>260</v>
       </c>
@@ -8043,7 +8040,7 @@
       <c r="H270" s="11"/>
       <c r="I270" s="11"/>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:9">
       <c r="A271" s="1">
         <v>261</v>
       </c>
@@ -8069,7 +8066,7 @@
       <c r="H271" s="11"/>
       <c r="I271" s="11"/>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:9">
       <c r="A272" s="1">
         <v>262</v>
       </c>
@@ -8095,7 +8092,7 @@
       <c r="H272" s="11"/>
       <c r="I272" s="11"/>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:10">
       <c r="A273" s="1">
         <v>263</v>
       </c>
@@ -8121,7 +8118,7 @@
       <c r="H273" s="11"/>
       <c r="I273" s="11"/>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:10">
       <c r="A274" s="1">
         <v>264</v>
       </c>
@@ -8147,7 +8144,7 @@
       <c r="H274" s="11"/>
       <c r="I274" s="11"/>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:10">
       <c r="A275" s="1">
         <v>265</v>
       </c>
@@ -8173,7 +8170,7 @@
       <c r="H275" s="11"/>
       <c r="I275" s="11"/>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:10">
       <c r="A276" s="1">
         <v>266</v>
       </c>
@@ -8199,7 +8196,7 @@
       <c r="H276" s="11"/>
       <c r="I276" s="11"/>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:10">
       <c r="A277" s="1">
         <v>267</v>
       </c>
@@ -8225,7 +8222,7 @@
       <c r="H277" s="11"/>
       <c r="I277" s="11"/>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:10">
       <c r="A278" s="1">
         <v>268</v>
       </c>
@@ -8251,7 +8248,7 @@
       <c r="H278" s="11"/>
       <c r="I278" s="11"/>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:10">
       <c r="A279" s="1">
         <v>269</v>
       </c>
@@ -8277,7 +8274,7 @@
       <c r="H279" s="11"/>
       <c r="I279" s="11"/>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:10">
       <c r="A280" s="1">
         <v>270</v>
       </c>
@@ -8303,7 +8300,7 @@
       <c r="H280" s="11"/>
       <c r="I280" s="11"/>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:10">
       <c r="A281" s="1">
         <v>271</v>
       </c>
@@ -8329,7 +8326,7 @@
       <c r="H281" s="11"/>
       <c r="I281" s="11"/>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:10">
       <c r="A282" s="1">
         <v>272</v>
       </c>
@@ -8355,7 +8352,7 @@
       <c r="H282" s="11"/>
       <c r="I282" s="11"/>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:10">
       <c r="A283" s="1">
         <v>273</v>
       </c>
@@ -8381,7 +8378,7 @@
       <c r="H283" s="11"/>
       <c r="I283" s="11"/>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:10">
       <c r="A284" s="1">
         <v>274</v>
       </c>
@@ -8407,7 +8404,7 @@
       <c r="H284" s="11"/>
       <c r="I284" s="11"/>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:10">
       <c r="A285" s="1">
         <v>275</v>
       </c>
@@ -8433,7 +8430,7 @@
       <c r="H285" s="11"/>
       <c r="I285" s="11"/>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:10">
       <c r="A286" s="1">
         <v>276</v>
       </c>
@@ -8466,7 +8463,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:10">
       <c r="A287" s="1">
         <v>277</v>
       </c>
@@ -8499,7 +8496,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:10">
       <c r="A288" s="1">
         <v>278</v>
       </c>
@@ -8532,7 +8529,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:10">
       <c r="A289" s="1">
         <v>279</v>
       </c>
@@ -8565,7 +8562,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:10">
       <c r="A290" s="1">
         <v>280</v>
       </c>
@@ -8598,7 +8595,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:10">
       <c r="A291" s="1">
         <v>281</v>
       </c>
@@ -8631,7 +8628,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:10">
       <c r="A292" s="1">
         <v>282</v>
       </c>
@@ -8664,7 +8661,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:10">
       <c r="A293" s="1">
         <v>283</v>
       </c>
@@ -8697,7 +8694,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:10">
       <c r="A294" s="1">
         <v>284</v>
       </c>
@@ -8730,7 +8727,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:10">
       <c r="A295" s="1">
         <v>285</v>
       </c>
@@ -8763,7 +8760,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:10">
       <c r="A296" s="1">
         <v>286</v>
       </c>
@@ -8796,7 +8793,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:10">
       <c r="A297" s="1">
         <v>287</v>
       </c>
@@ -8829,7 +8826,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:10">
       <c r="A298" s="1">
         <v>288</v>
       </c>
@@ -8862,7 +8859,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:10">
       <c r="A299" s="1">
         <v>289</v>
       </c>
@@ -8895,7 +8892,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:10">
       <c r="A300" s="1">
         <v>290</v>
       </c>
@@ -8928,7 +8925,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:10">
       <c r="A301" s="1">
         <v>291</v>
       </c>
@@ -8961,7 +8958,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:10">
       <c r="A302" s="1">
         <v>292</v>
       </c>
@@ -8994,7 +8991,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="303" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:10" s="1" customFormat="1">
       <c r="A303" s="1">
         <v>293</v>
       </c>
@@ -9027,7 +9024,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="304" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:10" s="1" customFormat="1">
       <c r="A304" s="1">
         <v>294</v>
       </c>
@@ -9060,7 +9057,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:10">
       <c r="A305" s="1">
         <v>295</v>
       </c>
@@ -9093,7 +9090,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:10">
       <c r="A306" s="1">
         <v>296</v>
       </c>
@@ -9126,7 +9123,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:10">
       <c r="A307" s="1">
         <v>297</v>
       </c>
@@ -9159,7 +9156,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:10">
       <c r="A308" s="1">
         <v>298</v>
       </c>
@@ -9192,7 +9189,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:10">
       <c r="A309" s="1">
         <v>298</v>
       </c>
@@ -9225,7 +9222,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:10">
       <c r="A310" s="1">
         <v>299</v>
       </c>
@@ -9258,7 +9255,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:10">
       <c r="A311" s="1">
         <v>300</v>
       </c>
@@ -9291,7 +9288,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:10">
       <c r="A312" s="1">
         <v>301</v>
       </c>
@@ -9324,7 +9321,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:10">
       <c r="A313" s="1">
         <v>302</v>
       </c>
@@ -9357,7 +9354,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:10">
       <c r="A314" s="1">
         <v>303</v>
       </c>
@@ -9390,7 +9387,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:10">
       <c r="A315" s="1">
         <v>304</v>
       </c>
@@ -9423,7 +9420,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:10">
       <c r="A316" s="1">
         <v>305</v>
       </c>
@@ -9456,7 +9453,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:10">
       <c r="A317" s="1">
         <v>306</v>
       </c>
@@ -9489,7 +9486,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:10">
       <c r="A318" s="1">
         <v>307</v>
       </c>
@@ -9522,7 +9519,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:10">
       <c r="A319" s="1">
         <v>308</v>
       </c>
@@ -9555,7 +9552,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:10">
       <c r="A320" s="1">
         <v>309</v>
       </c>
@@ -9588,7 +9585,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:10">
       <c r="A321" s="1">
         <v>310</v>
       </c>
@@ -9621,7 +9618,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:10">
       <c r="A322" s="1">
         <v>311</v>
       </c>
@@ -9654,7 +9651,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:10">
       <c r="A323" s="1">
         <v>312</v>
       </c>
@@ -9687,7 +9684,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:10">
       <c r="A324" s="1">
         <v>313</v>
       </c>
@@ -9720,7 +9717,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:10">
       <c r="A325" s="1">
         <v>314</v>
       </c>
@@ -9753,7 +9750,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:10">
       <c r="A326" s="1">
         <v>315</v>
       </c>
@@ -9786,7 +9783,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:10">
       <c r="A327" s="1">
         <v>316</v>
       </c>
@@ -9819,7 +9816,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:10">
       <c r="A328" s="1">
         <v>318</v>
       </c>
@@ -9852,7 +9849,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:10">
       <c r="A329" s="1">
         <v>319</v>
       </c>
@@ -9885,7 +9882,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:10">
       <c r="A330" s="1">
         <v>320</v>
       </c>
@@ -9918,7 +9915,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:10">
       <c r="A331" s="1">
         <v>321</v>
       </c>
@@ -9951,7 +9948,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:10">
       <c r="A332" s="1">
         <v>322</v>
       </c>
@@ -9984,7 +9981,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:10">
       <c r="A333" s="1">
         <v>323</v>
       </c>
@@ -10017,7 +10014,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:10">
       <c r="A334" s="1">
         <v>324</v>
       </c>
@@ -10050,7 +10047,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:10">
       <c r="A335" s="1">
         <v>325</v>
       </c>
@@ -10083,7 +10080,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:10">
       <c r="A336" s="1">
         <v>326</v>
       </c>
@@ -10116,7 +10113,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:10">
       <c r="A337" s="1">
         <v>327</v>
       </c>
@@ -10149,7 +10146,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:10">
       <c r="A338" s="1">
         <v>328</v>
       </c>
@@ -10182,7 +10179,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:10">
       <c r="A339" s="1">
         <v>329</v>
       </c>
@@ -10215,7 +10212,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:10">
       <c r="A340" s="1">
         <v>330</v>
       </c>
@@ -10248,7 +10245,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:10">
       <c r="A341" s="1">
         <v>331</v>
       </c>
@@ -10281,7 +10278,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:10">
       <c r="A342" s="1">
         <v>332</v>
       </c>
@@ -10314,7 +10311,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:10">
       <c r="A343" s="1">
         <v>333</v>
       </c>
@@ -10347,7 +10344,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:10">
       <c r="A344" s="1">
         <v>334</v>
       </c>
@@ -10380,7 +10377,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:10">
       <c r="A345" s="1">
         <v>335</v>
       </c>
@@ -10413,14 +10410,14 @@
         <v>23</v>
       </c>
     </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:10">
       <c r="A346" s="1">
         <v>336</v>
       </c>
       <c r="B346" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C346" s="16" t="str">
+      <c r="C346" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
@@ -10437,23 +10434,23 @@
         <v>46248.813194444447</v>
       </c>
       <c r="H346" s="11" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="I346" s="11" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="J346" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A347">
+    <row r="347" spans="1:10" ht="15">
+      <c r="A347" s="1">
         <v>337</v>
       </c>
       <c r="B347" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C347" s="16" t="str">
+      <c r="C347" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
@@ -10470,10 +10467,10 @@
         <v>46249.208333333336</v>
       </c>
       <c r="H347" s="11" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="I347" s="11" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="J347" s="1" t="s">
         <v>23</v>
@@ -10498,13 +10495,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{797F1036-D41E-43A4-9E6E-CBBB62F3CD31}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
   <cols>
-    <col min="3" max="3" width="13.33203125" customWidth="1"/>
-    <col min="4" max="4" width="12.88671875" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -10512,18 +10509,18 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C2">
         <v>245.84</v>
@@ -10532,12 +10529,12 @@
         <v>234.67</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C3">
         <v>176.6</v>
@@ -10546,12 +10543,12 @@
         <v>161.15</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C4">
         <v>174.26</v>
@@ -10560,12 +10557,12 @@
         <v>157.61000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C5">
         <v>376.96</v>
@@ -10574,12 +10571,12 @@
         <v>347.95</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C6">
         <v>399.41</v>
@@ -10588,12 +10585,12 @@
         <v>393.57</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C7">
         <v>20</v>
@@ -10602,12 +10599,12 @@
         <v>19.87</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C8">
         <v>21</v>
@@ -10616,12 +10613,12 @@
         <v>19.57</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C9">
         <v>21</v>
@@ -10630,12 +10627,12 @@
         <v>19.86</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C10">
         <v>131</v>
@@ -10644,12 +10641,12 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C11">
         <v>112</v>
@@ -10669,15 +10666,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56220E0F-EC16-4A8C-9E04-C7F8849C4B4D}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -10685,16 +10682,16 @@
         <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -10708,10 +10705,10 @@
         <v>214.99998842592322</v>
       </c>
       <c r="E2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -10725,10 +10722,10 @@
         <v>7.6381944444437977</v>
       </c>
       <c r="E3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -10742,10 +10739,10 @@
         <v>29.99998842592322</v>
       </c>
       <c r="E4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -10759,10 +10756,10 @@
         <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -10776,10 +10773,10 @@
         <v>59.99998842592322</v>
       </c>
       <c r="E6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -10793,10 +10790,10 @@
         <v>3.9999884259232203</v>
       </c>
       <c r="E7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -10811,10 +10808,10 @@
         <v>8.8881944444437977</v>
       </c>
       <c r="E8" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -10829,7 +10826,7 @@
         <v>6.1388888888905058</v>
       </c>
       <c r="E9" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -10843,25 +10840,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83DAFC4B-C207-418A-8501-0E1EC9E673B7}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -10872,7 +10869,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -10883,7 +10880,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -10894,7 +10891,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>86</v>
       </c>
@@ -10905,7 +10902,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -10916,7 +10913,7 @@
         <v>46631</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -10927,7 +10924,7 @@
         <v>48579</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -10938,7 +10935,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -10949,7 +10946,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -10960,7 +10957,7 @@
         <v>48579</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -10980,12 +10977,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11192,54 +11194,24 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
-    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1342" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17E8552E-A87F-4961-95B9-5A91E977E556}"/>
+  <xr:revisionPtr revIDLastSave="1345" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B18770FE-52D6-4DB0-A4D9-0F8E079C2577}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -429,6 +429,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -466,7 +469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -505,6 +508,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -844,8 +853,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J347" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J347" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J348" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J348" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1226,7 +1235,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
-  <dimension ref="A9:J347"/>
+  <dimension ref="A9:J348"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -10475,6 +10484,22 @@
       <c r="J347" s="1" t="s">
         <v>23</v>
       </c>
+    </row>
+    <row r="348" spans="1:10">
+      <c r="A348">
+        <v>338</v>
+      </c>
+      <c r="B348" s="13"/>
+      <c r="C348" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
+      </c>
+      <c r="D348" s="14"/>
+      <c r="E348" s="13"/>
+      <c r="F348" s="17"/>
+      <c r="G348" s="17"/>
+      <c r="H348" s="11"/>
+      <c r="I348" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10733,10 +10758,11 @@
         <v>46235</v>
       </c>
       <c r="C4" s="3">
-        <v>46264.999988425923</v>
+        <v>46260.82984953704</v>
       </c>
       <c r="D4" s="14">
-        <v>29.99998842592322</v>
+        <f>Indisp_Prog[[#This Row],[Fecha_Hora_Fin]]-Indisp_Prog[[#This Row],[Fecha_Hora_Inicio]]</f>
+        <v>25.829849537039991</v>
       </c>
       <c r="E4" t="s">
         <v>118</v>
@@ -10991,6 +11017,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100FB7AAE8C8816FD47B559A0CCF555AFF0" ma:contentTypeVersion="10" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5c9910934a78ddf693a6b708b52e9b37">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f95d585e-e7a7-414c-955d-38a47c8579bd" xmlns:ns3="33ab045e-9213-4eea-a9f2-a5b809105d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a9c61c95b4e11caed4e46447c2ca01e7" ns2:_="" ns3:_="">
     <xsd:import namespace="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
@@ -11193,25 +11228,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1345" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B18770FE-52D6-4DB0-A4D9-0F8E079C2577}"/>
+  <xr:revisionPtr revIDLastSave="1348" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F137CAFC-F283-484F-9B5E-7605E2962DC3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="123">
   <si>
     <t>ID</t>
   </si>
@@ -1254,7 +1254,7 @@
     <row r="9" spans="1:10">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -10489,13 +10489,19 @@
       <c r="A348">
         <v>338</v>
       </c>
-      <c r="B348" s="13"/>
+      <c r="B348" s="13" t="s">
+        <v>17</v>
+      </c>
       <c r="C348" s="16" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
-        <v>CET</v>
-      </c>
-      <c r="D348" s="14"/>
-      <c r="E348" s="13"/>
+        <v>CEM</v>
+      </c>
+      <c r="D348" s="14">
+        <v>70</v>
+      </c>
+      <c r="E348" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="F348" s="17"/>
       <c r="G348" s="17"/>
       <c r="H348" s="11"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1348" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F137CAFC-F283-484F-9B5E-7605E2962DC3}"/>
+  <xr:revisionPtr revIDLastSave="1351" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C79F8346-E6DF-4544-84A8-040D4FDFB56E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -429,9 +429,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
-  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -469,7 +466,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -511,9 +508,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -10502,8 +10496,12 @@
       <c r="E348" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F348" s="17"/>
-      <c r="G348" s="17"/>
+      <c r="F348" s="15">
+        <v>46262</v>
+      </c>
+      <c r="G348" s="15">
+        <v>46250.208333333336</v>
+      </c>
       <c r="H348" s="11"/>
       <c r="I348" s="11"/>
     </row>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1351" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C79F8346-E6DF-4544-84A8-040D4FDFB56E}"/>
+  <xr:revisionPtr revIDLastSave="1352" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFBBCE50-D8CA-4261-A51C-FBF9AB913003}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -10497,7 +10497,7 @@
         <v>11</v>
       </c>
       <c r="F348" s="15">
-        <v>46262</v>
+        <v>46262.939583333333</v>
       </c>
       <c r="G348" s="15">
         <v>46250.208333333336</v>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1352" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFBBCE50-D8CA-4261-A51C-FBF9AB913003}"/>
+  <xr:revisionPtr revIDLastSave="1354" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{597C9992-2867-470C-B338-EFABDF6C8F19}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="124">
   <si>
     <t>ID</t>
   </si>
@@ -384,6 +384,9 @@
   </si>
   <si>
     <t>Se realiza desacople TV para iniciar proceso de calentamiento uniforme.</t>
+  </si>
+  <si>
+    <t>Al DP filtrso succión bba LAC10/30</t>
   </si>
   <si>
     <t>P_Max_Bruta</t>
@@ -10500,9 +10503,11 @@
         <v>46262.939583333333</v>
       </c>
       <c r="G348" s="15">
-        <v>46250.208333333336</v>
-      </c>
-      <c r="H348" s="11"/>
+        <v>46250.243750000001</v>
+      </c>
+      <c r="H348" s="11" t="s">
+        <v>110</v>
+      </c>
       <c r="I348" s="11"/>
     </row>
   </sheetData>
@@ -10538,10 +10543,10 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -10549,7 +10554,7 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C2">
         <v>245.84</v>
@@ -10563,7 +10568,7 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C3">
         <v>176.6</v>
@@ -10577,7 +10582,7 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C4">
         <v>174.26</v>
@@ -10591,7 +10596,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C5">
         <v>376.96</v>
@@ -10605,7 +10610,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C6">
         <v>399.41</v>
@@ -10619,7 +10624,7 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C7">
         <v>20</v>
@@ -10633,7 +10638,7 @@
         <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C8">
         <v>21</v>
@@ -10647,7 +10652,7 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C9">
         <v>21</v>
@@ -10661,7 +10666,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C10">
         <v>131</v>
@@ -10675,7 +10680,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C11">
         <v>112</v>
@@ -10711,10 +10716,10 @@
         <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E1" t="s">
         <v>7</v>
@@ -10734,7 +10739,7 @@
         <v>214.99998842592322</v>
       </c>
       <c r="E2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -10751,7 +10756,7 @@
         <v>7.6381944444437977</v>
       </c>
       <c r="E3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -10769,7 +10774,7 @@
         <v>25.829849537039991</v>
       </c>
       <c r="E4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -10786,7 +10791,7 @@
         <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -10803,7 +10808,7 @@
         <v>59.99998842592322</v>
       </c>
       <c r="E6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -10820,7 +10825,7 @@
         <v>3.9999884259232203</v>
       </c>
       <c r="E7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -10838,7 +10843,7 @@
         <v>8.8881944444437977</v>
       </c>
       <c r="E8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -10856,7 +10861,7 @@
         <v>6.1388888888905058</v>
       </c>
       <c r="E9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -10882,10 +10887,10 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:3">

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1354" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{597C9992-2867-470C-B338-EFABDF6C8F19}"/>
+  <xr:revisionPtr revIDLastSave="1359" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07C8AB9F-9B3B-48C6-BF99-F97847931531}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="125">
   <si>
     <t>ID</t>
   </si>
@@ -387,6 +387,9 @@
   </si>
   <si>
     <t>Al DP filtrso succión bba LAC10/30</t>
+  </si>
+  <si>
+    <t>Filtros de succión obstruidos bbas agua alimentación.</t>
   </si>
   <si>
     <t>P_Max_Bruta</t>
@@ -10482,8 +10485,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="348" spans="1:10">
-      <c r="A348">
+    <row r="348" spans="1:10" ht="15">
+      <c r="A348" s="1">
         <v>338</v>
       </c>
       <c r="B348" s="13" t="s">
@@ -10508,7 +10511,12 @@
       <c r="H348" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="I348" s="11"/>
+      <c r="I348" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="J348" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10543,10 +10551,10 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -10554,7 +10562,7 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C2">
         <v>245.84</v>
@@ -10568,7 +10576,7 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C3">
         <v>176.6</v>
@@ -10582,7 +10590,7 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C4">
         <v>174.26</v>
@@ -10596,7 +10604,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C5">
         <v>376.96</v>
@@ -10610,7 +10618,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C6">
         <v>399.41</v>
@@ -10624,7 +10632,7 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C7">
         <v>20</v>
@@ -10638,7 +10646,7 @@
         <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8">
         <v>21</v>
@@ -10652,7 +10660,7 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C9">
         <v>21</v>
@@ -10666,7 +10674,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C10">
         <v>131</v>
@@ -10680,7 +10688,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C11">
         <v>112</v>
@@ -10716,10 +10724,10 @@
         <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E1" t="s">
         <v>7</v>
@@ -10739,7 +10747,7 @@
         <v>214.99998842592322</v>
       </c>
       <c r="E2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -10756,7 +10764,7 @@
         <v>7.6381944444437977</v>
       </c>
       <c r="E3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -10774,7 +10782,7 @@
         <v>25.829849537039991</v>
       </c>
       <c r="E4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -10791,7 +10799,7 @@
         <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -10808,7 +10816,7 @@
         <v>59.99998842592322</v>
       </c>
       <c r="E6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -10825,7 +10833,7 @@
         <v>3.9999884259232203</v>
       </c>
       <c r="E7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -10843,7 +10851,7 @@
         <v>8.8881944444437977</v>
       </c>
       <c r="E8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -10861,7 +10869,7 @@
         <v>6.1388888888905058</v>
       </c>
       <c r="E9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -10887,10 +10895,10 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:3">

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1359" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07C8AB9F-9B3B-48C6-BF99-F97847931531}"/>
+  <xr:revisionPtr revIDLastSave="1360" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91D90EA3-A88E-4D5F-B87B-C0AE3BA9C812}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -472,7 +472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -511,9 +511,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -10492,7 +10489,7 @@
       <c r="B348" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C348" s="16" t="str">
+      <c r="C348" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
@@ -10775,11 +10772,11 @@
         <v>46235</v>
       </c>
       <c r="C4" s="3">
-        <v>46260.82984953704</v>
+        <v>46262.82984953704</v>
       </c>
       <c r="D4" s="14">
         <f>Indisp_Prog[[#This Row],[Fecha_Hora_Fin]]-Indisp_Prog[[#This Row],[Fecha_Hora_Inicio]]</f>
-        <v>25.829849537039991</v>
+        <v>27.829849537039991</v>
       </c>
       <c r="E4" t="s">
         <v>120</v>
@@ -11020,6 +11017,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
@@ -11031,15 +11037,6 @@
     </SharedWithUsers>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11246,11 +11243,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1360" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91D90EA3-A88E-4D5F-B87B-C0AE3BA9C812}"/>
+  <xr:revisionPtr revIDLastSave="1361" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81B180EB-BEC6-40C2-A9D3-BE0EC3669F23}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -10772,11 +10772,11 @@
         <v>46235</v>
       </c>
       <c r="C4" s="3">
-        <v>46262.82984953704</v>
+        <v>46261.82984953704</v>
       </c>
       <c r="D4" s="14">
         <f>Indisp_Prog[[#This Row],[Fecha_Hora_Fin]]-Indisp_Prog[[#This Row],[Fecha_Hora_Inicio]]</f>
-        <v>27.829849537039991</v>
+        <v>26.829849537039991</v>
       </c>
       <c r="E4" t="s">
         <v>120</v>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1361" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81B180EB-BEC6-40C2-A9D3-BE0EC3669F23}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView minimized="1" xWindow="26148" yWindow="3612" windowWidth="17280" windowHeight="8928" firstSheet="1" activeTab="1" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="SegmentaciónDeDatos_Sitio">#N/A</definedName>
     <definedName name="SegmentaciónDeDatos_Unidad">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
@@ -435,7 +435,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -519,27 +519,17 @@
   </cellStyles>
   <dxfs count="12">
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -558,6 +548,16 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -850,23 +850,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J348" totalsRowShown="0" headerRowDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J348" totalsRowShown="0" headerRowDxfId="8">
   <autoFilter ref="A10:J348" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="3" xr3:uid="{AFE823F6-980E-4E32-B4F4-6ECDE10F377D}" name="ID"/>
-    <tableColumn id="1" xr3:uid="{CD000998-6E2C-4963-8605-37081D9C1A64}" name="Unidad" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{542F6635-555D-4F04-8C27-263AF6E0C9F1}" name="Sitio" dataDxfId="9">
+    <tableColumn id="1" xr3:uid="{CD000998-6E2C-4963-8605-37081D9C1A64}" name="Unidad" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{542F6635-555D-4F04-8C27-263AF6E0C9F1}" name="Sitio" dataDxfId="6">
       <calculatedColumnFormula>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6D2AC534-BC70-4E36-815D-053C7EC9A0CE}" name="Carga_Disponible" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{FBB18F6C-27E4-42D9-9835-9152B6D0D871}" name="Estado_Op" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{21A32989-F167-49C0-9D41-2BD3A8923998}" name="Fecha_Hora_Inicio" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{713F74B7-95D9-4F96-AA1E-57E68B8A7FE7}" name="Fecha_Hora_Final" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{20481209-2CB3-4DCC-A330-D866983AA4F9}" name="Motivo" dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{55FF6738-9798-4086-9AA1-DC8A3EF8081F}" name="Detalle" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{6D2AC534-BC70-4E36-815D-053C7EC9A0CE}" name="Carga_Disponible" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{FBB18F6C-27E4-42D9-9835-9152B6D0D871}" name="Estado_Op" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{21A32989-F167-49C0-9D41-2BD3A8923998}" name="Fecha_Hora_Inicio" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{713F74B7-95D9-4F96-AA1E-57E68B8A7FE7}" name="Fecha_Hora_Final" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{20481209-2CB3-4DCC-A330-D866983AA4F9}" name="Motivo" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{55FF6738-9798-4086-9AA1-DC8A3EF8081F}" name="Detalle" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{C2DE1A32-EBAC-4C95-A60E-FB6BAE643966}" name="Verificación"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -894,9 +894,9 @@
   </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{1EEE0FFC-B699-4850-9A13-72CF6FB78CA6}" name="Unidad"/>
-    <tableColumn id="2" xr3:uid="{BDB3B76C-8D9D-4A32-9C94-204172B9E68C}" name="Fecha_Hora_Inicio" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{A21A7F07-F50E-4006-B601-758B5E8BD7BE}" name="Fecha_Hora_Fin" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{F49EC928-7A7A-47BB-9275-EDE8B8DF6BC7}" name="Días_de_Mantenimiento" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{BDB3B76C-8D9D-4A32-9C94-204172B9E68C}" name="Fecha_Hora_Inicio" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{A21A7F07-F50E-4006-B601-758B5E8BD7BE}" name="Fecha_Hora_Fin" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{F49EC928-7A7A-47BB-9275-EDE8B8DF6BC7}" name="Días_de_Mantenimiento" dataDxfId="9"/>
     <tableColumn id="5" xr3:uid="{E5C19B72-F1F0-4F1D-9466-99048BCEFC0C}" name="Motivo"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1233,7 +1233,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
   <dimension ref="A9:J348"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
@@ -1248,13 +1248,13 @@
     <col min="12" max="12" width="33.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
         <v>338</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1286,7 +1286,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -1312,7 +1312,7 @@
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -1338,7 +1338,7 @@
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>3</v>
       </c>
@@ -1364,7 +1364,7 @@
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>4</v>
       </c>
@@ -1390,7 +1390,7 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>5</v>
       </c>
@@ -1416,7 +1416,7 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>6</v>
       </c>
@@ -1442,7 +1442,7 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>7</v>
       </c>
@@ -1468,7 +1468,7 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>8</v>
       </c>
@@ -1494,7 +1494,7 @@
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>9</v>
       </c>
@@ -1520,7 +1520,7 @@
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>10</v>
       </c>
@@ -1546,7 +1546,7 @@
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>11</v>
       </c>
@@ -1572,7 +1572,7 @@
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>12</v>
       </c>
@@ -1598,7 +1598,7 @@
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>13</v>
       </c>
@@ -1624,7 +1624,7 @@
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>14</v>
       </c>
@@ -1650,7 +1650,7 @@
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>15</v>
       </c>
@@ -1676,7 +1676,7 @@
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>16</v>
       </c>
@@ -1702,7 +1702,7 @@
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>17</v>
       </c>
@@ -1728,7 +1728,7 @@
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>18</v>
       </c>
@@ -1754,7 +1754,7 @@
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>19</v>
       </c>
@@ -1780,7 +1780,7 @@
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>20</v>
       </c>
@@ -1806,7 +1806,7 @@
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>21</v>
       </c>
@@ -1832,7 +1832,7 @@
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>22</v>
       </c>
@@ -1858,7 +1858,7 @@
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>23</v>
       </c>
@@ -1884,7 +1884,7 @@
       <c r="H33" s="11"/>
       <c r="I33" s="11"/>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24</v>
       </c>
@@ -1910,7 +1910,7 @@
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>25</v>
       </c>
@@ -1936,7 +1936,7 @@
       <c r="H35" s="11"/>
       <c r="I35" s="11"/>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>26</v>
       </c>
@@ -1962,7 +1962,7 @@
       <c r="H36" s="11"/>
       <c r="I36" s="11"/>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>27</v>
       </c>
@@ -1988,7 +1988,7 @@
       <c r="H37" s="11"/>
       <c r="I37" s="11"/>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>28</v>
       </c>
@@ -2014,7 +2014,7 @@
       <c r="H38" s="11"/>
       <c r="I38" s="11"/>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>29</v>
       </c>
@@ -2040,7 +2040,7 @@
       <c r="H39" s="11"/>
       <c r="I39" s="11"/>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>30</v>
       </c>
@@ -2066,7 +2066,7 @@
       <c r="H40" s="11"/>
       <c r="I40" s="11"/>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>31</v>
       </c>
@@ -2092,7 +2092,7 @@
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>32</v>
       </c>
@@ -2118,7 +2118,7 @@
       <c r="H42" s="11"/>
       <c r="I42" s="11"/>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>33</v>
       </c>
@@ -2144,7 +2144,7 @@
       <c r="H43" s="11"/>
       <c r="I43" s="11"/>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>34</v>
       </c>
@@ -2170,7 +2170,7 @@
       <c r="H44" s="11"/>
       <c r="I44" s="11"/>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>35</v>
       </c>
@@ -2196,7 +2196,7 @@
       <c r="H45" s="11"/>
       <c r="I45" s="11"/>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>36</v>
       </c>
@@ -2222,7 +2222,7 @@
       <c r="H46" s="11"/>
       <c r="I46" s="11"/>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>37</v>
       </c>
@@ -2248,7 +2248,7 @@
       <c r="H47" s="11"/>
       <c r="I47" s="11"/>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>38</v>
       </c>
@@ -2274,7 +2274,7 @@
       <c r="H48" s="11"/>
       <c r="I48" s="11"/>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>39</v>
       </c>
@@ -2300,7 +2300,7 @@
       <c r="H49" s="11"/>
       <c r="I49" s="11"/>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>40</v>
       </c>
@@ -2326,7 +2326,7 @@
       <c r="H50" s="11"/>
       <c r="I50" s="11"/>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>41</v>
       </c>
@@ -2352,7 +2352,7 @@
       <c r="H51" s="11"/>
       <c r="I51" s="11"/>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>42</v>
       </c>
@@ -2378,7 +2378,7 @@
       <c r="H52" s="11"/>
       <c r="I52" s="11"/>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>43</v>
       </c>
@@ -2404,7 +2404,7 @@
       <c r="H53" s="11"/>
       <c r="I53" s="11"/>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>44</v>
       </c>
@@ -2430,7 +2430,7 @@
       <c r="H54" s="11"/>
       <c r="I54" s="11"/>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>45</v>
       </c>
@@ -2456,7 +2456,7 @@
       <c r="H55" s="11"/>
       <c r="I55" s="11"/>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>46</v>
       </c>
@@ -2482,7 +2482,7 @@
       <c r="H56" s="11"/>
       <c r="I56" s="11"/>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>47</v>
       </c>
@@ -2508,7 +2508,7 @@
       <c r="H57" s="11"/>
       <c r="I57" s="11"/>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>48</v>
       </c>
@@ -2534,7 +2534,7 @@
       <c r="H58" s="11"/>
       <c r="I58" s="11"/>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>49</v>
       </c>
@@ -2560,7 +2560,7 @@
       <c r="H59" s="11"/>
       <c r="I59" s="11"/>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>50</v>
       </c>
@@ -2586,7 +2586,7 @@
       <c r="H60" s="11"/>
       <c r="I60" s="11"/>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>51</v>
       </c>
@@ -2612,7 +2612,7 @@
       <c r="H61" s="11"/>
       <c r="I61" s="11"/>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>52</v>
       </c>
@@ -2638,7 +2638,7 @@
       <c r="H62" s="11"/>
       <c r="I62" s="11"/>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>53</v>
       </c>
@@ -2664,7 +2664,7 @@
       <c r="H63" s="11"/>
       <c r="I63" s="11"/>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>54</v>
       </c>
@@ -2690,7 +2690,7 @@
       <c r="H64" s="11"/>
       <c r="I64" s="11"/>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>55</v>
       </c>
@@ -2716,7 +2716,7 @@
       <c r="H65" s="11"/>
       <c r="I65" s="11"/>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>56</v>
       </c>
@@ -2742,7 +2742,7 @@
       <c r="H66" s="11"/>
       <c r="I66" s="11"/>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>57</v>
       </c>
@@ -2768,7 +2768,7 @@
       <c r="H67" s="11"/>
       <c r="I67" s="11"/>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>58</v>
       </c>
@@ -2794,7 +2794,7 @@
       <c r="H68" s="11"/>
       <c r="I68" s="11"/>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>59</v>
       </c>
@@ -2820,7 +2820,7 @@
       <c r="H69" s="11"/>
       <c r="I69" s="11"/>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>60</v>
       </c>
@@ -2846,7 +2846,7 @@
       <c r="H70" s="11"/>
       <c r="I70" s="11"/>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>61</v>
       </c>
@@ -2872,7 +2872,7 @@
       <c r="H71" s="11"/>
       <c r="I71" s="11"/>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>62</v>
       </c>
@@ -2898,7 +2898,7 @@
       <c r="H72" s="11"/>
       <c r="I72" s="11"/>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>63</v>
       </c>
@@ -2924,7 +2924,7 @@
       <c r="H73" s="11"/>
       <c r="I73" s="11"/>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>64</v>
       </c>
@@ -2950,7 +2950,7 @@
       <c r="H74" s="11"/>
       <c r="I74" s="11"/>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>65</v>
       </c>
@@ -2976,7 +2976,7 @@
       <c r="H75" s="11"/>
       <c r="I75" s="11"/>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>66</v>
       </c>
@@ -3002,7 +3002,7 @@
       <c r="H76" s="11"/>
       <c r="I76" s="11"/>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>67</v>
       </c>
@@ -3028,7 +3028,7 @@
       <c r="H77" s="11"/>
       <c r="I77" s="11"/>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>68</v>
       </c>
@@ -3054,7 +3054,7 @@
       <c r="H78" s="11"/>
       <c r="I78" s="11"/>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>69</v>
       </c>
@@ -3080,7 +3080,7 @@
       <c r="H79" s="11"/>
       <c r="I79" s="11"/>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>70</v>
       </c>
@@ -3106,7 +3106,7 @@
       <c r="H80" s="11"/>
       <c r="I80" s="11"/>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>71</v>
       </c>
@@ -3132,7 +3132,7 @@
       <c r="H81" s="11"/>
       <c r="I81" s="11"/>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>72</v>
       </c>
@@ -3158,7 +3158,7 @@
       <c r="H82" s="11"/>
       <c r="I82" s="11"/>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>73</v>
       </c>
@@ -3184,7 +3184,7 @@
       <c r="H83" s="11"/>
       <c r="I83" s="11"/>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>74</v>
       </c>
@@ -3210,7 +3210,7 @@
       <c r="H84" s="11"/>
       <c r="I84" s="11"/>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>75</v>
       </c>
@@ -3236,7 +3236,7 @@
       <c r="H85" s="11"/>
       <c r="I85" s="11"/>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>76</v>
       </c>
@@ -3262,7 +3262,7 @@
       <c r="H86" s="11"/>
       <c r="I86" s="11"/>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>77</v>
       </c>
@@ -3288,7 +3288,7 @@
       <c r="H87" s="11"/>
       <c r="I87" s="11"/>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>78</v>
       </c>
@@ -3314,7 +3314,7 @@
       <c r="H88" s="11"/>
       <c r="I88" s="11"/>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>79</v>
       </c>
@@ -3340,7 +3340,7 @@
       <c r="H89" s="11"/>
       <c r="I89" s="11"/>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>80</v>
       </c>
@@ -3366,7 +3366,7 @@
       <c r="H90" s="11"/>
       <c r="I90" s="11"/>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>81</v>
       </c>
@@ -3392,7 +3392,7 @@
       <c r="H91" s="11"/>
       <c r="I91" s="11"/>
     </row>
-    <row r="92" spans="1:9">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>82</v>
       </c>
@@ -3418,7 +3418,7 @@
       <c r="H92" s="11"/>
       <c r="I92" s="11"/>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>83</v>
       </c>
@@ -3444,7 +3444,7 @@
       <c r="H93" s="11"/>
       <c r="I93" s="11"/>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>84</v>
       </c>
@@ -3470,7 +3470,7 @@
       <c r="H94" s="11"/>
       <c r="I94" s="11"/>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>85</v>
       </c>
@@ -3496,7 +3496,7 @@
       <c r="H95" s="11"/>
       <c r="I95" s="11"/>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>86</v>
       </c>
@@ -3522,7 +3522,7 @@
       <c r="H96" s="11"/>
       <c r="I96" s="11"/>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>87</v>
       </c>
@@ -3548,7 +3548,7 @@
       <c r="H97" s="11"/>
       <c r="I97" s="11"/>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>88</v>
       </c>
@@ -3574,7 +3574,7 @@
       <c r="H98" s="11"/>
       <c r="I98" s="11"/>
     </row>
-    <row r="99" spans="1:9">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>89</v>
       </c>
@@ -3600,7 +3600,7 @@
       <c r="H99" s="11"/>
       <c r="I99" s="11"/>
     </row>
-    <row r="100" spans="1:9">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>90</v>
       </c>
@@ -3626,7 +3626,7 @@
       <c r="H100" s="11"/>
       <c r="I100" s="11"/>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>91</v>
       </c>
@@ -3652,7 +3652,7 @@
       <c r="H101" s="11"/>
       <c r="I101" s="11"/>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>92</v>
       </c>
@@ -3678,7 +3678,7 @@
       <c r="H102" s="11"/>
       <c r="I102" s="11"/>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>93</v>
       </c>
@@ -3704,7 +3704,7 @@
       <c r="H103" s="11"/>
       <c r="I103" s="11"/>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>94</v>
       </c>
@@ -3730,7 +3730,7 @@
       <c r="H104" s="11"/>
       <c r="I104" s="11"/>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>95</v>
       </c>
@@ -3756,7 +3756,7 @@
       <c r="H105" s="11"/>
       <c r="I105" s="11"/>
     </row>
-    <row r="106" spans="1:9">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>96</v>
       </c>
@@ -3782,7 +3782,7 @@
       <c r="H106" s="11"/>
       <c r="I106" s="11"/>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>97</v>
       </c>
@@ -3808,7 +3808,7 @@
       <c r="H107" s="11"/>
       <c r="I107" s="11"/>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>98</v>
       </c>
@@ -3834,7 +3834,7 @@
       <c r="H108" s="11"/>
       <c r="I108" s="11"/>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>99</v>
       </c>
@@ -3860,7 +3860,7 @@
       <c r="H109" s="11"/>
       <c r="I109" s="11"/>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>100</v>
       </c>
@@ -3886,7 +3886,7 @@
       <c r="H110" s="11"/>
       <c r="I110" s="11"/>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>101</v>
       </c>
@@ -3912,7 +3912,7 @@
       <c r="H111" s="11"/>
       <c r="I111" s="11"/>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>102</v>
       </c>
@@ -3938,7 +3938,7 @@
       <c r="H112" s="11"/>
       <c r="I112" s="11"/>
     </row>
-    <row r="113" spans="1:9">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>103</v>
       </c>
@@ -3964,7 +3964,7 @@
       <c r="H113" s="11"/>
       <c r="I113" s="11"/>
     </row>
-    <row r="114" spans="1:9">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>104</v>
       </c>
@@ -3990,7 +3990,7 @@
       <c r="H114" s="11"/>
       <c r="I114" s="11"/>
     </row>
-    <row r="115" spans="1:9">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>105</v>
       </c>
@@ -4016,7 +4016,7 @@
       <c r="H115" s="11"/>
       <c r="I115" s="11"/>
     </row>
-    <row r="116" spans="1:9">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>106</v>
       </c>
@@ -4042,7 +4042,7 @@
       <c r="H116" s="11"/>
       <c r="I116" s="11"/>
     </row>
-    <row r="117" spans="1:9">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>107</v>
       </c>
@@ -4068,7 +4068,7 @@
       <c r="H117" s="11"/>
       <c r="I117" s="11"/>
     </row>
-    <row r="118" spans="1:9">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>108</v>
       </c>
@@ -4094,7 +4094,7 @@
       <c r="H118" s="11"/>
       <c r="I118" s="11"/>
     </row>
-    <row r="119" spans="1:9">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>109</v>
       </c>
@@ -4120,7 +4120,7 @@
       <c r="H119" s="11"/>
       <c r="I119" s="11"/>
     </row>
-    <row r="120" spans="1:9">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>110</v>
       </c>
@@ -4146,7 +4146,7 @@
       <c r="H120" s="11"/>
       <c r="I120" s="11"/>
     </row>
-    <row r="121" spans="1:9">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>111</v>
       </c>
@@ -4172,7 +4172,7 @@
       <c r="H121" s="11"/>
       <c r="I121" s="11"/>
     </row>
-    <row r="122" spans="1:9">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>112</v>
       </c>
@@ -4198,7 +4198,7 @@
       <c r="H122" s="11"/>
       <c r="I122" s="11"/>
     </row>
-    <row r="123" spans="1:9">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>113</v>
       </c>
@@ -4224,7 +4224,7 @@
       <c r="H123" s="11"/>
       <c r="I123" s="11"/>
     </row>
-    <row r="124" spans="1:9">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>114</v>
       </c>
@@ -4250,7 +4250,7 @@
       <c r="H124" s="11"/>
       <c r="I124" s="11"/>
     </row>
-    <row r="125" spans="1:9">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>115</v>
       </c>
@@ -4276,7 +4276,7 @@
       <c r="H125" s="11"/>
       <c r="I125" s="11"/>
     </row>
-    <row r="126" spans="1:9">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>116</v>
       </c>
@@ -4302,7 +4302,7 @@
       <c r="H126" s="11"/>
       <c r="I126" s="11"/>
     </row>
-    <row r="127" spans="1:9">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>117</v>
       </c>
@@ -4328,7 +4328,7 @@
       <c r="H127" s="11"/>
       <c r="I127" s="11"/>
     </row>
-    <row r="128" spans="1:9">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>118</v>
       </c>
@@ -4354,7 +4354,7 @@
       <c r="H128" s="11"/>
       <c r="I128" s="11"/>
     </row>
-    <row r="129" spans="1:9">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>119</v>
       </c>
@@ -4380,7 +4380,7 @@
       <c r="H129" s="11"/>
       <c r="I129" s="11"/>
     </row>
-    <row r="130" spans="1:9">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>120</v>
       </c>
@@ -4406,7 +4406,7 @@
       <c r="H130" s="11"/>
       <c r="I130" s="11"/>
     </row>
-    <row r="131" spans="1:9">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>121</v>
       </c>
@@ -4432,7 +4432,7 @@
       <c r="H131" s="11"/>
       <c r="I131" s="11"/>
     </row>
-    <row r="132" spans="1:9">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>122</v>
       </c>
@@ -4458,7 +4458,7 @@
       <c r="H132" s="11"/>
       <c r="I132" s="11"/>
     </row>
-    <row r="133" spans="1:9">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>123</v>
       </c>
@@ -4484,7 +4484,7 @@
       <c r="H133" s="11"/>
       <c r="I133" s="11"/>
     </row>
-    <row r="134" spans="1:9">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>124</v>
       </c>
@@ -4510,7 +4510,7 @@
       <c r="H134" s="11"/>
       <c r="I134" s="11"/>
     </row>
-    <row r="135" spans="1:9">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>125</v>
       </c>
@@ -4536,7 +4536,7 @@
       <c r="H135" s="11"/>
       <c r="I135" s="11"/>
     </row>
-    <row r="136" spans="1:9">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>126</v>
       </c>
@@ -4562,7 +4562,7 @@
       <c r="H136" s="11"/>
       <c r="I136" s="11"/>
     </row>
-    <row r="137" spans="1:9">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>127</v>
       </c>
@@ -4588,7 +4588,7 @@
       <c r="H137" s="11"/>
       <c r="I137" s="11"/>
     </row>
-    <row r="138" spans="1:9">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>128</v>
       </c>
@@ -4614,7 +4614,7 @@
       <c r="H138" s="11"/>
       <c r="I138" s="11"/>
     </row>
-    <row r="139" spans="1:9">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>129</v>
       </c>
@@ -4640,7 +4640,7 @@
       <c r="H139" s="11"/>
       <c r="I139" s="11"/>
     </row>
-    <row r="140" spans="1:9">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>130</v>
       </c>
@@ -4666,7 +4666,7 @@
       <c r="H140" s="11"/>
       <c r="I140" s="11"/>
     </row>
-    <row r="141" spans="1:9">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>131</v>
       </c>
@@ -4692,7 +4692,7 @@
       <c r="H141" s="11"/>
       <c r="I141" s="11"/>
     </row>
-    <row r="142" spans="1:9">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>132</v>
       </c>
@@ -4718,7 +4718,7 @@
       <c r="H142" s="11"/>
       <c r="I142" s="11"/>
     </row>
-    <row r="143" spans="1:9">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>133</v>
       </c>
@@ -4744,7 +4744,7 @@
       <c r="H143" s="11"/>
       <c r="I143" s="11"/>
     </row>
-    <row r="144" spans="1:9">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>134</v>
       </c>
@@ -4770,7 +4770,7 @@
       <c r="H144" s="11"/>
       <c r="I144" s="11"/>
     </row>
-    <row r="145" spans="1:9">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>135</v>
       </c>
@@ -4796,7 +4796,7 @@
       <c r="H145" s="11"/>
       <c r="I145" s="11"/>
     </row>
-    <row r="146" spans="1:9">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>136</v>
       </c>
@@ -4822,7 +4822,7 @@
       <c r="H146" s="11"/>
       <c r="I146" s="11"/>
     </row>
-    <row r="147" spans="1:9">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>137</v>
       </c>
@@ -4848,7 +4848,7 @@
       <c r="H147" s="11"/>
       <c r="I147" s="11"/>
     </row>
-    <row r="148" spans="1:9">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>138</v>
       </c>
@@ -4874,7 +4874,7 @@
       <c r="H148" s="11"/>
       <c r="I148" s="11"/>
     </row>
-    <row r="149" spans="1:9">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>139</v>
       </c>
@@ -4900,7 +4900,7 @@
       <c r="H149" s="11"/>
       <c r="I149" s="11"/>
     </row>
-    <row r="150" spans="1:9">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>140</v>
       </c>
@@ -4926,7 +4926,7 @@
       <c r="H150" s="11"/>
       <c r="I150" s="11"/>
     </row>
-    <row r="151" spans="1:9">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>141</v>
       </c>
@@ -4952,7 +4952,7 @@
       <c r="H151" s="11"/>
       <c r="I151" s="11"/>
     </row>
-    <row r="152" spans="1:9">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>142</v>
       </c>
@@ -4978,7 +4978,7 @@
       <c r="H152" s="11"/>
       <c r="I152" s="11"/>
     </row>
-    <row r="153" spans="1:9">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>143</v>
       </c>
@@ -5004,7 +5004,7 @@
       <c r="H153" s="11"/>
       <c r="I153" s="11"/>
     </row>
-    <row r="154" spans="1:9">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>144</v>
       </c>
@@ -5030,7 +5030,7 @@
       <c r="H154" s="11"/>
       <c r="I154" s="11"/>
     </row>
-    <row r="155" spans="1:9">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>145</v>
       </c>
@@ -5056,7 +5056,7 @@
       <c r="H155" s="11"/>
       <c r="I155" s="11"/>
     </row>
-    <row r="156" spans="1:9">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>146</v>
       </c>
@@ -5082,7 +5082,7 @@
       <c r="H156" s="11"/>
       <c r="I156" s="11"/>
     </row>
-    <row r="157" spans="1:9">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>147</v>
       </c>
@@ -5108,7 +5108,7 @@
       <c r="H157" s="11"/>
       <c r="I157" s="11"/>
     </row>
-    <row r="158" spans="1:9">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>148</v>
       </c>
@@ -5134,7 +5134,7 @@
       <c r="H158" s="11"/>
       <c r="I158" s="11"/>
     </row>
-    <row r="159" spans="1:9">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>149</v>
       </c>
@@ -5160,7 +5160,7 @@
       <c r="H159" s="11"/>
       <c r="I159" s="11"/>
     </row>
-    <row r="160" spans="1:9">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>150</v>
       </c>
@@ -5186,7 +5186,7 @@
       <c r="H160" s="11"/>
       <c r="I160" s="11"/>
     </row>
-    <row r="161" spans="1:9">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>151</v>
       </c>
@@ -5212,7 +5212,7 @@
       <c r="H161" s="11"/>
       <c r="I161" s="11"/>
     </row>
-    <row r="162" spans="1:9">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>152</v>
       </c>
@@ -5238,7 +5238,7 @@
       <c r="H162" s="11"/>
       <c r="I162" s="11"/>
     </row>
-    <row r="163" spans="1:9">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>153</v>
       </c>
@@ -5264,7 +5264,7 @@
       <c r="H163" s="11"/>
       <c r="I163" s="11"/>
     </row>
-    <row r="164" spans="1:9">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>154</v>
       </c>
@@ -5290,7 +5290,7 @@
       <c r="H164" s="11"/>
       <c r="I164" s="11"/>
     </row>
-    <row r="165" spans="1:9">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>155</v>
       </c>
@@ -5316,7 +5316,7 @@
       <c r="H165" s="11"/>
       <c r="I165" s="11"/>
     </row>
-    <row r="166" spans="1:9">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>156</v>
       </c>
@@ -5342,7 +5342,7 @@
       <c r="H166" s="11"/>
       <c r="I166" s="11"/>
     </row>
-    <row r="167" spans="1:9">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>157</v>
       </c>
@@ -5368,7 +5368,7 @@
       <c r="H167" s="11"/>
       <c r="I167" s="11"/>
     </row>
-    <row r="168" spans="1:9">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>158</v>
       </c>
@@ -5394,7 +5394,7 @@
       <c r="H168" s="11"/>
       <c r="I168" s="11"/>
     </row>
-    <row r="169" spans="1:9">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>159</v>
       </c>
@@ -5420,7 +5420,7 @@
       <c r="H169" s="11"/>
       <c r="I169" s="11"/>
     </row>
-    <row r="170" spans="1:9">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>160</v>
       </c>
@@ -5446,7 +5446,7 @@
       <c r="H170" s="11"/>
       <c r="I170" s="11"/>
     </row>
-    <row r="171" spans="1:9">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>161</v>
       </c>
@@ -5472,7 +5472,7 @@
       <c r="H171" s="11"/>
       <c r="I171" s="11"/>
     </row>
-    <row r="172" spans="1:9">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>162</v>
       </c>
@@ -5498,7 +5498,7 @@
       <c r="H172" s="11"/>
       <c r="I172" s="11"/>
     </row>
-    <row r="173" spans="1:9">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>163</v>
       </c>
@@ -5524,7 +5524,7 @@
       <c r="H173" s="11"/>
       <c r="I173" s="11"/>
     </row>
-    <row r="174" spans="1:9">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>164</v>
       </c>
@@ -5550,7 +5550,7 @@
       <c r="H174" s="11"/>
       <c r="I174" s="11"/>
     </row>
-    <row r="175" spans="1:9">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>165</v>
       </c>
@@ -5576,7 +5576,7 @@
       <c r="H175" s="11"/>
       <c r="I175" s="11"/>
     </row>
-    <row r="176" spans="1:9">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>166</v>
       </c>
@@ -5602,7 +5602,7 @@
       <c r="H176" s="11"/>
       <c r="I176" s="11"/>
     </row>
-    <row r="177" spans="1:9">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>167</v>
       </c>
@@ -5628,7 +5628,7 @@
       <c r="H177" s="11"/>
       <c r="I177" s="11"/>
     </row>
-    <row r="178" spans="1:9">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>168</v>
       </c>
@@ -5654,7 +5654,7 @@
       <c r="H178" s="11"/>
       <c r="I178" s="11"/>
     </row>
-    <row r="179" spans="1:9">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>169</v>
       </c>
@@ -5680,7 +5680,7 @@
       <c r="H179" s="11"/>
       <c r="I179" s="11"/>
     </row>
-    <row r="180" spans="1:9">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>170</v>
       </c>
@@ -5706,7 +5706,7 @@
       <c r="H180" s="11"/>
       <c r="I180" s="11"/>
     </row>
-    <row r="181" spans="1:9">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>171</v>
       </c>
@@ -5732,7 +5732,7 @@
       <c r="H181" s="11"/>
       <c r="I181" s="11"/>
     </row>
-    <row r="182" spans="1:9">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>172</v>
       </c>
@@ -5758,7 +5758,7 @@
       <c r="H182" s="11"/>
       <c r="I182" s="11"/>
     </row>
-    <row r="183" spans="1:9">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>173</v>
       </c>
@@ -5784,7 +5784,7 @@
       <c r="H183" s="11"/>
       <c r="I183" s="11"/>
     </row>
-    <row r="184" spans="1:9">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>174</v>
       </c>
@@ -5810,7 +5810,7 @@
       <c r="H184" s="11"/>
       <c r="I184" s="11"/>
     </row>
-    <row r="185" spans="1:9">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>175</v>
       </c>
@@ -5836,7 +5836,7 @@
       <c r="H185" s="11"/>
       <c r="I185" s="11"/>
     </row>
-    <row r="186" spans="1:9">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>176</v>
       </c>
@@ -5862,7 +5862,7 @@
       <c r="H186" s="11"/>
       <c r="I186" s="11"/>
     </row>
-    <row r="187" spans="1:9">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>177</v>
       </c>
@@ -5888,7 +5888,7 @@
       <c r="H187" s="11"/>
       <c r="I187" s="11"/>
     </row>
-    <row r="188" spans="1:9">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>178</v>
       </c>
@@ -5914,7 +5914,7 @@
       <c r="H188" s="11"/>
       <c r="I188" s="11"/>
     </row>
-    <row r="189" spans="1:9">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>179</v>
       </c>
@@ -5940,7 +5940,7 @@
       <c r="H189" s="11"/>
       <c r="I189" s="11"/>
     </row>
-    <row r="190" spans="1:9">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>180</v>
       </c>
@@ -5966,7 +5966,7 @@
       <c r="H190" s="11"/>
       <c r="I190" s="11"/>
     </row>
-    <row r="191" spans="1:9">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>181</v>
       </c>
@@ -5992,7 +5992,7 @@
       <c r="H191" s="11"/>
       <c r="I191" s="11"/>
     </row>
-    <row r="192" spans="1:9">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>182</v>
       </c>
@@ -6018,7 +6018,7 @@
       <c r="H192" s="11"/>
       <c r="I192" s="11"/>
     </row>
-    <row r="193" spans="1:9">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>183</v>
       </c>
@@ -6044,7 +6044,7 @@
       <c r="H193" s="11"/>
       <c r="I193" s="11"/>
     </row>
-    <row r="194" spans="1:9">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>184</v>
       </c>
@@ -6070,7 +6070,7 @@
       <c r="H194" s="11"/>
       <c r="I194" s="11"/>
     </row>
-    <row r="195" spans="1:9">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>185</v>
       </c>
@@ -6096,7 +6096,7 @@
       <c r="H195" s="11"/>
       <c r="I195" s="11"/>
     </row>
-    <row r="196" spans="1:9">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>186</v>
       </c>
@@ -6122,7 +6122,7 @@
       <c r="H196" s="11"/>
       <c r="I196" s="11"/>
     </row>
-    <row r="197" spans="1:9">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>187</v>
       </c>
@@ -6148,7 +6148,7 @@
       <c r="H197" s="11"/>
       <c r="I197" s="11"/>
     </row>
-    <row r="198" spans="1:9">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>188</v>
       </c>
@@ -6174,7 +6174,7 @@
       <c r="H198" s="11"/>
       <c r="I198" s="11"/>
     </row>
-    <row r="199" spans="1:9">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>189</v>
       </c>
@@ -6200,7 +6200,7 @@
       <c r="H199" s="11"/>
       <c r="I199" s="11"/>
     </row>
-    <row r="200" spans="1:9">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>190</v>
       </c>
@@ -6226,7 +6226,7 @@
       <c r="H200" s="11"/>
       <c r="I200" s="11"/>
     </row>
-    <row r="201" spans="1:9">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>191</v>
       </c>
@@ -6252,7 +6252,7 @@
       <c r="H201" s="11"/>
       <c r="I201" s="11"/>
     </row>
-    <row r="202" spans="1:9">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>192</v>
       </c>
@@ -6278,7 +6278,7 @@
       <c r="H202" s="11"/>
       <c r="I202" s="11"/>
     </row>
-    <row r="203" spans="1:9">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>193</v>
       </c>
@@ -6304,7 +6304,7 @@
       <c r="H203" s="11"/>
       <c r="I203" s="11"/>
     </row>
-    <row r="204" spans="1:9">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>194</v>
       </c>
@@ -6330,7 +6330,7 @@
       <c r="H204" s="11"/>
       <c r="I204" s="11"/>
     </row>
-    <row r="205" spans="1:9">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>195</v>
       </c>
@@ -6356,7 +6356,7 @@
       <c r="H205" s="11"/>
       <c r="I205" s="11"/>
     </row>
-    <row r="206" spans="1:9">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>196</v>
       </c>
@@ -6382,7 +6382,7 @@
       <c r="H206" s="11"/>
       <c r="I206" s="11"/>
     </row>
-    <row r="207" spans="1:9">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>197</v>
       </c>
@@ -6408,7 +6408,7 @@
       <c r="H207" s="11"/>
       <c r="I207" s="11"/>
     </row>
-    <row r="208" spans="1:9">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>198</v>
       </c>
@@ -6434,7 +6434,7 @@
       <c r="H208" s="11"/>
       <c r="I208" s="11"/>
     </row>
-    <row r="209" spans="1:9">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>199</v>
       </c>
@@ -6460,7 +6460,7 @@
       <c r="H209" s="11"/>
       <c r="I209" s="11"/>
     </row>
-    <row r="210" spans="1:9">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>200</v>
       </c>
@@ -6486,7 +6486,7 @@
       <c r="H210" s="11"/>
       <c r="I210" s="11"/>
     </row>
-    <row r="211" spans="1:9">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <v>201</v>
       </c>
@@ -6512,7 +6512,7 @@
       <c r="H211" s="11"/>
       <c r="I211" s="11"/>
     </row>
-    <row r="212" spans="1:9">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>202</v>
       </c>
@@ -6538,7 +6538,7 @@
       <c r="H212" s="11"/>
       <c r="I212" s="11"/>
     </row>
-    <row r="213" spans="1:9">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <v>203</v>
       </c>
@@ -6564,7 +6564,7 @@
       <c r="H213" s="11"/>
       <c r="I213" s="11"/>
     </row>
-    <row r="214" spans="1:9">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>204</v>
       </c>
@@ -6590,7 +6590,7 @@
       <c r="H214" s="11"/>
       <c r="I214" s="11"/>
     </row>
-    <row r="215" spans="1:9">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>205</v>
       </c>
@@ -6616,7 +6616,7 @@
       <c r="H215" s="11"/>
       <c r="I215" s="11"/>
     </row>
-    <row r="216" spans="1:9">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <v>206</v>
       </c>
@@ -6642,7 +6642,7 @@
       <c r="H216" s="11"/>
       <c r="I216" s="11"/>
     </row>
-    <row r="217" spans="1:9">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <v>207</v>
       </c>
@@ -6668,7 +6668,7 @@
       <c r="H217" s="11"/>
       <c r="I217" s="11"/>
     </row>
-    <row r="218" spans="1:9">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <v>208</v>
       </c>
@@ -6694,7 +6694,7 @@
       <c r="H218" s="11"/>
       <c r="I218" s="11"/>
     </row>
-    <row r="219" spans="1:9">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <v>209</v>
       </c>
@@ -6720,7 +6720,7 @@
       <c r="H219" s="11"/>
       <c r="I219" s="11"/>
     </row>
-    <row r="220" spans="1:9">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <v>210</v>
       </c>
@@ -6746,7 +6746,7 @@
       <c r="H220" s="11"/>
       <c r="I220" s="11"/>
     </row>
-    <row r="221" spans="1:9">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <v>211</v>
       </c>
@@ -6772,7 +6772,7 @@
       <c r="H221" s="11"/>
       <c r="I221" s="11"/>
     </row>
-    <row r="222" spans="1:9">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <v>212</v>
       </c>
@@ -6798,7 +6798,7 @@
       <c r="H222" s="11"/>
       <c r="I222" s="11"/>
     </row>
-    <row r="223" spans="1:9">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <v>213</v>
       </c>
@@ -6824,7 +6824,7 @@
       <c r="H223" s="11"/>
       <c r="I223" s="11"/>
     </row>
-    <row r="224" spans="1:9">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <v>214</v>
       </c>
@@ -6850,7 +6850,7 @@
       <c r="H224" s="11"/>
       <c r="I224" s="11"/>
     </row>
-    <row r="225" spans="1:9">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>215</v>
       </c>
@@ -6876,7 +6876,7 @@
       <c r="H225" s="11"/>
       <c r="I225" s="11"/>
     </row>
-    <row r="226" spans="1:9">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <v>216</v>
       </c>
@@ -6902,7 +6902,7 @@
       <c r="H226" s="11"/>
       <c r="I226" s="11"/>
     </row>
-    <row r="227" spans="1:9">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
         <v>217</v>
       </c>
@@ -6928,7 +6928,7 @@
       <c r="H227" s="11"/>
       <c r="I227" s="11"/>
     </row>
-    <row r="228" spans="1:9">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <v>218</v>
       </c>
@@ -6954,7 +6954,7 @@
       <c r="H228" s="11"/>
       <c r="I228" s="11"/>
     </row>
-    <row r="229" spans="1:9">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <v>219</v>
       </c>
@@ -6980,7 +6980,7 @@
       <c r="H229" s="11"/>
       <c r="I229" s="11"/>
     </row>
-    <row r="230" spans="1:9">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <v>220</v>
       </c>
@@ -7006,7 +7006,7 @@
       <c r="H230" s="11"/>
       <c r="I230" s="11"/>
     </row>
-    <row r="231" spans="1:9">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
         <v>221</v>
       </c>
@@ -7032,7 +7032,7 @@
       <c r="H231" s="11"/>
       <c r="I231" s="11"/>
     </row>
-    <row r="232" spans="1:9">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
         <v>222</v>
       </c>
@@ -7058,7 +7058,7 @@
       <c r="H232" s="11"/>
       <c r="I232" s="11"/>
     </row>
-    <row r="233" spans="1:9">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <v>223</v>
       </c>
@@ -7084,7 +7084,7 @@
       <c r="H233" s="11"/>
       <c r="I233" s="11"/>
     </row>
-    <row r="234" spans="1:9">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <v>224</v>
       </c>
@@ -7110,7 +7110,7 @@
       <c r="H234" s="11"/>
       <c r="I234" s="11"/>
     </row>
-    <row r="235" spans="1:9">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <v>225</v>
       </c>
@@ -7136,7 +7136,7 @@
       <c r="H235" s="11"/>
       <c r="I235" s="11"/>
     </row>
-    <row r="236" spans="1:9">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <v>226</v>
       </c>
@@ -7162,7 +7162,7 @@
       <c r="H236" s="11"/>
       <c r="I236" s="11"/>
     </row>
-    <row r="237" spans="1:9">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <v>227</v>
       </c>
@@ -7188,7 +7188,7 @@
       <c r="H237" s="11"/>
       <c r="I237" s="11"/>
     </row>
-    <row r="238" spans="1:9">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <v>228</v>
       </c>
@@ -7214,7 +7214,7 @@
       <c r="H238" s="11"/>
       <c r="I238" s="11"/>
     </row>
-    <row r="239" spans="1:9">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <v>229</v>
       </c>
@@ -7240,7 +7240,7 @@
       <c r="H239" s="11"/>
       <c r="I239" s="11"/>
     </row>
-    <row r="240" spans="1:9">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <v>230</v>
       </c>
@@ -7266,7 +7266,7 @@
       <c r="H240" s="11"/>
       <c r="I240" s="11"/>
     </row>
-    <row r="241" spans="1:9">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
         <v>231</v>
       </c>
@@ -7292,7 +7292,7 @@
       <c r="H241" s="11"/>
       <c r="I241" s="11"/>
     </row>
-    <row r="242" spans="1:9">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
         <v>232</v>
       </c>
@@ -7318,7 +7318,7 @@
       <c r="H242" s="11"/>
       <c r="I242" s="11"/>
     </row>
-    <row r="243" spans="1:9">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
         <v>233</v>
       </c>
@@ -7344,7 +7344,7 @@
       <c r="H243" s="11"/>
       <c r="I243" s="11"/>
     </row>
-    <row r="244" spans="1:9">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
         <v>234</v>
       </c>
@@ -7370,7 +7370,7 @@
       <c r="H244" s="11"/>
       <c r="I244" s="11"/>
     </row>
-    <row r="245" spans="1:9">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
         <v>235</v>
       </c>
@@ -7396,7 +7396,7 @@
       <c r="H245" s="11"/>
       <c r="I245" s="11"/>
     </row>
-    <row r="246" spans="1:9">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
         <v>236</v>
       </c>
@@ -7422,7 +7422,7 @@
       <c r="H246" s="11"/>
       <c r="I246" s="11"/>
     </row>
-    <row r="247" spans="1:9">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
         <v>237</v>
       </c>
@@ -7448,7 +7448,7 @@
       <c r="H247" s="11"/>
       <c r="I247" s="11"/>
     </row>
-    <row r="248" spans="1:9">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <v>238</v>
       </c>
@@ -7474,7 +7474,7 @@
       <c r="H248" s="11"/>
       <c r="I248" s="11"/>
     </row>
-    <row r="249" spans="1:9">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
         <v>239</v>
       </c>
@@ -7500,7 +7500,7 @@
       <c r="H249" s="11"/>
       <c r="I249" s="11"/>
     </row>
-    <row r="250" spans="1:9">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
         <v>240</v>
       </c>
@@ -7526,7 +7526,7 @@
       <c r="H250" s="11"/>
       <c r="I250" s="11"/>
     </row>
-    <row r="251" spans="1:9">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
         <v>241</v>
       </c>
@@ -7552,7 +7552,7 @@
       <c r="H251" s="11"/>
       <c r="I251" s="11"/>
     </row>
-    <row r="252" spans="1:9">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
         <v>242</v>
       </c>
@@ -7578,7 +7578,7 @@
       <c r="H252" s="11"/>
       <c r="I252" s="11"/>
     </row>
-    <row r="253" spans="1:9">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
         <v>243</v>
       </c>
@@ -7604,7 +7604,7 @@
       <c r="H253" s="11"/>
       <c r="I253" s="11"/>
     </row>
-    <row r="254" spans="1:9">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
         <v>244</v>
       </c>
@@ -7630,7 +7630,7 @@
       <c r="H254" s="11"/>
       <c r="I254" s="11"/>
     </row>
-    <row r="255" spans="1:9">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
         <v>245</v>
       </c>
@@ -7656,7 +7656,7 @@
       <c r="H255" s="11"/>
       <c r="I255" s="11"/>
     </row>
-    <row r="256" spans="1:9">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
         <v>246</v>
       </c>
@@ -7682,7 +7682,7 @@
       <c r="H256" s="11"/>
       <c r="I256" s="11"/>
     </row>
-    <row r="257" spans="1:9">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
         <v>247</v>
       </c>
@@ -7708,7 +7708,7 @@
       <c r="H257" s="11"/>
       <c r="I257" s="11"/>
     </row>
-    <row r="258" spans="1:9">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
         <v>248</v>
       </c>
@@ -7734,7 +7734,7 @@
       <c r="H258" s="11"/>
       <c r="I258" s="11"/>
     </row>
-    <row r="259" spans="1:9">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
         <v>249</v>
       </c>
@@ -7760,7 +7760,7 @@
       <c r="H259" s="11"/>
       <c r="I259" s="11"/>
     </row>
-    <row r="260" spans="1:9">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
         <v>250</v>
       </c>
@@ -7786,7 +7786,7 @@
       <c r="H260" s="11"/>
       <c r="I260" s="11"/>
     </row>
-    <row r="261" spans="1:9">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
         <v>251</v>
       </c>
@@ -7812,7 +7812,7 @@
       <c r="H261" s="11"/>
       <c r="I261" s="11"/>
     </row>
-    <row r="262" spans="1:9">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
         <v>252</v>
       </c>
@@ -7838,7 +7838,7 @@
       <c r="H262" s="11"/>
       <c r="I262" s="11"/>
     </row>
-    <row r="263" spans="1:9">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
         <v>253</v>
       </c>
@@ -7864,7 +7864,7 @@
       <c r="H263" s="11"/>
       <c r="I263" s="11"/>
     </row>
-    <row r="264" spans="1:9">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
         <v>254</v>
       </c>
@@ -7890,7 +7890,7 @@
       <c r="H264" s="11"/>
       <c r="I264" s="11"/>
     </row>
-    <row r="265" spans="1:9">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
         <v>255</v>
       </c>
@@ -7916,7 +7916,7 @@
       <c r="H265" s="11"/>
       <c r="I265" s="11"/>
     </row>
-    <row r="266" spans="1:9">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
         <v>256</v>
       </c>
@@ -7942,7 +7942,7 @@
       <c r="H266" s="11"/>
       <c r="I266" s="11"/>
     </row>
-    <row r="267" spans="1:9">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
         <v>257</v>
       </c>
@@ -7968,7 +7968,7 @@
       <c r="H267" s="11"/>
       <c r="I267" s="11"/>
     </row>
-    <row r="268" spans="1:9">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
         <v>258</v>
       </c>
@@ -7994,7 +7994,7 @@
       <c r="H268" s="11"/>
       <c r="I268" s="11"/>
     </row>
-    <row r="269" spans="1:9">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
         <v>259</v>
       </c>
@@ -8020,7 +8020,7 @@
       <c r="H269" s="11"/>
       <c r="I269" s="11"/>
     </row>
-    <row r="270" spans="1:9">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
         <v>260</v>
       </c>
@@ -8046,7 +8046,7 @@
       <c r="H270" s="11"/>
       <c r="I270" s="11"/>
     </row>
-    <row r="271" spans="1:9">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
         <v>261</v>
       </c>
@@ -8072,7 +8072,7 @@
       <c r="H271" s="11"/>
       <c r="I271" s="11"/>
     </row>
-    <row r="272" spans="1:9">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
         <v>262</v>
       </c>
@@ -8098,7 +8098,7 @@
       <c r="H272" s="11"/>
       <c r="I272" s="11"/>
     </row>
-    <row r="273" spans="1:10">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
         <v>263</v>
       </c>
@@ -8124,7 +8124,7 @@
       <c r="H273" s="11"/>
       <c r="I273" s="11"/>
     </row>
-    <row r="274" spans="1:10">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
         <v>264</v>
       </c>
@@ -8150,7 +8150,7 @@
       <c r="H274" s="11"/>
       <c r="I274" s="11"/>
     </row>
-    <row r="275" spans="1:10">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
         <v>265</v>
       </c>
@@ -8176,7 +8176,7 @@
       <c r="H275" s="11"/>
       <c r="I275" s="11"/>
     </row>
-    <row r="276" spans="1:10">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
         <v>266</v>
       </c>
@@ -8202,7 +8202,7 @@
       <c r="H276" s="11"/>
       <c r="I276" s="11"/>
     </row>
-    <row r="277" spans="1:10">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
         <v>267</v>
       </c>
@@ -8228,7 +8228,7 @@
       <c r="H277" s="11"/>
       <c r="I277" s="11"/>
     </row>
-    <row r="278" spans="1:10">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
         <v>268</v>
       </c>
@@ -8254,7 +8254,7 @@
       <c r="H278" s="11"/>
       <c r="I278" s="11"/>
     </row>
-    <row r="279" spans="1:10">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
         <v>269</v>
       </c>
@@ -8280,7 +8280,7 @@
       <c r="H279" s="11"/>
       <c r="I279" s="11"/>
     </row>
-    <row r="280" spans="1:10">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
         <v>270</v>
       </c>
@@ -8306,7 +8306,7 @@
       <c r="H280" s="11"/>
       <c r="I280" s="11"/>
     </row>
-    <row r="281" spans="1:10">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
         <v>271</v>
       </c>
@@ -8332,7 +8332,7 @@
       <c r="H281" s="11"/>
       <c r="I281" s="11"/>
     </row>
-    <row r="282" spans="1:10">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
         <v>272</v>
       </c>
@@ -8358,7 +8358,7 @@
       <c r="H282" s="11"/>
       <c r="I282" s="11"/>
     </row>
-    <row r="283" spans="1:10">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
         <v>273</v>
       </c>
@@ -8384,7 +8384,7 @@
       <c r="H283" s="11"/>
       <c r="I283" s="11"/>
     </row>
-    <row r="284" spans="1:10">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
         <v>274</v>
       </c>
@@ -8410,7 +8410,7 @@
       <c r="H284" s="11"/>
       <c r="I284" s="11"/>
     </row>
-    <row r="285" spans="1:10">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
         <v>275</v>
       </c>
@@ -8436,7 +8436,7 @@
       <c r="H285" s="11"/>
       <c r="I285" s="11"/>
     </row>
-    <row r="286" spans="1:10">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
         <v>276</v>
       </c>
@@ -8469,7 +8469,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="287" spans="1:10">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
         <v>277</v>
       </c>
@@ -8502,7 +8502,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="288" spans="1:10">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
         <v>278</v>
       </c>
@@ -8535,7 +8535,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="289" spans="1:10">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
         <v>279</v>
       </c>
@@ -8568,7 +8568,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="290" spans="1:10">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
         <v>280</v>
       </c>
@@ -8601,7 +8601,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="291" spans="1:10">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
         <v>281</v>
       </c>
@@ -8634,7 +8634,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="292" spans="1:10">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
         <v>282</v>
       </c>
@@ -8667,7 +8667,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="293" spans="1:10">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
         <v>283</v>
       </c>
@@ -8700,7 +8700,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="294" spans="1:10">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
         <v>284</v>
       </c>
@@ -8733,7 +8733,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="295" spans="1:10">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
         <v>285</v>
       </c>
@@ -8766,7 +8766,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="296" spans="1:10">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
         <v>286</v>
       </c>
@@ -8799,7 +8799,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="297" spans="1:10">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
         <v>287</v>
       </c>
@@ -8832,7 +8832,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="298" spans="1:10">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
         <v>288</v>
       </c>
@@ -8865,7 +8865,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="299" spans="1:10">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
         <v>289</v>
       </c>
@@ -8898,7 +8898,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="300" spans="1:10">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
         <v>290</v>
       </c>
@@ -8931,7 +8931,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="301" spans="1:10">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
         <v>291</v>
       </c>
@@ -8964,7 +8964,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="302" spans="1:10">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
         <v>292</v>
       </c>
@@ -8997,7 +8997,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="303" spans="1:10" s="1" customFormat="1">
+    <row r="303" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
         <v>293</v>
       </c>
@@ -9030,7 +9030,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="304" spans="1:10" s="1" customFormat="1">
+    <row r="304" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
         <v>294</v>
       </c>
@@ -9063,7 +9063,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="305" spans="1:10">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
         <v>295</v>
       </c>
@@ -9096,7 +9096,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="306" spans="1:10">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
         <v>296</v>
       </c>
@@ -9129,7 +9129,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="307" spans="1:10">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
         <v>297</v>
       </c>
@@ -9162,7 +9162,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="308" spans="1:10">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
         <v>298</v>
       </c>
@@ -9195,7 +9195,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="309" spans="1:10">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
         <v>298</v>
       </c>
@@ -9228,7 +9228,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="310" spans="1:10">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
         <v>299</v>
       </c>
@@ -9261,7 +9261,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="311" spans="1:10">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
         <v>300</v>
       </c>
@@ -9294,7 +9294,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="312" spans="1:10">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
         <v>301</v>
       </c>
@@ -9327,7 +9327,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="313" spans="1:10">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A313" s="1">
         <v>302</v>
       </c>
@@ -9360,7 +9360,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="314" spans="1:10">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A314" s="1">
         <v>303</v>
       </c>
@@ -9393,7 +9393,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="315" spans="1:10">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
         <v>304</v>
       </c>
@@ -9426,7 +9426,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="316" spans="1:10">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
         <v>305</v>
       </c>
@@ -9459,7 +9459,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="317" spans="1:10">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A317" s="1">
         <v>306</v>
       </c>
@@ -9492,7 +9492,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="318" spans="1:10">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
         <v>307</v>
       </c>
@@ -9525,7 +9525,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="319" spans="1:10">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A319" s="1">
         <v>308</v>
       </c>
@@ -9558,7 +9558,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="320" spans="1:10">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A320" s="1">
         <v>309</v>
       </c>
@@ -9591,7 +9591,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="321" spans="1:10">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A321" s="1">
         <v>310</v>
       </c>
@@ -9624,7 +9624,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="322" spans="1:10">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A322" s="1">
         <v>311</v>
       </c>
@@ -9657,7 +9657,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="323" spans="1:10">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A323" s="1">
         <v>312</v>
       </c>
@@ -9690,7 +9690,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="324" spans="1:10">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
         <v>313</v>
       </c>
@@ -9723,7 +9723,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="325" spans="1:10">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A325" s="1">
         <v>314</v>
       </c>
@@ -9756,7 +9756,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="326" spans="1:10">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A326" s="1">
         <v>315</v>
       </c>
@@ -9789,7 +9789,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="327" spans="1:10">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A327" s="1">
         <v>316</v>
       </c>
@@ -9822,7 +9822,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="328" spans="1:10">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A328" s="1">
         <v>318</v>
       </c>
@@ -9855,7 +9855,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="329" spans="1:10">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A329" s="1">
         <v>319</v>
       </c>
@@ -9888,7 +9888,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="330" spans="1:10">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A330" s="1">
         <v>320</v>
       </c>
@@ -9921,7 +9921,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="331" spans="1:10">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A331" s="1">
         <v>321</v>
       </c>
@@ -9954,7 +9954,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="332" spans="1:10">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A332" s="1">
         <v>322</v>
       </c>
@@ -9987,7 +9987,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="333" spans="1:10">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A333" s="1">
         <v>323</v>
       </c>
@@ -10020,7 +10020,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="334" spans="1:10">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A334" s="1">
         <v>324</v>
       </c>
@@ -10053,7 +10053,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="335" spans="1:10">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A335" s="1">
         <v>325</v>
       </c>
@@ -10086,7 +10086,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="336" spans="1:10">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A336" s="1">
         <v>326</v>
       </c>
@@ -10119,7 +10119,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="337" spans="1:10">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A337" s="1">
         <v>327</v>
       </c>
@@ -10152,7 +10152,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="338" spans="1:10">
+    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A338" s="1">
         <v>328</v>
       </c>
@@ -10185,7 +10185,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="339" spans="1:10">
+    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A339" s="1">
         <v>329</v>
       </c>
@@ -10218,7 +10218,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="340" spans="1:10">
+    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
         <v>330</v>
       </c>
@@ -10251,7 +10251,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="341" spans="1:10">
+    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
         <v>331</v>
       </c>
@@ -10284,7 +10284,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="342" spans="1:10">
+    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A342" s="1">
         <v>332</v>
       </c>
@@ -10317,7 +10317,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="343" spans="1:10">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A343" s="1">
         <v>333</v>
       </c>
@@ -10350,7 +10350,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="344" spans="1:10">
+    <row r="344" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A344" s="1">
         <v>334</v>
       </c>
@@ -10383,7 +10383,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="345" spans="1:10">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A345" s="1">
         <v>335</v>
       </c>
@@ -10416,7 +10416,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="346" spans="1:10">
+    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A346" s="1">
         <v>336</v>
       </c>
@@ -10449,7 +10449,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="347" spans="1:10" ht="15">
+    <row r="347" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A347" s="1">
         <v>337</v>
       </c>
@@ -10482,7 +10482,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="348" spans="1:10" ht="15">
+    <row r="348" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A348" s="1">
         <v>338</v>
       </c>
@@ -10534,13 +10534,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{797F1036-D41E-43A4-9E6E-CBBB62F3CD31}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="13.28515625" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -10554,7 +10554,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -10568,7 +10568,7 @@
         <v>234.67</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -10582,7 +10582,7 @@
         <v>161.15</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -10596,7 +10596,7 @@
         <v>157.61000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -10610,7 +10610,7 @@
         <v>347.95</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -10624,7 +10624,7 @@
         <v>393.57</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -10638,7 +10638,7 @@
         <v>19.87</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -10652,7 +10652,7 @@
         <v>19.57</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>86</v>
       </c>
@@ -10666,7 +10666,7 @@
         <v>19.86</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -10680,7 +10680,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -10705,7 +10705,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56220E0F-EC16-4A8C-9E04-C7F8849C4B4D}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
@@ -10713,7 +10713,7 @@
     <col min="5" max="5" width="30.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -10730,7 +10730,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -10747,7 +10747,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -10764,7 +10764,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -10782,7 +10782,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -10799,7 +10799,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -10816,7 +10816,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -10833,7 +10833,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -10851,7 +10851,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -10880,14 +10880,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83DAFC4B-C207-418A-8501-0E1EC9E673B7}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -10898,7 +10898,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -10909,7 +10909,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -10920,7 +10920,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -10931,7 +10931,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>86</v>
       </c>
@@ -10942,7 +10942,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -10953,7 +10953,7 @@
         <v>46631</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -10964,7 +10964,7 @@
         <v>48579</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -10975,7 +10975,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -10986,7 +10986,7 @@
         <v>46517</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -10997,7 +10997,7 @@
         <v>48579</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -11017,29 +11017,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100FB7AAE8C8816FD47B559A0CCF555AFF0" ma:contentTypeVersion="10" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5c9910934a78ddf693a6b708b52e9b37">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f95d585e-e7a7-414c-955d-38a47c8579bd" xmlns:ns3="33ab045e-9213-4eea-a9f2-a5b809105d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a9c61c95b4e11caed4e46447c2ca01e7" ns2:_="" ns3:_="">
     <xsd:import namespace="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
@@ -11242,16 +11219,64 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
+    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1361" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81B180EB-BEC6-40C2-A9D3-BE0EC3669F23}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="26148" yWindow="3612" windowWidth="17280" windowHeight="8928" firstSheet="1" activeTab="1" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="22932" yWindow="-144" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1361" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81B180EB-BEC6-40C2-A9D3-BE0EC3669F23}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-144" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView minimized="1" xWindow="26148" yWindow="3612" windowWidth="17280" windowHeight="8928" firstSheet="1" activeTab="1" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1361" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81B180EB-BEC6-40C2-A9D3-BE0EC3669F23}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="26148" yWindow="3612" windowWidth="17280" windowHeight="8928" firstSheet="1" activeTab="1" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1361" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81B180EB-BEC6-40C2-A9D3-BE0EC3669F23}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView minimized="1" xWindow="26148" yWindow="3372" windowWidth="17280" windowHeight="8928" firstSheet="1" activeTab="1" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1361" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81B180EB-BEC6-40C2-A9D3-BE0EC3669F23}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="26148" yWindow="3372" windowWidth="17280" windowHeight="8928" firstSheet="1" activeTab="1" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="22932" yWindow="-144" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1361" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81B180EB-BEC6-40C2-A9D3-BE0EC3669F23}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-144" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView minimized="1" xWindow="26148" yWindow="3372" windowWidth="17280" windowHeight="8928" firstSheet="1" activeTab="1" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -1250,7 +1250,7 @@
   <sheetData>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
+        <f ca="1">SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
         <v>338</v>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D11" s="14">
@@ -1320,7 +1320,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D12" s="14">
@@ -1346,7 +1346,7 @@
         <v>14</v>
       </c>
       <c r="C13" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D13" s="14">
@@ -1372,7 +1372,7 @@
         <v>15</v>
       </c>
       <c r="C14" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D14" s="14">
@@ -1398,7 +1398,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D15" s="14">
@@ -1424,7 +1424,7 @@
         <v>16</v>
       </c>
       <c r="C16" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D16" s="14">
@@ -1450,7 +1450,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D17" s="14">
@@ -1476,7 +1476,7 @@
         <v>15</v>
       </c>
       <c r="C18" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D18" s="14">
@@ -1502,7 +1502,7 @@
         <v>14</v>
       </c>
       <c r="C19" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D19" s="14">
@@ -1528,7 +1528,7 @@
         <v>17</v>
       </c>
       <c r="C20" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D20" s="14">
@@ -1554,7 +1554,7 @@
         <v>12</v>
       </c>
       <c r="C21" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D21" s="14">
@@ -1580,7 +1580,7 @@
         <v>17</v>
       </c>
       <c r="C22" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D22" s="14">
@@ -1606,7 +1606,7 @@
         <v>17</v>
       </c>
       <c r="C23" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D23" s="14">
@@ -1632,7 +1632,7 @@
         <v>17</v>
       </c>
       <c r="C24" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D24" s="14">
@@ -1658,7 +1658,7 @@
         <v>18</v>
       </c>
       <c r="C25" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D25" s="14">
@@ -1684,7 +1684,7 @@
         <v>15</v>
       </c>
       <c r="C26" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D26" s="14">
@@ -1710,7 +1710,7 @@
         <v>15</v>
       </c>
       <c r="C27" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D27" s="14">
@@ -1736,7 +1736,7 @@
         <v>18</v>
       </c>
       <c r="C28" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D28" s="14">
@@ -1762,7 +1762,7 @@
         <v>18</v>
       </c>
       <c r="C29" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D29" s="14">
@@ -1788,7 +1788,7 @@
         <v>18</v>
       </c>
       <c r="C30" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D30" s="14">
@@ -1814,7 +1814,7 @@
         <v>18</v>
       </c>
       <c r="C31" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D31" s="14">
@@ -1840,7 +1840,7 @@
         <v>16</v>
       </c>
       <c r="C32" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D32" s="14">
@@ -1866,7 +1866,7 @@
         <v>18</v>
       </c>
       <c r="C33" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D33" s="14">
@@ -1892,7 +1892,7 @@
         <v>18</v>
       </c>
       <c r="C34" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D34" s="14">
@@ -1918,7 +1918,7 @@
         <v>16</v>
       </c>
       <c r="C35" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D35" s="14">
@@ -1944,7 +1944,7 @@
         <v>15</v>
       </c>
       <c r="C36" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D36" s="14">
@@ -1970,7 +1970,7 @@
         <v>15</v>
       </c>
       <c r="C37" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D37" s="14">
@@ -1996,7 +1996,7 @@
         <v>15</v>
       </c>
       <c r="C38" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D38" s="14">
@@ -2022,7 +2022,7 @@
         <v>15</v>
       </c>
       <c r="C39" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D39" s="14">
@@ -2048,7 +2048,7 @@
         <v>17</v>
       </c>
       <c r="C40" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D40" s="14">
@@ -2074,7 +2074,7 @@
         <v>17</v>
       </c>
       <c r="C41" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D41" s="14">
@@ -2100,7 +2100,7 @@
         <v>15</v>
       </c>
       <c r="C42" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D42" s="14">
@@ -2126,7 +2126,7 @@
         <v>17</v>
       </c>
       <c r="C43" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D43" s="14">
@@ -2152,7 +2152,7 @@
         <v>17</v>
       </c>
       <c r="C44" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D44" s="14">
@@ -2178,7 +2178,7 @@
         <v>17</v>
       </c>
       <c r="C45" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D45" s="14">
@@ -2204,7 +2204,7 @@
         <v>17</v>
       </c>
       <c r="C46" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D46" s="14">
@@ -2230,7 +2230,7 @@
         <v>17</v>
       </c>
       <c r="C47" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D47" s="14">
@@ -2256,7 +2256,7 @@
         <v>17</v>
       </c>
       <c r="C48" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D48" s="14">
@@ -2282,7 +2282,7 @@
         <v>17</v>
       </c>
       <c r="C49" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D49" s="14">
@@ -2308,7 +2308,7 @@
         <v>15</v>
       </c>
       <c r="C50" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D50" s="14">
@@ -2334,7 +2334,7 @@
         <v>16</v>
       </c>
       <c r="C51" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D51" s="14">
@@ -2360,7 +2360,7 @@
         <v>16</v>
       </c>
       <c r="C52" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D52" s="14">
@@ -2386,7 +2386,7 @@
         <v>12</v>
       </c>
       <c r="C53" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D53" s="14">
@@ -2412,7 +2412,7 @@
         <v>12</v>
       </c>
       <c r="C54" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D54" s="14">
@@ -2438,7 +2438,7 @@
         <v>12</v>
       </c>
       <c r="C55" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D55" s="14">
@@ -2464,7 +2464,7 @@
         <v>12</v>
       </c>
       <c r="C56" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D56" s="14">
@@ -2490,7 +2490,7 @@
         <v>15</v>
       </c>
       <c r="C57" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D57" s="14">
@@ -2516,7 +2516,7 @@
         <v>12</v>
       </c>
       <c r="C58" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D58" s="14">
@@ -2542,7 +2542,7 @@
         <v>12</v>
       </c>
       <c r="C59" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D59" s="14">
@@ -2568,7 +2568,7 @@
         <v>12</v>
       </c>
       <c r="C60" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D60" s="14">
@@ -2594,7 +2594,7 @@
         <v>12</v>
       </c>
       <c r="C61" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D61" s="14">
@@ -2620,7 +2620,7 @@
         <v>17</v>
       </c>
       <c r="C62" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D62" s="14">
@@ -2646,7 +2646,7 @@
         <v>17</v>
       </c>
       <c r="C63" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D63" s="14">
@@ -2672,7 +2672,7 @@
         <v>17</v>
       </c>
       <c r="C64" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D64" s="14">
@@ -2698,7 +2698,7 @@
         <v>17</v>
       </c>
       <c r="C65" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D65" s="14">
@@ -2724,7 +2724,7 @@
         <v>17</v>
       </c>
       <c r="C66" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D66" s="14">
@@ -2750,7 +2750,7 @@
         <v>17</v>
       </c>
       <c r="C67" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D67" s="14">
@@ -2776,7 +2776,7 @@
         <v>17</v>
       </c>
       <c r="C68" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D68" s="14">
@@ -2802,7 +2802,7 @@
         <v>17</v>
       </c>
       <c r="C69" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D69" s="14">
@@ -2828,7 +2828,7 @@
         <v>18</v>
       </c>
       <c r="C70" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D70" s="14">
@@ -2854,7 +2854,7 @@
         <v>17</v>
       </c>
       <c r="C71" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D71" s="14">
@@ -2880,7 +2880,7 @@
         <v>17</v>
       </c>
       <c r="C72" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D72" s="14">
@@ -2906,7 +2906,7 @@
         <v>17</v>
       </c>
       <c r="C73" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D73" s="14">
@@ -2932,7 +2932,7 @@
         <v>16</v>
       </c>
       <c r="C74" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D74" s="14">
@@ -2958,7 +2958,7 @@
         <v>12</v>
       </c>
       <c r="C75" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D75" s="14">
@@ -2984,7 +2984,7 @@
         <v>17</v>
       </c>
       <c r="C76" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D76" s="14">
@@ -3010,7 +3010,7 @@
         <v>17</v>
       </c>
       <c r="C77" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D77" s="14">
@@ -3036,7 +3036,7 @@
         <v>17</v>
       </c>
       <c r="C78" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D78" s="14">
@@ -3062,7 +3062,7 @@
         <v>14</v>
       </c>
       <c r="C79" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D79" s="14">
@@ -3088,7 +3088,7 @@
         <v>14</v>
       </c>
       <c r="C80" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D80" s="14">
@@ -3114,7 +3114,7 @@
         <v>16</v>
       </c>
       <c r="C81" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D81" s="14">
@@ -3140,7 +3140,7 @@
         <v>14</v>
       </c>
       <c r="C82" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D82" s="14">
@@ -3166,7 +3166,7 @@
         <v>12</v>
       </c>
       <c r="C83" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D83" s="14">
@@ -3192,7 +3192,7 @@
         <v>15</v>
       </c>
       <c r="C84" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D84" s="14">
@@ -3218,7 +3218,7 @@
         <v>12</v>
       </c>
       <c r="C85" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D85" s="14">
@@ -3244,7 +3244,7 @@
         <v>12</v>
       </c>
       <c r="C86" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D86" s="14">
@@ -3270,7 +3270,7 @@
         <v>16</v>
       </c>
       <c r="C87" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D87" s="14">
@@ -3296,7 +3296,7 @@
         <v>15</v>
       </c>
       <c r="C88" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D88" s="14">
@@ -3322,7 +3322,7 @@
         <v>15</v>
       </c>
       <c r="C89" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D89" s="14">
@@ -3348,7 +3348,7 @@
         <v>15</v>
       </c>
       <c r="C90" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D90" s="14">
@@ -3374,7 +3374,7 @@
         <v>15</v>
       </c>
       <c r="C91" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D91" s="14">
@@ -3400,7 +3400,7 @@
         <v>15</v>
       </c>
       <c r="C92" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D92" s="14">
@@ -3426,7 +3426,7 @@
         <v>16</v>
       </c>
       <c r="C93" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D93" s="14">
@@ -3452,7 +3452,7 @@
         <v>15</v>
       </c>
       <c r="C94" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D94" s="14">
@@ -3478,7 +3478,7 @@
         <v>15</v>
       </c>
       <c r="C95" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D95" s="14">
@@ -3504,7 +3504,7 @@
         <v>15</v>
       </c>
       <c r="C96" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D96" s="14">
@@ -3530,7 +3530,7 @@
         <v>15</v>
       </c>
       <c r="C97" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D97" s="14">
@@ -3556,7 +3556,7 @@
         <v>15</v>
       </c>
       <c r="C98" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D98" s="14">
@@ -3582,7 +3582,7 @@
         <v>15</v>
       </c>
       <c r="C99" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D99" s="14">
@@ -3608,7 +3608,7 @@
         <v>15</v>
       </c>
       <c r="C100" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D100" s="14">
@@ -3634,7 +3634,7 @@
         <v>14</v>
       </c>
       <c r="C101" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D101" s="14">
@@ -3660,7 +3660,7 @@
         <v>14</v>
       </c>
       <c r="C102" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D102" s="14">
@@ -3686,7 +3686,7 @@
         <v>16</v>
       </c>
       <c r="C103" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D103" s="14">
@@ -3712,7 +3712,7 @@
         <v>15</v>
       </c>
       <c r="C104" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D104" s="14">
@@ -3738,7 +3738,7 @@
         <v>15</v>
       </c>
       <c r="C105" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D105" s="14">
@@ -3764,7 +3764,7 @@
         <v>12</v>
       </c>
       <c r="C106" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D106" s="14">
@@ -3790,7 +3790,7 @@
         <v>12</v>
       </c>
       <c r="C107" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D107" s="14">
@@ -3816,7 +3816,7 @@
         <v>15</v>
       </c>
       <c r="C108" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D108" s="14">
@@ -3842,7 +3842,7 @@
         <v>15</v>
       </c>
       <c r="C109" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D109" s="14">
@@ -3868,7 +3868,7 @@
         <v>15</v>
       </c>
       <c r="C110" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D110" s="14">
@@ -3894,7 +3894,7 @@
         <v>15</v>
       </c>
       <c r="C111" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D111" s="14">
@@ -3920,7 +3920,7 @@
         <v>12</v>
       </c>
       <c r="C112" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D112" s="14">
@@ -3946,7 +3946,7 @@
         <v>15</v>
       </c>
       <c r="C113" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D113" s="14">
@@ -3972,7 +3972,7 @@
         <v>15</v>
       </c>
       <c r="C114" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D114" s="14">
@@ -3998,7 +3998,7 @@
         <v>12</v>
       </c>
       <c r="C115" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D115" s="14">
@@ -4024,7 +4024,7 @@
         <v>12</v>
       </c>
       <c r="C116" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D116" s="14">
@@ -4050,7 +4050,7 @@
         <v>12</v>
       </c>
       <c r="C117" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D117" s="14">
@@ -4076,7 +4076,7 @@
         <v>17</v>
       </c>
       <c r="C118" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D118" s="14">
@@ -4102,7 +4102,7 @@
         <v>14</v>
       </c>
       <c r="C119" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D119" s="14">
@@ -4128,7 +4128,7 @@
         <v>17</v>
       </c>
       <c r="C120" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D120" s="14">
@@ -4154,7 +4154,7 @@
         <v>10</v>
       </c>
       <c r="C121" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D121" s="14">
@@ -4180,7 +4180,7 @@
         <v>18</v>
       </c>
       <c r="C122" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D122" s="14">
@@ -4206,7 +4206,7 @@
         <v>18</v>
       </c>
       <c r="C123" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D123" s="14">
@@ -4232,7 +4232,7 @@
         <v>14</v>
       </c>
       <c r="C124" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
       <c r="D124" s="14">
@@ -4258,7 +4258,7 @@
         <v>12</v>
       </c>
       <c r="C125" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D125" s="14">
@@ -4284,7 +4284,7 @@
         <v>12</v>
       </c>
       <c r="C126" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D126" s="14">
@@ -4310,7 +4310,7 @@
         <v>12</v>
       </c>
       <c r="C127" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D127" s="14">
@@ -4336,7 +4336,7 @@
         <v>12</v>
       </c>
       <c r="C128" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D128" s="14">
@@ -4362,7 +4362,7 @@
         <v>12</v>
       </c>
       <c r="C129" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D129" s="14">
@@ -4388,7 +4388,7 @@
         <v>12</v>
       </c>
       <c r="C130" s="13" t="str">
-        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <f ca="1">IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
       <c r="D130" s="14">
@@ -4414,7 +4414,7 @@
         <v>12</v>
       </c>
       <c r="C131" s="13" t="str">
-        <f>IF(OR(BD_GEN_